--- a/sample-list.xlsx
+++ b/sample-list.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.14.76\Lens Design\11. 문서\생산납기\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77865846-3A7E-43E4-A361-47DA9377C6EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20130" windowHeight="10815"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="502" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="742" uniqueCount="190">
   <si>
     <t>국가</t>
   </si>
@@ -562,17 +561,191 @@
   </si>
   <si>
     <t>제안렌즈</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>일본</t>
+  </si>
+  <si>
+    <t>PIA</t>
+  </si>
+  <si>
+    <t>남상규</t>
+  </si>
+  <si>
+    <t>Silver Wolf</t>
+  </si>
+  <si>
+    <t>정세희</t>
+  </si>
+  <si>
+    <t>Charmy Cat</t>
+  </si>
+  <si>
+    <t>국내</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>렌즈미</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>김우현</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>M</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>포멜로 브라운</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>포멜로 그레이</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>포멜로 틸그레이</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>칼립소 BE</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>칼립소 CH</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>칼립소 GR</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>키비 코지블랙</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">키비 블랙 </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">키비 초코 </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> Winsome Brown 1D -0.75</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> Winsome Brown 1D -1.75</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> Winsome Brown 1D -3.00</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> Winsome Brown 1D -3.50</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> Winsome Brown 1D -3.75</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> Winsome Brown 1D -4.00</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> Winsome Brown 1D -4.50</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> Winsome Brown 1D -5.50</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> Winsome Brown 1D -5.75</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> Winsome Brown 1M -0.75</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> Winsome Brown 1M -1.75</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> Winsome Brown 1M -3.00</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> Winsome Brown 1M -3.50</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> Winsome Brown 1M -3.75</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> Winsome Brown 1M -4.00</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> Winsome Brown 1M -4.50</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> Winsome Brown 1M -5.50</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> Winsome Brown 1M -5.75</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>중동</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Menicon</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>이상윤</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1D</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LIMIMOON 헤이즈 초코</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LIMIMOON 미스트 그레이</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Gleam Edge 볼드 브라운</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Gleam Edge 볼드 그레이</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.0_ "/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -598,6 +771,14 @@
       <sz val="11"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -648,7 +829,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -680,11 +861,36 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="3">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -698,7 +904,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Sheet2"/>
@@ -994,8 +1200,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AB42"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:AB75"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.25" style="2" customWidth="1"/>
@@ -2507,6 +2713,9 @@
       <c r="Y20" s="2" t="s">
         <v>67</v>
       </c>
+      <c r="Z20" s="4">
+        <v>46092</v>
+      </c>
       <c r="AB20" s="2" t="s">
         <v>97</v>
       </c>
@@ -3102,6 +3311,9 @@
       <c r="X29" s="2" t="s">
         <v>53</v>
       </c>
+      <c r="Y29" s="2" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="30" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
@@ -3782,6 +3994,21 @@
       <c r="O39" s="4">
         <v>46078</v>
       </c>
+      <c r="P39" s="4">
+        <v>46084</v>
+      </c>
+      <c r="Q39" s="4">
+        <v>46089</v>
+      </c>
+      <c r="R39" s="4">
+        <v>46090</v>
+      </c>
+      <c r="S39" s="4">
+        <v>46092</v>
+      </c>
+      <c r="T39" s="4">
+        <v>46092</v>
+      </c>
       <c r="V39" s="2" t="s">
         <v>134</v>
       </c>
@@ -3792,7 +4019,7 @@
         <v>100</v>
       </c>
       <c r="Y39" s="2" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
     </row>
     <row r="40" spans="1:25" x14ac:dyDescent="0.3">
@@ -3956,6 +4183,12 @@
       <c r="P42" s="4">
         <v>46079</v>
       </c>
+      <c r="Q42" s="4">
+        <v>46086</v>
+      </c>
+      <c r="R42" s="4">
+        <v>46087</v>
+      </c>
       <c r="V42" s="2" t="s">
         <v>66</v>
       </c>
@@ -3969,67 +4202,1454 @@
         <v>143</v>
       </c>
     </row>
+    <row r="43" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A43" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F43" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G43" s="7">
+        <v>15</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I43" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="J43" s="2">
+        <v>1</v>
+      </c>
+      <c r="K43" s="2">
+        <v>2</v>
+      </c>
+      <c r="L43" s="4">
+        <v>46055</v>
+      </c>
+      <c r="M43" s="4">
+        <v>46085</v>
+      </c>
+      <c r="N43" s="6"/>
+      <c r="O43" s="6"/>
+      <c r="P43" s="4">
+        <v>46085</v>
+      </c>
+      <c r="Q43" s="4">
+        <v>46093</v>
+      </c>
+      <c r="R43" s="4">
+        <v>46094</v>
+      </c>
+      <c r="S43" s="4">
+        <v>46094</v>
+      </c>
+      <c r="T43" s="4">
+        <v>46094</v>
+      </c>
+      <c r="V43" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="W43" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X43" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="Y43" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="44" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A44" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F44" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G44" s="7">
+        <v>15</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I44" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="J44" s="2">
+        <v>1</v>
+      </c>
+      <c r="K44" s="2">
+        <v>2</v>
+      </c>
+      <c r="L44" s="4">
+        <v>46055</v>
+      </c>
+      <c r="M44" s="4">
+        <v>46085</v>
+      </c>
+      <c r="N44" s="6"/>
+      <c r="O44" s="6"/>
+      <c r="P44" s="4">
+        <v>46085</v>
+      </c>
+      <c r="Q44" s="4">
+        <v>46093</v>
+      </c>
+      <c r="R44" s="4">
+        <v>46094</v>
+      </c>
+      <c r="S44" s="4">
+        <v>46094</v>
+      </c>
+      <c r="T44" s="4">
+        <v>46094</v>
+      </c>
+      <c r="V44" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="W44" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X44" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="Y44" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="45" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A45" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="F45" s="3">
+        <v>0.45</v>
+      </c>
+      <c r="G45" s="7">
+        <v>14.2</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I45" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="J45" s="2">
+        <v>1</v>
+      </c>
+      <c r="K45" s="2">
+        <v>1</v>
+      </c>
+      <c r="L45" s="4">
+        <v>46090</v>
+      </c>
+      <c r="N45" s="4">
+        <v>46085</v>
+      </c>
+      <c r="P45" s="4">
+        <v>46087</v>
+      </c>
+    </row>
+    <row r="46" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A46" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="F46" s="3">
+        <v>0.45</v>
+      </c>
+      <c r="G46" s="7">
+        <v>14.2</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I46" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="J46" s="2">
+        <v>1</v>
+      </c>
+      <c r="K46" s="2">
+        <v>1</v>
+      </c>
+      <c r="L46" s="4">
+        <v>46090</v>
+      </c>
+      <c r="N46" s="4">
+        <v>46085</v>
+      </c>
+      <c r="P46" s="4">
+        <v>46087</v>
+      </c>
+    </row>
+    <row r="47" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A47" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="F47" s="3">
+        <v>0.45</v>
+      </c>
+      <c r="G47" s="7">
+        <v>14.2</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I47" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="J47" s="2">
+        <v>1</v>
+      </c>
+      <c r="K47" s="2">
+        <v>1</v>
+      </c>
+      <c r="L47" s="4">
+        <v>46090</v>
+      </c>
+      <c r="N47" s="4">
+        <v>46085</v>
+      </c>
+      <c r="P47" s="4">
+        <v>46087</v>
+      </c>
+    </row>
+    <row r="48" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A48" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="F48" s="3">
+        <v>0.45</v>
+      </c>
+      <c r="G48" s="7">
+        <v>14.2</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I48" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="J48" s="2">
+        <v>1</v>
+      </c>
+      <c r="K48" s="2">
+        <v>1</v>
+      </c>
+      <c r="L48" s="4">
+        <v>46090</v>
+      </c>
+      <c r="N48" s="4">
+        <v>46085</v>
+      </c>
+      <c r="P48" s="4">
+        <v>46087</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A49" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="F49" s="3">
+        <v>0.45</v>
+      </c>
+      <c r="G49" s="7">
+        <v>14.2</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I49" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="J49" s="2">
+        <v>1</v>
+      </c>
+      <c r="K49" s="2">
+        <v>1</v>
+      </c>
+      <c r="L49" s="4">
+        <v>46090</v>
+      </c>
+      <c r="N49" s="4">
+        <v>46085</v>
+      </c>
+      <c r="P49" s="4">
+        <v>46087</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A50" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="F50" s="3">
+        <v>0.45</v>
+      </c>
+      <c r="G50" s="7">
+        <v>14.2</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I50" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="J50" s="2">
+        <v>1</v>
+      </c>
+      <c r="K50" s="2">
+        <v>1</v>
+      </c>
+      <c r="L50" s="4">
+        <v>46090</v>
+      </c>
+      <c r="N50" s="4">
+        <v>46085</v>
+      </c>
+      <c r="P50" s="4">
+        <v>46087</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A51" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="F51" s="3">
+        <v>0.45</v>
+      </c>
+      <c r="G51" s="7">
+        <v>14.2</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I51" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="J51" s="2">
+        <v>1</v>
+      </c>
+      <c r="K51" s="2">
+        <v>1</v>
+      </c>
+      <c r="L51" s="4">
+        <v>46090</v>
+      </c>
+      <c r="N51" s="4">
+        <v>46085</v>
+      </c>
+      <c r="P51" s="4">
+        <v>46087</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A52" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="F52" s="3">
+        <v>0.45</v>
+      </c>
+      <c r="G52" s="7">
+        <v>14.2</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I52" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="J52" s="2">
+        <v>1</v>
+      </c>
+      <c r="K52" s="2">
+        <v>1</v>
+      </c>
+      <c r="L52" s="4">
+        <v>46090</v>
+      </c>
+      <c r="N52" s="4">
+        <v>46085</v>
+      </c>
+      <c r="P52" s="4">
+        <v>46087</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A53" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="F53" s="3">
+        <v>0.45</v>
+      </c>
+      <c r="G53" s="7">
+        <v>14.2</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I53" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="J53" s="2">
+        <v>1</v>
+      </c>
+      <c r="K53" s="2">
+        <v>1</v>
+      </c>
+      <c r="L53" s="4">
+        <v>46090</v>
+      </c>
+      <c r="N53" s="4">
+        <v>46085</v>
+      </c>
+      <c r="P53" s="4">
+        <v>46087</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A54" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="F54" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G54" s="7">
+        <v>14.2</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I54" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="J54" s="2">
+        <v>1</v>
+      </c>
+      <c r="K54" s="2">
+        <v>1</v>
+      </c>
+      <c r="L54" s="4">
+        <v>46086</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A55" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="F55" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G55" s="7">
+        <v>14.2</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I55" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="J55" s="2">
+        <v>1</v>
+      </c>
+      <c r="K55" s="2">
+        <v>1</v>
+      </c>
+      <c r="L55" s="4">
+        <v>46086</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A56" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F56" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G56" s="7">
+        <v>14.2</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I56" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="J56" s="2">
+        <v>1</v>
+      </c>
+      <c r="K56" s="2">
+        <v>1</v>
+      </c>
+      <c r="L56" s="4">
+        <v>46086</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A57" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F57" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G57" s="7">
+        <v>14.2</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I57" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="J57" s="2">
+        <v>1</v>
+      </c>
+      <c r="K57" s="2">
+        <v>1</v>
+      </c>
+      <c r="L57" s="4">
+        <v>46086</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A58" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F58" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G58" s="7">
+        <v>14.2</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I58" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="J58" s="2">
+        <v>1</v>
+      </c>
+      <c r="K58" s="2">
+        <v>1</v>
+      </c>
+      <c r="L58" s="4">
+        <v>46086</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A59" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F59" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G59" s="7">
+        <v>14.2</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I59" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="J59" s="2">
+        <v>1</v>
+      </c>
+      <c r="K59" s="2">
+        <v>1</v>
+      </c>
+      <c r="L59" s="4">
+        <v>46086</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A60" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F60" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G60" s="7">
+        <v>14.2</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I60" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="J60" s="2">
+        <v>1</v>
+      </c>
+      <c r="K60" s="2">
+        <v>1</v>
+      </c>
+      <c r="L60" s="4">
+        <v>46086</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A61" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F61" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G61" s="7">
+        <v>14.2</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I61" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="J61" s="2">
+        <v>1</v>
+      </c>
+      <c r="K61" s="2">
+        <v>1</v>
+      </c>
+      <c r="L61" s="4">
+        <v>46086</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A62" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F62" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G62" s="7">
+        <v>14.2</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I62" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="J62" s="2">
+        <v>1</v>
+      </c>
+      <c r="K62" s="2">
+        <v>1</v>
+      </c>
+      <c r="L62" s="4">
+        <v>46086</v>
+      </c>
+    </row>
+    <row r="63" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A63" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F63" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G63" s="7">
+        <v>14.2</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I63" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="J63" s="2">
+        <v>1</v>
+      </c>
+      <c r="K63" s="2">
+        <v>1</v>
+      </c>
+      <c r="L63" s="4">
+        <v>46086</v>
+      </c>
+    </row>
+    <row r="64" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A64" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F64" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G64" s="7">
+        <v>14.2</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I64" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="J64" s="2">
+        <v>1</v>
+      </c>
+      <c r="K64" s="2">
+        <v>1</v>
+      </c>
+      <c r="L64" s="4">
+        <v>46086</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A65" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F65" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G65" s="7">
+        <v>14.2</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I65" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="J65" s="2">
+        <v>1</v>
+      </c>
+      <c r="K65" s="2">
+        <v>1</v>
+      </c>
+      <c r="L65" s="4">
+        <v>46086</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A66" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F66" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G66" s="7">
+        <v>14.2</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I66" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="J66" s="2">
+        <v>1</v>
+      </c>
+      <c r="K66" s="2">
+        <v>1</v>
+      </c>
+      <c r="L66" s="4">
+        <v>46086</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A67" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F67" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G67" s="7">
+        <v>14.2</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I67" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="J67" s="2">
+        <v>1</v>
+      </c>
+      <c r="K67" s="2">
+        <v>1</v>
+      </c>
+      <c r="L67" s="4">
+        <v>46086</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A68" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F68" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G68" s="7">
+        <v>14.2</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I68" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="J68" s="2">
+        <v>1</v>
+      </c>
+      <c r="K68" s="2">
+        <v>1</v>
+      </c>
+      <c r="L68" s="4">
+        <v>46086</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A69" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F69" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G69" s="7">
+        <v>14.2</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I69" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="J69" s="2">
+        <v>1</v>
+      </c>
+      <c r="K69" s="2">
+        <v>1</v>
+      </c>
+      <c r="L69" s="4">
+        <v>46086</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A70" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F70" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G70" s="7">
+        <v>14.2</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I70" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="J70" s="2">
+        <v>1</v>
+      </c>
+      <c r="K70" s="2">
+        <v>1</v>
+      </c>
+      <c r="L70" s="4">
+        <v>46086</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A71" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F71" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G71" s="7">
+        <v>14.2</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I71" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="J71" s="2">
+        <v>1</v>
+      </c>
+      <c r="K71" s="2">
+        <v>1</v>
+      </c>
+      <c r="L71" s="4">
+        <v>46086</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A72" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F72" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G72" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I72" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="J72" s="2">
+        <v>1</v>
+      </c>
+      <c r="K72" s="2">
+        <v>1</v>
+      </c>
+      <c r="L72" s="4">
+        <v>46092</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A73" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F73" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G73" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I73" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="J73" s="2">
+        <v>1</v>
+      </c>
+      <c r="K73" s="2">
+        <v>1</v>
+      </c>
+      <c r="L73" s="4">
+        <v>46092</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A74" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F74" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G74" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I74" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="J74" s="2">
+        <v>1</v>
+      </c>
+      <c r="K74" s="2">
+        <v>1</v>
+      </c>
+      <c r="L74" s="4">
+        <v>46092</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A75" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F75" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G75" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I75" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="J75" s="2">
+        <v>1</v>
+      </c>
+      <c r="K75" s="2">
+        <v>1</v>
+      </c>
+      <c r="L75" s="4">
+        <v>46092</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="V1:V38" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="V1:V38"/>
   <phoneticPr fontId="2" type="noConversion"/>
+  <conditionalFormatting sqref="I51:I53">
+    <cfRule type="expression" dxfId="2" priority="3" stopIfTrue="1">
+      <formula>$E3099:$E1048568="sub"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I62 I71">
+    <cfRule type="expression" dxfId="1" priority="2" stopIfTrue="1">
+      <formula>$E3102:$E1048571="sub"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I54:I61 I63:I70">
+    <cfRule type="expression" dxfId="0" priority="1" stopIfTrue="1">
+      <formula>$E3095:$E1048564="sub"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="9">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000000000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>Sheet2!$F$2:$F$4</xm:f>
           </x14:formula1>
-          <xm:sqref>W2:W37 W39:W1048576</xm:sqref>
+          <xm:sqref>W2:W37 Y39 W39:W1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000001000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>Sheet2!$G$2:$G$5</xm:f>
           </x14:formula1>
           <xm:sqref>X2:X37 X39:X1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000002000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>Sheet2!$E$2:$E$4</xm:f>
           </x14:formula1>
           <xm:sqref>H2:H37 H39:H1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000003000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>Sheet2!$D$2:$D$5</xm:f>
           </x14:formula1>
           <xm:sqref>G2:G37 G39:G1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000004000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>Sheet2!$C$2:$C$5</xm:f>
           </x14:formula1>
           <xm:sqref>F2:F37 F39:F1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000005000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>Sheet2!$B$2:$B$3</xm:f>
           </x14:formula1>
           <xm:sqref>E2:E37 E39:E1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000006000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>Sheet2!$A$2:$A$4</xm:f>
           </x14:formula1>
           <xm:sqref>D2:D37 D39:D1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000008000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'[복사본 sample-list.xlsx]Sheet2'!#REF!</xm:f>
           </x14:formula1>
           <xm:sqref>D38:H38 W38:X38</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{5AA6FBA5-1020-4249-B16C-255F826E1A33}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>Sheet2!$H$2:$H$7</xm:f>
           </x14:formula1>
-          <xm:sqref>Y2:Y1048576</xm:sqref>
+          <xm:sqref>Y2:Y38 Y40:Y1048576</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -4038,7 +5658,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>

--- a/sample-list.xlsx
+++ b/sample-list.xlsx
@@ -19,14 +19,14 @@
     <externalReference r:id="rId3"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$V$1:$V$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$V$1:$V$41</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="742" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="775" uniqueCount="194">
   <si>
     <t>국가</t>
   </si>
@@ -735,6 +735,22 @@
   </si>
   <si>
     <t>Gleam Edge 볼드 그레이</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SY9-Aurora B</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SY10-C 5th</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>파우더</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SY2</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1201,7 +1217,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AB75"/>
+  <dimension ref="A1:AB78"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.25" style="2" customWidth="1"/>
@@ -2675,7 +2691,7 @@
         <v>10</v>
       </c>
       <c r="L20" s="4">
-        <v>45621</v>
+        <v>45644</v>
       </c>
       <c r="M20" s="10">
         <v>46063</v>
@@ -2712,9 +2728,6 @@
       </c>
       <c r="Y20" s="2" t="s">
         <v>67</v>
-      </c>
-      <c r="Z20" s="4">
-        <v>46092</v>
       </c>
       <c r="AB20" s="2" t="s">
         <v>97</v>
@@ -2755,7 +2768,7 @@
         <v>10</v>
       </c>
       <c r="L21" s="4">
-        <v>45621</v>
+        <v>45644</v>
       </c>
       <c r="M21" s="10">
         <v>46063</v>
@@ -2792,6 +2805,9 @@
       </c>
       <c r="Y21" s="2" t="s">
         <v>67</v>
+      </c>
+      <c r="Z21" s="4">
+        <v>46092</v>
       </c>
       <c r="AB21" s="2" t="s">
         <v>97</v>
@@ -2823,41 +2839,55 @@
         <v>28</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>107</v>
+        <v>190</v>
       </c>
       <c r="J22" s="2">
         <v>1</v>
       </c>
       <c r="K22" s="2">
-        <v>1</v>
-      </c>
-      <c r="L22" s="6"/>
-      <c r="M22" s="6"/>
-      <c r="N22" s="6"/>
-      <c r="O22" s="6"/>
-      <c r="P22" s="10">
-        <v>46065</v>
-      </c>
-      <c r="Q22" s="10">
-        <v>46075</v>
+        <v>7</v>
+      </c>
+      <c r="L22" s="4">
+        <v>45644</v>
+      </c>
+      <c r="M22" s="10">
+        <v>46063</v>
+      </c>
+      <c r="N22" s="10">
+        <v>45940</v>
+      </c>
+      <c r="O22" s="10">
+        <v>45940</v>
+      </c>
+      <c r="P22" s="4">
+        <v>45959</v>
+      </c>
+      <c r="Q22" s="4">
+        <v>45963</v>
       </c>
       <c r="R22" s="4">
-        <v>46076</v>
+        <v>45965</v>
       </c>
       <c r="S22" s="4">
-        <v>46077</v>
+        <v>45966</v>
       </c>
       <c r="T22" s="4">
-        <v>46077</v>
+        <v>45966</v>
       </c>
       <c r="V22" s="2" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="W22" s="2" t="s">
-        <v>29</v>
+        <v>92</v>
       </c>
       <c r="X22" s="2" t="s">
         <v>53</v>
+      </c>
+      <c r="Y22" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z22" s="4">
+        <v>46065</v>
       </c>
     </row>
     <row r="23" spans="1:28" x14ac:dyDescent="0.3">
@@ -2886,41 +2916,55 @@
         <v>28</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>108</v>
+        <v>191</v>
       </c>
       <c r="J23" s="2">
         <v>1</v>
       </c>
       <c r="K23" s="2">
-        <v>1</v>
-      </c>
-      <c r="L23" s="6"/>
-      <c r="M23" s="6"/>
-      <c r="N23" s="6"/>
-      <c r="O23" s="6"/>
+        <v>5</v>
+      </c>
+      <c r="L23" s="4">
+        <v>45800</v>
+      </c>
+      <c r="M23" s="10">
+        <v>45999</v>
+      </c>
+      <c r="N23" s="10">
+        <v>46000</v>
+      </c>
+      <c r="O23" s="10">
+        <v>46001</v>
+      </c>
       <c r="P23" s="10">
-        <v>46065</v>
-      </c>
-      <c r="Q23" s="10">
-        <v>46075</v>
+        <v>46011</v>
+      </c>
+      <c r="Q23" s="4">
+        <v>46025</v>
       </c>
       <c r="R23" s="4">
-        <v>46076</v>
+        <v>46034</v>
       </c>
       <c r="S23" s="4">
-        <v>46077</v>
+        <v>46035</v>
       </c>
       <c r="T23" s="4">
-        <v>46077</v>
+        <v>46035</v>
       </c>
       <c r="V23" s="2" t="s">
         <v>76</v>
       </c>
       <c r="W23" s="2" t="s">
-        <v>29</v>
+        <v>92</v>
       </c>
       <c r="X23" s="2" t="s">
         <v>53</v>
+      </c>
+      <c r="Y23" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z23" s="4">
+        <v>46065</v>
       </c>
     </row>
     <row r="24" spans="1:28" x14ac:dyDescent="0.3">
@@ -2946,44 +2990,58 @@
         <v>14.5</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>28</v>
+        <v>192</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>109</v>
+        <v>193</v>
       </c>
       <c r="J24" s="2">
         <v>1</v>
       </c>
       <c r="K24" s="2">
-        <v>1</v>
-      </c>
-      <c r="L24" s="6"/>
-      <c r="M24" s="6"/>
-      <c r="N24" s="6"/>
-      <c r="O24" s="6"/>
+        <v>2</v>
+      </c>
+      <c r="L24" s="4">
+        <v>45302</v>
+      </c>
+      <c r="M24" s="10">
+        <v>45645</v>
+      </c>
+      <c r="N24" s="10">
+        <v>45652</v>
+      </c>
+      <c r="O24" s="10">
+        <v>45652</v>
+      </c>
       <c r="P24" s="10">
-        <v>46065</v>
+        <v>45670</v>
       </c>
       <c r="Q24" s="10">
-        <v>46075</v>
-      </c>
-      <c r="R24" s="4">
-        <v>46076</v>
+        <v>45672</v>
+      </c>
+      <c r="R24" s="10">
+        <v>45672</v>
       </c>
       <c r="S24" s="4">
-        <v>46077</v>
+        <v>45673</v>
       </c>
       <c r="T24" s="4">
-        <v>46077</v>
+        <v>45673</v>
       </c>
       <c r="V24" s="2" t="s">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="W24" s="2" t="s">
-        <v>29</v>
+        <v>92</v>
       </c>
       <c r="X24" s="2" t="s">
         <v>53</v>
+      </c>
+      <c r="Y24" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="Z24" s="4">
+        <v>46092</v>
       </c>
     </row>
     <row r="25" spans="1:28" x14ac:dyDescent="0.3">
@@ -3012,7 +3070,7 @@
         <v>28</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="J25" s="2">
         <v>1</v>
@@ -3040,7 +3098,7 @@
         <v>46077</v>
       </c>
       <c r="V25" s="2" t="s">
-        <v>99</v>
+        <v>76</v>
       </c>
       <c r="W25" s="2" t="s">
         <v>29</v>
@@ -3069,13 +3127,13 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G26" s="7">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>28</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="J26" s="2">
         <v>1</v>
@@ -3132,13 +3190,13 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G27" s="7">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>28</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="J27" s="2">
         <v>1</v>
@@ -3174,9 +3232,6 @@
       <c r="X27" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="Y27" s="2" t="s">
-        <v>58</v>
-      </c>
     </row>
     <row r="28" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
@@ -3198,13 +3253,13 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G28" s="7">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>28</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="J28" s="2">
         <v>1</v>
@@ -3217,13 +3272,13 @@
       <c r="N28" s="6"/>
       <c r="O28" s="6"/>
       <c r="P28" s="10">
-        <v>46066</v>
+        <v>46065</v>
       </c>
       <c r="Q28" s="10">
-        <v>46071</v>
+        <v>46075</v>
       </c>
       <c r="R28" s="4">
-        <v>46077</v>
+        <v>46076</v>
       </c>
       <c r="S28" s="4">
         <v>46077</v>
@@ -3243,13 +3298,13 @@
     </row>
     <row r="29" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>34</v>
@@ -3261,13 +3316,13 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G29" s="7">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>28</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="J29" s="2">
         <v>1</v>
@@ -3275,55 +3330,44 @@
       <c r="K29" s="2">
         <v>1</v>
       </c>
-      <c r="L29" s="10">
-        <v>46063</v>
-      </c>
-      <c r="M29" s="10">
-        <v>46063</v>
-      </c>
-      <c r="N29" s="10">
-        <v>46063</v>
-      </c>
-      <c r="O29" s="10">
-        <v>46066</v>
-      </c>
+      <c r="L29" s="6"/>
+      <c r="M29" s="6"/>
+      <c r="N29" s="6"/>
+      <c r="O29" s="6"/>
       <c r="P29" s="10">
-        <v>46074</v>
-      </c>
-      <c r="Q29" s="4">
+        <v>46065</v>
+      </c>
+      <c r="Q29" s="10">
+        <v>46075</v>
+      </c>
+      <c r="R29" s="4">
         <v>46076</v>
       </c>
-      <c r="R29" s="4">
-        <v>46078</v>
-      </c>
       <c r="S29" s="4">
-        <v>46080</v>
+        <v>46077</v>
       </c>
       <c r="T29" s="4">
-        <v>46080</v>
+        <v>46077</v>
       </c>
       <c r="V29" s="2" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="W29" s="2" t="s">
-        <v>96</v>
+        <v>29</v>
       </c>
       <c r="X29" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="Y29" s="2" t="s">
-        <v>58</v>
-      </c>
     </row>
     <row r="30" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>106</v>
+        <v>62</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>105</v>
+        <v>63</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>104</v>
+        <v>64</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>34</v>
@@ -3341,7 +3385,7 @@
         <v>28</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="J30" s="2">
         <v>1</v>
@@ -3349,32 +3393,30 @@
       <c r="K30" s="2">
         <v>1</v>
       </c>
-      <c r="L30" s="4">
-        <v>46052</v>
-      </c>
+      <c r="L30" s="6"/>
       <c r="M30" s="6"/>
       <c r="N30" s="6"/>
       <c r="O30" s="6"/>
-      <c r="P30" s="4">
-        <v>46053</v>
-      </c>
-      <c r="Q30" s="4">
+      <c r="P30" s="10">
         <v>46065</v>
       </c>
+      <c r="Q30" s="10">
+        <v>46075</v>
+      </c>
       <c r="R30" s="4">
-        <v>46066</v>
+        <v>46076</v>
       </c>
       <c r="S30" s="4">
-        <v>46066</v>
+        <v>46077</v>
       </c>
       <c r="T30" s="4">
-        <v>46066</v>
+        <v>46077</v>
       </c>
       <c r="V30" s="2" t="s">
-        <v>123</v>
+        <v>98</v>
       </c>
       <c r="W30" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X30" s="2" t="s">
         <v>53</v>
@@ -3385,13 +3427,13 @@
     </row>
     <row r="31" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>106</v>
+        <v>62</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>105</v>
+        <v>63</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>104</v>
+        <v>64</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>34</v>
@@ -3409,7 +3451,7 @@
         <v>28</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="J31" s="2">
         <v>1</v>
@@ -3417,49 +3459,44 @@
       <c r="K31" s="2">
         <v>1</v>
       </c>
-      <c r="L31" s="4">
-        <v>46052</v>
-      </c>
+      <c r="L31" s="6"/>
       <c r="M31" s="6"/>
       <c r="N31" s="6"/>
       <c r="O31" s="6"/>
-      <c r="P31" s="4">
-        <v>46053</v>
-      </c>
-      <c r="Q31" s="4">
-        <v>46065</v>
+      <c r="P31" s="10">
+        <v>46066</v>
+      </c>
+      <c r="Q31" s="10">
+        <v>46071</v>
       </c>
       <c r="R31" s="4">
-        <v>46066</v>
+        <v>46077</v>
       </c>
       <c r="S31" s="4">
-        <v>46066</v>
+        <v>46077</v>
       </c>
       <c r="T31" s="4">
-        <v>46066</v>
+        <v>46077</v>
       </c>
       <c r="V31" s="2" t="s">
-        <v>123</v>
+        <v>99</v>
       </c>
       <c r="W31" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X31" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="Y31" s="2" t="s">
-        <v>58</v>
-      </c>
     </row>
     <row r="32" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>106</v>
+        <v>43</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>105</v>
+        <v>44</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>104</v>
+        <v>45</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>34</v>
@@ -3471,13 +3508,13 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G32" s="7">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>28</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="J32" s="2">
         <v>1</v>
@@ -3485,32 +3522,38 @@
       <c r="K32" s="2">
         <v>1</v>
       </c>
-      <c r="L32" s="4">
-        <v>46052</v>
-      </c>
-      <c r="M32" s="6"/>
-      <c r="N32" s="6"/>
-      <c r="O32" s="6"/>
-      <c r="P32" s="4">
-        <v>46053</v>
+      <c r="L32" s="10">
+        <v>46063</v>
+      </c>
+      <c r="M32" s="10">
+        <v>46063</v>
+      </c>
+      <c r="N32" s="10">
+        <v>46063</v>
+      </c>
+      <c r="O32" s="10">
+        <v>46066</v>
+      </c>
+      <c r="P32" s="10">
+        <v>46074</v>
       </c>
       <c r="Q32" s="4">
-        <v>46065</v>
+        <v>46076</v>
       </c>
       <c r="R32" s="4">
-        <v>46066</v>
+        <v>46078</v>
       </c>
       <c r="S32" s="4">
-        <v>46066</v>
+        <v>46080</v>
       </c>
       <c r="T32" s="4">
-        <v>46066</v>
+        <v>46080</v>
       </c>
       <c r="V32" s="2" t="s">
-        <v>123</v>
+        <v>94</v>
       </c>
       <c r="W32" s="2" t="s">
-        <v>30</v>
+        <v>96</v>
       </c>
       <c r="X32" s="2" t="s">
         <v>53</v>
@@ -3521,13 +3564,13 @@
     </row>
     <row r="33" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>34</v>
@@ -3539,34 +3582,28 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G33" s="7">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>28</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>136</v>
+        <v>101</v>
       </c>
       <c r="J33" s="2">
         <v>1</v>
       </c>
       <c r="K33" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L33" s="4">
-        <v>45868</v>
-      </c>
-      <c r="M33" s="4">
-        <v>46055</v>
-      </c>
-      <c r="N33" s="4">
-        <v>46056</v>
-      </c>
-      <c r="O33" s="4">
-        <v>46056</v>
-      </c>
+        <v>46052</v>
+      </c>
+      <c r="M33" s="6"/>
+      <c r="N33" s="6"/>
+      <c r="O33" s="6"/>
       <c r="P33" s="4">
-        <v>46058</v>
+        <v>46053</v>
       </c>
       <c r="Q33" s="4">
         <v>46065</v>
@@ -3581,24 +3618,27 @@
         <v>46066</v>
       </c>
       <c r="V33" s="2" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="W33" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="X33" s="2" t="s">
         <v>53</v>
       </c>
+      <c r="Y33" s="2" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="34" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>34</v>
@@ -3610,34 +3650,28 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G34" s="7">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>28</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="J34" s="2">
         <v>1</v>
       </c>
       <c r="K34" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L34" s="4">
-        <v>45868</v>
-      </c>
-      <c r="M34" s="4">
-        <v>46055</v>
-      </c>
-      <c r="N34" s="4">
-        <v>46056</v>
-      </c>
-      <c r="O34" s="4">
-        <v>46056</v>
-      </c>
+        <v>46052</v>
+      </c>
+      <c r="M34" s="6"/>
+      <c r="N34" s="6"/>
+      <c r="O34" s="6"/>
       <c r="P34" s="4">
-        <v>46058</v>
+        <v>46053</v>
       </c>
       <c r="Q34" s="4">
         <v>46065</v>
@@ -3652,24 +3686,27 @@
         <v>46066</v>
       </c>
       <c r="V34" s="2" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="W34" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="X34" s="2" t="s">
         <v>53</v>
       </c>
+      <c r="Y34" s="2" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="35" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>34</v>
@@ -3681,34 +3718,28 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G35" s="7">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>28</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="J35" s="2">
         <v>1</v>
       </c>
       <c r="K35" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L35" s="4">
-        <v>45868</v>
-      </c>
-      <c r="M35" s="4">
-        <v>46055</v>
-      </c>
-      <c r="N35" s="4">
-        <v>46056</v>
-      </c>
-      <c r="O35" s="4">
-        <v>46056</v>
-      </c>
+        <v>46052</v>
+      </c>
+      <c r="M35" s="6"/>
+      <c r="N35" s="6"/>
+      <c r="O35" s="6"/>
       <c r="P35" s="4">
-        <v>46057</v>
+        <v>46053</v>
       </c>
       <c r="Q35" s="4">
         <v>46065</v>
@@ -3723,13 +3754,16 @@
         <v>46066</v>
       </c>
       <c r="V35" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="W35" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="X35" s="2" t="s">
         <v>53</v>
+      </c>
+      <c r="Y35" s="2" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="36" spans="1:25" x14ac:dyDescent="0.3">
@@ -3758,7 +3792,7 @@
         <v>28</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>121</v>
+        <v>136</v>
       </c>
       <c r="J36" s="2">
         <v>1</v>
@@ -3794,7 +3828,7 @@
         <v>46066</v>
       </c>
       <c r="V36" s="2" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="W36" s="2" t="s">
         <v>29</v>
@@ -3829,7 +3863,7 @@
         <v>28</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="J37" s="2">
         <v>1</v>
@@ -3865,7 +3899,7 @@
         <v>46066</v>
       </c>
       <c r="V37" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="W37" s="2" t="s">
         <v>29</v>
@@ -3876,52 +3910,52 @@
     </row>
     <row r="38" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F38" s="3">
         <v>0.55000000000000004</v>
       </c>
       <c r="G38" s="7">
-        <v>14.2</v>
+        <v>14.5</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>28</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="J38" s="2">
         <v>1</v>
       </c>
       <c r="K38" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L38" s="4">
-        <v>46062</v>
+        <v>45868</v>
       </c>
       <c r="M38" s="4">
-        <v>46062</v>
+        <v>46055</v>
       </c>
       <c r="N38" s="4">
-        <v>46063</v>
+        <v>46056</v>
       </c>
       <c r="O38" s="4">
-        <v>46063</v>
+        <v>46056</v>
       </c>
       <c r="P38" s="4">
-        <v>46063</v>
+        <v>46057</v>
       </c>
       <c r="Q38" s="4">
         <v>46065</v>
@@ -3930,107 +3964,101 @@
         <v>46066</v>
       </c>
       <c r="S38" s="4">
-        <v>46072</v>
+        <v>46066</v>
       </c>
       <c r="T38" s="4">
-        <v>46072</v>
+        <v>46066</v>
       </c>
       <c r="V38" s="2" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="W38" s="2" t="s">
-        <v>131</v>
+        <v>29</v>
       </c>
       <c r="X38" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="Y38" s="2" t="s">
-        <v>58</v>
-      </c>
     </row>
     <row r="39" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
-        <v>43</v>
+        <v>116</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>44</v>
+        <v>115</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>45</v>
+        <v>114</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F39" s="3">
-        <v>0.43</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="G39" s="7">
-        <v>14.2</v>
+        <v>14.5</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>132</v>
+        <v>28</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="J39" s="2">
         <v>1</v>
       </c>
       <c r="K39" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L39" s="4">
-        <v>46077</v>
+        <v>45868</v>
       </c>
       <c r="M39" s="4">
-        <v>46077</v>
+        <v>46055</v>
       </c>
       <c r="N39" s="4">
-        <v>46078</v>
+        <v>46056</v>
       </c>
       <c r="O39" s="4">
-        <v>46078</v>
+        <v>46056</v>
       </c>
       <c r="P39" s="4">
-        <v>46084</v>
+        <v>46058</v>
       </c>
       <c r="Q39" s="4">
-        <v>46089</v>
+        <v>46065</v>
       </c>
       <c r="R39" s="4">
-        <v>46090</v>
+        <v>46066</v>
       </c>
       <c r="S39" s="4">
-        <v>46092</v>
+        <v>46066</v>
       </c>
       <c r="T39" s="4">
-        <v>46092</v>
+        <v>46066</v>
       </c>
       <c r="V39" s="2" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="W39" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="X39" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="Y39" s="2" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
     </row>
     <row r="40" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
-        <v>62</v>
+        <v>116</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>63</v>
+        <v>115</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>64</v>
+        <v>114</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>34</v>
@@ -4048,66 +4076,78 @@
         <v>28</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>139</v>
+        <v>122</v>
       </c>
       <c r="J40" s="2">
         <v>1</v>
       </c>
       <c r="K40" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L40" s="4">
+        <v>45868</v>
+      </c>
+      <c r="M40" s="4">
+        <v>46055</v>
+      </c>
+      <c r="N40" s="4">
+        <v>46056</v>
+      </c>
+      <c r="O40" s="4">
+        <v>46056</v>
+      </c>
+      <c r="P40" s="4">
+        <v>46058</v>
+      </c>
+      <c r="Q40" s="4">
+        <v>46065</v>
+      </c>
+      <c r="R40" s="4">
         <v>46066</v>
       </c>
-      <c r="M40" s="6"/>
-      <c r="N40" s="6"/>
-      <c r="O40" s="6"/>
-      <c r="P40" s="4">
-        <v>46076</v>
-      </c>
-      <c r="Q40" s="4">
-        <v>46083</v>
+      <c r="S40" s="4">
+        <v>46066</v>
+      </c>
+      <c r="T40" s="4">
+        <v>46066</v>
       </c>
       <c r="V40" s="2" t="s">
-        <v>52</v>
+        <v>118</v>
       </c>
       <c r="W40" s="2" t="s">
         <v>29</v>
       </c>
       <c r="X40" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="Y40" s="2" t="s">
-        <v>143</v>
+        <v>53</v>
       </c>
     </row>
     <row r="41" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
-        <v>62</v>
+        <v>126</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>63</v>
+        <v>127</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F41" s="3">
         <v>0.55000000000000004</v>
       </c>
       <c r="G41" s="7">
-        <v>14.5</v>
+        <v>14.2</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>28</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="J41" s="2">
         <v>1</v>
@@ -4116,57 +4156,72 @@
         <v>1</v>
       </c>
       <c r="L41" s="4">
+        <v>46062</v>
+      </c>
+      <c r="M41" s="4">
+        <v>46062</v>
+      </c>
+      <c r="N41" s="4">
+        <v>46063</v>
+      </c>
+      <c r="O41" s="4">
+        <v>46063</v>
+      </c>
+      <c r="P41" s="4">
+        <v>46063</v>
+      </c>
+      <c r="Q41" s="4">
+        <v>46065</v>
+      </c>
+      <c r="R41" s="4">
         <v>46066</v>
       </c>
-      <c r="M41" s="6"/>
-      <c r="N41" s="6"/>
-      <c r="O41" s="6"/>
-      <c r="P41" s="4">
-        <v>46076</v>
-      </c>
-      <c r="Q41" s="4">
-        <v>46083</v>
+      <c r="S41" s="4">
+        <v>46072</v>
+      </c>
+      <c r="T41" s="4">
+        <v>46072</v>
       </c>
       <c r="V41" s="2" t="s">
-        <v>52</v>
+        <v>130</v>
       </c>
       <c r="W41" s="2" t="s">
-        <v>29</v>
+        <v>131</v>
       </c>
       <c r="X41" s="2" t="s">
-        <v>100</v>
+        <v>53</v>
       </c>
       <c r="Y41" s="2" t="s">
-        <v>143</v>
+        <v>58</v>
       </c>
     </row>
     <row r="42" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F42" s="3">
-        <v>0.55000000000000004</v>
+        <v>0.43</v>
       </c>
       <c r="G42" s="7">
-        <v>14.5</v>
+        <v>14.2</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>28</v>
+        <v>132</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="J42" s="2">
         <v>1</v>
@@ -4175,42 +4230,54 @@
         <v>1</v>
       </c>
       <c r="L42" s="4">
-        <v>46066</v>
-      </c>
-      <c r="M42" s="6"/>
-      <c r="N42" s="6"/>
-      <c r="O42" s="6"/>
+        <v>46077</v>
+      </c>
+      <c r="M42" s="4">
+        <v>46077</v>
+      </c>
+      <c r="N42" s="4">
+        <v>46078</v>
+      </c>
+      <c r="O42" s="4">
+        <v>46078</v>
+      </c>
       <c r="P42" s="4">
-        <v>46079</v>
+        <v>46084</v>
       </c>
       <c r="Q42" s="4">
-        <v>46086</v>
+        <v>46089</v>
       </c>
       <c r="R42" s="4">
-        <v>46087</v>
+        <v>46090</v>
+      </c>
+      <c r="S42" s="4">
+        <v>46092</v>
+      </c>
+      <c r="T42" s="4">
+        <v>46092</v>
       </c>
       <c r="V42" s="2" t="s">
-        <v>66</v>
+        <v>134</v>
       </c>
       <c r="W42" s="2" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="X42" s="2" t="s">
         <v>100</v>
       </c>
       <c r="Y42" s="2" t="s">
-        <v>143</v>
+        <v>33</v>
       </c>
     </row>
     <row r="43" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>145</v>
+        <v>62</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>146</v>
+        <v>63</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>147</v>
+        <v>64</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>34</v>
@@ -4222,48 +4289,37 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G43" s="7">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="H43" s="2" t="s">
         <v>28</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="J43" s="2">
         <v>1</v>
       </c>
       <c r="K43" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L43" s="4">
-        <v>46055</v>
-      </c>
-      <c r="M43" s="4">
-        <v>46085</v>
-      </c>
+        <v>46066</v>
+      </c>
+      <c r="M43" s="6"/>
       <c r="N43" s="6"/>
       <c r="O43" s="6"/>
       <c r="P43" s="4">
-        <v>46085</v>
+        <v>46076</v>
       </c>
       <c r="Q43" s="4">
-        <v>46093</v>
-      </c>
-      <c r="R43" s="4">
-        <v>46094</v>
-      </c>
-      <c r="S43" s="4">
-        <v>46094</v>
-      </c>
-      <c r="T43" s="4">
-        <v>46094</v>
+        <v>46083</v>
       </c>
       <c r="V43" s="2" t="s">
-        <v>149</v>
+        <v>52</v>
       </c>
       <c r="W43" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X43" s="2" t="s">
         <v>100</v>
@@ -4274,13 +4330,13 @@
     </row>
     <row r="44" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
-        <v>145</v>
+        <v>62</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>146</v>
+        <v>63</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>147</v>
+        <v>64</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>34</v>
@@ -4292,48 +4348,37 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G44" s="7">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="H44" s="2" t="s">
         <v>28</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="J44" s="2">
         <v>1</v>
       </c>
       <c r="K44" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L44" s="4">
-        <v>46055</v>
-      </c>
-      <c r="M44" s="4">
-        <v>46085</v>
-      </c>
+        <v>46066</v>
+      </c>
+      <c r="M44" s="6"/>
       <c r="N44" s="6"/>
       <c r="O44" s="6"/>
       <c r="P44" s="4">
-        <v>46085</v>
+        <v>46076</v>
       </c>
       <c r="Q44" s="4">
-        <v>46093</v>
-      </c>
-      <c r="R44" s="4">
-        <v>46094</v>
-      </c>
-      <c r="S44" s="4">
-        <v>46094</v>
-      </c>
-      <c r="T44" s="4">
-        <v>46094</v>
+        <v>46083</v>
       </c>
       <c r="V44" s="2" t="s">
-        <v>149</v>
+        <v>52</v>
       </c>
       <c r="W44" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X44" s="2" t="s">
         <v>100</v>
@@ -4344,31 +4389,31 @@
     </row>
     <row r="45" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>151</v>
+        <v>62</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>152</v>
+        <v>63</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>153</v>
+        <v>64</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>154</v>
+        <v>27</v>
       </c>
       <c r="F45" s="3">
-        <v>0.45</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="G45" s="7">
-        <v>14.2</v>
+        <v>14.5</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>28</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>155</v>
+        <v>141</v>
       </c>
       <c r="J45" s="2">
         <v>1</v>
@@ -4377,101 +4422,171 @@
         <v>1</v>
       </c>
       <c r="L45" s="4">
-        <v>46090</v>
-      </c>
-      <c r="N45" s="4">
-        <v>46085</v>
-      </c>
+        <v>46066</v>
+      </c>
+      <c r="M45" s="6"/>
+      <c r="N45" s="6"/>
+      <c r="O45" s="6"/>
       <c r="P45" s="4">
+        <v>46079</v>
+      </c>
+      <c r="Q45" s="4">
+        <v>46086</v>
+      </c>
+      <c r="R45" s="4">
         <v>46087</v>
+      </c>
+      <c r="V45" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="W45" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="X45" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="Y45" s="2" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="46" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>154</v>
+        <v>27</v>
       </c>
       <c r="F46" s="3">
-        <v>0.45</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="G46" s="7">
-        <v>14.2</v>
+        <v>15</v>
       </c>
       <c r="H46" s="2" t="s">
         <v>28</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="J46" s="2">
         <v>1</v>
       </c>
       <c r="K46" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L46" s="4">
-        <v>46090</v>
-      </c>
-      <c r="N46" s="4">
+        <v>46055</v>
+      </c>
+      <c r="M46" s="4">
         <v>46085</v>
       </c>
+      <c r="N46" s="6"/>
+      <c r="O46" s="6"/>
       <c r="P46" s="4">
-        <v>46087</v>
+        <v>46085</v>
+      </c>
+      <c r="Q46" s="4">
+        <v>46093</v>
+      </c>
+      <c r="R46" s="4">
+        <v>46094</v>
+      </c>
+      <c r="S46" s="4">
+        <v>46094</v>
+      </c>
+      <c r="T46" s="4">
+        <v>46094</v>
+      </c>
+      <c r="V46" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="W46" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X46" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="Y46" s="2" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="47" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>154</v>
+        <v>27</v>
       </c>
       <c r="F47" s="3">
-        <v>0.45</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="G47" s="7">
-        <v>14.2</v>
+        <v>15</v>
       </c>
       <c r="H47" s="2" t="s">
         <v>28</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="J47" s="2">
         <v>1</v>
       </c>
       <c r="K47" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L47" s="4">
-        <v>46090</v>
-      </c>
-      <c r="N47" s="4">
+        <v>46055</v>
+      </c>
+      <c r="M47" s="4">
         <v>46085</v>
       </c>
+      <c r="N47" s="6"/>
+      <c r="O47" s="6"/>
       <c r="P47" s="4">
-        <v>46087</v>
+        <v>46085</v>
+      </c>
+      <c r="Q47" s="4">
+        <v>46093</v>
+      </c>
+      <c r="R47" s="4">
+        <v>46094</v>
+      </c>
+      <c r="S47" s="4">
+        <v>46094</v>
+      </c>
+      <c r="T47" s="4">
+        <v>46094</v>
+      </c>
+      <c r="V47" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="W47" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X47" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="Y47" s="2" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="48" spans="1:25" x14ac:dyDescent="0.3">
@@ -4500,7 +4615,7 @@
         <v>28</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="J48" s="2">
         <v>1</v>
@@ -4544,7 +4659,7 @@
         <v>28</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="J49" s="2">
         <v>1</v>
@@ -4588,7 +4703,7 @@
         <v>28</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="J50" s="2">
         <v>1</v>
@@ -4631,8 +4746,8 @@
       <c r="H51" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I51" s="11" t="s">
-        <v>161</v>
+      <c r="I51" s="2" t="s">
+        <v>158</v>
       </c>
       <c r="J51" s="2">
         <v>1</v>
@@ -4675,8 +4790,8 @@
       <c r="H52" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I52" s="11" t="s">
-        <v>162</v>
+      <c r="I52" s="2" t="s">
+        <v>159</v>
       </c>
       <c r="J52" s="2">
         <v>1</v>
@@ -4719,8 +4834,8 @@
       <c r="H53" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I53" s="11" t="s">
-        <v>163</v>
+      <c r="I53" s="2" t="s">
+        <v>160</v>
       </c>
       <c r="J53" s="2">
         <v>1</v>
@@ -4740,22 +4855,22 @@
     </row>
     <row r="54" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
-        <v>182</v>
+        <v>151</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>183</v>
+        <v>152</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>184</v>
+        <v>153</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>185</v>
+        <v>154</v>
       </c>
       <c r="F54" s="3">
-        <v>0.55000000000000004</v>
+        <v>0.45</v>
       </c>
       <c r="G54" s="7">
         <v>14.2</v>
@@ -4764,7 +4879,7 @@
         <v>28</v>
       </c>
       <c r="I54" s="11" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="J54" s="2">
         <v>1</v>
@@ -4773,27 +4888,33 @@
         <v>1</v>
       </c>
       <c r="L54" s="4">
-        <v>46086</v>
+        <v>46090</v>
+      </c>
+      <c r="N54" s="4">
+        <v>46085</v>
+      </c>
+      <c r="P54" s="4">
+        <v>46087</v>
       </c>
     </row>
     <row r="55" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
-        <v>182</v>
+        <v>151</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>183</v>
+        <v>152</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>184</v>
+        <v>153</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>185</v>
+        <v>154</v>
       </c>
       <c r="F55" s="3">
-        <v>0.55000000000000004</v>
+        <v>0.45</v>
       </c>
       <c r="G55" s="7">
         <v>14.2</v>
@@ -4802,7 +4923,7 @@
         <v>28</v>
       </c>
       <c r="I55" s="11" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="J55" s="2">
         <v>1</v>
@@ -4811,27 +4932,33 @@
         <v>1</v>
       </c>
       <c r="L55" s="4">
-        <v>46086</v>
+        <v>46090</v>
+      </c>
+      <c r="N55" s="4">
+        <v>46085</v>
+      </c>
+      <c r="P55" s="4">
+        <v>46087</v>
       </c>
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
-        <v>182</v>
+        <v>151</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>183</v>
+        <v>152</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>184</v>
+        <v>153</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>27</v>
+        <v>154</v>
       </c>
       <c r="F56" s="3">
-        <v>0.55000000000000004</v>
+        <v>0.45</v>
       </c>
       <c r="G56" s="7">
         <v>14.2</v>
@@ -4840,7 +4967,7 @@
         <v>28</v>
       </c>
       <c r="I56" s="11" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="J56" s="2">
         <v>1</v>
@@ -4849,7 +4976,13 @@
         <v>1</v>
       </c>
       <c r="L56" s="4">
-        <v>46086</v>
+        <v>46090</v>
+      </c>
+      <c r="N56" s="4">
+        <v>46085</v>
+      </c>
+      <c r="P56" s="4">
+        <v>46087</v>
       </c>
     </row>
     <row r="57" spans="1:16" x14ac:dyDescent="0.3">
@@ -4866,7 +4999,7 @@
         <v>26</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>27</v>
+        <v>185</v>
       </c>
       <c r="F57" s="3">
         <v>0.55000000000000004</v>
@@ -4878,7 +5011,7 @@
         <v>28</v>
       </c>
       <c r="I57" s="11" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="J57" s="2">
         <v>1</v>
@@ -4904,7 +5037,7 @@
         <v>26</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>27</v>
+        <v>185</v>
       </c>
       <c r="F58" s="3">
         <v>0.55000000000000004</v>
@@ -4916,7 +5049,7 @@
         <v>28</v>
       </c>
       <c r="I58" s="11" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="J58" s="2">
         <v>1</v>
@@ -4954,7 +5087,7 @@
         <v>28</v>
       </c>
       <c r="I59" s="11" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="J59" s="2">
         <v>1</v>
@@ -4992,7 +5125,7 @@
         <v>28</v>
       </c>
       <c r="I60" s="11" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="J60" s="2">
         <v>1</v>
@@ -5030,7 +5163,7 @@
         <v>28</v>
       </c>
       <c r="I61" s="11" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="J61" s="2">
         <v>1</v>
@@ -5068,7 +5201,7 @@
         <v>28</v>
       </c>
       <c r="I62" s="11" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="J62" s="2">
         <v>1</v>
@@ -5106,7 +5239,7 @@
         <v>28</v>
       </c>
       <c r="I63" s="11" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="J63" s="2">
         <v>1</v>
@@ -5144,7 +5277,7 @@
         <v>28</v>
       </c>
       <c r="I64" s="11" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="J64" s="2">
         <v>1</v>
@@ -5182,7 +5315,7 @@
         <v>28</v>
       </c>
       <c r="I65" s="11" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="J65" s="2">
         <v>1</v>
@@ -5220,7 +5353,7 @@
         <v>28</v>
       </c>
       <c r="I66" s="11" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="J66" s="2">
         <v>1</v>
@@ -5258,7 +5391,7 @@
         <v>28</v>
       </c>
       <c r="I67" s="11" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="J67" s="2">
         <v>1</v>
@@ -5296,7 +5429,7 @@
         <v>28</v>
       </c>
       <c r="I68" s="11" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="J68" s="2">
         <v>1</v>
@@ -5334,7 +5467,7 @@
         <v>28</v>
       </c>
       <c r="I69" s="11" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="J69" s="2">
         <v>1</v>
@@ -5372,7 +5505,7 @@
         <v>28</v>
       </c>
       <c r="I70" s="11" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="J70" s="2">
         <v>1</v>
@@ -5410,7 +5543,7 @@
         <v>28</v>
       </c>
       <c r="I71" s="11" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="J71" s="2">
         <v>1</v>
@@ -5424,16 +5557,16 @@
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
-        <v>151</v>
+        <v>182</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>152</v>
+        <v>183</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>153</v>
+        <v>184</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>27</v>
@@ -5442,13 +5575,13 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G72" s="7">
-        <v>14.5</v>
+        <v>14.2</v>
       </c>
       <c r="H72" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I72" s="2" t="s">
-        <v>186</v>
+      <c r="I72" s="11" t="s">
+        <v>179</v>
       </c>
       <c r="J72" s="2">
         <v>1</v>
@@ -5457,21 +5590,21 @@
         <v>1</v>
       </c>
       <c r="L72" s="4">
-        <v>46092</v>
+        <v>46086</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
-        <v>151</v>
+        <v>182</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>152</v>
+        <v>183</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>153</v>
+        <v>184</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>27</v>
@@ -5480,13 +5613,13 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G73" s="7">
-        <v>14.5</v>
+        <v>14.2</v>
       </c>
       <c r="H73" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I73" s="2" t="s">
-        <v>187</v>
+      <c r="I73" s="11" t="s">
+        <v>180</v>
       </c>
       <c r="J73" s="2">
         <v>1</v>
@@ -5495,21 +5628,21 @@
         <v>1</v>
       </c>
       <c r="L73" s="4">
-        <v>46092</v>
+        <v>46086</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
-        <v>151</v>
+        <v>182</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>152</v>
+        <v>183</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>153</v>
+        <v>184</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>27</v>
@@ -5518,13 +5651,13 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G74" s="7">
-        <v>14.5</v>
+        <v>14.2</v>
       </c>
       <c r="H74" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I74" s="2" t="s">
-        <v>188</v>
+      <c r="I74" s="11" t="s">
+        <v>181</v>
       </c>
       <c r="J74" s="2">
         <v>1</v>
@@ -5533,7 +5666,7 @@
         <v>1</v>
       </c>
       <c r="L74" s="4">
-        <v>46092</v>
+        <v>46086</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.3">
@@ -5562,7 +5695,7 @@
         <v>28</v>
       </c>
       <c r="I75" s="2" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="J75" s="2">
         <v>1</v>
@@ -5574,22 +5707,136 @@
         <v>46092</v>
       </c>
     </row>
+    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A76" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F76" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G76" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I76" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="J76" s="2">
+        <v>1</v>
+      </c>
+      <c r="K76" s="2">
+        <v>1</v>
+      </c>
+      <c r="L76" s="4">
+        <v>46092</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A77" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F77" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G77" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I77" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="J77" s="2">
+        <v>1</v>
+      </c>
+      <c r="K77" s="2">
+        <v>1</v>
+      </c>
+      <c r="L77" s="4">
+        <v>46092</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A78" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F78" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G78" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I78" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="J78" s="2">
+        <v>1</v>
+      </c>
+      <c r="K78" s="2">
+        <v>1</v>
+      </c>
+      <c r="L78" s="4">
+        <v>46092</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="V1:V38"/>
+  <autoFilter ref="V1:V41"/>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="I51:I53">
+  <conditionalFormatting sqref="I54:I56">
     <cfRule type="expression" dxfId="2" priority="3" stopIfTrue="1">
-      <formula>$E3099:$E1048568="sub"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I62 I71">
-    <cfRule type="expression" dxfId="1" priority="2" stopIfTrue="1">
       <formula>$E3102:$E1048571="sub"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I54:I61 I63:I70">
+  <conditionalFormatting sqref="I65 I74">
+    <cfRule type="expression" dxfId="1" priority="2" stopIfTrue="1">
+      <formula>$E3105:$E1048574="sub"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I57:I64 I66:I73">
     <cfRule type="expression" dxfId="0" priority="1" stopIfTrue="1">
-      <formula>$E3095:$E1048564="sub"</formula>
+      <formula>$E3098:$E1048567="sub"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5601,55 +5848,55 @@
           <x14:formula1>
             <xm:f>Sheet2!$F$2:$F$4</xm:f>
           </x14:formula1>
-          <xm:sqref>W2:W37 Y39 W39:W1048576</xm:sqref>
+          <xm:sqref>W42:W1048576 Y42 W2:W40</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>Sheet2!$G$2:$G$5</xm:f>
           </x14:formula1>
-          <xm:sqref>X2:X37 X39:X1048576</xm:sqref>
+          <xm:sqref>X42:X1048576 X2:X40</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>Sheet2!$E$2:$E$4</xm:f>
           </x14:formula1>
-          <xm:sqref>H2:H37 H39:H1048576</xm:sqref>
+          <xm:sqref>H42:H1048576 H2:H40</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>Sheet2!$D$2:$D$5</xm:f>
           </x14:formula1>
-          <xm:sqref>G2:G37 G39:G1048576</xm:sqref>
+          <xm:sqref>G42:G1048576 G2:G40</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>Sheet2!$C$2:$C$5</xm:f>
           </x14:formula1>
-          <xm:sqref>F2:F37 F39:F1048576</xm:sqref>
+          <xm:sqref>F42:F1048576 F2:F40</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>Sheet2!$B$2:$B$3</xm:f>
           </x14:formula1>
-          <xm:sqref>E2:E37 E39:E1048576</xm:sqref>
+          <xm:sqref>E42:E1048576 E2:E40</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>Sheet2!$A$2:$A$4</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D37 D39:D1048576</xm:sqref>
+          <xm:sqref>D42:D1048576 D2:D40</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'[복사본 sample-list.xlsx]Sheet2'!#REF!</xm:f>
           </x14:formula1>
-          <xm:sqref>D38:H38 W38:X38</xm:sqref>
+          <xm:sqref>D41:H41 W41:X41</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>Sheet2!$H$2:$H$7</xm:f>
           </x14:formula1>
-          <xm:sqref>Y2:Y38 Y40:Y1048576</xm:sqref>
+          <xm:sqref>Y43:Y1048576 Y2:Y41</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/sample-list.xlsx
+++ b/sample-list.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20130" windowHeight="10815"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12165"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,14 +19,14 @@
     <externalReference r:id="rId3"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$V$1:$V$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$V$1:$V$42</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="775" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1086" uniqueCount="218">
   <si>
     <t>국가</t>
   </si>
@@ -634,123 +634,298 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t xml:space="preserve"> Winsome Brown 1D -1.75</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> Winsome Brown 1D -3.00</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> Winsome Brown 1D -3.50</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> Winsome Brown 1D -3.75</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> Winsome Brown 1D -4.00</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> Winsome Brown 1D -4.50</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> Winsome Brown 1D -5.50</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> Winsome Brown 1D -5.75</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>중동</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Menicon</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>이상윤</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1D</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LIMIMOON 미스트 그레이</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Gleam Edge 볼드 브라운</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Gleam Edge 볼드 그레이</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SY9-Aurora B</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SY10-C 5th</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>파우더</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SY2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LIMIMOON 헤이즈 초코</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>임수빈</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>임수빈</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>임수빈</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>칼립소 BK</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>일본</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PIA</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>남상규</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cofancy 流心泡芙</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Cofancy 星光</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>软</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>糖</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cofancy 月光奶油</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Cofancy 纯</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>榛小狗</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Cofancy </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>银</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>河</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>贝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>果</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ML1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ML2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ML3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>류미리</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t xml:space="preserve"> Winsome Brown 1D -0.75</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> Winsome Brown 1D -1.75</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> Winsome Brown 1D -3.00</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> Winsome Brown 1D -3.50</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> Winsome Brown 1D -3.75</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> Winsome Brown 1D -4.00</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> Winsome Brown 1D -4.50</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> Winsome Brown 1D -5.50</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> Winsome Brown 1D -5.75</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> Winsome Brown 1M -0.75</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> Winsome Brown 1M -1.75</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> Winsome Brown 1M -3.00</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> Winsome Brown 1M -3.50</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> Winsome Brown 1M -3.75</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> Winsome Brown 1M -4.00</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> Winsome Brown 1M -4.50</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> Winsome Brown 1M -5.50</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> Winsome Brown 1M -5.75</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>중동</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Menicon</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>이상윤</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1D</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>LIMIMOON 헤이즈 초코</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>LIMIMOON 미스트 그레이</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Gleam Edge 볼드 브라운</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Gleam Edge 볼드 그레이</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SY9-Aurora B</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SY10-C 5th</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>파우더</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SY2</t>
+    <t>Winsome brown 1M -0.75</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Winsome brown 1M -1.75</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Winsome brown 1M -2.00</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Winsome brown 1M -2.25</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Winsome brown 1M -3.00</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Winsome brown 1M -3.50</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Winsome brown 1M -3.25</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Winsome brown 1M -3.75</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Winsome brown 1M -4.00</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Winsome brown 1M -4.25</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Winsome brown 1M -4.50</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Winsome brown 1M -5.00</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Winsome brown 1M -5.25</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Winsome brown 1M -5.50</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Winsome brown 1M -5.75</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Winsome brown 1M -6.00</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Winsome brown 1M -7.50</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -761,7 +936,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.0_ "/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -797,8 +972,16 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -814,6 +997,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.34998626667073579"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -845,7 +1034,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -880,11 +1069,73 @@
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="11">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1217,7 +1468,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AB78"/>
+  <dimension ref="A1:AB96"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.25" style="2" customWidth="1"/>
@@ -2839,7 +3090,7 @@
         <v>28</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="J22" s="2">
         <v>1</v>
@@ -2916,7 +3167,7 @@
         <v>28</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="J23" s="2">
         <v>1</v>
@@ -2990,10 +3241,10 @@
         <v>14.5</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="J24" s="2">
         <v>1</v>
@@ -3038,7 +3289,7 @@
         <v>53</v>
       </c>
       <c r="Y24" s="2" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="Z24" s="4">
         <v>46092</v>
@@ -3863,40 +4114,31 @@
         <v>28</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>119</v>
+        <v>136</v>
       </c>
       <c r="J37" s="2">
         <v>1</v>
       </c>
       <c r="K37" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L37" s="4">
         <v>45868</v>
       </c>
       <c r="M37" s="4">
-        <v>46055</v>
+        <v>46093</v>
       </c>
       <c r="N37" s="4">
-        <v>46056</v>
+        <v>46093</v>
       </c>
       <c r="O37" s="4">
-        <v>46056</v>
+        <v>46093</v>
       </c>
       <c r="P37" s="4">
-        <v>46058</v>
+        <v>46098</v>
       </c>
       <c r="Q37" s="4">
-        <v>46065</v>
-      </c>
-      <c r="R37" s="4">
-        <v>46066</v>
-      </c>
-      <c r="S37" s="4">
-        <v>46066</v>
-      </c>
-      <c r="T37" s="4">
-        <v>46066</v>
+        <v>46100</v>
       </c>
       <c r="V37" s="2" t="s">
         <v>117</v>
@@ -3905,7 +4147,7 @@
         <v>29</v>
       </c>
       <c r="X37" s="2" t="s">
-        <v>53</v>
+        <v>100</v>
       </c>
     </row>
     <row r="38" spans="1:25" x14ac:dyDescent="0.3">
@@ -3934,7 +4176,7 @@
         <v>28</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="J38" s="2">
         <v>1</v>
@@ -3955,7 +4197,7 @@
         <v>46056</v>
       </c>
       <c r="P38" s="4">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="Q38" s="4">
         <v>46065</v>
@@ -3970,7 +4212,7 @@
         <v>46066</v>
       </c>
       <c r="V38" s="2" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="W38" s="2" t="s">
         <v>29</v>
@@ -4005,7 +4247,7 @@
         <v>28</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="J39" s="2">
         <v>1</v>
@@ -4026,7 +4268,7 @@
         <v>46056</v>
       </c>
       <c r="P39" s="4">
-        <v>46058</v>
+        <v>46057</v>
       </c>
       <c r="Q39" s="4">
         <v>46065</v>
@@ -4041,7 +4283,7 @@
         <v>46066</v>
       </c>
       <c r="V39" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="W39" s="2" t="s">
         <v>29</v>
@@ -4076,7 +4318,7 @@
         <v>28</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="J40" s="2">
         <v>1</v>
@@ -4112,7 +4354,7 @@
         <v>46066</v>
       </c>
       <c r="V40" s="2" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="W40" s="2" t="s">
         <v>29</v>
@@ -4123,52 +4365,52 @@
     </row>
     <row r="41" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F41" s="3">
         <v>0.55000000000000004</v>
       </c>
       <c r="G41" s="7">
-        <v>14.2</v>
+        <v>14.5</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>28</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="J41" s="2">
         <v>1</v>
       </c>
       <c r="K41" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L41" s="4">
-        <v>46062</v>
+        <v>45868</v>
       </c>
       <c r="M41" s="4">
-        <v>46062</v>
+        <v>46055</v>
       </c>
       <c r="N41" s="4">
-        <v>46063</v>
+        <v>46056</v>
       </c>
       <c r="O41" s="4">
-        <v>46063</v>
+        <v>46056</v>
       </c>
       <c r="P41" s="4">
-        <v>46063</v>
+        <v>46058</v>
       </c>
       <c r="Q41" s="4">
         <v>46065</v>
@@ -4177,33 +4419,30 @@
         <v>46066</v>
       </c>
       <c r="S41" s="4">
-        <v>46072</v>
+        <v>46066</v>
       </c>
       <c r="T41" s="4">
-        <v>46072</v>
+        <v>46066</v>
       </c>
       <c r="V41" s="2" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="W41" s="2" t="s">
-        <v>131</v>
+        <v>29</v>
       </c>
       <c r="X41" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="Y41" s="2" t="s">
-        <v>58</v>
-      </c>
     </row>
     <row r="42" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>43</v>
+        <v>126</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>44</v>
+        <v>127</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>45</v>
+        <v>128</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>26</v>
@@ -4212,16 +4451,16 @@
         <v>32</v>
       </c>
       <c r="F42" s="3">
-        <v>0.43</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="G42" s="7">
         <v>14.2</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>132</v>
+        <v>28</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="J42" s="2">
         <v>1</v>
@@ -4230,72 +4469,72 @@
         <v>1</v>
       </c>
       <c r="L42" s="4">
-        <v>46077</v>
+        <v>46062</v>
       </c>
       <c r="M42" s="4">
-        <v>46077</v>
+        <v>46062</v>
       </c>
       <c r="N42" s="4">
-        <v>46078</v>
+        <v>46063</v>
       </c>
       <c r="O42" s="4">
-        <v>46078</v>
+        <v>46063</v>
       </c>
       <c r="P42" s="4">
-        <v>46084</v>
+        <v>46063</v>
       </c>
       <c r="Q42" s="4">
-        <v>46089</v>
+        <v>46065</v>
       </c>
       <c r="R42" s="4">
-        <v>46090</v>
+        <v>46066</v>
       </c>
       <c r="S42" s="4">
-        <v>46092</v>
+        <v>46072</v>
       </c>
       <c r="T42" s="4">
-        <v>46092</v>
+        <v>46072</v>
       </c>
       <c r="V42" s="2" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="W42" s="2" t="s">
-        <v>33</v>
+        <v>131</v>
       </c>
       <c r="X42" s="2" t="s">
-        <v>100</v>
+        <v>53</v>
       </c>
       <c r="Y42" s="2" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
     </row>
     <row r="43" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F43" s="3">
-        <v>0.55000000000000004</v>
+        <v>0.43</v>
       </c>
       <c r="G43" s="7">
-        <v>14.5</v>
+        <v>14.2</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>28</v>
+        <v>132</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="J43" s="2">
         <v>1</v>
@@ -4304,28 +4543,43 @@
         <v>1</v>
       </c>
       <c r="L43" s="4">
-        <v>46066</v>
-      </c>
-      <c r="M43" s="6"/>
-      <c r="N43" s="6"/>
-      <c r="O43" s="6"/>
+        <v>46077</v>
+      </c>
+      <c r="M43" s="4">
+        <v>46077</v>
+      </c>
+      <c r="N43" s="4">
+        <v>46078</v>
+      </c>
+      <c r="O43" s="4">
+        <v>46078</v>
+      </c>
       <c r="P43" s="4">
-        <v>46076</v>
+        <v>46084</v>
       </c>
       <c r="Q43" s="4">
-        <v>46083</v>
+        <v>46089</v>
+      </c>
+      <c r="R43" s="4">
+        <v>46090</v>
+      </c>
+      <c r="S43" s="4">
+        <v>46092</v>
+      </c>
+      <c r="T43" s="4">
+        <v>46092</v>
       </c>
       <c r="V43" s="2" t="s">
-        <v>52</v>
+        <v>134</v>
       </c>
       <c r="W43" s="2" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="X43" s="2" t="s">
         <v>100</v>
       </c>
       <c r="Y43" s="2" t="s">
-        <v>143</v>
+        <v>33</v>
       </c>
     </row>
     <row r="44" spans="1:25" x14ac:dyDescent="0.3">
@@ -4354,7 +4608,7 @@
         <v>28</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J44" s="2">
         <v>1</v>
@@ -4413,7 +4667,7 @@
         <v>28</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J45" s="2">
         <v>1</v>
@@ -4428,16 +4682,13 @@
       <c r="N45" s="6"/>
       <c r="O45" s="6"/>
       <c r="P45" s="4">
-        <v>46079</v>
+        <v>46076</v>
       </c>
       <c r="Q45" s="4">
-        <v>46086</v>
-      </c>
-      <c r="R45" s="4">
-        <v>46087</v>
+        <v>46083</v>
       </c>
       <c r="V45" s="2" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="W45" s="2" t="s">
         <v>29</v>
@@ -4451,13 +4702,13 @@
     </row>
     <row r="46" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
-        <v>145</v>
+        <v>62</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>146</v>
+        <v>63</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>147</v>
+        <v>64</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>34</v>
@@ -4469,48 +4720,40 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G46" s="7">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="H46" s="2" t="s">
         <v>28</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="J46" s="2">
         <v>1</v>
       </c>
       <c r="K46" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L46" s="4">
-        <v>46055</v>
-      </c>
-      <c r="M46" s="4">
-        <v>46085</v>
-      </c>
+        <v>46066</v>
+      </c>
+      <c r="M46" s="6"/>
       <c r="N46" s="6"/>
       <c r="O46" s="6"/>
       <c r="P46" s="4">
-        <v>46085</v>
+        <v>46079</v>
       </c>
       <c r="Q46" s="4">
-        <v>46093</v>
+        <v>46086</v>
       </c>
       <c r="R46" s="4">
-        <v>46094</v>
-      </c>
-      <c r="S46" s="4">
-        <v>46094</v>
-      </c>
-      <c r="T46" s="4">
-        <v>46094</v>
+        <v>46087</v>
       </c>
       <c r="V46" s="2" t="s">
-        <v>149</v>
+        <v>66</v>
       </c>
       <c r="W46" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X46" s="2" t="s">
         <v>100</v>
@@ -4545,7 +4788,7 @@
         <v>28</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="J47" s="2">
         <v>1</v>
@@ -4591,49 +4834,75 @@
     </row>
     <row r="48" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>154</v>
+        <v>27</v>
       </c>
       <c r="F48" s="3">
-        <v>0.45</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="G48" s="7">
-        <v>14.2</v>
+        <v>15</v>
       </c>
       <c r="H48" s="2" t="s">
         <v>28</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="J48" s="2">
         <v>1</v>
       </c>
       <c r="K48" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L48" s="4">
-        <v>46090</v>
-      </c>
-      <c r="N48" s="4">
+        <v>46055</v>
+      </c>
+      <c r="M48" s="4">
         <v>46085</v>
       </c>
+      <c r="N48" s="6"/>
+      <c r="O48" s="6"/>
       <c r="P48" s="4">
-        <v>46087</v>
-      </c>
-    </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.3">
+        <v>46085</v>
+      </c>
+      <c r="Q48" s="4">
+        <v>46093</v>
+      </c>
+      <c r="R48" s="4">
+        <v>46094</v>
+      </c>
+      <c r="S48" s="4">
+        <v>46094</v>
+      </c>
+      <c r="T48" s="4">
+        <v>46094</v>
+      </c>
+      <c r="V48" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="W48" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X48" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="Y48" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="49" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
         <v>151</v>
       </c>
@@ -4659,7 +4928,7 @@
         <v>28</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J49" s="2">
         <v>1</v>
@@ -4670,14 +4939,27 @@
       <c r="L49" s="4">
         <v>46090</v>
       </c>
+      <c r="M49" s="12"/>
       <c r="N49" s="4">
         <v>46085</v>
       </c>
+      <c r="O49" s="4">
+        <v>46086</v>
+      </c>
       <c r="P49" s="4">
         <v>46087</v>
       </c>
-    </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="V49" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="W49" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="X49" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="50" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
         <v>151</v>
       </c>
@@ -4703,7 +4985,7 @@
         <v>28</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="J50" s="2">
         <v>1</v>
@@ -4714,14 +4996,27 @@
       <c r="L50" s="4">
         <v>46090</v>
       </c>
+      <c r="M50" s="12"/>
       <c r="N50" s="4">
         <v>46085</v>
       </c>
+      <c r="O50" s="4">
+        <v>46086</v>
+      </c>
       <c r="P50" s="4">
         <v>46087</v>
       </c>
-    </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="V50" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="W50" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="X50" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="51" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
         <v>151</v>
       </c>
@@ -4747,7 +5042,7 @@
         <v>28</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J51" s="2">
         <v>1</v>
@@ -4758,14 +5053,27 @@
       <c r="L51" s="4">
         <v>46090</v>
       </c>
+      <c r="M51" s="12"/>
       <c r="N51" s="4">
         <v>46085</v>
       </c>
+      <c r="O51" s="4">
+        <v>46086</v>
+      </c>
       <c r="P51" s="4">
         <v>46087</v>
       </c>
-    </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="V51" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="W51" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="X51" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="52" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
         <v>151</v>
       </c>
@@ -4791,7 +5099,7 @@
         <v>28</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="J52" s="2">
         <v>1</v>
@@ -4802,14 +5110,27 @@
       <c r="L52" s="4">
         <v>46090</v>
       </c>
+      <c r="M52" s="12"/>
       <c r="N52" s="4">
         <v>46085</v>
       </c>
+      <c r="O52" s="4">
+        <v>46086</v>
+      </c>
       <c r="P52" s="4">
         <v>46087</v>
       </c>
-    </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="V52" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="W52" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="X52" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="53" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
         <v>151</v>
       </c>
@@ -4835,7 +5156,7 @@
         <v>28</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="J53" s="2">
         <v>1</v>
@@ -4846,14 +5167,27 @@
       <c r="L53" s="4">
         <v>46090</v>
       </c>
+      <c r="M53" s="12"/>
       <c r="N53" s="4">
         <v>46085</v>
       </c>
+      <c r="O53" s="4">
+        <v>46086</v>
+      </c>
       <c r="P53" s="4">
         <v>46087</v>
       </c>
-    </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="V53" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="W53" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="X53" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="54" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
         <v>151</v>
       </c>
@@ -4878,8 +5212,8 @@
       <c r="H54" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I54" s="11" t="s">
-        <v>161</v>
+      <c r="I54" s="2" t="s">
+        <v>160</v>
       </c>
       <c r="J54" s="2">
         <v>1</v>
@@ -4890,14 +5224,27 @@
       <c r="L54" s="4">
         <v>46090</v>
       </c>
+      <c r="M54" s="12"/>
       <c r="N54" s="4">
         <v>46085</v>
       </c>
+      <c r="O54" s="4">
+        <v>46086</v>
+      </c>
       <c r="P54" s="4">
         <v>46087</v>
       </c>
-    </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="V54" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="W54" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="X54" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="55" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
         <v>151</v>
       </c>
@@ -4922,8 +5269,8 @@
       <c r="H55" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I55" s="11" t="s">
-        <v>162</v>
+      <c r="I55" s="2" t="s">
+        <v>187</v>
       </c>
       <c r="J55" s="2">
         <v>1</v>
@@ -4934,14 +5281,27 @@
       <c r="L55" s="4">
         <v>46090</v>
       </c>
+      <c r="M55" s="12"/>
       <c r="N55" s="4">
         <v>46085</v>
       </c>
+      <c r="O55" s="4">
+        <v>46086</v>
+      </c>
       <c r="P55" s="4">
         <v>46087</v>
       </c>
-    </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="V55" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="W55" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="X55" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="56" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
         <v>151</v>
       </c>
@@ -4967,7 +5327,7 @@
         <v>28</v>
       </c>
       <c r="I56" s="11" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="J56" s="2">
         <v>1</v>
@@ -4978,31 +5338,44 @@
       <c r="L56" s="4">
         <v>46090</v>
       </c>
+      <c r="M56" s="12"/>
       <c r="N56" s="4">
         <v>46085</v>
       </c>
+      <c r="O56" s="4">
+        <v>46086</v>
+      </c>
       <c r="P56" s="4">
         <v>46087</v>
       </c>
-    </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="V56" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="W56" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="X56" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="57" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
-        <v>182</v>
+        <v>151</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>183</v>
+        <v>152</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>184</v>
+        <v>153</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>185</v>
+        <v>154</v>
       </c>
       <c r="F57" s="3">
-        <v>0.55000000000000004</v>
+        <v>0.45</v>
       </c>
       <c r="G57" s="7">
         <v>14.2</v>
@@ -5011,7 +5384,7 @@
         <v>28</v>
       </c>
       <c r="I57" s="11" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="J57" s="2">
         <v>1</v>
@@ -5020,27 +5393,46 @@
         <v>1</v>
       </c>
       <c r="L57" s="4">
+        <v>46090</v>
+      </c>
+      <c r="M57" s="12"/>
+      <c r="N57" s="4">
+        <v>46085</v>
+      </c>
+      <c r="O57" s="4">
         <v>46086</v>
       </c>
-    </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="P57" s="4">
+        <v>46087</v>
+      </c>
+      <c r="V57" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="W57" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="X57" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="58" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
-        <v>182</v>
+        <v>151</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>183</v>
+        <v>152</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>184</v>
+        <v>153</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>185</v>
+        <v>154</v>
       </c>
       <c r="F58" s="3">
-        <v>0.55000000000000004</v>
+        <v>0.45</v>
       </c>
       <c r="G58" s="7">
         <v>14.2</v>
@@ -5049,7 +5441,7 @@
         <v>28</v>
       </c>
       <c r="I58" s="11" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="J58" s="2">
         <v>1</v>
@@ -5058,24 +5450,43 @@
         <v>1</v>
       </c>
       <c r="L58" s="4">
+        <v>46090</v>
+      </c>
+      <c r="M58" s="12"/>
+      <c r="N58" s="4">
+        <v>46085</v>
+      </c>
+      <c r="O58" s="4">
         <v>46086</v>
       </c>
-    </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="P58" s="4">
+        <v>46087</v>
+      </c>
+      <c r="V58" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="W58" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="X58" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="59" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>27</v>
+        <v>175</v>
       </c>
       <c r="F59" s="3">
         <v>0.55000000000000004</v>
@@ -5087,7 +5498,7 @@
         <v>28</v>
       </c>
       <c r="I59" s="11" t="s">
-        <v>166</v>
+        <v>200</v>
       </c>
       <c r="J59" s="2">
         <v>1</v>
@@ -5098,22 +5509,43 @@
       <c r="L59" s="4">
         <v>46086</v>
       </c>
-    </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="P59" s="4">
+        <v>46094</v>
+      </c>
+      <c r="S59" s="4">
+        <v>46112</v>
+      </c>
+      <c r="T59" s="4">
+        <v>46112</v>
+      </c>
+      <c r="V59" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="W59" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X59" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="Y59" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="60" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>27</v>
+        <v>175</v>
       </c>
       <c r="F60" s="3">
         <v>0.55000000000000004</v>
@@ -5125,7 +5557,7 @@
         <v>28</v>
       </c>
       <c r="I60" s="11" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="J60" s="2">
         <v>1</v>
@@ -5136,16 +5568,37 @@
       <c r="L60" s="4">
         <v>46086</v>
       </c>
-    </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="P60" s="4">
+        <v>46094</v>
+      </c>
+      <c r="S60" s="4">
+        <v>46112</v>
+      </c>
+      <c r="T60" s="4">
+        <v>46112</v>
+      </c>
+      <c r="V60" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="W60" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X60" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="Y60" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="61" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>26</v>
@@ -5163,7 +5616,7 @@
         <v>28</v>
       </c>
       <c r="I61" s="11" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="J61" s="2">
         <v>1</v>
@@ -5174,16 +5627,37 @@
       <c r="L61" s="4">
         <v>46086</v>
       </c>
-    </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="P61" s="4">
+        <v>46094</v>
+      </c>
+      <c r="S61" s="4">
+        <v>46112</v>
+      </c>
+      <c r="T61" s="4">
+        <v>46112</v>
+      </c>
+      <c r="V61" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="W61" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X61" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="Y61" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="62" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>26</v>
@@ -5201,7 +5675,7 @@
         <v>28</v>
       </c>
       <c r="I62" s="11" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="J62" s="2">
         <v>1</v>
@@ -5212,16 +5686,37 @@
       <c r="L62" s="4">
         <v>46086</v>
       </c>
-    </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="P62" s="4">
+        <v>46094</v>
+      </c>
+      <c r="S62" s="4">
+        <v>46112</v>
+      </c>
+      <c r="T62" s="4">
+        <v>46112</v>
+      </c>
+      <c r="V62" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="W62" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X62" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="Y62" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="63" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>26</v>
@@ -5239,7 +5734,7 @@
         <v>28</v>
       </c>
       <c r="I63" s="11" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="J63" s="2">
         <v>1</v>
@@ -5250,16 +5745,37 @@
       <c r="L63" s="4">
         <v>46086</v>
       </c>
-    </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="P63" s="4">
+        <v>46094</v>
+      </c>
+      <c r="S63" s="4">
+        <v>46112</v>
+      </c>
+      <c r="T63" s="4">
+        <v>46112</v>
+      </c>
+      <c r="V63" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="W63" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X63" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="Y63" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="64" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>26</v>
@@ -5277,7 +5793,7 @@
         <v>28</v>
       </c>
       <c r="I64" s="11" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="J64" s="2">
         <v>1</v>
@@ -5288,16 +5804,37 @@
       <c r="L64" s="4">
         <v>46086</v>
       </c>
-    </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="P64" s="4">
+        <v>46094</v>
+      </c>
+      <c r="S64" s="4">
+        <v>46112</v>
+      </c>
+      <c r="T64" s="4">
+        <v>46112</v>
+      </c>
+      <c r="V64" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="W64" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X64" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="Y64" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="65" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>26</v>
@@ -5315,7 +5852,7 @@
         <v>28</v>
       </c>
       <c r="I65" s="11" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="J65" s="2">
         <v>1</v>
@@ -5326,16 +5863,37 @@
       <c r="L65" s="4">
         <v>46086</v>
       </c>
-    </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="P65" s="4">
+        <v>46094</v>
+      </c>
+      <c r="S65" s="4">
+        <v>46112</v>
+      </c>
+      <c r="T65" s="4">
+        <v>46112</v>
+      </c>
+      <c r="V65" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="W65" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X65" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="Y65" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="66" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>26</v>
@@ -5353,7 +5911,7 @@
         <v>28</v>
       </c>
       <c r="I66" s="11" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="J66" s="2">
         <v>1</v>
@@ -5364,16 +5922,37 @@
       <c r="L66" s="4">
         <v>46086</v>
       </c>
-    </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="P66" s="4">
+        <v>46094</v>
+      </c>
+      <c r="S66" s="4">
+        <v>46112</v>
+      </c>
+      <c r="T66" s="4">
+        <v>46112</v>
+      </c>
+      <c r="V66" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="W66" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X66" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="Y66" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="67" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>26</v>
@@ -5391,7 +5970,7 @@
         <v>28</v>
       </c>
       <c r="I67" s="11" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="J67" s="2">
         <v>1</v>
@@ -5402,16 +5981,37 @@
       <c r="L67" s="4">
         <v>46086</v>
       </c>
-    </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="P67" s="4">
+        <v>46094</v>
+      </c>
+      <c r="S67" s="4">
+        <v>46112</v>
+      </c>
+      <c r="T67" s="4">
+        <v>46112</v>
+      </c>
+      <c r="V67" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="W67" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X67" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="Y67" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="68" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>26</v>
@@ -5429,7 +6029,7 @@
         <v>28</v>
       </c>
       <c r="I68" s="11" t="s">
-        <v>175</v>
+        <v>201</v>
       </c>
       <c r="J68" s="2">
         <v>1</v>
@@ -5440,16 +6040,37 @@
       <c r="L68" s="4">
         <v>46086</v>
       </c>
-    </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="P68" s="4">
+        <v>46094</v>
+      </c>
+      <c r="S68" s="4">
+        <v>46112</v>
+      </c>
+      <c r="T68" s="4">
+        <v>46112</v>
+      </c>
+      <c r="V68" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="W68" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X68" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="Y68" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="69" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>26</v>
@@ -5467,7 +6088,7 @@
         <v>28</v>
       </c>
       <c r="I69" s="11" t="s">
-        <v>176</v>
+        <v>202</v>
       </c>
       <c r="J69" s="2">
         <v>1</v>
@@ -5478,16 +6099,37 @@
       <c r="L69" s="4">
         <v>46086</v>
       </c>
-    </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="P69" s="4">
+        <v>46094</v>
+      </c>
+      <c r="S69" s="4">
+        <v>46112</v>
+      </c>
+      <c r="T69" s="4">
+        <v>46112</v>
+      </c>
+      <c r="V69" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="W69" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X69" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="Y69" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="70" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>26</v>
@@ -5505,7 +6147,7 @@
         <v>28</v>
       </c>
       <c r="I70" s="11" t="s">
-        <v>177</v>
+        <v>203</v>
       </c>
       <c r="J70" s="2">
         <v>1</v>
@@ -5516,16 +6158,37 @@
       <c r="L70" s="4">
         <v>46086</v>
       </c>
-    </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="P70" s="4">
+        <v>46094</v>
+      </c>
+      <c r="S70" s="4">
+        <v>46112</v>
+      </c>
+      <c r="T70" s="4">
+        <v>46112</v>
+      </c>
+      <c r="V70" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="W70" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X70" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="Y70" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="71" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>26</v>
@@ -5543,7 +6206,7 @@
         <v>28</v>
       </c>
       <c r="I71" s="11" t="s">
-        <v>178</v>
+        <v>204</v>
       </c>
       <c r="J71" s="2">
         <v>1</v>
@@ -5554,16 +6217,37 @@
       <c r="L71" s="4">
         <v>46086</v>
       </c>
-    </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="P71" s="4">
+        <v>46094</v>
+      </c>
+      <c r="S71" s="4">
+        <v>46112</v>
+      </c>
+      <c r="T71" s="4">
+        <v>46112</v>
+      </c>
+      <c r="V71" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="W71" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X71" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="Y71" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="72" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>26</v>
@@ -5581,7 +6265,7 @@
         <v>28</v>
       </c>
       <c r="I72" s="11" t="s">
-        <v>179</v>
+        <v>205</v>
       </c>
       <c r="J72" s="2">
         <v>1</v>
@@ -5592,16 +6276,37 @@
       <c r="L72" s="4">
         <v>46086</v>
       </c>
-    </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="P72" s="4">
+        <v>46094</v>
+      </c>
+      <c r="S72" s="4">
+        <v>46112</v>
+      </c>
+      <c r="T72" s="4">
+        <v>46112</v>
+      </c>
+      <c r="V72" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="W72" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X72" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="Y72" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="73" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>26</v>
@@ -5619,7 +6324,7 @@
         <v>28</v>
       </c>
       <c r="I73" s="11" t="s">
-        <v>180</v>
+        <v>207</v>
       </c>
       <c r="J73" s="2">
         <v>1</v>
@@ -5630,16 +6335,37 @@
       <c r="L73" s="4">
         <v>46086</v>
       </c>
-    </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="P73" s="4">
+        <v>46094</v>
+      </c>
+      <c r="S73" s="4">
+        <v>46112</v>
+      </c>
+      <c r="T73" s="4">
+        <v>46112</v>
+      </c>
+      <c r="V73" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="W73" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X73" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="Y73" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="74" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>26</v>
@@ -5657,7 +6383,7 @@
         <v>28</v>
       </c>
       <c r="I74" s="11" t="s">
-        <v>181</v>
+        <v>206</v>
       </c>
       <c r="J74" s="2">
         <v>1</v>
@@ -5668,19 +6394,40 @@
       <c r="L74" s="4">
         <v>46086</v>
       </c>
-    </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="P74" s="4">
+        <v>46094</v>
+      </c>
+      <c r="S74" s="4">
+        <v>46112</v>
+      </c>
+      <c r="T74" s="4">
+        <v>46112</v>
+      </c>
+      <c r="V74" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="W74" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X74" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="Y74" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="75" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
-        <v>151</v>
+        <v>172</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>152</v>
+        <v>173</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>153</v>
+        <v>174</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>27</v>
@@ -5689,13 +6436,13 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G75" s="7">
-        <v>14.5</v>
+        <v>14.2</v>
       </c>
       <c r="H75" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I75" s="2" t="s">
-        <v>186</v>
+      <c r="I75" s="11" t="s">
+        <v>208</v>
       </c>
       <c r="J75" s="2">
         <v>1</v>
@@ -5704,21 +6451,42 @@
         <v>1</v>
       </c>
       <c r="L75" s="4">
-        <v>46092</v>
-      </c>
-    </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
+        <v>46086</v>
+      </c>
+      <c r="P75" s="4">
+        <v>46094</v>
+      </c>
+      <c r="S75" s="4">
+        <v>46112</v>
+      </c>
+      <c r="T75" s="4">
+        <v>46112</v>
+      </c>
+      <c r="V75" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="W75" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X75" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="Y75" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="76" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
-        <v>151</v>
+        <v>172</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>152</v>
+        <v>173</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>153</v>
+        <v>174</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>27</v>
@@ -5727,13 +6495,13 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G76" s="7">
-        <v>14.5</v>
+        <v>14.2</v>
       </c>
       <c r="H76" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I76" s="2" t="s">
-        <v>187</v>
+      <c r="I76" s="11" t="s">
+        <v>209</v>
       </c>
       <c r="J76" s="2">
         <v>1</v>
@@ -5742,21 +6510,42 @@
         <v>1</v>
       </c>
       <c r="L76" s="4">
-        <v>46092</v>
-      </c>
-    </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
+        <v>46086</v>
+      </c>
+      <c r="P76" s="4">
+        <v>46094</v>
+      </c>
+      <c r="S76" s="4">
+        <v>46112</v>
+      </c>
+      <c r="T76" s="4">
+        <v>46112</v>
+      </c>
+      <c r="V76" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="W76" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X76" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="Y76" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="77" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
-        <v>151</v>
+        <v>172</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>152</v>
+        <v>173</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>153</v>
+        <v>174</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>27</v>
@@ -5765,13 +6554,13 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G77" s="7">
-        <v>14.5</v>
+        <v>14.2</v>
       </c>
       <c r="H77" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I77" s="2" t="s">
-        <v>188</v>
+      <c r="I77" s="11" t="s">
+        <v>210</v>
       </c>
       <c r="J77" s="2">
         <v>1</v>
@@ -5780,21 +6569,42 @@
         <v>1</v>
       </c>
       <c r="L77" s="4">
-        <v>46092</v>
-      </c>
-    </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
+        <v>46086</v>
+      </c>
+      <c r="P77" s="4">
+        <v>46094</v>
+      </c>
+      <c r="S77" s="4">
+        <v>46112</v>
+      </c>
+      <c r="T77" s="4">
+        <v>46112</v>
+      </c>
+      <c r="V77" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="W77" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X77" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="Y77" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="78" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
-        <v>151</v>
+        <v>172</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>152</v>
+        <v>173</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>153</v>
+        <v>174</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>27</v>
@@ -5803,40 +6613,1083 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G78" s="7">
+        <v>14.2</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I78" s="11" t="s">
+        <v>211</v>
+      </c>
+      <c r="J78" s="2">
+        <v>1</v>
+      </c>
+      <c r="K78" s="2">
+        <v>1</v>
+      </c>
+      <c r="L78" s="4">
+        <v>46086</v>
+      </c>
+      <c r="P78" s="4">
+        <v>46094</v>
+      </c>
+      <c r="S78" s="4">
+        <v>46112</v>
+      </c>
+      <c r="T78" s="4">
+        <v>46112</v>
+      </c>
+      <c r="V78" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="W78" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X78" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="Y78" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="79" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A79" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F79" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G79" s="7">
+        <v>14.2</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I79" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="J79" s="2">
+        <v>1</v>
+      </c>
+      <c r="K79" s="2">
+        <v>1</v>
+      </c>
+      <c r="L79" s="4">
+        <v>46086</v>
+      </c>
+      <c r="P79" s="4">
+        <v>46094</v>
+      </c>
+      <c r="S79" s="4">
+        <v>46112</v>
+      </c>
+      <c r="T79" s="4">
+        <v>46112</v>
+      </c>
+      <c r="V79" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="W79" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X79" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="Y79" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="80" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A80" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F80" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G80" s="7">
+        <v>14.2</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I80" s="11" t="s">
+        <v>213</v>
+      </c>
+      <c r="J80" s="2">
+        <v>1</v>
+      </c>
+      <c r="K80" s="2">
+        <v>1</v>
+      </c>
+      <c r="L80" s="4">
+        <v>46086</v>
+      </c>
+      <c r="P80" s="4">
+        <v>46094</v>
+      </c>
+      <c r="S80" s="4">
+        <v>46112</v>
+      </c>
+      <c r="T80" s="4">
+        <v>46112</v>
+      </c>
+      <c r="V80" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="W80" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X80" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="Y80" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="81" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A81" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F81" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G81" s="7">
+        <v>14.2</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I81" s="11" t="s">
+        <v>214</v>
+      </c>
+      <c r="J81" s="2">
+        <v>1</v>
+      </c>
+      <c r="K81" s="2">
+        <v>1</v>
+      </c>
+      <c r="L81" s="4">
+        <v>46086</v>
+      </c>
+      <c r="P81" s="4">
+        <v>46094</v>
+      </c>
+      <c r="S81" s="4">
+        <v>46112</v>
+      </c>
+      <c r="T81" s="4">
+        <v>46112</v>
+      </c>
+      <c r="V81" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="W81" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X81" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="Y81" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="82" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A82" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F82" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G82" s="7">
+        <v>14.2</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I82" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="J82" s="2">
+        <v>1</v>
+      </c>
+      <c r="K82" s="2">
+        <v>1</v>
+      </c>
+      <c r="L82" s="4">
+        <v>46086</v>
+      </c>
+      <c r="P82" s="4">
+        <v>46094</v>
+      </c>
+      <c r="S82" s="4">
+        <v>46112</v>
+      </c>
+      <c r="T82" s="4">
+        <v>46112</v>
+      </c>
+      <c r="V82" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="W82" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X82" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="Y82" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="83" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A83" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F83" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G83" s="7">
+        <v>14.2</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I83" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="J83" s="2">
+        <v>1</v>
+      </c>
+      <c r="K83" s="2">
+        <v>1</v>
+      </c>
+      <c r="L83" s="4">
+        <v>46086</v>
+      </c>
+      <c r="P83" s="4">
+        <v>46094</v>
+      </c>
+      <c r="S83" s="4">
+        <v>46112</v>
+      </c>
+      <c r="T83" s="4">
+        <v>46112</v>
+      </c>
+      <c r="V83" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="W83" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X83" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="Y83" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="84" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A84" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F84" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G84" s="7">
+        <v>14.2</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I84" s="11" t="s">
+        <v>217</v>
+      </c>
+      <c r="J84" s="2">
+        <v>1</v>
+      </c>
+      <c r="K84" s="2">
+        <v>1</v>
+      </c>
+      <c r="L84" s="4">
+        <v>46086</v>
+      </c>
+      <c r="P84" s="4">
+        <v>46094</v>
+      </c>
+      <c r="S84" s="4">
+        <v>46112</v>
+      </c>
+      <c r="T84" s="4">
+        <v>46112</v>
+      </c>
+      <c r="V84" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="W84" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X84" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="Y84" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="85" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A85" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F85" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G85" s="7">
         <v>14.5</v>
       </c>
-      <c r="H78" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="I78" s="2" t="s">
+      <c r="H85" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I85" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="J85" s="2">
+        <v>1</v>
+      </c>
+      <c r="K85" s="2">
+        <v>1</v>
+      </c>
+      <c r="L85" s="4">
+        <v>46092</v>
+      </c>
+      <c r="M85" s="12"/>
+      <c r="N85" s="4">
+        <v>46093</v>
+      </c>
+      <c r="O85" s="4">
+        <v>46094</v>
+      </c>
+      <c r="V85" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="W85" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="X85" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="Y85" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="86" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A86" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F86" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G86" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I86" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="J86" s="2">
+        <v>1</v>
+      </c>
+      <c r="K86" s="2">
+        <v>1</v>
+      </c>
+      <c r="L86" s="4">
+        <v>46092</v>
+      </c>
+      <c r="M86" s="12"/>
+      <c r="N86" s="4">
+        <v>46093</v>
+      </c>
+      <c r="O86" s="4">
+        <v>46094</v>
+      </c>
+      <c r="V86" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="W86" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="X86" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="Y86" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="87" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A87" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F87" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G87" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I87" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="J87" s="2">
+        <v>1</v>
+      </c>
+      <c r="K87" s="2">
+        <v>1</v>
+      </c>
+      <c r="L87" s="4">
+        <v>46092</v>
+      </c>
+      <c r="M87" s="12"/>
+      <c r="N87" s="4">
+        <v>46093</v>
+      </c>
+      <c r="O87" s="4">
+        <v>46094</v>
+      </c>
+      <c r="V87" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="W87" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="X87" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="Y87" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="88" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A88" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F88" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G88" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I88" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="J88" s="2">
+        <v>1</v>
+      </c>
+      <c r="K88" s="2">
+        <v>1</v>
+      </c>
+      <c r="L88" s="4">
+        <v>46092</v>
+      </c>
+      <c r="M88" s="12"/>
+      <c r="N88" s="4">
+        <v>46093</v>
+      </c>
+      <c r="O88" s="4">
+        <v>46094</v>
+      </c>
+      <c r="V88" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="W88" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="X88" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="Y88" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="89" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A89" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B89" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="J78" s="2">
-        <v>1</v>
-      </c>
-      <c r="K78" s="2">
-        <v>1</v>
-      </c>
-      <c r="L78" s="4">
-        <v>46092</v>
+      <c r="C89" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F89" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G89" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I89" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="J89" s="2">
+        <v>1</v>
+      </c>
+      <c r="K89" s="2">
+        <v>1</v>
+      </c>
+      <c r="L89" s="4">
+        <v>46094</v>
+      </c>
+      <c r="V89" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="W89" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="X89" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="Y89" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="90" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A90" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F90" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G90" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I90" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="J90" s="2">
+        <v>1</v>
+      </c>
+      <c r="K90" s="2">
+        <v>1</v>
+      </c>
+      <c r="L90" s="4">
+        <v>46094</v>
+      </c>
+      <c r="V90" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="W90" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="X90" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="Y90" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="91" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A91" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F91" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G91" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I91" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="J91" s="2">
+        <v>1</v>
+      </c>
+      <c r="K91" s="2">
+        <v>1</v>
+      </c>
+      <c r="L91" s="4">
+        <v>46094</v>
+      </c>
+      <c r="V91" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="W91" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="X91" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="Y91" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="92" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A92" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F92" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G92" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I92" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="J92" s="2">
+        <v>1</v>
+      </c>
+      <c r="K92" s="2">
+        <v>1</v>
+      </c>
+      <c r="L92" s="4">
+        <v>46094</v>
+      </c>
+      <c r="V92" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="W92" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="X92" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="Y92" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="93" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A93" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F93" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G93" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I93" s="13" t="s">
+        <v>194</v>
+      </c>
+      <c r="J93" s="2">
+        <v>1</v>
+      </c>
+      <c r="K93" s="2">
+        <v>1</v>
+      </c>
+      <c r="L93" s="4">
+        <v>46094</v>
+      </c>
+      <c r="V93" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="W93" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="X93" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="Y93" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="94" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A94" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F94" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G94" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I94" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="J94" s="2">
+        <v>1</v>
+      </c>
+      <c r="K94" s="2">
+        <v>1</v>
+      </c>
+      <c r="L94" s="4">
+        <v>46098</v>
+      </c>
+      <c r="V94" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="W94" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="X94" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="Y94" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="95" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A95" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F95" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G95" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I95" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="J95" s="2">
+        <v>1</v>
+      </c>
+      <c r="K95" s="2">
+        <v>1</v>
+      </c>
+      <c r="L95" s="4">
+        <v>46098</v>
+      </c>
+      <c r="V95" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="W95" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="X95" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="Y95" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="96" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A96" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F96" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G96" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I96" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="J96" s="2">
+        <v>1</v>
+      </c>
+      <c r="K96" s="2">
+        <v>1</v>
+      </c>
+      <c r="L96" s="4">
+        <v>46098</v>
+      </c>
+      <c r="V96" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="W96" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="X96" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="Y96" s="2" t="s">
+        <v>58</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="V1:V41"/>
+  <autoFilter ref="V1:V42"/>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="I54:I56">
-    <cfRule type="expression" dxfId="2" priority="3" stopIfTrue="1">
-      <formula>$E3102:$E1048571="sub"</formula>
+  <conditionalFormatting sqref="I59:I66">
+    <cfRule type="expression" dxfId="10" priority="5" stopIfTrue="1">
+      <formula>$E3101:$E1048570="sub"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I65 I74">
-    <cfRule type="expression" dxfId="1" priority="2" stopIfTrue="1">
-      <formula>$E3105:$E1048574="sub"</formula>
+  <conditionalFormatting sqref="I56:I58">
+    <cfRule type="expression" dxfId="9" priority="11" stopIfTrue="1">
+      <formula>$E3106:$E1048575="sub"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I57:I64 I66:I73">
-    <cfRule type="expression" dxfId="0" priority="1" stopIfTrue="1">
-      <formula>$E3098:$E1048567="sub"</formula>
+  <conditionalFormatting sqref="I80">
+    <cfRule type="expression" dxfId="8" priority="15" stopIfTrue="1">
+      <formula>$E10:$E3124="sub"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I79">
+    <cfRule type="expression" dxfId="7" priority="19" stopIfTrue="1">
+      <formula>$E10:$E3124="sub"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I78">
+    <cfRule type="expression" dxfId="6" priority="23" stopIfTrue="1">
+      <formula>$E10:$E3124="sub"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I84">
+    <cfRule type="expression" dxfId="5" priority="45" stopIfTrue="1">
+      <formula>$E11:$E3125="sub"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I83">
+    <cfRule type="expression" dxfId="4" priority="50" stopIfTrue="1">
+      <formula>$E11:$E3125="sub"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I81:I82">
+    <cfRule type="expression" dxfId="3" priority="54" stopIfTrue="1">
+      <formula>$E10:$E3124="sub"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I76:I77">
+    <cfRule type="expression" dxfId="2" priority="55" stopIfTrue="1">
+      <formula>$E9:$E3123="sub"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I67">
+    <cfRule type="expression" dxfId="1" priority="56" stopIfTrue="1">
+      <formula>$E3115:$E1048576="sub"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I68:I75">
+    <cfRule type="expression" dxfId="0" priority="57" stopIfTrue="1">
+      <formula>$E2:$E3117="sub"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5848,55 +7701,55 @@
           <x14:formula1>
             <xm:f>Sheet2!$F$2:$F$4</xm:f>
           </x14:formula1>
-          <xm:sqref>W42:W1048576 Y42 W2:W40</xm:sqref>
+          <xm:sqref>W2:W41 Y43 W43:W1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>Sheet2!$G$2:$G$5</xm:f>
           </x14:formula1>
-          <xm:sqref>X42:X1048576 X2:X40</xm:sqref>
+          <xm:sqref>X2:X41 X43:X1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>Sheet2!$E$2:$E$4</xm:f>
           </x14:formula1>
-          <xm:sqref>H42:H1048576 H2:H40</xm:sqref>
+          <xm:sqref>H2:H41 H43:H1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>Sheet2!$D$2:$D$5</xm:f>
           </x14:formula1>
-          <xm:sqref>G42:G1048576 G2:G40</xm:sqref>
+          <xm:sqref>G2:G41 G43:G1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>Sheet2!$C$2:$C$5</xm:f>
           </x14:formula1>
-          <xm:sqref>F42:F1048576 F2:F40</xm:sqref>
+          <xm:sqref>F2:F41 F43:F1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>Sheet2!$B$2:$B$3</xm:f>
           </x14:formula1>
-          <xm:sqref>E42:E1048576 E2:E40</xm:sqref>
+          <xm:sqref>E2:E41 E43:E1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>Sheet2!$A$2:$A$4</xm:f>
           </x14:formula1>
-          <xm:sqref>D42:D1048576 D2:D40</xm:sqref>
+          <xm:sqref>D2:D41 D43:D1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'[복사본 sample-list.xlsx]Sheet2'!#REF!</xm:f>
           </x14:formula1>
-          <xm:sqref>D41:H41 W41:X41</xm:sqref>
+          <xm:sqref>D42:H42 W42:X42</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>Sheet2!$H$2:$H$7</xm:f>
           </x14:formula1>
-          <xm:sqref>Y43:Y1048576 Y2:Y41</xm:sqref>
+          <xm:sqref>Y2:Y42 Y44:Y1048576</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/sample-list.xlsx
+++ b/sample-list.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1086" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1196" uniqueCount="230">
   <si>
     <t>국가</t>
   </si>
@@ -869,14 +869,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Winsome brown 1M -2.00</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Winsome brown 1M -2.25</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Winsome brown 1M -3.00</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -885,10 +877,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Winsome brown 1M -3.25</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Winsome brown 1M -3.75</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -897,22 +885,10 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Winsome brown 1M -4.25</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Winsome brown 1M -4.50</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Winsome brown 1M -5.00</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Winsome brown 1M -5.25</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Winsome brown 1M -5.50</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -921,11 +897,65 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Winsome brown 1M -6.00</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Winsome brown 1M -7.50</t>
+    <t>Mystical Black 1D -2.00</t>
+  </si>
+  <si>
+    <t>Mystical Black 1D -2.25</t>
+  </si>
+  <si>
+    <t>Mystical Black 1D -3.25</t>
+  </si>
+  <si>
+    <t>Mystical Black 1D -3.5</t>
+  </si>
+  <si>
+    <t>Mystical Black 1D -4.25</t>
+  </si>
+  <si>
+    <t>Mystical Black 1D -5.00</t>
+  </si>
+  <si>
+    <t>Mystical Black 1D -5.25</t>
+  </si>
+  <si>
+    <t>Mystical Black 1D -6.00</t>
+  </si>
+  <si>
+    <t>Shimmering Gray 1D -2.00</t>
+  </si>
+  <si>
+    <t>Shimmering Gray 1D -2.25</t>
+  </si>
+  <si>
+    <t>Shimmering Gray 1D -3.00</t>
+  </si>
+  <si>
+    <t>Shimmering Gray 1D -3.25</t>
+  </si>
+  <si>
+    <t>Shimmering Gray 1D -3.50</t>
+  </si>
+  <si>
+    <t>Shimmering Gray 1D -4.25</t>
+  </si>
+  <si>
+    <t>Shimmering Gray 1D -5.25</t>
+  </si>
+  <si>
+    <t>Shimmering Gray 1D -7.50</t>
+  </si>
+  <si>
+    <t>류미리</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Brilliant Brown 1M -3.00</t>
+  </si>
+  <si>
+    <t>Misty Grey 1M -3.00</t>
+  </si>
+  <si>
+    <t>임수빈</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1079,7 +1109,84 @@
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="11">
+  <dxfs count="22">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1468,7 +1575,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AB96"/>
+  <dimension ref="A1:AB106"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.25" style="2" customWidth="1"/>
@@ -4140,6 +4247,15 @@
       <c r="Q37" s="4">
         <v>46100</v>
       </c>
+      <c r="R37" s="4">
+        <v>46101</v>
+      </c>
+      <c r="S37" s="4">
+        <v>46104</v>
+      </c>
+      <c r="T37" s="4">
+        <v>46104</v>
+      </c>
       <c r="V37" s="2" t="s">
         <v>117</v>
       </c>
@@ -4147,7 +4263,7 @@
         <v>29</v>
       </c>
       <c r="X37" s="2" t="s">
-        <v>100</v>
+        <v>53</v>
       </c>
     </row>
     <row r="38" spans="1:25" x14ac:dyDescent="0.3">
@@ -4949,6 +5065,9 @@
       <c r="P49" s="4">
         <v>46087</v>
       </c>
+      <c r="T49" s="4">
+        <v>46100</v>
+      </c>
       <c r="V49" s="2" t="s">
         <v>186</v>
       </c>
@@ -5006,6 +5125,9 @@
       <c r="P50" s="4">
         <v>46087</v>
       </c>
+      <c r="T50" s="4">
+        <v>46100</v>
+      </c>
       <c r="V50" s="2" t="s">
         <v>186</v>
       </c>
@@ -5063,6 +5185,9 @@
       <c r="P51" s="4">
         <v>46087</v>
       </c>
+      <c r="T51" s="4">
+        <v>46100</v>
+      </c>
       <c r="V51" s="2" t="s">
         <v>186</v>
       </c>
@@ -5512,6 +5637,9 @@
       <c r="P59" s="4">
         <v>46094</v>
       </c>
+      <c r="Q59" s="4">
+        <v>46103</v>
+      </c>
       <c r="S59" s="4">
         <v>46112</v>
       </c>
@@ -5571,6 +5699,9 @@
       <c r="P60" s="4">
         <v>46094</v>
       </c>
+      <c r="Q60" s="4">
+        <v>46103</v>
+      </c>
       <c r="S60" s="4">
         <v>46112</v>
       </c>
@@ -5630,6 +5761,9 @@
       <c r="P61" s="4">
         <v>46094</v>
       </c>
+      <c r="Q61" s="4">
+        <v>46103</v>
+      </c>
       <c r="S61" s="4">
         <v>46112</v>
       </c>
@@ -5689,6 +5823,9 @@
       <c r="P62" s="4">
         <v>46094</v>
       </c>
+      <c r="Q62" s="4">
+        <v>46103</v>
+      </c>
       <c r="S62" s="4">
         <v>46112</v>
       </c>
@@ -5748,6 +5885,9 @@
       <c r="P63" s="4">
         <v>46094</v>
       </c>
+      <c r="Q63" s="4">
+        <v>46103</v>
+      </c>
       <c r="S63" s="4">
         <v>46112</v>
       </c>
@@ -5807,6 +5947,9 @@
       <c r="P64" s="4">
         <v>46094</v>
       </c>
+      <c r="Q64" s="4">
+        <v>46103</v>
+      </c>
       <c r="S64" s="4">
         <v>46112</v>
       </c>
@@ -5866,6 +6009,9 @@
       <c r="P65" s="4">
         <v>46094</v>
       </c>
+      <c r="Q65" s="4">
+        <v>46103</v>
+      </c>
       <c r="S65" s="4">
         <v>46112</v>
       </c>
@@ -5925,6 +6071,9 @@
       <c r="P66" s="4">
         <v>46094</v>
       </c>
+      <c r="Q66" s="4">
+        <v>46103</v>
+      </c>
       <c r="S66" s="4">
         <v>46112</v>
       </c>
@@ -5984,6 +6133,9 @@
       <c r="P67" s="4">
         <v>46094</v>
       </c>
+      <c r="Q67" s="4">
+        <v>46103</v>
+      </c>
       <c r="S67" s="4">
         <v>46112</v>
       </c>
@@ -6043,6 +6195,9 @@
       <c r="P68" s="4">
         <v>46094</v>
       </c>
+      <c r="Q68" s="4">
+        <v>46103</v>
+      </c>
       <c r="S68" s="4">
         <v>46112</v>
       </c>
@@ -6102,6 +6257,9 @@
       <c r="P69" s="4">
         <v>46094</v>
       </c>
+      <c r="Q69" s="4">
+        <v>46103</v>
+      </c>
       <c r="S69" s="4">
         <v>46112</v>
       </c>
@@ -6161,6 +6319,9 @@
       <c r="P70" s="4">
         <v>46094</v>
       </c>
+      <c r="Q70" s="4">
+        <v>46103</v>
+      </c>
       <c r="S70" s="4">
         <v>46112</v>
       </c>
@@ -6220,6 +6381,9 @@
       <c r="P71" s="4">
         <v>46094</v>
       </c>
+      <c r="Q71" s="4">
+        <v>46103</v>
+      </c>
       <c r="S71" s="4">
         <v>46112</v>
       </c>
@@ -6279,6 +6443,9 @@
       <c r="P72" s="4">
         <v>46094</v>
       </c>
+      <c r="Q72" s="4">
+        <v>46103</v>
+      </c>
       <c r="S72" s="4">
         <v>46112</v>
       </c>
@@ -6324,7 +6491,7 @@
         <v>28</v>
       </c>
       <c r="I73" s="11" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="J73" s="2">
         <v>1</v>
@@ -6337,6 +6504,9 @@
       </c>
       <c r="P73" s="4">
         <v>46094</v>
+      </c>
+      <c r="Q73" s="4">
+        <v>46103</v>
       </c>
       <c r="S73" s="4">
         <v>46112</v>
@@ -6383,7 +6553,7 @@
         <v>28</v>
       </c>
       <c r="I74" s="11" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="J74" s="2">
         <v>1</v>
@@ -6396,6 +6566,9 @@
       </c>
       <c r="P74" s="4">
         <v>46094</v>
+      </c>
+      <c r="Q74" s="4">
+        <v>46103</v>
       </c>
       <c r="S74" s="4">
         <v>46112</v>
@@ -6456,6 +6629,9 @@
       <c r="P75" s="4">
         <v>46094</v>
       </c>
+      <c r="Q75" s="4">
+        <v>46103</v>
+      </c>
       <c r="S75" s="4">
         <v>46112</v>
       </c>
@@ -6515,6 +6691,9 @@
       <c r="P76" s="4">
         <v>46094</v>
       </c>
+      <c r="Q76" s="4">
+        <v>46103</v>
+      </c>
       <c r="S76" s="4">
         <v>46112</v>
       </c>
@@ -6542,7 +6721,7 @@
         <v>173</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>174</v>
+        <v>45</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>26</v>
@@ -6571,14 +6750,11 @@
       <c r="L77" s="4">
         <v>46086</v>
       </c>
-      <c r="P77" s="4">
-        <v>46094</v>
-      </c>
       <c r="S77" s="4">
-        <v>46112</v>
+        <v>46142</v>
       </c>
       <c r="T77" s="4">
-        <v>46112</v>
+        <v>46142</v>
       </c>
       <c r="V77" s="2" t="s">
         <v>149</v>
@@ -6587,7 +6763,7 @@
         <v>30</v>
       </c>
       <c r="X77" s="2" t="s">
-        <v>100</v>
+        <v>137</v>
       </c>
       <c r="Y77" s="2" t="s">
         <v>58</v>
@@ -6601,7 +6777,7 @@
         <v>173</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>174</v>
+        <v>45</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>26</v>
@@ -6630,14 +6806,11 @@
       <c r="L78" s="4">
         <v>46086</v>
       </c>
-      <c r="P78" s="4">
-        <v>46094</v>
-      </c>
       <c r="S78" s="4">
-        <v>46112</v>
+        <v>46142</v>
       </c>
       <c r="T78" s="4">
-        <v>46112</v>
+        <v>46142</v>
       </c>
       <c r="V78" s="2" t="s">
         <v>149</v>
@@ -6646,7 +6819,7 @@
         <v>30</v>
       </c>
       <c r="X78" s="2" t="s">
-        <v>100</v>
+        <v>137</v>
       </c>
       <c r="Y78" s="2" t="s">
         <v>58</v>
@@ -6660,7 +6833,7 @@
         <v>173</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>174</v>
+        <v>45</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>26</v>
@@ -6689,14 +6862,11 @@
       <c r="L79" s="4">
         <v>46086</v>
       </c>
-      <c r="P79" s="4">
-        <v>46094</v>
-      </c>
       <c r="S79" s="4">
-        <v>46112</v>
+        <v>46142</v>
       </c>
       <c r="T79" s="4">
-        <v>46112</v>
+        <v>46142</v>
       </c>
       <c r="V79" s="2" t="s">
         <v>149</v>
@@ -6705,7 +6875,7 @@
         <v>30</v>
       </c>
       <c r="X79" s="2" t="s">
-        <v>100</v>
+        <v>137</v>
       </c>
       <c r="Y79" s="2" t="s">
         <v>58</v>
@@ -6719,7 +6889,7 @@
         <v>173</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>174</v>
+        <v>45</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>26</v>
@@ -6748,14 +6918,11 @@
       <c r="L80" s="4">
         <v>46086</v>
       </c>
-      <c r="P80" s="4">
-        <v>46094</v>
-      </c>
       <c r="S80" s="4">
-        <v>46112</v>
+        <v>46142</v>
       </c>
       <c r="T80" s="4">
-        <v>46112</v>
+        <v>46142</v>
       </c>
       <c r="V80" s="2" t="s">
         <v>149</v>
@@ -6764,7 +6931,7 @@
         <v>30</v>
       </c>
       <c r="X80" s="2" t="s">
-        <v>100</v>
+        <v>137</v>
       </c>
       <c r="Y80" s="2" t="s">
         <v>58</v>
@@ -6778,7 +6945,7 @@
         <v>173</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>174</v>
+        <v>45</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>26</v>
@@ -6807,14 +6974,11 @@
       <c r="L81" s="4">
         <v>46086</v>
       </c>
-      <c r="P81" s="4">
-        <v>46094</v>
-      </c>
       <c r="S81" s="4">
-        <v>46112</v>
+        <v>46142</v>
       </c>
       <c r="T81" s="4">
-        <v>46112</v>
+        <v>46142</v>
       </c>
       <c r="V81" s="2" t="s">
         <v>149</v>
@@ -6823,7 +6987,7 @@
         <v>30</v>
       </c>
       <c r="X81" s="2" t="s">
-        <v>100</v>
+        <v>137</v>
       </c>
       <c r="Y81" s="2" t="s">
         <v>58</v>
@@ -6837,7 +7001,7 @@
         <v>173</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>174</v>
+        <v>45</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>26</v>
@@ -6866,14 +7030,11 @@
       <c r="L82" s="4">
         <v>46086</v>
       </c>
-      <c r="P82" s="4">
-        <v>46094</v>
-      </c>
       <c r="S82" s="4">
-        <v>46112</v>
+        <v>46142</v>
       </c>
       <c r="T82" s="4">
-        <v>46112</v>
+        <v>46142</v>
       </c>
       <c r="V82" s="2" t="s">
         <v>149</v>
@@ -6882,7 +7043,7 @@
         <v>30</v>
       </c>
       <c r="X82" s="2" t="s">
-        <v>100</v>
+        <v>137</v>
       </c>
       <c r="Y82" s="2" t="s">
         <v>58</v>
@@ -6896,7 +7057,7 @@
         <v>173</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>174</v>
+        <v>45</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>26</v>
@@ -6925,14 +7086,11 @@
       <c r="L83" s="4">
         <v>46086</v>
       </c>
-      <c r="P83" s="4">
-        <v>46094</v>
-      </c>
       <c r="S83" s="4">
-        <v>46112</v>
+        <v>46142</v>
       </c>
       <c r="T83" s="4">
-        <v>46112</v>
+        <v>46142</v>
       </c>
       <c r="V83" s="2" t="s">
         <v>149</v>
@@ -6941,7 +7099,7 @@
         <v>30</v>
       </c>
       <c r="X83" s="2" t="s">
-        <v>100</v>
+        <v>137</v>
       </c>
       <c r="Y83" s="2" t="s">
         <v>58</v>
@@ -6955,7 +7113,7 @@
         <v>173</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>174</v>
+        <v>45</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>26</v>
@@ -6984,14 +7142,11 @@
       <c r="L84" s="4">
         <v>46086</v>
       </c>
-      <c r="P84" s="4">
-        <v>46094</v>
-      </c>
       <c r="S84" s="4">
-        <v>46112</v>
+        <v>46142</v>
       </c>
       <c r="T84" s="4">
-        <v>46112</v>
+        <v>46142</v>
       </c>
       <c r="V84" s="2" t="s">
         <v>149</v>
@@ -7000,7 +7155,7 @@
         <v>30</v>
       </c>
       <c r="X84" s="2" t="s">
-        <v>100</v>
+        <v>137</v>
       </c>
       <c r="Y84" s="2" t="s">
         <v>58</v>
@@ -7008,16 +7163,16 @@
     </row>
     <row r="85" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
-        <v>151</v>
+        <v>172</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>152</v>
+        <v>173</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>153</v>
+        <v>45</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>27</v>
@@ -7026,13 +7181,13 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G85" s="7">
-        <v>14.5</v>
+        <v>14.2</v>
       </c>
       <c r="H85" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I85" s="2" t="s">
-        <v>183</v>
+      <c r="I85" s="11" t="s">
+        <v>218</v>
       </c>
       <c r="J85" s="2">
         <v>1</v>
@@ -7041,20 +7196,19 @@
         <v>1</v>
       </c>
       <c r="L85" s="4">
-        <v>46092</v>
-      </c>
-      <c r="M85" s="12"/>
-      <c r="N85" s="4">
-        <v>46093</v>
-      </c>
-      <c r="O85" s="4">
-        <v>46094</v>
+        <v>46086</v>
+      </c>
+      <c r="S85" s="4">
+        <v>46142</v>
+      </c>
+      <c r="T85" s="4">
+        <v>46142</v>
       </c>
       <c r="V85" s="2" t="s">
-        <v>184</v>
+        <v>226</v>
       </c>
       <c r="W85" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="X85" s="2" t="s">
         <v>137</v>
@@ -7065,16 +7219,16 @@
     </row>
     <row r="86" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
-        <v>151</v>
+        <v>172</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>152</v>
+        <v>173</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>153</v>
+        <v>45</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>27</v>
@@ -7083,13 +7237,13 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G86" s="7">
-        <v>14.5</v>
+        <v>14.2</v>
       </c>
       <c r="H86" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I86" s="2" t="s">
-        <v>176</v>
+      <c r="I86" s="11" t="s">
+        <v>219</v>
       </c>
       <c r="J86" s="2">
         <v>1</v>
@@ -7098,20 +7252,19 @@
         <v>1</v>
       </c>
       <c r="L86" s="4">
-        <v>46092</v>
-      </c>
-      <c r="M86" s="12"/>
-      <c r="N86" s="4">
-        <v>46093</v>
-      </c>
-      <c r="O86" s="4">
-        <v>46094</v>
+        <v>46086</v>
+      </c>
+      <c r="S86" s="4">
+        <v>46142</v>
+      </c>
+      <c r="T86" s="4">
+        <v>46142</v>
       </c>
       <c r="V86" s="2" t="s">
-        <v>184</v>
+        <v>226</v>
       </c>
       <c r="W86" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="X86" s="2" t="s">
         <v>137</v>
@@ -7122,16 +7275,16 @@
     </row>
     <row r="87" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
-        <v>151</v>
+        <v>172</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>152</v>
+        <v>173</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>153</v>
+        <v>45</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>27</v>
@@ -7140,13 +7293,13 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G87" s="7">
-        <v>14.5</v>
+        <v>14.2</v>
       </c>
       <c r="H87" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I87" s="2" t="s">
-        <v>177</v>
+      <c r="I87" s="11" t="s">
+        <v>220</v>
       </c>
       <c r="J87" s="2">
         <v>1</v>
@@ -7155,20 +7308,19 @@
         <v>1</v>
       </c>
       <c r="L87" s="4">
-        <v>46092</v>
-      </c>
-      <c r="M87" s="12"/>
-      <c r="N87" s="4">
-        <v>46093</v>
-      </c>
-      <c r="O87" s="4">
-        <v>46094</v>
+        <v>46086</v>
+      </c>
+      <c r="S87" s="4">
+        <v>46142</v>
+      </c>
+      <c r="T87" s="4">
+        <v>46142</v>
       </c>
       <c r="V87" s="2" t="s">
-        <v>185</v>
+        <v>226</v>
       </c>
       <c r="W87" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="X87" s="2" t="s">
         <v>137</v>
@@ -7179,16 +7331,16 @@
     </row>
     <row r="88" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
-        <v>151</v>
+        <v>172</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>152</v>
+        <v>173</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>153</v>
+        <v>45</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>27</v>
@@ -7197,13 +7349,13 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G88" s="7">
-        <v>14.5</v>
+        <v>14.2</v>
       </c>
       <c r="H88" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I88" s="2" t="s">
-        <v>178</v>
+      <c r="I88" s="11" t="s">
+        <v>221</v>
       </c>
       <c r="J88" s="2">
         <v>1</v>
@@ -7212,20 +7364,19 @@
         <v>1</v>
       </c>
       <c r="L88" s="4">
-        <v>46092</v>
-      </c>
-      <c r="M88" s="12"/>
-      <c r="N88" s="4">
-        <v>46093</v>
-      </c>
-      <c r="O88" s="4">
-        <v>46094</v>
+        <v>46086</v>
+      </c>
+      <c r="S88" s="4">
+        <v>46142</v>
+      </c>
+      <c r="T88" s="4">
+        <v>46142</v>
       </c>
       <c r="V88" s="2" t="s">
-        <v>185</v>
+        <v>226</v>
       </c>
       <c r="W88" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="X88" s="2" t="s">
         <v>137</v>
@@ -7236,16 +7387,16 @@
     </row>
     <row r="89" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>189</v>
+        <v>173</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>190</v>
+        <v>45</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>27</v>
@@ -7254,13 +7405,13 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G89" s="7">
-        <v>14.5</v>
+        <v>14.2</v>
       </c>
       <c r="H89" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I89" s="2" t="s">
-        <v>191</v>
+      <c r="I89" s="11" t="s">
+        <v>222</v>
       </c>
       <c r="J89" s="2">
         <v>1</v>
@@ -7269,13 +7420,19 @@
         <v>1</v>
       </c>
       <c r="L89" s="4">
-        <v>46094</v>
+        <v>46086</v>
+      </c>
+      <c r="S89" s="4">
+        <v>46142</v>
+      </c>
+      <c r="T89" s="4">
+        <v>46142</v>
       </c>
       <c r="V89" s="2" t="s">
-        <v>184</v>
+        <v>226</v>
       </c>
       <c r="W89" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="X89" s="2" t="s">
         <v>137</v>
@@ -7286,16 +7443,16 @@
     </row>
     <row r="90" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>189</v>
+        <v>173</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>190</v>
+        <v>45</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>27</v>
@@ -7304,13 +7461,13 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G90" s="7">
-        <v>14.5</v>
+        <v>14.2</v>
       </c>
       <c r="H90" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I90" s="2" t="s">
-        <v>192</v>
+      <c r="I90" s="11" t="s">
+        <v>223</v>
       </c>
       <c r="J90" s="2">
         <v>1</v>
@@ -7319,13 +7476,19 @@
         <v>1</v>
       </c>
       <c r="L90" s="4">
-        <v>46094</v>
+        <v>46086</v>
+      </c>
+      <c r="S90" s="4">
+        <v>46142</v>
+      </c>
+      <c r="T90" s="4">
+        <v>46142</v>
       </c>
       <c r="V90" s="2" t="s">
-        <v>184</v>
+        <v>226</v>
       </c>
       <c r="W90" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="X90" s="2" t="s">
         <v>137</v>
@@ -7336,16 +7499,16 @@
     </row>
     <row r="91" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>189</v>
+        <v>173</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>190</v>
+        <v>45</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>27</v>
@@ -7354,13 +7517,13 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G91" s="7">
-        <v>14.5</v>
+        <v>14.2</v>
       </c>
       <c r="H91" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I91" s="2" t="s">
-        <v>193</v>
+      <c r="I91" s="11" t="s">
+        <v>224</v>
       </c>
       <c r="J91" s="2">
         <v>1</v>
@@ -7369,13 +7532,19 @@
         <v>1</v>
       </c>
       <c r="L91" s="4">
-        <v>46094</v>
+        <v>46086</v>
+      </c>
+      <c r="S91" s="4">
+        <v>46142</v>
+      </c>
+      <c r="T91" s="4">
+        <v>46142</v>
       </c>
       <c r="V91" s="2" t="s">
-        <v>185</v>
+        <v>226</v>
       </c>
       <c r="W91" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="X91" s="2" t="s">
         <v>137</v>
@@ -7386,16 +7555,16 @@
     </row>
     <row r="92" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>189</v>
+        <v>173</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>190</v>
+        <v>45</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>27</v>
@@ -7404,13 +7573,13 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G92" s="7">
-        <v>14.5</v>
+        <v>14.2</v>
       </c>
       <c r="H92" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I92" s="2" t="s">
-        <v>195</v>
+      <c r="I92" s="11" t="s">
+        <v>225</v>
       </c>
       <c r="J92" s="2">
         <v>1</v>
@@ -7419,13 +7588,19 @@
         <v>1</v>
       </c>
       <c r="L92" s="4">
-        <v>46094</v>
+        <v>46086</v>
+      </c>
+      <c r="S92" s="4">
+        <v>46142</v>
+      </c>
+      <c r="T92" s="4">
+        <v>46142</v>
       </c>
       <c r="V92" s="2" t="s">
-        <v>185</v>
+        <v>226</v>
       </c>
       <c r="W92" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="X92" s="2" t="s">
         <v>137</v>
@@ -7436,16 +7611,16 @@
     </row>
     <row r="93" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>189</v>
+        <v>173</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>190</v>
+        <v>45</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>27</v>
@@ -7454,13 +7629,13 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G93" s="7">
-        <v>14.5</v>
+        <v>14.2</v>
       </c>
       <c r="H93" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I93" s="13" t="s">
-        <v>194</v>
+      <c r="I93" s="11" t="s">
+        <v>227</v>
       </c>
       <c r="J93" s="2">
         <v>1</v>
@@ -7469,13 +7644,19 @@
         <v>1</v>
       </c>
       <c r="L93" s="4">
-        <v>46094</v>
+        <v>46086</v>
+      </c>
+      <c r="S93" s="4">
+        <v>46142</v>
+      </c>
+      <c r="T93" s="4">
+        <v>46142</v>
       </c>
       <c r="V93" s="2" t="s">
-        <v>185</v>
+        <v>226</v>
       </c>
       <c r="W93" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="X93" s="2" t="s">
         <v>137</v>
@@ -7486,16 +7667,16 @@
     </row>
     <row r="94" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>189</v>
+        <v>173</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>190</v>
+        <v>45</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>27</v>
@@ -7504,13 +7685,13 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G94" s="7">
-        <v>14.5</v>
+        <v>14.2</v>
       </c>
       <c r="H94" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I94" s="2" t="s">
-        <v>196</v>
+      <c r="I94" s="11" t="s">
+        <v>228</v>
       </c>
       <c r="J94" s="2">
         <v>1</v>
@@ -7519,13 +7700,19 @@
         <v>1</v>
       </c>
       <c r="L94" s="4">
-        <v>46098</v>
+        <v>46086</v>
+      </c>
+      <c r="S94" s="4">
+        <v>46142</v>
+      </c>
+      <c r="T94" s="4">
+        <v>46142</v>
       </c>
       <c r="V94" s="2" t="s">
-        <v>199</v>
+        <v>229</v>
       </c>
       <c r="W94" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="X94" s="2" t="s">
         <v>137</v>
@@ -7536,13 +7723,13 @@
     </row>
     <row r="95" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
-        <v>188</v>
+        <v>151</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>189</v>
+        <v>152</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>190</v>
+        <v>153</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>34</v>
@@ -7560,7 +7747,7 @@
         <v>28</v>
       </c>
       <c r="I95" s="2" t="s">
-        <v>197</v>
+        <v>183</v>
       </c>
       <c r="J95" s="2">
         <v>1</v>
@@ -7569,10 +7756,17 @@
         <v>1</v>
       </c>
       <c r="L95" s="4">
-        <v>46098</v>
+        <v>46092</v>
+      </c>
+      <c r="M95" s="12"/>
+      <c r="N95" s="4">
+        <v>46093</v>
+      </c>
+      <c r="O95" s="4">
+        <v>46094</v>
       </c>
       <c r="V95" s="2" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="W95" s="2" t="s">
         <v>29</v>
@@ -7586,13 +7780,13 @@
     </row>
     <row r="96" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
-        <v>188</v>
+        <v>151</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>189</v>
+        <v>152</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>190</v>
+        <v>153</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>34</v>
@@ -7609,8 +7803,8 @@
       <c r="H96" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I96" s="13" t="s">
-        <v>198</v>
+      <c r="I96" s="2" t="s">
+        <v>176</v>
       </c>
       <c r="J96" s="2">
         <v>1</v>
@@ -7619,10 +7813,17 @@
         <v>1</v>
       </c>
       <c r="L96" s="4">
-        <v>46098</v>
+        <v>46092</v>
+      </c>
+      <c r="M96" s="12"/>
+      <c r="N96" s="4">
+        <v>46093</v>
+      </c>
+      <c r="O96" s="4">
+        <v>46094</v>
       </c>
       <c r="V96" s="2" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="W96" s="2" t="s">
         <v>29</v>
@@ -7631,6 +7832,535 @@
         <v>137</v>
       </c>
       <c r="Y96" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="97" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A97" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F97" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G97" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="H97" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I97" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="J97" s="2">
+        <v>1</v>
+      </c>
+      <c r="K97" s="2">
+        <v>1</v>
+      </c>
+      <c r="L97" s="4">
+        <v>46092</v>
+      </c>
+      <c r="M97" s="12"/>
+      <c r="N97" s="4">
+        <v>46093</v>
+      </c>
+      <c r="O97" s="4">
+        <v>46094</v>
+      </c>
+      <c r="V97" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="W97" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="X97" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="Y97" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="98" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A98" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F98" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G98" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I98" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="J98" s="2">
+        <v>1</v>
+      </c>
+      <c r="K98" s="2">
+        <v>1</v>
+      </c>
+      <c r="L98" s="4">
+        <v>46092</v>
+      </c>
+      <c r="M98" s="12"/>
+      <c r="N98" s="4">
+        <v>46093</v>
+      </c>
+      <c r="O98" s="4">
+        <v>46094</v>
+      </c>
+      <c r="V98" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="W98" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="X98" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="Y98" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="99" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A99" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F99" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G99" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I99" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="J99" s="2">
+        <v>1</v>
+      </c>
+      <c r="K99" s="2">
+        <v>1</v>
+      </c>
+      <c r="L99" s="4">
+        <v>46094</v>
+      </c>
+      <c r="T99" s="4">
+        <v>46117</v>
+      </c>
+      <c r="V99" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="W99" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="X99" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="Y99" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="100" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A100" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F100" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G100" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I100" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="J100" s="2">
+        <v>1</v>
+      </c>
+      <c r="K100" s="2">
+        <v>1</v>
+      </c>
+      <c r="L100" s="4">
+        <v>46094</v>
+      </c>
+      <c r="T100" s="4">
+        <v>46117</v>
+      </c>
+      <c r="V100" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="W100" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="X100" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="Y100" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="101" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A101" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F101" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G101" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="H101" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I101" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="J101" s="2">
+        <v>1</v>
+      </c>
+      <c r="K101" s="2">
+        <v>1</v>
+      </c>
+      <c r="L101" s="4">
+        <v>46094</v>
+      </c>
+      <c r="T101" s="4">
+        <v>46117</v>
+      </c>
+      <c r="V101" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="W101" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="X101" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="Y101" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="102" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A102" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F102" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G102" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="H102" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I102" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="J102" s="2">
+        <v>1</v>
+      </c>
+      <c r="K102" s="2">
+        <v>1</v>
+      </c>
+      <c r="L102" s="4">
+        <v>46094</v>
+      </c>
+      <c r="T102" s="4">
+        <v>46117</v>
+      </c>
+      <c r="V102" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="W102" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="X102" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="Y102" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="103" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A103" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E103" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F103" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G103" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="H103" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I103" s="13" t="s">
+        <v>194</v>
+      </c>
+      <c r="J103" s="2">
+        <v>1</v>
+      </c>
+      <c r="K103" s="2">
+        <v>1</v>
+      </c>
+      <c r="L103" s="4">
+        <v>46094</v>
+      </c>
+      <c r="T103" s="4">
+        <v>46117</v>
+      </c>
+      <c r="V103" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="W103" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="X103" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="Y103" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="104" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A104" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E104" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F104" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G104" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="H104" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I104" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="J104" s="2">
+        <v>1</v>
+      </c>
+      <c r="K104" s="2">
+        <v>1</v>
+      </c>
+      <c r="L104" s="4">
+        <v>46098</v>
+      </c>
+      <c r="V104" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="W104" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="X104" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="Y104" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="105" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A105" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E105" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F105" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G105" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="H105" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I105" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="J105" s="2">
+        <v>1</v>
+      </c>
+      <c r="K105" s="2">
+        <v>1</v>
+      </c>
+      <c r="L105" s="4">
+        <v>46098</v>
+      </c>
+      <c r="V105" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="W105" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="X105" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="Y105" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="106" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A106" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E106" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F106" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G106" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="H106" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I106" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="J106" s="2">
+        <v>1</v>
+      </c>
+      <c r="K106" s="2">
+        <v>1</v>
+      </c>
+      <c r="L106" s="4">
+        <v>46098</v>
+      </c>
+      <c r="V106" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="W106" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="X106" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="Y106" s="2" t="s">
         <v>58</v>
       </c>
     </row>
@@ -7638,58 +8368,113 @@
   <autoFilter ref="V1:V42"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="I59:I66">
-    <cfRule type="expression" dxfId="10" priority="5" stopIfTrue="1">
+    <cfRule type="expression" dxfId="21" priority="5" stopIfTrue="1">
       <formula>$E3101:$E1048570="sub"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I56:I58">
-    <cfRule type="expression" dxfId="9" priority="11" stopIfTrue="1">
+    <cfRule type="expression" dxfId="20" priority="11" stopIfTrue="1">
       <formula>$E3106:$E1048575="sub"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="I70">
+    <cfRule type="expression" dxfId="19" priority="72" stopIfTrue="1">
+      <formula>$E6:$E3131="sub"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I83">
+    <cfRule type="expression" dxfId="18" priority="95" stopIfTrue="1">
+      <formula>$E12:$E3136="sub"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I82">
+    <cfRule type="expression" dxfId="17" priority="101" stopIfTrue="1">
+      <formula>$E12:$E3136="sub"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I81">
+    <cfRule type="expression" dxfId="16" priority="107" stopIfTrue="1">
+      <formula>$E12:$E3136="sub"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="I80">
-    <cfRule type="expression" dxfId="8" priority="15" stopIfTrue="1">
-      <formula>$E10:$E3124="sub"</formula>
+    <cfRule type="expression" dxfId="15" priority="113" stopIfTrue="1">
+      <formula>$E12:$E3136="sub"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I79">
-    <cfRule type="expression" dxfId="7" priority="19" stopIfTrue="1">
-      <formula>$E10:$E3124="sub"</formula>
+    <cfRule type="expression" dxfId="14" priority="119" stopIfTrue="1">
+      <formula>$E12:$E3136="sub"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I78">
-    <cfRule type="expression" dxfId="6" priority="23" stopIfTrue="1">
-      <formula>$E10:$E3124="sub"</formula>
+    <cfRule type="expression" dxfId="13" priority="125" stopIfTrue="1">
+      <formula>$E12:$E3136="sub"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I84">
-    <cfRule type="expression" dxfId="5" priority="45" stopIfTrue="1">
-      <formula>$E11:$E3125="sub"</formula>
+  <conditionalFormatting sqref="I90">
+    <cfRule type="expression" dxfId="12" priority="149" stopIfTrue="1">
+      <formula>$E13:$E3137="sub"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I83">
-    <cfRule type="expression" dxfId="4" priority="50" stopIfTrue="1">
-      <formula>$E11:$E3125="sub"</formula>
+  <conditionalFormatting sqref="I89">
+    <cfRule type="expression" dxfId="11" priority="156" stopIfTrue="1">
+      <formula>$E13:$E3137="sub"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I81:I82">
-    <cfRule type="expression" dxfId="3" priority="54" stopIfTrue="1">
-      <formula>$E10:$E3124="sub"</formula>
+  <conditionalFormatting sqref="I88">
+    <cfRule type="expression" dxfId="10" priority="163" stopIfTrue="1">
+      <formula>$E13:$E3137="sub"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I76:I77">
-    <cfRule type="expression" dxfId="2" priority="55" stopIfTrue="1">
-      <formula>$E9:$E3123="sub"</formula>
+  <conditionalFormatting sqref="I87">
+    <cfRule type="expression" dxfId="9" priority="170" stopIfTrue="1">
+      <formula>$E13:$E3137="sub"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I86">
+    <cfRule type="expression" dxfId="8" priority="177" stopIfTrue="1">
+      <formula>$E13:$E3137="sub"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I94">
+    <cfRule type="expression" dxfId="7" priority="213" stopIfTrue="1">
+      <formula>$E15:$E3139="sub"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I91:I93">
+    <cfRule type="expression" dxfId="6" priority="220" stopIfTrue="1">
+      <formula>$E13:$E3137="sub"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I84:I85">
+    <cfRule type="expression" dxfId="5" priority="221" stopIfTrue="1">
+      <formula>$E12:$E3136="sub"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I73:I74">
+    <cfRule type="expression" dxfId="4" priority="222" stopIfTrue="1">
+      <formula>$E9:$E3133="sub"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I68:I69">
+    <cfRule type="expression" dxfId="3" priority="223" stopIfTrue="1">
+      <formula>$E2:$E3127="sub"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I75:I77">
+    <cfRule type="expression" dxfId="2" priority="224" stopIfTrue="1">
+      <formula>$E10:$E3134="sub"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I67">
-    <cfRule type="expression" dxfId="1" priority="56" stopIfTrue="1">
-      <formula>$E3115:$E1048576="sub"</formula>
+    <cfRule type="expression" dxfId="1" priority="225" stopIfTrue="1">
+      <formula>$E3125:$E1048576="sub"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I68:I75">
-    <cfRule type="expression" dxfId="0" priority="57" stopIfTrue="1">
-      <formula>$E2:$E3117="sub"</formula>
+  <conditionalFormatting sqref="I71:I72">
+    <cfRule type="expression" dxfId="0" priority="226" stopIfTrue="1">
+      <formula>$E8:$E3133="sub"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/sample-list.xlsx
+++ b/sample-list.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1196" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1262" uniqueCount="237">
   <si>
     <t>국가</t>
   </si>
@@ -956,6 +956,29 @@
   </si>
   <si>
     <t>임수빈</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SH40</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SH41</t>
+  </si>
+  <si>
+    <t>SH42</t>
+  </si>
+  <si>
+    <t>SH43</t>
+  </si>
+  <si>
+    <t>SH44</t>
+  </si>
+  <si>
+    <t>SH45</t>
+  </si>
+  <si>
+    <t>류미리</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1575,7 +1598,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AB106"/>
+  <dimension ref="A1:AB112"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.25" style="2" customWidth="1"/>
@@ -2108,6 +2131,18 @@
       <c r="M7" s="4">
         <v>46072</v>
       </c>
+      <c r="N7" s="4">
+        <v>46090</v>
+      </c>
+      <c r="O7" s="4">
+        <v>46090</v>
+      </c>
+      <c r="P7" s="4">
+        <v>46103</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>46106</v>
+      </c>
       <c r="V7" s="2" t="s">
         <v>52</v>
       </c>
@@ -7772,7 +7807,7 @@
         <v>29</v>
       </c>
       <c r="X95" s="2" t="s">
-        <v>137</v>
+        <v>100</v>
       </c>
       <c r="Y95" s="2" t="s">
         <v>58</v>
@@ -7829,7 +7864,7 @@
         <v>29</v>
       </c>
       <c r="X96" s="2" t="s">
-        <v>137</v>
+        <v>100</v>
       </c>
       <c r="Y96" s="2" t="s">
         <v>58</v>
@@ -7886,7 +7921,7 @@
         <v>29</v>
       </c>
       <c r="X97" s="2" t="s">
-        <v>137</v>
+        <v>100</v>
       </c>
       <c r="Y97" s="2" t="s">
         <v>58</v>
@@ -7943,7 +7978,7 @@
         <v>29</v>
       </c>
       <c r="X98" s="2" t="s">
-        <v>137</v>
+        <v>100</v>
       </c>
       <c r="Y98" s="2" t="s">
         <v>58</v>
@@ -7996,7 +8031,7 @@
         <v>29</v>
       </c>
       <c r="X99" s="2" t="s">
-        <v>137</v>
+        <v>100</v>
       </c>
       <c r="Y99" s="2" t="s">
         <v>58</v>
@@ -8049,7 +8084,7 @@
         <v>29</v>
       </c>
       <c r="X100" s="2" t="s">
-        <v>137</v>
+        <v>100</v>
       </c>
       <c r="Y100" s="2" t="s">
         <v>58</v>
@@ -8102,7 +8137,7 @@
         <v>29</v>
       </c>
       <c r="X101" s="2" t="s">
-        <v>137</v>
+        <v>100</v>
       </c>
       <c r="Y101" s="2" t="s">
         <v>58</v>
@@ -8155,7 +8190,7 @@
         <v>29</v>
       </c>
       <c r="X102" s="2" t="s">
-        <v>137</v>
+        <v>100</v>
       </c>
       <c r="Y102" s="2" t="s">
         <v>58</v>
@@ -8208,7 +8243,7 @@
         <v>29</v>
       </c>
       <c r="X103" s="2" t="s">
-        <v>137</v>
+        <v>100</v>
       </c>
       <c r="Y103" s="2" t="s">
         <v>58</v>
@@ -8251,6 +8286,9 @@
       <c r="L104" s="4">
         <v>46098</v>
       </c>
+      <c r="N104" s="4">
+        <v>46107</v>
+      </c>
       <c r="V104" s="2" t="s">
         <v>199</v>
       </c>
@@ -8334,7 +8372,7 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G106" s="7">
-        <v>14.5</v>
+        <v>14.2</v>
       </c>
       <c r="H106" s="2" t="s">
         <v>28</v>
@@ -8361,6 +8399,324 @@
         <v>137</v>
       </c>
       <c r="Y106" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="107" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A107" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E107" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F107" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G107" s="7">
+        <v>14.2</v>
+      </c>
+      <c r="H107" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I107" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="J107" s="2">
+        <v>1</v>
+      </c>
+      <c r="K107" s="2">
+        <v>1</v>
+      </c>
+      <c r="L107" s="4">
+        <v>46104</v>
+      </c>
+      <c r="N107" s="4">
+        <v>46106</v>
+      </c>
+      <c r="V107" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="W107" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X107" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="Y107" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="108" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A108" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E108" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F108" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G108" s="7">
+        <v>14.2</v>
+      </c>
+      <c r="H108" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I108" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="J108" s="2">
+        <v>1</v>
+      </c>
+      <c r="K108" s="2">
+        <v>1</v>
+      </c>
+      <c r="L108" s="4">
+        <v>46104</v>
+      </c>
+      <c r="N108" s="4">
+        <v>46106</v>
+      </c>
+      <c r="V108" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="W108" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X108" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="Y108" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="109" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A109" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="D109" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E109" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F109" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G109" s="7">
+        <v>14.2</v>
+      </c>
+      <c r="H109" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I109" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="J109" s="2">
+        <v>1</v>
+      </c>
+      <c r="K109" s="2">
+        <v>1</v>
+      </c>
+      <c r="L109" s="4">
+        <v>46104</v>
+      </c>
+      <c r="N109" s="4">
+        <v>46106</v>
+      </c>
+      <c r="V109" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="W109" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X109" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="Y109" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="110" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A110" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="D110" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E110" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F110" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G110" s="7">
+        <v>14.2</v>
+      </c>
+      <c r="H110" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I110" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="J110" s="2">
+        <v>1</v>
+      </c>
+      <c r="K110" s="2">
+        <v>1</v>
+      </c>
+      <c r="L110" s="4">
+        <v>46104</v>
+      </c>
+      <c r="N110" s="4">
+        <v>46106</v>
+      </c>
+      <c r="V110" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="W110" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X110" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="Y110" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="111" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A111" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E111" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F111" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G111" s="7">
+        <v>14.2</v>
+      </c>
+      <c r="H111" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I111" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="J111" s="2">
+        <v>1</v>
+      </c>
+      <c r="K111" s="2">
+        <v>1</v>
+      </c>
+      <c r="L111" s="4">
+        <v>46104</v>
+      </c>
+      <c r="N111" s="4">
+        <v>46106</v>
+      </c>
+      <c r="V111" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="W111" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X111" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="Y111" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="112" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A112" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E112" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F112" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G112" s="7">
+        <v>14.2</v>
+      </c>
+      <c r="H112" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I112" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="J112" s="2">
+        <v>1</v>
+      </c>
+      <c r="K112" s="2">
+        <v>1</v>
+      </c>
+      <c r="L112" s="4">
+        <v>46104</v>
+      </c>
+      <c r="N112" s="4">
+        <v>46106</v>
+      </c>
+      <c r="V112" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="W112" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X112" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="Y112" s="2" t="s">
         <v>58</v>
       </c>
     </row>

--- a/sample-list.xlsx
+++ b/sample-list.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1262" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1328" uniqueCount="242">
   <si>
     <t>국가</t>
   </si>
@@ -980,6 +980,21 @@
   <si>
     <t>류미리</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SN-I1</t>
+  </si>
+  <si>
+    <t>SN-I2</t>
+  </si>
+  <si>
+    <t>SN-I3</t>
+  </si>
+  <si>
+    <t>SN-I4</t>
+  </si>
+  <si>
+    <t>SN-I5</t>
   </si>
 </sst>
 </file>
@@ -1598,7 +1613,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AB112"/>
+  <dimension ref="A1:AB118"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.25" style="2" customWidth="1"/>
@@ -8286,6 +8301,7 @@
       <c r="L104" s="4">
         <v>46098</v>
       </c>
+      <c r="M104" s="6"/>
       <c r="N104" s="4">
         <v>46107</v>
       </c>
@@ -8339,6 +8355,7 @@
       <c r="L105" s="4">
         <v>46098</v>
       </c>
+      <c r="M105" s="6"/>
       <c r="V105" s="2" t="s">
         <v>199</v>
       </c>
@@ -8389,6 +8406,7 @@
       <c r="L106" s="4">
         <v>46098</v>
       </c>
+      <c r="M106" s="6"/>
       <c r="V106" s="2" t="s">
         <v>199</v>
       </c>
@@ -8439,6 +8457,7 @@
       <c r="L107" s="4">
         <v>46104</v>
       </c>
+      <c r="M107" s="6"/>
       <c r="N107" s="4">
         <v>46106</v>
       </c>
@@ -8492,6 +8511,7 @@
       <c r="L108" s="4">
         <v>46104</v>
       </c>
+      <c r="M108" s="6"/>
       <c r="N108" s="4">
         <v>46106</v>
       </c>
@@ -8545,6 +8565,7 @@
       <c r="L109" s="4">
         <v>46104</v>
       </c>
+      <c r="M109" s="6"/>
       <c r="N109" s="4">
         <v>46106</v>
       </c>
@@ -8598,6 +8619,7 @@
       <c r="L110" s="4">
         <v>46104</v>
       </c>
+      <c r="M110" s="6"/>
       <c r="N110" s="4">
         <v>46106</v>
       </c>
@@ -8651,6 +8673,7 @@
       <c r="L111" s="4">
         <v>46104</v>
       </c>
+      <c r="M111" s="6"/>
       <c r="N111" s="4">
         <v>46106</v>
       </c>
@@ -8704,6 +8727,7 @@
       <c r="L112" s="4">
         <v>46104</v>
       </c>
+      <c r="M112" s="6"/>
       <c r="N112" s="4">
         <v>46106</v>
       </c>
@@ -8719,6 +8743,326 @@
       <c r="Y112" s="2" t="s">
         <v>58</v>
       </c>
+    </row>
+    <row r="113" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A113" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E113" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F113" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G113" s="7">
+        <v>15</v>
+      </c>
+      <c r="H113" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I113" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="J113" s="2">
+        <v>1</v>
+      </c>
+      <c r="K113" s="2">
+        <v>1</v>
+      </c>
+      <c r="L113" s="4">
+        <v>46107</v>
+      </c>
+      <c r="N113" s="4">
+        <v>46108</v>
+      </c>
+      <c r="V113" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="W113" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X113" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="Y113" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="114" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A114" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E114" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F114" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G114" s="7">
+        <v>15</v>
+      </c>
+      <c r="H114" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I114" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="J114" s="2">
+        <v>1</v>
+      </c>
+      <c r="K114" s="2">
+        <v>1</v>
+      </c>
+      <c r="L114" s="4">
+        <v>46107</v>
+      </c>
+      <c r="N114" s="4">
+        <v>46108</v>
+      </c>
+      <c r="V114" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="W114" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X114" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="Y114" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="115" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A115" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E115" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F115" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G115" s="7">
+        <v>15</v>
+      </c>
+      <c r="H115" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I115" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="J115" s="2">
+        <v>1</v>
+      </c>
+      <c r="K115" s="2">
+        <v>1</v>
+      </c>
+      <c r="L115" s="4">
+        <v>46107</v>
+      </c>
+      <c r="N115" s="4">
+        <v>46108</v>
+      </c>
+      <c r="V115" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="W115" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X115" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="Y115" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="116" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A116" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C116" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D116" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E116" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F116" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G116" s="7">
+        <v>15</v>
+      </c>
+      <c r="H116" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I116" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="J116" s="2">
+        <v>1</v>
+      </c>
+      <c r="K116" s="2">
+        <v>1</v>
+      </c>
+      <c r="L116" s="4">
+        <v>46107</v>
+      </c>
+      <c r="N116" s="4">
+        <v>46108</v>
+      </c>
+      <c r="V116" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="W116" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X116" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="Y116" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="117" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A117" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C117" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D117" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E117" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F117" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G117" s="7">
+        <v>15</v>
+      </c>
+      <c r="H117" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I117" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="J117" s="2">
+        <v>1</v>
+      </c>
+      <c r="K117" s="2">
+        <v>1</v>
+      </c>
+      <c r="L117" s="4">
+        <v>46107</v>
+      </c>
+      <c r="N117" s="4">
+        <v>46108</v>
+      </c>
+      <c r="V117" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="W117" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X117" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="Y117" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="118" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A118" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C118" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D118" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E118" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F118" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G118" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="H118" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I118" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="J118" s="2">
+        <v>1</v>
+      </c>
+      <c r="K118" s="2">
+        <v>3</v>
+      </c>
+      <c r="L118" s="4">
+        <v>45995</v>
+      </c>
+      <c r="M118" s="4">
+        <v>46107</v>
+      </c>
+      <c r="P118" s="10"/>
+      <c r="V118" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="W118" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="X118" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="Y118" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="AB118" s="9"/>
     </row>
   </sheetData>
   <autoFilter ref="V1:V42"/>
@@ -8735,102 +9079,102 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="I70">
     <cfRule type="expression" dxfId="19" priority="72" stopIfTrue="1">
-      <formula>$E6:$E3131="sub"</formula>
+      <formula>$E6:$E3127="sub"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I83">
     <cfRule type="expression" dxfId="18" priority="95" stopIfTrue="1">
-      <formula>$E12:$E3136="sub"</formula>
+      <formula>$E12:$E3132="sub"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I82">
     <cfRule type="expression" dxfId="17" priority="101" stopIfTrue="1">
-      <formula>$E12:$E3136="sub"</formula>
+      <formula>$E12:$E3132="sub"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I81">
     <cfRule type="expression" dxfId="16" priority="107" stopIfTrue="1">
-      <formula>$E12:$E3136="sub"</formula>
+      <formula>$E12:$E3132="sub"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I80">
     <cfRule type="expression" dxfId="15" priority="113" stopIfTrue="1">
-      <formula>$E12:$E3136="sub"</formula>
+      <formula>$E12:$E3132="sub"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I79">
     <cfRule type="expression" dxfId="14" priority="119" stopIfTrue="1">
-      <formula>$E12:$E3136="sub"</formula>
+      <formula>$E12:$E3132="sub"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I78">
     <cfRule type="expression" dxfId="13" priority="125" stopIfTrue="1">
-      <formula>$E12:$E3136="sub"</formula>
+      <formula>$E12:$E3132="sub"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I90">
     <cfRule type="expression" dxfId="12" priority="149" stopIfTrue="1">
-      <formula>$E13:$E3137="sub"</formula>
+      <formula>$E13:$E3133="sub"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I89">
     <cfRule type="expression" dxfId="11" priority="156" stopIfTrue="1">
-      <formula>$E13:$E3137="sub"</formula>
+      <formula>$E13:$E3133="sub"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I88">
     <cfRule type="expression" dxfId="10" priority="163" stopIfTrue="1">
-      <formula>$E13:$E3137="sub"</formula>
+      <formula>$E13:$E3133="sub"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I87">
     <cfRule type="expression" dxfId="9" priority="170" stopIfTrue="1">
-      <formula>$E13:$E3137="sub"</formula>
+      <formula>$E13:$E3133="sub"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I86">
     <cfRule type="expression" dxfId="8" priority="177" stopIfTrue="1">
-      <formula>$E13:$E3137="sub"</formula>
+      <formula>$E13:$E3133="sub"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I94">
     <cfRule type="expression" dxfId="7" priority="213" stopIfTrue="1">
-      <formula>$E15:$E3139="sub"</formula>
+      <formula>$E15:$E3135="sub"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I91:I93">
-    <cfRule type="expression" dxfId="6" priority="220" stopIfTrue="1">
-      <formula>$E13:$E3137="sub"</formula>
+    <cfRule type="expression" dxfId="6" priority="234" stopIfTrue="1">
+      <formula>$E13:$E3133="sub"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I84:I85">
-    <cfRule type="expression" dxfId="5" priority="221" stopIfTrue="1">
-      <formula>$E12:$E3136="sub"</formula>
+    <cfRule type="expression" dxfId="5" priority="235" stopIfTrue="1">
+      <formula>$E12:$E3132="sub"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I73:I74">
-    <cfRule type="expression" dxfId="4" priority="222" stopIfTrue="1">
-      <formula>$E9:$E3133="sub"</formula>
+    <cfRule type="expression" dxfId="4" priority="236" stopIfTrue="1">
+      <formula>$E9:$E3129="sub"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I68:I69">
-    <cfRule type="expression" dxfId="3" priority="223" stopIfTrue="1">
-      <formula>$E2:$E3127="sub"</formula>
+    <cfRule type="expression" dxfId="3" priority="237" stopIfTrue="1">
+      <formula>$E2:$E3123="sub"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I75:I77">
-    <cfRule type="expression" dxfId="2" priority="224" stopIfTrue="1">
-      <formula>$E10:$E3134="sub"</formula>
+    <cfRule type="expression" dxfId="2" priority="238" stopIfTrue="1">
+      <formula>$E10:$E3130="sub"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I67">
-    <cfRule type="expression" dxfId="1" priority="225" stopIfTrue="1">
-      <formula>$E3125:$E1048576="sub"</formula>
+    <cfRule type="expression" dxfId="1" priority="239" stopIfTrue="1">
+      <formula>$E3121:$E1048576="sub"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I71:I72">
-    <cfRule type="expression" dxfId="0" priority="226" stopIfTrue="1">
-      <formula>$E8:$E3133="sub"</formula>
+    <cfRule type="expression" dxfId="0" priority="240" stopIfTrue="1">
+      <formula>$E8:$E3129="sub"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/sample-list.xlsx
+++ b/sample-list.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12165"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25200" windowHeight="11025"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1328" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1395" uniqueCount="254">
   <si>
     <t>국가</t>
   </si>
@@ -550,10 +550,6 @@
   </si>
   <si>
     <t>Dewy Quartz A-축고정 브랜드 제안</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>X (3차 미만)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -995,6 +991,58 @@
   </si>
   <si>
     <t>SN-I5</t>
+  </si>
+  <si>
+    <t>진행중</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>진행중</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">중동 </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sky Optical</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>이철은</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>액상</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Green 2-C</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hazel 2-C</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hazel 1-C</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Gray 3-C</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Brown 4-C</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Brown 3-C </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>FRP</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1613,7 +1661,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AB118"/>
+  <dimension ref="A1:AB124"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.25" style="2" customWidth="1"/>
@@ -1792,7 +1840,7 @@
         <v>53</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>142</v>
+        <v>58</v>
       </c>
       <c r="Z2" s="4">
         <v>46041</v>
@@ -2158,6 +2206,15 @@
       <c r="Q7" s="4">
         <v>46106</v>
       </c>
+      <c r="R7" s="4">
+        <v>46111</v>
+      </c>
+      <c r="S7" s="4">
+        <v>46112</v>
+      </c>
+      <c r="T7" s="4">
+        <v>46112</v>
+      </c>
       <c r="V7" s="2" t="s">
         <v>52</v>
       </c>
@@ -2165,7 +2222,10 @@
         <v>29</v>
       </c>
       <c r="X7" s="2" t="s">
-        <v>137</v>
+        <v>53</v>
+      </c>
+      <c r="Y7" s="2" t="s">
+        <v>58</v>
       </c>
       <c r="AB7" s="9" t="s">
         <v>138</v>
@@ -3247,7 +3307,7 @@
         <v>28</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="J22" s="2">
         <v>1</v>
@@ -3324,7 +3384,7 @@
         <v>28</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="J23" s="2">
         <v>1</v>
@@ -3374,6 +3434,10 @@
       <c r="Z23" s="4">
         <v>46065</v>
       </c>
+      <c r="AA23" s="4">
+        <v>46112</v>
+      </c>
+      <c r="AB23" s="4"/>
     </row>
     <row r="24" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
@@ -3398,10 +3462,10 @@
         <v>14.5</v>
       </c>
       <c r="H24" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="I24" s="2" t="s">
         <v>181</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>182</v>
       </c>
       <c r="J24" s="2">
         <v>1</v>
@@ -4745,7 +4809,7 @@
         <v>100</v>
       </c>
       <c r="Y43" s="2" t="s">
-        <v>33</v>
+        <v>253</v>
       </c>
     </row>
     <row r="44" spans="1:25" x14ac:dyDescent="0.3">
@@ -4804,7 +4868,7 @@
         <v>100</v>
       </c>
       <c r="Y44" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="45" spans="1:25" x14ac:dyDescent="0.3">
@@ -4863,7 +4927,7 @@
         <v>100</v>
       </c>
       <c r="Y45" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="46" spans="1:25" x14ac:dyDescent="0.3">
@@ -4925,18 +4989,18 @@
         <v>100</v>
       </c>
       <c r="Y46" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="47" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B47" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="C47" s="2" t="s">
         <v>146</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>147</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>34</v>
@@ -4954,7 +5018,7 @@
         <v>28</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J47" s="2">
         <v>1</v>
@@ -4986,7 +5050,7 @@
         <v>46094</v>
       </c>
       <c r="V47" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="W47" s="2" t="s">
         <v>30</v>
@@ -4995,18 +5059,18 @@
         <v>100</v>
       </c>
       <c r="Y47" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="48" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B48" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="B48" s="2" t="s">
+      <c r="C48" s="2" t="s">
         <v>146</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>147</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>34</v>
@@ -5024,7 +5088,7 @@
         <v>28</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J48" s="2">
         <v>1</v>
@@ -5056,7 +5120,7 @@
         <v>46094</v>
       </c>
       <c r="V48" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="W48" s="2" t="s">
         <v>30</v>
@@ -5065,24 +5129,24 @@
         <v>100</v>
       </c>
       <c r="Y48" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="49" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B49" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="B49" s="2" t="s">
+      <c r="C49" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>153</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F49" s="3">
         <v>0.45</v>
@@ -5094,7 +5158,7 @@
         <v>28</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="J49" s="2">
         <v>1</v>
@@ -5119,7 +5183,7 @@
         <v>46100</v>
       </c>
       <c r="V49" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="W49" s="2" t="s">
         <v>29</v>
@@ -5130,19 +5194,19 @@
     </row>
     <row r="50" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B50" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="B50" s="2" t="s">
+      <c r="C50" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>153</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F50" s="3">
         <v>0.45</v>
@@ -5154,7 +5218,7 @@
         <v>28</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J50" s="2">
         <v>1</v>
@@ -5179,7 +5243,7 @@
         <v>46100</v>
       </c>
       <c r="V50" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="W50" s="2" t="s">
         <v>29</v>
@@ -5190,19 +5254,19 @@
     </row>
     <row r="51" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B51" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="B51" s="2" t="s">
+      <c r="C51" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>153</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F51" s="3">
         <v>0.45</v>
@@ -5214,7 +5278,7 @@
         <v>28</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="J51" s="2">
         <v>1</v>
@@ -5239,7 +5303,7 @@
         <v>46100</v>
       </c>
       <c r="V51" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="W51" s="2" t="s">
         <v>29</v>
@@ -5250,19 +5314,19 @@
     </row>
     <row r="52" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B52" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="B52" s="2" t="s">
+      <c r="C52" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>153</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F52" s="3">
         <v>0.45</v>
@@ -5274,7 +5338,7 @@
         <v>28</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J52" s="2">
         <v>1</v>
@@ -5296,7 +5360,7 @@
         <v>46087</v>
       </c>
       <c r="V52" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="W52" s="2" t="s">
         <v>29</v>
@@ -5307,19 +5371,19 @@
     </row>
     <row r="53" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B53" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="B53" s="2" t="s">
+      <c r="C53" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>153</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F53" s="3">
         <v>0.45</v>
@@ -5331,7 +5395,7 @@
         <v>28</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="J53" s="2">
         <v>1</v>
@@ -5353,7 +5417,7 @@
         <v>46087</v>
       </c>
       <c r="V53" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="W53" s="2" t="s">
         <v>29</v>
@@ -5364,19 +5428,19 @@
     </row>
     <row r="54" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B54" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="B54" s="2" t="s">
+      <c r="C54" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>153</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F54" s="3">
         <v>0.45</v>
@@ -5388,7 +5452,7 @@
         <v>28</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="J54" s="2">
         <v>1</v>
@@ -5410,7 +5474,7 @@
         <v>46087</v>
       </c>
       <c r="V54" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="W54" s="2" t="s">
         <v>29</v>
@@ -5421,19 +5485,19 @@
     </row>
     <row r="55" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B55" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="B55" s="2" t="s">
+      <c r="C55" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>153</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F55" s="3">
         <v>0.45</v>
@@ -5445,7 +5509,7 @@
         <v>28</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="J55" s="2">
         <v>1</v>
@@ -5467,7 +5531,7 @@
         <v>46087</v>
       </c>
       <c r="V55" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="W55" s="2" t="s">
         <v>29</v>
@@ -5478,19 +5542,19 @@
     </row>
     <row r="56" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B56" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="B56" s="2" t="s">
+      <c r="C56" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>153</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F56" s="3">
         <v>0.45</v>
@@ -5502,7 +5566,7 @@
         <v>28</v>
       </c>
       <c r="I56" s="11" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J56" s="2">
         <v>1</v>
@@ -5524,7 +5588,7 @@
         <v>46087</v>
       </c>
       <c r="V56" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="W56" s="2" t="s">
         <v>29</v>
@@ -5535,19 +5599,19 @@
     </row>
     <row r="57" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B57" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="B57" s="2" t="s">
+      <c r="C57" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>153</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F57" s="3">
         <v>0.45</v>
@@ -5559,7 +5623,7 @@
         <v>28</v>
       </c>
       <c r="I57" s="11" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J57" s="2">
         <v>1</v>
@@ -5581,7 +5645,7 @@
         <v>46087</v>
       </c>
       <c r="V57" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="W57" s="2" t="s">
         <v>29</v>
@@ -5592,19 +5656,19 @@
     </row>
     <row r="58" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B58" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="B58" s="2" t="s">
+      <c r="C58" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>153</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F58" s="3">
         <v>0.45</v>
@@ -5616,7 +5680,7 @@
         <v>28</v>
       </c>
       <c r="I58" s="11" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="J58" s="2">
         <v>1</v>
@@ -5638,7 +5702,7 @@
         <v>46087</v>
       </c>
       <c r="V58" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="W58" s="2" t="s">
         <v>29</v>
@@ -5649,19 +5713,19 @@
     </row>
     <row r="59" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B59" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="B59" s="2" t="s">
+      <c r="C59" s="2" t="s">
         <v>173</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>174</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F59" s="3">
         <v>0.55000000000000004</v>
@@ -5673,7 +5737,7 @@
         <v>28</v>
       </c>
       <c r="I59" s="11" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="J59" s="2">
         <v>1</v>
@@ -5697,13 +5761,13 @@
         <v>46112</v>
       </c>
       <c r="V59" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="W59" s="2" t="s">
         <v>30</v>
       </c>
       <c r="X59" s="2" t="s">
-        <v>100</v>
+        <v>53</v>
       </c>
       <c r="Y59" s="2" t="s">
         <v>58</v>
@@ -5711,19 +5775,19 @@
     </row>
     <row r="60" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B60" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="B60" s="2" t="s">
+      <c r="C60" s="2" t="s">
         <v>173</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>174</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F60" s="3">
         <v>0.55000000000000004</v>
@@ -5735,7 +5799,7 @@
         <v>28</v>
       </c>
       <c r="I60" s="11" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J60" s="2">
         <v>1</v>
@@ -5759,13 +5823,13 @@
         <v>46112</v>
       </c>
       <c r="V60" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="W60" s="2" t="s">
         <v>30</v>
       </c>
       <c r="X60" s="2" t="s">
-        <v>100</v>
+        <v>53</v>
       </c>
       <c r="Y60" s="2" t="s">
         <v>58</v>
@@ -5773,13 +5837,13 @@
     </row>
     <row r="61" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B61" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="B61" s="2" t="s">
+      <c r="C61" s="2" t="s">
         <v>173</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>174</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>26</v>
@@ -5797,7 +5861,7 @@
         <v>28</v>
       </c>
       <c r="I61" s="11" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="J61" s="2">
         <v>1</v>
@@ -5821,13 +5885,13 @@
         <v>46112</v>
       </c>
       <c r="V61" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="W61" s="2" t="s">
         <v>30</v>
       </c>
       <c r="X61" s="2" t="s">
-        <v>100</v>
+        <v>53</v>
       </c>
       <c r="Y61" s="2" t="s">
         <v>58</v>
@@ -5835,13 +5899,13 @@
     </row>
     <row r="62" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B62" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="B62" s="2" t="s">
+      <c r="C62" s="2" t="s">
         <v>173</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>174</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>26</v>
@@ -5859,7 +5923,7 @@
         <v>28</v>
       </c>
       <c r="I62" s="11" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="J62" s="2">
         <v>1</v>
@@ -5883,13 +5947,13 @@
         <v>46112</v>
       </c>
       <c r="V62" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="W62" s="2" t="s">
         <v>30</v>
       </c>
       <c r="X62" s="2" t="s">
-        <v>100</v>
+        <v>53</v>
       </c>
       <c r="Y62" s="2" t="s">
         <v>58</v>
@@ -5897,13 +5961,13 @@
     </row>
     <row r="63" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B63" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="B63" s="2" t="s">
+      <c r="C63" s="2" t="s">
         <v>173</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>174</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>26</v>
@@ -5921,7 +5985,7 @@
         <v>28</v>
       </c>
       <c r="I63" s="11" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="J63" s="2">
         <v>1</v>
@@ -5945,13 +6009,13 @@
         <v>46112</v>
       </c>
       <c r="V63" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="W63" s="2" t="s">
         <v>30</v>
       </c>
       <c r="X63" s="2" t="s">
-        <v>100</v>
+        <v>53</v>
       </c>
       <c r="Y63" s="2" t="s">
         <v>58</v>
@@ -5959,13 +6023,13 @@
     </row>
     <row r="64" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B64" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="B64" s="2" t="s">
+      <c r="C64" s="2" t="s">
         <v>173</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>174</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>26</v>
@@ -5983,7 +6047,7 @@
         <v>28</v>
       </c>
       <c r="I64" s="11" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J64" s="2">
         <v>1</v>
@@ -6007,13 +6071,13 @@
         <v>46112</v>
       </c>
       <c r="V64" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="W64" s="2" t="s">
         <v>30</v>
       </c>
       <c r="X64" s="2" t="s">
-        <v>100</v>
+        <v>53</v>
       </c>
       <c r="Y64" s="2" t="s">
         <v>58</v>
@@ -6021,13 +6085,13 @@
     </row>
     <row r="65" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B65" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="B65" s="2" t="s">
+      <c r="C65" s="2" t="s">
         <v>173</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>174</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>26</v>
@@ -6045,7 +6109,7 @@
         <v>28</v>
       </c>
       <c r="I65" s="11" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J65" s="2">
         <v>1</v>
@@ -6069,13 +6133,13 @@
         <v>46112</v>
       </c>
       <c r="V65" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="W65" s="2" t="s">
         <v>30</v>
       </c>
       <c r="X65" s="2" t="s">
-        <v>100</v>
+        <v>53</v>
       </c>
       <c r="Y65" s="2" t="s">
         <v>58</v>
@@ -6083,13 +6147,13 @@
     </row>
     <row r="66" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B66" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="B66" s="2" t="s">
+      <c r="C66" s="2" t="s">
         <v>173</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>174</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>26</v>
@@ -6107,7 +6171,7 @@
         <v>28</v>
       </c>
       <c r="I66" s="11" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J66" s="2">
         <v>1</v>
@@ -6131,13 +6195,13 @@
         <v>46112</v>
       </c>
       <c r="V66" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="W66" s="2" t="s">
         <v>30</v>
       </c>
       <c r="X66" s="2" t="s">
-        <v>100</v>
+        <v>53</v>
       </c>
       <c r="Y66" s="2" t="s">
         <v>58</v>
@@ -6145,13 +6209,13 @@
     </row>
     <row r="67" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B67" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="B67" s="2" t="s">
+      <c r="C67" s="2" t="s">
         <v>173</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>174</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>26</v>
@@ -6169,7 +6233,7 @@
         <v>28</v>
       </c>
       <c r="I67" s="11" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J67" s="2">
         <v>1</v>
@@ -6193,13 +6257,13 @@
         <v>46112</v>
       </c>
       <c r="V67" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="W67" s="2" t="s">
         <v>30</v>
       </c>
       <c r="X67" s="2" t="s">
-        <v>100</v>
+        <v>53</v>
       </c>
       <c r="Y67" s="2" t="s">
         <v>58</v>
@@ -6207,13 +6271,13 @@
     </row>
     <row r="68" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B68" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="B68" s="2" t="s">
+      <c r="C68" s="2" t="s">
         <v>173</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>174</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>26</v>
@@ -6231,7 +6295,7 @@
         <v>28</v>
       </c>
       <c r="I68" s="11" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="J68" s="2">
         <v>1</v>
@@ -6255,13 +6319,13 @@
         <v>46112</v>
       </c>
       <c r="V68" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="W68" s="2" t="s">
         <v>30</v>
       </c>
       <c r="X68" s="2" t="s">
-        <v>100</v>
+        <v>53</v>
       </c>
       <c r="Y68" s="2" t="s">
         <v>58</v>
@@ -6269,13 +6333,13 @@
     </row>
     <row r="69" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B69" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="B69" s="2" t="s">
+      <c r="C69" s="2" t="s">
         <v>173</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>174</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>26</v>
@@ -6293,7 +6357,7 @@
         <v>28</v>
       </c>
       <c r="I69" s="11" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="J69" s="2">
         <v>1</v>
@@ -6317,13 +6381,13 @@
         <v>46112</v>
       </c>
       <c r="V69" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="W69" s="2" t="s">
         <v>30</v>
       </c>
       <c r="X69" s="2" t="s">
-        <v>100</v>
+        <v>53</v>
       </c>
       <c r="Y69" s="2" t="s">
         <v>58</v>
@@ -6331,13 +6395,13 @@
     </row>
     <row r="70" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B70" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="B70" s="2" t="s">
+      <c r="C70" s="2" t="s">
         <v>173</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>174</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>26</v>
@@ -6355,7 +6419,7 @@
         <v>28</v>
       </c>
       <c r="I70" s="11" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="J70" s="2">
         <v>1</v>
@@ -6379,13 +6443,13 @@
         <v>46112</v>
       </c>
       <c r="V70" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="W70" s="2" t="s">
         <v>30</v>
       </c>
       <c r="X70" s="2" t="s">
-        <v>100</v>
+        <v>53</v>
       </c>
       <c r="Y70" s="2" t="s">
         <v>58</v>
@@ -6393,13 +6457,13 @@
     </row>
     <row r="71" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B71" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="B71" s="2" t="s">
+      <c r="C71" s="2" t="s">
         <v>173</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>174</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>26</v>
@@ -6417,7 +6481,7 @@
         <v>28</v>
       </c>
       <c r="I71" s="11" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="J71" s="2">
         <v>1</v>
@@ -6441,13 +6505,13 @@
         <v>46112</v>
       </c>
       <c r="V71" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="W71" s="2" t="s">
         <v>30</v>
       </c>
       <c r="X71" s="2" t="s">
-        <v>100</v>
+        <v>53</v>
       </c>
       <c r="Y71" s="2" t="s">
         <v>58</v>
@@ -6455,13 +6519,13 @@
     </row>
     <row r="72" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B72" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="B72" s="2" t="s">
+      <c r="C72" s="2" t="s">
         <v>173</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>174</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>26</v>
@@ -6479,7 +6543,7 @@
         <v>28</v>
       </c>
       <c r="I72" s="11" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="J72" s="2">
         <v>1</v>
@@ -6503,13 +6567,13 @@
         <v>46112</v>
       </c>
       <c r="V72" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="W72" s="2" t="s">
         <v>30</v>
       </c>
       <c r="X72" s="2" t="s">
-        <v>100</v>
+        <v>53</v>
       </c>
       <c r="Y72" s="2" t="s">
         <v>58</v>
@@ -6517,13 +6581,13 @@
     </row>
     <row r="73" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B73" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="B73" s="2" t="s">
+      <c r="C73" s="2" t="s">
         <v>173</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>174</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>26</v>
@@ -6541,7 +6605,7 @@
         <v>28</v>
       </c>
       <c r="I73" s="11" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="J73" s="2">
         <v>1</v>
@@ -6565,13 +6629,13 @@
         <v>46112</v>
       </c>
       <c r="V73" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="W73" s="2" t="s">
         <v>30</v>
       </c>
       <c r="X73" s="2" t="s">
-        <v>100</v>
+        <v>53</v>
       </c>
       <c r="Y73" s="2" t="s">
         <v>58</v>
@@ -6579,13 +6643,13 @@
     </row>
     <row r="74" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B74" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="B74" s="2" t="s">
+      <c r="C74" s="2" t="s">
         <v>173</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>174</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>26</v>
@@ -6603,7 +6667,7 @@
         <v>28</v>
       </c>
       <c r="I74" s="11" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="J74" s="2">
         <v>1</v>
@@ -6627,13 +6691,13 @@
         <v>46112</v>
       </c>
       <c r="V74" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="W74" s="2" t="s">
         <v>30</v>
       </c>
       <c r="X74" s="2" t="s">
-        <v>100</v>
+        <v>53</v>
       </c>
       <c r="Y74" s="2" t="s">
         <v>58</v>
@@ -6641,13 +6705,13 @@
     </row>
     <row r="75" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B75" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="B75" s="2" t="s">
+      <c r="C75" s="2" t="s">
         <v>173</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>174</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>26</v>
@@ -6665,7 +6729,7 @@
         <v>28</v>
       </c>
       <c r="I75" s="11" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="J75" s="2">
         <v>1</v>
@@ -6689,13 +6753,13 @@
         <v>46112</v>
       </c>
       <c r="V75" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="W75" s="2" t="s">
         <v>30</v>
       </c>
       <c r="X75" s="2" t="s">
-        <v>100</v>
+        <v>53</v>
       </c>
       <c r="Y75" s="2" t="s">
         <v>58</v>
@@ -6703,13 +6767,13 @@
     </row>
     <row r="76" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B76" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="B76" s="2" t="s">
+      <c r="C76" s="2" t="s">
         <v>173</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>174</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>26</v>
@@ -6727,7 +6791,7 @@
         <v>28</v>
       </c>
       <c r="I76" s="11" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="J76" s="2">
         <v>1</v>
@@ -6751,13 +6815,13 @@
         <v>46112</v>
       </c>
       <c r="V76" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="W76" s="2" t="s">
         <v>30</v>
       </c>
       <c r="X76" s="2" t="s">
-        <v>100</v>
+        <v>53</v>
       </c>
       <c r="Y76" s="2" t="s">
         <v>58</v>
@@ -6765,10 +6829,10 @@
     </row>
     <row r="77" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B77" s="2" t="s">
         <v>172</v>
-      </c>
-      <c r="B77" s="2" t="s">
-        <v>173</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>45</v>
@@ -6789,7 +6853,7 @@
         <v>28</v>
       </c>
       <c r="I77" s="11" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="J77" s="2">
         <v>1</v>
@@ -6807,7 +6871,7 @@
         <v>46142</v>
       </c>
       <c r="V77" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="W77" s="2" t="s">
         <v>30</v>
@@ -6821,10 +6885,10 @@
     </row>
     <row r="78" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B78" s="2" t="s">
         <v>172</v>
-      </c>
-      <c r="B78" s="2" t="s">
-        <v>173</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>45</v>
@@ -6845,7 +6909,7 @@
         <v>28</v>
       </c>
       <c r="I78" s="11" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J78" s="2">
         <v>1</v>
@@ -6863,7 +6927,7 @@
         <v>46142</v>
       </c>
       <c r="V78" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="W78" s="2" t="s">
         <v>30</v>
@@ -6877,10 +6941,10 @@
     </row>
     <row r="79" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B79" s="2" t="s">
         <v>172</v>
-      </c>
-      <c r="B79" s="2" t="s">
-        <v>173</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>45</v>
@@ -6901,7 +6965,7 @@
         <v>28</v>
       </c>
       <c r="I79" s="11" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="J79" s="2">
         <v>1</v>
@@ -6919,7 +6983,7 @@
         <v>46142</v>
       </c>
       <c r="V79" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="W79" s="2" t="s">
         <v>30</v>
@@ -6933,10 +6997,10 @@
     </row>
     <row r="80" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B80" s="2" t="s">
         <v>172</v>
-      </c>
-      <c r="B80" s="2" t="s">
-        <v>173</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>45</v>
@@ -6957,7 +7021,7 @@
         <v>28</v>
       </c>
       <c r="I80" s="11" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J80" s="2">
         <v>1</v>
@@ -6975,7 +7039,7 @@
         <v>46142</v>
       </c>
       <c r="V80" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="W80" s="2" t="s">
         <v>30</v>
@@ -6989,10 +7053,10 @@
     </row>
     <row r="81" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B81" s="2" t="s">
         <v>172</v>
-      </c>
-      <c r="B81" s="2" t="s">
-        <v>173</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>45</v>
@@ -7013,7 +7077,7 @@
         <v>28</v>
       </c>
       <c r="I81" s="11" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="J81" s="2">
         <v>1</v>
@@ -7031,7 +7095,7 @@
         <v>46142</v>
       </c>
       <c r="V81" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="W81" s="2" t="s">
         <v>30</v>
@@ -7045,10 +7109,10 @@
     </row>
     <row r="82" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B82" s="2" t="s">
         <v>172</v>
-      </c>
-      <c r="B82" s="2" t="s">
-        <v>173</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>45</v>
@@ -7069,7 +7133,7 @@
         <v>28</v>
       </c>
       <c r="I82" s="11" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="J82" s="2">
         <v>1</v>
@@ -7087,7 +7151,7 @@
         <v>46142</v>
       </c>
       <c r="V82" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="W82" s="2" t="s">
         <v>30</v>
@@ -7101,10 +7165,10 @@
     </row>
     <row r="83" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B83" s="2" t="s">
         <v>172</v>
-      </c>
-      <c r="B83" s="2" t="s">
-        <v>173</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>45</v>
@@ -7125,7 +7189,7 @@
         <v>28</v>
       </c>
       <c r="I83" s="11" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="J83" s="2">
         <v>1</v>
@@ -7143,7 +7207,7 @@
         <v>46142</v>
       </c>
       <c r="V83" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="W83" s="2" t="s">
         <v>30</v>
@@ -7157,10 +7221,10 @@
     </row>
     <row r="84" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B84" s="2" t="s">
         <v>172</v>
-      </c>
-      <c r="B84" s="2" t="s">
-        <v>173</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>45</v>
@@ -7181,7 +7245,7 @@
         <v>28</v>
       </c>
       <c r="I84" s="11" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="J84" s="2">
         <v>1</v>
@@ -7199,7 +7263,7 @@
         <v>46142</v>
       </c>
       <c r="V84" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="W84" s="2" t="s">
         <v>30</v>
@@ -7213,10 +7277,10 @@
     </row>
     <row r="85" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B85" s="2" t="s">
         <v>172</v>
-      </c>
-      <c r="B85" s="2" t="s">
-        <v>173</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>45</v>
@@ -7237,7 +7301,7 @@
         <v>28</v>
       </c>
       <c r="I85" s="11" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="J85" s="2">
         <v>1</v>
@@ -7255,7 +7319,7 @@
         <v>46142</v>
       </c>
       <c r="V85" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="W85" s="2" t="s">
         <v>30</v>
@@ -7269,10 +7333,10 @@
     </row>
     <row r="86" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B86" s="2" t="s">
         <v>172</v>
-      </c>
-      <c r="B86" s="2" t="s">
-        <v>173</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>45</v>
@@ -7293,7 +7357,7 @@
         <v>28</v>
       </c>
       <c r="I86" s="11" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="J86" s="2">
         <v>1</v>
@@ -7311,7 +7375,7 @@
         <v>46142</v>
       </c>
       <c r="V86" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="W86" s="2" t="s">
         <v>30</v>
@@ -7325,10 +7389,10 @@
     </row>
     <row r="87" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B87" s="2" t="s">
         <v>172</v>
-      </c>
-      <c r="B87" s="2" t="s">
-        <v>173</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>45</v>
@@ -7349,7 +7413,7 @@
         <v>28</v>
       </c>
       <c r="I87" s="11" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="J87" s="2">
         <v>1</v>
@@ -7367,7 +7431,7 @@
         <v>46142</v>
       </c>
       <c r="V87" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="W87" s="2" t="s">
         <v>30</v>
@@ -7381,10 +7445,10 @@
     </row>
     <row r="88" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B88" s="2" t="s">
         <v>172</v>
-      </c>
-      <c r="B88" s="2" t="s">
-        <v>173</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>45</v>
@@ -7405,7 +7469,7 @@
         <v>28</v>
       </c>
       <c r="I88" s="11" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="J88" s="2">
         <v>1</v>
@@ -7423,7 +7487,7 @@
         <v>46142</v>
       </c>
       <c r="V88" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="W88" s="2" t="s">
         <v>30</v>
@@ -7437,10 +7501,10 @@
     </row>
     <row r="89" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B89" s="2" t="s">
         <v>172</v>
-      </c>
-      <c r="B89" s="2" t="s">
-        <v>173</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>45</v>
@@ -7461,7 +7525,7 @@
         <v>28</v>
       </c>
       <c r="I89" s="11" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="J89" s="2">
         <v>1</v>
@@ -7479,7 +7543,7 @@
         <v>46142</v>
       </c>
       <c r="V89" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="W89" s="2" t="s">
         <v>30</v>
@@ -7493,10 +7557,10 @@
     </row>
     <row r="90" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B90" s="2" t="s">
         <v>172</v>
-      </c>
-      <c r="B90" s="2" t="s">
-        <v>173</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>45</v>
@@ -7517,7 +7581,7 @@
         <v>28</v>
       </c>
       <c r="I90" s="11" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="J90" s="2">
         <v>1</v>
@@ -7535,7 +7599,7 @@
         <v>46142</v>
       </c>
       <c r="V90" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="W90" s="2" t="s">
         <v>30</v>
@@ -7549,10 +7613,10 @@
     </row>
     <row r="91" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B91" s="2" t="s">
         <v>172</v>
-      </c>
-      <c r="B91" s="2" t="s">
-        <v>173</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>45</v>
@@ -7573,7 +7637,7 @@
         <v>28</v>
       </c>
       <c r="I91" s="11" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="J91" s="2">
         <v>1</v>
@@ -7591,7 +7655,7 @@
         <v>46142</v>
       </c>
       <c r="V91" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="W91" s="2" t="s">
         <v>30</v>
@@ -7605,10 +7669,10 @@
     </row>
     <row r="92" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B92" s="2" t="s">
         <v>172</v>
-      </c>
-      <c r="B92" s="2" t="s">
-        <v>173</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>45</v>
@@ -7629,7 +7693,7 @@
         <v>28</v>
       </c>
       <c r="I92" s="11" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="J92" s="2">
         <v>1</v>
@@ -7647,7 +7711,7 @@
         <v>46142</v>
       </c>
       <c r="V92" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="W92" s="2" t="s">
         <v>30</v>
@@ -7661,10 +7725,10 @@
     </row>
     <row r="93" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B93" s="2" t="s">
         <v>172</v>
-      </c>
-      <c r="B93" s="2" t="s">
-        <v>173</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>45</v>
@@ -7685,7 +7749,7 @@
         <v>28</v>
       </c>
       <c r="I93" s="11" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="J93" s="2">
         <v>1</v>
@@ -7703,7 +7767,7 @@
         <v>46142</v>
       </c>
       <c r="V93" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="W93" s="2" t="s">
         <v>30</v>
@@ -7717,10 +7781,10 @@
     </row>
     <row r="94" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B94" s="2" t="s">
         <v>172</v>
-      </c>
-      <c r="B94" s="2" t="s">
-        <v>173</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>45</v>
@@ -7741,7 +7805,7 @@
         <v>28</v>
       </c>
       <c r="I94" s="11" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="J94" s="2">
         <v>1</v>
@@ -7759,7 +7823,7 @@
         <v>46142</v>
       </c>
       <c r="V94" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="W94" s="2" t="s">
         <v>30</v>
@@ -7773,13 +7837,13 @@
     </row>
     <row r="95" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B95" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="B95" s="2" t="s">
+      <c r="C95" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="C95" s="2" t="s">
-        <v>153</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>34</v>
@@ -7797,7 +7861,7 @@
         <v>28</v>
       </c>
       <c r="I95" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="J95" s="2">
         <v>1</v>
@@ -7815,14 +7879,26 @@
       <c r="O95" s="4">
         <v>46094</v>
       </c>
+      <c r="Q95" s="4">
+        <v>46111</v>
+      </c>
+      <c r="R95" s="4">
+        <v>46112</v>
+      </c>
+      <c r="S95" s="4">
+        <v>46113</v>
+      </c>
+      <c r="T95" s="4">
+        <v>46113</v>
+      </c>
       <c r="V95" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="W95" s="2" t="s">
         <v>29</v>
       </c>
       <c r="X95" s="2" t="s">
-        <v>100</v>
+        <v>53</v>
       </c>
       <c r="Y95" s="2" t="s">
         <v>58</v>
@@ -7830,13 +7906,13 @@
     </row>
     <row r="96" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B96" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="B96" s="2" t="s">
+      <c r="C96" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="C96" s="2" t="s">
-        <v>153</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>34</v>
@@ -7854,7 +7930,7 @@
         <v>28</v>
       </c>
       <c r="I96" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J96" s="2">
         <v>1</v>
@@ -7872,14 +7948,26 @@
       <c r="O96" s="4">
         <v>46094</v>
       </c>
+      <c r="Q96" s="4">
+        <v>46111</v>
+      </c>
+      <c r="R96" s="4">
+        <v>46112</v>
+      </c>
+      <c r="S96" s="4">
+        <v>46113</v>
+      </c>
+      <c r="T96" s="4">
+        <v>46113</v>
+      </c>
       <c r="V96" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="W96" s="2" t="s">
         <v>29</v>
       </c>
       <c r="X96" s="2" t="s">
-        <v>100</v>
+        <v>53</v>
       </c>
       <c r="Y96" s="2" t="s">
         <v>58</v>
@@ -7887,13 +7975,13 @@
     </row>
     <row r="97" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B97" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="B97" s="2" t="s">
+      <c r="C97" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="C97" s="2" t="s">
-        <v>153</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>34</v>
@@ -7911,7 +7999,7 @@
         <v>28</v>
       </c>
       <c r="I97" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J97" s="2">
         <v>1</v>
@@ -7929,14 +8017,26 @@
       <c r="O97" s="4">
         <v>46094</v>
       </c>
+      <c r="Q97" s="4">
+        <v>46111</v>
+      </c>
+      <c r="R97" s="4">
+        <v>46112</v>
+      </c>
+      <c r="S97" s="4">
+        <v>46113</v>
+      </c>
+      <c r="T97" s="4">
+        <v>46113</v>
+      </c>
       <c r="V97" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="W97" s="2" t="s">
         <v>29</v>
       </c>
       <c r="X97" s="2" t="s">
-        <v>100</v>
+        <v>53</v>
       </c>
       <c r="Y97" s="2" t="s">
         <v>58</v>
@@ -7944,13 +8044,13 @@
     </row>
     <row r="98" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B98" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="B98" s="2" t="s">
+      <c r="C98" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="C98" s="2" t="s">
-        <v>153</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>34</v>
@@ -7968,7 +8068,7 @@
         <v>28</v>
       </c>
       <c r="I98" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J98" s="2">
         <v>1</v>
@@ -7986,14 +8086,26 @@
       <c r="O98" s="4">
         <v>46094</v>
       </c>
+      <c r="Q98" s="4">
+        <v>46111</v>
+      </c>
+      <c r="R98" s="4">
+        <v>46112</v>
+      </c>
+      <c r="S98" s="4">
+        <v>46113</v>
+      </c>
+      <c r="T98" s="4">
+        <v>46113</v>
+      </c>
       <c r="V98" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="W98" s="2" t="s">
         <v>29</v>
       </c>
       <c r="X98" s="2" t="s">
-        <v>100</v>
+        <v>53</v>
       </c>
       <c r="Y98" s="2" t="s">
         <v>58</v>
@@ -8001,13 +8113,13 @@
     </row>
     <row r="99" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B99" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="B99" s="2" t="s">
+      <c r="C99" s="2" t="s">
         <v>189</v>
-      </c>
-      <c r="C99" s="2" t="s">
-        <v>190</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>34</v>
@@ -8025,7 +8137,7 @@
         <v>28</v>
       </c>
       <c r="I99" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="J99" s="2">
         <v>1</v>
@@ -8040,7 +8152,7 @@
         <v>46117</v>
       </c>
       <c r="V99" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="W99" s="2" t="s">
         <v>29</v>
@@ -8054,13 +8166,13 @@
     </row>
     <row r="100" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B100" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="B100" s="2" t="s">
+      <c r="C100" s="2" t="s">
         <v>189</v>
-      </c>
-      <c r="C100" s="2" t="s">
-        <v>190</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>34</v>
@@ -8078,7 +8190,7 @@
         <v>28</v>
       </c>
       <c r="I100" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="J100" s="2">
         <v>1</v>
@@ -8093,7 +8205,7 @@
         <v>46117</v>
       </c>
       <c r="V100" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="W100" s="2" t="s">
         <v>29</v>
@@ -8107,13 +8219,13 @@
     </row>
     <row r="101" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B101" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="B101" s="2" t="s">
+      <c r="C101" s="2" t="s">
         <v>189</v>
-      </c>
-      <c r="C101" s="2" t="s">
-        <v>190</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>34</v>
@@ -8131,7 +8243,7 @@
         <v>28</v>
       </c>
       <c r="I101" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="J101" s="2">
         <v>1</v>
@@ -8146,7 +8258,7 @@
         <v>46117</v>
       </c>
       <c r="V101" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="W101" s="2" t="s">
         <v>29</v>
@@ -8160,13 +8272,13 @@
     </row>
     <row r="102" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B102" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="B102" s="2" t="s">
+      <c r="C102" s="2" t="s">
         <v>189</v>
-      </c>
-      <c r="C102" s="2" t="s">
-        <v>190</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>34</v>
@@ -8184,7 +8296,7 @@
         <v>28</v>
       </c>
       <c r="I102" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="J102" s="2">
         <v>1</v>
@@ -8199,7 +8311,7 @@
         <v>46117</v>
       </c>
       <c r="V102" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="W102" s="2" t="s">
         <v>29</v>
@@ -8213,13 +8325,13 @@
     </row>
     <row r="103" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A103" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B103" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="B103" s="2" t="s">
+      <c r="C103" s="2" t="s">
         <v>189</v>
-      </c>
-      <c r="C103" s="2" t="s">
-        <v>190</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>34</v>
@@ -8237,7 +8349,7 @@
         <v>28</v>
       </c>
       <c r="I103" s="13" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="J103" s="2">
         <v>1</v>
@@ -8252,7 +8364,7 @@
         <v>46117</v>
       </c>
       <c r="V103" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="W103" s="2" t="s">
         <v>29</v>
@@ -8266,13 +8378,13 @@
     </row>
     <row r="104" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B104" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="B104" s="2" t="s">
+      <c r="C104" s="2" t="s">
         <v>189</v>
-      </c>
-      <c r="C104" s="2" t="s">
-        <v>190</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>34</v>
@@ -8290,7 +8402,7 @@
         <v>28</v>
       </c>
       <c r="I104" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J104" s="2">
         <v>1</v>
@@ -8303,16 +8415,22 @@
       </c>
       <c r="M104" s="6"/>
       <c r="N104" s="4">
-        <v>46107</v>
+        <v>46111</v>
+      </c>
+      <c r="O104" s="4">
+        <v>46112</v>
+      </c>
+      <c r="P104" s="4">
+        <v>46111</v>
       </c>
       <c r="V104" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="W104" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="X104" s="2" t="s">
-        <v>137</v>
+        <v>241</v>
       </c>
       <c r="Y104" s="2" t="s">
         <v>58</v>
@@ -8320,13 +8438,13 @@
     </row>
     <row r="105" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A105" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B105" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="B105" s="2" t="s">
+      <c r="C105" s="2" t="s">
         <v>189</v>
-      </c>
-      <c r="C105" s="2" t="s">
-        <v>190</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>34</v>
@@ -8344,7 +8462,7 @@
         <v>28</v>
       </c>
       <c r="I105" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J105" s="2">
         <v>1</v>
@@ -8356,11 +8474,17 @@
         <v>46098</v>
       </c>
       <c r="M105" s="6"/>
+      <c r="N105" s="4">
+        <v>46111</v>
+      </c>
+      <c r="O105" s="4">
+        <v>46112</v>
+      </c>
       <c r="V105" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="W105" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="X105" s="2" t="s">
         <v>137</v>
@@ -8371,13 +8495,13 @@
     </row>
     <row r="106" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A106" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B106" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="B106" s="2" t="s">
+      <c r="C106" s="2" t="s">
         <v>189</v>
-      </c>
-      <c r="C106" s="2" t="s">
-        <v>190</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>34</v>
@@ -8395,7 +8519,7 @@
         <v>28</v>
       </c>
       <c r="I106" s="13" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="J106" s="2">
         <v>1</v>
@@ -8407,14 +8531,23 @@
         <v>46098</v>
       </c>
       <c r="M106" s="6"/>
+      <c r="N106" s="4">
+        <v>46111</v>
+      </c>
+      <c r="O106" s="4">
+        <v>46112</v>
+      </c>
+      <c r="P106" s="4">
+        <v>46111</v>
+      </c>
       <c r="V106" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="W106" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="X106" s="2" t="s">
-        <v>137</v>
+        <v>242</v>
       </c>
       <c r="Y106" s="2" t="s">
         <v>58</v>
@@ -8422,13 +8555,13 @@
     </row>
     <row r="107" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A107" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B107" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="B107" s="2" t="s">
+      <c r="C107" s="2" t="s">
         <v>189</v>
-      </c>
-      <c r="C107" s="2" t="s">
-        <v>190</v>
       </c>
       <c r="D107" s="2" t="s">
         <v>26</v>
@@ -8446,7 +8579,7 @@
         <v>28</v>
       </c>
       <c r="I107" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="J107" s="2">
         <v>1</v>
@@ -8462,7 +8595,7 @@
         <v>46106</v>
       </c>
       <c r="V107" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="W107" s="2" t="s">
         <v>30</v>
@@ -8476,13 +8609,13 @@
     </row>
     <row r="108" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A108" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B108" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="B108" s="2" t="s">
+      <c r="C108" s="2" t="s">
         <v>189</v>
-      </c>
-      <c r="C108" s="2" t="s">
-        <v>190</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>26</v>
@@ -8500,7 +8633,7 @@
         <v>28</v>
       </c>
       <c r="I108" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="J108" s="2">
         <v>1</v>
@@ -8516,7 +8649,7 @@
         <v>46106</v>
       </c>
       <c r="V108" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="W108" s="2" t="s">
         <v>30</v>
@@ -8530,13 +8663,13 @@
     </row>
     <row r="109" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A109" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B109" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="B109" s="2" t="s">
+      <c r="C109" s="2" t="s">
         <v>189</v>
-      </c>
-      <c r="C109" s="2" t="s">
-        <v>190</v>
       </c>
       <c r="D109" s="2" t="s">
         <v>26</v>
@@ -8554,7 +8687,7 @@
         <v>28</v>
       </c>
       <c r="I109" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="J109" s="2">
         <v>1</v>
@@ -8570,7 +8703,7 @@
         <v>46106</v>
       </c>
       <c r="V109" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="W109" s="2" t="s">
         <v>30</v>
@@ -8584,13 +8717,13 @@
     </row>
     <row r="110" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B110" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="B110" s="2" t="s">
+      <c r="C110" s="2" t="s">
         <v>189</v>
-      </c>
-      <c r="C110" s="2" t="s">
-        <v>190</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>26</v>
@@ -8608,7 +8741,7 @@
         <v>28</v>
       </c>
       <c r="I110" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="J110" s="2">
         <v>1</v>
@@ -8624,7 +8757,7 @@
         <v>46106</v>
       </c>
       <c r="V110" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="W110" s="2" t="s">
         <v>30</v>
@@ -8638,13 +8771,13 @@
     </row>
     <row r="111" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A111" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B111" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="B111" s="2" t="s">
+      <c r="C111" s="2" t="s">
         <v>189</v>
-      </c>
-      <c r="C111" s="2" t="s">
-        <v>190</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>26</v>
@@ -8662,7 +8795,7 @@
         <v>28</v>
       </c>
       <c r="I111" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="J111" s="2">
         <v>1</v>
@@ -8678,7 +8811,7 @@
         <v>46106</v>
       </c>
       <c r="V111" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="W111" s="2" t="s">
         <v>30</v>
@@ -8692,13 +8825,13 @@
     </row>
     <row r="112" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B112" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="B112" s="2" t="s">
+      <c r="C112" s="2" t="s">
         <v>189</v>
-      </c>
-      <c r="C112" s="2" t="s">
-        <v>190</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>26</v>
@@ -8716,7 +8849,7 @@
         <v>28</v>
       </c>
       <c r="I112" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J112" s="2">
         <v>1</v>
@@ -8732,7 +8865,7 @@
         <v>46106</v>
       </c>
       <c r="V112" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="W112" s="2" t="s">
         <v>30</v>
@@ -8770,7 +8903,7 @@
         <v>28</v>
       </c>
       <c r="I113" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="J113" s="2">
         <v>1</v>
@@ -8785,7 +8918,7 @@
         <v>46108</v>
       </c>
       <c r="V113" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="W113" s="2" t="s">
         <v>30</v>
@@ -8823,7 +8956,7 @@
         <v>28</v>
       </c>
       <c r="I114" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="J114" s="2">
         <v>1</v>
@@ -8838,7 +8971,7 @@
         <v>46108</v>
       </c>
       <c r="V114" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="W114" s="2" t="s">
         <v>30</v>
@@ -8876,7 +9009,7 @@
         <v>28</v>
       </c>
       <c r="I115" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="J115" s="2">
         <v>1</v>
@@ -8891,7 +9024,7 @@
         <v>46108</v>
       </c>
       <c r="V115" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="W115" s="2" t="s">
         <v>30</v>
@@ -8929,7 +9062,7 @@
         <v>28</v>
       </c>
       <c r="I116" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="J116" s="2">
         <v>1</v>
@@ -8944,7 +9077,7 @@
         <v>46108</v>
       </c>
       <c r="V116" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="W116" s="2" t="s">
         <v>30</v>
@@ -8982,7 +9115,7 @@
         <v>28</v>
       </c>
       <c r="I117" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="J117" s="2">
         <v>1</v>
@@ -8997,7 +9130,7 @@
         <v>46108</v>
       </c>
       <c r="V117" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="W117" s="2" t="s">
         <v>30</v>
@@ -9063,6 +9196,450 @@
         <v>58</v>
       </c>
       <c r="AB118" s="9"/>
+    </row>
+    <row r="119" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A119" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="B119" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="C119" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="D119" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E119" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F119" s="3">
+        <v>0.43</v>
+      </c>
+      <c r="G119" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="H119" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="I119" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="J119" s="2">
+        <v>1</v>
+      </c>
+      <c r="K119" s="2">
+        <v>1</v>
+      </c>
+      <c r="L119" s="4">
+        <v>45896</v>
+      </c>
+      <c r="N119" s="4">
+        <v>45897</v>
+      </c>
+      <c r="O119" s="4">
+        <v>45897</v>
+      </c>
+      <c r="P119" s="4">
+        <v>45897</v>
+      </c>
+      <c r="Q119" s="4">
+        <v>45903</v>
+      </c>
+      <c r="R119" s="4">
+        <v>45905</v>
+      </c>
+      <c r="S119" s="4">
+        <v>45908</v>
+      </c>
+      <c r="T119" s="4">
+        <v>45908</v>
+      </c>
+      <c r="V119" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="W119" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="X119" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y119" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z119" s="4">
+        <v>46112</v>
+      </c>
+    </row>
+    <row r="120" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A120" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="C120" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="D120" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E120" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F120" s="3">
+        <v>0.43</v>
+      </c>
+      <c r="G120" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="H120" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="I120" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="J120" s="2">
+        <v>1</v>
+      </c>
+      <c r="K120" s="2">
+        <v>1</v>
+      </c>
+      <c r="L120" s="4">
+        <v>45896</v>
+      </c>
+      <c r="N120" s="4">
+        <v>45897</v>
+      </c>
+      <c r="O120" s="4">
+        <v>45897</v>
+      </c>
+      <c r="P120" s="4">
+        <v>45897</v>
+      </c>
+      <c r="Q120" s="4">
+        <v>45903</v>
+      </c>
+      <c r="R120" s="4">
+        <v>45905</v>
+      </c>
+      <c r="S120" s="4">
+        <v>45908</v>
+      </c>
+      <c r="T120" s="4">
+        <v>45908</v>
+      </c>
+      <c r="V120" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="W120" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="X120" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y120" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z120" s="4">
+        <v>46112</v>
+      </c>
+    </row>
+    <row r="121" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A121" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="D121" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E121" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F121" s="3">
+        <v>0.43</v>
+      </c>
+      <c r="G121" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="H121" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="I121" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="J121" s="2">
+        <v>1</v>
+      </c>
+      <c r="K121" s="2">
+        <v>1</v>
+      </c>
+      <c r="L121" s="4">
+        <v>45944</v>
+      </c>
+      <c r="N121" s="4">
+        <v>45945</v>
+      </c>
+      <c r="O121" s="4">
+        <v>45947</v>
+      </c>
+      <c r="P121" s="4">
+        <v>45950</v>
+      </c>
+      <c r="Q121" s="4">
+        <v>45954</v>
+      </c>
+      <c r="R121" s="4">
+        <v>45957</v>
+      </c>
+      <c r="S121" s="4">
+        <v>45958</v>
+      </c>
+      <c r="T121" s="4">
+        <v>45958</v>
+      </c>
+      <c r="V121" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="W121" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="X121" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y121" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z121" s="4">
+        <v>46112</v>
+      </c>
+    </row>
+    <row r="122" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A122" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="C122" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="D122" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E122" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F122" s="3">
+        <v>0.43</v>
+      </c>
+      <c r="G122" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="H122" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="I122" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="J122" s="2">
+        <v>1</v>
+      </c>
+      <c r="K122" s="2">
+        <v>1</v>
+      </c>
+      <c r="L122" s="4">
+        <v>45944</v>
+      </c>
+      <c r="N122" s="4">
+        <v>45945</v>
+      </c>
+      <c r="O122" s="4">
+        <v>45947</v>
+      </c>
+      <c r="P122" s="4">
+        <v>45950</v>
+      </c>
+      <c r="Q122" s="4">
+        <v>45954</v>
+      </c>
+      <c r="R122" s="4">
+        <v>45957</v>
+      </c>
+      <c r="S122" s="4">
+        <v>45958</v>
+      </c>
+      <c r="T122" s="4">
+        <v>45958</v>
+      </c>
+      <c r="V122" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="W122" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="X122" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y122" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z122" s="4">
+        <v>46112</v>
+      </c>
+    </row>
+    <row r="123" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A123" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="B123" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="C123" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="D123" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E123" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F123" s="3">
+        <v>0.43</v>
+      </c>
+      <c r="G123" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="H123" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="I123" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="J123" s="2">
+        <v>1</v>
+      </c>
+      <c r="K123" s="2">
+        <v>1</v>
+      </c>
+      <c r="L123" s="4">
+        <v>46024</v>
+      </c>
+      <c r="N123" s="4">
+        <v>46044</v>
+      </c>
+      <c r="O123" s="4">
+        <v>46044</v>
+      </c>
+      <c r="P123" s="4">
+        <v>46045</v>
+      </c>
+      <c r="Q123" s="4">
+        <v>46052</v>
+      </c>
+      <c r="R123" s="4">
+        <v>46055</v>
+      </c>
+      <c r="S123" s="4">
+        <v>46058</v>
+      </c>
+      <c r="T123" s="4">
+        <v>46058</v>
+      </c>
+      <c r="V123" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="W123" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="X123" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y123" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z123" s="4">
+        <v>46112</v>
+      </c>
+    </row>
+    <row r="124" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A124" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="B124" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="C124" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="D124" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E124" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F124" s="3">
+        <v>0.43</v>
+      </c>
+      <c r="G124" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="H124" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="I124" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="J124" s="2">
+        <v>1</v>
+      </c>
+      <c r="K124" s="2">
+        <v>1</v>
+      </c>
+      <c r="L124" s="4">
+        <v>46024</v>
+      </c>
+      <c r="N124" s="4">
+        <v>46044</v>
+      </c>
+      <c r="O124" s="4">
+        <v>46044</v>
+      </c>
+      <c r="P124" s="4">
+        <v>46045</v>
+      </c>
+      <c r="Q124" s="4">
+        <v>46052</v>
+      </c>
+      <c r="R124" s="4">
+        <v>46055</v>
+      </c>
+      <c r="S124" s="4">
+        <v>46058</v>
+      </c>
+      <c r="T124" s="4">
+        <v>46058</v>
+      </c>
+      <c r="V124" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="W124" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="X124" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y124" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z124" s="4">
+        <v>46112</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="V1:V42"/>
@@ -9374,7 +9951,7 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="H7" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>

--- a/sample-list.xlsx
+++ b/sample-list.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25200" windowHeight="11025"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13965"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,14 +19,14 @@
     <externalReference r:id="rId3"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$V$1:$V$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$V$1:$V$136</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1395" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1532" uniqueCount="274">
   <si>
     <t>국가</t>
   </si>
@@ -873,10 +873,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Winsome brown 1M -3.75</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Winsome brown 1M -4.00</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1042,6 +1038,87 @@
   </si>
   <si>
     <t>FRP</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Winsome brown 1M -2.00</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Winsome brown 1M -2.25</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>대기</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Winsome brown 1M -3.25</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Winsome brown 1M -4.25</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Winsome brown 1M -5.00</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Winsome brown 1M -5.25</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Winsome brown 1M -6.00</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Winsome brown 1M -7.50</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>대기</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Beige Glow</t>
+  </si>
+  <si>
+    <t>Orange Glow</t>
+  </si>
+  <si>
+    <t>Purple Glow</t>
+  </si>
+  <si>
+    <t>중국</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Lemonade</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>임건훈</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1D</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>S27</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>임수빈</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>S25C</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>제안렌즈</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1195,7 +1272,21 @@
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="22">
+  <dxfs count="24">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1661,7 +1752,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AB124"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:AB136"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.25" style="2" customWidth="1"/>
@@ -1769,7 +1861,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>43</v>
       </c>
@@ -1846,7 +1938,7 @@
         <v>46041</v>
       </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>43</v>
       </c>
@@ -2000,7 +2092,7 @@
         <v>46041</v>
       </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>43</v>
       </c>
@@ -2077,7 +2169,7 @@
         <v>46041</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>43</v>
       </c>
@@ -2154,7 +2246,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>43</v>
       </c>
@@ -2291,7 +2383,7 @@
         <v>45975</v>
       </c>
       <c r="V8" s="2" t="s">
-        <v>66</v>
+        <v>271</v>
       </c>
       <c r="W8" s="2" t="s">
         <v>30</v>
@@ -2335,7 +2427,7 @@
         <v>28</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>68</v>
+        <v>270</v>
       </c>
       <c r="J9" s="2">
         <v>1</v>
@@ -2343,32 +2435,32 @@
       <c r="K9" s="2">
         <v>2</v>
       </c>
-      <c r="L9" s="4">
-        <v>45992</v>
+      <c r="L9" s="5">
+        <v>45790</v>
       </c>
       <c r="M9" s="4">
-        <v>46030</v>
+        <v>45853</v>
       </c>
       <c r="N9" s="4">
-        <v>46030</v>
+        <v>45853</v>
       </c>
       <c r="O9" s="4">
-        <v>46035</v>
+        <v>45853</v>
       </c>
       <c r="P9" s="4">
-        <v>46031</v>
+        <v>45864</v>
       </c>
       <c r="Q9" s="4">
-        <v>46035</v>
+        <v>45894</v>
       </c>
       <c r="R9" s="4">
-        <v>46036</v>
+        <v>45895</v>
       </c>
       <c r="S9" s="4">
-        <v>45975</v>
+        <v>45896</v>
       </c>
       <c r="T9" s="4">
-        <v>45975</v>
+        <v>45896</v>
       </c>
       <c r="V9" s="2" t="s">
         <v>66</v>
@@ -2380,7 +2472,13 @@
         <v>53</v>
       </c>
       <c r="Y9" s="2" t="s">
-        <v>67</v>
+        <v>58</v>
+      </c>
+      <c r="Z9" s="4">
+        <v>45982</v>
+      </c>
+      <c r="AA9" s="4">
+        <v>46064</v>
       </c>
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.3">
@@ -2409,7 +2507,7 @@
         <v>28</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>135</v>
+        <v>272</v>
       </c>
       <c r="J10" s="2">
         <v>1</v>
@@ -2417,28 +2515,32 @@
       <c r="K10" s="2">
         <v>1</v>
       </c>
-      <c r="L10" s="4">
-        <v>45713</v>
-      </c>
-      <c r="M10" s="5"/>
+      <c r="L10" s="5">
+        <v>45887</v>
+      </c>
+      <c r="M10" s="4">
+        <v>45887</v>
+      </c>
       <c r="N10" s="4">
-        <v>46219</v>
+        <v>45889</v>
       </c>
       <c r="O10" s="4">
-        <v>46221</v>
-      </c>
-      <c r="P10" s="5"/>
+        <v>45890</v>
+      </c>
+      <c r="P10" s="4">
+        <v>45892</v>
+      </c>
       <c r="Q10" s="4">
-        <v>46231</v>
+        <v>45914</v>
       </c>
       <c r="R10" s="4">
-        <v>46232</v>
+        <v>45915</v>
       </c>
       <c r="S10" s="4">
-        <v>46234</v>
+        <v>45916</v>
       </c>
       <c r="T10" s="4">
-        <v>45869</v>
+        <v>45916</v>
       </c>
       <c r="V10" s="2" t="s">
         <v>66</v>
@@ -2449,114 +2551,123 @@
       <c r="X10" s="2" t="s">
         <v>53</v>
       </c>
+      <c r="Y10" s="2" t="s">
+        <v>58</v>
+      </c>
       <c r="Z10" s="4">
-        <v>46065</v>
+        <v>46003</v>
       </c>
       <c r="AA10" s="4">
-        <v>46078</v>
+        <v>46052</v>
       </c>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F11" s="3">
-        <v>0.43</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="G11" s="7">
-        <v>14.5</v>
+        <v>14.2</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>28</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="J11" s="2">
         <v>1</v>
       </c>
       <c r="K11" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L11" s="4">
-        <v>46042</v>
+        <v>45992</v>
       </c>
       <c r="M11" s="4">
-        <v>46042</v>
+        <v>46030</v>
       </c>
       <c r="N11" s="4">
-        <v>46044</v>
+        <v>46030</v>
       </c>
       <c r="O11" s="4">
-        <v>46044</v>
+        <v>46035</v>
       </c>
       <c r="P11" s="4">
-        <v>46045</v>
+        <v>46031</v>
       </c>
       <c r="Q11" s="4">
-        <v>46051</v>
+        <v>46035</v>
       </c>
       <c r="R11" s="4">
-        <v>46057</v>
+        <v>46036</v>
       </c>
       <c r="S11" s="4">
-        <v>46058</v>
+        <v>45975</v>
       </c>
       <c r="T11" s="4">
-        <v>46058</v>
+        <v>45975</v>
       </c>
       <c r="V11" s="2" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="W11" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="X11" s="2" t="s">
         <v>53</v>
       </c>
       <c r="Y11" s="2" t="s">
-        <v>58</v>
+        <v>67</v>
+      </c>
+      <c r="Z11" s="4">
+        <v>46064</v>
+      </c>
+      <c r="AA11" s="4">
+        <v>46077</v>
       </c>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F12" s="3">
-        <v>0.43</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="G12" s="7">
-        <v>14.5</v>
+        <v>14.2</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>28</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>73</v>
+        <v>135</v>
       </c>
       <c r="J12" s="2">
         <v>1</v>
@@ -2565,37 +2676,33 @@
         <v>1</v>
       </c>
       <c r="L12" s="4">
-        <v>46042</v>
-      </c>
-      <c r="M12" s="4">
-        <v>46042</v>
-      </c>
+        <v>45713</v>
+      </c>
+      <c r="M12" s="5"/>
       <c r="N12" s="4">
-        <v>46044</v>
+        <v>46219</v>
       </c>
       <c r="O12" s="4">
-        <v>46044</v>
-      </c>
-      <c r="P12" s="4">
-        <v>46045</v>
-      </c>
+        <v>46221</v>
+      </c>
+      <c r="P12" s="5"/>
       <c r="Q12" s="4">
-        <v>46051</v>
+        <v>46231</v>
       </c>
       <c r="R12" s="4">
-        <v>46057</v>
+        <v>46232</v>
       </c>
       <c r="S12" s="4">
-        <v>46058</v>
+        <v>46234</v>
       </c>
       <c r="T12" s="4">
-        <v>46058</v>
+        <v>45869</v>
       </c>
       <c r="V12" s="2" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="W12" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="X12" s="2" t="s">
         <v>53</v>
@@ -2603,8 +2710,14 @@
       <c r="Y12" s="2" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="Z12" s="4">
+        <v>46064</v>
+      </c>
+      <c r="AA12" s="4">
+        <v>46078</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>69</v>
       </c>
@@ -2630,7 +2743,7 @@
         <v>28</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="J13" s="2">
         <v>1</v>
@@ -2666,7 +2779,7 @@
         <v>46058</v>
       </c>
       <c r="V13" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="W13" s="2" t="s">
         <v>33</v>
@@ -2678,24 +2791,24 @@
         <v>58</v>
       </c>
     </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F14" s="3">
-        <v>0.55000000000000004</v>
+        <v>0.43</v>
       </c>
       <c r="G14" s="7">
         <v>14.5</v>
@@ -2704,7 +2817,7 @@
         <v>28</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="J14" s="2">
         <v>1</v>
@@ -2713,35 +2826,37 @@
         <v>1</v>
       </c>
       <c r="L14" s="4">
-        <v>45995</v>
-      </c>
-      <c r="M14" s="5"/>
+        <v>46042</v>
+      </c>
+      <c r="M14" s="4">
+        <v>46042</v>
+      </c>
       <c r="N14" s="4">
-        <v>46003</v>
+        <v>46044</v>
       </c>
       <c r="O14" s="4">
-        <v>46007</v>
+        <v>46044</v>
       </c>
       <c r="P14" s="4">
-        <v>46003</v>
+        <v>46045</v>
       </c>
       <c r="Q14" s="4">
-        <v>46014</v>
+        <v>46051</v>
       </c>
       <c r="R14" s="4">
-        <v>46015</v>
+        <v>46057</v>
       </c>
       <c r="S14" s="4">
-        <v>46015</v>
+        <v>46058</v>
       </c>
       <c r="T14" s="4">
-        <v>46015</v>
+        <v>46058</v>
       </c>
       <c r="V14" s="2" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="W14" s="2" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="X14" s="2" t="s">
         <v>53</v>
@@ -2750,24 +2865,24 @@
         <v>58</v>
       </c>
     </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F15" s="3">
-        <v>0.55000000000000004</v>
+        <v>0.43</v>
       </c>
       <c r="G15" s="7">
         <v>14.5</v>
@@ -2776,7 +2891,7 @@
         <v>28</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="J15" s="2">
         <v>1</v>
@@ -2785,35 +2900,37 @@
         <v>1</v>
       </c>
       <c r="L15" s="4">
-        <v>45995</v>
-      </c>
-      <c r="M15" s="5"/>
+        <v>46042</v>
+      </c>
+      <c r="M15" s="4">
+        <v>46042</v>
+      </c>
       <c r="N15" s="4">
-        <v>46003</v>
+        <v>46044</v>
       </c>
       <c r="O15" s="4">
-        <v>46007</v>
+        <v>46044</v>
       </c>
       <c r="P15" s="4">
-        <v>46003</v>
+        <v>46045</v>
       </c>
       <c r="Q15" s="4">
-        <v>46014</v>
+        <v>46051</v>
       </c>
       <c r="R15" s="4">
-        <v>46015</v>
+        <v>46057</v>
       </c>
       <c r="S15" s="4">
-        <v>46015</v>
+        <v>46058</v>
       </c>
       <c r="T15" s="4">
-        <v>46015</v>
+        <v>46058</v>
       </c>
       <c r="V15" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="W15" s="2" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="X15" s="2" t="s">
         <v>53</v>
@@ -2857,25 +2974,29 @@
         <v>1</v>
       </c>
       <c r="L16" s="4">
-        <v>46055</v>
+        <v>45995</v>
       </c>
       <c r="M16" s="5"/>
-      <c r="N16" s="5"/>
-      <c r="O16" s="5"/>
+      <c r="N16" s="4">
+        <v>46003</v>
+      </c>
+      <c r="O16" s="4">
+        <v>46007</v>
+      </c>
       <c r="P16" s="4">
-        <v>46038</v>
+        <v>46003</v>
       </c>
       <c r="Q16" s="4">
-        <v>46043</v>
+        <v>46014</v>
       </c>
       <c r="R16" s="4">
-        <v>46045</v>
+        <v>46015</v>
       </c>
       <c r="S16" s="4">
-        <v>46045</v>
+        <v>46015</v>
       </c>
       <c r="T16" s="4">
-        <v>46045</v>
+        <v>46015</v>
       </c>
       <c r="V16" s="2" t="s">
         <v>81</v>
@@ -2888,9 +3009,6 @@
       </c>
       <c r="Y16" s="2" t="s">
         <v>58</v>
-      </c>
-      <c r="AB16" s="2" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="17" spans="1:28" x14ac:dyDescent="0.3">
@@ -2928,25 +3046,29 @@
         <v>1</v>
       </c>
       <c r="L17" s="4">
-        <v>46055</v>
+        <v>45995</v>
       </c>
       <c r="M17" s="5"/>
-      <c r="N17" s="5"/>
-      <c r="O17" s="5"/>
+      <c r="N17" s="4">
+        <v>46003</v>
+      </c>
+      <c r="O17" s="4">
+        <v>46007</v>
+      </c>
       <c r="P17" s="4">
-        <v>46038</v>
+        <v>46003</v>
       </c>
       <c r="Q17" s="4">
-        <v>46043</v>
+        <v>46014</v>
       </c>
       <c r="R17" s="4">
-        <v>46045</v>
+        <v>46015</v>
       </c>
       <c r="S17" s="4">
-        <v>46045</v>
+        <v>46015</v>
       </c>
       <c r="T17" s="4">
-        <v>46045</v>
+        <v>46015</v>
       </c>
       <c r="V17" s="2" t="s">
         <v>81</v>
@@ -2959,9 +3081,6 @@
       </c>
       <c r="Y17" s="2" t="s">
         <v>58</v>
-      </c>
-      <c r="AB17" s="2" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="18" spans="1:28" x14ac:dyDescent="0.3">
@@ -2996,37 +3115,28 @@
         <v>1</v>
       </c>
       <c r="K18" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L18" s="4">
-        <v>45995</v>
-      </c>
-      <c r="M18" s="4">
         <v>46055</v>
       </c>
-      <c r="N18" s="4">
-        <v>46057</v>
-      </c>
-      <c r="O18" s="4">
-        <v>46064</v>
-      </c>
-      <c r="P18" s="10">
-        <v>46065</v>
+      <c r="M18" s="5"/>
+      <c r="N18" s="5"/>
+      <c r="O18" s="5"/>
+      <c r="P18" s="4">
+        <v>46038</v>
       </c>
       <c r="Q18" s="4">
-        <v>46075</v>
+        <v>46043</v>
       </c>
       <c r="R18" s="4">
-        <v>46076</v>
+        <v>46045</v>
       </c>
       <c r="S18" s="4">
-        <v>46076</v>
+        <v>46045</v>
       </c>
       <c r="T18" s="4">
-        <v>46076</v>
-      </c>
-      <c r="U18" s="4">
-        <v>46077</v>
+        <v>46045</v>
       </c>
       <c r="V18" s="2" t="s">
         <v>81</v>
@@ -3040,8 +3150,8 @@
       <c r="Y18" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="AB18" s="9" t="s">
-        <v>87</v>
+      <c r="AB18" s="2" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="19" spans="1:28" x14ac:dyDescent="0.3">
@@ -3076,37 +3186,28 @@
         <v>1</v>
       </c>
       <c r="K19" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L19" s="4">
-        <v>45995</v>
-      </c>
-      <c r="M19" s="4">
         <v>46055</v>
       </c>
-      <c r="N19" s="4">
-        <v>46057</v>
-      </c>
-      <c r="O19" s="4">
-        <v>46064</v>
-      </c>
-      <c r="P19" s="10">
-        <v>46065</v>
+      <c r="M19" s="5"/>
+      <c r="N19" s="5"/>
+      <c r="O19" s="5"/>
+      <c r="P19" s="4">
+        <v>46038</v>
       </c>
       <c r="Q19" s="4">
-        <v>46075</v>
+        <v>46043</v>
       </c>
       <c r="R19" s="4">
-        <v>46076</v>
+        <v>46045</v>
       </c>
       <c r="S19" s="4">
-        <v>46076</v>
+        <v>46045</v>
       </c>
       <c r="T19" s="4">
-        <v>46076</v>
-      </c>
-      <c r="U19" s="4">
-        <v>46077</v>
+        <v>46045</v>
       </c>
       <c r="V19" s="2" t="s">
         <v>81</v>
@@ -3120,19 +3221,19 @@
       <c r="Y19" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="AB19" s="9" t="s">
-        <v>87</v>
+      <c r="AB19" s="2" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="20" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>34</v>
@@ -3150,66 +3251,72 @@
         <v>28</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="J20" s="2">
         <v>1</v>
       </c>
       <c r="K20" s="2">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="L20" s="4">
-        <v>45644</v>
-      </c>
-      <c r="M20" s="10">
-        <v>46063</v>
-      </c>
-      <c r="N20" s="10">
-        <v>46063</v>
-      </c>
-      <c r="O20" s="10">
-        <v>46063</v>
+        <v>45995</v>
+      </c>
+      <c r="M20" s="4">
+        <v>46055</v>
+      </c>
+      <c r="N20" s="4">
+        <v>46057</v>
+      </c>
+      <c r="O20" s="4">
+        <v>46064</v>
       </c>
       <c r="P20" s="10">
-        <v>46063</v>
-      </c>
-      <c r="Q20" s="10">
-        <v>46073</v>
+        <v>46065</v>
+      </c>
+      <c r="Q20" s="4">
+        <v>46075</v>
       </c>
       <c r="R20" s="4">
         <v>46076</v>
       </c>
       <c r="S20" s="4">
-        <v>46079</v>
+        <v>46076</v>
       </c>
       <c r="T20" s="4">
-        <v>46079</v>
+        <v>46076</v>
+      </c>
+      <c r="U20" s="4">
+        <v>46077</v>
       </c>
       <c r="V20" s="2" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="W20" s="2" t="s">
-        <v>92</v>
+        <v>29</v>
       </c>
       <c r="X20" s="2" t="s">
         <v>53</v>
       </c>
       <c r="Y20" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="AB20" s="2" t="s">
-        <v>97</v>
+        <v>58</v>
+      </c>
+      <c r="Z20" s="4">
+        <v>46107</v>
+      </c>
+      <c r="AB20" s="9" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="21" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>34</v>
@@ -3227,66 +3334,66 @@
         <v>28</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="J21" s="2">
         <v>1</v>
       </c>
       <c r="K21" s="2">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="L21" s="4">
-        <v>45644</v>
-      </c>
-      <c r="M21" s="10">
-        <v>46063</v>
-      </c>
-      <c r="N21" s="10">
-        <v>46063</v>
-      </c>
-      <c r="O21" s="10">
-        <v>46063</v>
+        <v>45995</v>
+      </c>
+      <c r="M21" s="4">
+        <v>46055</v>
+      </c>
+      <c r="N21" s="4">
+        <v>46057</v>
+      </c>
+      <c r="O21" s="4">
+        <v>46064</v>
       </c>
       <c r="P21" s="10">
-        <v>46063</v>
-      </c>
-      <c r="Q21" s="10">
-        <v>46073</v>
+        <v>46065</v>
+      </c>
+      <c r="Q21" s="4">
+        <v>46075</v>
       </c>
       <c r="R21" s="4">
         <v>46076</v>
       </c>
       <c r="S21" s="4">
-        <v>46079</v>
+        <v>46076</v>
       </c>
       <c r="T21" s="4">
-        <v>46079</v>
+        <v>46076</v>
+      </c>
+      <c r="U21" s="4">
+        <v>46077</v>
       </c>
       <c r="V21" s="2" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="W21" s="2" t="s">
-        <v>92</v>
+        <v>29</v>
       </c>
       <c r="X21" s="2" t="s">
         <v>53</v>
       </c>
       <c r="Y21" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="Z21" s="4">
-        <v>46092</v>
-      </c>
-      <c r="AB21" s="2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="22" spans="1:28" x14ac:dyDescent="0.3">
+        <v>58</v>
+      </c>
+      <c r="AB21" s="9" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="22" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>62</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>64</v>
@@ -3307,13 +3414,13 @@
         <v>28</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>178</v>
+        <v>90</v>
       </c>
       <c r="J22" s="2">
         <v>1</v>
       </c>
       <c r="K22" s="2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L22" s="4">
         <v>45644</v>
@@ -3322,28 +3429,28 @@
         <v>46063</v>
       </c>
       <c r="N22" s="10">
-        <v>45940</v>
+        <v>46063</v>
       </c>
       <c r="O22" s="10">
-        <v>45940</v>
-      </c>
-      <c r="P22" s="4">
-        <v>45959</v>
-      </c>
-      <c r="Q22" s="4">
-        <v>45963</v>
+        <v>46063</v>
+      </c>
+      <c r="P22" s="10">
+        <v>46063</v>
+      </c>
+      <c r="Q22" s="10">
+        <v>46073</v>
       </c>
       <c r="R22" s="4">
-        <v>45965</v>
+        <v>46076</v>
       </c>
       <c r="S22" s="4">
-        <v>45966</v>
+        <v>46079</v>
       </c>
       <c r="T22" s="4">
-        <v>45966</v>
+        <v>46079</v>
       </c>
       <c r="V22" s="2" t="s">
-        <v>51</v>
+        <v>93</v>
       </c>
       <c r="W22" s="2" t="s">
         <v>92</v>
@@ -3354,16 +3461,16 @@
       <c r="Y22" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="Z22" s="4">
-        <v>46065</v>
-      </c>
-    </row>
-    <row r="23" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="AB22" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="23" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>62</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>64</v>
@@ -3384,43 +3491,43 @@
         <v>28</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>179</v>
+        <v>91</v>
       </c>
       <c r="J23" s="2">
         <v>1</v>
       </c>
       <c r="K23" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L23" s="4">
-        <v>45800</v>
+        <v>45644</v>
       </c>
       <c r="M23" s="10">
-        <v>45999</v>
+        <v>46063</v>
       </c>
       <c r="N23" s="10">
-        <v>46000</v>
+        <v>46063</v>
       </c>
       <c r="O23" s="10">
-        <v>46001</v>
+        <v>46063</v>
       </c>
       <c r="P23" s="10">
-        <v>46011</v>
-      </c>
-      <c r="Q23" s="4">
-        <v>46025</v>
+        <v>46063</v>
+      </c>
+      <c r="Q23" s="10">
+        <v>46073</v>
       </c>
       <c r="R23" s="4">
-        <v>46034</v>
+        <v>46076</v>
       </c>
       <c r="S23" s="4">
-        <v>46035</v>
+        <v>46079</v>
       </c>
       <c r="T23" s="4">
-        <v>46035</v>
+        <v>46079</v>
       </c>
       <c r="V23" s="2" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="W23" s="2" t="s">
         <v>92</v>
@@ -3432,14 +3539,13 @@
         <v>67</v>
       </c>
       <c r="Z23" s="4">
-        <v>46065</v>
-      </c>
-      <c r="AA23" s="4">
-        <v>46112</v>
-      </c>
-      <c r="AB23" s="4"/>
-    </row>
-    <row r="24" spans="1:28" x14ac:dyDescent="0.3">
+        <v>46092</v>
+      </c>
+      <c r="AB23" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="24" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>62</v>
       </c>
@@ -3462,46 +3568,46 @@
         <v>14.5</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>180</v>
+        <v>28</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="J24" s="2">
         <v>1</v>
       </c>
       <c r="K24" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L24" s="4">
-        <v>45302</v>
+        <v>45644</v>
       </c>
       <c r="M24" s="10">
-        <v>45645</v>
+        <v>46063</v>
       </c>
       <c r="N24" s="10">
-        <v>45652</v>
+        <v>45940</v>
       </c>
       <c r="O24" s="10">
-        <v>45652</v>
-      </c>
-      <c r="P24" s="10">
-        <v>45670</v>
-      </c>
-      <c r="Q24" s="10">
-        <v>45672</v>
-      </c>
-      <c r="R24" s="10">
-        <v>45672</v>
+        <v>45940</v>
+      </c>
+      <c r="P24" s="4">
+        <v>45959</v>
+      </c>
+      <c r="Q24" s="4">
+        <v>45963</v>
+      </c>
+      <c r="R24" s="4">
+        <v>45965</v>
       </c>
       <c r="S24" s="4">
-        <v>45673</v>
+        <v>45966</v>
       </c>
       <c r="T24" s="4">
-        <v>45673</v>
+        <v>45966</v>
       </c>
       <c r="V24" s="2" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="W24" s="2" t="s">
         <v>92</v>
@@ -3513,10 +3619,10 @@
         <v>67</v>
       </c>
       <c r="Z24" s="4">
-        <v>46092</v>
-      </c>
-    </row>
-    <row r="25" spans="1:28" x14ac:dyDescent="0.3">
+        <v>46065</v>
+      </c>
+    </row>
+    <row r="25" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>62</v>
       </c>
@@ -3542,44 +3648,62 @@
         <v>28</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>107</v>
+        <v>179</v>
       </c>
       <c r="J25" s="2">
         <v>1</v>
       </c>
       <c r="K25" s="2">
-        <v>1</v>
-      </c>
-      <c r="L25" s="6"/>
-      <c r="M25" s="6"/>
-      <c r="N25" s="6"/>
-      <c r="O25" s="6"/>
+        <v>5</v>
+      </c>
+      <c r="L25" s="4">
+        <v>45800</v>
+      </c>
+      <c r="M25" s="10">
+        <v>45999</v>
+      </c>
+      <c r="N25" s="10">
+        <v>46000</v>
+      </c>
+      <c r="O25" s="10">
+        <v>46001</v>
+      </c>
       <c r="P25" s="10">
-        <v>46065</v>
-      </c>
-      <c r="Q25" s="10">
-        <v>46075</v>
+        <v>46011</v>
+      </c>
+      <c r="Q25" s="4">
+        <v>46025</v>
       </c>
       <c r="R25" s="4">
-        <v>46076</v>
+        <v>46034</v>
       </c>
       <c r="S25" s="4">
-        <v>46077</v>
+        <v>46035</v>
       </c>
       <c r="T25" s="4">
-        <v>46077</v>
+        <v>46035</v>
       </c>
       <c r="V25" s="2" t="s">
         <v>76</v>
       </c>
       <c r="W25" s="2" t="s">
-        <v>29</v>
+        <v>92</v>
       </c>
       <c r="X25" s="2" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="26" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="Y25" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z25" s="4">
+        <v>46065</v>
+      </c>
+      <c r="AA25" s="4">
+        <v>46112</v>
+      </c>
+      <c r="AB25" s="4"/>
+    </row>
+    <row r="26" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>62</v>
       </c>
@@ -3602,47 +3726,61 @@
         <v>14.5</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>28</v>
+        <v>180</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>108</v>
+        <v>181</v>
       </c>
       <c r="J26" s="2">
         <v>1</v>
       </c>
       <c r="K26" s="2">
-        <v>1</v>
-      </c>
-      <c r="L26" s="6"/>
-      <c r="M26" s="6"/>
-      <c r="N26" s="6"/>
-      <c r="O26" s="6"/>
+        <v>2</v>
+      </c>
+      <c r="L26" s="4">
+        <v>45302</v>
+      </c>
+      <c r="M26" s="10">
+        <v>45645</v>
+      </c>
+      <c r="N26" s="10">
+        <v>45652</v>
+      </c>
+      <c r="O26" s="10">
+        <v>45652</v>
+      </c>
       <c r="P26" s="10">
-        <v>46065</v>
+        <v>45670</v>
       </c>
       <c r="Q26" s="10">
-        <v>46075</v>
-      </c>
-      <c r="R26" s="4">
-        <v>46076</v>
+        <v>45672</v>
+      </c>
+      <c r="R26" s="10">
+        <v>45672</v>
       </c>
       <c r="S26" s="4">
-        <v>46077</v>
+        <v>45673</v>
       </c>
       <c r="T26" s="4">
-        <v>46077</v>
+        <v>45673</v>
       </c>
       <c r="V26" s="2" t="s">
         <v>76</v>
       </c>
       <c r="W26" s="2" t="s">
-        <v>29</v>
+        <v>92</v>
       </c>
       <c r="X26" s="2" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="27" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="Y26" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z26" s="4">
+        <v>46092</v>
+      </c>
+    </row>
+    <row r="27" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>62</v>
       </c>
@@ -3668,7 +3806,7 @@
         <v>28</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="J27" s="2">
         <v>1</v>
@@ -3696,7 +3834,7 @@
         <v>46077</v>
       </c>
       <c r="V27" s="2" t="s">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="W27" s="2" t="s">
         <v>29</v>
@@ -3705,7 +3843,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="28" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>62</v>
       </c>
@@ -3731,7 +3869,7 @@
         <v>28</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="J28" s="2">
         <v>1</v>
@@ -3759,7 +3897,7 @@
         <v>46077</v>
       </c>
       <c r="V28" s="2" t="s">
-        <v>99</v>
+        <v>76</v>
       </c>
       <c r="W28" s="2" t="s">
         <v>29</v>
@@ -3788,13 +3926,13 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G29" s="7">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>28</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="J29" s="2">
         <v>1</v>
@@ -3822,7 +3960,7 @@
         <v>46077</v>
       </c>
       <c r="V29" s="2" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="W29" s="2" t="s">
         <v>29</v>
@@ -3830,8 +3968,11 @@
       <c r="X29" s="2" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="30" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="Y29" s="2" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="30" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>62</v>
       </c>
@@ -3851,13 +3992,13 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G30" s="7">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>28</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="J30" s="2">
         <v>1</v>
@@ -3885,7 +4026,7 @@
         <v>46077</v>
       </c>
       <c r="V30" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="W30" s="2" t="s">
         <v>29</v>
@@ -3893,11 +4034,8 @@
       <c r="X30" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="Y30" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="31" spans="1:28" x14ac:dyDescent="0.3">
+    </row>
+    <row r="31" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>62</v>
       </c>
@@ -3923,7 +4061,7 @@
         <v>28</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="J31" s="2">
         <v>1</v>
@@ -3936,13 +4074,13 @@
       <c r="N31" s="6"/>
       <c r="O31" s="6"/>
       <c r="P31" s="10">
-        <v>46066</v>
+        <v>46065</v>
       </c>
       <c r="Q31" s="10">
-        <v>46071</v>
+        <v>46075</v>
       </c>
       <c r="R31" s="4">
-        <v>46077</v>
+        <v>46076</v>
       </c>
       <c r="S31" s="4">
         <v>46077</v>
@@ -3951,7 +4089,7 @@
         <v>46077</v>
       </c>
       <c r="V31" s="2" t="s">
-        <v>99</v>
+        <v>76</v>
       </c>
       <c r="W31" s="2" t="s">
         <v>29</v>
@@ -3962,13 +4100,13 @@
     </row>
     <row r="32" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>34</v>
@@ -3980,13 +4118,13 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G32" s="7">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>28</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>95</v>
+        <v>112</v>
       </c>
       <c r="J32" s="2">
         <v>1</v>
@@ -3994,55 +4132,47 @@
       <c r="K32" s="2">
         <v>1</v>
       </c>
-      <c r="L32" s="10">
-        <v>46063</v>
-      </c>
-      <c r="M32" s="10">
-        <v>46063</v>
-      </c>
-      <c r="N32" s="10">
-        <v>46063</v>
-      </c>
-      <c r="O32" s="10">
-        <v>46066</v>
-      </c>
+      <c r="L32" s="6"/>
+      <c r="M32" s="6"/>
+      <c r="N32" s="6"/>
+      <c r="O32" s="6"/>
       <c r="P32" s="10">
-        <v>46074</v>
-      </c>
-      <c r="Q32" s="4">
+        <v>46065</v>
+      </c>
+      <c r="Q32" s="10">
+        <v>46075</v>
+      </c>
+      <c r="R32" s="4">
         <v>46076</v>
       </c>
-      <c r="R32" s="4">
-        <v>46078</v>
-      </c>
       <c r="S32" s="4">
-        <v>46080</v>
+        <v>46077</v>
       </c>
       <c r="T32" s="4">
-        <v>46080</v>
+        <v>46077</v>
       </c>
       <c r="V32" s="2" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="W32" s="2" t="s">
-        <v>96</v>
+        <v>29</v>
       </c>
       <c r="X32" s="2" t="s">
         <v>53</v>
       </c>
       <c r="Y32" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="33" spans="1:25" x14ac:dyDescent="0.3">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="33" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>106</v>
+        <v>62</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>105</v>
+        <v>63</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>104</v>
+        <v>64</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>34</v>
@@ -4060,7 +4190,7 @@
         <v>28</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="J33" s="2">
         <v>1</v>
@@ -4068,49 +4198,44 @@
       <c r="K33" s="2">
         <v>1</v>
       </c>
-      <c r="L33" s="4">
-        <v>46052</v>
-      </c>
+      <c r="L33" s="6"/>
       <c r="M33" s="6"/>
       <c r="N33" s="6"/>
       <c r="O33" s="6"/>
-      <c r="P33" s="4">
-        <v>46053</v>
-      </c>
-      <c r="Q33" s="4">
-        <v>46065</v>
+      <c r="P33" s="10">
+        <v>46066</v>
+      </c>
+      <c r="Q33" s="10">
+        <v>46071</v>
       </c>
       <c r="R33" s="4">
-        <v>46066</v>
+        <v>46077</v>
       </c>
       <c r="S33" s="4">
-        <v>46066</v>
+        <v>46077</v>
       </c>
       <c r="T33" s="4">
-        <v>46066</v>
+        <v>46077</v>
       </c>
       <c r="V33" s="2" t="s">
-        <v>123</v>
+        <v>99</v>
       </c>
       <c r="W33" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X33" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="Y33" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="34" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="34" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>106</v>
+        <v>43</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>105</v>
+        <v>44</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>104</v>
+        <v>45</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>34</v>
@@ -4122,13 +4247,13 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G34" s="7">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>28</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="J34" s="2">
         <v>1</v>
@@ -4136,32 +4261,38 @@
       <c r="K34" s="2">
         <v>1</v>
       </c>
-      <c r="L34" s="4">
-        <v>46052</v>
-      </c>
-      <c r="M34" s="6"/>
-      <c r="N34" s="6"/>
-      <c r="O34" s="6"/>
-      <c r="P34" s="4">
-        <v>46053</v>
+      <c r="L34" s="10">
+        <v>46063</v>
+      </c>
+      <c r="M34" s="10">
+        <v>46063</v>
+      </c>
+      <c r="N34" s="10">
+        <v>46063</v>
+      </c>
+      <c r="O34" s="10">
+        <v>46066</v>
+      </c>
+      <c r="P34" s="10">
+        <v>46074</v>
       </c>
       <c r="Q34" s="4">
-        <v>46065</v>
+        <v>46076</v>
       </c>
       <c r="R34" s="4">
-        <v>46066</v>
+        <v>46078</v>
       </c>
       <c r="S34" s="4">
-        <v>46066</v>
+        <v>46080</v>
       </c>
       <c r="T34" s="4">
-        <v>46066</v>
+        <v>46080</v>
       </c>
       <c r="V34" s="2" t="s">
-        <v>123</v>
+        <v>94</v>
       </c>
       <c r="W34" s="2" t="s">
-        <v>30</v>
+        <v>96</v>
       </c>
       <c r="X34" s="2" t="s">
         <v>53</v>
@@ -4196,7 +4327,7 @@
         <v>28</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="J35" s="2">
         <v>1</v>
@@ -4240,13 +4371,13 @@
     </row>
     <row r="36" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>34</v>
@@ -4258,34 +4389,28 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G36" s="7">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>28</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>136</v>
+        <v>102</v>
       </c>
       <c r="J36" s="2">
         <v>1</v>
       </c>
       <c r="K36" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L36" s="4">
-        <v>45868</v>
-      </c>
-      <c r="M36" s="4">
-        <v>46055</v>
-      </c>
-      <c r="N36" s="4">
-        <v>46056</v>
-      </c>
-      <c r="O36" s="4">
-        <v>46056</v>
-      </c>
+        <v>46052</v>
+      </c>
+      <c r="M36" s="6"/>
+      <c r="N36" s="6"/>
+      <c r="O36" s="6"/>
       <c r="P36" s="4">
-        <v>46058</v>
+        <v>46053</v>
       </c>
       <c r="Q36" s="4">
         <v>46065</v>
@@ -4300,24 +4425,27 @@
         <v>46066</v>
       </c>
       <c r="V36" s="2" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="W36" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="X36" s="2" t="s">
         <v>53</v>
       </c>
+      <c r="Y36" s="2" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="37" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>34</v>
@@ -4329,55 +4457,52 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G37" s="7">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="H37" s="2" t="s">
         <v>28</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>136</v>
+        <v>103</v>
       </c>
       <c r="J37" s="2">
         <v>1</v>
       </c>
       <c r="K37" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L37" s="4">
-        <v>45868</v>
-      </c>
-      <c r="M37" s="4">
-        <v>46093</v>
-      </c>
-      <c r="N37" s="4">
-        <v>46093</v>
-      </c>
-      <c r="O37" s="4">
-        <v>46093</v>
-      </c>
+        <v>46052</v>
+      </c>
+      <c r="M37" s="6"/>
+      <c r="N37" s="6"/>
+      <c r="O37" s="6"/>
       <c r="P37" s="4">
-        <v>46098</v>
+        <v>46053</v>
       </c>
       <c r="Q37" s="4">
-        <v>46100</v>
+        <v>46065</v>
       </c>
       <c r="R37" s="4">
-        <v>46101</v>
+        <v>46066</v>
       </c>
       <c r="S37" s="4">
-        <v>46104</v>
+        <v>46066</v>
       </c>
       <c r="T37" s="4">
-        <v>46104</v>
+        <v>46066</v>
       </c>
       <c r="V37" s="2" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="W37" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="X37" s="2" t="s">
         <v>53</v>
+      </c>
+      <c r="Y37" s="2" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="38" spans="1:25" x14ac:dyDescent="0.3">
@@ -4406,7 +4531,7 @@
         <v>28</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>119</v>
+        <v>136</v>
       </c>
       <c r="J38" s="2">
         <v>1</v>
@@ -4449,6 +4574,9 @@
       </c>
       <c r="X38" s="2" t="s">
         <v>53</v>
+      </c>
+      <c r="Y38" s="2" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="39" spans="1:25" x14ac:dyDescent="0.3">
@@ -4477,49 +4605,52 @@
         <v>28</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>120</v>
+        <v>136</v>
       </c>
       <c r="J39" s="2">
         <v>1</v>
       </c>
       <c r="K39" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L39" s="4">
         <v>45868</v>
       </c>
       <c r="M39" s="4">
-        <v>46055</v>
+        <v>46093</v>
       </c>
       <c r="N39" s="4">
-        <v>46056</v>
+        <v>46093</v>
       </c>
       <c r="O39" s="4">
-        <v>46056</v>
+        <v>46093</v>
       </c>
       <c r="P39" s="4">
-        <v>46057</v>
+        <v>46098</v>
       </c>
       <c r="Q39" s="4">
-        <v>46065</v>
+        <v>46100</v>
       </c>
       <c r="R39" s="4">
-        <v>46066</v>
+        <v>46101</v>
       </c>
       <c r="S39" s="4">
-        <v>46066</v>
+        <v>46104</v>
       </c>
       <c r="T39" s="4">
-        <v>46066</v>
+        <v>46104</v>
       </c>
       <c r="V39" s="2" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="W39" s="2" t="s">
         <v>29</v>
       </c>
       <c r="X39" s="2" t="s">
         <v>53</v>
+      </c>
+      <c r="Y39" s="2" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="40" spans="1:25" x14ac:dyDescent="0.3">
@@ -4548,7 +4679,7 @@
         <v>28</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J40" s="2">
         <v>1</v>
@@ -4584,7 +4715,7 @@
         <v>46066</v>
       </c>
       <c r="V40" s="2" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="W40" s="2" t="s">
         <v>29</v>
@@ -4592,8 +4723,11 @@
       <c r="X40" s="2" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="41" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Y40" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="41" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
         <v>116</v>
       </c>
@@ -4619,7 +4753,7 @@
         <v>28</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J41" s="2">
         <v>1</v>
@@ -4640,7 +4774,7 @@
         <v>46056</v>
       </c>
       <c r="P41" s="4">
-        <v>46058</v>
+        <v>46057</v>
       </c>
       <c r="Q41" s="4">
         <v>46065</v>
@@ -4655,7 +4789,7 @@
         <v>46066</v>
       </c>
       <c r="V41" s="2" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="W41" s="2" t="s">
         <v>29</v>
@@ -4664,54 +4798,54 @@
         <v>53</v>
       </c>
     </row>
-    <row r="42" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F42" s="3">
         <v>0.55000000000000004</v>
       </c>
       <c r="G42" s="7">
-        <v>14.2</v>
+        <v>14.5</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>28</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="J42" s="2">
         <v>1</v>
       </c>
       <c r="K42" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L42" s="4">
-        <v>46062</v>
+        <v>45868</v>
       </c>
       <c r="M42" s="4">
-        <v>46062</v>
+        <v>46055</v>
       </c>
       <c r="N42" s="4">
-        <v>46063</v>
+        <v>46056</v>
       </c>
       <c r="O42" s="4">
-        <v>46063</v>
+        <v>46056</v>
       </c>
       <c r="P42" s="4">
-        <v>46063</v>
+        <v>46058</v>
       </c>
       <c r="Q42" s="4">
         <v>46065</v>
@@ -4720,217 +4854,241 @@
         <v>46066</v>
       </c>
       <c r="S42" s="4">
-        <v>46072</v>
+        <v>46066</v>
       </c>
       <c r="T42" s="4">
-        <v>46072</v>
+        <v>46066</v>
       </c>
       <c r="V42" s="2" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="W42" s="2" t="s">
-        <v>131</v>
+        <v>29</v>
       </c>
       <c r="X42" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="Y42" s="2" t="s">
+    </row>
+    <row r="43" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F43" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G43" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I43" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="J43" s="2">
+        <v>1</v>
+      </c>
+      <c r="K43" s="2">
+        <v>4</v>
+      </c>
+      <c r="L43" s="4">
+        <v>45868</v>
+      </c>
+      <c r="M43" s="4">
+        <v>46055</v>
+      </c>
+      <c r="N43" s="4">
+        <v>46056</v>
+      </c>
+      <c r="O43" s="4">
+        <v>46056</v>
+      </c>
+      <c r="P43" s="4">
+        <v>46058</v>
+      </c>
+      <c r="Q43" s="4">
+        <v>46065</v>
+      </c>
+      <c r="R43" s="4">
+        <v>46066</v>
+      </c>
+      <c r="S43" s="4">
+        <v>46066</v>
+      </c>
+      <c r="T43" s="4">
+        <v>46066</v>
+      </c>
+      <c r="V43" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="W43" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="X43" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="44" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F44" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G44" s="7">
+        <v>14.2</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I44" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="J44" s="2">
+        <v>1</v>
+      </c>
+      <c r="K44" s="2">
+        <v>1</v>
+      </c>
+      <c r="L44" s="4">
+        <v>46062</v>
+      </c>
+      <c r="M44" s="4">
+        <v>46062</v>
+      </c>
+      <c r="N44" s="4">
+        <v>46063</v>
+      </c>
+      <c r="O44" s="4">
+        <v>46063</v>
+      </c>
+      <c r="P44" s="4">
+        <v>46063</v>
+      </c>
+      <c r="Q44" s="4">
+        <v>46065</v>
+      </c>
+      <c r="R44" s="4">
+        <v>46066</v>
+      </c>
+      <c r="S44" s="4">
+        <v>46072</v>
+      </c>
+      <c r="T44" s="4">
+        <v>46072</v>
+      </c>
+      <c r="V44" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="W44" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="X44" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y44" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="43" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A43" s="2" t="s">
+    <row r="45" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B43" s="2" t="s">
+      <c r="B45" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C43" s="2" t="s">
+      <c r="C45" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="D43" s="2" t="s">
+      <c r="D45" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E43" s="2" t="s">
+      <c r="E45" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="F43" s="3">
+      <c r="F45" s="3">
         <v>0.43</v>
       </c>
-      <c r="G43" s="7">
+      <c r="G45" s="7">
         <v>14.2</v>
       </c>
-      <c r="H43" s="2" t="s">
+      <c r="H45" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="I43" s="2" t="s">
+      <c r="I45" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="J43" s="2">
-        <v>1</v>
-      </c>
-      <c r="K43" s="2">
-        <v>1</v>
-      </c>
-      <c r="L43" s="4">
+      <c r="J45" s="2">
+        <v>1</v>
+      </c>
+      <c r="K45" s="2">
+        <v>1</v>
+      </c>
+      <c r="L45" s="4">
         <v>46077</v>
       </c>
-      <c r="M43" s="4">
+      <c r="M45" s="4">
         <v>46077</v>
       </c>
-      <c r="N43" s="4">
+      <c r="N45" s="4">
         <v>46078</v>
       </c>
-      <c r="O43" s="4">
+      <c r="O45" s="4">
         <v>46078</v>
       </c>
-      <c r="P43" s="4">
+      <c r="P45" s="4">
         <v>46084</v>
       </c>
-      <c r="Q43" s="4">
+      <c r="Q45" s="4">
         <v>46089</v>
       </c>
-      <c r="R43" s="4">
+      <c r="R45" s="4">
         <v>46090</v>
       </c>
-      <c r="S43" s="4">
+      <c r="S45" s="4">
         <v>46092</v>
       </c>
-      <c r="T43" s="4">
+      <c r="T45" s="4">
         <v>46092</v>
       </c>
-      <c r="V43" s="2" t="s">
+      <c r="V45" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="W43" s="2" t="s">
+      <c r="W45" s="2" t="s">
         <v>33</v>
-      </c>
-      <c r="X43" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="Y43" s="2" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="44" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A44" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="G44" s="7">
-        <v>14.5</v>
-      </c>
-      <c r="H44" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="I44" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="J44" s="2">
-        <v>1</v>
-      </c>
-      <c r="K44" s="2">
-        <v>1</v>
-      </c>
-      <c r="L44" s="4">
-        <v>46066</v>
-      </c>
-      <c r="M44" s="6"/>
-      <c r="N44" s="6"/>
-      <c r="O44" s="6"/>
-      <c r="P44" s="4">
-        <v>46076</v>
-      </c>
-      <c r="Q44" s="4">
-        <v>46083</v>
-      </c>
-      <c r="V44" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="W44" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="X44" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="Y44" s="2" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="45" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A45" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F45" s="3">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="G45" s="7">
-        <v>14.5</v>
-      </c>
-      <c r="H45" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="I45" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="J45" s="2">
-        <v>1</v>
-      </c>
-      <c r="K45" s="2">
-        <v>1</v>
-      </c>
-      <c r="L45" s="4">
-        <v>46066</v>
-      </c>
-      <c r="M45" s="6"/>
-      <c r="N45" s="6"/>
-      <c r="O45" s="6"/>
-      <c r="P45" s="4">
-        <v>46076</v>
-      </c>
-      <c r="Q45" s="4">
-        <v>46083</v>
-      </c>
-      <c r="V45" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="W45" s="2" t="s">
-        <v>29</v>
       </c>
       <c r="X45" s="2" t="s">
         <v>100</v>
       </c>
       <c r="Y45" s="2" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="46" spans="1:25" x14ac:dyDescent="0.3">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="46" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>62</v>
       </c>
@@ -4956,7 +5114,7 @@
         <v>28</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="J46" s="2">
         <v>1</v>
@@ -4971,16 +5129,13 @@
       <c r="N46" s="6"/>
       <c r="O46" s="6"/>
       <c r="P46" s="4">
-        <v>46079</v>
+        <v>46076</v>
       </c>
       <c r="Q46" s="4">
-        <v>46086</v>
-      </c>
-      <c r="R46" s="4">
-        <v>46087</v>
+        <v>46083</v>
       </c>
       <c r="V46" s="2" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="W46" s="2" t="s">
         <v>29</v>
@@ -4992,15 +5147,15 @@
         <v>142</v>
       </c>
     </row>
-    <row r="47" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
-        <v>144</v>
+        <v>62</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>145</v>
+        <v>63</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>146</v>
+        <v>64</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>34</v>
@@ -5012,48 +5167,37 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G47" s="7">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="H47" s="2" t="s">
         <v>28</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="J47" s="2">
         <v>1</v>
       </c>
       <c r="K47" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L47" s="4">
-        <v>46055</v>
-      </c>
-      <c r="M47" s="4">
-        <v>46085</v>
-      </c>
+        <v>46066</v>
+      </c>
+      <c r="M47" s="6"/>
       <c r="N47" s="6"/>
       <c r="O47" s="6"/>
       <c r="P47" s="4">
-        <v>46085</v>
+        <v>46076</v>
       </c>
       <c r="Q47" s="4">
-        <v>46093</v>
-      </c>
-      <c r="R47" s="4">
-        <v>46094</v>
-      </c>
-      <c r="S47" s="4">
-        <v>46094</v>
-      </c>
-      <c r="T47" s="4">
-        <v>46094</v>
+        <v>46083</v>
       </c>
       <c r="V47" s="2" t="s">
-        <v>148</v>
+        <v>52</v>
       </c>
       <c r="W47" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X47" s="2" t="s">
         <v>100</v>
@@ -5064,13 +5208,13 @@
     </row>
     <row r="48" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
-        <v>144</v>
+        <v>62</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>145</v>
+        <v>63</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>146</v>
+        <v>64</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>34</v>
@@ -5082,48 +5226,40 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G48" s="7">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="H48" s="2" t="s">
         <v>28</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="J48" s="2">
         <v>1</v>
       </c>
       <c r="K48" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L48" s="4">
-        <v>46055</v>
-      </c>
-      <c r="M48" s="4">
-        <v>46085</v>
-      </c>
+        <v>46066</v>
+      </c>
+      <c r="M48" s="6"/>
       <c r="N48" s="6"/>
       <c r="O48" s="6"/>
       <c r="P48" s="4">
-        <v>46085</v>
+        <v>46079</v>
       </c>
       <c r="Q48" s="4">
-        <v>46093</v>
+        <v>46086</v>
       </c>
       <c r="R48" s="4">
-        <v>46094</v>
-      </c>
-      <c r="S48" s="4">
-        <v>46094</v>
-      </c>
-      <c r="T48" s="4">
-        <v>46094</v>
+        <v>46087</v>
       </c>
       <c r="V48" s="2" t="s">
-        <v>148</v>
+        <v>66</v>
       </c>
       <c r="W48" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X48" s="2" t="s">
         <v>100</v>
@@ -5134,125 +5270,145 @@
     </row>
     <row r="49" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>153</v>
+        <v>27</v>
       </c>
       <c r="F49" s="3">
-        <v>0.45</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="G49" s="7">
-        <v>14.2</v>
+        <v>15</v>
       </c>
       <c r="H49" s="2" t="s">
         <v>28</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="J49" s="2">
         <v>1</v>
       </c>
       <c r="K49" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L49" s="4">
-        <v>46090</v>
-      </c>
-      <c r="M49" s="12"/>
-      <c r="N49" s="4">
+        <v>46055</v>
+      </c>
+      <c r="M49" s="4">
         <v>46085</v>
       </c>
-      <c r="O49" s="4">
-        <v>46086</v>
-      </c>
+      <c r="N49" s="6"/>
+      <c r="O49" s="6"/>
       <c r="P49" s="4">
-        <v>46087</v>
+        <v>46085</v>
+      </c>
+      <c r="Q49" s="4">
+        <v>46093</v>
+      </c>
+      <c r="R49" s="4">
+        <v>46094</v>
+      </c>
+      <c r="S49" s="4">
+        <v>46094</v>
       </c>
       <c r="T49" s="4">
-        <v>46100</v>
+        <v>46094</v>
       </c>
       <c r="V49" s="2" t="s">
-        <v>185</v>
+        <v>148</v>
       </c>
       <c r="W49" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="X49" s="2" t="s">
         <v>100</v>
       </c>
+      <c r="Y49" s="2" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="50" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>153</v>
+        <v>27</v>
       </c>
       <c r="F50" s="3">
-        <v>0.45</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="G50" s="7">
-        <v>14.2</v>
+        <v>15</v>
       </c>
       <c r="H50" s="2" t="s">
         <v>28</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="J50" s="2">
         <v>1</v>
       </c>
       <c r="K50" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L50" s="4">
-        <v>46090</v>
-      </c>
-      <c r="M50" s="12"/>
-      <c r="N50" s="4">
+        <v>46055</v>
+      </c>
+      <c r="M50" s="4">
         <v>46085</v>
       </c>
-      <c r="O50" s="4">
-        <v>46086</v>
-      </c>
+      <c r="N50" s="6"/>
+      <c r="O50" s="6"/>
       <c r="P50" s="4">
-        <v>46087</v>
+        <v>46085</v>
+      </c>
+      <c r="Q50" s="4">
+        <v>46093</v>
+      </c>
+      <c r="R50" s="4">
+        <v>46094</v>
+      </c>
+      <c r="S50" s="4">
+        <v>46094</v>
       </c>
       <c r="T50" s="4">
-        <v>46100</v>
+        <v>46094</v>
       </c>
       <c r="V50" s="2" t="s">
-        <v>185</v>
+        <v>148</v>
       </c>
       <c r="W50" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="X50" s="2" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="51" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Y50" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="51" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
         <v>150</v>
       </c>
@@ -5278,7 +5434,7 @@
         <v>28</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="J51" s="2">
         <v>1</v>
@@ -5312,7 +5468,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="52" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
         <v>150</v>
       </c>
@@ -5338,7 +5494,7 @@
         <v>28</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="J52" s="2">
         <v>1</v>
@@ -5359,6 +5515,9 @@
       <c r="P52" s="4">
         <v>46087</v>
       </c>
+      <c r="T52" s="4">
+        <v>46100</v>
+      </c>
       <c r="V52" s="2" t="s">
         <v>185</v>
       </c>
@@ -5366,10 +5525,10 @@
         <v>29</v>
       </c>
       <c r="X52" s="2" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="53" spans="1:25" x14ac:dyDescent="0.3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="53" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
         <v>150</v>
       </c>
@@ -5395,7 +5554,7 @@
         <v>28</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="J53" s="2">
         <v>1</v>
@@ -5416,6 +5575,9 @@
       <c r="P53" s="4">
         <v>46087</v>
       </c>
+      <c r="T53" s="4">
+        <v>46100</v>
+      </c>
       <c r="V53" s="2" t="s">
         <v>185</v>
       </c>
@@ -5423,10 +5585,10 @@
         <v>29</v>
       </c>
       <c r="X53" s="2" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="54" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="54" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
         <v>150</v>
       </c>
@@ -5452,7 +5614,7 @@
         <v>28</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="J54" s="2">
         <v>1</v>
@@ -5483,7 +5645,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="55" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
         <v>150</v>
       </c>
@@ -5509,7 +5671,7 @@
         <v>28</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>186</v>
+        <v>158</v>
       </c>
       <c r="J55" s="2">
         <v>1</v>
@@ -5540,7 +5702,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="56" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:25" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
         <v>150</v>
       </c>
@@ -5565,8 +5727,8 @@
       <c r="H56" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I56" s="11" t="s">
-        <v>160</v>
+      <c r="I56" s="2" t="s">
+        <v>159</v>
       </c>
       <c r="J56" s="2">
         <v>1</v>
@@ -5597,7 +5759,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="57" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:25" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
         <v>150</v>
       </c>
@@ -5622,8 +5784,8 @@
       <c r="H57" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I57" s="11" t="s">
-        <v>161</v>
+      <c r="I57" s="2" t="s">
+        <v>186</v>
       </c>
       <c r="J57" s="2">
         <v>1</v>
@@ -5654,7 +5816,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="58" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
         <v>150</v>
       </c>
@@ -5680,7 +5842,7 @@
         <v>28</v>
       </c>
       <c r="I58" s="11" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="J58" s="2">
         <v>1</v>
@@ -5711,24 +5873,24 @@
         <v>137</v>
       </c>
     </row>
-    <row r="59" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
-        <v>171</v>
+        <v>150</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>172</v>
+        <v>151</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>173</v>
+        <v>152</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>174</v>
+        <v>153</v>
       </c>
       <c r="F59" s="3">
-        <v>0.55000000000000004</v>
+        <v>0.45</v>
       </c>
       <c r="G59" s="7">
         <v>14.2</v>
@@ -5737,7 +5899,7 @@
         <v>28</v>
       </c>
       <c r="I59" s="11" t="s">
-        <v>199</v>
+        <v>161</v>
       </c>
       <c r="J59" s="2">
         <v>1</v>
@@ -5746,51 +5908,46 @@
         <v>1</v>
       </c>
       <c r="L59" s="4">
+        <v>46090</v>
+      </c>
+      <c r="M59" s="12"/>
+      <c r="N59" s="4">
+        <v>46085</v>
+      </c>
+      <c r="O59" s="4">
         <v>46086</v>
       </c>
       <c r="P59" s="4">
-        <v>46094</v>
-      </c>
-      <c r="Q59" s="4">
-        <v>46103</v>
-      </c>
-      <c r="S59" s="4">
-        <v>46112</v>
-      </c>
-      <c r="T59" s="4">
-        <v>46112</v>
+        <v>46087</v>
       </c>
       <c r="V59" s="2" t="s">
-        <v>148</v>
+        <v>185</v>
       </c>
       <c r="W59" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X59" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="Y59" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="60" spans="1:25" x14ac:dyDescent="0.3">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="60" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
-        <v>171</v>
+        <v>150</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>172</v>
+        <v>151</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>173</v>
+        <v>152</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>174</v>
+        <v>153</v>
       </c>
       <c r="F60" s="3">
-        <v>0.55000000000000004</v>
+        <v>0.45</v>
       </c>
       <c r="G60" s="7">
         <v>14.2</v>
@@ -5799,7 +5956,7 @@
         <v>28</v>
       </c>
       <c r="I60" s="11" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="J60" s="2">
         <v>1</v>
@@ -5808,31 +5965,26 @@
         <v>1</v>
       </c>
       <c r="L60" s="4">
+        <v>46090</v>
+      </c>
+      <c r="M60" s="12"/>
+      <c r="N60" s="4">
+        <v>46085</v>
+      </c>
+      <c r="O60" s="4">
         <v>46086</v>
       </c>
       <c r="P60" s="4">
-        <v>46094</v>
-      </c>
-      <c r="Q60" s="4">
-        <v>46103</v>
-      </c>
-      <c r="S60" s="4">
-        <v>46112</v>
-      </c>
-      <c r="T60" s="4">
-        <v>46112</v>
+        <v>46087</v>
       </c>
       <c r="V60" s="2" t="s">
-        <v>148</v>
+        <v>185</v>
       </c>
       <c r="W60" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X60" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="Y60" s="2" t="s">
-        <v>58</v>
+        <v>137</v>
       </c>
     </row>
     <row r="61" spans="1:25" x14ac:dyDescent="0.3">
@@ -5849,7 +6001,7 @@
         <v>26</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>27</v>
+        <v>174</v>
       </c>
       <c r="F61" s="3">
         <v>0.55000000000000004</v>
@@ -5861,7 +6013,7 @@
         <v>28</v>
       </c>
       <c r="I61" s="11" t="s">
-        <v>164</v>
+        <v>199</v>
       </c>
       <c r="J61" s="2">
         <v>1</v>
@@ -5877,6 +6029,9 @@
       </c>
       <c r="Q61" s="4">
         <v>46103</v>
+      </c>
+      <c r="R61" s="4">
+        <v>46105</v>
       </c>
       <c r="S61" s="4">
         <v>46112</v>
@@ -5911,7 +6066,7 @@
         <v>26</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>27</v>
+        <v>174</v>
       </c>
       <c r="F62" s="3">
         <v>0.55000000000000004</v>
@@ -5923,7 +6078,7 @@
         <v>28</v>
       </c>
       <c r="I62" s="11" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="J62" s="2">
         <v>1</v>
@@ -5939,6 +6094,9 @@
       </c>
       <c r="Q62" s="4">
         <v>46103</v>
+      </c>
+      <c r="R62" s="4">
+        <v>46105</v>
       </c>
       <c r="S62" s="4">
         <v>46112</v>
@@ -5985,7 +6143,7 @@
         <v>28</v>
       </c>
       <c r="I63" s="11" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="J63" s="2">
         <v>1</v>
@@ -6001,6 +6159,9 @@
       </c>
       <c r="Q63" s="4">
         <v>46103</v>
+      </c>
+      <c r="R63" s="4">
+        <v>46105</v>
       </c>
       <c r="S63" s="4">
         <v>46112</v>
@@ -6047,7 +6208,7 @@
         <v>28</v>
       </c>
       <c r="I64" s="11" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="J64" s="2">
         <v>1</v>
@@ -6063,6 +6224,9 @@
       </c>
       <c r="Q64" s="4">
         <v>46103</v>
+      </c>
+      <c r="R64" s="4">
+        <v>46105</v>
       </c>
       <c r="S64" s="4">
         <v>46112</v>
@@ -6109,7 +6273,7 @@
         <v>28</v>
       </c>
       <c r="I65" s="11" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="J65" s="2">
         <v>1</v>
@@ -6125,6 +6289,9 @@
       </c>
       <c r="Q65" s="4">
         <v>46103</v>
+      </c>
+      <c r="R65" s="4">
+        <v>46105</v>
       </c>
       <c r="S65" s="4">
         <v>46112</v>
@@ -6171,7 +6338,7 @@
         <v>28</v>
       </c>
       <c r="I66" s="11" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="J66" s="2">
         <v>1</v>
@@ -6187,6 +6354,9 @@
       </c>
       <c r="Q66" s="4">
         <v>46103</v>
+      </c>
+      <c r="R66" s="4">
+        <v>46105</v>
       </c>
       <c r="S66" s="4">
         <v>46112</v>
@@ -6233,7 +6403,7 @@
         <v>28</v>
       </c>
       <c r="I67" s="11" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="J67" s="2">
         <v>1</v>
@@ -6249,6 +6419,9 @@
       </c>
       <c r="Q67" s="4">
         <v>46103</v>
+      </c>
+      <c r="R67" s="4">
+        <v>46105</v>
       </c>
       <c r="S67" s="4">
         <v>46112</v>
@@ -6295,7 +6468,7 @@
         <v>28</v>
       </c>
       <c r="I68" s="11" t="s">
-        <v>200</v>
+        <v>169</v>
       </c>
       <c r="J68" s="2">
         <v>1</v>
@@ -6311,6 +6484,9 @@
       </c>
       <c r="Q68" s="4">
         <v>46103</v>
+      </c>
+      <c r="R68" s="4">
+        <v>46105</v>
       </c>
       <c r="S68" s="4">
         <v>46112</v>
@@ -6357,7 +6533,7 @@
         <v>28</v>
       </c>
       <c r="I69" s="11" t="s">
-        <v>201</v>
+        <v>170</v>
       </c>
       <c r="J69" s="2">
         <v>1</v>
@@ -6373,6 +6549,9 @@
       </c>
       <c r="Q69" s="4">
         <v>46103</v>
+      </c>
+      <c r="R69" s="4">
+        <v>46105</v>
       </c>
       <c r="S69" s="4">
         <v>46112</v>
@@ -6419,7 +6598,7 @@
         <v>28</v>
       </c>
       <c r="I70" s="11" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="J70" s="2">
         <v>1</v>
@@ -6435,6 +6614,9 @@
       </c>
       <c r="Q70" s="4">
         <v>46103</v>
+      </c>
+      <c r="R70" s="4">
+        <v>46105</v>
       </c>
       <c r="S70" s="4">
         <v>46112</v>
@@ -6481,7 +6663,7 @@
         <v>28</v>
       </c>
       <c r="I71" s="11" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="J71" s="2">
         <v>1</v>
@@ -6497,6 +6679,9 @@
       </c>
       <c r="Q71" s="4">
         <v>46103</v>
+      </c>
+      <c r="R71" s="4">
+        <v>46105</v>
       </c>
       <c r="S71" s="4">
         <v>46112</v>
@@ -6543,7 +6728,7 @@
         <v>28</v>
       </c>
       <c r="I72" s="11" t="s">
-        <v>204</v>
+        <v>253</v>
       </c>
       <c r="J72" s="2">
         <v>1</v>
@@ -6552,19 +6737,7 @@
         <v>1</v>
       </c>
       <c r="L72" s="4">
-        <v>46086</v>
-      </c>
-      <c r="P72" s="4">
-        <v>46094</v>
-      </c>
-      <c r="Q72" s="4">
-        <v>46103</v>
-      </c>
-      <c r="S72" s="4">
-        <v>46112</v>
-      </c>
-      <c r="T72" s="4">
-        <v>46112</v>
+        <v>46097</v>
       </c>
       <c r="V72" s="2" t="s">
         <v>148</v>
@@ -6573,7 +6746,7 @@
         <v>30</v>
       </c>
       <c r="X72" s="2" t="s">
-        <v>53</v>
+        <v>255</v>
       </c>
       <c r="Y72" s="2" t="s">
         <v>58</v>
@@ -6605,7 +6778,7 @@
         <v>28</v>
       </c>
       <c r="I73" s="11" t="s">
-        <v>205</v>
+        <v>254</v>
       </c>
       <c r="J73" s="2">
         <v>1</v>
@@ -6614,19 +6787,7 @@
         <v>1</v>
       </c>
       <c r="L73" s="4">
-        <v>46086</v>
-      </c>
-      <c r="P73" s="4">
-        <v>46094</v>
-      </c>
-      <c r="Q73" s="4">
-        <v>46103</v>
-      </c>
-      <c r="S73" s="4">
-        <v>46112</v>
-      </c>
-      <c r="T73" s="4">
-        <v>46112</v>
+        <v>46097</v>
       </c>
       <c r="V73" s="2" t="s">
         <v>148</v>
@@ -6635,7 +6796,7 @@
         <v>30</v>
       </c>
       <c r="X73" s="2" t="s">
-        <v>53</v>
+        <v>255</v>
       </c>
       <c r="Y73" s="2" t="s">
         <v>58</v>
@@ -6667,7 +6828,7 @@
         <v>28</v>
       </c>
       <c r="I74" s="11" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="J74" s="2">
         <v>1</v>
@@ -6683,6 +6844,9 @@
       </c>
       <c r="Q74" s="4">
         <v>46103</v>
+      </c>
+      <c r="R74" s="4">
+        <v>46105</v>
       </c>
       <c r="S74" s="4">
         <v>46112</v>
@@ -6729,7 +6893,7 @@
         <v>28</v>
       </c>
       <c r="I75" s="11" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="J75" s="2">
         <v>1</v>
@@ -6745,6 +6909,9 @@
       </c>
       <c r="Q75" s="4">
         <v>46103</v>
+      </c>
+      <c r="R75" s="4">
+        <v>46105</v>
       </c>
       <c r="S75" s="4">
         <v>46112</v>
@@ -6791,7 +6958,7 @@
         <v>28</v>
       </c>
       <c r="I76" s="11" t="s">
-        <v>208</v>
+        <v>256</v>
       </c>
       <c r="J76" s="2">
         <v>1</v>
@@ -6800,19 +6967,7 @@
         <v>1</v>
       </c>
       <c r="L76" s="4">
-        <v>46086</v>
-      </c>
-      <c r="P76" s="4">
-        <v>46094</v>
-      </c>
-      <c r="Q76" s="4">
-        <v>46103</v>
-      </c>
-      <c r="S76" s="4">
-        <v>46112</v>
-      </c>
-      <c r="T76" s="4">
-        <v>46112</v>
+        <v>46097</v>
       </c>
       <c r="V76" s="2" t="s">
         <v>148</v>
@@ -6821,7 +6976,7 @@
         <v>30</v>
       </c>
       <c r="X76" s="2" t="s">
-        <v>53</v>
+        <v>262</v>
       </c>
       <c r="Y76" s="2" t="s">
         <v>58</v>
@@ -6835,7 +6990,7 @@
         <v>172</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>45</v>
+        <v>173</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>26</v>
@@ -6853,7 +7008,7 @@
         <v>28</v>
       </c>
       <c r="I77" s="11" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="J77" s="2">
         <v>1</v>
@@ -6864,11 +7019,20 @@
       <c r="L77" s="4">
         <v>46086</v>
       </c>
+      <c r="P77" s="4">
+        <v>46094</v>
+      </c>
+      <c r="Q77" s="4">
+        <v>46103</v>
+      </c>
+      <c r="R77" s="4">
+        <v>46105</v>
+      </c>
       <c r="S77" s="4">
-        <v>46142</v>
+        <v>46112</v>
       </c>
       <c r="T77" s="4">
-        <v>46142</v>
+        <v>46112</v>
       </c>
       <c r="V77" s="2" t="s">
         <v>148</v>
@@ -6877,7 +7041,7 @@
         <v>30</v>
       </c>
       <c r="X77" s="2" t="s">
-        <v>137</v>
+        <v>53</v>
       </c>
       <c r="Y77" s="2" t="s">
         <v>58</v>
@@ -6891,7 +7055,7 @@
         <v>172</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>45</v>
+        <v>173</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>26</v>
@@ -6909,7 +7073,7 @@
         <v>28</v>
       </c>
       <c r="I78" s="11" t="s">
-        <v>210</v>
+        <v>257</v>
       </c>
       <c r="J78" s="2">
         <v>1</v>
@@ -6918,13 +7082,7 @@
         <v>1</v>
       </c>
       <c r="L78" s="4">
-        <v>46086</v>
-      </c>
-      <c r="S78" s="4">
-        <v>46142</v>
-      </c>
-      <c r="T78" s="4">
-        <v>46142</v>
+        <v>46097</v>
       </c>
       <c r="V78" s="2" t="s">
         <v>148</v>
@@ -6933,7 +7091,7 @@
         <v>30</v>
       </c>
       <c r="X78" s="2" t="s">
-        <v>137</v>
+        <v>255</v>
       </c>
       <c r="Y78" s="2" t="s">
         <v>58</v>
@@ -6947,7 +7105,7 @@
         <v>172</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>45</v>
+        <v>173</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>26</v>
@@ -6965,7 +7123,7 @@
         <v>28</v>
       </c>
       <c r="I79" s="11" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="J79" s="2">
         <v>1</v>
@@ -6976,11 +7134,20 @@
       <c r="L79" s="4">
         <v>46086</v>
       </c>
+      <c r="P79" s="4">
+        <v>46094</v>
+      </c>
+      <c r="Q79" s="4">
+        <v>46103</v>
+      </c>
+      <c r="R79" s="4">
+        <v>46105</v>
+      </c>
       <c r="S79" s="4">
-        <v>46142</v>
+        <v>46112</v>
       </c>
       <c r="T79" s="4">
-        <v>46142</v>
+        <v>46112</v>
       </c>
       <c r="V79" s="2" t="s">
         <v>148</v>
@@ -6989,7 +7156,7 @@
         <v>30</v>
       </c>
       <c r="X79" s="2" t="s">
-        <v>137</v>
+        <v>53</v>
       </c>
       <c r="Y79" s="2" t="s">
         <v>58</v>
@@ -7003,7 +7170,7 @@
         <v>172</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>45</v>
+        <v>173</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>26</v>
@@ -7021,7 +7188,7 @@
         <v>28</v>
       </c>
       <c r="I80" s="11" t="s">
-        <v>212</v>
+        <v>258</v>
       </c>
       <c r="J80" s="2">
         <v>1</v>
@@ -7030,13 +7197,7 @@
         <v>1</v>
       </c>
       <c r="L80" s="4">
-        <v>46086</v>
-      </c>
-      <c r="S80" s="4">
-        <v>46142</v>
-      </c>
-      <c r="T80" s="4">
-        <v>46142</v>
+        <v>46097</v>
       </c>
       <c r="V80" s="2" t="s">
         <v>148</v>
@@ -7045,7 +7206,7 @@
         <v>30</v>
       </c>
       <c r="X80" s="2" t="s">
-        <v>137</v>
+        <v>255</v>
       </c>
       <c r="Y80" s="2" t="s">
         <v>58</v>
@@ -7059,7 +7220,7 @@
         <v>172</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>45</v>
+        <v>173</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>26</v>
@@ -7077,7 +7238,7 @@
         <v>28</v>
       </c>
       <c r="I81" s="11" t="s">
-        <v>213</v>
+        <v>259</v>
       </c>
       <c r="J81" s="2">
         <v>1</v>
@@ -7086,13 +7247,7 @@
         <v>1</v>
       </c>
       <c r="L81" s="4">
-        <v>46086</v>
-      </c>
-      <c r="S81" s="4">
-        <v>46142</v>
-      </c>
-      <c r="T81" s="4">
-        <v>46142</v>
+        <v>46097</v>
       </c>
       <c r="V81" s="2" t="s">
         <v>148</v>
@@ -7101,7 +7256,7 @@
         <v>30</v>
       </c>
       <c r="X81" s="2" t="s">
-        <v>137</v>
+        <v>255</v>
       </c>
       <c r="Y81" s="2" t="s">
         <v>58</v>
@@ -7115,7 +7270,7 @@
         <v>172</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>45</v>
+        <v>173</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>26</v>
@@ -7133,7 +7288,7 @@
         <v>28</v>
       </c>
       <c r="I82" s="11" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="J82" s="2">
         <v>1</v>
@@ -7144,11 +7299,20 @@
       <c r="L82" s="4">
         <v>46086</v>
       </c>
+      <c r="P82" s="4">
+        <v>46094</v>
+      </c>
+      <c r="Q82" s="4">
+        <v>46103</v>
+      </c>
+      <c r="R82" s="4">
+        <v>46105</v>
+      </c>
       <c r="S82" s="4">
-        <v>46142</v>
+        <v>46112</v>
       </c>
       <c r="T82" s="4">
-        <v>46142</v>
+        <v>46112</v>
       </c>
       <c r="V82" s="2" t="s">
         <v>148</v>
@@ -7157,7 +7321,7 @@
         <v>30</v>
       </c>
       <c r="X82" s="2" t="s">
-        <v>137</v>
+        <v>53</v>
       </c>
       <c r="Y82" s="2" t="s">
         <v>58</v>
@@ -7171,7 +7335,7 @@
         <v>172</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>45</v>
+        <v>173</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>26</v>
@@ -7189,7 +7353,7 @@
         <v>28</v>
       </c>
       <c r="I83" s="11" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="J83" s="2">
         <v>1</v>
@@ -7200,11 +7364,20 @@
       <c r="L83" s="4">
         <v>46086</v>
       </c>
+      <c r="P83" s="4">
+        <v>46094</v>
+      </c>
+      <c r="Q83" s="4">
+        <v>46103</v>
+      </c>
+      <c r="R83" s="4">
+        <v>46105</v>
+      </c>
       <c r="S83" s="4">
-        <v>46142</v>
+        <v>46112</v>
       </c>
       <c r="T83" s="4">
-        <v>46142</v>
+        <v>46112</v>
       </c>
       <c r="V83" s="2" t="s">
         <v>148</v>
@@ -7213,7 +7386,7 @@
         <v>30</v>
       </c>
       <c r="X83" s="2" t="s">
-        <v>137</v>
+        <v>53</v>
       </c>
       <c r="Y83" s="2" t="s">
         <v>58</v>
@@ -7227,7 +7400,7 @@
         <v>172</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>45</v>
+        <v>173</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>26</v>
@@ -7245,7 +7418,7 @@
         <v>28</v>
       </c>
       <c r="I84" s="11" t="s">
-        <v>216</v>
+        <v>260</v>
       </c>
       <c r="J84" s="2">
         <v>1</v>
@@ -7254,13 +7427,7 @@
         <v>1</v>
       </c>
       <c r="L84" s="4">
-        <v>46086</v>
-      </c>
-      <c r="S84" s="4">
-        <v>46142</v>
-      </c>
-      <c r="T84" s="4">
-        <v>46142</v>
+        <v>46097</v>
       </c>
       <c r="V84" s="2" t="s">
         <v>148</v>
@@ -7269,7 +7436,7 @@
         <v>30</v>
       </c>
       <c r="X84" s="2" t="s">
-        <v>137</v>
+        <v>255</v>
       </c>
       <c r="Y84" s="2" t="s">
         <v>58</v>
@@ -7283,7 +7450,7 @@
         <v>172</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>45</v>
+        <v>173</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>26</v>
@@ -7301,7 +7468,7 @@
         <v>28</v>
       </c>
       <c r="I85" s="11" t="s">
-        <v>217</v>
+        <v>261</v>
       </c>
       <c r="J85" s="2">
         <v>1</v>
@@ -7310,22 +7477,16 @@
         <v>1</v>
       </c>
       <c r="L85" s="4">
-        <v>46086</v>
-      </c>
-      <c r="S85" s="4">
-        <v>46142</v>
-      </c>
-      <c r="T85" s="4">
-        <v>46142</v>
+        <v>46097</v>
       </c>
       <c r="V85" s="2" t="s">
-        <v>225</v>
+        <v>148</v>
       </c>
       <c r="W85" s="2" t="s">
         <v>30</v>
       </c>
       <c r="X85" s="2" t="s">
-        <v>137</v>
+        <v>255</v>
       </c>
       <c r="Y85" s="2" t="s">
         <v>58</v>
@@ -7357,7 +7518,7 @@
         <v>28</v>
       </c>
       <c r="I86" s="11" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="J86" s="2">
         <v>1</v>
@@ -7368,14 +7529,8 @@
       <c r="L86" s="4">
         <v>46086</v>
       </c>
-      <c r="S86" s="4">
-        <v>46142</v>
-      </c>
-      <c r="T86" s="4">
-        <v>46142</v>
-      </c>
       <c r="V86" s="2" t="s">
-        <v>225</v>
+        <v>148</v>
       </c>
       <c r="W86" s="2" t="s">
         <v>30</v>
@@ -7413,7 +7568,7 @@
         <v>28</v>
       </c>
       <c r="I87" s="11" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="J87" s="2">
         <v>1</v>
@@ -7424,14 +7579,8 @@
       <c r="L87" s="4">
         <v>46086</v>
       </c>
-      <c r="S87" s="4">
-        <v>46142</v>
-      </c>
-      <c r="T87" s="4">
-        <v>46142</v>
-      </c>
       <c r="V87" s="2" t="s">
-        <v>225</v>
+        <v>148</v>
       </c>
       <c r="W87" s="2" t="s">
         <v>30</v>
@@ -7469,7 +7618,7 @@
         <v>28</v>
       </c>
       <c r="I88" s="11" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="J88" s="2">
         <v>1</v>
@@ -7480,14 +7629,8 @@
       <c r="L88" s="4">
         <v>46086</v>
       </c>
-      <c r="S88" s="4">
-        <v>46142</v>
-      </c>
-      <c r="T88" s="4">
-        <v>46142</v>
-      </c>
       <c r="V88" s="2" t="s">
-        <v>225</v>
+        <v>148</v>
       </c>
       <c r="W88" s="2" t="s">
         <v>30</v>
@@ -7525,7 +7668,7 @@
         <v>28</v>
       </c>
       <c r="I89" s="11" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="J89" s="2">
         <v>1</v>
@@ -7536,14 +7679,8 @@
       <c r="L89" s="4">
         <v>46086</v>
       </c>
-      <c r="S89" s="4">
-        <v>46142</v>
-      </c>
-      <c r="T89" s="4">
-        <v>46142</v>
-      </c>
       <c r="V89" s="2" t="s">
-        <v>225</v>
+        <v>148</v>
       </c>
       <c r="W89" s="2" t="s">
         <v>30</v>
@@ -7581,7 +7718,7 @@
         <v>28</v>
       </c>
       <c r="I90" s="11" t="s">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="J90" s="2">
         <v>1</v>
@@ -7592,14 +7729,8 @@
       <c r="L90" s="4">
         <v>46086</v>
       </c>
-      <c r="S90" s="4">
-        <v>46142</v>
-      </c>
-      <c r="T90" s="4">
-        <v>46142</v>
-      </c>
       <c r="V90" s="2" t="s">
-        <v>225</v>
+        <v>148</v>
       </c>
       <c r="W90" s="2" t="s">
         <v>30</v>
@@ -7637,7 +7768,7 @@
         <v>28</v>
       </c>
       <c r="I91" s="11" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="J91" s="2">
         <v>1</v>
@@ -7648,14 +7779,8 @@
       <c r="L91" s="4">
         <v>46086</v>
       </c>
-      <c r="S91" s="4">
-        <v>46142</v>
-      </c>
-      <c r="T91" s="4">
-        <v>46142</v>
-      </c>
       <c r="V91" s="2" t="s">
-        <v>225</v>
+        <v>148</v>
       </c>
       <c r="W91" s="2" t="s">
         <v>30</v>
@@ -7693,7 +7818,7 @@
         <v>28</v>
       </c>
       <c r="I92" s="11" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="J92" s="2">
         <v>1</v>
@@ -7704,14 +7829,8 @@
       <c r="L92" s="4">
         <v>46086</v>
       </c>
-      <c r="S92" s="4">
-        <v>46142</v>
-      </c>
-      <c r="T92" s="4">
-        <v>46142</v>
-      </c>
       <c r="V92" s="2" t="s">
-        <v>225</v>
+        <v>148</v>
       </c>
       <c r="W92" s="2" t="s">
         <v>30</v>
@@ -7749,7 +7868,7 @@
         <v>28</v>
       </c>
       <c r="I93" s="11" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="J93" s="2">
         <v>1</v>
@@ -7760,14 +7879,8 @@
       <c r="L93" s="4">
         <v>46086</v>
       </c>
-      <c r="S93" s="4">
-        <v>46142</v>
-      </c>
-      <c r="T93" s="4">
-        <v>46142</v>
-      </c>
       <c r="V93" s="2" t="s">
-        <v>225</v>
+        <v>148</v>
       </c>
       <c r="W93" s="2" t="s">
         <v>30</v>
@@ -7779,7 +7892,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="94" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
         <v>171</v>
       </c>
@@ -7805,7 +7918,7 @@
         <v>28</v>
       </c>
       <c r="I94" s="11" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="J94" s="2">
         <v>1</v>
@@ -7823,7 +7936,7 @@
         <v>46142</v>
       </c>
       <c r="V94" s="2" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="W94" s="2" t="s">
         <v>30</v>
@@ -7835,18 +7948,18 @@
         <v>58</v>
       </c>
     </row>
-    <row r="95" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
-        <v>150</v>
+        <v>171</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>151</v>
+        <v>172</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>152</v>
+        <v>45</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>27</v>
@@ -7855,13 +7968,13 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G95" s="7">
-        <v>14.5</v>
+        <v>14.2</v>
       </c>
       <c r="H95" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I95" s="2" t="s">
-        <v>182</v>
+      <c r="I95" s="11" t="s">
+        <v>217</v>
       </c>
       <c r="J95" s="2">
         <v>1</v>
@@ -7870,52 +7983,39 @@
         <v>1</v>
       </c>
       <c r="L95" s="4">
-        <v>46092</v>
-      </c>
-      <c r="M95" s="12"/>
-      <c r="N95" s="4">
-        <v>46093</v>
-      </c>
-      <c r="O95" s="4">
-        <v>46094</v>
-      </c>
-      <c r="Q95" s="4">
-        <v>46111</v>
-      </c>
-      <c r="R95" s="4">
-        <v>46112</v>
+        <v>46086</v>
       </c>
       <c r="S95" s="4">
-        <v>46113</v>
+        <v>46142</v>
       </c>
       <c r="T95" s="4">
-        <v>46113</v>
+        <v>46142</v>
       </c>
       <c r="V95" s="2" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="W95" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="X95" s="2" t="s">
-        <v>53</v>
+        <v>137</v>
       </c>
       <c r="Y95" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="96" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
-        <v>150</v>
+        <v>171</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>151</v>
+        <v>172</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>152</v>
+        <v>45</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>27</v>
@@ -7924,13 +8024,13 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G96" s="7">
-        <v>14.5</v>
+        <v>14.2</v>
       </c>
       <c r="H96" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I96" s="2" t="s">
-        <v>175</v>
+      <c r="I96" s="11" t="s">
+        <v>218</v>
       </c>
       <c r="J96" s="2">
         <v>1</v>
@@ -7939,52 +8039,39 @@
         <v>1</v>
       </c>
       <c r="L96" s="4">
-        <v>46092</v>
-      </c>
-      <c r="M96" s="12"/>
-      <c r="N96" s="4">
-        <v>46093</v>
-      </c>
-      <c r="O96" s="4">
-        <v>46094</v>
-      </c>
-      <c r="Q96" s="4">
-        <v>46111</v>
-      </c>
-      <c r="R96" s="4">
-        <v>46112</v>
+        <v>46086</v>
       </c>
       <c r="S96" s="4">
-        <v>46113</v>
+        <v>46142</v>
       </c>
       <c r="T96" s="4">
-        <v>46113</v>
+        <v>46142</v>
       </c>
       <c r="V96" s="2" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="W96" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="X96" s="2" t="s">
-        <v>53</v>
+        <v>137</v>
       </c>
       <c r="Y96" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="97" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
-        <v>150</v>
+        <v>171</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>151</v>
+        <v>172</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>152</v>
+        <v>45</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>27</v>
@@ -7993,13 +8080,13 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G97" s="7">
-        <v>14.5</v>
+        <v>14.2</v>
       </c>
       <c r="H97" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I97" s="2" t="s">
-        <v>176</v>
+      <c r="I97" s="11" t="s">
+        <v>219</v>
       </c>
       <c r="J97" s="2">
         <v>1</v>
@@ -8008,52 +8095,39 @@
         <v>1</v>
       </c>
       <c r="L97" s="4">
-        <v>46092</v>
-      </c>
-      <c r="M97" s="12"/>
-      <c r="N97" s="4">
-        <v>46093</v>
-      </c>
-      <c r="O97" s="4">
-        <v>46094</v>
-      </c>
-      <c r="Q97" s="4">
-        <v>46111</v>
-      </c>
-      <c r="R97" s="4">
-        <v>46112</v>
+        <v>46086</v>
       </c>
       <c r="S97" s="4">
-        <v>46113</v>
+        <v>46142</v>
       </c>
       <c r="T97" s="4">
-        <v>46113</v>
+        <v>46142</v>
       </c>
       <c r="V97" s="2" t="s">
-        <v>184</v>
+        <v>224</v>
       </c>
       <c r="W97" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="X97" s="2" t="s">
-        <v>53</v>
+        <v>137</v>
       </c>
       <c r="Y97" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="98" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
-        <v>150</v>
+        <v>171</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>151</v>
+        <v>172</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>152</v>
+        <v>45</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>27</v>
@@ -8062,13 +8136,13 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G98" s="7">
-        <v>14.5</v>
+        <v>14.2</v>
       </c>
       <c r="H98" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I98" s="2" t="s">
-        <v>177</v>
+      <c r="I98" s="11" t="s">
+        <v>220</v>
       </c>
       <c r="J98" s="2">
         <v>1</v>
@@ -8077,52 +8151,39 @@
         <v>1</v>
       </c>
       <c r="L98" s="4">
-        <v>46092</v>
-      </c>
-      <c r="M98" s="12"/>
-      <c r="N98" s="4">
-        <v>46093</v>
-      </c>
-      <c r="O98" s="4">
-        <v>46094</v>
-      </c>
-      <c r="Q98" s="4">
-        <v>46111</v>
-      </c>
-      <c r="R98" s="4">
-        <v>46112</v>
+        <v>46086</v>
       </c>
       <c r="S98" s="4">
-        <v>46113</v>
+        <v>46142</v>
       </c>
       <c r="T98" s="4">
-        <v>46113</v>
+        <v>46142</v>
       </c>
       <c r="V98" s="2" t="s">
-        <v>184</v>
+        <v>224</v>
       </c>
       <c r="W98" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="X98" s="2" t="s">
-        <v>53</v>
+        <v>137</v>
       </c>
       <c r="Y98" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="99" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="s">
-        <v>187</v>
+        <v>171</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>189</v>
+        <v>45</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>27</v>
@@ -8131,13 +8192,13 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G99" s="7">
-        <v>14.5</v>
+        <v>14.2</v>
       </c>
       <c r="H99" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I99" s="2" t="s">
-        <v>190</v>
+      <c r="I99" s="11" t="s">
+        <v>221</v>
       </c>
       <c r="J99" s="2">
         <v>1</v>
@@ -8146,36 +8207,39 @@
         <v>1</v>
       </c>
       <c r="L99" s="4">
-        <v>46094</v>
+        <v>46086</v>
+      </c>
+      <c r="S99" s="4">
+        <v>46142</v>
       </c>
       <c r="T99" s="4">
-        <v>46117</v>
+        <v>46142</v>
       </c>
       <c r="V99" s="2" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="W99" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="X99" s="2" t="s">
-        <v>100</v>
+        <v>137</v>
       </c>
       <c r="Y99" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="100" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="s">
-        <v>187</v>
+        <v>171</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>189</v>
+        <v>45</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>27</v>
@@ -8184,13 +8248,13 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G100" s="7">
-        <v>14.5</v>
+        <v>14.2</v>
       </c>
       <c r="H100" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I100" s="2" t="s">
-        <v>191</v>
+      <c r="I100" s="11" t="s">
+        <v>222</v>
       </c>
       <c r="J100" s="2">
         <v>1</v>
@@ -8199,36 +8263,39 @@
         <v>1</v>
       </c>
       <c r="L100" s="4">
-        <v>46094</v>
+        <v>46086</v>
+      </c>
+      <c r="S100" s="4">
+        <v>46142</v>
       </c>
       <c r="T100" s="4">
-        <v>46117</v>
+        <v>46142</v>
       </c>
       <c r="V100" s="2" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="W100" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="X100" s="2" t="s">
-        <v>100</v>
+        <v>137</v>
       </c>
       <c r="Y100" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="101" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="s">
-        <v>187</v>
+        <v>171</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>189</v>
+        <v>45</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>27</v>
@@ -8237,13 +8304,13 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G101" s="7">
-        <v>14.5</v>
+        <v>14.2</v>
       </c>
       <c r="H101" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I101" s="2" t="s">
-        <v>192</v>
+      <c r="I101" s="11" t="s">
+        <v>223</v>
       </c>
       <c r="J101" s="2">
         <v>1</v>
@@ -8252,36 +8319,39 @@
         <v>1</v>
       </c>
       <c r="L101" s="4">
-        <v>46094</v>
+        <v>46086</v>
+      </c>
+      <c r="S101" s="4">
+        <v>46142</v>
       </c>
       <c r="T101" s="4">
-        <v>46117</v>
+        <v>46142</v>
       </c>
       <c r="V101" s="2" t="s">
-        <v>184</v>
+        <v>224</v>
       </c>
       <c r="W101" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="X101" s="2" t="s">
-        <v>100</v>
+        <v>137</v>
       </c>
       <c r="Y101" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="102" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
-        <v>187</v>
+        <v>171</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>189</v>
+        <v>45</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>27</v>
@@ -8290,13 +8360,13 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G102" s="7">
-        <v>14.5</v>
+        <v>14.2</v>
       </c>
       <c r="H102" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I102" s="2" t="s">
-        <v>194</v>
+      <c r="I102" s="11" t="s">
+        <v>225</v>
       </c>
       <c r="J102" s="2">
         <v>1</v>
@@ -8305,36 +8375,39 @@
         <v>1</v>
       </c>
       <c r="L102" s="4">
-        <v>46094</v>
+        <v>46086</v>
+      </c>
+      <c r="S102" s="4">
+        <v>46142</v>
       </c>
       <c r="T102" s="4">
-        <v>46117</v>
+        <v>46142</v>
       </c>
       <c r="V102" s="2" t="s">
-        <v>184</v>
+        <v>224</v>
       </c>
       <c r="W102" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="X102" s="2" t="s">
-        <v>100</v>
+        <v>137</v>
       </c>
       <c r="Y102" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="103" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" s="2" t="s">
-        <v>187</v>
+        <v>171</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>189</v>
+        <v>45</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>27</v>
@@ -8343,13 +8416,13 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G103" s="7">
-        <v>14.5</v>
+        <v>14.2</v>
       </c>
       <c r="H103" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I103" s="13" t="s">
-        <v>193</v>
+      <c r="I103" s="11" t="s">
+        <v>226</v>
       </c>
       <c r="J103" s="2">
         <v>1</v>
@@ -8358,33 +8431,36 @@
         <v>1</v>
       </c>
       <c r="L103" s="4">
-        <v>46094</v>
+        <v>46086</v>
+      </c>
+      <c r="S103" s="4">
+        <v>46142</v>
       </c>
       <c r="T103" s="4">
-        <v>46117</v>
+        <v>46142</v>
       </c>
       <c r="V103" s="2" t="s">
-        <v>184</v>
+        <v>227</v>
       </c>
       <c r="W103" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="X103" s="2" t="s">
-        <v>100</v>
+        <v>137</v>
       </c>
       <c r="Y103" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="104" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>188</v>
+        <v>151</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>189</v>
+        <v>152</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>34</v>
@@ -8402,7 +8478,7 @@
         <v>28</v>
       </c>
       <c r="I104" s="2" t="s">
-        <v>195</v>
+        <v>182</v>
       </c>
       <c r="J104" s="2">
         <v>1</v>
@@ -8411,40 +8487,49 @@
         <v>1</v>
       </c>
       <c r="L104" s="4">
-        <v>46098</v>
-      </c>
-      <c r="M104" s="6"/>
+        <v>46092</v>
+      </c>
+      <c r="M104" s="12"/>
       <c r="N104" s="4">
+        <v>46093</v>
+      </c>
+      <c r="O104" s="4">
+        <v>46094</v>
+      </c>
+      <c r="Q104" s="4">
         <v>46111</v>
       </c>
-      <c r="O104" s="4">
+      <c r="R104" s="4">
         <v>46112</v>
       </c>
-      <c r="P104" s="4">
-        <v>46111</v>
+      <c r="S104" s="4">
+        <v>46113</v>
+      </c>
+      <c r="T104" s="4">
+        <v>46113</v>
       </c>
       <c r="V104" s="2" t="s">
-        <v>198</v>
+        <v>183</v>
       </c>
       <c r="W104" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X104" s="2" t="s">
-        <v>241</v>
+        <v>53</v>
       </c>
       <c r="Y104" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="105" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" s="2" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>188</v>
+        <v>151</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>189</v>
+        <v>152</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>34</v>
@@ -8462,7 +8547,7 @@
         <v>28</v>
       </c>
       <c r="I105" s="2" t="s">
-        <v>196</v>
+        <v>175</v>
       </c>
       <c r="J105" s="2">
         <v>1</v>
@@ -8471,37 +8556,49 @@
         <v>1</v>
       </c>
       <c r="L105" s="4">
-        <v>46098</v>
-      </c>
-      <c r="M105" s="6"/>
+        <v>46092</v>
+      </c>
+      <c r="M105" s="12"/>
       <c r="N105" s="4">
+        <v>46093</v>
+      </c>
+      <c r="O105" s="4">
+        <v>46094</v>
+      </c>
+      <c r="Q105" s="4">
         <v>46111</v>
       </c>
-      <c r="O105" s="4">
+      <c r="R105" s="4">
         <v>46112</v>
       </c>
+      <c r="S105" s="4">
+        <v>46113</v>
+      </c>
+      <c r="T105" s="4">
+        <v>46113</v>
+      </c>
       <c r="V105" s="2" t="s">
-        <v>198</v>
+        <v>183</v>
       </c>
       <c r="W105" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X105" s="2" t="s">
-        <v>137</v>
+        <v>53</v>
       </c>
       <c r="Y105" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="106" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" s="2" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>188</v>
+        <v>151</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>189</v>
+        <v>152</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>34</v>
@@ -8513,13 +8610,13 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G106" s="7">
-        <v>14.2</v>
+        <v>14.5</v>
       </c>
       <c r="H106" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I106" s="13" t="s">
-        <v>197</v>
+      <c r="I106" s="2" t="s">
+        <v>176</v>
       </c>
       <c r="J106" s="2">
         <v>1</v>
@@ -8528,43 +8625,52 @@
         <v>1</v>
       </c>
       <c r="L106" s="4">
-        <v>46098</v>
-      </c>
-      <c r="M106" s="6"/>
+        <v>46092</v>
+      </c>
+      <c r="M106" s="12"/>
       <c r="N106" s="4">
+        <v>46093</v>
+      </c>
+      <c r="O106" s="4">
+        <v>46094</v>
+      </c>
+      <c r="Q106" s="4">
         <v>46111</v>
       </c>
-      <c r="O106" s="4">
+      <c r="R106" s="4">
         <v>46112</v>
       </c>
-      <c r="P106" s="4">
-        <v>46111</v>
+      <c r="S106" s="4">
+        <v>46113</v>
+      </c>
+      <c r="T106" s="4">
+        <v>46113</v>
       </c>
       <c r="V106" s="2" t="s">
-        <v>198</v>
+        <v>184</v>
       </c>
       <c r="W106" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X106" s="2" t="s">
-        <v>242</v>
+        <v>53</v>
       </c>
       <c r="Y106" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="107" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" s="2" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>188</v>
+        <v>151</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>189</v>
+        <v>152</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>27</v>
@@ -8573,13 +8679,13 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G107" s="7">
-        <v>14.2</v>
+        <v>14.5</v>
       </c>
       <c r="H107" s="2" t="s">
         <v>28</v>
       </c>
       <c r="I107" s="2" t="s">
-        <v>229</v>
+        <v>177</v>
       </c>
       <c r="J107" s="2">
         <v>1</v>
@@ -8588,26 +8694,41 @@
         <v>1</v>
       </c>
       <c r="L107" s="4">
-        <v>46104</v>
-      </c>
-      <c r="M107" s="6"/>
+        <v>46092</v>
+      </c>
+      <c r="M107" s="12"/>
       <c r="N107" s="4">
-        <v>46106</v>
+        <v>46093</v>
+      </c>
+      <c r="O107" s="4">
+        <v>46094</v>
+      </c>
+      <c r="Q107" s="4">
+        <v>46111</v>
+      </c>
+      <c r="R107" s="4">
+        <v>46112</v>
+      </c>
+      <c r="S107" s="4">
+        <v>46113</v>
+      </c>
+      <c r="T107" s="4">
+        <v>46113</v>
       </c>
       <c r="V107" s="2" t="s">
-        <v>148</v>
+        <v>184</v>
       </c>
       <c r="W107" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X107" s="2" t="s">
-        <v>137</v>
+        <v>53</v>
       </c>
       <c r="Y107" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="108" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" s="2" t="s">
         <v>187</v>
       </c>
@@ -8618,7 +8739,7 @@
         <v>189</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E108" s="2" t="s">
         <v>27</v>
@@ -8627,13 +8748,13 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G108" s="7">
-        <v>14.2</v>
+        <v>14.5</v>
       </c>
       <c r="H108" s="2" t="s">
         <v>28</v>
       </c>
       <c r="I108" s="2" t="s">
-        <v>230</v>
+        <v>190</v>
       </c>
       <c r="J108" s="2">
         <v>1</v>
@@ -8642,26 +8763,25 @@
         <v>1</v>
       </c>
       <c r="L108" s="4">
-        <v>46104</v>
-      </c>
-      <c r="M108" s="6"/>
-      <c r="N108" s="4">
-        <v>46106</v>
+        <v>46094</v>
+      </c>
+      <c r="T108" s="4">
+        <v>46117</v>
       </c>
       <c r="V108" s="2" t="s">
-        <v>148</v>
+        <v>183</v>
       </c>
       <c r="W108" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X108" s="2" t="s">
-        <v>137</v>
+        <v>100</v>
       </c>
       <c r="Y108" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="109" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" s="2" t="s">
         <v>187</v>
       </c>
@@ -8672,7 +8792,7 @@
         <v>189</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>27</v>
@@ -8681,13 +8801,13 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G109" s="7">
-        <v>14.2</v>
+        <v>14.5</v>
       </c>
       <c r="H109" s="2" t="s">
         <v>28</v>
       </c>
       <c r="I109" s="2" t="s">
-        <v>231</v>
+        <v>191</v>
       </c>
       <c r="J109" s="2">
         <v>1</v>
@@ -8696,26 +8816,25 @@
         <v>1</v>
       </c>
       <c r="L109" s="4">
-        <v>46104</v>
-      </c>
-      <c r="M109" s="6"/>
-      <c r="N109" s="4">
-        <v>46106</v>
+        <v>46094</v>
+      </c>
+      <c r="T109" s="4">
+        <v>46117</v>
       </c>
       <c r="V109" s="2" t="s">
-        <v>235</v>
+        <v>183</v>
       </c>
       <c r="W109" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X109" s="2" t="s">
-        <v>137</v>
+        <v>100</v>
       </c>
       <c r="Y109" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="110" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="s">
         <v>187</v>
       </c>
@@ -8726,7 +8845,7 @@
         <v>189</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>27</v>
@@ -8735,13 +8854,13 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G110" s="7">
-        <v>14.2</v>
+        <v>14.5</v>
       </c>
       <c r="H110" s="2" t="s">
         <v>28</v>
       </c>
       <c r="I110" s="2" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="J110" s="2">
         <v>1</v>
@@ -8750,26 +8869,25 @@
         <v>1</v>
       </c>
       <c r="L110" s="4">
-        <v>46104</v>
-      </c>
-      <c r="M110" s="6"/>
-      <c r="N110" s="4">
-        <v>46106</v>
+        <v>46094</v>
+      </c>
+      <c r="T110" s="4">
+        <v>46117</v>
       </c>
       <c r="V110" s="2" t="s">
-        <v>148</v>
+        <v>184</v>
       </c>
       <c r="W110" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X110" s="2" t="s">
-        <v>137</v>
+        <v>100</v>
       </c>
       <c r="Y110" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="111" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" s="2" t="s">
         <v>187</v>
       </c>
@@ -8780,7 +8898,7 @@
         <v>189</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E111" s="2" t="s">
         <v>27</v>
@@ -8789,13 +8907,13 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G111" s="7">
-        <v>14.2</v>
+        <v>14.5</v>
       </c>
       <c r="H111" s="2" t="s">
         <v>28</v>
       </c>
       <c r="I111" s="2" t="s">
-        <v>233</v>
+        <v>194</v>
       </c>
       <c r="J111" s="2">
         <v>1</v>
@@ -8804,26 +8922,25 @@
         <v>1</v>
       </c>
       <c r="L111" s="4">
-        <v>46104</v>
-      </c>
-      <c r="M111" s="6"/>
-      <c r="N111" s="4">
-        <v>46106</v>
+        <v>46094</v>
+      </c>
+      <c r="T111" s="4">
+        <v>46117</v>
       </c>
       <c r="V111" s="2" t="s">
-        <v>148</v>
+        <v>184</v>
       </c>
       <c r="W111" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X111" s="2" t="s">
-        <v>137</v>
+        <v>100</v>
       </c>
       <c r="Y111" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="112" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
         <v>187</v>
       </c>
@@ -8834,7 +8951,7 @@
         <v>189</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>27</v>
@@ -8843,13 +8960,13 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G112" s="7">
-        <v>14.2</v>
+        <v>14.5</v>
       </c>
       <c r="H112" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I112" s="2" t="s">
-        <v>234</v>
+      <c r="I112" s="13" t="s">
+        <v>193</v>
       </c>
       <c r="J112" s="2">
         <v>1</v>
@@ -8858,37 +8975,36 @@
         <v>1</v>
       </c>
       <c r="L112" s="4">
-        <v>46104</v>
-      </c>
-      <c r="M112" s="6"/>
-      <c r="N112" s="4">
-        <v>46106</v>
+        <v>46094</v>
+      </c>
+      <c r="T112" s="4">
+        <v>46117</v>
       </c>
       <c r="V112" s="2" t="s">
-        <v>148</v>
+        <v>184</v>
       </c>
       <c r="W112" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X112" s="2" t="s">
-        <v>137</v>
+        <v>100</v>
       </c>
       <c r="Y112" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="113" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" s="2" t="s">
-        <v>62</v>
+        <v>187</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>63</v>
+        <v>188</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>64</v>
+        <v>189</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>27</v>
@@ -8897,13 +9013,13 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G113" s="7">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="H113" s="2" t="s">
         <v>28</v>
       </c>
       <c r="I113" s="2" t="s">
-        <v>236</v>
+        <v>195</v>
       </c>
       <c r="J113" s="2">
         <v>1</v>
@@ -8912,36 +9028,43 @@
         <v>1</v>
       </c>
       <c r="L113" s="4">
-        <v>46107</v>
-      </c>
+        <v>46098</v>
+      </c>
+      <c r="M113" s="6"/>
       <c r="N113" s="4">
-        <v>46108</v>
+        <v>46111</v>
+      </c>
+      <c r="O113" s="4">
+        <v>46112</v>
+      </c>
+      <c r="P113" s="4">
+        <v>46111</v>
       </c>
       <c r="V113" s="2" t="s">
-        <v>148</v>
+        <v>198</v>
       </c>
       <c r="W113" s="2" t="s">
         <v>30</v>
       </c>
       <c r="X113" s="2" t="s">
-        <v>137</v>
+        <v>240</v>
       </c>
       <c r="Y113" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="114" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
-        <v>62</v>
+        <v>187</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>63</v>
+        <v>188</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>64</v>
+        <v>189</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>27</v>
@@ -8950,13 +9073,13 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G114" s="7">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="H114" s="2" t="s">
         <v>28</v>
       </c>
       <c r="I114" s="2" t="s">
-        <v>237</v>
+        <v>196</v>
       </c>
       <c r="J114" s="2">
         <v>1</v>
@@ -8965,13 +9088,17 @@
         <v>1</v>
       </c>
       <c r="L114" s="4">
-        <v>46107</v>
-      </c>
+        <v>46098</v>
+      </c>
+      <c r="M114" s="6"/>
       <c r="N114" s="4">
-        <v>46108</v>
+        <v>46111</v>
+      </c>
+      <c r="O114" s="4">
+        <v>46112</v>
       </c>
       <c r="V114" s="2" t="s">
-        <v>148</v>
+        <v>198</v>
       </c>
       <c r="W114" s="2" t="s">
         <v>30</v>
@@ -8983,18 +9110,18 @@
         <v>58</v>
       </c>
     </row>
-    <row r="115" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" s="2" t="s">
-        <v>62</v>
+        <v>187</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>63</v>
+        <v>188</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>64</v>
+        <v>189</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E115" s="2" t="s">
         <v>27</v>
@@ -9003,13 +9130,13 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G115" s="7">
-        <v>15</v>
+        <v>14.2</v>
       </c>
       <c r="H115" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I115" s="2" t="s">
-        <v>238</v>
+      <c r="I115" s="13" t="s">
+        <v>197</v>
       </c>
       <c r="J115" s="2">
         <v>1</v>
@@ -9018,19 +9145,26 @@
         <v>1</v>
       </c>
       <c r="L115" s="4">
-        <v>46107</v>
-      </c>
+        <v>46098</v>
+      </c>
+      <c r="M115" s="6"/>
       <c r="N115" s="4">
-        <v>46108</v>
+        <v>46111</v>
+      </c>
+      <c r="O115" s="4">
+        <v>46112</v>
+      </c>
+      <c r="P115" s="4">
+        <v>46111</v>
       </c>
       <c r="V115" s="2" t="s">
-        <v>148</v>
+        <v>198</v>
       </c>
       <c r="W115" s="2" t="s">
         <v>30</v>
       </c>
       <c r="X115" s="2" t="s">
-        <v>137</v>
+        <v>241</v>
       </c>
       <c r="Y115" s="2" t="s">
         <v>58</v>
@@ -9038,13 +9172,13 @@
     </row>
     <row r="116" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A116" s="2" t="s">
-        <v>62</v>
+        <v>187</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>63</v>
+        <v>188</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>64</v>
+        <v>189</v>
       </c>
       <c r="D116" s="2" t="s">
         <v>26</v>
@@ -9056,13 +9190,13 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G116" s="7">
-        <v>15</v>
+        <v>14.2</v>
       </c>
       <c r="H116" s="2" t="s">
         <v>28</v>
       </c>
       <c r="I116" s="2" t="s">
-        <v>239</v>
+        <v>228</v>
       </c>
       <c r="J116" s="2">
         <v>1</v>
@@ -9071,10 +9205,11 @@
         <v>1</v>
       </c>
       <c r="L116" s="4">
-        <v>46107</v>
-      </c>
+        <v>46104</v>
+      </c>
+      <c r="M116" s="6"/>
       <c r="N116" s="4">
-        <v>46108</v>
+        <v>46106</v>
       </c>
       <c r="V116" s="2" t="s">
         <v>148</v>
@@ -9091,13 +9226,13 @@
     </row>
     <row r="117" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A117" s="2" t="s">
-        <v>62</v>
+        <v>187</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>63</v>
+        <v>188</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>64</v>
+        <v>189</v>
       </c>
       <c r="D117" s="2" t="s">
         <v>26</v>
@@ -9109,13 +9244,13 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G117" s="7">
-        <v>15</v>
+        <v>14.2</v>
       </c>
       <c r="H117" s="2" t="s">
         <v>28</v>
       </c>
       <c r="I117" s="2" t="s">
-        <v>240</v>
+        <v>229</v>
       </c>
       <c r="J117" s="2">
         <v>1</v>
@@ -9124,10 +9259,11 @@
         <v>1</v>
       </c>
       <c r="L117" s="4">
-        <v>46107</v>
-      </c>
+        <v>46104</v>
+      </c>
+      <c r="M117" s="6"/>
       <c r="N117" s="4">
-        <v>46108</v>
+        <v>46106</v>
       </c>
       <c r="V117" s="2" t="s">
         <v>148</v>
@@ -9142,18 +9278,18 @@
         <v>58</v>
       </c>
     </row>
-    <row r="118" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" s="2" t="s">
-        <v>62</v>
+        <v>187</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>83</v>
+        <v>188</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>84</v>
+        <v>189</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="E118" s="2" t="s">
         <v>27</v>
@@ -9162,32 +9298,32 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G118" s="7">
-        <v>14.5</v>
+        <v>14.2</v>
       </c>
       <c r="H118" s="2" t="s">
         <v>28</v>
       </c>
       <c r="I118" s="2" t="s">
-        <v>86</v>
+        <v>230</v>
       </c>
       <c r="J118" s="2">
         <v>1</v>
       </c>
       <c r="K118" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L118" s="4">
-        <v>45995</v>
-      </c>
-      <c r="M118" s="4">
-        <v>46107</v>
-      </c>
-      <c r="P118" s="10"/>
+        <v>46104</v>
+      </c>
+      <c r="M118" s="6"/>
+      <c r="N118" s="4">
+        <v>46106</v>
+      </c>
       <c r="V118" s="2" t="s">
-        <v>66</v>
+        <v>234</v>
       </c>
       <c r="W118" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="X118" s="2" t="s">
         <v>137</v>
@@ -9195,35 +9331,34 @@
       <c r="Y118" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="AB118" s="9"/>
     </row>
     <row r="119" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A119" s="2" t="s">
-        <v>243</v>
+        <v>187</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>244</v>
+        <v>188</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>245</v>
+        <v>189</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F119" s="3">
-        <v>0.43</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="G119" s="7">
-        <v>14.5</v>
+        <v>14.2</v>
       </c>
       <c r="H119" s="2" t="s">
-        <v>246</v>
+        <v>28</v>
       </c>
       <c r="I119" s="2" t="s">
-        <v>247</v>
+        <v>231</v>
       </c>
       <c r="J119" s="2">
         <v>1</v>
@@ -9232,72 +9367,52 @@
         <v>1</v>
       </c>
       <c r="L119" s="4">
-        <v>45896</v>
-      </c>
+        <v>46104</v>
+      </c>
+      <c r="M119" s="6"/>
       <c r="N119" s="4">
-        <v>45897</v>
-      </c>
-      <c r="O119" s="4">
-        <v>45897</v>
-      </c>
-      <c r="P119" s="4">
-        <v>45897</v>
-      </c>
-      <c r="Q119" s="4">
-        <v>45903</v>
-      </c>
-      <c r="R119" s="4">
-        <v>45905</v>
-      </c>
-      <c r="S119" s="4">
-        <v>45908</v>
-      </c>
-      <c r="T119" s="4">
-        <v>45908</v>
+        <v>46106</v>
       </c>
       <c r="V119" s="2" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="W119" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="X119" s="2" t="s">
-        <v>53</v>
+        <v>137</v>
       </c>
       <c r="Y119" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="Z119" s="4">
-        <v>46112</v>
+        <v>58</v>
       </c>
     </row>
     <row r="120" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A120" s="2" t="s">
-        <v>243</v>
+        <v>187</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>244</v>
+        <v>188</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>245</v>
+        <v>189</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F120" s="3">
-        <v>0.43</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="G120" s="7">
-        <v>14.5</v>
+        <v>14.2</v>
       </c>
       <c r="H120" s="2" t="s">
-        <v>246</v>
+        <v>28</v>
       </c>
       <c r="I120" s="2" t="s">
-        <v>248</v>
+        <v>232</v>
       </c>
       <c r="J120" s="2">
         <v>1</v>
@@ -9306,72 +9421,52 @@
         <v>1</v>
       </c>
       <c r="L120" s="4">
-        <v>45896</v>
-      </c>
+        <v>46104</v>
+      </c>
+      <c r="M120" s="6"/>
       <c r="N120" s="4">
-        <v>45897</v>
-      </c>
-      <c r="O120" s="4">
-        <v>45897</v>
-      </c>
-      <c r="P120" s="4">
-        <v>45897</v>
-      </c>
-      <c r="Q120" s="4">
-        <v>45903</v>
-      </c>
-      <c r="R120" s="4">
-        <v>45905</v>
-      </c>
-      <c r="S120" s="4">
-        <v>45908</v>
-      </c>
-      <c r="T120" s="4">
-        <v>45908</v>
+        <v>46106</v>
       </c>
       <c r="V120" s="2" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="W120" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="X120" s="2" t="s">
-        <v>53</v>
+        <v>137</v>
       </c>
       <c r="Y120" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="Z120" s="4">
-        <v>46112</v>
+        <v>58</v>
       </c>
     </row>
     <row r="121" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A121" s="2" t="s">
-        <v>243</v>
+        <v>187</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>244</v>
+        <v>188</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>245</v>
+        <v>189</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F121" s="3">
-        <v>0.43</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="G121" s="7">
-        <v>14.5</v>
+        <v>14.2</v>
       </c>
       <c r="H121" s="2" t="s">
-        <v>246</v>
+        <v>28</v>
       </c>
       <c r="I121" s="2" t="s">
-        <v>249</v>
+        <v>233</v>
       </c>
       <c r="J121" s="2">
         <v>1</v>
@@ -9380,72 +9475,52 @@
         <v>1</v>
       </c>
       <c r="L121" s="4">
-        <v>45944</v>
-      </c>
+        <v>46104</v>
+      </c>
+      <c r="M121" s="6"/>
       <c r="N121" s="4">
-        <v>45945</v>
-      </c>
-      <c r="O121" s="4">
-        <v>45947</v>
-      </c>
-      <c r="P121" s="4">
-        <v>45950</v>
-      </c>
-      <c r="Q121" s="4">
-        <v>45954</v>
-      </c>
-      <c r="R121" s="4">
-        <v>45957</v>
-      </c>
-      <c r="S121" s="4">
-        <v>45958</v>
-      </c>
-      <c r="T121" s="4">
-        <v>45958</v>
+        <v>46106</v>
       </c>
       <c r="V121" s="2" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="W121" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="X121" s="2" t="s">
-        <v>53</v>
+        <v>137</v>
       </c>
       <c r="Y121" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="Z121" s="4">
-        <v>46112</v>
+        <v>58</v>
       </c>
     </row>
     <row r="122" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
-        <v>243</v>
+        <v>62</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>244</v>
+        <v>63</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>245</v>
+        <v>64</v>
       </c>
       <c r="D122" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F122" s="3">
-        <v>0.43</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="G122" s="7">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="H122" s="2" t="s">
-        <v>246</v>
+        <v>28</v>
       </c>
       <c r="I122" s="2" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="J122" s="2">
         <v>1</v>
@@ -9454,72 +9529,51 @@
         <v>1</v>
       </c>
       <c r="L122" s="4">
-        <v>45944</v>
+        <v>46107</v>
       </c>
       <c r="N122" s="4">
-        <v>45945</v>
-      </c>
-      <c r="O122" s="4">
-        <v>45947</v>
-      </c>
-      <c r="P122" s="4">
-        <v>45950</v>
-      </c>
-      <c r="Q122" s="4">
-        <v>45954</v>
-      </c>
-      <c r="R122" s="4">
-        <v>45957</v>
-      </c>
-      <c r="S122" s="4">
-        <v>45958</v>
-      </c>
-      <c r="T122" s="4">
-        <v>45958</v>
+        <v>46108</v>
       </c>
       <c r="V122" s="2" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="W122" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="X122" s="2" t="s">
-        <v>53</v>
+        <v>137</v>
       </c>
       <c r="Y122" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="Z122" s="4">
-        <v>46112</v>
+        <v>58</v>
       </c>
     </row>
     <row r="123" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A123" s="2" t="s">
-        <v>243</v>
+        <v>62</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>244</v>
+        <v>63</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>245</v>
+        <v>64</v>
       </c>
       <c r="D123" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F123" s="3">
-        <v>0.43</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="G123" s="7">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="H123" s="2" t="s">
-        <v>246</v>
+        <v>28</v>
       </c>
       <c r="I123" s="2" t="s">
-        <v>251</v>
+        <v>236</v>
       </c>
       <c r="J123" s="2">
         <v>1</v>
@@ -9528,230 +9582,1010 @@
         <v>1</v>
       </c>
       <c r="L123" s="4">
-        <v>46024</v>
+        <v>46107</v>
       </c>
       <c r="N123" s="4">
-        <v>46044</v>
-      </c>
-      <c r="O123" s="4">
-        <v>46044</v>
-      </c>
-      <c r="P123" s="4">
-        <v>46045</v>
-      </c>
-      <c r="Q123" s="4">
-        <v>46052</v>
-      </c>
-      <c r="R123" s="4">
-        <v>46055</v>
-      </c>
-      <c r="S123" s="4">
-        <v>46058</v>
-      </c>
-      <c r="T123" s="4">
-        <v>46058</v>
+        <v>46108</v>
       </c>
       <c r="V123" s="2" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="W123" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="X123" s="2" t="s">
-        <v>53</v>
+        <v>137</v>
       </c>
       <c r="Y123" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="Z123" s="4">
-        <v>46112</v>
+        <v>58</v>
       </c>
     </row>
     <row r="124" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A124" s="2" t="s">
-        <v>243</v>
+        <v>62</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>244</v>
+        <v>63</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>245</v>
+        <v>64</v>
       </c>
       <c r="D124" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E124" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F124" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G124" s="7">
+        <v>15</v>
+      </c>
+      <c r="H124" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I124" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="J124" s="2">
+        <v>1</v>
+      </c>
+      <c r="K124" s="2">
+        <v>1</v>
+      </c>
+      <c r="L124" s="4">
+        <v>46107</v>
+      </c>
+      <c r="N124" s="4">
+        <v>46108</v>
+      </c>
+      <c r="V124" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="W124" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X124" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="Y124" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="125" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A125" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C125" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D125" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E125" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F125" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G125" s="7">
+        <v>15</v>
+      </c>
+      <c r="H125" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I125" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="J125" s="2">
+        <v>1</v>
+      </c>
+      <c r="K125" s="2">
+        <v>1</v>
+      </c>
+      <c r="L125" s="4">
+        <v>46107</v>
+      </c>
+      <c r="N125" s="4">
+        <v>46108</v>
+      </c>
+      <c r="V125" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="W125" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X125" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="Y125" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="126" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A126" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E126" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F126" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G126" s="7">
+        <v>15</v>
+      </c>
+      <c r="H126" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I126" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="J126" s="2">
+        <v>1</v>
+      </c>
+      <c r="K126" s="2">
+        <v>1</v>
+      </c>
+      <c r="L126" s="4">
+        <v>46107</v>
+      </c>
+      <c r="N126" s="4">
+        <v>46108</v>
+      </c>
+      <c r="V126" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="W126" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X126" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="Y126" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="127" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A127" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B127" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C127" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E127" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F127" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G127" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="H127" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I127" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="J127" s="2">
+        <v>1</v>
+      </c>
+      <c r="K127" s="2">
+        <v>3</v>
+      </c>
+      <c r="L127" s="4">
+        <v>45995</v>
+      </c>
+      <c r="M127" s="4">
+        <v>46107</v>
+      </c>
+      <c r="N127" s="4">
+        <v>46111</v>
+      </c>
+      <c r="O127" s="4">
+        <v>46112</v>
+      </c>
+      <c r="P127" s="10"/>
+      <c r="V127" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="W127" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="X127" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="Y127" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="AB127" s="9"/>
+    </row>
+    <row r="128" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A128" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="B128" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="C128" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="D128" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E128" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="F124" s="3">
+      <c r="F128" s="3">
         <v>0.43</v>
       </c>
-      <c r="G124" s="7">
+      <c r="G128" s="7">
         <v>14.5</v>
       </c>
-      <c r="H124" s="2" t="s">
+      <c r="H128" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="I128" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="I124" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="J124" s="2">
-        <v>1</v>
-      </c>
-      <c r="K124" s="2">
-        <v>1</v>
-      </c>
-      <c r="L124" s="4">
+      <c r="J128" s="2">
+        <v>1</v>
+      </c>
+      <c r="K128" s="2">
+        <v>1</v>
+      </c>
+      <c r="L128" s="4">
+        <v>45896</v>
+      </c>
+      <c r="N128" s="4">
+        <v>45897</v>
+      </c>
+      <c r="O128" s="4">
+        <v>45897</v>
+      </c>
+      <c r="P128" s="4">
+        <v>45897</v>
+      </c>
+      <c r="Q128" s="4">
+        <v>45903</v>
+      </c>
+      <c r="R128" s="4">
+        <v>45905</v>
+      </c>
+      <c r="S128" s="4">
+        <v>45908</v>
+      </c>
+      <c r="T128" s="4">
+        <v>45908</v>
+      </c>
+      <c r="V128" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="W128" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="X128" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y128" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z128" s="4">
+        <v>46112</v>
+      </c>
+    </row>
+    <row r="129" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A129" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="B129" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="C129" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="D129" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E129" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F129" s="3">
+        <v>0.43</v>
+      </c>
+      <c r="G129" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="H129" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="I129" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="J129" s="2">
+        <v>1</v>
+      </c>
+      <c r="K129" s="2">
+        <v>1</v>
+      </c>
+      <c r="L129" s="4">
+        <v>45896</v>
+      </c>
+      <c r="N129" s="4">
+        <v>45897</v>
+      </c>
+      <c r="O129" s="4">
+        <v>45897</v>
+      </c>
+      <c r="P129" s="4">
+        <v>45897</v>
+      </c>
+      <c r="Q129" s="4">
+        <v>45903</v>
+      </c>
+      <c r="R129" s="4">
+        <v>45905</v>
+      </c>
+      <c r="S129" s="4">
+        <v>45908</v>
+      </c>
+      <c r="T129" s="4">
+        <v>45908</v>
+      </c>
+      <c r="V129" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="W129" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="X129" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y129" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z129" s="4">
+        <v>46112</v>
+      </c>
+    </row>
+    <row r="130" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A130" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="B130" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="C130" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="D130" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E130" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F130" s="3">
+        <v>0.43</v>
+      </c>
+      <c r="G130" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="H130" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="I130" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="J130" s="2">
+        <v>1</v>
+      </c>
+      <c r="K130" s="2">
+        <v>1</v>
+      </c>
+      <c r="L130" s="4">
+        <v>45944</v>
+      </c>
+      <c r="N130" s="4">
+        <v>45945</v>
+      </c>
+      <c r="O130" s="4">
+        <v>45947</v>
+      </c>
+      <c r="P130" s="4">
+        <v>45950</v>
+      </c>
+      <c r="Q130" s="4">
+        <v>45954</v>
+      </c>
+      <c r="R130" s="4">
+        <v>45957</v>
+      </c>
+      <c r="S130" s="4">
+        <v>45958</v>
+      </c>
+      <c r="T130" s="4">
+        <v>45958</v>
+      </c>
+      <c r="V130" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="W130" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="X130" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y130" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z130" s="4">
+        <v>46112</v>
+      </c>
+    </row>
+    <row r="131" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A131" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="B131" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="C131" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="D131" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E131" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F131" s="3">
+        <v>0.43</v>
+      </c>
+      <c r="G131" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="H131" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="I131" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="J131" s="2">
+        <v>1</v>
+      </c>
+      <c r="K131" s="2">
+        <v>1</v>
+      </c>
+      <c r="L131" s="4">
+        <v>45944</v>
+      </c>
+      <c r="N131" s="4">
+        <v>45945</v>
+      </c>
+      <c r="O131" s="4">
+        <v>45947</v>
+      </c>
+      <c r="P131" s="4">
+        <v>45950</v>
+      </c>
+      <c r="Q131" s="4">
+        <v>45954</v>
+      </c>
+      <c r="R131" s="4">
+        <v>45957</v>
+      </c>
+      <c r="S131" s="4">
+        <v>45958</v>
+      </c>
+      <c r="T131" s="4">
+        <v>45958</v>
+      </c>
+      <c r="V131" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="W131" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="X131" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y131" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z131" s="4">
+        <v>46112</v>
+      </c>
+    </row>
+    <row r="132" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A132" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="B132" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="C132" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="D132" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E132" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F132" s="3">
+        <v>0.43</v>
+      </c>
+      <c r="G132" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="H132" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="I132" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="J132" s="2">
+        <v>1</v>
+      </c>
+      <c r="K132" s="2">
+        <v>1</v>
+      </c>
+      <c r="L132" s="4">
         <v>46024</v>
       </c>
-      <c r="N124" s="4">
+      <c r="N132" s="4">
         <v>46044</v>
       </c>
-      <c r="O124" s="4">
+      <c r="O132" s="4">
         <v>46044</v>
       </c>
-      <c r="P124" s="4">
+      <c r="P132" s="4">
         <v>46045</v>
       </c>
-      <c r="Q124" s="4">
+      <c r="Q132" s="4">
         <v>46052</v>
       </c>
-      <c r="R124" s="4">
+      <c r="R132" s="4">
         <v>46055</v>
       </c>
-      <c r="S124" s="4">
+      <c r="S132" s="4">
         <v>46058</v>
       </c>
-      <c r="T124" s="4">
+      <c r="T132" s="4">
         <v>46058</v>
       </c>
-      <c r="V124" s="2" t="s">
+      <c r="V132" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="W124" s="2" t="s">
+      <c r="W132" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="X124" s="2" t="s">
+      <c r="X132" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="Y124" s="2" t="s">
+      <c r="Y132" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="Z124" s="4">
+      <c r="Z132" s="4">
         <v>46112</v>
       </c>
     </row>
+    <row r="133" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A133" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="B133" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="C133" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="D133" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E133" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F133" s="3">
+        <v>0.43</v>
+      </c>
+      <c r="G133" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="H133" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="I133" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="J133" s="2">
+        <v>1</v>
+      </c>
+      <c r="K133" s="2">
+        <v>1</v>
+      </c>
+      <c r="L133" s="4">
+        <v>46024</v>
+      </c>
+      <c r="N133" s="4">
+        <v>46044</v>
+      </c>
+      <c r="O133" s="4">
+        <v>46044</v>
+      </c>
+      <c r="P133" s="4">
+        <v>46045</v>
+      </c>
+      <c r="Q133" s="4">
+        <v>46052</v>
+      </c>
+      <c r="R133" s="4">
+        <v>46055</v>
+      </c>
+      <c r="S133" s="4">
+        <v>46058</v>
+      </c>
+      <c r="T133" s="4">
+        <v>46058</v>
+      </c>
+      <c r="V133" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="W133" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="X133" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y133" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z133" s="4">
+        <v>46112</v>
+      </c>
+    </row>
+    <row r="134" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A134" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="C134" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="D134" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E134" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="F134" s="3">
+        <v>0.45</v>
+      </c>
+      <c r="G134" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="H134" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="I134" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="J134" s="2">
+        <v>1</v>
+      </c>
+      <c r="K134" s="2">
+        <v>1</v>
+      </c>
+      <c r="L134" s="4">
+        <v>46104</v>
+      </c>
+      <c r="N134" s="4">
+        <v>46105</v>
+      </c>
+      <c r="O134" s="4">
+        <v>46110</v>
+      </c>
+      <c r="P134" s="4">
+        <v>46111</v>
+      </c>
+      <c r="Q134" s="4">
+        <v>46112</v>
+      </c>
+      <c r="T134" s="4">
+        <v>46115</v>
+      </c>
+      <c r="V134" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="W134" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="X134" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="Y134" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="135" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A135" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="B135" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="C135" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="D135" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E135" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="F135" s="3">
+        <v>0.45</v>
+      </c>
+      <c r="G135" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="H135" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="I135" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="J135" s="2">
+        <v>1</v>
+      </c>
+      <c r="K135" s="2">
+        <v>1</v>
+      </c>
+      <c r="L135" s="4">
+        <v>46104</v>
+      </c>
+      <c r="N135" s="4">
+        <v>46105</v>
+      </c>
+      <c r="O135" s="4">
+        <v>46110</v>
+      </c>
+      <c r="P135" s="4">
+        <v>46111</v>
+      </c>
+      <c r="Q135" s="4">
+        <v>46112</v>
+      </c>
+      <c r="T135" s="4">
+        <v>46115</v>
+      </c>
+      <c r="V135" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="W135" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="X135" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="Y135" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="136" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A136" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="B136" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="C136" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="D136" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E136" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="F136" s="3">
+        <v>0.45</v>
+      </c>
+      <c r="G136" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="H136" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="I136" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="J136" s="2">
+        <v>1</v>
+      </c>
+      <c r="K136" s="2">
+        <v>1</v>
+      </c>
+      <c r="L136" s="4">
+        <v>46104</v>
+      </c>
+      <c r="N136" s="4">
+        <v>46105</v>
+      </c>
+      <c r="O136" s="4">
+        <v>46110</v>
+      </c>
+      <c r="P136" s="4">
+        <v>46111</v>
+      </c>
+      <c r="Q136" s="4">
+        <v>46112</v>
+      </c>
+      <c r="T136" s="4">
+        <v>46115</v>
+      </c>
+      <c r="V136" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="W136" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="X136" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="Y136" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="V1:V42"/>
+  <autoFilter ref="V1:V136">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="정세희"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="I59:I66">
-    <cfRule type="expression" dxfId="21" priority="5" stopIfTrue="1">
-      <formula>$E3101:$E1048570="sub"</formula>
+  <conditionalFormatting sqref="I61:I68">
+    <cfRule type="expression" dxfId="23" priority="6" stopIfTrue="1">
+      <formula>$E3103:$E1048572="sub"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I56:I58">
-    <cfRule type="expression" dxfId="20" priority="11" stopIfTrue="1">
-      <formula>$E3106:$E1048575="sub"</formula>
+  <conditionalFormatting sqref="I58:I60">
+    <cfRule type="expression" dxfId="22" priority="12" stopIfTrue="1">
+      <formula>$E3108:$E1="sub"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I70">
-    <cfRule type="expression" dxfId="19" priority="72" stopIfTrue="1">
-      <formula>$E6:$E3127="sub"</formula>
+  <conditionalFormatting sqref="I77">
+    <cfRule type="expression" dxfId="21" priority="73" stopIfTrue="1">
+      <formula>$E11:$E3138="sub"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I83">
-    <cfRule type="expression" dxfId="18" priority="95" stopIfTrue="1">
-      <formula>$E12:$E3132="sub"</formula>
+  <conditionalFormatting sqref="I92">
+    <cfRule type="expression" dxfId="20" priority="96" stopIfTrue="1">
+      <formula>$E14:$E3141="sub"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I82">
-    <cfRule type="expression" dxfId="17" priority="101" stopIfTrue="1">
-      <formula>$E12:$E3132="sub"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I81">
-    <cfRule type="expression" dxfId="16" priority="107" stopIfTrue="1">
-      <formula>$E12:$E3132="sub"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I80">
-    <cfRule type="expression" dxfId="15" priority="113" stopIfTrue="1">
-      <formula>$E12:$E3132="sub"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I79">
-    <cfRule type="expression" dxfId="14" priority="119" stopIfTrue="1">
-      <formula>$E12:$E3132="sub"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I78">
-    <cfRule type="expression" dxfId="13" priority="125" stopIfTrue="1">
-      <formula>$E12:$E3132="sub"</formula>
+  <conditionalFormatting sqref="I91">
+    <cfRule type="expression" dxfId="19" priority="102" stopIfTrue="1">
+      <formula>$E14:$E3141="sub"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I90">
-    <cfRule type="expression" dxfId="12" priority="149" stopIfTrue="1">
-      <formula>$E13:$E3133="sub"</formula>
+    <cfRule type="expression" dxfId="18" priority="108" stopIfTrue="1">
+      <formula>$E14:$E3141="sub"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I89">
-    <cfRule type="expression" dxfId="11" priority="156" stopIfTrue="1">
-      <formula>$E13:$E3133="sub"</formula>
+    <cfRule type="expression" dxfId="17" priority="114" stopIfTrue="1">
+      <formula>$E14:$E3141="sub"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I88">
-    <cfRule type="expression" dxfId="10" priority="163" stopIfTrue="1">
-      <formula>$E13:$E3133="sub"</formula>
+    <cfRule type="expression" dxfId="16" priority="120" stopIfTrue="1">
+      <formula>$E14:$E3141="sub"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I87">
-    <cfRule type="expression" dxfId="9" priority="170" stopIfTrue="1">
-      <formula>$E13:$E3133="sub"</formula>
+    <cfRule type="expression" dxfId="15" priority="126" stopIfTrue="1">
+      <formula>$E14:$E3141="sub"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I99">
+    <cfRule type="expression" dxfId="14" priority="150" stopIfTrue="1">
+      <formula>$E15:$E3142="sub"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I98">
+    <cfRule type="expression" dxfId="13" priority="157" stopIfTrue="1">
+      <formula>$E15:$E3142="sub"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I97">
+    <cfRule type="expression" dxfId="12" priority="164" stopIfTrue="1">
+      <formula>$E15:$E3142="sub"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I96">
+    <cfRule type="expression" dxfId="11" priority="171" stopIfTrue="1">
+      <formula>$E15:$E3142="sub"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I95">
+    <cfRule type="expression" dxfId="10" priority="178" stopIfTrue="1">
+      <formula>$E15:$E3142="sub"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I103">
+    <cfRule type="expression" dxfId="9" priority="214" stopIfTrue="1">
+      <formula>$E17:$E3144="sub"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I78 I76">
+    <cfRule type="expression" dxfId="8" priority="1" stopIfTrue="1">
+      <formula>$E11:$E3139="sub"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I86">
-    <cfRule type="expression" dxfId="8" priority="177" stopIfTrue="1">
-      <formula>$E13:$E3133="sub"</formula>
+    <cfRule type="expression" dxfId="7" priority="282" stopIfTrue="1">
+      <formula>$E14:$E3141="sub"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I94">
-    <cfRule type="expression" dxfId="7" priority="213" stopIfTrue="1">
-      <formula>$E15:$E3135="sub"</formula>
+  <conditionalFormatting sqref="I79:I81">
+    <cfRule type="expression" dxfId="6" priority="287" stopIfTrue="1">
+      <formula>$E12:$E3139="sub"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I91:I93">
-    <cfRule type="expression" dxfId="6" priority="234" stopIfTrue="1">
-      <formula>$E13:$E3133="sub"</formula>
+  <conditionalFormatting sqref="I82:I85">
+    <cfRule type="expression" dxfId="5" priority="289" stopIfTrue="1">
+      <formula>$E12:$E3139="sub"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I84:I85">
-    <cfRule type="expression" dxfId="5" priority="235" stopIfTrue="1">
-      <formula>$E12:$E3132="sub"</formula>
+  <conditionalFormatting sqref="I100:I102">
+    <cfRule type="expression" dxfId="4" priority="291" stopIfTrue="1">
+      <formula>$E15:$E3142="sub"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I73:I74">
-    <cfRule type="expression" dxfId="4" priority="236" stopIfTrue="1">
-      <formula>$E9:$E3129="sub"</formula>
+  <conditionalFormatting sqref="I93:I94">
+    <cfRule type="expression" dxfId="3" priority="292" stopIfTrue="1">
+      <formula>$E14:$E3141="sub"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I68:I69">
-    <cfRule type="expression" dxfId="3" priority="237" stopIfTrue="1">
-      <formula>$E2:$E3123="sub"</formula>
+  <conditionalFormatting sqref="I75">
+    <cfRule type="expression" dxfId="2" priority="294" stopIfTrue="1">
+      <formula>$E8:$E3138="sub"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I75:I77">
-    <cfRule type="expression" dxfId="2" priority="238" stopIfTrue="1">
-      <formula>$E10:$E3130="sub"</formula>
+  <conditionalFormatting sqref="I70:I74">
+    <cfRule type="expression" dxfId="1" priority="298" stopIfTrue="1">
+      <formula>$E2:$E3132="sub"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I67">
-    <cfRule type="expression" dxfId="1" priority="239" stopIfTrue="1">
-      <formula>$E3121:$E1048576="sub"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I71:I72">
-    <cfRule type="expression" dxfId="0" priority="240" stopIfTrue="1">
-      <formula>$E8:$E3129="sub"</formula>
+  <conditionalFormatting sqref="I69">
+    <cfRule type="expression" dxfId="0" priority="299" stopIfTrue="1">
+      <formula>$E3130:$E1048576="sub"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9763,55 +10597,55 @@
           <x14:formula1>
             <xm:f>Sheet2!$F$2:$F$4</xm:f>
           </x14:formula1>
-          <xm:sqref>W2:W41 Y43 W43:W1048576</xm:sqref>
+          <xm:sqref>W45:W1048576 Y45 W2:W43</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>Sheet2!$G$2:$G$5</xm:f>
           </x14:formula1>
-          <xm:sqref>X2:X41 X43:X1048576</xm:sqref>
+          <xm:sqref>X45:X1048576 X2:X43</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>Sheet2!$E$2:$E$4</xm:f>
           </x14:formula1>
-          <xm:sqref>H2:H41 H43:H1048576</xm:sqref>
+          <xm:sqref>H45:H1048576 H2:H43</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>Sheet2!$D$2:$D$5</xm:f>
           </x14:formula1>
-          <xm:sqref>G2:G41 G43:G1048576</xm:sqref>
+          <xm:sqref>G45:G1048576 G2:G43</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>Sheet2!$C$2:$C$5</xm:f>
           </x14:formula1>
-          <xm:sqref>F2:F41 F43:F1048576</xm:sqref>
+          <xm:sqref>F45:F1048576 F2:F43</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>Sheet2!$B$2:$B$3</xm:f>
           </x14:formula1>
-          <xm:sqref>E2:E41 E43:E1048576</xm:sqref>
+          <xm:sqref>E45:E1048576 E2:E43</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>Sheet2!$A$2:$A$4</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D41 D43:D1048576</xm:sqref>
+          <xm:sqref>D45:D1048576 D2:D43</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'[복사본 sample-list.xlsx]Sheet2'!#REF!</xm:f>
           </x14:formula1>
-          <xm:sqref>D42:H42 W42:X42</xm:sqref>
+          <xm:sqref>D44:H44 W44:X44</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>Sheet2!$H$2:$H$7</xm:f>
           </x14:formula1>
-          <xm:sqref>Y2:Y42 Y44:Y1048576</xm:sqref>
+          <xm:sqref>Y2:Y44 Y46:Y1048576</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/sample-list.xlsx
+++ b/sample-list.xlsx
@@ -19,14 +19,14 @@
     <externalReference r:id="rId3"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$V$1:$V$136</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$AB$139</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1532" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1565" uniqueCount="274">
   <si>
     <t>국가</t>
   </si>
@@ -375,10 +375,6 @@
   </si>
   <si>
     <t>S관</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>STD 를 6번으로함</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1049,10 +1045,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>대기</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Winsome brown 1M -3.25</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1077,10 +1069,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>대기</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Beige Glow</t>
   </si>
   <si>
@@ -1119,6 +1107,18 @@
   </si>
   <si>
     <t>제안렌즈</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>태국</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>류미리</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>류미리</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1752,8 +1752,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:AB136"/>
+  <dimension ref="A1:AB139"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.25" style="2" customWidth="1"/>
@@ -1861,7 +1860,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>43</v>
       </c>
@@ -1938,7 +1937,7 @@
         <v>46041</v>
       </c>
     </row>
-    <row r="3" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>43</v>
       </c>
@@ -2092,7 +2091,7 @@
         <v>46041</v>
       </c>
     </row>
-    <row r="5" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>43</v>
       </c>
@@ -2169,7 +2168,7 @@
         <v>46041</v>
       </c>
     </row>
-    <row r="6" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>43</v>
       </c>
@@ -2246,7 +2245,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="7" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>43</v>
       </c>
@@ -2320,7 +2319,7 @@
         <v>58</v>
       </c>
       <c r="AB7" s="9" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="8" spans="1:28" x14ac:dyDescent="0.3">
@@ -2383,7 +2382,7 @@
         <v>45975</v>
       </c>
       <c r="V8" s="2" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="W8" s="2" t="s">
         <v>30</v>
@@ -2427,7 +2426,7 @@
         <v>28</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="J9" s="2">
         <v>1</v>
@@ -2507,7 +2506,7 @@
         <v>28</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="J10" s="2">
         <v>1</v>
@@ -2667,7 +2666,7 @@
         <v>28</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="J12" s="2">
         <v>1</v>
@@ -2717,7 +2716,7 @@
         <v>46078</v>
       </c>
     </row>
-    <row r="13" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>69</v>
       </c>
@@ -2791,7 +2790,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="14" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>69</v>
       </c>
@@ -2865,7 +2864,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="15" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>69</v>
       </c>
@@ -3037,7 +3036,7 @@
         <v>28</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J17" s="2">
         <v>1</v>
@@ -3046,29 +3045,25 @@
         <v>1</v>
       </c>
       <c r="L17" s="4">
-        <v>45995</v>
+        <v>46055</v>
       </c>
       <c r="M17" s="5"/>
-      <c r="N17" s="4">
-        <v>46003</v>
-      </c>
-      <c r="O17" s="4">
-        <v>46007</v>
-      </c>
+      <c r="N17" s="5"/>
+      <c r="O17" s="5"/>
       <c r="P17" s="4">
-        <v>46003</v>
+        <v>46038</v>
       </c>
       <c r="Q17" s="4">
-        <v>46014</v>
+        <v>46043</v>
       </c>
       <c r="R17" s="4">
-        <v>46015</v>
+        <v>46045</v>
       </c>
       <c r="S17" s="4">
-        <v>46015</v>
+        <v>46045</v>
       </c>
       <c r="T17" s="4">
-        <v>46015</v>
+        <v>46045</v>
       </c>
       <c r="V17" s="2" t="s">
         <v>81</v>
@@ -3081,6 +3076,9 @@
       </c>
       <c r="Y17" s="2" t="s">
         <v>58</v>
+      </c>
+      <c r="AB17" s="2" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="18" spans="1:28" x14ac:dyDescent="0.3">
@@ -3115,28 +3113,37 @@
         <v>1</v>
       </c>
       <c r="K18" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L18" s="4">
+        <v>45995</v>
+      </c>
+      <c r="M18" s="4">
         <v>46055</v>
       </c>
-      <c r="M18" s="5"/>
-      <c r="N18" s="5"/>
-      <c r="O18" s="5"/>
-      <c r="P18" s="4">
-        <v>46038</v>
+      <c r="N18" s="4">
+        <v>46057</v>
+      </c>
+      <c r="O18" s="4">
+        <v>46064</v>
+      </c>
+      <c r="P18" s="10">
+        <v>46065</v>
       </c>
       <c r="Q18" s="4">
-        <v>46043</v>
+        <v>46075</v>
       </c>
       <c r="R18" s="4">
-        <v>46045</v>
+        <v>46076</v>
       </c>
       <c r="S18" s="4">
-        <v>46045</v>
+        <v>46076</v>
       </c>
       <c r="T18" s="4">
-        <v>46045</v>
+        <v>46076</v>
+      </c>
+      <c r="U18" s="4">
+        <v>46077</v>
       </c>
       <c r="V18" s="2" t="s">
         <v>81</v>
@@ -3150,8 +3157,11 @@
       <c r="Y18" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="AB18" s="2" t="s">
-        <v>88</v>
+      <c r="Z18" s="4">
+        <v>46107</v>
+      </c>
+      <c r="AB18" s="9" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="19" spans="1:28" x14ac:dyDescent="0.3">
@@ -3251,43 +3261,38 @@
         <v>28</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J20" s="2">
         <v>1</v>
       </c>
       <c r="K20" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L20" s="4">
         <v>45995</v>
       </c>
-      <c r="M20" s="4">
-        <v>46055</v>
-      </c>
+      <c r="M20" s="5"/>
       <c r="N20" s="4">
-        <v>46057</v>
+        <v>46003</v>
       </c>
       <c r="O20" s="4">
-        <v>46064</v>
-      </c>
-      <c r="P20" s="10">
-        <v>46065</v>
+        <v>46007</v>
+      </c>
+      <c r="P20" s="4">
+        <v>46003</v>
       </c>
       <c r="Q20" s="4">
-        <v>46075</v>
+        <v>46014</v>
       </c>
       <c r="R20" s="4">
-        <v>46076</v>
+        <v>46015</v>
       </c>
       <c r="S20" s="4">
-        <v>46076</v>
+        <v>46015</v>
       </c>
       <c r="T20" s="4">
-        <v>46076</v>
-      </c>
-      <c r="U20" s="4">
-        <v>46077</v>
+        <v>46015</v>
       </c>
       <c r="V20" s="2" t="s">
         <v>81</v>
@@ -3300,12 +3305,6 @@
       </c>
       <c r="Y20" s="2" t="s">
         <v>58</v>
-      </c>
-      <c r="Z20" s="4">
-        <v>46107</v>
-      </c>
-      <c r="AB20" s="9" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="21" spans="1:28" x14ac:dyDescent="0.3">
@@ -3388,7 +3387,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="22" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>62</v>
       </c>
@@ -3461,11 +3460,8 @@
       <c r="Y22" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="AB22" s="2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="23" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="23" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>62</v>
       </c>
@@ -3541,11 +3537,8 @@
       <c r="Z23" s="4">
         <v>46092</v>
       </c>
-      <c r="AB23" s="2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="24" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="24" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>62</v>
       </c>
@@ -3571,7 +3564,7 @@
         <v>28</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J24" s="2">
         <v>1</v>
@@ -3622,7 +3615,7 @@
         <v>46065</v>
       </c>
     </row>
-    <row r="25" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>62</v>
       </c>
@@ -3648,7 +3641,7 @@
         <v>28</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="J25" s="2">
         <v>1</v>
@@ -3703,7 +3696,7 @@
       </c>
       <c r="AB25" s="4"/>
     </row>
-    <row r="26" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>62</v>
       </c>
@@ -3726,10 +3719,10 @@
         <v>14.5</v>
       </c>
       <c r="H26" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="I26" s="2" t="s">
         <v>180</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>181</v>
       </c>
       <c r="J26" s="2">
         <v>1</v>
@@ -3780,7 +3773,7 @@
         <v>46092</v>
       </c>
     </row>
-    <row r="27" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>62</v>
       </c>
@@ -3806,7 +3799,7 @@
         <v>28</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="J27" s="2">
         <v>1</v>
@@ -3843,7 +3836,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="28" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>62</v>
       </c>
@@ -3869,7 +3862,7 @@
         <v>28</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J28" s="2">
         <v>1</v>
@@ -3911,10 +3904,10 @@
         <v>62</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>34</v>
@@ -3932,47 +3925,44 @@
         <v>28</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>109</v>
+        <v>86</v>
       </c>
       <c r="J29" s="2">
         <v>1</v>
       </c>
       <c r="K29" s="2">
-        <v>1</v>
-      </c>
-      <c r="L29" s="6"/>
-      <c r="M29" s="6"/>
-      <c r="N29" s="6"/>
-      <c r="O29" s="6"/>
+        <v>3</v>
+      </c>
+      <c r="L29" s="4">
+        <v>45995</v>
+      </c>
+      <c r="M29" s="4">
+        <v>46107</v>
+      </c>
+      <c r="N29" s="4">
+        <v>46111</v>
+      </c>
+      <c r="O29" s="4">
+        <v>46112</v>
+      </c>
       <c r="P29" s="10">
-        <v>46065</v>
-      </c>
-      <c r="Q29" s="10">
-        <v>46075</v>
-      </c>
-      <c r="R29" s="4">
-        <v>46076</v>
-      </c>
-      <c r="S29" s="4">
-        <v>46077</v>
-      </c>
-      <c r="T29" s="4">
-        <v>46077</v>
+        <v>46117</v>
       </c>
       <c r="V29" s="2" t="s">
-        <v>98</v>
+        <v>66</v>
       </c>
       <c r="W29" s="2" t="s">
         <v>29</v>
       </c>
       <c r="X29" s="2" t="s">
-        <v>53</v>
+        <v>99</v>
       </c>
       <c r="Y29" s="2" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="30" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+        <v>58</v>
+      </c>
+      <c r="AB29" s="9"/>
+    </row>
+    <row r="30" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>62</v>
       </c>
@@ -3998,7 +3988,7 @@
         <v>28</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="J30" s="2">
         <v>1</v>
@@ -4026,7 +4016,7 @@
         <v>46077</v>
       </c>
       <c r="V30" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="W30" s="2" t="s">
         <v>29</v>
@@ -4034,8 +4024,11 @@
       <c r="X30" s="2" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="31" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Y30" s="2" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="31" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>62</v>
       </c>
@@ -4055,13 +4048,13 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G31" s="7">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>28</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="J31" s="2">
         <v>1</v>
@@ -4089,7 +4082,7 @@
         <v>46077</v>
       </c>
       <c r="V31" s="2" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="W31" s="2" t="s">
         <v>29</v>
@@ -4124,7 +4117,7 @@
         <v>28</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="J32" s="2">
         <v>1</v>
@@ -4152,7 +4145,7 @@
         <v>46077</v>
       </c>
       <c r="V32" s="2" t="s">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="W32" s="2" t="s">
         <v>29</v>
@@ -4160,11 +4153,8 @@
       <c r="X32" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="Y32" s="2" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="33" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="33" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>62</v>
       </c>
@@ -4190,7 +4180,7 @@
         <v>28</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="J33" s="2">
         <v>1</v>
@@ -4203,13 +4193,13 @@
       <c r="N33" s="6"/>
       <c r="O33" s="6"/>
       <c r="P33" s="10">
-        <v>46066</v>
+        <v>46065</v>
       </c>
       <c r="Q33" s="10">
-        <v>46071</v>
+        <v>46075</v>
       </c>
       <c r="R33" s="4">
-        <v>46077</v>
+        <v>46076</v>
       </c>
       <c r="S33" s="4">
         <v>46077</v>
@@ -4218,7 +4208,7 @@
         <v>46077</v>
       </c>
       <c r="V33" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="W33" s="2" t="s">
         <v>29</v>
@@ -4226,16 +4216,19 @@
       <c r="X33" s="2" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="34" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Y33" s="2" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="34" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>34</v>
@@ -4247,13 +4240,13 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G34" s="7">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>28</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>95</v>
+        <v>112</v>
       </c>
       <c r="J34" s="2">
         <v>1</v>
@@ -4261,55 +4254,44 @@
       <c r="K34" s="2">
         <v>1</v>
       </c>
-      <c r="L34" s="10">
-        <v>46063</v>
-      </c>
-      <c r="M34" s="10">
-        <v>46063</v>
-      </c>
-      <c r="N34" s="10">
-        <v>46063</v>
-      </c>
-      <c r="O34" s="10">
+      <c r="L34" s="6"/>
+      <c r="M34" s="6"/>
+      <c r="N34" s="6"/>
+      <c r="O34" s="6"/>
+      <c r="P34" s="10">
         <v>46066</v>
       </c>
-      <c r="P34" s="10">
-        <v>46074</v>
-      </c>
-      <c r="Q34" s="4">
-        <v>46076</v>
+      <c r="Q34" s="10">
+        <v>46071</v>
       </c>
       <c r="R34" s="4">
-        <v>46078</v>
+        <v>46077</v>
       </c>
       <c r="S34" s="4">
-        <v>46080</v>
+        <v>46077</v>
       </c>
       <c r="T34" s="4">
-        <v>46080</v>
+        <v>46077</v>
       </c>
       <c r="V34" s="2" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="W34" s="2" t="s">
-        <v>96</v>
+        <v>29</v>
       </c>
       <c r="X34" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="Y34" s="2" t="s">
-        <v>58</v>
-      </c>
     </row>
     <row r="35" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>106</v>
+        <v>43</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>105</v>
+        <v>44</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>104</v>
+        <v>45</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>34</v>
@@ -4321,13 +4303,13 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G35" s="7">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>28</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="J35" s="2">
         <v>1</v>
@@ -4335,32 +4317,38 @@
       <c r="K35" s="2">
         <v>1</v>
       </c>
-      <c r="L35" s="4">
-        <v>46052</v>
-      </c>
-      <c r="M35" s="6"/>
-      <c r="N35" s="6"/>
-      <c r="O35" s="6"/>
-      <c r="P35" s="4">
-        <v>46053</v>
+      <c r="L35" s="10">
+        <v>46063</v>
+      </c>
+      <c r="M35" s="10">
+        <v>46063</v>
+      </c>
+      <c r="N35" s="10">
+        <v>46063</v>
+      </c>
+      <c r="O35" s="10">
+        <v>46066</v>
+      </c>
+      <c r="P35" s="10">
+        <v>46074</v>
       </c>
       <c r="Q35" s="4">
-        <v>46065</v>
+        <v>46076</v>
       </c>
       <c r="R35" s="4">
-        <v>46066</v>
+        <v>46078</v>
       </c>
       <c r="S35" s="4">
-        <v>46066</v>
+        <v>46080</v>
       </c>
       <c r="T35" s="4">
-        <v>46066</v>
+        <v>46080</v>
       </c>
       <c r="V35" s="2" t="s">
-        <v>123</v>
+        <v>94</v>
       </c>
       <c r="W35" s="2" t="s">
-        <v>30</v>
+        <v>96</v>
       </c>
       <c r="X35" s="2" t="s">
         <v>53</v>
@@ -4371,13 +4359,13 @@
     </row>
     <row r="36" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>34</v>
@@ -4395,7 +4383,7 @@
         <v>28</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="J36" s="2">
         <v>1</v>
@@ -4425,7 +4413,7 @@
         <v>46066</v>
       </c>
       <c r="V36" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="W36" s="2" t="s">
         <v>30</v>
@@ -4439,13 +4427,13 @@
     </row>
     <row r="37" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>34</v>
@@ -4463,7 +4451,7 @@
         <v>28</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="J37" s="2">
         <v>1</v>
@@ -4493,7 +4481,7 @@
         <v>46066</v>
       </c>
       <c r="V37" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="W37" s="2" t="s">
         <v>30</v>
@@ -4507,13 +4495,13 @@
     </row>
     <row r="38" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>34</v>
@@ -4525,34 +4513,28 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G38" s="7">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>28</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>136</v>
+        <v>102</v>
       </c>
       <c r="J38" s="2">
         <v>1</v>
       </c>
       <c r="K38" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L38" s="4">
-        <v>45868</v>
-      </c>
-      <c r="M38" s="4">
-        <v>46055</v>
-      </c>
-      <c r="N38" s="4">
-        <v>46056</v>
-      </c>
-      <c r="O38" s="4">
-        <v>46056</v>
-      </c>
+        <v>46052</v>
+      </c>
+      <c r="M38" s="6"/>
+      <c r="N38" s="6"/>
+      <c r="O38" s="6"/>
       <c r="P38" s="4">
-        <v>46058</v>
+        <v>46053</v>
       </c>
       <c r="Q38" s="4">
         <v>46065</v>
@@ -4567,10 +4549,10 @@
         <v>46066</v>
       </c>
       <c r="V38" s="2" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="W38" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="X38" s="2" t="s">
         <v>53</v>
@@ -4581,13 +4563,13 @@
     </row>
     <row r="39" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>34</v>
@@ -4605,43 +4587,43 @@
         <v>28</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="J39" s="2">
         <v>1</v>
       </c>
       <c r="K39" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L39" s="4">
         <v>45868</v>
       </c>
       <c r="M39" s="4">
-        <v>46093</v>
+        <v>46055</v>
       </c>
       <c r="N39" s="4">
-        <v>46093</v>
+        <v>46056</v>
       </c>
       <c r="O39" s="4">
-        <v>46093</v>
+        <v>46056</v>
       </c>
       <c r="P39" s="4">
-        <v>46098</v>
+        <v>46058</v>
       </c>
       <c r="Q39" s="4">
-        <v>46100</v>
+        <v>46065</v>
       </c>
       <c r="R39" s="4">
-        <v>46101</v>
+        <v>46066</v>
       </c>
       <c r="S39" s="4">
-        <v>46104</v>
+        <v>46066</v>
       </c>
       <c r="T39" s="4">
-        <v>46104</v>
+        <v>46066</v>
       </c>
       <c r="V39" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="W39" s="2" t="s">
         <v>29</v>
@@ -4655,13 +4637,13 @@
     </row>
     <row r="40" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>34</v>
@@ -4679,43 +4661,43 @@
         <v>28</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>119</v>
+        <v>135</v>
       </c>
       <c r="J40" s="2">
         <v>1</v>
       </c>
       <c r="K40" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L40" s="4">
         <v>45868</v>
       </c>
       <c r="M40" s="4">
-        <v>46055</v>
+        <v>46093</v>
       </c>
       <c r="N40" s="4">
-        <v>46056</v>
+        <v>46093</v>
       </c>
       <c r="O40" s="4">
-        <v>46056</v>
+        <v>46093</v>
       </c>
       <c r="P40" s="4">
-        <v>46058</v>
+        <v>46098</v>
       </c>
       <c r="Q40" s="4">
-        <v>46065</v>
+        <v>46100</v>
       </c>
       <c r="R40" s="4">
-        <v>46066</v>
+        <v>46101</v>
       </c>
       <c r="S40" s="4">
-        <v>46066</v>
+        <v>46104</v>
       </c>
       <c r="T40" s="4">
-        <v>46066</v>
+        <v>46104</v>
       </c>
       <c r="V40" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="W40" s="2" t="s">
         <v>29</v>
@@ -4727,15 +4709,15 @@
         <v>58</v>
       </c>
     </row>
-    <row r="41" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>34</v>
@@ -4753,7 +4735,7 @@
         <v>28</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J41" s="2">
         <v>1</v>
@@ -4774,7 +4756,7 @@
         <v>46056</v>
       </c>
       <c r="P41" s="4">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="Q41" s="4">
         <v>46065</v>
@@ -4789,7 +4771,7 @@
         <v>46066</v>
       </c>
       <c r="V41" s="2" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="W41" s="2" t="s">
         <v>29</v>
@@ -4797,16 +4779,19 @@
       <c r="X41" s="2" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="42" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Y41" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="42" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>34</v>
@@ -4824,7 +4809,7 @@
         <v>28</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J42" s="2">
         <v>1</v>
@@ -4845,7 +4830,7 @@
         <v>46056</v>
       </c>
       <c r="P42" s="4">
-        <v>46058</v>
+        <v>46057</v>
       </c>
       <c r="Q42" s="4">
         <v>46065</v>
@@ -4869,15 +4854,15 @@
         <v>53</v>
       </c>
     </row>
-    <row r="43" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>34</v>
@@ -4895,7 +4880,7 @@
         <v>28</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J43" s="2">
         <v>1</v>
@@ -4931,7 +4916,7 @@
         <v>46066</v>
       </c>
       <c r="V43" s="2" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="W43" s="2" t="s">
         <v>29</v>
@@ -4940,54 +4925,54 @@
         <v>53</v>
       </c>
     </row>
-    <row r="44" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>128</v>
+        <v>113</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F44" s="3">
         <v>0.55000000000000004</v>
       </c>
       <c r="G44" s="7">
-        <v>14.2</v>
+        <v>14.5</v>
       </c>
       <c r="H44" s="2" t="s">
         <v>28</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="J44" s="2">
         <v>1</v>
       </c>
       <c r="K44" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L44" s="4">
-        <v>46062</v>
+        <v>45868</v>
       </c>
       <c r="M44" s="4">
-        <v>46062</v>
+        <v>46055</v>
       </c>
       <c r="N44" s="4">
-        <v>46063</v>
+        <v>46056</v>
       </c>
       <c r="O44" s="4">
-        <v>46063</v>
+        <v>46056</v>
       </c>
       <c r="P44" s="4">
-        <v>46063</v>
+        <v>46058</v>
       </c>
       <c r="Q44" s="4">
         <v>46065</v>
@@ -4996,33 +4981,30 @@
         <v>46066</v>
       </c>
       <c r="S44" s="4">
-        <v>46072</v>
+        <v>46066</v>
       </c>
       <c r="T44" s="4">
-        <v>46072</v>
+        <v>46066</v>
       </c>
       <c r="V44" s="2" t="s">
-        <v>130</v>
+        <v>117</v>
       </c>
       <c r="W44" s="2" t="s">
-        <v>131</v>
+        <v>29</v>
       </c>
       <c r="X44" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="Y44" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="45" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="45" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>43</v>
+        <v>125</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>44</v>
+        <v>126</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>45</v>
+        <v>127</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>26</v>
@@ -5031,179 +5013,206 @@
         <v>32</v>
       </c>
       <c r="F45" s="3">
-        <v>0.43</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="G45" s="7">
         <v>14.2</v>
       </c>
       <c r="H45" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I45" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="J45" s="2">
+        <v>1</v>
+      </c>
+      <c r="K45" s="2">
+        <v>1</v>
+      </c>
+      <c r="L45" s="4">
+        <v>46062</v>
+      </c>
+      <c r="M45" s="4">
+        <v>46062</v>
+      </c>
+      <c r="N45" s="4">
+        <v>46063</v>
+      </c>
+      <c r="O45" s="4">
+        <v>46063</v>
+      </c>
+      <c r="P45" s="4">
+        <v>46063</v>
+      </c>
+      <c r="Q45" s="4">
+        <v>46065</v>
+      </c>
+      <c r="R45" s="4">
+        <v>46066</v>
+      </c>
+      <c r="S45" s="4">
+        <v>46072</v>
+      </c>
+      <c r="T45" s="4">
+        <v>46072</v>
+      </c>
+      <c r="V45" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="W45" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="X45" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y45" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="46" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A46" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F46" s="3">
+        <v>0.43</v>
+      </c>
+      <c r="G46" s="7">
+        <v>14.2</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="I46" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="I45" s="2" t="s">
+      <c r="J46" s="2">
+        <v>1</v>
+      </c>
+      <c r="K46" s="2">
+        <v>1</v>
+      </c>
+      <c r="L46" s="4">
+        <v>46077</v>
+      </c>
+      <c r="M46" s="4">
+        <v>46077</v>
+      </c>
+      <c r="N46" s="4">
+        <v>46078</v>
+      </c>
+      <c r="O46" s="4">
+        <v>46078</v>
+      </c>
+      <c r="P46" s="4">
+        <v>46084</v>
+      </c>
+      <c r="Q46" s="4">
+        <v>46089</v>
+      </c>
+      <c r="R46" s="4">
+        <v>46090</v>
+      </c>
+      <c r="S46" s="4">
+        <v>46092</v>
+      </c>
+      <c r="T46" s="4">
+        <v>46092</v>
+      </c>
+      <c r="V46" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="J45" s="2">
-        <v>1</v>
-      </c>
-      <c r="K45" s="2">
-        <v>1</v>
-      </c>
-      <c r="L45" s="4">
+      <c r="W46" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="X46" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y46" s="2" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="47" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A47" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F47" s="3">
+        <v>0.43</v>
+      </c>
+      <c r="G47" s="7">
+        <v>14.2</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="I47" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="J47" s="2">
+        <v>1</v>
+      </c>
+      <c r="K47" s="2">
+        <v>2</v>
+      </c>
+      <c r="L47" s="4">
         <v>46077</v>
       </c>
-      <c r="M45" s="4">
-        <v>46077</v>
-      </c>
-      <c r="N45" s="4">
-        <v>46078</v>
-      </c>
-      <c r="O45" s="4">
-        <v>46078</v>
-      </c>
-      <c r="P45" s="4">
+      <c r="M47" s="4">
+        <v>46113</v>
+      </c>
+      <c r="N47" s="4">
+        <v>46113</v>
+      </c>
+      <c r="P47" s="4">
         <v>46084</v>
       </c>
-      <c r="Q45" s="4">
+      <c r="Q47" s="4">
         <v>46089</v>
       </c>
-      <c r="R45" s="4">
+      <c r="R47" s="4">
         <v>46090</v>
       </c>
-      <c r="S45" s="4">
+      <c r="S47" s="4">
         <v>46092</v>
       </c>
-      <c r="T45" s="4">
+      <c r="T47" s="4">
         <v>46092</v>
       </c>
-      <c r="V45" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="W45" s="2" t="s">
+      <c r="V47" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="W47" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="X45" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="Y45" s="2" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="46" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F46" s="3">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="G46" s="7">
-        <v>14.5</v>
-      </c>
-      <c r="H46" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="I46" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="J46" s="2">
-        <v>1</v>
-      </c>
-      <c r="K46" s="2">
-        <v>1</v>
-      </c>
-      <c r="L46" s="4">
-        <v>46066</v>
-      </c>
-      <c r="M46" s="6"/>
-      <c r="N46" s="6"/>
-      <c r="O46" s="6"/>
-      <c r="P46" s="4">
-        <v>46076</v>
-      </c>
-      <c r="Q46" s="4">
-        <v>46083</v>
-      </c>
-      <c r="V46" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="W46" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="X46" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="Y46" s="2" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="47" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="G47" s="7">
-        <v>14.5</v>
-      </c>
-      <c r="H47" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="I47" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="J47" s="2">
-        <v>1</v>
-      </c>
-      <c r="K47" s="2">
-        <v>1</v>
-      </c>
-      <c r="L47" s="4">
-        <v>46066</v>
-      </c>
-      <c r="M47" s="6"/>
-      <c r="N47" s="6"/>
-      <c r="O47" s="6"/>
-      <c r="P47" s="4">
-        <v>46076</v>
-      </c>
-      <c r="Q47" s="4">
-        <v>46083</v>
-      </c>
-      <c r="V47" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="W47" s="2" t="s">
-        <v>29</v>
-      </c>
       <c r="X47" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="Y47" s="2" t="s">
-        <v>142</v>
+        <v>251</v>
       </c>
     </row>
     <row r="48" spans="1:25" x14ac:dyDescent="0.3">
@@ -5232,7 +5241,7 @@
         <v>28</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="J48" s="2">
         <v>1</v>
@@ -5247,36 +5256,33 @@
       <c r="N48" s="6"/>
       <c r="O48" s="6"/>
       <c r="P48" s="4">
-        <v>46079</v>
+        <v>46076</v>
       </c>
       <c r="Q48" s="4">
-        <v>46086</v>
-      </c>
-      <c r="R48" s="4">
-        <v>46087</v>
+        <v>46083</v>
       </c>
       <c r="V48" s="2" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="W48" s="2" t="s">
         <v>29</v>
       </c>
       <c r="X48" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="Y48" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="49" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
-        <v>144</v>
+        <v>62</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>145</v>
+        <v>63</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>146</v>
+        <v>64</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>34</v>
@@ -5288,65 +5294,54 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G49" s="7">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="H49" s="2" t="s">
         <v>28</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="J49" s="2">
         <v>1</v>
       </c>
       <c r="K49" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L49" s="4">
-        <v>46055</v>
-      </c>
-      <c r="M49" s="4">
-        <v>46085</v>
-      </c>
+        <v>46066</v>
+      </c>
+      <c r="M49" s="6"/>
       <c r="N49" s="6"/>
       <c r="O49" s="6"/>
       <c r="P49" s="4">
-        <v>46085</v>
+        <v>46076</v>
       </c>
       <c r="Q49" s="4">
-        <v>46093</v>
-      </c>
-      <c r="R49" s="4">
-        <v>46094</v>
-      </c>
-      <c r="S49" s="4">
-        <v>46094</v>
-      </c>
-      <c r="T49" s="4">
-        <v>46094</v>
+        <v>46083</v>
       </c>
       <c r="V49" s="2" t="s">
-        <v>148</v>
+        <v>52</v>
       </c>
       <c r="W49" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X49" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="Y49" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="50" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
-        <v>144</v>
+        <v>62</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>145</v>
+        <v>63</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>146</v>
+        <v>64</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>34</v>
@@ -5358,308 +5353,337 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G50" s="7">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="H50" s="2" t="s">
         <v>28</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="J50" s="2">
         <v>1</v>
       </c>
       <c r="K50" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L50" s="4">
-        <v>46055</v>
-      </c>
-      <c r="M50" s="4">
-        <v>46085</v>
-      </c>
+        <v>46066</v>
+      </c>
+      <c r="M50" s="6"/>
       <c r="N50" s="6"/>
       <c r="O50" s="6"/>
       <c r="P50" s="4">
+        <v>46079</v>
+      </c>
+      <c r="Q50" s="4">
+        <v>46086</v>
+      </c>
+      <c r="R50" s="4">
+        <v>46087</v>
+      </c>
+      <c r="V50" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="W50" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="X50" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y50" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="51" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A51" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F51" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G51" s="7">
+        <v>15</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I51" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="J51" s="2">
+        <v>1</v>
+      </c>
+      <c r="K51" s="2">
+        <v>1</v>
+      </c>
+      <c r="L51" s="4">
+        <v>46055</v>
+      </c>
+      <c r="N51" s="6"/>
+      <c r="O51" s="6"/>
+      <c r="P51" s="4">
+        <v>46060</v>
+      </c>
+      <c r="Q51" s="4">
+        <v>46063</v>
+      </c>
+      <c r="R51" s="4">
+        <v>46064</v>
+      </c>
+      <c r="S51" s="4">
+        <v>46066</v>
+      </c>
+      <c r="T51" s="4">
+        <v>46066</v>
+      </c>
+      <c r="V51" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="W51" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X51" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y51" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="52" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A52" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F52" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G52" s="7">
+        <v>15</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I52" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="J52" s="2">
+        <v>1</v>
+      </c>
+      <c r="K52" s="2">
+        <v>1</v>
+      </c>
+      <c r="L52" s="4">
+        <v>46055</v>
+      </c>
+      <c r="N52" s="6"/>
+      <c r="O52" s="6"/>
+      <c r="P52" s="4">
+        <v>46060</v>
+      </c>
+      <c r="Q52" s="4">
+        <v>46063</v>
+      </c>
+      <c r="R52" s="4">
+        <v>46064</v>
+      </c>
+      <c r="S52" s="4">
+        <v>46066</v>
+      </c>
+      <c r="T52" s="4">
+        <v>46066</v>
+      </c>
+      <c r="V52" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="W52" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X52" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y52" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="53" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A53" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F53" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G53" s="7">
+        <v>15</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I53" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="J53" s="2">
+        <v>1</v>
+      </c>
+      <c r="K53" s="2">
+        <v>2</v>
+      </c>
+      <c r="L53" s="4">
+        <v>46055</v>
+      </c>
+      <c r="M53" s="4">
         <v>46085</v>
       </c>
-      <c r="Q50" s="4">
+      <c r="N53" s="6"/>
+      <c r="O53" s="6"/>
+      <c r="P53" s="4">
+        <v>46085</v>
+      </c>
+      <c r="Q53" s="4">
         <v>46093</v>
       </c>
-      <c r="R50" s="4">
+      <c r="R53" s="4">
         <v>46094</v>
       </c>
-      <c r="S50" s="4">
+      <c r="S53" s="4">
         <v>46094</v>
       </c>
-      <c r="T50" s="4">
+      <c r="T53" s="4">
         <v>46094</v>
       </c>
-      <c r="V50" s="2" t="s">
+      <c r="V53" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="W53" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X53" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y53" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="54" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A54" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F54" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G54" s="7">
+        <v>15</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I54" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="W50" s="2" t="s">
+      <c r="J54" s="2">
+        <v>1</v>
+      </c>
+      <c r="K54" s="2">
+        <v>2</v>
+      </c>
+      <c r="L54" s="4">
+        <v>46055</v>
+      </c>
+      <c r="M54" s="4">
+        <v>46085</v>
+      </c>
+      <c r="N54" s="6"/>
+      <c r="O54" s="6"/>
+      <c r="P54" s="4">
+        <v>46085</v>
+      </c>
+      <c r="Q54" s="4">
+        <v>46093</v>
+      </c>
+      <c r="R54" s="4">
+        <v>46094</v>
+      </c>
+      <c r="S54" s="4">
+        <v>46094</v>
+      </c>
+      <c r="T54" s="4">
+        <v>46094</v>
+      </c>
+      <c r="V54" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="W54" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="X50" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="Y50" s="2" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="51" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="2" t="s">
+      <c r="X54" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y54" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="55" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A55" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B55" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="B51" s="2" t="s">
+      <c r="C55" s="2" t="s">
         <v>151</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="F51" s="3">
-        <v>0.45</v>
-      </c>
-      <c r="G51" s="7">
-        <v>14.2</v>
-      </c>
-      <c r="H51" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="I51" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="J51" s="2">
-        <v>1</v>
-      </c>
-      <c r="K51" s="2">
-        <v>1</v>
-      </c>
-      <c r="L51" s="4">
-        <v>46090</v>
-      </c>
-      <c r="M51" s="12"/>
-      <c r="N51" s="4">
-        <v>46085</v>
-      </c>
-      <c r="O51" s="4">
-        <v>46086</v>
-      </c>
-      <c r="P51" s="4">
-        <v>46087</v>
-      </c>
-      <c r="T51" s="4">
-        <v>46100</v>
-      </c>
-      <c r="V51" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="W51" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="X51" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="52" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="F52" s="3">
-        <v>0.45</v>
-      </c>
-      <c r="G52" s="7">
-        <v>14.2</v>
-      </c>
-      <c r="H52" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="I52" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="J52" s="2">
-        <v>1</v>
-      </c>
-      <c r="K52" s="2">
-        <v>1</v>
-      </c>
-      <c r="L52" s="4">
-        <v>46090</v>
-      </c>
-      <c r="M52" s="12"/>
-      <c r="N52" s="4">
-        <v>46085</v>
-      </c>
-      <c r="O52" s="4">
-        <v>46086</v>
-      </c>
-      <c r="P52" s="4">
-        <v>46087</v>
-      </c>
-      <c r="T52" s="4">
-        <v>46100</v>
-      </c>
-      <c r="V52" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="W52" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="X52" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="53" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="F53" s="3">
-        <v>0.45</v>
-      </c>
-      <c r="G53" s="7">
-        <v>14.2</v>
-      </c>
-      <c r="H53" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="I53" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="J53" s="2">
-        <v>1</v>
-      </c>
-      <c r="K53" s="2">
-        <v>1</v>
-      </c>
-      <c r="L53" s="4">
-        <v>46090</v>
-      </c>
-      <c r="M53" s="12"/>
-      <c r="N53" s="4">
-        <v>46085</v>
-      </c>
-      <c r="O53" s="4">
-        <v>46086</v>
-      </c>
-      <c r="P53" s="4">
-        <v>46087</v>
-      </c>
-      <c r="T53" s="4">
-        <v>46100</v>
-      </c>
-      <c r="V53" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="W53" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="X53" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="54" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="F54" s="3">
-        <v>0.45</v>
-      </c>
-      <c r="G54" s="7">
-        <v>14.2</v>
-      </c>
-      <c r="H54" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="I54" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="J54" s="2">
-        <v>1</v>
-      </c>
-      <c r="K54" s="2">
-        <v>1</v>
-      </c>
-      <c r="L54" s="4">
-        <v>46090</v>
-      </c>
-      <c r="M54" s="12"/>
-      <c r="N54" s="4">
-        <v>46085</v>
-      </c>
-      <c r="O54" s="4">
-        <v>46086</v>
-      </c>
-      <c r="P54" s="4">
-        <v>46087</v>
-      </c>
-      <c r="V54" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="W54" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="X54" s="2" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="55" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>152</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F55" s="3">
         <v>0.45</v>
@@ -5671,7 +5695,7 @@
         <v>28</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="J55" s="2">
         <v>1</v>
@@ -5692,31 +5716,34 @@
       <c r="P55" s="4">
         <v>46087</v>
       </c>
+      <c r="T55" s="4">
+        <v>46100</v>
+      </c>
       <c r="V55" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="W55" s="2" t="s">
         <v>29</v>
       </c>
       <c r="X55" s="2" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="56" spans="1:25" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="56" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B56" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="B56" s="2" t="s">
+      <c r="C56" s="2" t="s">
         <v>151</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>152</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F56" s="3">
         <v>0.45</v>
@@ -5728,7 +5755,7 @@
         <v>28</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="J56" s="2">
         <v>1</v>
@@ -5749,31 +5776,34 @@
       <c r="P56" s="4">
         <v>46087</v>
       </c>
+      <c r="T56" s="4">
+        <v>46100</v>
+      </c>
       <c r="V56" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="W56" s="2" t="s">
         <v>29</v>
       </c>
       <c r="X56" s="2" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="57" spans="1:25" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="57" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B57" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="B57" s="2" t="s">
+      <c r="C57" s="2" t="s">
         <v>151</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>152</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F57" s="3">
         <v>0.45</v>
@@ -5785,7 +5815,7 @@
         <v>28</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>186</v>
+        <v>155</v>
       </c>
       <c r="J57" s="2">
         <v>1</v>
@@ -5806,31 +5836,34 @@
       <c r="P57" s="4">
         <v>46087</v>
       </c>
+      <c r="T57" s="4">
+        <v>46100</v>
+      </c>
       <c r="V57" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="W57" s="2" t="s">
         <v>29</v>
       </c>
       <c r="X57" s="2" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="58" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="58" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B58" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="B58" s="2" t="s">
+      <c r="C58" s="2" t="s">
         <v>151</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>152</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F58" s="3">
         <v>0.45</v>
@@ -5841,8 +5874,8 @@
       <c r="H58" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I58" s="11" t="s">
-        <v>160</v>
+      <c r="I58" s="2" t="s">
+        <v>156</v>
       </c>
       <c r="J58" s="2">
         <v>1</v>
@@ -5864,30 +5897,30 @@
         <v>46087</v>
       </c>
       <c r="V58" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="W58" s="2" t="s">
         <v>29</v>
       </c>
       <c r="X58" s="2" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="59" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="59" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B59" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="B59" s="2" t="s">
+      <c r="C59" s="2" t="s">
         <v>151</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>152</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F59" s="3">
         <v>0.45</v>
@@ -5898,8 +5931,8 @@
       <c r="H59" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I59" s="11" t="s">
-        <v>161</v>
+      <c r="I59" s="2" t="s">
+        <v>157</v>
       </c>
       <c r="J59" s="2">
         <v>1</v>
@@ -5921,30 +5954,30 @@
         <v>46087</v>
       </c>
       <c r="V59" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="W59" s="2" t="s">
         <v>29</v>
       </c>
       <c r="X59" s="2" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="60" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="60" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B60" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="B60" s="2" t="s">
+      <c r="C60" s="2" t="s">
         <v>151</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>152</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F60" s="3">
         <v>0.45</v>
@@ -5955,8 +5988,8 @@
       <c r="H60" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I60" s="11" t="s">
-        <v>162</v>
+      <c r="I60" s="2" t="s">
+        <v>158</v>
       </c>
       <c r="J60" s="2">
         <v>1</v>
@@ -5978,33 +6011,33 @@
         <v>46087</v>
       </c>
       <c r="V60" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="W60" s="2" t="s">
         <v>29</v>
       </c>
       <c r="X60" s="2" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="61" spans="1:25" x14ac:dyDescent="0.3">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="61" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
-        <v>171</v>
+        <v>149</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>172</v>
+        <v>150</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>173</v>
+        <v>151</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>174</v>
+        <v>152</v>
       </c>
       <c r="F61" s="3">
-        <v>0.55000000000000004</v>
+        <v>0.45</v>
       </c>
       <c r="G61" s="7">
         <v>14.2</v>
@@ -6012,8 +6045,8 @@
       <c r="H61" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I61" s="11" t="s">
-        <v>199</v>
+      <c r="I61" s="2" t="s">
+        <v>185</v>
       </c>
       <c r="J61" s="2">
         <v>1</v>
@@ -6022,54 +6055,46 @@
         <v>1</v>
       </c>
       <c r="L61" s="4">
+        <v>46090</v>
+      </c>
+      <c r="M61" s="12"/>
+      <c r="N61" s="4">
+        <v>46085</v>
+      </c>
+      <c r="O61" s="4">
         <v>46086</v>
       </c>
       <c r="P61" s="4">
-        <v>46094</v>
-      </c>
-      <c r="Q61" s="4">
-        <v>46103</v>
-      </c>
-      <c r="R61" s="4">
-        <v>46105</v>
-      </c>
-      <c r="S61" s="4">
-        <v>46112</v>
-      </c>
-      <c r="T61" s="4">
-        <v>46112</v>
+        <v>46087</v>
       </c>
       <c r="V61" s="2" t="s">
-        <v>148</v>
+        <v>184</v>
       </c>
       <c r="W61" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X61" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="Y61" s="2" t="s">
-        <v>58</v>
+        <v>136</v>
       </c>
     </row>
     <row r="62" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
-        <v>171</v>
+        <v>149</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>172</v>
+        <v>150</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>173</v>
+        <v>151</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>174</v>
+        <v>152</v>
       </c>
       <c r="F62" s="3">
-        <v>0.55000000000000004</v>
+        <v>0.45</v>
       </c>
       <c r="G62" s="7">
         <v>14.2</v>
@@ -6078,7 +6103,7 @@
         <v>28</v>
       </c>
       <c r="I62" s="11" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="J62" s="2">
         <v>1</v>
@@ -6087,54 +6112,46 @@
         <v>1</v>
       </c>
       <c r="L62" s="4">
+        <v>46090</v>
+      </c>
+      <c r="M62" s="12"/>
+      <c r="N62" s="4">
+        <v>46085</v>
+      </c>
+      <c r="O62" s="4">
         <v>46086</v>
       </c>
       <c r="P62" s="4">
-        <v>46094</v>
-      </c>
-      <c r="Q62" s="4">
-        <v>46103</v>
-      </c>
-      <c r="R62" s="4">
-        <v>46105</v>
-      </c>
-      <c r="S62" s="4">
-        <v>46112</v>
-      </c>
-      <c r="T62" s="4">
-        <v>46112</v>
+        <v>46087</v>
       </c>
       <c r="V62" s="2" t="s">
-        <v>148</v>
+        <v>184</v>
       </c>
       <c r="W62" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X62" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="Y62" s="2" t="s">
-        <v>58</v>
+        <v>136</v>
       </c>
     </row>
     <row r="63" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
-        <v>171</v>
+        <v>149</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>172</v>
+        <v>150</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>173</v>
+        <v>151</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>27</v>
+        <v>152</v>
       </c>
       <c r="F63" s="3">
-        <v>0.55000000000000004</v>
+        <v>0.45</v>
       </c>
       <c r="G63" s="7">
         <v>14.2</v>
@@ -6143,7 +6160,7 @@
         <v>28</v>
       </c>
       <c r="I63" s="11" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="J63" s="2">
         <v>1</v>
@@ -6152,54 +6169,46 @@
         <v>1</v>
       </c>
       <c r="L63" s="4">
+        <v>46090</v>
+      </c>
+      <c r="M63" s="12"/>
+      <c r="N63" s="4">
+        <v>46085</v>
+      </c>
+      <c r="O63" s="4">
         <v>46086</v>
       </c>
       <c r="P63" s="4">
-        <v>46094</v>
-      </c>
-      <c r="Q63" s="4">
-        <v>46103</v>
-      </c>
-      <c r="R63" s="4">
-        <v>46105</v>
-      </c>
-      <c r="S63" s="4">
-        <v>46112</v>
-      </c>
-      <c r="T63" s="4">
-        <v>46112</v>
+        <v>46087</v>
       </c>
       <c r="V63" s="2" t="s">
-        <v>148</v>
+        <v>184</v>
       </c>
       <c r="W63" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X63" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="Y63" s="2" t="s">
-        <v>58</v>
+        <v>136</v>
       </c>
     </row>
     <row r="64" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
-        <v>171</v>
+        <v>149</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>172</v>
+        <v>150</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>173</v>
+        <v>151</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>27</v>
+        <v>152</v>
       </c>
       <c r="F64" s="3">
-        <v>0.55000000000000004</v>
+        <v>0.45</v>
       </c>
       <c r="G64" s="7">
         <v>14.2</v>
@@ -6208,7 +6217,7 @@
         <v>28</v>
       </c>
       <c r="I64" s="11" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="J64" s="2">
         <v>1</v>
@@ -6217,51 +6226,43 @@
         <v>1</v>
       </c>
       <c r="L64" s="4">
+        <v>46090</v>
+      </c>
+      <c r="M64" s="12"/>
+      <c r="N64" s="4">
+        <v>46085</v>
+      </c>
+      <c r="O64" s="4">
         <v>46086</v>
       </c>
       <c r="P64" s="4">
-        <v>46094</v>
-      </c>
-      <c r="Q64" s="4">
-        <v>46103</v>
-      </c>
-      <c r="R64" s="4">
-        <v>46105</v>
-      </c>
-      <c r="S64" s="4">
-        <v>46112</v>
-      </c>
-      <c r="T64" s="4">
-        <v>46112</v>
+        <v>46087</v>
       </c>
       <c r="V64" s="2" t="s">
-        <v>148</v>
+        <v>184</v>
       </c>
       <c r="W64" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X64" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="Y64" s="2" t="s">
-        <v>58</v>
+        <v>136</v>
       </c>
     </row>
     <row r="65" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B65" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="B65" s="2" t="s">
+      <c r="C65" s="2" t="s">
         <v>172</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>173</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>27</v>
+        <v>173</v>
       </c>
       <c r="F65" s="3">
         <v>0.55000000000000004</v>
@@ -6273,7 +6274,7 @@
         <v>28</v>
       </c>
       <c r="I65" s="11" t="s">
-        <v>166</v>
+        <v>198</v>
       </c>
       <c r="J65" s="2">
         <v>1</v>
@@ -6300,7 +6301,7 @@
         <v>46112</v>
       </c>
       <c r="V65" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="W65" s="2" t="s">
         <v>30</v>
@@ -6314,19 +6315,19 @@
     </row>
     <row r="66" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B66" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="B66" s="2" t="s">
+      <c r="C66" s="2" t="s">
         <v>172</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>173</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>27</v>
+        <v>173</v>
       </c>
       <c r="F66" s="3">
         <v>0.55000000000000004</v>
@@ -6338,7 +6339,7 @@
         <v>28</v>
       </c>
       <c r="I66" s="11" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="J66" s="2">
         <v>1</v>
@@ -6365,7 +6366,7 @@
         <v>46112</v>
       </c>
       <c r="V66" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="W66" s="2" t="s">
         <v>30</v>
@@ -6379,13 +6380,13 @@
     </row>
     <row r="67" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B67" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="B67" s="2" t="s">
+      <c r="C67" s="2" t="s">
         <v>172</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>173</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>26</v>
@@ -6403,7 +6404,7 @@
         <v>28</v>
       </c>
       <c r="I67" s="11" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="J67" s="2">
         <v>1</v>
@@ -6430,7 +6431,7 @@
         <v>46112</v>
       </c>
       <c r="V67" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="W67" s="2" t="s">
         <v>30</v>
@@ -6444,13 +6445,13 @@
     </row>
     <row r="68" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B68" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="B68" s="2" t="s">
+      <c r="C68" s="2" t="s">
         <v>172</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>173</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>26</v>
@@ -6468,7 +6469,7 @@
         <v>28</v>
       </c>
       <c r="I68" s="11" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="J68" s="2">
         <v>1</v>
@@ -6495,7 +6496,7 @@
         <v>46112</v>
       </c>
       <c r="V68" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="W68" s="2" t="s">
         <v>30</v>
@@ -6509,13 +6510,13 @@
     </row>
     <row r="69" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B69" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="B69" s="2" t="s">
+      <c r="C69" s="2" t="s">
         <v>172</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>173</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>26</v>
@@ -6533,7 +6534,7 @@
         <v>28</v>
       </c>
       <c r="I69" s="11" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="J69" s="2">
         <v>1</v>
@@ -6560,7 +6561,7 @@
         <v>46112</v>
       </c>
       <c r="V69" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="W69" s="2" t="s">
         <v>30</v>
@@ -6574,13 +6575,13 @@
     </row>
     <row r="70" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B70" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="B70" s="2" t="s">
+      <c r="C70" s="2" t="s">
         <v>172</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>173</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>26</v>
@@ -6598,7 +6599,7 @@
         <v>28</v>
       </c>
       <c r="I70" s="11" t="s">
-        <v>200</v>
+        <v>166</v>
       </c>
       <c r="J70" s="2">
         <v>1</v>
@@ -6625,7 +6626,7 @@
         <v>46112</v>
       </c>
       <c r="V70" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="W70" s="2" t="s">
         <v>30</v>
@@ -6639,13 +6640,13 @@
     </row>
     <row r="71" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B71" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="B71" s="2" t="s">
+      <c r="C71" s="2" t="s">
         <v>172</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>173</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>26</v>
@@ -6663,7 +6664,7 @@
         <v>28</v>
       </c>
       <c r="I71" s="11" t="s">
-        <v>201</v>
+        <v>167</v>
       </c>
       <c r="J71" s="2">
         <v>1</v>
@@ -6690,7 +6691,7 @@
         <v>46112</v>
       </c>
       <c r="V71" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="W71" s="2" t="s">
         <v>30</v>
@@ -6704,13 +6705,13 @@
     </row>
     <row r="72" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B72" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="B72" s="2" t="s">
+      <c r="C72" s="2" t="s">
         <v>172</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>173</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>26</v>
@@ -6728,7 +6729,7 @@
         <v>28</v>
       </c>
       <c r="I72" s="11" t="s">
-        <v>253</v>
+        <v>168</v>
       </c>
       <c r="J72" s="2">
         <v>1</v>
@@ -6737,16 +6738,31 @@
         <v>1</v>
       </c>
       <c r="L72" s="4">
-        <v>46097</v>
+        <v>46086</v>
+      </c>
+      <c r="P72" s="4">
+        <v>46094</v>
+      </c>
+      <c r="Q72" s="4">
+        <v>46103</v>
+      </c>
+      <c r="R72" s="4">
+        <v>46105</v>
+      </c>
+      <c r="S72" s="4">
+        <v>46112</v>
+      </c>
+      <c r="T72" s="4">
+        <v>46112</v>
       </c>
       <c r="V72" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="W72" s="2" t="s">
         <v>30</v>
       </c>
       <c r="X72" s="2" t="s">
-        <v>255</v>
+        <v>53</v>
       </c>
       <c r="Y72" s="2" t="s">
         <v>58</v>
@@ -6754,13 +6770,13 @@
     </row>
     <row r="73" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B73" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="B73" s="2" t="s">
+      <c r="C73" s="2" t="s">
         <v>172</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>173</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>26</v>
@@ -6778,7 +6794,7 @@
         <v>28</v>
       </c>
       <c r="I73" s="11" t="s">
-        <v>254</v>
+        <v>169</v>
       </c>
       <c r="J73" s="2">
         <v>1</v>
@@ -6787,16 +6803,31 @@
         <v>1</v>
       </c>
       <c r="L73" s="4">
-        <v>46097</v>
+        <v>46086</v>
+      </c>
+      <c r="P73" s="4">
+        <v>46094</v>
+      </c>
+      <c r="Q73" s="4">
+        <v>46103</v>
+      </c>
+      <c r="R73" s="4">
+        <v>46105</v>
+      </c>
+      <c r="S73" s="4">
+        <v>46112</v>
+      </c>
+      <c r="T73" s="4">
+        <v>46112</v>
       </c>
       <c r="V73" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="W73" s="2" t="s">
         <v>30</v>
       </c>
       <c r="X73" s="2" t="s">
-        <v>255</v>
+        <v>53</v>
       </c>
       <c r="Y73" s="2" t="s">
         <v>58</v>
@@ -6804,13 +6835,13 @@
     </row>
     <row r="74" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B74" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="B74" s="2" t="s">
+      <c r="C74" s="2" t="s">
         <v>172</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>173</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>26</v>
@@ -6828,7 +6859,7 @@
         <v>28</v>
       </c>
       <c r="I74" s="11" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="J74" s="2">
         <v>1</v>
@@ -6855,7 +6886,7 @@
         <v>46112</v>
       </c>
       <c r="V74" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="W74" s="2" t="s">
         <v>30</v>
@@ -6869,13 +6900,13 @@
     </row>
     <row r="75" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B75" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="B75" s="2" t="s">
+      <c r="C75" s="2" t="s">
         <v>172</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>173</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>26</v>
@@ -6893,7 +6924,7 @@
         <v>28</v>
       </c>
       <c r="I75" s="11" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="J75" s="2">
         <v>1</v>
@@ -6920,7 +6951,7 @@
         <v>46112</v>
       </c>
       <c r="V75" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="W75" s="2" t="s">
         <v>30</v>
@@ -6934,13 +6965,13 @@
     </row>
     <row r="76" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B76" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="B76" s="2" t="s">
+      <c r="C76" s="2" t="s">
         <v>172</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>173</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>26</v>
@@ -6958,7 +6989,7 @@
         <v>28</v>
       </c>
       <c r="I76" s="11" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="J76" s="2">
         <v>1</v>
@@ -6969,14 +7000,23 @@
       <c r="L76" s="4">
         <v>46097</v>
       </c>
+      <c r="P76" s="4">
+        <v>46117</v>
+      </c>
+      <c r="Q76" s="4">
+        <v>46118</v>
+      </c>
+      <c r="R76" s="4">
+        <v>46119</v>
+      </c>
       <c r="V76" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="W76" s="2" t="s">
         <v>30</v>
       </c>
       <c r="X76" s="2" t="s">
-        <v>262</v>
+        <v>99</v>
       </c>
       <c r="Y76" s="2" t="s">
         <v>58</v>
@@ -6984,13 +7024,13 @@
     </row>
     <row r="77" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B77" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="B77" s="2" t="s">
+      <c r="C77" s="2" t="s">
         <v>172</v>
-      </c>
-      <c r="C77" s="2" t="s">
-        <v>173</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>26</v>
@@ -7008,7 +7048,7 @@
         <v>28</v>
       </c>
       <c r="I77" s="11" t="s">
-        <v>204</v>
+        <v>253</v>
       </c>
       <c r="J77" s="2">
         <v>1</v>
@@ -7017,31 +7057,25 @@
         <v>1</v>
       </c>
       <c r="L77" s="4">
-        <v>46086</v>
+        <v>46097</v>
       </c>
       <c r="P77" s="4">
-        <v>46094</v>
+        <v>46117</v>
       </c>
       <c r="Q77" s="4">
-        <v>46103</v>
+        <v>46118</v>
       </c>
       <c r="R77" s="4">
-        <v>46105</v>
-      </c>
-      <c r="S77" s="4">
-        <v>46112</v>
-      </c>
-      <c r="T77" s="4">
-        <v>46112</v>
+        <v>46119</v>
       </c>
       <c r="V77" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="W77" s="2" t="s">
         <v>30</v>
       </c>
       <c r="X77" s="2" t="s">
-        <v>53</v>
+        <v>99</v>
       </c>
       <c r="Y77" s="2" t="s">
         <v>58</v>
@@ -7049,13 +7083,13 @@
     </row>
     <row r="78" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B78" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="B78" s="2" t="s">
+      <c r="C78" s="2" t="s">
         <v>172</v>
-      </c>
-      <c r="C78" s="2" t="s">
-        <v>173</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>26</v>
@@ -7073,7 +7107,7 @@
         <v>28</v>
       </c>
       <c r="I78" s="11" t="s">
-        <v>257</v>
+        <v>201</v>
       </c>
       <c r="J78" s="2">
         <v>1</v>
@@ -7082,16 +7116,31 @@
         <v>1</v>
       </c>
       <c r="L78" s="4">
-        <v>46097</v>
+        <v>46086</v>
+      </c>
+      <c r="P78" s="4">
+        <v>46094</v>
+      </c>
+      <c r="Q78" s="4">
+        <v>46103</v>
+      </c>
+      <c r="R78" s="4">
+        <v>46105</v>
+      </c>
+      <c r="S78" s="4">
+        <v>46112</v>
+      </c>
+      <c r="T78" s="4">
+        <v>46112</v>
       </c>
       <c r="V78" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="W78" s="2" t="s">
         <v>30</v>
       </c>
       <c r="X78" s="2" t="s">
-        <v>255</v>
+        <v>53</v>
       </c>
       <c r="Y78" s="2" t="s">
         <v>58</v>
@@ -7099,13 +7148,13 @@
     </row>
     <row r="79" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B79" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="B79" s="2" t="s">
+      <c r="C79" s="2" t="s">
         <v>172</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>173</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>26</v>
@@ -7123,7 +7172,7 @@
         <v>28</v>
       </c>
       <c r="I79" s="11" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="J79" s="2">
         <v>1</v>
@@ -7150,7 +7199,7 @@
         <v>46112</v>
       </c>
       <c r="V79" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="W79" s="2" t="s">
         <v>30</v>
@@ -7164,13 +7213,13 @@
     </row>
     <row r="80" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B80" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="B80" s="2" t="s">
+      <c r="C80" s="2" t="s">
         <v>172</v>
-      </c>
-      <c r="C80" s="2" t="s">
-        <v>173</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>26</v>
@@ -7188,7 +7237,7 @@
         <v>28</v>
       </c>
       <c r="I80" s="11" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="J80" s="2">
         <v>1</v>
@@ -7199,14 +7248,23 @@
       <c r="L80" s="4">
         <v>46097</v>
       </c>
+      <c r="P80" s="4">
+        <v>46117</v>
+      </c>
+      <c r="Q80" s="4">
+        <v>46118</v>
+      </c>
+      <c r="R80" s="4">
+        <v>46119</v>
+      </c>
       <c r="V80" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="W80" s="2" t="s">
         <v>30</v>
       </c>
       <c r="X80" s="2" t="s">
-        <v>255</v>
+        <v>41</v>
       </c>
       <c r="Y80" s="2" t="s">
         <v>58</v>
@@ -7214,13 +7272,13 @@
     </row>
     <row r="81" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B81" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="B81" s="2" t="s">
+      <c r="C81" s="2" t="s">
         <v>172</v>
-      </c>
-      <c r="C81" s="2" t="s">
-        <v>173</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>26</v>
@@ -7238,7 +7296,7 @@
         <v>28</v>
       </c>
       <c r="I81" s="11" t="s">
-        <v>259</v>
+        <v>203</v>
       </c>
       <c r="J81" s="2">
         <v>1</v>
@@ -7247,16 +7305,31 @@
         <v>1</v>
       </c>
       <c r="L81" s="4">
-        <v>46097</v>
+        <v>46086</v>
+      </c>
+      <c r="P81" s="4">
+        <v>46094</v>
+      </c>
+      <c r="Q81" s="4">
+        <v>46103</v>
+      </c>
+      <c r="R81" s="4">
+        <v>46105</v>
+      </c>
+      <c r="S81" s="4">
+        <v>46112</v>
+      </c>
+      <c r="T81" s="4">
+        <v>46112</v>
       </c>
       <c r="V81" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="W81" s="2" t="s">
         <v>30</v>
       </c>
       <c r="X81" s="2" t="s">
-        <v>255</v>
+        <v>53</v>
       </c>
       <c r="Y81" s="2" t="s">
         <v>58</v>
@@ -7264,13 +7337,13 @@
     </row>
     <row r="82" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B82" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="B82" s="2" t="s">
+      <c r="C82" s="2" t="s">
         <v>172</v>
-      </c>
-      <c r="C82" s="2" t="s">
-        <v>173</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>26</v>
@@ -7288,7 +7361,7 @@
         <v>28</v>
       </c>
       <c r="I82" s="11" t="s">
-        <v>206</v>
+        <v>255</v>
       </c>
       <c r="J82" s="2">
         <v>1</v>
@@ -7297,31 +7370,25 @@
         <v>1</v>
       </c>
       <c r="L82" s="4">
-        <v>46086</v>
+        <v>46097</v>
       </c>
       <c r="P82" s="4">
-        <v>46094</v>
+        <v>46117</v>
       </c>
       <c r="Q82" s="4">
-        <v>46103</v>
+        <v>46118</v>
       </c>
       <c r="R82" s="4">
-        <v>46105</v>
-      </c>
-      <c r="S82" s="4">
-        <v>46112</v>
-      </c>
-      <c r="T82" s="4">
-        <v>46112</v>
+        <v>46119</v>
       </c>
       <c r="V82" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="W82" s="2" t="s">
         <v>30</v>
       </c>
       <c r="X82" s="2" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="Y82" s="2" t="s">
         <v>58</v>
@@ -7329,13 +7396,13 @@
     </row>
     <row r="83" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B83" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="B83" s="2" t="s">
+      <c r="C83" s="2" t="s">
         <v>172</v>
-      </c>
-      <c r="C83" s="2" t="s">
-        <v>173</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>26</v>
@@ -7353,7 +7420,7 @@
         <v>28</v>
       </c>
       <c r="I83" s="11" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="J83" s="2">
         <v>1</v>
@@ -7380,7 +7447,7 @@
         <v>46112</v>
       </c>
       <c r="V83" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="W83" s="2" t="s">
         <v>30</v>
@@ -7394,13 +7461,13 @@
     </row>
     <row r="84" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B84" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="B84" s="2" t="s">
+      <c r="C84" s="2" t="s">
         <v>172</v>
-      </c>
-      <c r="C84" s="2" t="s">
-        <v>173</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>26</v>
@@ -7418,7 +7485,7 @@
         <v>28</v>
       </c>
       <c r="I84" s="11" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="J84" s="2">
         <v>1</v>
@@ -7429,14 +7496,23 @@
       <c r="L84" s="4">
         <v>46097</v>
       </c>
+      <c r="P84" s="4">
+        <v>46117</v>
+      </c>
+      <c r="Q84" s="4">
+        <v>46118</v>
+      </c>
+      <c r="R84" s="4">
+        <v>46119</v>
+      </c>
       <c r="V84" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="W84" s="2" t="s">
         <v>30</v>
       </c>
       <c r="X84" s="2" t="s">
-        <v>255</v>
+        <v>41</v>
       </c>
       <c r="Y84" s="2" t="s">
         <v>58</v>
@@ -7444,13 +7520,13 @@
     </row>
     <row r="85" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B85" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="B85" s="2" t="s">
+      <c r="C85" s="2" t="s">
         <v>172</v>
-      </c>
-      <c r="C85" s="2" t="s">
-        <v>173</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>26</v>
@@ -7468,7 +7544,7 @@
         <v>28</v>
       </c>
       <c r="I85" s="11" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="J85" s="2">
         <v>1</v>
@@ -7479,14 +7555,23 @@
       <c r="L85" s="4">
         <v>46097</v>
       </c>
+      <c r="P85" s="4">
+        <v>46117</v>
+      </c>
+      <c r="Q85" s="4">
+        <v>46118</v>
+      </c>
+      <c r="R85" s="4">
+        <v>46119</v>
+      </c>
       <c r="V85" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="W85" s="2" t="s">
         <v>30</v>
       </c>
       <c r="X85" s="2" t="s">
-        <v>255</v>
+        <v>41</v>
       </c>
       <c r="Y85" s="2" t="s">
         <v>58</v>
@@ -7494,13 +7579,13 @@
     </row>
     <row r="86" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B86" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="B86" s="2" t="s">
+      <c r="C86" s="2" t="s">
         <v>172</v>
-      </c>
-      <c r="C86" s="2" t="s">
-        <v>45</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>26</v>
@@ -7518,7 +7603,7 @@
         <v>28</v>
       </c>
       <c r="I86" s="11" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="J86" s="2">
         <v>1</v>
@@ -7529,14 +7614,29 @@
       <c r="L86" s="4">
         <v>46086</v>
       </c>
+      <c r="P86" s="4">
+        <v>46094</v>
+      </c>
+      <c r="Q86" s="4">
+        <v>46103</v>
+      </c>
+      <c r="R86" s="4">
+        <v>46105</v>
+      </c>
+      <c r="S86" s="4">
+        <v>46112</v>
+      </c>
+      <c r="T86" s="4">
+        <v>46112</v>
+      </c>
       <c r="V86" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="W86" s="2" t="s">
         <v>30</v>
       </c>
       <c r="X86" s="2" t="s">
-        <v>137</v>
+        <v>53</v>
       </c>
       <c r="Y86" s="2" t="s">
         <v>58</v>
@@ -7544,13 +7644,13 @@
     </row>
     <row r="87" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B87" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="B87" s="2" t="s">
+      <c r="C87" s="2" t="s">
         <v>172</v>
-      </c>
-      <c r="C87" s="2" t="s">
-        <v>45</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>26</v>
@@ -7568,7 +7668,7 @@
         <v>28</v>
       </c>
       <c r="I87" s="11" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="J87" s="2">
         <v>1</v>
@@ -7579,14 +7679,29 @@
       <c r="L87" s="4">
         <v>46086</v>
       </c>
+      <c r="P87" s="4">
+        <v>46094</v>
+      </c>
+      <c r="Q87" s="4">
+        <v>46103</v>
+      </c>
+      <c r="R87" s="4">
+        <v>46105</v>
+      </c>
+      <c r="S87" s="4">
+        <v>46112</v>
+      </c>
+      <c r="T87" s="4">
+        <v>46112</v>
+      </c>
       <c r="V87" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="W87" s="2" t="s">
         <v>30</v>
       </c>
       <c r="X87" s="2" t="s">
-        <v>137</v>
+        <v>53</v>
       </c>
       <c r="Y87" s="2" t="s">
         <v>58</v>
@@ -7594,13 +7709,13 @@
     </row>
     <row r="88" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B88" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="B88" s="2" t="s">
+      <c r="C88" s="2" t="s">
         <v>172</v>
-      </c>
-      <c r="C88" s="2" t="s">
-        <v>45</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>26</v>
@@ -7618,7 +7733,7 @@
         <v>28</v>
       </c>
       <c r="I88" s="11" t="s">
-        <v>210</v>
+        <v>258</v>
       </c>
       <c r="J88" s="2">
         <v>1</v>
@@ -7627,16 +7742,25 @@
         <v>1</v>
       </c>
       <c r="L88" s="4">
-        <v>46086</v>
+        <v>46097</v>
+      </c>
+      <c r="P88" s="4">
+        <v>46117</v>
+      </c>
+      <c r="Q88" s="4">
+        <v>46118</v>
+      </c>
+      <c r="R88" s="4">
+        <v>46119</v>
       </c>
       <c r="V88" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="W88" s="2" t="s">
         <v>30</v>
       </c>
       <c r="X88" s="2" t="s">
-        <v>137</v>
+        <v>41</v>
       </c>
       <c r="Y88" s="2" t="s">
         <v>58</v>
@@ -7644,13 +7768,13 @@
     </row>
     <row r="89" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B89" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="B89" s="2" t="s">
+      <c r="C89" s="2" t="s">
         <v>172</v>
-      </c>
-      <c r="C89" s="2" t="s">
-        <v>45</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>26</v>
@@ -7668,7 +7792,7 @@
         <v>28</v>
       </c>
       <c r="I89" s="11" t="s">
-        <v>211</v>
+        <v>259</v>
       </c>
       <c r="J89" s="2">
         <v>1</v>
@@ -7677,16 +7801,25 @@
         <v>1</v>
       </c>
       <c r="L89" s="4">
-        <v>46086</v>
+        <v>46097</v>
+      </c>
+      <c r="P89" s="4">
+        <v>46117</v>
+      </c>
+      <c r="Q89" s="4">
+        <v>46118</v>
+      </c>
+      <c r="R89" s="4">
+        <v>46119</v>
       </c>
       <c r="V89" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="W89" s="2" t="s">
         <v>30</v>
       </c>
       <c r="X89" s="2" t="s">
-        <v>137</v>
+        <v>41</v>
       </c>
       <c r="Y89" s="2" t="s">
         <v>58</v>
@@ -7694,10 +7827,10 @@
     </row>
     <row r="90" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B90" s="2" t="s">
         <v>171</v>
-      </c>
-      <c r="B90" s="2" t="s">
-        <v>172</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>45</v>
@@ -7718,7 +7851,7 @@
         <v>28</v>
       </c>
       <c r="I90" s="11" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="J90" s="2">
         <v>1</v>
@@ -7730,13 +7863,13 @@
         <v>46086</v>
       </c>
       <c r="V90" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="W90" s="2" t="s">
         <v>30</v>
       </c>
       <c r="X90" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="Y90" s="2" t="s">
         <v>58</v>
@@ -7744,10 +7877,10 @@
     </row>
     <row r="91" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B91" s="2" t="s">
         <v>171</v>
-      </c>
-      <c r="B91" s="2" t="s">
-        <v>172</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>45</v>
@@ -7768,7 +7901,7 @@
         <v>28</v>
       </c>
       <c r="I91" s="11" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="J91" s="2">
         <v>1</v>
@@ -7780,13 +7913,13 @@
         <v>46086</v>
       </c>
       <c r="V91" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="W91" s="2" t="s">
         <v>30</v>
       </c>
       <c r="X91" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="Y91" s="2" t="s">
         <v>58</v>
@@ -7794,10 +7927,10 @@
     </row>
     <row r="92" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B92" s="2" t="s">
         <v>171</v>
-      </c>
-      <c r="B92" s="2" t="s">
-        <v>172</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>45</v>
@@ -7818,7 +7951,7 @@
         <v>28</v>
       </c>
       <c r="I92" s="11" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="J92" s="2">
         <v>1</v>
@@ -7830,13 +7963,13 @@
         <v>46086</v>
       </c>
       <c r="V92" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="W92" s="2" t="s">
         <v>30</v>
       </c>
       <c r="X92" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="Y92" s="2" t="s">
         <v>58</v>
@@ -7844,10 +7977,10 @@
     </row>
     <row r="93" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B93" s="2" t="s">
         <v>171</v>
-      </c>
-      <c r="B93" s="2" t="s">
-        <v>172</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>45</v>
@@ -7868,7 +8001,7 @@
         <v>28</v>
       </c>
       <c r="I93" s="11" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="J93" s="2">
         <v>1</v>
@@ -7880,24 +8013,24 @@
         <v>46086</v>
       </c>
       <c r="V93" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="W93" s="2" t="s">
         <v>30</v>
       </c>
       <c r="X93" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="Y93" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="94" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B94" s="2" t="s">
         <v>171</v>
-      </c>
-      <c r="B94" s="2" t="s">
-        <v>172</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>45</v>
@@ -7918,7 +8051,7 @@
         <v>28</v>
       </c>
       <c r="I94" s="11" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="J94" s="2">
         <v>1</v>
@@ -7929,31 +8062,25 @@
       <c r="L94" s="4">
         <v>46086</v>
       </c>
-      <c r="S94" s="4">
-        <v>46142</v>
-      </c>
-      <c r="T94" s="4">
-        <v>46142</v>
-      </c>
       <c r="V94" s="2" t="s">
-        <v>224</v>
+        <v>147</v>
       </c>
       <c r="W94" s="2" t="s">
         <v>30</v>
       </c>
       <c r="X94" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="Y94" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="95" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B95" s="2" t="s">
         <v>171</v>
-      </c>
-      <c r="B95" s="2" t="s">
-        <v>172</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>45</v>
@@ -7974,7 +8101,7 @@
         <v>28</v>
       </c>
       <c r="I95" s="11" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="J95" s="2">
         <v>1</v>
@@ -7985,31 +8112,25 @@
       <c r="L95" s="4">
         <v>46086</v>
       </c>
-      <c r="S95" s="4">
-        <v>46142</v>
-      </c>
-      <c r="T95" s="4">
-        <v>46142</v>
-      </c>
       <c r="V95" s="2" t="s">
-        <v>224</v>
+        <v>147</v>
       </c>
       <c r="W95" s="2" t="s">
         <v>30</v>
       </c>
       <c r="X95" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="Y95" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="96" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B96" s="2" t="s">
         <v>171</v>
-      </c>
-      <c r="B96" s="2" t="s">
-        <v>172</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>45</v>
@@ -8030,7 +8151,7 @@
         <v>28</v>
       </c>
       <c r="I96" s="11" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="J96" s="2">
         <v>1</v>
@@ -8041,31 +8162,25 @@
       <c r="L96" s="4">
         <v>46086</v>
       </c>
-      <c r="S96" s="4">
-        <v>46142</v>
-      </c>
-      <c r="T96" s="4">
-        <v>46142</v>
-      </c>
       <c r="V96" s="2" t="s">
-        <v>224</v>
+        <v>147</v>
       </c>
       <c r="W96" s="2" t="s">
         <v>30</v>
       </c>
       <c r="X96" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="Y96" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="97" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B97" s="2" t="s">
         <v>171</v>
-      </c>
-      <c r="B97" s="2" t="s">
-        <v>172</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>45</v>
@@ -8086,7 +8201,7 @@
         <v>28</v>
       </c>
       <c r="I97" s="11" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="J97" s="2">
         <v>1</v>
@@ -8097,31 +8212,25 @@
       <c r="L97" s="4">
         <v>46086</v>
       </c>
-      <c r="S97" s="4">
-        <v>46142</v>
-      </c>
-      <c r="T97" s="4">
-        <v>46142</v>
-      </c>
       <c r="V97" s="2" t="s">
-        <v>224</v>
+        <v>147</v>
       </c>
       <c r="W97" s="2" t="s">
         <v>30</v>
       </c>
       <c r="X97" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="Y97" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="98" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B98" s="2" t="s">
         <v>171</v>
-      </c>
-      <c r="B98" s="2" t="s">
-        <v>172</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>45</v>
@@ -8142,7 +8251,7 @@
         <v>28</v>
       </c>
       <c r="I98" s="11" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="J98" s="2">
         <v>1</v>
@@ -8160,24 +8269,24 @@
         <v>46142</v>
       </c>
       <c r="V98" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="W98" s="2" t="s">
         <v>30</v>
       </c>
       <c r="X98" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="Y98" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="99" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B99" s="2" t="s">
         <v>171</v>
-      </c>
-      <c r="B99" s="2" t="s">
-        <v>172</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>45</v>
@@ -8198,7 +8307,7 @@
         <v>28</v>
       </c>
       <c r="I99" s="11" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="J99" s="2">
         <v>1</v>
@@ -8216,24 +8325,24 @@
         <v>46142</v>
       </c>
       <c r="V99" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="W99" s="2" t="s">
         <v>30</v>
       </c>
       <c r="X99" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="Y99" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="100" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B100" s="2" t="s">
         <v>171</v>
-      </c>
-      <c r="B100" s="2" t="s">
-        <v>172</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>45</v>
@@ -8254,7 +8363,7 @@
         <v>28</v>
       </c>
       <c r="I100" s="11" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="J100" s="2">
         <v>1</v>
@@ -8272,24 +8381,24 @@
         <v>46142</v>
       </c>
       <c r="V100" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="W100" s="2" t="s">
         <v>30</v>
       </c>
       <c r="X100" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="Y100" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="101" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B101" s="2" t="s">
         <v>171</v>
-      </c>
-      <c r="B101" s="2" t="s">
-        <v>172</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>45</v>
@@ -8310,7 +8419,7 @@
         <v>28</v>
       </c>
       <c r="I101" s="11" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="J101" s="2">
         <v>1</v>
@@ -8328,24 +8437,24 @@
         <v>46142</v>
       </c>
       <c r="V101" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="W101" s="2" t="s">
         <v>30</v>
       </c>
       <c r="X101" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="Y101" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="102" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B102" s="2" t="s">
         <v>171</v>
-      </c>
-      <c r="B102" s="2" t="s">
-        <v>172</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>45</v>
@@ -8366,7 +8475,7 @@
         <v>28</v>
       </c>
       <c r="I102" s="11" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="J102" s="2">
         <v>1</v>
@@ -8384,24 +8493,24 @@
         <v>46142</v>
       </c>
       <c r="V102" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="W102" s="2" t="s">
         <v>30</v>
       </c>
       <c r="X102" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="Y102" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="103" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A103" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B103" s="2" t="s">
         <v>171</v>
-      </c>
-      <c r="B103" s="2" t="s">
-        <v>172</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>45</v>
@@ -8422,7 +8531,7 @@
         <v>28</v>
       </c>
       <c r="I103" s="11" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="J103" s="2">
         <v>1</v>
@@ -8440,30 +8549,30 @@
         <v>46142</v>
       </c>
       <c r="V103" s="2" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="W103" s="2" t="s">
         <v>30</v>
       </c>
       <c r="X103" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="Y103" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="104" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="s">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>151</v>
+        <v>171</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>152</v>
+        <v>45</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>27</v>
@@ -8472,13 +8581,13 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G104" s="7">
-        <v>14.5</v>
+        <v>14.2</v>
       </c>
       <c r="H104" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I104" s="2" t="s">
-        <v>182</v>
+      <c r="I104" s="11" t="s">
+        <v>221</v>
       </c>
       <c r="J104" s="2">
         <v>1</v>
@@ -8487,52 +8596,39 @@
         <v>1</v>
       </c>
       <c r="L104" s="4">
-        <v>46092</v>
-      </c>
-      <c r="M104" s="12"/>
-      <c r="N104" s="4">
-        <v>46093</v>
-      </c>
-      <c r="O104" s="4">
-        <v>46094</v>
-      </c>
-      <c r="Q104" s="4">
-        <v>46111</v>
-      </c>
-      <c r="R104" s="4">
-        <v>46112</v>
+        <v>46086</v>
       </c>
       <c r="S104" s="4">
-        <v>46113</v>
+        <v>46142</v>
       </c>
       <c r="T104" s="4">
-        <v>46113</v>
+        <v>46142</v>
       </c>
       <c r="V104" s="2" t="s">
-        <v>183</v>
+        <v>223</v>
       </c>
       <c r="W104" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="X104" s="2" t="s">
-        <v>53</v>
+        <v>136</v>
       </c>
       <c r="Y104" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="105" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A105" s="2" t="s">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>151</v>
+        <v>171</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>152</v>
+        <v>45</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>27</v>
@@ -8541,13 +8637,13 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G105" s="7">
-        <v>14.5</v>
+        <v>14.2</v>
       </c>
       <c r="H105" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I105" s="2" t="s">
-        <v>175</v>
+      <c r="I105" s="11" t="s">
+        <v>222</v>
       </c>
       <c r="J105" s="2">
         <v>1</v>
@@ -8556,52 +8652,39 @@
         <v>1</v>
       </c>
       <c r="L105" s="4">
-        <v>46092</v>
-      </c>
-      <c r="M105" s="12"/>
-      <c r="N105" s="4">
-        <v>46093</v>
-      </c>
-      <c r="O105" s="4">
-        <v>46094</v>
-      </c>
-      <c r="Q105" s="4">
-        <v>46111</v>
-      </c>
-      <c r="R105" s="4">
-        <v>46112</v>
+        <v>46086</v>
       </c>
       <c r="S105" s="4">
-        <v>46113</v>
+        <v>46142</v>
       </c>
       <c r="T105" s="4">
-        <v>46113</v>
+        <v>46142</v>
       </c>
       <c r="V105" s="2" t="s">
-        <v>183</v>
+        <v>223</v>
       </c>
       <c r="W105" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="X105" s="2" t="s">
-        <v>53</v>
+        <v>136</v>
       </c>
       <c r="Y105" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="106" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A106" s="2" t="s">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>151</v>
+        <v>171</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>152</v>
+        <v>45</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>27</v>
@@ -8610,13 +8693,13 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G106" s="7">
-        <v>14.5</v>
+        <v>14.2</v>
       </c>
       <c r="H106" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I106" s="2" t="s">
-        <v>176</v>
+      <c r="I106" s="11" t="s">
+        <v>224</v>
       </c>
       <c r="J106" s="2">
         <v>1</v>
@@ -8625,52 +8708,39 @@
         <v>1</v>
       </c>
       <c r="L106" s="4">
-        <v>46092</v>
-      </c>
-      <c r="M106" s="12"/>
-      <c r="N106" s="4">
-        <v>46093</v>
-      </c>
-      <c r="O106" s="4">
-        <v>46094</v>
-      </c>
-      <c r="Q106" s="4">
-        <v>46111</v>
-      </c>
-      <c r="R106" s="4">
-        <v>46112</v>
+        <v>46086</v>
       </c>
       <c r="S106" s="4">
-        <v>46113</v>
+        <v>46142</v>
       </c>
       <c r="T106" s="4">
-        <v>46113</v>
+        <v>46142</v>
       </c>
       <c r="V106" s="2" t="s">
-        <v>184</v>
+        <v>223</v>
       </c>
       <c r="W106" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="X106" s="2" t="s">
-        <v>53</v>
+        <v>136</v>
       </c>
       <c r="Y106" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="107" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A107" s="2" t="s">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>151</v>
+        <v>171</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>152</v>
+        <v>45</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>27</v>
@@ -8679,13 +8749,13 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G107" s="7">
-        <v>14.5</v>
+        <v>14.2</v>
       </c>
       <c r="H107" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I107" s="2" t="s">
-        <v>177</v>
+      <c r="I107" s="11" t="s">
+        <v>225</v>
       </c>
       <c r="J107" s="2">
         <v>1</v>
@@ -8694,49 +8764,36 @@
         <v>1</v>
       </c>
       <c r="L107" s="4">
-        <v>46092</v>
-      </c>
-      <c r="M107" s="12"/>
-      <c r="N107" s="4">
-        <v>46093</v>
-      </c>
-      <c r="O107" s="4">
-        <v>46094</v>
-      </c>
-      <c r="Q107" s="4">
-        <v>46111</v>
-      </c>
-      <c r="R107" s="4">
-        <v>46112</v>
+        <v>46086</v>
       </c>
       <c r="S107" s="4">
-        <v>46113</v>
+        <v>46142</v>
       </c>
       <c r="T107" s="4">
-        <v>46113</v>
+        <v>46142</v>
       </c>
       <c r="V107" s="2" t="s">
-        <v>184</v>
+        <v>226</v>
       </c>
       <c r="W107" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="X107" s="2" t="s">
-        <v>53</v>
+        <v>136</v>
       </c>
       <c r="Y107" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="108" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A108" s="2" t="s">
-        <v>187</v>
+        <v>149</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>188</v>
+        <v>150</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>189</v>
+        <v>151</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>34</v>
@@ -8754,7 +8811,7 @@
         <v>28</v>
       </c>
       <c r="I108" s="2" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="J108" s="2">
         <v>1</v>
@@ -8763,33 +8820,49 @@
         <v>1</v>
       </c>
       <c r="L108" s="4">
+        <v>46092</v>
+      </c>
+      <c r="M108" s="12"/>
+      <c r="N108" s="4">
+        <v>46093</v>
+      </c>
+      <c r="O108" s="4">
         <v>46094</v>
       </c>
+      <c r="Q108" s="4">
+        <v>46111</v>
+      </c>
+      <c r="R108" s="4">
+        <v>46112</v>
+      </c>
+      <c r="S108" s="4">
+        <v>46113</v>
+      </c>
       <c r="T108" s="4">
-        <v>46117</v>
+        <v>46113</v>
       </c>
       <c r="V108" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="W108" s="2" t="s">
         <v>29</v>
       </c>
       <c r="X108" s="2" t="s">
-        <v>100</v>
+        <v>53</v>
       </c>
       <c r="Y108" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="109" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A109" s="2" t="s">
-        <v>187</v>
+        <v>149</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>188</v>
+        <v>150</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>189</v>
+        <v>151</v>
       </c>
       <c r="D109" s="2" t="s">
         <v>34</v>
@@ -8807,7 +8880,7 @@
         <v>28</v>
       </c>
       <c r="I109" s="2" t="s">
-        <v>191</v>
+        <v>174</v>
       </c>
       <c r="J109" s="2">
         <v>1</v>
@@ -8816,33 +8889,49 @@
         <v>1</v>
       </c>
       <c r="L109" s="4">
+        <v>46092</v>
+      </c>
+      <c r="M109" s="12"/>
+      <c r="N109" s="4">
+        <v>46093</v>
+      </c>
+      <c r="O109" s="4">
         <v>46094</v>
       </c>
+      <c r="Q109" s="4">
+        <v>46111</v>
+      </c>
+      <c r="R109" s="4">
+        <v>46112</v>
+      </c>
+      <c r="S109" s="4">
+        <v>46113</v>
+      </c>
       <c r="T109" s="4">
-        <v>46117</v>
+        <v>46113</v>
       </c>
       <c r="V109" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="W109" s="2" t="s">
         <v>29</v>
       </c>
       <c r="X109" s="2" t="s">
-        <v>100</v>
+        <v>53</v>
       </c>
       <c r="Y109" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="110" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="s">
-        <v>187</v>
+        <v>149</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>188</v>
+        <v>150</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>189</v>
+        <v>151</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>34</v>
@@ -8860,7 +8949,7 @@
         <v>28</v>
       </c>
       <c r="I110" s="2" t="s">
-        <v>192</v>
+        <v>175</v>
       </c>
       <c r="J110" s="2">
         <v>1</v>
@@ -8869,33 +8958,49 @@
         <v>1</v>
       </c>
       <c r="L110" s="4">
+        <v>46092</v>
+      </c>
+      <c r="M110" s="12"/>
+      <c r="N110" s="4">
+        <v>46093</v>
+      </c>
+      <c r="O110" s="4">
         <v>46094</v>
       </c>
+      <c r="Q110" s="4">
+        <v>46111</v>
+      </c>
+      <c r="R110" s="4">
+        <v>46112</v>
+      </c>
+      <c r="S110" s="4">
+        <v>46113</v>
+      </c>
       <c r="T110" s="4">
-        <v>46117</v>
+        <v>46113</v>
       </c>
       <c r="V110" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="W110" s="2" t="s">
         <v>29</v>
       </c>
       <c r="X110" s="2" t="s">
-        <v>100</v>
+        <v>53</v>
       </c>
       <c r="Y110" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="111" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A111" s="2" t="s">
-        <v>187</v>
+        <v>149</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>188</v>
+        <v>150</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>189</v>
+        <v>151</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>34</v>
@@ -8913,7 +9018,7 @@
         <v>28</v>
       </c>
       <c r="I111" s="2" t="s">
-        <v>194</v>
+        <v>176</v>
       </c>
       <c r="J111" s="2">
         <v>1</v>
@@ -8922,33 +9027,49 @@
         <v>1</v>
       </c>
       <c r="L111" s="4">
+        <v>46092</v>
+      </c>
+      <c r="M111" s="12"/>
+      <c r="N111" s="4">
+        <v>46093</v>
+      </c>
+      <c r="O111" s="4">
         <v>46094</v>
       </c>
+      <c r="Q111" s="4">
+        <v>46111</v>
+      </c>
+      <c r="R111" s="4">
+        <v>46112</v>
+      </c>
+      <c r="S111" s="4">
+        <v>46113</v>
+      </c>
       <c r="T111" s="4">
-        <v>46117</v>
+        <v>46113</v>
       </c>
       <c r="V111" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="W111" s="2" t="s">
         <v>29</v>
       </c>
       <c r="X111" s="2" t="s">
-        <v>100</v>
+        <v>53</v>
       </c>
       <c r="Y111" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="112" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="B112" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="B112" s="2" t="s">
+      <c r="C112" s="2" t="s">
         <v>188</v>
-      </c>
-      <c r="C112" s="2" t="s">
-        <v>189</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>34</v>
@@ -8965,8 +9086,8 @@
       <c r="H112" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I112" s="13" t="s">
-        <v>193</v>
+      <c r="I112" s="2" t="s">
+        <v>189</v>
       </c>
       <c r="J112" s="2">
         <v>1</v>
@@ -8981,27 +9102,27 @@
         <v>46117</v>
       </c>
       <c r="V112" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="W112" s="2" t="s">
         <v>29</v>
       </c>
       <c r="X112" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="Y112" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="113" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A113" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="B113" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="B113" s="2" t="s">
+      <c r="C113" s="2" t="s">
         <v>188</v>
-      </c>
-      <c r="C113" s="2" t="s">
-        <v>189</v>
       </c>
       <c r="D113" s="2" t="s">
         <v>34</v>
@@ -9019,7 +9140,7 @@
         <v>28</v>
       </c>
       <c r="I113" s="2" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="J113" s="2">
         <v>1</v>
@@ -9028,40 +9149,33 @@
         <v>1</v>
       </c>
       <c r="L113" s="4">
-        <v>46098</v>
-      </c>
-      <c r="M113" s="6"/>
-      <c r="N113" s="4">
-        <v>46111</v>
-      </c>
-      <c r="O113" s="4">
-        <v>46112</v>
-      </c>
-      <c r="P113" s="4">
-        <v>46111</v>
+        <v>46094</v>
+      </c>
+      <c r="T113" s="4">
+        <v>46117</v>
       </c>
       <c r="V113" s="2" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
       <c r="W113" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X113" s="2" t="s">
-        <v>240</v>
+        <v>99</v>
       </c>
       <c r="Y113" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="114" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="B114" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="B114" s="2" t="s">
+      <c r="C114" s="2" t="s">
         <v>188</v>
-      </c>
-      <c r="C114" s="2" t="s">
-        <v>189</v>
       </c>
       <c r="D114" s="2" t="s">
         <v>34</v>
@@ -9079,7 +9193,7 @@
         <v>28</v>
       </c>
       <c r="I114" s="2" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="J114" s="2">
         <v>1</v>
@@ -9088,37 +9202,33 @@
         <v>1</v>
       </c>
       <c r="L114" s="4">
-        <v>46098</v>
-      </c>
-      <c r="M114" s="6"/>
-      <c r="N114" s="4">
-        <v>46111</v>
-      </c>
-      <c r="O114" s="4">
-        <v>46112</v>
+        <v>46094</v>
+      </c>
+      <c r="T114" s="4">
+        <v>46117</v>
       </c>
       <c r="V114" s="2" t="s">
-        <v>198</v>
+        <v>183</v>
       </c>
       <c r="W114" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X114" s="2" t="s">
-        <v>137</v>
+        <v>99</v>
       </c>
       <c r="Y114" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="115" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A115" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="B115" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="B115" s="2" t="s">
+      <c r="C115" s="2" t="s">
         <v>188</v>
-      </c>
-      <c r="C115" s="2" t="s">
-        <v>189</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>34</v>
@@ -9130,13 +9240,13 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G115" s="7">
-        <v>14.2</v>
+        <v>14.5</v>
       </c>
       <c r="H115" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I115" s="13" t="s">
-        <v>197</v>
+      <c r="I115" s="2" t="s">
+        <v>193</v>
       </c>
       <c r="J115" s="2">
         <v>1</v>
@@ -9145,43 +9255,36 @@
         <v>1</v>
       </c>
       <c r="L115" s="4">
-        <v>46098</v>
-      </c>
-      <c r="M115" s="6"/>
-      <c r="N115" s="4">
-        <v>46111</v>
-      </c>
-      <c r="O115" s="4">
-        <v>46112</v>
-      </c>
-      <c r="P115" s="4">
-        <v>46111</v>
+        <v>46094</v>
+      </c>
+      <c r="T115" s="4">
+        <v>46117</v>
       </c>
       <c r="V115" s="2" t="s">
-        <v>198</v>
+        <v>183</v>
       </c>
       <c r="W115" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X115" s="2" t="s">
-        <v>241</v>
+        <v>99</v>
       </c>
       <c r="Y115" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="116" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A116" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="B116" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="B116" s="2" t="s">
+      <c r="C116" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="C116" s="2" t="s">
-        <v>189</v>
-      </c>
       <c r="D116" s="2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>27</v>
@@ -9190,13 +9293,13 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G116" s="7">
-        <v>14.2</v>
+        <v>14.5</v>
       </c>
       <c r="H116" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I116" s="2" t="s">
-        <v>228</v>
+      <c r="I116" s="13" t="s">
+        <v>192</v>
       </c>
       <c r="J116" s="2">
         <v>1</v>
@@ -9205,37 +9308,36 @@
         <v>1</v>
       </c>
       <c r="L116" s="4">
-        <v>46104</v>
-      </c>
-      <c r="M116" s="6"/>
-      <c r="N116" s="4">
-        <v>46106</v>
+        <v>46094</v>
+      </c>
+      <c r="T116" s="4">
+        <v>46117</v>
       </c>
       <c r="V116" s="2" t="s">
-        <v>148</v>
+        <v>183</v>
       </c>
       <c r="W116" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X116" s="2" t="s">
-        <v>137</v>
+        <v>99</v>
       </c>
       <c r="Y116" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="117" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A117" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="B117" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="B117" s="2" t="s">
+      <c r="C117" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="C117" s="2" t="s">
-        <v>189</v>
-      </c>
       <c r="D117" s="2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>27</v>
@@ -9244,13 +9346,13 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G117" s="7">
-        <v>14.2</v>
+        <v>14.5</v>
       </c>
       <c r="H117" s="2" t="s">
         <v>28</v>
       </c>
       <c r="I117" s="2" t="s">
-        <v>229</v>
+        <v>194</v>
       </c>
       <c r="J117" s="2">
         <v>1</v>
@@ -9259,37 +9361,43 @@
         <v>1</v>
       </c>
       <c r="L117" s="4">
-        <v>46104</v>
+        <v>46098</v>
       </c>
       <c r="M117" s="6"/>
       <c r="N117" s="4">
-        <v>46106</v>
+        <v>46111</v>
+      </c>
+      <c r="O117" s="4">
+        <v>46112</v>
+      </c>
+      <c r="P117" s="4">
+        <v>46111</v>
       </c>
       <c r="V117" s="2" t="s">
-        <v>148</v>
+        <v>197</v>
       </c>
       <c r="W117" s="2" t="s">
         <v>30</v>
       </c>
       <c r="X117" s="2" t="s">
-        <v>137</v>
+        <v>239</v>
       </c>
       <c r="Y117" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="118" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A118" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="B118" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="B118" s="2" t="s">
+      <c r="C118" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="C118" s="2" t="s">
-        <v>189</v>
-      </c>
       <c r="D118" s="2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E118" s="2" t="s">
         <v>27</v>
@@ -9298,13 +9406,13 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G118" s="7">
-        <v>14.2</v>
+        <v>14.5</v>
       </c>
       <c r="H118" s="2" t="s">
         <v>28</v>
       </c>
       <c r="I118" s="2" t="s">
-        <v>230</v>
+        <v>195</v>
       </c>
       <c r="J118" s="2">
         <v>1</v>
@@ -9313,37 +9421,40 @@
         <v>1</v>
       </c>
       <c r="L118" s="4">
-        <v>46104</v>
+        <v>46098</v>
       </c>
       <c r="M118" s="6"/>
       <c r="N118" s="4">
-        <v>46106</v>
+        <v>46111</v>
+      </c>
+      <c r="O118" s="4">
+        <v>46112</v>
       </c>
       <c r="V118" s="2" t="s">
-        <v>234</v>
+        <v>197</v>
       </c>
       <c r="W118" s="2" t="s">
         <v>30</v>
       </c>
       <c r="X118" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="Y118" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="119" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A119" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="B119" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="B119" s="2" t="s">
+      <c r="C119" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="C119" s="2" t="s">
-        <v>189</v>
-      </c>
       <c r="D119" s="2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E119" s="2" t="s">
         <v>27</v>
@@ -9357,8 +9468,8 @@
       <c r="H119" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I119" s="2" t="s">
-        <v>231</v>
+      <c r="I119" s="13" t="s">
+        <v>196</v>
       </c>
       <c r="J119" s="2">
         <v>1</v>
@@ -9367,34 +9478,40 @@
         <v>1</v>
       </c>
       <c r="L119" s="4">
-        <v>46104</v>
+        <v>46098</v>
       </c>
       <c r="M119" s="6"/>
       <c r="N119" s="4">
-        <v>46106</v>
+        <v>46111</v>
+      </c>
+      <c r="O119" s="4">
+        <v>46112</v>
+      </c>
+      <c r="P119" s="4">
+        <v>46111</v>
       </c>
       <c r="V119" s="2" t="s">
-        <v>148</v>
+        <v>197</v>
       </c>
       <c r="W119" s="2" t="s">
         <v>30</v>
       </c>
       <c r="X119" s="2" t="s">
-        <v>137</v>
+        <v>240</v>
       </c>
       <c r="Y119" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="120" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A120" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="B120" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="B120" s="2" t="s">
+      <c r="C120" s="2" t="s">
         <v>188</v>
-      </c>
-      <c r="C120" s="2" t="s">
-        <v>189</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>26</v>
@@ -9412,7 +9529,7 @@
         <v>28</v>
       </c>
       <c r="I120" s="2" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="J120" s="2">
         <v>1</v>
@@ -9428,27 +9545,27 @@
         <v>46106</v>
       </c>
       <c r="V120" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="W120" s="2" t="s">
         <v>30</v>
       </c>
       <c r="X120" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="Y120" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="121" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A121" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="B121" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="B121" s="2" t="s">
+      <c r="C121" s="2" t="s">
         <v>188</v>
-      </c>
-      <c r="C121" s="2" t="s">
-        <v>189</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>26</v>
@@ -9466,7 +9583,7 @@
         <v>28</v>
       </c>
       <c r="I121" s="2" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="J121" s="2">
         <v>1</v>
@@ -9482,27 +9599,27 @@
         <v>46106</v>
       </c>
       <c r="V121" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="W121" s="2" t="s">
         <v>30</v>
       </c>
       <c r="X121" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="Y121" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="122" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
-        <v>62</v>
+        <v>186</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>63</v>
+        <v>187</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>64</v>
+        <v>188</v>
       </c>
       <c r="D122" s="2" t="s">
         <v>26</v>
@@ -9514,13 +9631,13 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G122" s="7">
-        <v>15</v>
+        <v>14.2</v>
       </c>
       <c r="H122" s="2" t="s">
         <v>28</v>
       </c>
       <c r="I122" s="2" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="J122" s="2">
         <v>1</v>
@@ -9529,33 +9646,34 @@
         <v>1</v>
       </c>
       <c r="L122" s="4">
-        <v>46107</v>
-      </c>
+        <v>46104</v>
+      </c>
+      <c r="M122" s="6"/>
       <c r="N122" s="4">
-        <v>46108</v>
+        <v>46106</v>
       </c>
       <c r="V122" s="2" t="s">
-        <v>148</v>
+        <v>233</v>
       </c>
       <c r="W122" s="2" t="s">
         <v>30</v>
       </c>
       <c r="X122" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="Y122" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="123" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A123" s="2" t="s">
-        <v>62</v>
+        <v>186</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>63</v>
+        <v>187</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>64</v>
+        <v>188</v>
       </c>
       <c r="D123" s="2" t="s">
         <v>26</v>
@@ -9567,13 +9685,13 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G123" s="7">
-        <v>15</v>
+        <v>14.2</v>
       </c>
       <c r="H123" s="2" t="s">
         <v>28</v>
       </c>
       <c r="I123" s="2" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="J123" s="2">
         <v>1</v>
@@ -9582,33 +9700,34 @@
         <v>1</v>
       </c>
       <c r="L123" s="4">
-        <v>46107</v>
-      </c>
+        <v>46104</v>
+      </c>
+      <c r="M123" s="6"/>
       <c r="N123" s="4">
-        <v>46108</v>
+        <v>46106</v>
       </c>
       <c r="V123" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="W123" s="2" t="s">
         <v>30</v>
       </c>
       <c r="X123" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="Y123" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="124" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A124" s="2" t="s">
-        <v>62</v>
+        <v>186</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>63</v>
+        <v>187</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>64</v>
+        <v>188</v>
       </c>
       <c r="D124" s="2" t="s">
         <v>26</v>
@@ -9620,13 +9739,13 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G124" s="7">
-        <v>15</v>
+        <v>14.2</v>
       </c>
       <c r="H124" s="2" t="s">
         <v>28</v>
       </c>
       <c r="I124" s="2" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="J124" s="2">
         <v>1</v>
@@ -9635,33 +9754,34 @@
         <v>1</v>
       </c>
       <c r="L124" s="4">
-        <v>46107</v>
-      </c>
+        <v>46104</v>
+      </c>
+      <c r="M124" s="6"/>
       <c r="N124" s="4">
-        <v>46108</v>
+        <v>46106</v>
       </c>
       <c r="V124" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="W124" s="2" t="s">
         <v>30</v>
       </c>
       <c r="X124" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="Y124" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="125" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A125" s="2" t="s">
-        <v>62</v>
+        <v>186</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>63</v>
+        <v>187</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>64</v>
+        <v>188</v>
       </c>
       <c r="D125" s="2" t="s">
         <v>26</v>
@@ -9673,13 +9793,13 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G125" s="7">
-        <v>15</v>
+        <v>14.2</v>
       </c>
       <c r="H125" s="2" t="s">
         <v>28</v>
       </c>
       <c r="I125" s="2" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="J125" s="2">
         <v>1</v>
@@ -9688,25 +9808,26 @@
         <v>1</v>
       </c>
       <c r="L125" s="4">
-        <v>46107</v>
-      </c>
+        <v>46104</v>
+      </c>
+      <c r="M125" s="6"/>
       <c r="N125" s="4">
-        <v>46108</v>
+        <v>46106</v>
       </c>
       <c r="V125" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="W125" s="2" t="s">
         <v>30</v>
       </c>
       <c r="X125" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="Y125" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="126" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A126" s="2" t="s">
         <v>62</v>
       </c>
@@ -9732,7 +9853,7 @@
         <v>28</v>
       </c>
       <c r="I126" s="2" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="J126" s="2">
         <v>1</v>
@@ -9746,31 +9867,34 @@
       <c r="N126" s="4">
         <v>46108</v>
       </c>
+      <c r="P126" s="4">
+        <v>46116</v>
+      </c>
       <c r="V126" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="W126" s="2" t="s">
         <v>30</v>
       </c>
       <c r="X126" s="2" t="s">
-        <v>137</v>
+        <v>99</v>
       </c>
       <c r="Y126" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="127" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A127" s="2" t="s">
         <v>62</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="E127" s="2" t="s">
         <v>27</v>
@@ -9779,74 +9903,69 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G127" s="7">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="H127" s="2" t="s">
         <v>28</v>
       </c>
       <c r="I127" s="2" t="s">
-        <v>86</v>
+        <v>235</v>
       </c>
       <c r="J127" s="2">
         <v>1</v>
       </c>
       <c r="K127" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L127" s="4">
-        <v>45995</v>
-      </c>
-      <c r="M127" s="4">
         <v>46107</v>
       </c>
       <c r="N127" s="4">
-        <v>46111</v>
-      </c>
-      <c r="O127" s="4">
-        <v>46112</v>
-      </c>
-      <c r="P127" s="10"/>
+        <v>46108</v>
+      </c>
+      <c r="P127" s="4">
+        <v>46116</v>
+      </c>
       <c r="V127" s="2" t="s">
-        <v>66</v>
+        <v>147</v>
       </c>
       <c r="W127" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="X127" s="2" t="s">
-        <v>137</v>
+        <v>99</v>
       </c>
       <c r="Y127" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="AB127" s="9"/>
-    </row>
-    <row r="128" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="128" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A128" s="2" t="s">
-        <v>242</v>
+        <v>62</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>243</v>
+        <v>63</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>244</v>
+        <v>64</v>
       </c>
       <c r="D128" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F128" s="3">
-        <v>0.43</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="G128" s="7">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="H128" s="2" t="s">
-        <v>245</v>
+        <v>28</v>
       </c>
       <c r="I128" s="2" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="J128" s="2">
         <v>1</v>
@@ -9855,72 +9974,54 @@
         <v>1</v>
       </c>
       <c r="L128" s="4">
-        <v>45896</v>
+        <v>46107</v>
       </c>
       <c r="N128" s="4">
-        <v>45897</v>
-      </c>
-      <c r="O128" s="4">
-        <v>45897</v>
+        <v>46108</v>
       </c>
       <c r="P128" s="4">
-        <v>45897</v>
-      </c>
-      <c r="Q128" s="4">
-        <v>45903</v>
-      </c>
-      <c r="R128" s="4">
-        <v>45905</v>
-      </c>
-      <c r="S128" s="4">
-        <v>45908</v>
-      </c>
-      <c r="T128" s="4">
-        <v>45908</v>
+        <v>46116</v>
       </c>
       <c r="V128" s="2" t="s">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="W128" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="X128" s="2" t="s">
-        <v>53</v>
+        <v>99</v>
       </c>
       <c r="Y128" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="Z128" s="4">
-        <v>46112</v>
-      </c>
-    </row>
-    <row r="129" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="129" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A129" s="2" t="s">
-        <v>242</v>
+        <v>62</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>243</v>
+        <v>63</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>244</v>
+        <v>64</v>
       </c>
       <c r="D129" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F129" s="3">
-        <v>0.43</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="G129" s="7">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="H129" s="2" t="s">
-        <v>245</v>
+        <v>28</v>
       </c>
       <c r="I129" s="2" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="J129" s="2">
         <v>1</v>
@@ -9929,72 +10030,54 @@
         <v>1</v>
       </c>
       <c r="L129" s="4">
-        <v>45896</v>
+        <v>46107</v>
       </c>
       <c r="N129" s="4">
-        <v>45897</v>
-      </c>
-      <c r="O129" s="4">
-        <v>45897</v>
+        <v>46108</v>
       </c>
       <c r="P129" s="4">
-        <v>45897</v>
-      </c>
-      <c r="Q129" s="4">
-        <v>45903</v>
-      </c>
-      <c r="R129" s="4">
-        <v>45905</v>
-      </c>
-      <c r="S129" s="4">
-        <v>45908</v>
-      </c>
-      <c r="T129" s="4">
-        <v>45908</v>
+        <v>46116</v>
       </c>
       <c r="V129" s="2" t="s">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="W129" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="X129" s="2" t="s">
-        <v>53</v>
+        <v>99</v>
       </c>
       <c r="Y129" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="Z129" s="4">
-        <v>46112</v>
-      </c>
-    </row>
-    <row r="130" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="130" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A130" s="2" t="s">
-        <v>242</v>
+        <v>62</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>243</v>
+        <v>63</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>244</v>
+        <v>64</v>
       </c>
       <c r="D130" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F130" s="3">
-        <v>0.43</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="G130" s="7">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="H130" s="2" t="s">
-        <v>245</v>
+        <v>28</v>
       </c>
       <c r="I130" s="2" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="J130" s="2">
         <v>1</v>
@@ -10003,54 +10086,36 @@
         <v>1</v>
       </c>
       <c r="L130" s="4">
-        <v>45944</v>
+        <v>46107</v>
       </c>
       <c r="N130" s="4">
-        <v>45945</v>
-      </c>
-      <c r="O130" s="4">
-        <v>45947</v>
+        <v>46108</v>
       </c>
       <c r="P130" s="4">
-        <v>45950</v>
-      </c>
-      <c r="Q130" s="4">
-        <v>45954</v>
-      </c>
-      <c r="R130" s="4">
-        <v>45957</v>
-      </c>
-      <c r="S130" s="4">
-        <v>45958</v>
-      </c>
-      <c r="T130" s="4">
-        <v>45958</v>
+        <v>46116</v>
       </c>
       <c r="V130" s="2" t="s">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="W130" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="X130" s="2" t="s">
-        <v>53</v>
+        <v>99</v>
       </c>
       <c r="Y130" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="Z130" s="4">
-        <v>46112</v>
-      </c>
-    </row>
-    <row r="131" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="131" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A131" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="B131" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="B131" s="2" t="s">
+      <c r="C131" s="2" t="s">
         <v>243</v>
-      </c>
-      <c r="C131" s="2" t="s">
-        <v>244</v>
       </c>
       <c r="D131" s="2" t="s">
         <v>26</v>
@@ -10065,11 +10130,11 @@
         <v>14.5</v>
       </c>
       <c r="H131" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="I131" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="I131" s="2" t="s">
-        <v>249</v>
-      </c>
       <c r="J131" s="2">
         <v>1</v>
       </c>
@@ -10077,31 +10142,31 @@
         <v>1</v>
       </c>
       <c r="L131" s="4">
-        <v>45944</v>
+        <v>45896</v>
       </c>
       <c r="N131" s="4">
-        <v>45945</v>
+        <v>45897</v>
       </c>
       <c r="O131" s="4">
-        <v>45947</v>
+        <v>45897</v>
       </c>
       <c r="P131" s="4">
-        <v>45950</v>
+        <v>45897</v>
       </c>
       <c r="Q131" s="4">
-        <v>45954</v>
+        <v>45903</v>
       </c>
       <c r="R131" s="4">
-        <v>45957</v>
+        <v>45905</v>
       </c>
       <c r="S131" s="4">
-        <v>45958</v>
+        <v>45908</v>
       </c>
       <c r="T131" s="4">
-        <v>45958</v>
+        <v>45908</v>
       </c>
       <c r="V131" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="W131" s="2" t="s">
         <v>29</v>
@@ -10116,15 +10181,15 @@
         <v>46112</v>
       </c>
     </row>
-    <row r="132" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A132" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="B132" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="B132" s="2" t="s">
+      <c r="C132" s="2" t="s">
         <v>243</v>
-      </c>
-      <c r="C132" s="2" t="s">
-        <v>244</v>
       </c>
       <c r="D132" s="2" t="s">
         <v>26</v>
@@ -10139,10 +10204,10 @@
         <v>14.5</v>
       </c>
       <c r="H132" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="I132" s="2" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="J132" s="2">
         <v>1</v>
@@ -10151,31 +10216,31 @@
         <v>1</v>
       </c>
       <c r="L132" s="4">
-        <v>46024</v>
+        <v>45896</v>
       </c>
       <c r="N132" s="4">
-        <v>46044</v>
+        <v>45897</v>
       </c>
       <c r="O132" s="4">
-        <v>46044</v>
+        <v>45897</v>
       </c>
       <c r="P132" s="4">
-        <v>46045</v>
+        <v>45897</v>
       </c>
       <c r="Q132" s="4">
-        <v>46052</v>
+        <v>45903</v>
       </c>
       <c r="R132" s="4">
-        <v>46055</v>
+        <v>45905</v>
       </c>
       <c r="S132" s="4">
-        <v>46058</v>
+        <v>45908</v>
       </c>
       <c r="T132" s="4">
-        <v>46058</v>
+        <v>45908</v>
       </c>
       <c r="V132" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="W132" s="2" t="s">
         <v>29</v>
@@ -10190,15 +10255,15 @@
         <v>46112</v>
       </c>
     </row>
-    <row r="133" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A133" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="B133" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="B133" s="2" t="s">
+      <c r="C133" s="2" t="s">
         <v>243</v>
-      </c>
-      <c r="C133" s="2" t="s">
-        <v>244</v>
       </c>
       <c r="D133" s="2" t="s">
         <v>26</v>
@@ -10213,10 +10278,10 @@
         <v>14.5</v>
       </c>
       <c r="H133" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="I133" s="2" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="J133" s="2">
         <v>1</v>
@@ -10225,31 +10290,31 @@
         <v>1</v>
       </c>
       <c r="L133" s="4">
-        <v>46024</v>
+        <v>45944</v>
       </c>
       <c r="N133" s="4">
-        <v>46044</v>
+        <v>45945</v>
       </c>
       <c r="O133" s="4">
-        <v>46044</v>
+        <v>45947</v>
       </c>
       <c r="P133" s="4">
-        <v>46045</v>
+        <v>45950</v>
       </c>
       <c r="Q133" s="4">
-        <v>46052</v>
+        <v>45954</v>
       </c>
       <c r="R133" s="4">
-        <v>46055</v>
+        <v>45957</v>
       </c>
       <c r="S133" s="4">
-        <v>46058</v>
+        <v>45958</v>
       </c>
       <c r="T133" s="4">
-        <v>46058</v>
+        <v>45958</v>
       </c>
       <c r="V133" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="W133" s="2" t="s">
         <v>29</v>
@@ -10266,31 +10331,31 @@
     </row>
     <row r="134" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A134" s="2" t="s">
-        <v>266</v>
+        <v>241</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>267</v>
+        <v>242</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>268</v>
+        <v>243</v>
       </c>
       <c r="D134" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>269</v>
+        <v>32</v>
       </c>
       <c r="F134" s="3">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="G134" s="7">
         <v>14.5</v>
       </c>
       <c r="H134" s="2" t="s">
-        <v>132</v>
+        <v>244</v>
       </c>
       <c r="I134" s="2" t="s">
-        <v>263</v>
+        <v>248</v>
       </c>
       <c r="J134" s="2">
         <v>1</v>
@@ -10299,63 +10364,72 @@
         <v>1</v>
       </c>
       <c r="L134" s="4">
-        <v>46104</v>
+        <v>45944</v>
       </c>
       <c r="N134" s="4">
-        <v>46105</v>
+        <v>45945</v>
       </c>
       <c r="O134" s="4">
-        <v>46110</v>
+        <v>45947</v>
       </c>
       <c r="P134" s="4">
-        <v>46111</v>
+        <v>45950</v>
       </c>
       <c r="Q134" s="4">
-        <v>46112</v>
+        <v>45954</v>
+      </c>
+      <c r="R134" s="4">
+        <v>45957</v>
+      </c>
+      <c r="S134" s="4">
+        <v>45958</v>
       </c>
       <c r="T134" s="4">
-        <v>46115</v>
+        <v>45958</v>
       </c>
       <c r="V134" s="2" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="W134" s="2" t="s">
         <v>29</v>
       </c>
       <c r="X134" s="2" t="s">
-        <v>137</v>
+        <v>53</v>
       </c>
       <c r="Y134" s="2" t="s">
-        <v>142</v>
+        <v>33</v>
+      </c>
+      <c r="Z134" s="4">
+        <v>46112</v>
       </c>
     </row>
     <row r="135" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A135" s="2" t="s">
-        <v>266</v>
+        <v>241</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>267</v>
+        <v>242</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>268</v>
+        <v>243</v>
       </c>
       <c r="D135" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>269</v>
+        <v>32</v>
       </c>
       <c r="F135" s="3">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="G135" s="7">
         <v>14.5</v>
       </c>
       <c r="H135" s="2" t="s">
-        <v>132</v>
+        <v>244</v>
       </c>
       <c r="I135" s="2" t="s">
-        <v>264</v>
+        <v>249</v>
       </c>
       <c r="J135" s="2">
         <v>1</v>
@@ -10364,63 +10438,72 @@
         <v>1</v>
       </c>
       <c r="L135" s="4">
-        <v>46104</v>
+        <v>46024</v>
       </c>
       <c r="N135" s="4">
-        <v>46105</v>
+        <v>46044</v>
       </c>
       <c r="O135" s="4">
-        <v>46110</v>
+        <v>46044</v>
       </c>
       <c r="P135" s="4">
-        <v>46111</v>
+        <v>46045</v>
       </c>
       <c r="Q135" s="4">
-        <v>46112</v>
+        <v>46052</v>
+      </c>
+      <c r="R135" s="4">
+        <v>46055</v>
+      </c>
+      <c r="S135" s="4">
+        <v>46058</v>
       </c>
       <c r="T135" s="4">
-        <v>46115</v>
+        <v>46058</v>
       </c>
       <c r="V135" s="2" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="W135" s="2" t="s">
         <v>29</v>
       </c>
       <c r="X135" s="2" t="s">
-        <v>137</v>
+        <v>53</v>
       </c>
       <c r="Y135" s="2" t="s">
-        <v>142</v>
+        <v>33</v>
+      </c>
+      <c r="Z135" s="4">
+        <v>46112</v>
       </c>
     </row>
     <row r="136" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A136" s="2" t="s">
-        <v>266</v>
+        <v>241</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>267</v>
+        <v>242</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>268</v>
+        <v>243</v>
       </c>
       <c r="D136" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>269</v>
+        <v>32</v>
       </c>
       <c r="F136" s="3">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="G136" s="7">
         <v>14.5</v>
       </c>
       <c r="H136" s="2" t="s">
-        <v>132</v>
+        <v>244</v>
       </c>
       <c r="I136" s="2" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
       <c r="J136" s="2">
         <v>1</v>
@@ -10429,163 +10512,379 @@
         <v>1</v>
       </c>
       <c r="L136" s="4">
-        <v>46104</v>
+        <v>46024</v>
       </c>
       <c r="N136" s="4">
-        <v>46105</v>
+        <v>46044</v>
       </c>
       <c r="O136" s="4">
-        <v>46110</v>
+        <v>46044</v>
       </c>
       <c r="P136" s="4">
-        <v>46111</v>
+        <v>46045</v>
       </c>
       <c r="Q136" s="4">
-        <v>46112</v>
+        <v>46052</v>
+      </c>
+      <c r="R136" s="4">
+        <v>46055</v>
+      </c>
+      <c r="S136" s="4">
+        <v>46058</v>
       </c>
       <c r="T136" s="4">
-        <v>46115</v>
+        <v>46058</v>
       </c>
       <c r="V136" s="2" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="W136" s="2" t="s">
         <v>29</v>
       </c>
       <c r="X136" s="2" t="s">
-        <v>137</v>
+        <v>53</v>
       </c>
       <c r="Y136" s="2" t="s">
-        <v>142</v>
+        <v>33</v>
+      </c>
+      <c r="Z136" s="4">
+        <v>46112</v>
+      </c>
+    </row>
+    <row r="137" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A137" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="B137" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="C137" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="D137" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E137" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="F137" s="3">
+        <v>0.45</v>
+      </c>
+      <c r="G137" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="H137" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="I137" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="J137" s="2">
+        <v>1</v>
+      </c>
+      <c r="K137" s="2">
+        <v>1</v>
+      </c>
+      <c r="L137" s="4">
+        <v>46104</v>
+      </c>
+      <c r="N137" s="4">
+        <v>46105</v>
+      </c>
+      <c r="O137" s="4">
+        <v>46110</v>
+      </c>
+      <c r="P137" s="4">
+        <v>46111</v>
+      </c>
+      <c r="Q137" s="4">
+        <v>46112</v>
+      </c>
+      <c r="R137" s="4">
+        <v>46115</v>
+      </c>
+      <c r="S137" s="4">
+        <v>46118</v>
+      </c>
+      <c r="T137" s="4">
+        <v>46118</v>
+      </c>
+      <c r="V137" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="W137" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="X137" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y137" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="138" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A138" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="B138" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="C138" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="D138" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E138" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="F138" s="3">
+        <v>0.45</v>
+      </c>
+      <c r="G138" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="H138" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="I138" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="J138" s="2">
+        <v>1</v>
+      </c>
+      <c r="K138" s="2">
+        <v>1</v>
+      </c>
+      <c r="L138" s="4">
+        <v>46104</v>
+      </c>
+      <c r="N138" s="4">
+        <v>46105</v>
+      </c>
+      <c r="O138" s="4">
+        <v>46110</v>
+      </c>
+      <c r="P138" s="4">
+        <v>46111</v>
+      </c>
+      <c r="Q138" s="4">
+        <v>46112</v>
+      </c>
+      <c r="R138" s="4">
+        <v>46115</v>
+      </c>
+      <c r="S138" s="4">
+        <v>46118</v>
+      </c>
+      <c r="T138" s="4">
+        <v>46118</v>
+      </c>
+      <c r="V138" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="W138" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="X138" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y138" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="139" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A139" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="B139" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="C139" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="D139" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E139" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="F139" s="3">
+        <v>0.45</v>
+      </c>
+      <c r="G139" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="H139" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="I139" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="J139" s="2">
+        <v>1</v>
+      </c>
+      <c r="K139" s="2">
+        <v>1</v>
+      </c>
+      <c r="L139" s="4">
+        <v>46104</v>
+      </c>
+      <c r="N139" s="4">
+        <v>46105</v>
+      </c>
+      <c r="O139" s="4">
+        <v>46110</v>
+      </c>
+      <c r="P139" s="4">
+        <v>46111</v>
+      </c>
+      <c r="Q139" s="4">
+        <v>46112</v>
+      </c>
+      <c r="R139" s="4">
+        <v>46115</v>
+      </c>
+      <c r="S139" s="4">
+        <v>46118</v>
+      </c>
+      <c r="T139" s="4">
+        <v>46118</v>
+      </c>
+      <c r="V139" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="W139" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="X139" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y139" s="2" t="s">
+        <v>141</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="V1:V136">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="정세희"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:AB139"/>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="I61:I68">
+  <conditionalFormatting sqref="I65:I72">
     <cfRule type="expression" dxfId="23" priority="6" stopIfTrue="1">
-      <formula>$E3103:$E1048572="sub"</formula>
+      <formula>$E3107:$E1048576="sub"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I58:I60">
-    <cfRule type="expression" dxfId="22" priority="12" stopIfTrue="1">
-      <formula>$E3108:$E1="sub"</formula>
+  <conditionalFormatting sqref="I81">
+    <cfRule type="expression" dxfId="22" priority="73" stopIfTrue="1">
+      <formula>$E11:$E3141="sub"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I77">
-    <cfRule type="expression" dxfId="21" priority="73" stopIfTrue="1">
-      <formula>$E11:$E3138="sub"</formula>
+  <conditionalFormatting sqref="I96">
+    <cfRule type="expression" dxfId="21" priority="96" stopIfTrue="1">
+      <formula>$E14:$E3144="sub"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I95">
+    <cfRule type="expression" dxfId="20" priority="102" stopIfTrue="1">
+      <formula>$E14:$E3144="sub"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I94">
+    <cfRule type="expression" dxfId="19" priority="108" stopIfTrue="1">
+      <formula>$E14:$E3144="sub"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I93">
+    <cfRule type="expression" dxfId="18" priority="114" stopIfTrue="1">
+      <formula>$E14:$E3144="sub"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I92">
-    <cfRule type="expression" dxfId="20" priority="96" stopIfTrue="1">
-      <formula>$E14:$E3141="sub"</formula>
+    <cfRule type="expression" dxfId="17" priority="120" stopIfTrue="1">
+      <formula>$E14:$E3144="sub"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I91">
-    <cfRule type="expression" dxfId="19" priority="102" stopIfTrue="1">
-      <formula>$E14:$E3141="sub"</formula>
+    <cfRule type="expression" dxfId="16" priority="126" stopIfTrue="1">
+      <formula>$E14:$E3144="sub"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I103">
+    <cfRule type="expression" dxfId="15" priority="150" stopIfTrue="1">
+      <formula>$E15:$E3145="sub"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I102">
+    <cfRule type="expression" dxfId="14" priority="157" stopIfTrue="1">
+      <formula>$E15:$E3145="sub"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I101">
+    <cfRule type="expression" dxfId="13" priority="164" stopIfTrue="1">
+      <formula>$E15:$E3145="sub"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I100">
+    <cfRule type="expression" dxfId="12" priority="171" stopIfTrue="1">
+      <formula>$E15:$E3145="sub"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I99">
+    <cfRule type="expression" dxfId="11" priority="178" stopIfTrue="1">
+      <formula>$E15:$E3145="sub"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I82 I80">
+    <cfRule type="expression" dxfId="10" priority="1" stopIfTrue="1">
+      <formula>$E11:$E3142="sub"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I90">
-    <cfRule type="expression" dxfId="18" priority="108" stopIfTrue="1">
-      <formula>$E14:$E3141="sub"</formula>
+    <cfRule type="expression" dxfId="9" priority="282" stopIfTrue="1">
+      <formula>$E14:$E3144="sub"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I89">
-    <cfRule type="expression" dxfId="17" priority="114" stopIfTrue="1">
-      <formula>$E14:$E3141="sub"</formula>
+  <conditionalFormatting sqref="I79">
+    <cfRule type="expression" dxfId="8" priority="294" stopIfTrue="1">
+      <formula>$E8:$E3141="sub"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I88">
-    <cfRule type="expression" dxfId="16" priority="120" stopIfTrue="1">
-      <formula>$E14:$E3141="sub"</formula>
+  <conditionalFormatting sqref="I107">
+    <cfRule type="expression" dxfId="7" priority="360" stopIfTrue="1">
+      <formula>$E17:$E3147="sub"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I87">
-    <cfRule type="expression" dxfId="15" priority="126" stopIfTrue="1">
-      <formula>$E14:$E3141="sub"</formula>
+  <conditionalFormatting sqref="I104:I106">
+    <cfRule type="expression" dxfId="6" priority="387" stopIfTrue="1">
+      <formula>$E15:$E3145="sub"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I99">
-    <cfRule type="expression" dxfId="14" priority="150" stopIfTrue="1">
-      <formula>$E15:$E3142="sub"</formula>
+  <conditionalFormatting sqref="I62:I64">
+    <cfRule type="expression" dxfId="5" priority="388" stopIfTrue="1">
+      <formula>$E1:$E3111="sub"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I98">
-    <cfRule type="expression" dxfId="13" priority="157" stopIfTrue="1">
-      <formula>$E15:$E3142="sub"</formula>
+  <conditionalFormatting sqref="I83:I85">
+    <cfRule type="expression" dxfId="4" priority="389" stopIfTrue="1">
+      <formula>$E12:$E3142="sub"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I97">
-    <cfRule type="expression" dxfId="12" priority="164" stopIfTrue="1">
-      <formula>$E15:$E3142="sub"</formula>
+  <conditionalFormatting sqref="I86:I89">
+    <cfRule type="expression" dxfId="3" priority="390" stopIfTrue="1">
+      <formula>$E12:$E3142="sub"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I96">
-    <cfRule type="expression" dxfId="11" priority="171" stopIfTrue="1">
-      <formula>$E15:$E3142="sub"</formula>
+  <conditionalFormatting sqref="I97:I98">
+    <cfRule type="expression" dxfId="2" priority="391" stopIfTrue="1">
+      <formula>$E14:$E3144="sub"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I95">
-    <cfRule type="expression" dxfId="10" priority="178" stopIfTrue="1">
-      <formula>$E15:$E3142="sub"</formula>
+  <conditionalFormatting sqref="I74:I78">
+    <cfRule type="expression" dxfId="1" priority="392" stopIfTrue="1">
+      <formula>$E2:$E3135="sub"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I103">
-    <cfRule type="expression" dxfId="9" priority="214" stopIfTrue="1">
-      <formula>$E17:$E3144="sub"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I78 I76">
-    <cfRule type="expression" dxfId="8" priority="1" stopIfTrue="1">
-      <formula>$E11:$E3139="sub"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I86">
-    <cfRule type="expression" dxfId="7" priority="282" stopIfTrue="1">
-      <formula>$E14:$E3141="sub"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I79:I81">
-    <cfRule type="expression" dxfId="6" priority="287" stopIfTrue="1">
-      <formula>$E12:$E3139="sub"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I82:I85">
-    <cfRule type="expression" dxfId="5" priority="289" stopIfTrue="1">
-      <formula>$E12:$E3139="sub"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I100:I102">
-    <cfRule type="expression" dxfId="4" priority="291" stopIfTrue="1">
-      <formula>$E15:$E3142="sub"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I93:I94">
-    <cfRule type="expression" dxfId="3" priority="292" stopIfTrue="1">
-      <formula>$E14:$E3141="sub"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I75">
-    <cfRule type="expression" dxfId="2" priority="294" stopIfTrue="1">
-      <formula>$E8:$E3138="sub"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I70:I74">
-    <cfRule type="expression" dxfId="1" priority="298" stopIfTrue="1">
-      <formula>$E2:$E3132="sub"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I69">
-    <cfRule type="expression" dxfId="0" priority="299" stopIfTrue="1">
-      <formula>$E3130:$E1048576="sub"</formula>
+  <conditionalFormatting sqref="I73">
+    <cfRule type="expression" dxfId="0" priority="393" stopIfTrue="1">
+      <formula>$E3133:$E1048576="sub"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10597,55 +10896,55 @@
           <x14:formula1>
             <xm:f>Sheet2!$F$2:$F$4</xm:f>
           </x14:formula1>
-          <xm:sqref>W45:W1048576 Y45 W2:W43</xm:sqref>
+          <xm:sqref>Y46:Y47 W46:W1048576 W2:W44</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>Sheet2!$G$2:$G$5</xm:f>
           </x14:formula1>
-          <xm:sqref>X45:X1048576 X2:X43</xm:sqref>
+          <xm:sqref>X2:X44 X46:X1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>Sheet2!$E$2:$E$4</xm:f>
           </x14:formula1>
-          <xm:sqref>H45:H1048576 H2:H43</xm:sqref>
+          <xm:sqref>H46:H1048576 H2:H44</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>Sheet2!$D$2:$D$5</xm:f>
           </x14:formula1>
-          <xm:sqref>G45:G1048576 G2:G43</xm:sqref>
+          <xm:sqref>G46:G1048576 G2:G44</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>Sheet2!$C$2:$C$5</xm:f>
           </x14:formula1>
-          <xm:sqref>F45:F1048576 F2:F43</xm:sqref>
+          <xm:sqref>F46:F1048576 F2:F44</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>Sheet2!$B$2:$B$3</xm:f>
           </x14:formula1>
-          <xm:sqref>E45:E1048576 E2:E43</xm:sqref>
+          <xm:sqref>E46:E1048576 E2:E44</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>Sheet2!$A$2:$A$4</xm:f>
           </x14:formula1>
-          <xm:sqref>D45:D1048576 D2:D43</xm:sqref>
+          <xm:sqref>D46:D1048576 D2:D44</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'[복사본 sample-list.xlsx]Sheet2'!#REF!</xm:f>
           </x14:formula1>
-          <xm:sqref>D44:H44 W44:X44</xm:sqref>
+          <xm:sqref>D45:H45 W45:X45</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>Sheet2!$H$2:$H$7</xm:f>
           </x14:formula1>
-          <xm:sqref>Y2:Y44 Y46:Y1048576</xm:sqref>
+          <xm:sqref>Y48:Y1048576 Y2:Y45</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -10785,7 +11084,7 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="H7" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
   </sheetData>

--- a/sample-list.xlsx
+++ b/sample-list.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13965"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="17565"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1565" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1585" uniqueCount="280">
   <si>
     <t>국가</t>
   </si>
@@ -1119,6 +1119,30 @@
   </si>
   <si>
     <t>류미리</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>일본</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ACE</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>aisei</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PS水光</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>김소연</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>김소연</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1752,7 +1776,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AB139"/>
+  <dimension ref="A1:AB141"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.25" style="2" customWidth="1"/>
@@ -9373,6 +9397,9 @@
       <c r="P117" s="4">
         <v>46111</v>
       </c>
+      <c r="T117" s="4">
+        <v>46126</v>
+      </c>
       <c r="V117" s="2" t="s">
         <v>197</v>
       </c>
@@ -9430,6 +9457,9 @@
       <c r="O118" s="4">
         <v>46112</v>
       </c>
+      <c r="T118" s="4">
+        <v>46126</v>
+      </c>
       <c r="V118" s="2" t="s">
         <v>197</v>
       </c>
@@ -9490,6 +9520,9 @@
       <c r="P119" s="4">
         <v>46111</v>
       </c>
+      <c r="T119" s="4">
+        <v>46126</v>
+      </c>
       <c r="V119" s="2" t="s">
         <v>197</v>
       </c>
@@ -9870,6 +9903,9 @@
       <c r="P126" s="4">
         <v>46116</v>
       </c>
+      <c r="T126" s="4">
+        <v>46126</v>
+      </c>
       <c r="V126" s="2" t="s">
         <v>147</v>
       </c>
@@ -9926,6 +9962,9 @@
       <c r="P127" s="4">
         <v>46116</v>
       </c>
+      <c r="T127" s="4">
+        <v>46126</v>
+      </c>
       <c r="V127" s="2" t="s">
         <v>147</v>
       </c>
@@ -9982,6 +10021,9 @@
       <c r="P128" s="4">
         <v>46116</v>
       </c>
+      <c r="T128" s="4">
+        <v>46126</v>
+      </c>
       <c r="V128" s="2" t="s">
         <v>147</v>
       </c>
@@ -10038,6 +10080,9 @@
       <c r="P129" s="4">
         <v>46116</v>
       </c>
+      <c r="T129" s="4">
+        <v>46126</v>
+      </c>
       <c r="V129" s="2" t="s">
         <v>147</v>
       </c>
@@ -10094,6 +10139,9 @@
       <c r="P130" s="4">
         <v>46116</v>
       </c>
+      <c r="T130" s="4">
+        <v>46126</v>
+      </c>
       <c r="V130" s="2" t="s">
         <v>147</v>
       </c>
@@ -10761,6 +10809,124 @@
         <v>53</v>
       </c>
       <c r="Y139" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="140" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A140" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="B140" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C140" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D140" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E140" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F140" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G140" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="H140" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I140" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="J140" s="2">
+        <v>1</v>
+      </c>
+      <c r="K140" s="2">
+        <v>1</v>
+      </c>
+      <c r="L140" s="4">
+        <v>46111</v>
+      </c>
+      <c r="N140" s="4">
+        <v>46111</v>
+      </c>
+      <c r="P140" s="4">
+        <v>46116</v>
+      </c>
+      <c r="T140" s="4">
+        <v>46126</v>
+      </c>
+      <c r="V140" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="W140" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X140" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="Y140" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="141" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A141" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="B141" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C141" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D141" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E141" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F141" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G141" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="H141" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I141" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="J141" s="2">
+        <v>1</v>
+      </c>
+      <c r="K141" s="2">
+        <v>1</v>
+      </c>
+      <c r="L141" s="4">
+        <v>46111</v>
+      </c>
+      <c r="N141" s="4">
+        <v>46111</v>
+      </c>
+      <c r="P141" s="4">
+        <v>46116</v>
+      </c>
+      <c r="T141" s="4">
+        <v>46126</v>
+      </c>
+      <c r="V141" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="W141" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X141" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="Y141" s="2" t="s">
         <v>141</v>
       </c>
     </row>
@@ -10908,31 +11074,31 @@
           <x14:formula1>
             <xm:f>Sheet2!$E$2:$E$4</xm:f>
           </x14:formula1>
-          <xm:sqref>H46:H1048576 H2:H44</xm:sqref>
+          <xm:sqref>H2:H44 H46:H1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>Sheet2!$D$2:$D$5</xm:f>
           </x14:formula1>
-          <xm:sqref>G46:G1048576 G2:G44</xm:sqref>
+          <xm:sqref>G2:G44 G46:G1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>Sheet2!$C$2:$C$5</xm:f>
           </x14:formula1>
-          <xm:sqref>F46:F1048576 F2:F44</xm:sqref>
+          <xm:sqref>F2:F44 F46:F1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>Sheet2!$B$2:$B$3</xm:f>
           </x14:formula1>
-          <xm:sqref>E46:E1048576 E2:E44</xm:sqref>
+          <xm:sqref>E2:E44 E46:E1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>Sheet2!$A$2:$A$4</xm:f>
           </x14:formula1>
-          <xm:sqref>D46:D1048576 D2:D44</xm:sqref>
+          <xm:sqref>D2:D44 D46:D1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>

--- a/sample-list.xlsx
+++ b/sample-list.xlsx
@@ -19,14 +19,14 @@
     <externalReference r:id="rId3"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$AB$139</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$AB$141</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1585" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1598" uniqueCount="284">
   <si>
     <t>국가</t>
   </si>
@@ -734,7 +734,336 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Cofancy 流心泡芙</t>
+    <t>ML1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ML2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ML3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>류미리</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> Winsome Brown 1D -0.75</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Winsome brown 1M -0.75</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Winsome brown 1M -1.75</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Winsome brown 1M -3.00</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Winsome brown 1M -3.50</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Winsome brown 1M -4.00</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Winsome brown 1M -4.50</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Winsome brown 1M -5.50</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Winsome brown 1M -5.75</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mystical Black 1D -2.00</t>
+  </si>
+  <si>
+    <t>Mystical Black 1D -2.25</t>
+  </si>
+  <si>
+    <t>Mystical Black 1D -3.25</t>
+  </si>
+  <si>
+    <t>Mystical Black 1D -3.5</t>
+  </si>
+  <si>
+    <t>Mystical Black 1D -4.25</t>
+  </si>
+  <si>
+    <t>Mystical Black 1D -5.00</t>
+  </si>
+  <si>
+    <t>Mystical Black 1D -5.25</t>
+  </si>
+  <si>
+    <t>Mystical Black 1D -6.00</t>
+  </si>
+  <si>
+    <t>Shimmering Gray 1D -2.00</t>
+  </si>
+  <si>
+    <t>Shimmering Gray 1D -2.25</t>
+  </si>
+  <si>
+    <t>Shimmering Gray 1D -3.00</t>
+  </si>
+  <si>
+    <t>Shimmering Gray 1D -3.25</t>
+  </si>
+  <si>
+    <t>Shimmering Gray 1D -3.50</t>
+  </si>
+  <si>
+    <t>Shimmering Gray 1D -4.25</t>
+  </si>
+  <si>
+    <t>Shimmering Gray 1D -5.25</t>
+  </si>
+  <si>
+    <t>Shimmering Gray 1D -7.50</t>
+  </si>
+  <si>
+    <t>류미리</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Brilliant Brown 1M -3.00</t>
+  </si>
+  <si>
+    <t>Misty Grey 1M -3.00</t>
+  </si>
+  <si>
+    <t>임수빈</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SH40</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SH41</t>
+  </si>
+  <si>
+    <t>SH42</t>
+  </si>
+  <si>
+    <t>SH43</t>
+  </si>
+  <si>
+    <t>SH44</t>
+  </si>
+  <si>
+    <t>SH45</t>
+  </si>
+  <si>
+    <t>류미리</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SN-I1</t>
+  </si>
+  <si>
+    <t>SN-I2</t>
+  </si>
+  <si>
+    <t>SN-I3</t>
+  </si>
+  <si>
+    <t>SN-I4</t>
+  </si>
+  <si>
+    <t>SN-I5</t>
+  </si>
+  <si>
+    <t>진행중</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>진행중</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">중동 </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sky Optical</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>이철은</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>액상</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Green 2-C</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hazel 2-C</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hazel 1-C</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Gray 3-C</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Brown 4-C</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Brown 3-C </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>FRP</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Winsome brown 1M -2.00</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Winsome brown 1M -2.25</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Winsome brown 1M -3.25</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Winsome brown 1M -4.25</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Winsome brown 1M -5.00</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Winsome brown 1M -5.25</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Winsome brown 1M -6.00</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Winsome brown 1M -7.50</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Beige Glow</t>
+  </si>
+  <si>
+    <t>Orange Glow</t>
+  </si>
+  <si>
+    <t>Purple Glow</t>
+  </si>
+  <si>
+    <t>중국</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Lemonade</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>임건훈</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1D</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>S27</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>임수빈</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>S25C</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>제안렌즈</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>태국</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>류미리</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>류미리</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>일본</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ACE</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>aisei</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PS水光</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>김소연</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>김소연</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>C관</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>C관</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>제안렌즈</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>제안렌즈</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cofancy 流心泡芙/Molten  Puff</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -760,28 +1089,12 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>糖</t>
+      <t>糖/Gummy Mini</t>
     </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Cofancy 月光奶油</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>Cofancy 纯</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>榛小狗</t>
-    </r>
+    <t>Cofancy 月光奶油Luna Cream</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -828,321 +1141,35 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>果</t>
+      <t>果/Silver Bagel</t>
     </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>ML1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ML2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ML3</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>류미리</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> Winsome Brown 1D -0.75</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Winsome brown 1M -0.75</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Winsome brown 1M -1.75</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Winsome brown 1M -3.00</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Winsome brown 1M -3.50</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Winsome brown 1M -4.00</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Winsome brown 1M -4.50</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Winsome brown 1M -5.50</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Winsome brown 1M -5.75</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Mystical Black 1D -2.00</t>
-  </si>
-  <si>
-    <t>Mystical Black 1D -2.25</t>
-  </si>
-  <si>
-    <t>Mystical Black 1D -3.25</t>
-  </si>
-  <si>
-    <t>Mystical Black 1D -3.5</t>
-  </si>
-  <si>
-    <t>Mystical Black 1D -4.25</t>
-  </si>
-  <si>
-    <t>Mystical Black 1D -5.00</t>
-  </si>
-  <si>
-    <t>Mystical Black 1D -5.25</t>
-  </si>
-  <si>
-    <t>Mystical Black 1D -6.00</t>
-  </si>
-  <si>
-    <t>Shimmering Gray 1D -2.00</t>
-  </si>
-  <si>
-    <t>Shimmering Gray 1D -2.25</t>
-  </si>
-  <si>
-    <t>Shimmering Gray 1D -3.00</t>
-  </si>
-  <si>
-    <t>Shimmering Gray 1D -3.25</t>
-  </si>
-  <si>
-    <t>Shimmering Gray 1D -3.50</t>
-  </si>
-  <si>
-    <t>Shimmering Gray 1D -4.25</t>
-  </si>
-  <si>
-    <t>Shimmering Gray 1D -5.25</t>
-  </si>
-  <si>
-    <t>Shimmering Gray 1D -7.50</t>
-  </si>
-  <si>
-    <t>류미리</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Brilliant Brown 1M -3.00</t>
-  </si>
-  <si>
-    <t>Misty Grey 1M -3.00</t>
-  </si>
-  <si>
-    <t>임수빈</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SH40</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SH41</t>
-  </si>
-  <si>
-    <t>SH42</t>
-  </si>
-  <si>
-    <t>SH43</t>
-  </si>
-  <si>
-    <t>SH44</t>
-  </si>
-  <si>
-    <t>SH45</t>
-  </si>
-  <si>
-    <t>류미리</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SN-I1</t>
-  </si>
-  <si>
-    <t>SN-I2</t>
-  </si>
-  <si>
-    <t>SN-I3</t>
-  </si>
-  <si>
-    <t>SN-I4</t>
-  </si>
-  <si>
-    <t>SN-I5</t>
-  </si>
-  <si>
-    <t>진행중</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>진행중</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">중동 </t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sky Optical</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>이철은</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>액상</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Green 2-C</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Hazel 2-C</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Hazel 1-C</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Gray 3-C</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Brown 4-C</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Brown 3-C </t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>FRP</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Winsome brown 1M -2.00</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Winsome brown 1M -2.25</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Winsome brown 1M -3.25</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Winsome brown 1M -4.25</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Winsome brown 1M -5.00</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Winsome brown 1M -5.25</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Winsome brown 1M -6.00</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Winsome brown 1M -7.50</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Beige Glow</t>
-  </si>
-  <si>
-    <t>Orange Glow</t>
-  </si>
-  <si>
-    <t>Purple Glow</t>
-  </si>
-  <si>
-    <t>중국</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Lemonade</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>임건훈</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1D</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>S27</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>임수빈</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>S25C</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>제안렌즈</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>태국</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>류미리</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>류미리</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>일본</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ACE</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>aisei</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>PS水光</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>김소연</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>김소연</t>
+    <r>
+      <t>Cofancy 纯</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>榛小狗</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">/纯榛小狗 </t>
+    </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1153,7 +1180,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.0_ "/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1195,6 +1222,21 @@
       <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1251,7 +1293,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1290,6 +1332,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2406,7 +2454,7 @@
         <v>45975</v>
       </c>
       <c r="V8" s="2" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="W8" s="2" t="s">
         <v>30</v>
@@ -2450,7 +2498,7 @@
         <v>28</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="J9" s="2">
         <v>1</v>
@@ -2530,7 +2578,7 @@
         <v>28</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="J10" s="2">
         <v>1</v>
@@ -4049,7 +4097,7 @@
         <v>53</v>
       </c>
       <c r="Y30" s="2" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
     </row>
     <row r="31" spans="1:28" x14ac:dyDescent="0.3">
@@ -4114,6 +4162,9 @@
       <c r="X31" s="2" t="s">
         <v>53</v>
       </c>
+      <c r="Y31" s="2" t="s">
+        <v>277</v>
+      </c>
     </row>
     <row r="32" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
@@ -4241,7 +4292,7 @@
         <v>53</v>
       </c>
       <c r="Y33" s="2" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
     </row>
     <row r="34" spans="1:25" x14ac:dyDescent="0.3">
@@ -4306,6 +4357,9 @@
       <c r="X34" s="2" t="s">
         <v>53</v>
       </c>
+      <c r="Y34" s="2" t="s">
+        <v>278</v>
+      </c>
     </row>
     <row r="35" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
@@ -4877,6 +4931,9 @@
       <c r="X42" s="2" t="s">
         <v>53</v>
       </c>
+      <c r="Y42" s="2" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="43" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
@@ -5165,12 +5222,12 @@
         <v>53</v>
       </c>
       <c r="Y46" s="2" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
     </row>
     <row r="47" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>44</v>
@@ -5236,7 +5293,7 @@
         <v>99</v>
       </c>
       <c r="Y47" s="2" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
     </row>
     <row r="48" spans="1:25" x14ac:dyDescent="0.3">
@@ -5264,7 +5321,7 @@
       <c r="H48" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I48" s="2" t="s">
+      <c r="I48" s="14" t="s">
         <v>138</v>
       </c>
       <c r="J48" s="2">
@@ -5285,6 +5342,15 @@
       <c r="Q48" s="4">
         <v>46083</v>
       </c>
+      <c r="R48" s="4">
+        <v>46093</v>
+      </c>
+      <c r="S48" s="4">
+        <v>46094</v>
+      </c>
+      <c r="T48" s="4">
+        <v>46094</v>
+      </c>
       <c r="V48" s="2" t="s">
         <v>52</v>
       </c>
@@ -5292,7 +5358,7 @@
         <v>29</v>
       </c>
       <c r="X48" s="2" t="s">
-        <v>99</v>
+        <v>53</v>
       </c>
       <c r="Y48" s="2" t="s">
         <v>141</v>
@@ -5323,7 +5389,7 @@
       <c r="H49" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I49" s="2" t="s">
+      <c r="I49" s="15" t="s">
         <v>139</v>
       </c>
       <c r="J49" s="2">
@@ -5344,6 +5410,15 @@
       <c r="Q49" s="4">
         <v>46083</v>
       </c>
+      <c r="R49" s="4">
+        <v>46093</v>
+      </c>
+      <c r="S49" s="4">
+        <v>46094</v>
+      </c>
+      <c r="T49" s="4">
+        <v>46094</v>
+      </c>
       <c r="V49" s="2" t="s">
         <v>52</v>
       </c>
@@ -5351,7 +5426,7 @@
         <v>29</v>
       </c>
       <c r="X49" s="2" t="s">
-        <v>99</v>
+        <v>53</v>
       </c>
       <c r="Y49" s="2" t="s">
         <v>141</v>
@@ -5474,7 +5549,7 @@
         <v>46066</v>
       </c>
       <c r="V51" s="2" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="W51" s="2" t="s">
         <v>30</v>
@@ -5541,7 +5616,7 @@
         <v>46066</v>
       </c>
       <c r="V52" s="2" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="W52" s="2" t="s">
         <v>30</v>
@@ -5740,6 +5815,15 @@
       <c r="P55" s="4">
         <v>46087</v>
       </c>
+      <c r="Q55" s="4">
+        <v>46098</v>
+      </c>
+      <c r="R55" s="4">
+        <v>46099</v>
+      </c>
+      <c r="S55" s="4">
+        <v>46100</v>
+      </c>
       <c r="T55" s="4">
         <v>46100</v>
       </c>
@@ -5750,7 +5834,10 @@
         <v>29</v>
       </c>
       <c r="X55" s="2" t="s">
-        <v>99</v>
+        <v>53</v>
+      </c>
+      <c r="Y55" s="2" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="56" spans="1:25" x14ac:dyDescent="0.3">
@@ -5800,6 +5887,15 @@
       <c r="P56" s="4">
         <v>46087</v>
       </c>
+      <c r="Q56" s="4">
+        <v>46098</v>
+      </c>
+      <c r="R56" s="4">
+        <v>46099</v>
+      </c>
+      <c r="S56" s="4">
+        <v>46100</v>
+      </c>
       <c r="T56" s="4">
         <v>46100</v>
       </c>
@@ -5810,7 +5906,10 @@
         <v>29</v>
       </c>
       <c r="X56" s="2" t="s">
-        <v>99</v>
+        <v>53</v>
+      </c>
+      <c r="Y56" s="2" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="57" spans="1:25" x14ac:dyDescent="0.3">
@@ -5860,6 +5959,15 @@
       <c r="P57" s="4">
         <v>46087</v>
       </c>
+      <c r="Q57" s="4">
+        <v>46098</v>
+      </c>
+      <c r="R57" s="4">
+        <v>46099</v>
+      </c>
+      <c r="S57" s="4">
+        <v>46100</v>
+      </c>
       <c r="T57" s="4">
         <v>46100</v>
       </c>
@@ -5870,7 +5978,10 @@
         <v>29</v>
       </c>
       <c r="X57" s="2" t="s">
-        <v>99</v>
+        <v>53</v>
+      </c>
+      <c r="Y57" s="2" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="58" spans="1:25" x14ac:dyDescent="0.3">
@@ -5929,6 +6040,9 @@
       <c r="X58" s="2" t="s">
         <v>136</v>
       </c>
+      <c r="Y58" s="2" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="59" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
@@ -5986,6 +6100,9 @@
       <c r="X59" s="2" t="s">
         <v>136</v>
       </c>
+      <c r="Y59" s="2" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="60" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
@@ -6043,6 +6160,9 @@
       <c r="X60" s="2" t="s">
         <v>136</v>
       </c>
+      <c r="Y60" s="2" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="61" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
@@ -6100,6 +6220,9 @@
       <c r="X61" s="2" t="s">
         <v>136</v>
       </c>
+      <c r="Y61" s="2" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="62" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
@@ -6157,6 +6280,9 @@
       <c r="X62" s="2" t="s">
         <v>136</v>
       </c>
+      <c r="Y62" s="2" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="63" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
@@ -6214,6 +6340,9 @@
       <c r="X63" s="2" t="s">
         <v>136</v>
       </c>
+      <c r="Y63" s="2" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="64" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
@@ -6271,6 +6400,9 @@
       <c r="X64" s="2" t="s">
         <v>136</v>
       </c>
+      <c r="Y64" s="2" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="65" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
@@ -6298,7 +6430,7 @@
         <v>28</v>
       </c>
       <c r="I65" s="11" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="J65" s="2">
         <v>1</v>
@@ -6883,7 +7015,7 @@
         <v>28</v>
       </c>
       <c r="I74" s="11" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="J74" s="2">
         <v>1</v>
@@ -6948,7 +7080,7 @@
         <v>28</v>
       </c>
       <c r="I75" s="11" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="J75" s="2">
         <v>1</v>
@@ -7013,7 +7145,7 @@
         <v>28</v>
       </c>
       <c r="I76" s="11" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="J76" s="2">
         <v>1</v>
@@ -7072,7 +7204,7 @@
         <v>28</v>
       </c>
       <c r="I77" s="11" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="J77" s="2">
         <v>1</v>
@@ -7131,7 +7263,7 @@
         <v>28</v>
       </c>
       <c r="I78" s="11" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="J78" s="2">
         <v>1</v>
@@ -7196,7 +7328,7 @@
         <v>28</v>
       </c>
       <c r="I79" s="11" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="J79" s="2">
         <v>1</v>
@@ -7261,7 +7393,7 @@
         <v>28</v>
       </c>
       <c r="I80" s="11" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="J80" s="2">
         <v>1</v>
@@ -7320,7 +7452,7 @@
         <v>28</v>
       </c>
       <c r="I81" s="11" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="J81" s="2">
         <v>1</v>
@@ -7385,7 +7517,7 @@
         <v>28</v>
       </c>
       <c r="I82" s="11" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="J82" s="2">
         <v>1</v>
@@ -7444,7 +7576,7 @@
         <v>28</v>
       </c>
       <c r="I83" s="11" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="J83" s="2">
         <v>1</v>
@@ -7509,7 +7641,7 @@
         <v>28</v>
       </c>
       <c r="I84" s="11" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="J84" s="2">
         <v>1</v>
@@ -7568,7 +7700,7 @@
         <v>28</v>
       </c>
       <c r="I85" s="11" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="J85" s="2">
         <v>1</v>
@@ -7627,7 +7759,7 @@
         <v>28</v>
       </c>
       <c r="I86" s="11" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="J86" s="2">
         <v>1</v>
@@ -7692,7 +7824,7 @@
         <v>28</v>
       </c>
       <c r="I87" s="11" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="J87" s="2">
         <v>1</v>
@@ -7757,7 +7889,7 @@
         <v>28</v>
       </c>
       <c r="I88" s="11" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="J88" s="2">
         <v>1</v>
@@ -7816,7 +7948,7 @@
         <v>28</v>
       </c>
       <c r="I89" s="11" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="J89" s="2">
         <v>1</v>
@@ -7875,7 +8007,7 @@
         <v>28</v>
       </c>
       <c r="I90" s="11" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="J90" s="2">
         <v>1</v>
@@ -7925,7 +8057,7 @@
         <v>28</v>
       </c>
       <c r="I91" s="11" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="J91" s="2">
         <v>1</v>
@@ -7975,7 +8107,7 @@
         <v>28</v>
       </c>
       <c r="I92" s="11" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="J92" s="2">
         <v>1</v>
@@ -8025,7 +8157,7 @@
         <v>28</v>
       </c>
       <c r="I93" s="11" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="J93" s="2">
         <v>1</v>
@@ -8075,7 +8207,7 @@
         <v>28</v>
       </c>
       <c r="I94" s="11" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="J94" s="2">
         <v>1</v>
@@ -8125,7 +8257,7 @@
         <v>28</v>
       </c>
       <c r="I95" s="11" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="J95" s="2">
         <v>1</v>
@@ -8175,7 +8307,7 @@
         <v>28</v>
       </c>
       <c r="I96" s="11" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="J96" s="2">
         <v>1</v>
@@ -8225,7 +8357,7 @@
         <v>28</v>
       </c>
       <c r="I97" s="11" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="J97" s="2">
         <v>1</v>
@@ -8275,7 +8407,7 @@
         <v>28</v>
       </c>
       <c r="I98" s="11" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="J98" s="2">
         <v>1</v>
@@ -8293,7 +8425,7 @@
         <v>46142</v>
       </c>
       <c r="V98" s="2" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="W98" s="2" t="s">
         <v>30</v>
@@ -8331,7 +8463,7 @@
         <v>28</v>
       </c>
       <c r="I99" s="11" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="J99" s="2">
         <v>1</v>
@@ -8349,7 +8481,7 @@
         <v>46142</v>
       </c>
       <c r="V99" s="2" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="W99" s="2" t="s">
         <v>30</v>
@@ -8387,7 +8519,7 @@
         <v>28</v>
       </c>
       <c r="I100" s="11" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="J100" s="2">
         <v>1</v>
@@ -8405,7 +8537,7 @@
         <v>46142</v>
       </c>
       <c r="V100" s="2" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="W100" s="2" t="s">
         <v>30</v>
@@ -8443,7 +8575,7 @@
         <v>28</v>
       </c>
       <c r="I101" s="11" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="J101" s="2">
         <v>1</v>
@@ -8461,7 +8593,7 @@
         <v>46142</v>
       </c>
       <c r="V101" s="2" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="W101" s="2" t="s">
         <v>30</v>
@@ -8499,7 +8631,7 @@
         <v>28</v>
       </c>
       <c r="I102" s="11" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="J102" s="2">
         <v>1</v>
@@ -8517,7 +8649,7 @@
         <v>46142</v>
       </c>
       <c r="V102" s="2" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="W102" s="2" t="s">
         <v>30</v>
@@ -8555,7 +8687,7 @@
         <v>28</v>
       </c>
       <c r="I103" s="11" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="J103" s="2">
         <v>1</v>
@@ -8573,7 +8705,7 @@
         <v>46142</v>
       </c>
       <c r="V103" s="2" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="W103" s="2" t="s">
         <v>30</v>
@@ -8611,7 +8743,7 @@
         <v>28</v>
       </c>
       <c r="I104" s="11" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="J104" s="2">
         <v>1</v>
@@ -8629,7 +8761,7 @@
         <v>46142</v>
       </c>
       <c r="V104" s="2" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="W104" s="2" t="s">
         <v>30</v>
@@ -8667,7 +8799,7 @@
         <v>28</v>
       </c>
       <c r="I105" s="11" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="J105" s="2">
         <v>1</v>
@@ -8685,7 +8817,7 @@
         <v>46142</v>
       </c>
       <c r="V105" s="2" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="W105" s="2" t="s">
         <v>30</v>
@@ -8723,7 +8855,7 @@
         <v>28</v>
       </c>
       <c r="I106" s="11" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="J106" s="2">
         <v>1</v>
@@ -8741,7 +8873,7 @@
         <v>46142</v>
       </c>
       <c r="V106" s="2" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="W106" s="2" t="s">
         <v>30</v>
@@ -8779,7 +8911,7 @@
         <v>28</v>
       </c>
       <c r="I107" s="11" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="J107" s="2">
         <v>1</v>
@@ -8797,7 +8929,7 @@
         <v>46142</v>
       </c>
       <c r="V107" s="2" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="W107" s="2" t="s">
         <v>30</v>
@@ -9111,7 +9243,7 @@
         <v>28</v>
       </c>
       <c r="I112" s="2" t="s">
-        <v>189</v>
+        <v>279</v>
       </c>
       <c r="J112" s="2">
         <v>1</v>
@@ -9122,6 +9254,12 @@
       <c r="L112" s="4">
         <v>46094</v>
       </c>
+      <c r="M112" s="4">
+        <v>46094</v>
+      </c>
+      <c r="P112" s="4">
+        <v>46101</v>
+      </c>
       <c r="T112" s="4">
         <v>46117</v>
       </c>
@@ -9129,7 +9267,7 @@
         <v>182</v>
       </c>
       <c r="W112" s="2" t="s">
-        <v>29</v>
+        <v>275</v>
       </c>
       <c r="X112" s="2" t="s">
         <v>99</v>
@@ -9164,7 +9302,7 @@
         <v>28</v>
       </c>
       <c r="I113" s="2" t="s">
-        <v>190</v>
+        <v>280</v>
       </c>
       <c r="J113" s="2">
         <v>1</v>
@@ -9175,6 +9313,12 @@
       <c r="L113" s="4">
         <v>46094</v>
       </c>
+      <c r="M113" s="4">
+        <v>46094</v>
+      </c>
+      <c r="P113" s="4">
+        <v>46101</v>
+      </c>
       <c r="T113" s="4">
         <v>46117</v>
       </c>
@@ -9182,7 +9326,7 @@
         <v>182</v>
       </c>
       <c r="W113" s="2" t="s">
-        <v>29</v>
+        <v>276</v>
       </c>
       <c r="X113" s="2" t="s">
         <v>99</v>
@@ -9217,7 +9361,7 @@
         <v>28</v>
       </c>
       <c r="I114" s="2" t="s">
-        <v>191</v>
+        <v>281</v>
       </c>
       <c r="J114" s="2">
         <v>1</v>
@@ -9228,6 +9372,12 @@
       <c r="L114" s="4">
         <v>46094</v>
       </c>
+      <c r="M114" s="4">
+        <v>46094</v>
+      </c>
+      <c r="P114" s="4">
+        <v>46101</v>
+      </c>
       <c r="T114" s="4">
         <v>46117</v>
       </c>
@@ -9235,7 +9385,7 @@
         <v>183</v>
       </c>
       <c r="W114" s="2" t="s">
-        <v>29</v>
+        <v>276</v>
       </c>
       <c r="X114" s="2" t="s">
         <v>99</v>
@@ -9270,7 +9420,7 @@
         <v>28</v>
       </c>
       <c r="I115" s="2" t="s">
-        <v>193</v>
+        <v>282</v>
       </c>
       <c r="J115" s="2">
         <v>1</v>
@@ -9281,6 +9431,12 @@
       <c r="L115" s="4">
         <v>46094</v>
       </c>
+      <c r="M115" s="4">
+        <v>46094</v>
+      </c>
+      <c r="P115" s="4">
+        <v>46101</v>
+      </c>
       <c r="T115" s="4">
         <v>46117</v>
       </c>
@@ -9288,7 +9444,7 @@
         <v>183</v>
       </c>
       <c r="W115" s="2" t="s">
-        <v>29</v>
+        <v>130</v>
       </c>
       <c r="X115" s="2" t="s">
         <v>99</v>
@@ -9323,7 +9479,7 @@
         <v>28</v>
       </c>
       <c r="I116" s="13" t="s">
-        <v>192</v>
+        <v>283</v>
       </c>
       <c r="J116" s="2">
         <v>1</v>
@@ -9334,6 +9490,12 @@
       <c r="L116" s="4">
         <v>46094</v>
       </c>
+      <c r="M116" s="4">
+        <v>46094</v>
+      </c>
+      <c r="P116" s="4">
+        <v>46101</v>
+      </c>
       <c r="T116" s="4">
         <v>46117</v>
       </c>
@@ -9341,7 +9503,7 @@
         <v>183</v>
       </c>
       <c r="W116" s="2" t="s">
-        <v>29</v>
+        <v>276</v>
       </c>
       <c r="X116" s="2" t="s">
         <v>99</v>
@@ -9376,7 +9538,7 @@
         <v>28</v>
       </c>
       <c r="I117" s="2" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="J117" s="2">
         <v>1</v>
@@ -9401,13 +9563,13 @@
         <v>46126</v>
       </c>
       <c r="V117" s="2" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="W117" s="2" t="s">
         <v>30</v>
       </c>
       <c r="X117" s="2" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="Y117" s="2" t="s">
         <v>58</v>
@@ -9439,7 +9601,7 @@
         <v>28</v>
       </c>
       <c r="I118" s="2" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="J118" s="2">
         <v>1</v>
@@ -9461,7 +9623,7 @@
         <v>46126</v>
       </c>
       <c r="V118" s="2" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="W118" s="2" t="s">
         <v>30</v>
@@ -9499,7 +9661,7 @@
         <v>28</v>
       </c>
       <c r="I119" s="13" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="J119" s="2">
         <v>1</v>
@@ -9524,13 +9686,13 @@
         <v>46126</v>
       </c>
       <c r="V119" s="2" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="W119" s="2" t="s">
         <v>30</v>
       </c>
       <c r="X119" s="2" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="Y119" s="2" t="s">
         <v>58</v>
@@ -9562,7 +9724,7 @@
         <v>28</v>
       </c>
       <c r="I120" s="2" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="J120" s="2">
         <v>1</v>
@@ -9616,7 +9778,7 @@
         <v>28</v>
       </c>
       <c r="I121" s="2" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="J121" s="2">
         <v>1</v>
@@ -9670,7 +9832,7 @@
         <v>28</v>
       </c>
       <c r="I122" s="2" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="J122" s="2">
         <v>1</v>
@@ -9686,7 +9848,7 @@
         <v>46106</v>
       </c>
       <c r="V122" s="2" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="W122" s="2" t="s">
         <v>30</v>
@@ -9724,7 +9886,7 @@
         <v>28</v>
       </c>
       <c r="I123" s="2" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="J123" s="2">
         <v>1</v>
@@ -9778,7 +9940,7 @@
         <v>28</v>
       </c>
       <c r="I124" s="2" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="J124" s="2">
         <v>1</v>
@@ -9832,7 +9994,7 @@
         <v>28</v>
       </c>
       <c r="I125" s="2" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="J125" s="2">
         <v>1</v>
@@ -9886,7 +10048,7 @@
         <v>28</v>
       </c>
       <c r="I126" s="2" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="J126" s="2">
         <v>1</v>
@@ -9945,7 +10107,7 @@
         <v>28</v>
       </c>
       <c r="I127" s="2" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="J127" s="2">
         <v>1</v>
@@ -10004,7 +10166,7 @@
         <v>28</v>
       </c>
       <c r="I128" s="2" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="J128" s="2">
         <v>1</v>
@@ -10063,7 +10225,7 @@
         <v>28</v>
       </c>
       <c r="I129" s="2" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="J129" s="2">
         <v>1</v>
@@ -10122,7 +10284,7 @@
         <v>28</v>
       </c>
       <c r="I130" s="2" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="J130" s="2">
         <v>1</v>
@@ -10157,13 +10319,13 @@
     </row>
     <row r="131" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A131" s="2" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="D131" s="2" t="s">
         <v>26</v>
@@ -10178,10 +10340,10 @@
         <v>14.5</v>
       </c>
       <c r="H131" s="2" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="I131" s="2" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="J131" s="2">
         <v>1</v>
@@ -10231,13 +10393,13 @@
     </row>
     <row r="132" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A132" s="2" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="D132" s="2" t="s">
         <v>26</v>
@@ -10252,10 +10414,10 @@
         <v>14.5</v>
       </c>
       <c r="H132" s="2" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="I132" s="2" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="J132" s="2">
         <v>1</v>
@@ -10305,13 +10467,13 @@
     </row>
     <row r="133" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A133" s="2" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="D133" s="2" t="s">
         <v>26</v>
@@ -10326,10 +10488,10 @@
         <v>14.5</v>
       </c>
       <c r="H133" s="2" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="I133" s="2" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="J133" s="2">
         <v>1</v>
@@ -10379,13 +10541,13 @@
     </row>
     <row r="134" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A134" s="2" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="D134" s="2" t="s">
         <v>26</v>
@@ -10400,10 +10562,10 @@
         <v>14.5</v>
       </c>
       <c r="H134" s="2" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="I134" s="2" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="J134" s="2">
         <v>1</v>
@@ -10453,13 +10615,13 @@
     </row>
     <row r="135" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A135" s="2" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="D135" s="2" t="s">
         <v>26</v>
@@ -10474,10 +10636,10 @@
         <v>14.5</v>
       </c>
       <c r="H135" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="I135" s="2" t="s">
         <v>244</v>
-      </c>
-      <c r="I135" s="2" t="s">
-        <v>249</v>
       </c>
       <c r="J135" s="2">
         <v>1</v>
@@ -10527,13 +10689,13 @@
     </row>
     <row r="136" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A136" s="2" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="D136" s="2" t="s">
         <v>26</v>
@@ -10548,10 +10710,10 @@
         <v>14.5</v>
       </c>
       <c r="H136" s="2" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="I136" s="2" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="J136" s="2">
         <v>1</v>
@@ -10601,19 +10763,19 @@
     </row>
     <row r="137" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A137" s="2" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="D137" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="F137" s="3">
         <v>0.45</v>
@@ -10625,7 +10787,7 @@
         <v>131</v>
       </c>
       <c r="I137" s="2" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="J137" s="2">
         <v>1</v>
@@ -10672,19 +10834,19 @@
     </row>
     <row r="138" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A138" s="2" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="D138" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="F138" s="3">
         <v>0.45</v>
@@ -10696,7 +10858,7 @@
         <v>131</v>
       </c>
       <c r="I138" s="2" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="J138" s="2">
         <v>1</v>
@@ -10743,19 +10905,19 @@
     </row>
     <row r="139" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A139" s="2" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="D139" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="F139" s="3">
         <v>0.45</v>
@@ -10767,7 +10929,7 @@
         <v>131</v>
       </c>
       <c r="I139" s="2" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="J139" s="2">
         <v>1</v>
@@ -10814,10 +10976,10 @@
     </row>
     <row r="140" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A140" s="2" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>84</v>
@@ -10838,7 +11000,7 @@
         <v>28</v>
       </c>
       <c r="I140" s="2" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="J140" s="2">
         <v>1</v>
@@ -10859,7 +11021,7 @@
         <v>46126</v>
       </c>
       <c r="V140" s="2" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="W140" s="2" t="s">
         <v>30</v>
@@ -10873,10 +11035,10 @@
     </row>
     <row r="141" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A141" s="2" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>84</v>
@@ -10897,7 +11059,7 @@
         <v>28</v>
       </c>
       <c r="I141" s="2" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="J141" s="2">
         <v>1</v>
@@ -10918,7 +11080,7 @@
         <v>46126</v>
       </c>
       <c r="V141" s="2" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="W141" s="2" t="s">
         <v>30</v>
@@ -10931,7 +11093,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AB139"/>
+  <autoFilter ref="A1:AB141"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="I65:I72">
     <cfRule type="expression" dxfId="23" priority="6" stopIfTrue="1">

--- a/sample-list.xlsx
+++ b/sample-list.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="17565"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12165"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -17,16 +17,17 @@
   </sheets>
   <externalReferences>
     <externalReference r:id="rId3"/>
+    <externalReference r:id="rId4"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$AB$141</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$AB$156</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1598" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1762" uniqueCount="300">
   <si>
     <t>국가</t>
   </si>
@@ -884,14 +885,6 @@
   </si>
   <si>
     <t>SN-I5</t>
-  </si>
-  <si>
-    <t>진행중</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>진행중</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">중동 </t>
@@ -1170,6 +1163,78 @@
       </rPr>
       <t xml:space="preserve">/纯榛小狗 </t>
     </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>from-eyes</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>윤형낙</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>orange star</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>gray star</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">일본 </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>프롬아이</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>윤형낙</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>glow Brosn (펄+축고정)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Glow Gray (펄+축고정)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Gold Light</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pure Ring</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>대기</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PIA</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PPB</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Unrolla A</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Unrolla B</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>완료</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>진행중</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1293,7 +1358,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1338,6 +1403,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1527,6 +1595,19 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="Sheet2"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -1824,7 +1905,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AB141"/>
+  <dimension ref="A1:AB157"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.25" style="2" customWidth="1"/>
@@ -2454,7 +2535,7 @@
         <v>45975</v>
       </c>
       <c r="V8" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="W8" s="2" t="s">
         <v>30</v>
@@ -2498,7 +2579,7 @@
         <v>28</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="J9" s="2">
         <v>1</v>
@@ -2578,7 +2659,7 @@
         <v>28</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="J10" s="2">
         <v>1</v>
@@ -4020,6 +4101,18 @@
       <c r="P29" s="10">
         <v>46117</v>
       </c>
+      <c r="Q29" s="4">
+        <v>46125</v>
+      </c>
+      <c r="R29" s="4">
+        <v>46126</v>
+      </c>
+      <c r="S29" s="4">
+        <v>46127</v>
+      </c>
+      <c r="T29" s="4">
+        <v>46127</v>
+      </c>
       <c r="V29" s="2" t="s">
         <v>66</v>
       </c>
@@ -4027,7 +4120,7 @@
         <v>29</v>
       </c>
       <c r="X29" s="2" t="s">
-        <v>99</v>
+        <v>298</v>
       </c>
       <c r="Y29" s="2" t="s">
         <v>58</v>
@@ -4097,7 +4190,7 @@
         <v>53</v>
       </c>
       <c r="Y30" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="31" spans="1:28" x14ac:dyDescent="0.3">
@@ -4163,7 +4256,7 @@
         <v>53</v>
       </c>
       <c r="Y31" s="2" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="32" spans="1:28" x14ac:dyDescent="0.3">
@@ -4292,7 +4385,7 @@
         <v>53</v>
       </c>
       <c r="Y33" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="34" spans="1:25" x14ac:dyDescent="0.3">
@@ -4358,7 +4451,7 @@
         <v>53</v>
       </c>
       <c r="Y34" s="2" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="35" spans="1:25" x14ac:dyDescent="0.3">
@@ -4813,40 +4906,19 @@
         <v>28</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="J41" s="2">
         <v>1</v>
       </c>
       <c r="K41" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L41" s="4">
         <v>45868</v>
       </c>
       <c r="M41" s="4">
-        <v>46055</v>
-      </c>
-      <c r="N41" s="4">
-        <v>46056</v>
-      </c>
-      <c r="O41" s="4">
-        <v>46056</v>
-      </c>
-      <c r="P41" s="4">
-        <v>46058</v>
-      </c>
-      <c r="Q41" s="4">
-        <v>46065</v>
-      </c>
-      <c r="R41" s="4">
-        <v>46066</v>
-      </c>
-      <c r="S41" s="4">
-        <v>46066</v>
-      </c>
-      <c r="T41" s="4">
-        <v>46066</v>
+        <v>46122</v>
       </c>
       <c r="V41" s="2" t="s">
         <v>116</v>
@@ -4855,7 +4927,7 @@
         <v>29</v>
       </c>
       <c r="X41" s="2" t="s">
-        <v>53</v>
+        <v>299</v>
       </c>
       <c r="Y41" s="2" t="s">
         <v>58</v>
@@ -4887,7 +4959,7 @@
         <v>28</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J42" s="2">
         <v>1</v>
@@ -4908,7 +4980,7 @@
         <v>46056</v>
       </c>
       <c r="P42" s="4">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="Q42" s="4">
         <v>46065</v>
@@ -4923,7 +4995,7 @@
         <v>46066</v>
       </c>
       <c r="V42" s="2" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="W42" s="2" t="s">
         <v>29</v>
@@ -4961,49 +5033,31 @@
         <v>28</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J43" s="2">
         <v>1</v>
       </c>
       <c r="K43" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L43" s="4">
         <v>45868</v>
       </c>
       <c r="M43" s="4">
-        <v>46055</v>
-      </c>
-      <c r="N43" s="4">
-        <v>46056</v>
-      </c>
-      <c r="O43" s="4">
-        <v>46056</v>
-      </c>
-      <c r="P43" s="4">
-        <v>46058</v>
-      </c>
-      <c r="Q43" s="4">
-        <v>46065</v>
-      </c>
-      <c r="R43" s="4">
-        <v>46066</v>
-      </c>
-      <c r="S43" s="4">
-        <v>46066</v>
-      </c>
-      <c r="T43" s="4">
-        <v>46066</v>
+        <v>46122</v>
       </c>
       <c r="V43" s="2" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="W43" s="2" t="s">
         <v>29</v>
       </c>
       <c r="X43" s="2" t="s">
-        <v>53</v>
+        <v>299</v>
+      </c>
+      <c r="Y43" s="2" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="44" spans="1:25" x14ac:dyDescent="0.3">
@@ -5032,7 +5086,7 @@
         <v>28</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J44" s="2">
         <v>1</v>
@@ -5053,7 +5107,7 @@
         <v>46056</v>
       </c>
       <c r="P44" s="4">
-        <v>46058</v>
+        <v>46057</v>
       </c>
       <c r="Q44" s="4">
         <v>46065</v>
@@ -5068,7 +5122,7 @@
         <v>46066</v>
       </c>
       <c r="V44" s="2" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="W44" s="2" t="s">
         <v>29</v>
@@ -5076,55 +5130,58 @@
       <c r="X44" s="2" t="s">
         <v>53</v>
       </c>
+      <c r="Y44" s="2" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="45" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F45" s="3">
         <v>0.55000000000000004</v>
       </c>
       <c r="G45" s="7">
-        <v>14.2</v>
+        <v>14.5</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>28</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="J45" s="2">
         <v>1</v>
       </c>
       <c r="K45" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L45" s="4">
-        <v>46062</v>
+        <v>45868</v>
       </c>
       <c r="M45" s="4">
-        <v>46062</v>
+        <v>46055</v>
       </c>
       <c r="N45" s="4">
-        <v>46063</v>
+        <v>46056</v>
       </c>
       <c r="O45" s="4">
-        <v>46063</v>
+        <v>46056</v>
       </c>
       <c r="P45" s="4">
-        <v>46063</v>
+        <v>46058</v>
       </c>
       <c r="Q45" s="4">
         <v>46065</v>
@@ -5133,196 +5190,169 @@
         <v>46066</v>
       </c>
       <c r="S45" s="4">
-        <v>46072</v>
+        <v>46066</v>
       </c>
       <c r="T45" s="4">
-        <v>46072</v>
+        <v>46066</v>
       </c>
       <c r="V45" s="2" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="W45" s="2" t="s">
-        <v>130</v>
+        <v>29</v>
       </c>
       <c r="X45" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="Y45" s="2" t="s">
-        <v>58</v>
-      </c>
     </row>
     <row r="46" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
-        <v>43</v>
+        <v>115</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>44</v>
+        <v>114</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>45</v>
+        <v>113</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F46" s="3">
-        <v>0.43</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="G46" s="7">
-        <v>14.2</v>
+        <v>14.5</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>131</v>
+        <v>28</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="J46" s="2">
         <v>1</v>
       </c>
       <c r="K46" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L46" s="4">
-        <v>46077</v>
+        <v>45868</v>
       </c>
       <c r="M46" s="4">
-        <v>46077</v>
-      </c>
-      <c r="N46" s="4">
-        <v>46078</v>
-      </c>
-      <c r="O46" s="4">
-        <v>46078</v>
-      </c>
-      <c r="P46" s="4">
-        <v>46084</v>
-      </c>
-      <c r="Q46" s="4">
-        <v>46089</v>
-      </c>
-      <c r="R46" s="4">
-        <v>46090</v>
-      </c>
-      <c r="S46" s="4">
-        <v>46092</v>
-      </c>
-      <c r="T46" s="4">
-        <v>46092</v>
+        <v>46122</v>
       </c>
       <c r="V46" s="2" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="W46" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="X46" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="Y46" s="2" t="s">
-        <v>246</v>
+        <v>293</v>
       </c>
     </row>
     <row r="47" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
-        <v>266</v>
+        <v>115</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>44</v>
+        <v>114</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>45</v>
+        <v>113</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F47" s="3">
-        <v>0.43</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="G47" s="7">
-        <v>14.2</v>
+        <v>14.5</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>131</v>
+        <v>28</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="J47" s="2">
         <v>1</v>
       </c>
       <c r="K47" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L47" s="4">
-        <v>46077</v>
+        <v>45868</v>
       </c>
       <c r="M47" s="4">
-        <v>46113</v>
+        <v>46055</v>
       </c>
       <c r="N47" s="4">
-        <v>46113</v>
+        <v>46056</v>
+      </c>
+      <c r="O47" s="4">
+        <v>46056</v>
       </c>
       <c r="P47" s="4">
-        <v>46084</v>
+        <v>46058</v>
       </c>
       <c r="Q47" s="4">
-        <v>46089</v>
+        <v>46065</v>
       </c>
       <c r="R47" s="4">
-        <v>46090</v>
+        <v>46066</v>
       </c>
       <c r="S47" s="4">
-        <v>46092</v>
+        <v>46066</v>
       </c>
       <c r="T47" s="4">
-        <v>46092</v>
+        <v>46066</v>
       </c>
       <c r="V47" s="2" t="s">
-        <v>76</v>
+        <v>117</v>
       </c>
       <c r="W47" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="X47" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="Y47" s="2" t="s">
-        <v>246</v>
+        <v>53</v>
       </c>
     </row>
     <row r="48" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
-        <v>62</v>
+        <v>125</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>63</v>
+        <v>126</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>64</v>
+        <v>127</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F48" s="3">
         <v>0.55000000000000004</v>
       </c>
       <c r="G48" s="7">
-        <v>14.5</v>
+        <v>14.2</v>
       </c>
       <c r="H48" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I48" s="14" t="s">
-        <v>138</v>
+      <c r="I48" s="2" t="s">
+        <v>128</v>
       </c>
       <c r="J48" s="2">
         <v>1</v>
@@ -5331,66 +5361,72 @@
         <v>1</v>
       </c>
       <c r="L48" s="4">
+        <v>46062</v>
+      </c>
+      <c r="M48" s="4">
+        <v>46062</v>
+      </c>
+      <c r="N48" s="4">
+        <v>46063</v>
+      </c>
+      <c r="O48" s="4">
+        <v>46063</v>
+      </c>
+      <c r="P48" s="4">
+        <v>46063</v>
+      </c>
+      <c r="Q48" s="4">
+        <v>46065</v>
+      </c>
+      <c r="R48" s="4">
         <v>46066</v>
       </c>
-      <c r="M48" s="6"/>
-      <c r="N48" s="6"/>
-      <c r="O48" s="6"/>
-      <c r="P48" s="4">
-        <v>46076</v>
-      </c>
-      <c r="Q48" s="4">
-        <v>46083</v>
-      </c>
-      <c r="R48" s="4">
-        <v>46093</v>
-      </c>
       <c r="S48" s="4">
-        <v>46094</v>
+        <v>46072</v>
       </c>
       <c r="T48" s="4">
-        <v>46094</v>
+        <v>46072</v>
       </c>
       <c r="V48" s="2" t="s">
-        <v>52</v>
+        <v>129</v>
       </c>
       <c r="W48" s="2" t="s">
-        <v>29</v>
+        <v>130</v>
       </c>
       <c r="X48" s="2" t="s">
         <v>53</v>
       </c>
       <c r="Y48" s="2" t="s">
-        <v>141</v>
+        <v>58</v>
       </c>
     </row>
     <row r="49" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F49" s="3">
-        <v>0.55000000000000004</v>
+        <v>0.43</v>
       </c>
       <c r="G49" s="7">
-        <v>14.5</v>
+        <v>14.2</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="I49" s="15" t="s">
-        <v>139</v>
+        <v>131</v>
+      </c>
+      <c r="I49" s="2" t="s">
+        <v>132</v>
       </c>
       <c r="J49" s="2">
         <v>1</v>
@@ -5399,110 +5435,110 @@
         <v>1</v>
       </c>
       <c r="L49" s="4">
-        <v>46066</v>
-      </c>
-      <c r="M49" s="6"/>
-      <c r="N49" s="6"/>
-      <c r="O49" s="6"/>
+        <v>46077</v>
+      </c>
+      <c r="M49" s="4">
+        <v>46077</v>
+      </c>
+      <c r="N49" s="4">
+        <v>46078</v>
+      </c>
+      <c r="O49" s="4">
+        <v>46078</v>
+      </c>
       <c r="P49" s="4">
-        <v>46076</v>
+        <v>46084</v>
       </c>
       <c r="Q49" s="4">
-        <v>46083</v>
+        <v>46089</v>
       </c>
       <c r="R49" s="4">
-        <v>46093</v>
+        <v>46090</v>
       </c>
       <c r="S49" s="4">
-        <v>46094</v>
+        <v>46092</v>
       </c>
       <c r="T49" s="4">
-        <v>46094</v>
+        <v>46092</v>
       </c>
       <c r="V49" s="2" t="s">
-        <v>52</v>
+        <v>133</v>
       </c>
       <c r="W49" s="2" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="X49" s="2" t="s">
         <v>53</v>
       </c>
       <c r="Y49" s="2" t="s">
-        <v>141</v>
+        <v>244</v>
       </c>
     </row>
     <row r="50" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
-        <v>62</v>
+        <v>264</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F50" s="3">
-        <v>0.55000000000000004</v>
+        <v>0.43</v>
       </c>
       <c r="G50" s="7">
-        <v>14.5</v>
+        <v>14.2</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>28</v>
+        <v>131</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="J50" s="2">
         <v>1</v>
       </c>
       <c r="K50" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L50" s="4">
-        <v>46066</v>
-      </c>
-      <c r="M50" s="6"/>
-      <c r="N50" s="6"/>
-      <c r="O50" s="6"/>
-      <c r="P50" s="4">
-        <v>46079</v>
-      </c>
-      <c r="Q50" s="4">
-        <v>46086</v>
-      </c>
-      <c r="R50" s="4">
-        <v>46087</v>
+        <v>46077</v>
+      </c>
+      <c r="M50" s="4">
+        <v>46113</v>
+      </c>
+      <c r="N50" s="4">
+        <v>46125</v>
       </c>
       <c r="V50" s="2" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="W50" s="2" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="X50" s="2" t="s">
-        <v>53</v>
+        <v>99</v>
       </c>
       <c r="Y50" s="2" t="s">
-        <v>141</v>
+        <v>244</v>
       </c>
     </row>
     <row r="51" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
-        <v>143</v>
+        <v>62</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>144</v>
+        <v>63</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>145</v>
+        <v>64</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>34</v>
@@ -5514,13 +5550,13 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G51" s="7">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="H51" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I51" s="2" t="s">
-        <v>146</v>
+      <c r="I51" s="14" t="s">
+        <v>138</v>
       </c>
       <c r="J51" s="2">
         <v>1</v>
@@ -5529,30 +5565,31 @@
         <v>1</v>
       </c>
       <c r="L51" s="4">
-        <v>46055</v>
-      </c>
+        <v>46066</v>
+      </c>
+      <c r="M51" s="6"/>
       <c r="N51" s="6"/>
       <c r="O51" s="6"/>
       <c r="P51" s="4">
-        <v>46060</v>
+        <v>46076</v>
       </c>
       <c r="Q51" s="4">
-        <v>46063</v>
+        <v>46083</v>
       </c>
       <c r="R51" s="4">
-        <v>46064</v>
+        <v>46093</v>
       </c>
       <c r="S51" s="4">
-        <v>46066</v>
+        <v>46094</v>
       </c>
       <c r="T51" s="4">
-        <v>46066</v>
+        <v>46094</v>
       </c>
       <c r="V51" s="2" t="s">
-        <v>267</v>
+        <v>52</v>
       </c>
       <c r="W51" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X51" s="2" t="s">
         <v>53</v>
@@ -5563,13 +5600,13 @@
     </row>
     <row r="52" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
-        <v>143</v>
+        <v>62</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>144</v>
+        <v>63</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>145</v>
+        <v>64</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>34</v>
@@ -5581,13 +5618,13 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G52" s="7">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="H52" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I52" s="2" t="s">
-        <v>148</v>
+      <c r="I52" s="15" t="s">
+        <v>139</v>
       </c>
       <c r="J52" s="2">
         <v>1</v>
@@ -5596,30 +5633,31 @@
         <v>1</v>
       </c>
       <c r="L52" s="4">
-        <v>46055</v>
-      </c>
+        <v>46066</v>
+      </c>
+      <c r="M52" s="6"/>
       <c r="N52" s="6"/>
       <c r="O52" s="6"/>
       <c r="P52" s="4">
-        <v>46060</v>
+        <v>46076</v>
       </c>
       <c r="Q52" s="4">
-        <v>46063</v>
+        <v>46083</v>
       </c>
       <c r="R52" s="4">
-        <v>46064</v>
+        <v>46093</v>
       </c>
       <c r="S52" s="4">
-        <v>46066</v>
+        <v>46094</v>
       </c>
       <c r="T52" s="4">
-        <v>46066</v>
+        <v>46094</v>
       </c>
       <c r="V52" s="2" t="s">
-        <v>268</v>
+        <v>52</v>
       </c>
       <c r="W52" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X52" s="2" t="s">
         <v>53</v>
@@ -5630,13 +5668,13 @@
     </row>
     <row r="53" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
-        <v>143</v>
+        <v>62</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>144</v>
+        <v>63</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>145</v>
+        <v>64</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>34</v>
@@ -5648,48 +5686,40 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G53" s="7">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="H53" s="2" t="s">
         <v>28</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="J53" s="2">
         <v>1</v>
       </c>
       <c r="K53" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L53" s="4">
-        <v>46055</v>
-      </c>
-      <c r="M53" s="4">
-        <v>46085</v>
-      </c>
+        <v>46066</v>
+      </c>
+      <c r="M53" s="6"/>
       <c r="N53" s="6"/>
       <c r="O53" s="6"/>
       <c r="P53" s="4">
-        <v>46085</v>
+        <v>46079</v>
       </c>
       <c r="Q53" s="4">
-        <v>46093</v>
+        <v>46086</v>
       </c>
       <c r="R53" s="4">
-        <v>46094</v>
-      </c>
-      <c r="S53" s="4">
-        <v>46094</v>
-      </c>
-      <c r="T53" s="4">
-        <v>46094</v>
+        <v>46087</v>
       </c>
       <c r="V53" s="2" t="s">
-        <v>147</v>
+        <v>66</v>
       </c>
       <c r="W53" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X53" s="2" t="s">
         <v>53</v>
@@ -5724,39 +5754,36 @@
         <v>28</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="J54" s="2">
         <v>1</v>
       </c>
       <c r="K54" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L54" s="4">
         <v>46055</v>
-      </c>
-      <c r="M54" s="4">
-        <v>46085</v>
       </c>
       <c r="N54" s="6"/>
       <c r="O54" s="6"/>
       <c r="P54" s="4">
-        <v>46085</v>
+        <v>46060</v>
       </c>
       <c r="Q54" s="4">
-        <v>46093</v>
+        <v>46063</v>
       </c>
       <c r="R54" s="4">
-        <v>46094</v>
+        <v>46064</v>
       </c>
       <c r="S54" s="4">
-        <v>46094</v>
+        <v>46066</v>
       </c>
       <c r="T54" s="4">
-        <v>46094</v>
+        <v>46066</v>
       </c>
       <c r="V54" s="2" t="s">
-        <v>147</v>
+        <v>265</v>
       </c>
       <c r="W54" s="2" t="s">
         <v>30</v>
@@ -5770,31 +5797,31 @@
     </row>
     <row r="55" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>152</v>
+        <v>27</v>
       </c>
       <c r="F55" s="3">
-        <v>0.45</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="G55" s="7">
-        <v>14.2</v>
+        <v>15</v>
       </c>
       <c r="H55" s="2" t="s">
         <v>28</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="J55" s="2">
         <v>1</v>
@@ -5803,185 +5830,176 @@
         <v>1</v>
       </c>
       <c r="L55" s="4">
-        <v>46090</v>
-      </c>
-      <c r="M55" s="12"/>
-      <c r="N55" s="4">
-        <v>46085</v>
-      </c>
-      <c r="O55" s="4">
-        <v>46086</v>
-      </c>
+        <v>46055</v>
+      </c>
+      <c r="N55" s="6"/>
+      <c r="O55" s="6"/>
       <c r="P55" s="4">
-        <v>46087</v>
+        <v>46060</v>
       </c>
       <c r="Q55" s="4">
-        <v>46098</v>
+        <v>46063</v>
       </c>
       <c r="R55" s="4">
-        <v>46099</v>
+        <v>46064</v>
       </c>
       <c r="S55" s="4">
-        <v>46100</v>
+        <v>46066</v>
       </c>
       <c r="T55" s="4">
-        <v>46100</v>
+        <v>46066</v>
       </c>
       <c r="V55" s="2" t="s">
-        <v>184</v>
+        <v>266</v>
       </c>
       <c r="W55" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="X55" s="2" t="s">
         <v>53</v>
       </c>
       <c r="Y55" s="2" t="s">
-        <v>58</v>
+        <v>141</v>
       </c>
     </row>
     <row r="56" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>152</v>
+        <v>27</v>
       </c>
       <c r="F56" s="3">
-        <v>0.45</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="G56" s="7">
-        <v>14.2</v>
+        <v>15</v>
       </c>
       <c r="H56" s="2" t="s">
         <v>28</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="J56" s="2">
         <v>1</v>
       </c>
       <c r="K56" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L56" s="4">
-        <v>46090</v>
-      </c>
-      <c r="M56" s="12"/>
-      <c r="N56" s="4">
+        <v>46055</v>
+      </c>
+      <c r="M56" s="4">
         <v>46085</v>
       </c>
-      <c r="O56" s="4">
-        <v>46086</v>
-      </c>
+      <c r="N56" s="6"/>
+      <c r="O56" s="6"/>
       <c r="P56" s="4">
-        <v>46087</v>
+        <v>46085</v>
       </c>
       <c r="Q56" s="4">
-        <v>46098</v>
+        <v>46093</v>
       </c>
       <c r="R56" s="4">
-        <v>46099</v>
+        <v>46094</v>
       </c>
       <c r="S56" s="4">
-        <v>46100</v>
+        <v>46094</v>
       </c>
       <c r="T56" s="4">
-        <v>46100</v>
+        <v>46094</v>
       </c>
       <c r="V56" s="2" t="s">
-        <v>184</v>
+        <v>147</v>
       </c>
       <c r="W56" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="X56" s="2" t="s">
         <v>53</v>
       </c>
       <c r="Y56" s="2" t="s">
-        <v>58</v>
+        <v>141</v>
       </c>
     </row>
     <row r="57" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>152</v>
+        <v>27</v>
       </c>
       <c r="F57" s="3">
-        <v>0.45</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="G57" s="7">
-        <v>14.2</v>
+        <v>15</v>
       </c>
       <c r="H57" s="2" t="s">
         <v>28</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="J57" s="2">
         <v>1</v>
       </c>
       <c r="K57" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L57" s="4">
-        <v>46090</v>
-      </c>
-      <c r="M57" s="12"/>
-      <c r="N57" s="4">
+        <v>46055</v>
+      </c>
+      <c r="M57" s="4">
         <v>46085</v>
       </c>
-      <c r="O57" s="4">
-        <v>46086</v>
-      </c>
+      <c r="N57" s="6"/>
+      <c r="O57" s="6"/>
       <c r="P57" s="4">
-        <v>46087</v>
+        <v>46085</v>
       </c>
       <c r="Q57" s="4">
-        <v>46098</v>
+        <v>46093</v>
       </c>
       <c r="R57" s="4">
-        <v>46099</v>
+        <v>46094</v>
       </c>
       <c r="S57" s="4">
-        <v>46100</v>
+        <v>46094</v>
       </c>
       <c r="T57" s="4">
-        <v>46100</v>
+        <v>46094</v>
       </c>
       <c r="V57" s="2" t="s">
-        <v>184</v>
+        <v>147</v>
       </c>
       <c r="W57" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="X57" s="2" t="s">
         <v>53</v>
       </c>
       <c r="Y57" s="2" t="s">
-        <v>58</v>
+        <v>141</v>
       </c>
     </row>
     <row r="58" spans="1:25" x14ac:dyDescent="0.3">
@@ -6010,7 +6028,7 @@
         <v>28</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="J58" s="2">
         <v>1</v>
@@ -6031,6 +6049,18 @@
       <c r="P58" s="4">
         <v>46087</v>
       </c>
+      <c r="Q58" s="4">
+        <v>46098</v>
+      </c>
+      <c r="R58" s="4">
+        <v>46099</v>
+      </c>
+      <c r="S58" s="4">
+        <v>46100</v>
+      </c>
+      <c r="T58" s="4">
+        <v>46100</v>
+      </c>
       <c r="V58" s="2" t="s">
         <v>184</v>
       </c>
@@ -6038,7 +6068,7 @@
         <v>29</v>
       </c>
       <c r="X58" s="2" t="s">
-        <v>136</v>
+        <v>53</v>
       </c>
       <c r="Y58" s="2" t="s">
         <v>58</v>
@@ -6070,7 +6100,7 @@
         <v>28</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="J59" s="2">
         <v>1</v>
@@ -6091,6 +6121,18 @@
       <c r="P59" s="4">
         <v>46087</v>
       </c>
+      <c r="Q59" s="4">
+        <v>46098</v>
+      </c>
+      <c r="R59" s="4">
+        <v>46099</v>
+      </c>
+      <c r="S59" s="4">
+        <v>46100</v>
+      </c>
+      <c r="T59" s="4">
+        <v>46100</v>
+      </c>
       <c r="V59" s="2" t="s">
         <v>184</v>
       </c>
@@ -6098,13 +6140,13 @@
         <v>29</v>
       </c>
       <c r="X59" s="2" t="s">
-        <v>136</v>
+        <v>53</v>
       </c>
       <c r="Y59" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="60" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
         <v>149</v>
       </c>
@@ -6130,7 +6172,7 @@
         <v>28</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="J60" s="2">
         <v>1</v>
@@ -6151,6 +6193,18 @@
       <c r="P60" s="4">
         <v>46087</v>
       </c>
+      <c r="Q60" s="4">
+        <v>46098</v>
+      </c>
+      <c r="R60" s="4">
+        <v>46099</v>
+      </c>
+      <c r="S60" s="4">
+        <v>46100</v>
+      </c>
+      <c r="T60" s="4">
+        <v>46100</v>
+      </c>
       <c r="V60" s="2" t="s">
         <v>184</v>
       </c>
@@ -6158,13 +6212,13 @@
         <v>29</v>
       </c>
       <c r="X60" s="2" t="s">
-        <v>136</v>
+        <v>53</v>
       </c>
       <c r="Y60" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="61" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
         <v>149</v>
       </c>
@@ -6190,7 +6244,7 @@
         <v>28</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>185</v>
+        <v>156</v>
       </c>
       <c r="J61" s="2">
         <v>1</v>
@@ -6249,8 +6303,8 @@
       <c r="H62" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I62" s="11" t="s">
-        <v>159</v>
+      <c r="I62" s="2" t="s">
+        <v>157</v>
       </c>
       <c r="J62" s="2">
         <v>1</v>
@@ -6284,7 +6338,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="63" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
         <v>149</v>
       </c>
@@ -6309,8 +6363,8 @@
       <c r="H63" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I63" s="11" t="s">
-        <v>160</v>
+      <c r="I63" s="2" t="s">
+        <v>158</v>
       </c>
       <c r="J63" s="2">
         <v>1</v>
@@ -6344,7 +6398,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="64" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
         <v>149</v>
       </c>
@@ -6369,8 +6423,8 @@
       <c r="H64" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I64" s="11" t="s">
-        <v>161</v>
+      <c r="I64" s="2" t="s">
+        <v>185</v>
       </c>
       <c r="J64" s="2">
         <v>1</v>
@@ -6406,22 +6460,22 @@
     </row>
     <row r="65" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
-        <v>170</v>
+        <v>149</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>171</v>
+        <v>150</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>172</v>
+        <v>151</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>173</v>
+        <v>152</v>
       </c>
       <c r="F65" s="3">
-        <v>0.55000000000000004</v>
+        <v>0.45</v>
       </c>
       <c r="G65" s="7">
         <v>14.2</v>
@@ -6430,7 +6484,7 @@
         <v>28</v>
       </c>
       <c r="I65" s="11" t="s">
-        <v>193</v>
+        <v>159</v>
       </c>
       <c r="J65" s="2">
         <v>1</v>
@@ -6439,31 +6493,26 @@
         <v>1</v>
       </c>
       <c r="L65" s="4">
+        <v>46090</v>
+      </c>
+      <c r="M65" s="12"/>
+      <c r="N65" s="4">
+        <v>46085</v>
+      </c>
+      <c r="O65" s="4">
         <v>46086</v>
       </c>
       <c r="P65" s="4">
-        <v>46094</v>
-      </c>
-      <c r="Q65" s="4">
-        <v>46103</v>
-      </c>
-      <c r="R65" s="4">
-        <v>46105</v>
-      </c>
-      <c r="S65" s="4">
-        <v>46112</v>
-      </c>
-      <c r="T65" s="4">
-        <v>46112</v>
+        <v>46087</v>
       </c>
       <c r="V65" s="2" t="s">
-        <v>147</v>
+        <v>184</v>
       </c>
       <c r="W65" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X65" s="2" t="s">
-        <v>53</v>
+        <v>136</v>
       </c>
       <c r="Y65" s="2" t="s">
         <v>58</v>
@@ -6471,22 +6520,22 @@
     </row>
     <row r="66" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
-        <v>170</v>
+        <v>149</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>171</v>
+        <v>150</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>172</v>
+        <v>151</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>173</v>
+        <v>152</v>
       </c>
       <c r="F66" s="3">
-        <v>0.55000000000000004</v>
+        <v>0.45</v>
       </c>
       <c r="G66" s="7">
         <v>14.2</v>
@@ -6495,7 +6544,7 @@
         <v>28</v>
       </c>
       <c r="I66" s="11" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="J66" s="2">
         <v>1</v>
@@ -6504,31 +6553,26 @@
         <v>1</v>
       </c>
       <c r="L66" s="4">
+        <v>46090</v>
+      </c>
+      <c r="M66" s="12"/>
+      <c r="N66" s="4">
+        <v>46085</v>
+      </c>
+      <c r="O66" s="4">
         <v>46086</v>
       </c>
       <c r="P66" s="4">
-        <v>46094</v>
-      </c>
-      <c r="Q66" s="4">
-        <v>46103</v>
-      </c>
-      <c r="R66" s="4">
-        <v>46105</v>
-      </c>
-      <c r="S66" s="4">
-        <v>46112</v>
-      </c>
-      <c r="T66" s="4">
-        <v>46112</v>
+        <v>46087</v>
       </c>
       <c r="V66" s="2" t="s">
-        <v>147</v>
+        <v>184</v>
       </c>
       <c r="W66" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X66" s="2" t="s">
-        <v>53</v>
+        <v>136</v>
       </c>
       <c r="Y66" s="2" t="s">
         <v>58</v>
@@ -6536,22 +6580,22 @@
     </row>
     <row r="67" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
-        <v>170</v>
+        <v>149</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>171</v>
+        <v>150</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>172</v>
+        <v>151</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>27</v>
+        <v>152</v>
       </c>
       <c r="F67" s="3">
-        <v>0.55000000000000004</v>
+        <v>0.45</v>
       </c>
       <c r="G67" s="7">
         <v>14.2</v>
@@ -6560,7 +6604,7 @@
         <v>28</v>
       </c>
       <c r="I67" s="11" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="J67" s="2">
         <v>1</v>
@@ -6569,31 +6613,26 @@
         <v>1</v>
       </c>
       <c r="L67" s="4">
+        <v>46090</v>
+      </c>
+      <c r="M67" s="12"/>
+      <c r="N67" s="4">
+        <v>46085</v>
+      </c>
+      <c r="O67" s="4">
         <v>46086</v>
       </c>
       <c r="P67" s="4">
-        <v>46094</v>
-      </c>
-      <c r="Q67" s="4">
-        <v>46103</v>
-      </c>
-      <c r="R67" s="4">
-        <v>46105</v>
-      </c>
-      <c r="S67" s="4">
-        <v>46112</v>
-      </c>
-      <c r="T67" s="4">
-        <v>46112</v>
+        <v>46087</v>
       </c>
       <c r="V67" s="2" t="s">
-        <v>147</v>
+        <v>184</v>
       </c>
       <c r="W67" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X67" s="2" t="s">
-        <v>53</v>
+        <v>136</v>
       </c>
       <c r="Y67" s="2" t="s">
         <v>58</v>
@@ -6613,7 +6652,7 @@
         <v>26</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>27</v>
+        <v>173</v>
       </c>
       <c r="F68" s="3">
         <v>0.55000000000000004</v>
@@ -6625,7 +6664,7 @@
         <v>28</v>
       </c>
       <c r="I68" s="11" t="s">
-        <v>164</v>
+        <v>193</v>
       </c>
       <c r="J68" s="2">
         <v>1</v>
@@ -6678,7 +6717,7 @@
         <v>26</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>27</v>
+        <v>173</v>
       </c>
       <c r="F69" s="3">
         <v>0.55000000000000004</v>
@@ -6690,7 +6729,7 @@
         <v>28</v>
       </c>
       <c r="I69" s="11" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="J69" s="2">
         <v>1</v>
@@ -6755,7 +6794,7 @@
         <v>28</v>
       </c>
       <c r="I70" s="11" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="J70" s="2">
         <v>1</v>
@@ -6820,7 +6859,7 @@
         <v>28</v>
       </c>
       <c r="I71" s="11" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="J71" s="2">
         <v>1</v>
@@ -6885,7 +6924,7 @@
         <v>28</v>
       </c>
       <c r="I72" s="11" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="J72" s="2">
         <v>1</v>
@@ -6950,7 +6989,7 @@
         <v>28</v>
       </c>
       <c r="I73" s="11" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="J73" s="2">
         <v>1</v>
@@ -7015,7 +7054,7 @@
         <v>28</v>
       </c>
       <c r="I74" s="11" t="s">
-        <v>194</v>
+        <v>167</v>
       </c>
       <c r="J74" s="2">
         <v>1</v>
@@ -7080,7 +7119,7 @@
         <v>28</v>
       </c>
       <c r="I75" s="11" t="s">
-        <v>195</v>
+        <v>168</v>
       </c>
       <c r="J75" s="2">
         <v>1</v>
@@ -7145,7 +7184,7 @@
         <v>28</v>
       </c>
       <c r="I76" s="11" t="s">
-        <v>247</v>
+        <v>169</v>
       </c>
       <c r="J76" s="2">
         <v>1</v>
@@ -7154,16 +7193,22 @@
         <v>1</v>
       </c>
       <c r="L76" s="4">
-        <v>46097</v>
+        <v>46086</v>
       </c>
       <c r="P76" s="4">
-        <v>46117</v>
+        <v>46094</v>
       </c>
       <c r="Q76" s="4">
-        <v>46118</v>
+        <v>46103</v>
       </c>
       <c r="R76" s="4">
-        <v>46119</v>
+        <v>46105</v>
+      </c>
+      <c r="S76" s="4">
+        <v>46112</v>
+      </c>
+      <c r="T76" s="4">
+        <v>46112</v>
       </c>
       <c r="V76" s="2" t="s">
         <v>147</v>
@@ -7172,7 +7217,7 @@
         <v>30</v>
       </c>
       <c r="X76" s="2" t="s">
-        <v>99</v>
+        <v>53</v>
       </c>
       <c r="Y76" s="2" t="s">
         <v>58</v>
@@ -7204,7 +7249,7 @@
         <v>28</v>
       </c>
       <c r="I77" s="11" t="s">
-        <v>248</v>
+        <v>194</v>
       </c>
       <c r="J77" s="2">
         <v>1</v>
@@ -7213,16 +7258,22 @@
         <v>1</v>
       </c>
       <c r="L77" s="4">
-        <v>46097</v>
+        <v>46086</v>
       </c>
       <c r="P77" s="4">
-        <v>46117</v>
+        <v>46094</v>
       </c>
       <c r="Q77" s="4">
-        <v>46118</v>
+        <v>46103</v>
       </c>
       <c r="R77" s="4">
-        <v>46119</v>
+        <v>46105</v>
+      </c>
+      <c r="S77" s="4">
+        <v>46112</v>
+      </c>
+      <c r="T77" s="4">
+        <v>46112</v>
       </c>
       <c r="V77" s="2" t="s">
         <v>147</v>
@@ -7231,7 +7282,7 @@
         <v>30</v>
       </c>
       <c r="X77" s="2" t="s">
-        <v>99</v>
+        <v>53</v>
       </c>
       <c r="Y77" s="2" t="s">
         <v>58</v>
@@ -7263,7 +7314,7 @@
         <v>28</v>
       </c>
       <c r="I78" s="11" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J78" s="2">
         <v>1</v>
@@ -7328,7 +7379,7 @@
         <v>28</v>
       </c>
       <c r="I79" s="11" t="s">
-        <v>197</v>
+        <v>245</v>
       </c>
       <c r="J79" s="2">
         <v>1</v>
@@ -7337,22 +7388,16 @@
         <v>1</v>
       </c>
       <c r="L79" s="4">
-        <v>46086</v>
+        <v>46097</v>
       </c>
       <c r="P79" s="4">
-        <v>46094</v>
+        <v>46117</v>
       </c>
       <c r="Q79" s="4">
-        <v>46103</v>
+        <v>46118</v>
       </c>
       <c r="R79" s="4">
-        <v>46105</v>
-      </c>
-      <c r="S79" s="4">
-        <v>46112</v>
-      </c>
-      <c r="T79" s="4">
-        <v>46112</v>
+        <v>46119</v>
       </c>
       <c r="V79" s="2" t="s">
         <v>147</v>
@@ -7361,7 +7406,7 @@
         <v>30</v>
       </c>
       <c r="X79" s="2" t="s">
-        <v>53</v>
+        <v>99</v>
       </c>
       <c r="Y79" s="2" t="s">
         <v>58</v>
@@ -7393,7 +7438,7 @@
         <v>28</v>
       </c>
       <c r="I80" s="11" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="J80" s="2">
         <v>1</v>
@@ -7420,7 +7465,7 @@
         <v>30</v>
       </c>
       <c r="X80" s="2" t="s">
-        <v>41</v>
+        <v>99</v>
       </c>
       <c r="Y80" s="2" t="s">
         <v>58</v>
@@ -7452,7 +7497,7 @@
         <v>28</v>
       </c>
       <c r="I81" s="11" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="J81" s="2">
         <v>1</v>
@@ -7517,7 +7562,7 @@
         <v>28</v>
       </c>
       <c r="I82" s="11" t="s">
-        <v>250</v>
+        <v>197</v>
       </c>
       <c r="J82" s="2">
         <v>1</v>
@@ -7526,16 +7571,22 @@
         <v>1</v>
       </c>
       <c r="L82" s="4">
-        <v>46097</v>
+        <v>46086</v>
       </c>
       <c r="P82" s="4">
-        <v>46117</v>
+        <v>46094</v>
       </c>
       <c r="Q82" s="4">
-        <v>46118</v>
+        <v>46103</v>
       </c>
       <c r="R82" s="4">
-        <v>46119</v>
+        <v>46105</v>
+      </c>
+      <c r="S82" s="4">
+        <v>46112</v>
+      </c>
+      <c r="T82" s="4">
+        <v>46112</v>
       </c>
       <c r="V82" s="2" t="s">
         <v>147</v>
@@ -7544,7 +7595,7 @@
         <v>30</v>
       </c>
       <c r="X82" s="2" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="Y82" s="2" t="s">
         <v>58</v>
@@ -7576,7 +7627,7 @@
         <v>28</v>
       </c>
       <c r="I83" s="11" t="s">
-        <v>199</v>
+        <v>247</v>
       </c>
       <c r="J83" s="2">
         <v>1</v>
@@ -7585,22 +7636,16 @@
         <v>1</v>
       </c>
       <c r="L83" s="4">
-        <v>46086</v>
+        <v>46097</v>
       </c>
       <c r="P83" s="4">
-        <v>46094</v>
+        <v>46117</v>
       </c>
       <c r="Q83" s="4">
-        <v>46103</v>
+        <v>46118</v>
       </c>
       <c r="R83" s="4">
-        <v>46105</v>
-      </c>
-      <c r="S83" s="4">
-        <v>46112</v>
-      </c>
-      <c r="T83" s="4">
-        <v>46112</v>
+        <v>46119</v>
       </c>
       <c r="V83" s="2" t="s">
         <v>147</v>
@@ -7609,7 +7654,7 @@
         <v>30</v>
       </c>
       <c r="X83" s="2" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="Y83" s="2" t="s">
         <v>58</v>
@@ -7641,7 +7686,7 @@
         <v>28</v>
       </c>
       <c r="I84" s="11" t="s">
-        <v>251</v>
+        <v>198</v>
       </c>
       <c r="J84" s="2">
         <v>1</v>
@@ -7650,16 +7695,22 @@
         <v>1</v>
       </c>
       <c r="L84" s="4">
-        <v>46097</v>
+        <v>46086</v>
       </c>
       <c r="P84" s="4">
-        <v>46117</v>
+        <v>46094</v>
       </c>
       <c r="Q84" s="4">
-        <v>46118</v>
+        <v>46103</v>
       </c>
       <c r="R84" s="4">
-        <v>46119</v>
+        <v>46105</v>
+      </c>
+      <c r="S84" s="4">
+        <v>46112</v>
+      </c>
+      <c r="T84" s="4">
+        <v>46112</v>
       </c>
       <c r="V84" s="2" t="s">
         <v>147</v>
@@ -7668,7 +7719,7 @@
         <v>30</v>
       </c>
       <c r="X84" s="2" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="Y84" s="2" t="s">
         <v>58</v>
@@ -7700,7 +7751,7 @@
         <v>28</v>
       </c>
       <c r="I85" s="11" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="J85" s="2">
         <v>1</v>
@@ -7759,7 +7810,7 @@
         <v>28</v>
       </c>
       <c r="I86" s="11" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="J86" s="2">
         <v>1</v>
@@ -7824,7 +7875,7 @@
         <v>28</v>
       </c>
       <c r="I87" s="11" t="s">
-        <v>201</v>
+        <v>249</v>
       </c>
       <c r="J87" s="2">
         <v>1</v>
@@ -7833,22 +7884,16 @@
         <v>1</v>
       </c>
       <c r="L87" s="4">
-        <v>46086</v>
+        <v>46097</v>
       </c>
       <c r="P87" s="4">
-        <v>46094</v>
+        <v>46117</v>
       </c>
       <c r="Q87" s="4">
-        <v>46103</v>
+        <v>46118</v>
       </c>
       <c r="R87" s="4">
-        <v>46105</v>
-      </c>
-      <c r="S87" s="4">
-        <v>46112</v>
-      </c>
-      <c r="T87" s="4">
-        <v>46112</v>
+        <v>46119</v>
       </c>
       <c r="V87" s="2" t="s">
         <v>147</v>
@@ -7857,7 +7902,7 @@
         <v>30</v>
       </c>
       <c r="X87" s="2" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="Y87" s="2" t="s">
         <v>58</v>
@@ -7889,7 +7934,7 @@
         <v>28</v>
       </c>
       <c r="I88" s="11" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="J88" s="2">
         <v>1</v>
@@ -7948,7 +7993,7 @@
         <v>28</v>
       </c>
       <c r="I89" s="11" t="s">
-        <v>254</v>
+        <v>200</v>
       </c>
       <c r="J89" s="2">
         <v>1</v>
@@ -7957,16 +8002,22 @@
         <v>1</v>
       </c>
       <c r="L89" s="4">
-        <v>46097</v>
+        <v>46086</v>
       </c>
       <c r="P89" s="4">
-        <v>46117</v>
+        <v>46094</v>
       </c>
       <c r="Q89" s="4">
-        <v>46118</v>
+        <v>46103</v>
       </c>
       <c r="R89" s="4">
-        <v>46119</v>
+        <v>46105</v>
+      </c>
+      <c r="S89" s="4">
+        <v>46112</v>
+      </c>
+      <c r="T89" s="4">
+        <v>46112</v>
       </c>
       <c r="V89" s="2" t="s">
         <v>147</v>
@@ -7975,7 +8026,7 @@
         <v>30</v>
       </c>
       <c r="X89" s="2" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="Y89" s="2" t="s">
         <v>58</v>
@@ -7989,7 +8040,7 @@
         <v>171</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>45</v>
+        <v>172</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>26</v>
@@ -8007,7 +8058,7 @@
         <v>28</v>
       </c>
       <c r="I90" s="11" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="J90" s="2">
         <v>1</v>
@@ -8018,6 +8069,21 @@
       <c r="L90" s="4">
         <v>46086</v>
       </c>
+      <c r="P90" s="4">
+        <v>46094</v>
+      </c>
+      <c r="Q90" s="4">
+        <v>46103</v>
+      </c>
+      <c r="R90" s="4">
+        <v>46105</v>
+      </c>
+      <c r="S90" s="4">
+        <v>46112</v>
+      </c>
+      <c r="T90" s="4">
+        <v>46112</v>
+      </c>
       <c r="V90" s="2" t="s">
         <v>147</v>
       </c>
@@ -8025,7 +8091,7 @@
         <v>30</v>
       </c>
       <c r="X90" s="2" t="s">
-        <v>136</v>
+        <v>53</v>
       </c>
       <c r="Y90" s="2" t="s">
         <v>58</v>
@@ -8039,7 +8105,7 @@
         <v>171</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>45</v>
+        <v>172</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>26</v>
@@ -8057,7 +8123,7 @@
         <v>28</v>
       </c>
       <c r="I91" s="11" t="s">
-        <v>203</v>
+        <v>251</v>
       </c>
       <c r="J91" s="2">
         <v>1</v>
@@ -8066,7 +8132,16 @@
         <v>1</v>
       </c>
       <c r="L91" s="4">
-        <v>46086</v>
+        <v>46097</v>
+      </c>
+      <c r="P91" s="4">
+        <v>46117</v>
+      </c>
+      <c r="Q91" s="4">
+        <v>46118</v>
+      </c>
+      <c r="R91" s="4">
+        <v>46119</v>
       </c>
       <c r="V91" s="2" t="s">
         <v>147</v>
@@ -8075,7 +8150,7 @@
         <v>30</v>
       </c>
       <c r="X91" s="2" t="s">
-        <v>136</v>
+        <v>41</v>
       </c>
       <c r="Y91" s="2" t="s">
         <v>58</v>
@@ -8089,7 +8164,7 @@
         <v>171</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>45</v>
+        <v>172</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>26</v>
@@ -8107,7 +8182,7 @@
         <v>28</v>
       </c>
       <c r="I92" s="11" t="s">
-        <v>204</v>
+        <v>252</v>
       </c>
       <c r="J92" s="2">
         <v>1</v>
@@ -8116,7 +8191,16 @@
         <v>1</v>
       </c>
       <c r="L92" s="4">
-        <v>46086</v>
+        <v>46097</v>
+      </c>
+      <c r="P92" s="4">
+        <v>46117</v>
+      </c>
+      <c r="Q92" s="4">
+        <v>46118</v>
+      </c>
+      <c r="R92" s="4">
+        <v>46119</v>
       </c>
       <c r="V92" s="2" t="s">
         <v>147</v>
@@ -8125,7 +8209,7 @@
         <v>30</v>
       </c>
       <c r="X92" s="2" t="s">
-        <v>136</v>
+        <v>41</v>
       </c>
       <c r="Y92" s="2" t="s">
         <v>58</v>
@@ -8157,7 +8241,7 @@
         <v>28</v>
       </c>
       <c r="I93" s="11" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="J93" s="2">
         <v>1</v>
@@ -8207,7 +8291,7 @@
         <v>28</v>
       </c>
       <c r="I94" s="11" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="J94" s="2">
         <v>1</v>
@@ -8257,7 +8341,7 @@
         <v>28</v>
       </c>
       <c r="I95" s="11" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="J95" s="2">
         <v>1</v>
@@ -8307,7 +8391,7 @@
         <v>28</v>
       </c>
       <c r="I96" s="11" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="J96" s="2">
         <v>1</v>
@@ -8357,7 +8441,7 @@
         <v>28</v>
       </c>
       <c r="I97" s="11" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="J97" s="2">
         <v>1</v>
@@ -8407,7 +8491,7 @@
         <v>28</v>
       </c>
       <c r="I98" s="11" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="J98" s="2">
         <v>1</v>
@@ -8418,14 +8502,8 @@
       <c r="L98" s="4">
         <v>46086</v>
       </c>
-      <c r="S98" s="4">
-        <v>46142</v>
-      </c>
-      <c r="T98" s="4">
-        <v>46142</v>
-      </c>
       <c r="V98" s="2" t="s">
-        <v>218</v>
+        <v>147</v>
       </c>
       <c r="W98" s="2" t="s">
         <v>30</v>
@@ -8463,7 +8541,7 @@
         <v>28</v>
       </c>
       <c r="I99" s="11" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="J99" s="2">
         <v>1</v>
@@ -8474,14 +8552,8 @@
       <c r="L99" s="4">
         <v>46086</v>
       </c>
-      <c r="S99" s="4">
-        <v>46142</v>
-      </c>
-      <c r="T99" s="4">
-        <v>46142</v>
-      </c>
       <c r="V99" s="2" t="s">
-        <v>218</v>
+        <v>147</v>
       </c>
       <c r="W99" s="2" t="s">
         <v>30</v>
@@ -8519,7 +8591,7 @@
         <v>28</v>
       </c>
       <c r="I100" s="11" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="J100" s="2">
         <v>1</v>
@@ -8530,14 +8602,8 @@
       <c r="L100" s="4">
         <v>46086</v>
       </c>
-      <c r="S100" s="4">
-        <v>46142</v>
-      </c>
-      <c r="T100" s="4">
-        <v>46142</v>
-      </c>
       <c r="V100" s="2" t="s">
-        <v>218</v>
+        <v>147</v>
       </c>
       <c r="W100" s="2" t="s">
         <v>30</v>
@@ -8575,7 +8641,7 @@
         <v>28</v>
       </c>
       <c r="I101" s="11" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="J101" s="2">
         <v>1</v>
@@ -8631,7 +8697,7 @@
         <v>28</v>
       </c>
       <c r="I102" s="11" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="J102" s="2">
         <v>1</v>
@@ -8687,7 +8753,7 @@
         <v>28</v>
       </c>
       <c r="I103" s="11" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="J103" s="2">
         <v>1</v>
@@ -8743,7 +8809,7 @@
         <v>28</v>
       </c>
       <c r="I104" s="11" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="J104" s="2">
         <v>1</v>
@@ -8799,7 +8865,7 @@
         <v>28</v>
       </c>
       <c r="I105" s="11" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="J105" s="2">
         <v>1</v>
@@ -8855,7 +8921,7 @@
         <v>28</v>
       </c>
       <c r="I106" s="11" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="J106" s="2">
         <v>1</v>
@@ -8911,7 +8977,7 @@
         <v>28</v>
       </c>
       <c r="I107" s="11" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="J107" s="2">
         <v>1</v>
@@ -8929,7 +8995,7 @@
         <v>46142</v>
       </c>
       <c r="V107" s="2" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="W107" s="2" t="s">
         <v>30</v>
@@ -8943,16 +9009,16 @@
     </row>
     <row r="108" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A108" s="2" t="s">
-        <v>149</v>
+        <v>170</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>150</v>
+        <v>171</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>151</v>
+        <v>45</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="E108" s="2" t="s">
         <v>27</v>
@@ -8961,13 +9027,13 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G108" s="7">
-        <v>14.5</v>
+        <v>14.2</v>
       </c>
       <c r="H108" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I108" s="2" t="s">
-        <v>181</v>
+      <c r="I108" s="11" t="s">
+        <v>217</v>
       </c>
       <c r="J108" s="2">
         <v>1</v>
@@ -8976,35 +9042,22 @@
         <v>1</v>
       </c>
       <c r="L108" s="4">
-        <v>46092</v>
-      </c>
-      <c r="M108" s="12"/>
-      <c r="N108" s="4">
-        <v>46093</v>
-      </c>
-      <c r="O108" s="4">
-        <v>46094</v>
-      </c>
-      <c r="Q108" s="4">
-        <v>46111</v>
-      </c>
-      <c r="R108" s="4">
-        <v>46112</v>
+        <v>46086</v>
       </c>
       <c r="S108" s="4">
-        <v>46113</v>
+        <v>46142</v>
       </c>
       <c r="T108" s="4">
-        <v>46113</v>
+        <v>46142</v>
       </c>
       <c r="V108" s="2" t="s">
-        <v>182</v>
+        <v>218</v>
       </c>
       <c r="W108" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="X108" s="2" t="s">
-        <v>53</v>
+        <v>136</v>
       </c>
       <c r="Y108" s="2" t="s">
         <v>58</v>
@@ -9012,16 +9065,16 @@
     </row>
     <row r="109" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A109" s="2" t="s">
-        <v>149</v>
+        <v>170</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>150</v>
+        <v>171</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>151</v>
+        <v>45</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>27</v>
@@ -9030,13 +9083,13 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G109" s="7">
-        <v>14.5</v>
+        <v>14.2</v>
       </c>
       <c r="H109" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I109" s="2" t="s">
-        <v>174</v>
+      <c r="I109" s="11" t="s">
+        <v>219</v>
       </c>
       <c r="J109" s="2">
         <v>1</v>
@@ -9045,35 +9098,22 @@
         <v>1</v>
       </c>
       <c r="L109" s="4">
-        <v>46092</v>
-      </c>
-      <c r="M109" s="12"/>
-      <c r="N109" s="4">
-        <v>46093</v>
-      </c>
-      <c r="O109" s="4">
-        <v>46094</v>
-      </c>
-      <c r="Q109" s="4">
-        <v>46111</v>
-      </c>
-      <c r="R109" s="4">
-        <v>46112</v>
+        <v>46086</v>
       </c>
       <c r="S109" s="4">
-        <v>46113</v>
+        <v>46142</v>
       </c>
       <c r="T109" s="4">
-        <v>46113</v>
+        <v>46142</v>
       </c>
       <c r="V109" s="2" t="s">
-        <v>182</v>
+        <v>218</v>
       </c>
       <c r="W109" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="X109" s="2" t="s">
-        <v>53</v>
+        <v>136</v>
       </c>
       <c r="Y109" s="2" t="s">
         <v>58</v>
@@ -9081,16 +9121,16 @@
     </row>
     <row r="110" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="s">
-        <v>149</v>
+        <v>170</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>150</v>
+        <v>171</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>151</v>
+        <v>45</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>27</v>
@@ -9099,13 +9139,13 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G110" s="7">
-        <v>14.5</v>
+        <v>14.2</v>
       </c>
       <c r="H110" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I110" s="2" t="s">
-        <v>175</v>
+      <c r="I110" s="11" t="s">
+        <v>220</v>
       </c>
       <c r="J110" s="2">
         <v>1</v>
@@ -9114,35 +9154,22 @@
         <v>1</v>
       </c>
       <c r="L110" s="4">
-        <v>46092</v>
-      </c>
-      <c r="M110" s="12"/>
-      <c r="N110" s="4">
-        <v>46093</v>
-      </c>
-      <c r="O110" s="4">
-        <v>46094</v>
-      </c>
-      <c r="Q110" s="4">
-        <v>46111</v>
-      </c>
-      <c r="R110" s="4">
-        <v>46112</v>
+        <v>46086</v>
       </c>
       <c r="S110" s="4">
-        <v>46113</v>
+        <v>46142</v>
       </c>
       <c r="T110" s="4">
-        <v>46113</v>
+        <v>46142</v>
       </c>
       <c r="V110" s="2" t="s">
-        <v>183</v>
+        <v>221</v>
       </c>
       <c r="W110" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="X110" s="2" t="s">
-        <v>53</v>
+        <v>136</v>
       </c>
       <c r="Y110" s="2" t="s">
         <v>58</v>
@@ -9174,7 +9201,7 @@
         <v>28</v>
       </c>
       <c r="I111" s="2" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="J111" s="2">
         <v>1</v>
@@ -9205,7 +9232,7 @@
         <v>46113</v>
       </c>
       <c r="V111" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="W111" s="2" t="s">
         <v>29</v>
@@ -9219,13 +9246,13 @@
     </row>
     <row r="112" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
-        <v>186</v>
+        <v>149</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>188</v>
+        <v>151</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>34</v>
@@ -9243,7 +9270,7 @@
         <v>28</v>
       </c>
       <c r="I112" s="2" t="s">
-        <v>279</v>
+        <v>174</v>
       </c>
       <c r="J112" s="2">
         <v>1</v>
@@ -9252,25 +9279,35 @@
         <v>1</v>
       </c>
       <c r="L112" s="4">
+        <v>46092</v>
+      </c>
+      <c r="M112" s="12"/>
+      <c r="N112" s="4">
+        <v>46093</v>
+      </c>
+      <c r="O112" s="4">
         <v>46094</v>
       </c>
-      <c r="M112" s="4">
-        <v>46094</v>
-      </c>
-      <c r="P112" s="4">
-        <v>46101</v>
+      <c r="Q112" s="4">
+        <v>46111</v>
+      </c>
+      <c r="R112" s="4">
+        <v>46112</v>
+      </c>
+      <c r="S112" s="4">
+        <v>46113</v>
       </c>
       <c r="T112" s="4">
-        <v>46117</v>
+        <v>46113</v>
       </c>
       <c r="V112" s="2" t="s">
         <v>182</v>
       </c>
       <c r="W112" s="2" t="s">
-        <v>275</v>
+        <v>29</v>
       </c>
       <c r="X112" s="2" t="s">
-        <v>99</v>
+        <v>53</v>
       </c>
       <c r="Y112" s="2" t="s">
         <v>58</v>
@@ -9278,13 +9315,13 @@
     </row>
     <row r="113" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A113" s="2" t="s">
-        <v>186</v>
+        <v>149</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>188</v>
+        <v>151</v>
       </c>
       <c r="D113" s="2" t="s">
         <v>34</v>
@@ -9302,7 +9339,7 @@
         <v>28</v>
       </c>
       <c r="I113" s="2" t="s">
-        <v>280</v>
+        <v>175</v>
       </c>
       <c r="J113" s="2">
         <v>1</v>
@@ -9311,25 +9348,35 @@
         <v>1</v>
       </c>
       <c r="L113" s="4">
+        <v>46092</v>
+      </c>
+      <c r="M113" s="12"/>
+      <c r="N113" s="4">
+        <v>46093</v>
+      </c>
+      <c r="O113" s="4">
         <v>46094</v>
       </c>
-      <c r="M113" s="4">
-        <v>46094</v>
-      </c>
-      <c r="P113" s="4">
-        <v>46101</v>
+      <c r="Q113" s="4">
+        <v>46111</v>
+      </c>
+      <c r="R113" s="4">
+        <v>46112</v>
+      </c>
+      <c r="S113" s="4">
+        <v>46113</v>
       </c>
       <c r="T113" s="4">
-        <v>46117</v>
+        <v>46113</v>
       </c>
       <c r="V113" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="W113" s="2" t="s">
-        <v>276</v>
+        <v>29</v>
       </c>
       <c r="X113" s="2" t="s">
-        <v>99</v>
+        <v>53</v>
       </c>
       <c r="Y113" s="2" t="s">
         <v>58</v>
@@ -9337,13 +9384,13 @@
     </row>
     <row r="114" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
-        <v>186</v>
+        <v>149</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>188</v>
+        <v>151</v>
       </c>
       <c r="D114" s="2" t="s">
         <v>34</v>
@@ -9361,7 +9408,7 @@
         <v>28</v>
       </c>
       <c r="I114" s="2" t="s">
-        <v>281</v>
+        <v>176</v>
       </c>
       <c r="J114" s="2">
         <v>1</v>
@@ -9370,25 +9417,35 @@
         <v>1</v>
       </c>
       <c r="L114" s="4">
+        <v>46092</v>
+      </c>
+      <c r="M114" s="12"/>
+      <c r="N114" s="4">
+        <v>46093</v>
+      </c>
+      <c r="O114" s="4">
         <v>46094</v>
       </c>
-      <c r="M114" s="4">
-        <v>46094</v>
-      </c>
-      <c r="P114" s="4">
-        <v>46101</v>
+      <c r="Q114" s="4">
+        <v>46111</v>
+      </c>
+      <c r="R114" s="4">
+        <v>46112</v>
+      </c>
+      <c r="S114" s="4">
+        <v>46113</v>
       </c>
       <c r="T114" s="4">
-        <v>46117</v>
+        <v>46113</v>
       </c>
       <c r="V114" s="2" t="s">
         <v>183</v>
       </c>
       <c r="W114" s="2" t="s">
-        <v>276</v>
+        <v>29</v>
       </c>
       <c r="X114" s="2" t="s">
-        <v>99</v>
+        <v>53</v>
       </c>
       <c r="Y114" s="2" t="s">
         <v>58</v>
@@ -9420,7 +9477,7 @@
         <v>28</v>
       </c>
       <c r="I115" s="2" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="J115" s="2">
         <v>1</v>
@@ -9441,10 +9498,10 @@
         <v>46117</v>
       </c>
       <c r="V115" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="W115" s="2" t="s">
-        <v>130</v>
+        <v>273</v>
       </c>
       <c r="X115" s="2" t="s">
         <v>99</v>
@@ -9478,8 +9535,8 @@
       <c r="H116" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I116" s="13" t="s">
-        <v>283</v>
+      <c r="I116" s="2" t="s">
+        <v>278</v>
       </c>
       <c r="J116" s="2">
         <v>1</v>
@@ -9500,10 +9557,10 @@
         <v>46117</v>
       </c>
       <c r="V116" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="W116" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="X116" s="2" t="s">
         <v>99</v>
@@ -9538,7 +9595,7 @@
         <v>28</v>
       </c>
       <c r="I117" s="2" t="s">
-        <v>189</v>
+        <v>279</v>
       </c>
       <c r="J117" s="2">
         <v>1</v>
@@ -9547,29 +9604,25 @@
         <v>1</v>
       </c>
       <c r="L117" s="4">
-        <v>46098</v>
-      </c>
-      <c r="M117" s="6"/>
-      <c r="N117" s="4">
-        <v>46111</v>
-      </c>
-      <c r="O117" s="4">
-        <v>46112</v>
+        <v>46094</v>
+      </c>
+      <c r="M117" s="4">
+        <v>46094</v>
       </c>
       <c r="P117" s="4">
-        <v>46111</v>
+        <v>46101</v>
       </c>
       <c r="T117" s="4">
-        <v>46126</v>
+        <v>46117</v>
       </c>
       <c r="V117" s="2" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="W117" s="2" t="s">
-        <v>30</v>
+        <v>274</v>
       </c>
       <c r="X117" s="2" t="s">
-        <v>234</v>
+        <v>99</v>
       </c>
       <c r="Y117" s="2" t="s">
         <v>58</v>
@@ -9601,7 +9654,7 @@
         <v>28</v>
       </c>
       <c r="I118" s="2" t="s">
-        <v>190</v>
+        <v>280</v>
       </c>
       <c r="J118" s="2">
         <v>1</v>
@@ -9610,26 +9663,25 @@
         <v>1</v>
       </c>
       <c r="L118" s="4">
-        <v>46098</v>
-      </c>
-      <c r="M118" s="6"/>
-      <c r="N118" s="4">
-        <v>46111</v>
-      </c>
-      <c r="O118" s="4">
-        <v>46112</v>
+        <v>46094</v>
+      </c>
+      <c r="M118" s="4">
+        <v>46094</v>
+      </c>
+      <c r="P118" s="4">
+        <v>46101</v>
       </c>
       <c r="T118" s="4">
-        <v>46126</v>
+        <v>46117</v>
       </c>
       <c r="V118" s="2" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="W118" s="2" t="s">
-        <v>30</v>
+        <v>130</v>
       </c>
       <c r="X118" s="2" t="s">
-        <v>136</v>
+        <v>99</v>
       </c>
       <c r="Y118" s="2" t="s">
         <v>58</v>
@@ -9655,13 +9707,13 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G119" s="7">
-        <v>14.2</v>
+        <v>14.5</v>
       </c>
       <c r="H119" s="2" t="s">
         <v>28</v>
       </c>
       <c r="I119" s="13" t="s">
-        <v>191</v>
+        <v>281</v>
       </c>
       <c r="J119" s="2">
         <v>1</v>
@@ -9670,29 +9722,25 @@
         <v>1</v>
       </c>
       <c r="L119" s="4">
-        <v>46098</v>
-      </c>
-      <c r="M119" s="6"/>
-      <c r="N119" s="4">
-        <v>46111</v>
-      </c>
-      <c r="O119" s="4">
-        <v>46112</v>
+        <v>46094</v>
+      </c>
+      <c r="M119" s="4">
+        <v>46094</v>
       </c>
       <c r="P119" s="4">
-        <v>46111</v>
+        <v>46101</v>
       </c>
       <c r="T119" s="4">
-        <v>46126</v>
+        <v>46117</v>
       </c>
       <c r="V119" s="2" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="W119" s="2" t="s">
-        <v>30</v>
+        <v>274</v>
       </c>
       <c r="X119" s="2" t="s">
-        <v>235</v>
+        <v>99</v>
       </c>
       <c r="Y119" s="2" t="s">
         <v>58</v>
@@ -9709,7 +9757,7 @@
         <v>188</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E120" s="2" t="s">
         <v>27</v>
@@ -9718,13 +9766,13 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G120" s="7">
-        <v>14.2</v>
+        <v>14.5</v>
       </c>
       <c r="H120" s="2" t="s">
         <v>28</v>
       </c>
       <c r="I120" s="2" t="s">
-        <v>222</v>
+        <v>189</v>
       </c>
       <c r="J120" s="2">
         <v>1</v>
@@ -9733,20 +9781,38 @@
         <v>1</v>
       </c>
       <c r="L120" s="4">
-        <v>46104</v>
+        <v>46098</v>
       </c>
       <c r="M120" s="6"/>
       <c r="N120" s="4">
-        <v>46106</v>
+        <v>46111</v>
+      </c>
+      <c r="O120" s="4">
+        <v>46112</v>
+      </c>
+      <c r="P120" s="4">
+        <v>46111</v>
+      </c>
+      <c r="Q120" s="4">
+        <v>46123</v>
+      </c>
+      <c r="R120" s="4">
+        <v>46124</v>
+      </c>
+      <c r="S120" s="4">
+        <v>46126</v>
+      </c>
+      <c r="T120" s="4">
+        <v>46126</v>
       </c>
       <c r="V120" s="2" t="s">
-        <v>147</v>
+        <v>192</v>
       </c>
       <c r="W120" s="2" t="s">
         <v>30</v>
       </c>
       <c r="X120" s="2" t="s">
-        <v>136</v>
+        <v>53</v>
       </c>
       <c r="Y120" s="2" t="s">
         <v>58</v>
@@ -9763,7 +9829,7 @@
         <v>188</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E121" s="2" t="s">
         <v>27</v>
@@ -9772,13 +9838,13 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G121" s="7">
-        <v>14.2</v>
+        <v>14.5</v>
       </c>
       <c r="H121" s="2" t="s">
         <v>28</v>
       </c>
       <c r="I121" s="2" t="s">
-        <v>223</v>
+        <v>190</v>
       </c>
       <c r="J121" s="2">
         <v>1</v>
@@ -9787,20 +9853,38 @@
         <v>1</v>
       </c>
       <c r="L121" s="4">
-        <v>46104</v>
+        <v>46098</v>
       </c>
       <c r="M121" s="6"/>
       <c r="N121" s="4">
-        <v>46106</v>
+        <v>46111</v>
+      </c>
+      <c r="O121" s="4">
+        <v>46112</v>
+      </c>
+      <c r="P121" s="4">
+        <v>46116</v>
+      </c>
+      <c r="Q121" s="4">
+        <v>46123</v>
+      </c>
+      <c r="R121" s="4">
+        <v>46124</v>
+      </c>
+      <c r="S121" s="4">
+        <v>46126</v>
+      </c>
+      <c r="T121" s="4">
+        <v>46126</v>
       </c>
       <c r="V121" s="2" t="s">
-        <v>147</v>
+        <v>192</v>
       </c>
       <c r="W121" s="2" t="s">
         <v>30</v>
       </c>
       <c r="X121" s="2" t="s">
-        <v>136</v>
+        <v>53</v>
       </c>
       <c r="Y121" s="2" t="s">
         <v>58</v>
@@ -9817,7 +9901,7 @@
         <v>188</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>27</v>
@@ -9831,8 +9915,8 @@
       <c r="H122" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I122" s="2" t="s">
-        <v>224</v>
+      <c r="I122" s="13" t="s">
+        <v>191</v>
       </c>
       <c r="J122" s="2">
         <v>1</v>
@@ -9841,20 +9925,38 @@
         <v>1</v>
       </c>
       <c r="L122" s="4">
-        <v>46104</v>
+        <v>46098</v>
       </c>
       <c r="M122" s="6"/>
       <c r="N122" s="4">
-        <v>46106</v>
+        <v>46111</v>
+      </c>
+      <c r="O122" s="4">
+        <v>46112</v>
+      </c>
+      <c r="P122" s="4">
+        <v>46111</v>
+      </c>
+      <c r="Q122" s="4">
+        <v>46124</v>
+      </c>
+      <c r="R122" s="4">
+        <v>46126</v>
+      </c>
+      <c r="S122" s="4">
+        <v>46126</v>
+      </c>
+      <c r="T122" s="4">
+        <v>46126</v>
       </c>
       <c r="V122" s="2" t="s">
-        <v>228</v>
+        <v>192</v>
       </c>
       <c r="W122" s="2" t="s">
         <v>30</v>
       </c>
       <c r="X122" s="2" t="s">
-        <v>136</v>
+        <v>53</v>
       </c>
       <c r="Y122" s="2" t="s">
         <v>58</v>
@@ -9886,7 +9988,7 @@
         <v>28</v>
       </c>
       <c r="I123" s="2" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="J123" s="2">
         <v>1</v>
@@ -9940,7 +10042,7 @@
         <v>28</v>
       </c>
       <c r="I124" s="2" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="J124" s="2">
         <v>1</v>
@@ -9994,7 +10096,7 @@
         <v>28</v>
       </c>
       <c r="I125" s="2" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="J125" s="2">
         <v>1</v>
@@ -10010,7 +10112,7 @@
         <v>46106</v>
       </c>
       <c r="V125" s="2" t="s">
-        <v>147</v>
+        <v>228</v>
       </c>
       <c r="W125" s="2" t="s">
         <v>30</v>
@@ -10024,13 +10126,13 @@
     </row>
     <row r="126" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A126" s="2" t="s">
-        <v>62</v>
+        <v>186</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>63</v>
+        <v>187</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>64</v>
+        <v>188</v>
       </c>
       <c r="D126" s="2" t="s">
         <v>26</v>
@@ -10042,13 +10144,13 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G126" s="7">
-        <v>15</v>
+        <v>14.2</v>
       </c>
       <c r="H126" s="2" t="s">
         <v>28</v>
       </c>
       <c r="I126" s="2" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="J126" s="2">
         <v>1</v>
@@ -10057,16 +10159,11 @@
         <v>1</v>
       </c>
       <c r="L126" s="4">
-        <v>46107</v>
-      </c>
+        <v>46104</v>
+      </c>
+      <c r="M126" s="6"/>
       <c r="N126" s="4">
-        <v>46108</v>
-      </c>
-      <c r="P126" s="4">
-        <v>46116</v>
-      </c>
-      <c r="T126" s="4">
-        <v>46126</v>
+        <v>46106</v>
       </c>
       <c r="V126" s="2" t="s">
         <v>147</v>
@@ -10075,7 +10172,7 @@
         <v>30</v>
       </c>
       <c r="X126" s="2" t="s">
-        <v>99</v>
+        <v>136</v>
       </c>
       <c r="Y126" s="2" t="s">
         <v>58</v>
@@ -10083,13 +10180,13 @@
     </row>
     <row r="127" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A127" s="2" t="s">
-        <v>62</v>
+        <v>186</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>63</v>
+        <v>187</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>64</v>
+        <v>188</v>
       </c>
       <c r="D127" s="2" t="s">
         <v>26</v>
@@ -10101,13 +10198,13 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G127" s="7">
-        <v>15</v>
+        <v>14.2</v>
       </c>
       <c r="H127" s="2" t="s">
         <v>28</v>
       </c>
       <c r="I127" s="2" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="J127" s="2">
         <v>1</v>
@@ -10116,16 +10213,11 @@
         <v>1</v>
       </c>
       <c r="L127" s="4">
-        <v>46107</v>
-      </c>
+        <v>46104</v>
+      </c>
+      <c r="M127" s="6"/>
       <c r="N127" s="4">
-        <v>46108</v>
-      </c>
-      <c r="P127" s="4">
-        <v>46116</v>
-      </c>
-      <c r="T127" s="4">
-        <v>46126</v>
+        <v>46106</v>
       </c>
       <c r="V127" s="2" t="s">
         <v>147</v>
@@ -10134,7 +10226,7 @@
         <v>30</v>
       </c>
       <c r="X127" s="2" t="s">
-        <v>99</v>
+        <v>136</v>
       </c>
       <c r="Y127" s="2" t="s">
         <v>58</v>
@@ -10142,13 +10234,13 @@
     </row>
     <row r="128" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A128" s="2" t="s">
-        <v>62</v>
+        <v>186</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>63</v>
+        <v>187</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>64</v>
+        <v>188</v>
       </c>
       <c r="D128" s="2" t="s">
         <v>26</v>
@@ -10160,13 +10252,13 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G128" s="7">
-        <v>15</v>
+        <v>14.2</v>
       </c>
       <c r="H128" s="2" t="s">
         <v>28</v>
       </c>
       <c r="I128" s="2" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="J128" s="2">
         <v>1</v>
@@ -10175,16 +10267,11 @@
         <v>1</v>
       </c>
       <c r="L128" s="4">
-        <v>46107</v>
-      </c>
+        <v>46104</v>
+      </c>
+      <c r="M128" s="6"/>
       <c r="N128" s="4">
-        <v>46108</v>
-      </c>
-      <c r="P128" s="4">
-        <v>46116</v>
-      </c>
-      <c r="T128" s="4">
-        <v>46126</v>
+        <v>46106</v>
       </c>
       <c r="V128" s="2" t="s">
         <v>147</v>
@@ -10193,7 +10280,7 @@
         <v>30</v>
       </c>
       <c r="X128" s="2" t="s">
-        <v>99</v>
+        <v>136</v>
       </c>
       <c r="Y128" s="2" t="s">
         <v>58</v>
@@ -10225,7 +10312,7 @@
         <v>28</v>
       </c>
       <c r="I129" s="2" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="J129" s="2">
         <v>1</v>
@@ -10242,6 +10329,15 @@
       <c r="P129" s="4">
         <v>46116</v>
       </c>
+      <c r="Q129" s="4">
+        <v>46122</v>
+      </c>
+      <c r="R129" s="4">
+        <v>46125</v>
+      </c>
+      <c r="S129" s="4">
+        <v>46126</v>
+      </c>
       <c r="T129" s="4">
         <v>46126</v>
       </c>
@@ -10252,7 +10348,7 @@
         <v>30</v>
       </c>
       <c r="X129" s="2" t="s">
-        <v>99</v>
+        <v>53</v>
       </c>
       <c r="Y129" s="2" t="s">
         <v>58</v>
@@ -10284,7 +10380,7 @@
         <v>28</v>
       </c>
       <c r="I130" s="2" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="J130" s="2">
         <v>1</v>
@@ -10301,6 +10397,15 @@
       <c r="P130" s="4">
         <v>46116</v>
       </c>
+      <c r="Q130" s="4">
+        <v>46122</v>
+      </c>
+      <c r="R130" s="4">
+        <v>46125</v>
+      </c>
+      <c r="S130" s="4">
+        <v>46126</v>
+      </c>
       <c r="T130" s="4">
         <v>46126</v>
       </c>
@@ -10311,7 +10416,7 @@
         <v>30</v>
       </c>
       <c r="X130" s="2" t="s">
-        <v>99</v>
+        <v>53</v>
       </c>
       <c r="Y130" s="2" t="s">
         <v>58</v>
@@ -10319,31 +10424,31 @@
     </row>
     <row r="131" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A131" s="2" t="s">
-        <v>236</v>
+        <v>62</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>237</v>
+        <v>63</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>238</v>
+        <v>64</v>
       </c>
       <c r="D131" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F131" s="3">
-        <v>0.43</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="G131" s="7">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="H131" s="2" t="s">
-        <v>239</v>
+        <v>28</v>
       </c>
       <c r="I131" s="2" t="s">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="J131" s="2">
         <v>1</v>
@@ -10352,72 +10457,66 @@
         <v>1</v>
       </c>
       <c r="L131" s="4">
-        <v>45896</v>
+        <v>46107</v>
       </c>
       <c r="N131" s="4">
-        <v>45897</v>
-      </c>
-      <c r="O131" s="4">
-        <v>45897</v>
+        <v>46108</v>
       </c>
       <c r="P131" s="4">
-        <v>45897</v>
+        <v>46116</v>
       </c>
       <c r="Q131" s="4">
-        <v>45903</v>
+        <v>46122</v>
       </c>
       <c r="R131" s="4">
-        <v>45905</v>
+        <v>46125</v>
       </c>
       <c r="S131" s="4">
-        <v>45908</v>
+        <v>46126</v>
       </c>
       <c r="T131" s="4">
-        <v>45908</v>
+        <v>46126</v>
       </c>
       <c r="V131" s="2" t="s">
-        <v>133</v>
+        <v>147</v>
       </c>
       <c r="W131" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="X131" s="2" t="s">
         <v>53</v>
       </c>
       <c r="Y131" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="Z131" s="4">
-        <v>46112</v>
+        <v>58</v>
       </c>
     </row>
     <row r="132" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A132" s="2" t="s">
-        <v>236</v>
+        <v>62</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>237</v>
+        <v>63</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>238</v>
+        <v>64</v>
       </c>
       <c r="D132" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F132" s="3">
-        <v>0.43</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="G132" s="7">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="H132" s="2" t="s">
-        <v>239</v>
+        <v>28</v>
       </c>
       <c r="I132" s="2" t="s">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="J132" s="2">
         <v>1</v>
@@ -10426,72 +10525,66 @@
         <v>1</v>
       </c>
       <c r="L132" s="4">
-        <v>45896</v>
+        <v>46107</v>
       </c>
       <c r="N132" s="4">
-        <v>45897</v>
-      </c>
-      <c r="O132" s="4">
-        <v>45897</v>
+        <v>46108</v>
       </c>
       <c r="P132" s="4">
-        <v>45897</v>
+        <v>46116</v>
       </c>
       <c r="Q132" s="4">
-        <v>45903</v>
+        <v>46122</v>
       </c>
       <c r="R132" s="4">
-        <v>45905</v>
+        <v>46125</v>
       </c>
       <c r="S132" s="4">
-        <v>45908</v>
+        <v>46126</v>
       </c>
       <c r="T132" s="4">
-        <v>45908</v>
+        <v>46126</v>
       </c>
       <c r="V132" s="2" t="s">
-        <v>133</v>
+        <v>147</v>
       </c>
       <c r="W132" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="X132" s="2" t="s">
         <v>53</v>
       </c>
       <c r="Y132" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="Z132" s="4">
-        <v>46112</v>
+        <v>58</v>
       </c>
     </row>
     <row r="133" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A133" s="2" t="s">
-        <v>236</v>
+        <v>62</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>237</v>
+        <v>63</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>238</v>
+        <v>64</v>
       </c>
       <c r="D133" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F133" s="3">
-        <v>0.43</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="G133" s="7">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="H133" s="2" t="s">
-        <v>239</v>
+        <v>28</v>
       </c>
       <c r="I133" s="2" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="J133" s="2">
         <v>1</v>
@@ -10500,54 +10593,48 @@
         <v>1</v>
       </c>
       <c r="L133" s="4">
-        <v>45944</v>
+        <v>46107</v>
       </c>
       <c r="N133" s="4">
-        <v>45945</v>
-      </c>
-      <c r="O133" s="4">
-        <v>45947</v>
+        <v>46108</v>
       </c>
       <c r="P133" s="4">
-        <v>45950</v>
+        <v>46116</v>
       </c>
       <c r="Q133" s="4">
-        <v>45954</v>
+        <v>46122</v>
       </c>
       <c r="R133" s="4">
-        <v>45957</v>
+        <v>46125</v>
       </c>
       <c r="S133" s="4">
-        <v>45958</v>
+        <v>46126</v>
       </c>
       <c r="T133" s="4">
-        <v>45958</v>
+        <v>46126</v>
       </c>
       <c r="V133" s="2" t="s">
-        <v>133</v>
+        <v>147</v>
       </c>
       <c r="W133" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="X133" s="2" t="s">
         <v>53</v>
       </c>
       <c r="Y133" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="Z133" s="4">
-        <v>46112</v>
+        <v>58</v>
       </c>
     </row>
     <row r="134" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A134" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="C134" s="2" t="s">
         <v>236</v>
-      </c>
-      <c r="B134" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="C134" s="2" t="s">
-        <v>238</v>
       </c>
       <c r="D134" s="2" t="s">
         <v>26</v>
@@ -10562,10 +10649,10 @@
         <v>14.5</v>
       </c>
       <c r="H134" s="2" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="I134" s="2" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="J134" s="2">
         <v>1</v>
@@ -10574,28 +10661,28 @@
         <v>1</v>
       </c>
       <c r="L134" s="4">
-        <v>45944</v>
+        <v>45896</v>
       </c>
       <c r="N134" s="4">
-        <v>45945</v>
+        <v>45897</v>
       </c>
       <c r="O134" s="4">
-        <v>45947</v>
+        <v>45897</v>
       </c>
       <c r="P134" s="4">
-        <v>45950</v>
+        <v>45897</v>
       </c>
       <c r="Q134" s="4">
-        <v>45954</v>
+        <v>45903</v>
       </c>
       <c r="R134" s="4">
-        <v>45957</v>
+        <v>45905</v>
       </c>
       <c r="S134" s="4">
-        <v>45958</v>
+        <v>45908</v>
       </c>
       <c r="T134" s="4">
-        <v>45958</v>
+        <v>45908</v>
       </c>
       <c r="V134" s="2" t="s">
         <v>133</v>
@@ -10615,13 +10702,13 @@
     </row>
     <row r="135" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A135" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="B135" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="C135" s="2" t="s">
         <v>236</v>
-      </c>
-      <c r="B135" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="C135" s="2" t="s">
-        <v>238</v>
       </c>
       <c r="D135" s="2" t="s">
         <v>26</v>
@@ -10636,11 +10723,11 @@
         <v>14.5</v>
       </c>
       <c r="H135" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="I135" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="I135" s="2" t="s">
-        <v>244</v>
-      </c>
       <c r="J135" s="2">
         <v>1</v>
       </c>
@@ -10648,28 +10735,28 @@
         <v>1</v>
       </c>
       <c r="L135" s="4">
-        <v>46024</v>
+        <v>45896</v>
       </c>
       <c r="N135" s="4">
-        <v>46044</v>
+        <v>45897</v>
       </c>
       <c r="O135" s="4">
-        <v>46044</v>
+        <v>45897</v>
       </c>
       <c r="P135" s="4">
-        <v>46045</v>
+        <v>45897</v>
       </c>
       <c r="Q135" s="4">
-        <v>46052</v>
+        <v>45903</v>
       </c>
       <c r="R135" s="4">
-        <v>46055</v>
+        <v>45905</v>
       </c>
       <c r="S135" s="4">
-        <v>46058</v>
+        <v>45908</v>
       </c>
       <c r="T135" s="4">
-        <v>46058</v>
+        <v>45908</v>
       </c>
       <c r="V135" s="2" t="s">
         <v>133</v>
@@ -10689,13 +10776,13 @@
     </row>
     <row r="136" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A136" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="B136" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="C136" s="2" t="s">
         <v>236</v>
-      </c>
-      <c r="B136" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="C136" s="2" t="s">
-        <v>238</v>
       </c>
       <c r="D136" s="2" t="s">
         <v>26</v>
@@ -10710,10 +10797,10 @@
         <v>14.5</v>
       </c>
       <c r="H136" s="2" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="I136" s="2" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="J136" s="2">
         <v>1</v>
@@ -10722,28 +10809,28 @@
         <v>1</v>
       </c>
       <c r="L136" s="4">
-        <v>46024</v>
+        <v>45944</v>
       </c>
       <c r="N136" s="4">
-        <v>46044</v>
+        <v>45945</v>
       </c>
       <c r="O136" s="4">
-        <v>46044</v>
+        <v>45947</v>
       </c>
       <c r="P136" s="4">
-        <v>46045</v>
+        <v>45950</v>
       </c>
       <c r="Q136" s="4">
-        <v>46052</v>
+        <v>45954</v>
       </c>
       <c r="R136" s="4">
-        <v>46055</v>
+        <v>45957</v>
       </c>
       <c r="S136" s="4">
-        <v>46058</v>
+        <v>45958</v>
       </c>
       <c r="T136" s="4">
-        <v>46058</v>
+        <v>45958</v>
       </c>
       <c r="V136" s="2" t="s">
         <v>133</v>
@@ -10763,31 +10850,31 @@
     </row>
     <row r="137" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A137" s="2" t="s">
-        <v>258</v>
+        <v>234</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>259</v>
+        <v>235</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>260</v>
+        <v>236</v>
       </c>
       <c r="D137" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>261</v>
+        <v>32</v>
       </c>
       <c r="F137" s="3">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="G137" s="7">
         <v>14.5</v>
       </c>
       <c r="H137" s="2" t="s">
-        <v>131</v>
+        <v>237</v>
       </c>
       <c r="I137" s="2" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="J137" s="2">
         <v>1</v>
@@ -10796,31 +10883,31 @@
         <v>1</v>
       </c>
       <c r="L137" s="4">
-        <v>46104</v>
+        <v>45944</v>
       </c>
       <c r="N137" s="4">
-        <v>46105</v>
+        <v>45945</v>
       </c>
       <c r="O137" s="4">
-        <v>46110</v>
+        <v>45947</v>
       </c>
       <c r="P137" s="4">
-        <v>46111</v>
+        <v>45950</v>
       </c>
       <c r="Q137" s="4">
-        <v>46112</v>
+        <v>45954</v>
       </c>
       <c r="R137" s="4">
-        <v>46115</v>
+        <v>45957</v>
       </c>
       <c r="S137" s="4">
-        <v>46118</v>
+        <v>45958</v>
       </c>
       <c r="T137" s="4">
-        <v>46118</v>
+        <v>45958</v>
       </c>
       <c r="V137" s="2" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="W137" s="2" t="s">
         <v>29</v>
@@ -10829,36 +10916,39 @@
         <v>53</v>
       </c>
       <c r="Y137" s="2" t="s">
-        <v>141</v>
+        <v>33</v>
+      </c>
+      <c r="Z137" s="4">
+        <v>46112</v>
       </c>
     </row>
     <row r="138" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A138" s="2" t="s">
-        <v>258</v>
+        <v>234</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>259</v>
+        <v>235</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>260</v>
+        <v>236</v>
       </c>
       <c r="D138" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>261</v>
+        <v>32</v>
       </c>
       <c r="F138" s="3">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="G138" s="7">
         <v>14.5</v>
       </c>
       <c r="H138" s="2" t="s">
-        <v>131</v>
+        <v>237</v>
       </c>
       <c r="I138" s="2" t="s">
-        <v>256</v>
+        <v>242</v>
       </c>
       <c r="J138" s="2">
         <v>1</v>
@@ -10867,31 +10957,31 @@
         <v>1</v>
       </c>
       <c r="L138" s="4">
-        <v>46104</v>
+        <v>46024</v>
       </c>
       <c r="N138" s="4">
-        <v>46105</v>
+        <v>46044</v>
       </c>
       <c r="O138" s="4">
-        <v>46110</v>
+        <v>46044</v>
       </c>
       <c r="P138" s="4">
-        <v>46111</v>
+        <v>46045</v>
       </c>
       <c r="Q138" s="4">
-        <v>46112</v>
+        <v>46052</v>
       </c>
       <c r="R138" s="4">
-        <v>46115</v>
+        <v>46055</v>
       </c>
       <c r="S138" s="4">
-        <v>46118</v>
+        <v>46058</v>
       </c>
       <c r="T138" s="4">
-        <v>46118</v>
+        <v>46058</v>
       </c>
       <c r="V138" s="2" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="W138" s="2" t="s">
         <v>29</v>
@@ -10900,36 +10990,39 @@
         <v>53</v>
       </c>
       <c r="Y138" s="2" t="s">
-        <v>141</v>
+        <v>33</v>
+      </c>
+      <c r="Z138" s="4">
+        <v>46112</v>
       </c>
     </row>
     <row r="139" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A139" s="2" t="s">
-        <v>258</v>
+        <v>234</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>259</v>
+        <v>235</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>260</v>
+        <v>236</v>
       </c>
       <c r="D139" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>261</v>
+        <v>32</v>
       </c>
       <c r="F139" s="3">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="G139" s="7">
         <v>14.5</v>
       </c>
       <c r="H139" s="2" t="s">
-        <v>131</v>
+        <v>237</v>
       </c>
       <c r="I139" s="2" t="s">
-        <v>257</v>
+        <v>243</v>
       </c>
       <c r="J139" s="2">
         <v>1</v>
@@ -10938,31 +11031,31 @@
         <v>1</v>
       </c>
       <c r="L139" s="4">
-        <v>46104</v>
+        <v>46024</v>
       </c>
       <c r="N139" s="4">
-        <v>46105</v>
+        <v>46044</v>
       </c>
       <c r="O139" s="4">
-        <v>46110</v>
+        <v>46044</v>
       </c>
       <c r="P139" s="4">
-        <v>46111</v>
+        <v>46045</v>
       </c>
       <c r="Q139" s="4">
-        <v>46112</v>
+        <v>46052</v>
       </c>
       <c r="R139" s="4">
-        <v>46115</v>
+        <v>46055</v>
       </c>
       <c r="S139" s="4">
-        <v>46118</v>
+        <v>46058</v>
       </c>
       <c r="T139" s="4">
-        <v>46118</v>
+        <v>46058</v>
       </c>
       <c r="V139" s="2" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="W139" s="2" t="s">
         <v>29</v>
@@ -10971,36 +11064,39 @@
         <v>53</v>
       </c>
       <c r="Y139" s="2" t="s">
-        <v>141</v>
+        <v>33</v>
+      </c>
+      <c r="Z139" s="4">
+        <v>46112</v>
       </c>
     </row>
     <row r="140" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A140" s="2" t="s">
-        <v>269</v>
+        <v>256</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>270</v>
+        <v>257</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>84</v>
+        <v>258</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>27</v>
+        <v>259</v>
       </c>
       <c r="F140" s="3">
-        <v>0.55000000000000004</v>
+        <v>0.45</v>
       </c>
       <c r="G140" s="7">
         <v>14.5</v>
       </c>
       <c r="H140" s="2" t="s">
-        <v>28</v>
+        <v>131</v>
       </c>
       <c r="I140" s="2" t="s">
-        <v>271</v>
+        <v>253</v>
       </c>
       <c r="J140" s="2">
         <v>1</v>
@@ -11009,25 +11105,37 @@
         <v>1</v>
       </c>
       <c r="L140" s="4">
+        <v>46104</v>
+      </c>
+      <c r="N140" s="4">
+        <v>46105</v>
+      </c>
+      <c r="O140" s="4">
+        <v>46110</v>
+      </c>
+      <c r="P140" s="4">
         <v>46111</v>
       </c>
-      <c r="N140" s="4">
-        <v>46111</v>
-      </c>
-      <c r="P140" s="4">
-        <v>46116</v>
+      <c r="Q140" s="4">
+        <v>46112</v>
+      </c>
+      <c r="R140" s="4">
+        <v>46115</v>
+      </c>
+      <c r="S140" s="4">
+        <v>46118</v>
       </c>
       <c r="T140" s="4">
-        <v>46126</v>
+        <v>46118</v>
       </c>
       <c r="V140" s="2" t="s">
-        <v>273</v>
+        <v>147</v>
       </c>
       <c r="W140" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X140" s="2" t="s">
-        <v>99</v>
+        <v>53</v>
       </c>
       <c r="Y140" s="2" t="s">
         <v>141</v>
@@ -11035,31 +11143,31 @@
     </row>
     <row r="141" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A141" s="2" t="s">
-        <v>269</v>
+        <v>256</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>270</v>
+        <v>257</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>84</v>
+        <v>258</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>27</v>
+        <v>259</v>
       </c>
       <c r="F141" s="3">
-        <v>0.55000000000000004</v>
+        <v>0.45</v>
       </c>
       <c r="G141" s="7">
         <v>14.5</v>
       </c>
       <c r="H141" s="2" t="s">
-        <v>28</v>
+        <v>131</v>
       </c>
       <c r="I141" s="2" t="s">
-        <v>272</v>
+        <v>254</v>
       </c>
       <c r="J141" s="2">
         <v>1</v>
@@ -11068,211 +11176,1186 @@
         <v>1</v>
       </c>
       <c r="L141" s="4">
+        <v>46104</v>
+      </c>
+      <c r="N141" s="4">
+        <v>46105</v>
+      </c>
+      <c r="O141" s="4">
+        <v>46110</v>
+      </c>
+      <c r="P141" s="4">
         <v>46111</v>
       </c>
-      <c r="N141" s="4">
-        <v>46111</v>
-      </c>
-      <c r="P141" s="4">
-        <v>46116</v>
+      <c r="Q141" s="4">
+        <v>46112</v>
+      </c>
+      <c r="R141" s="4">
+        <v>46115</v>
+      </c>
+      <c r="S141" s="4">
+        <v>46118</v>
       </c>
       <c r="T141" s="4">
-        <v>46126</v>
+        <v>46118</v>
       </c>
       <c r="V141" s="2" t="s">
-        <v>274</v>
+        <v>147</v>
       </c>
       <c r="W141" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X141" s="2" t="s">
-        <v>99</v>
+        <v>53</v>
       </c>
       <c r="Y141" s="2" t="s">
         <v>141</v>
       </c>
     </row>
+    <row r="142" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A142" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="B142" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="C142" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="D142" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E142" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="F142" s="3">
+        <v>0.45</v>
+      </c>
+      <c r="G142" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="H142" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="I142" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="J142" s="2">
+        <v>1</v>
+      </c>
+      <c r="K142" s="2">
+        <v>1</v>
+      </c>
+      <c r="L142" s="4">
+        <v>46104</v>
+      </c>
+      <c r="N142" s="4">
+        <v>46105</v>
+      </c>
+      <c r="O142" s="4">
+        <v>46110</v>
+      </c>
+      <c r="P142" s="4">
+        <v>46111</v>
+      </c>
+      <c r="Q142" s="4">
+        <v>46112</v>
+      </c>
+      <c r="R142" s="4">
+        <v>46115</v>
+      </c>
+      <c r="S142" s="4">
+        <v>46118</v>
+      </c>
+      <c r="T142" s="4">
+        <v>46118</v>
+      </c>
+      <c r="V142" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="W142" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="X142" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y142" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="143" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A143" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="B143" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="C143" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D143" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E143" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F143" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G143" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="H143" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I143" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="J143" s="2">
+        <v>1</v>
+      </c>
+      <c r="K143" s="2">
+        <v>1</v>
+      </c>
+      <c r="L143" s="4">
+        <v>46111</v>
+      </c>
+      <c r="N143" s="4">
+        <v>46111</v>
+      </c>
+      <c r="P143" s="4">
+        <v>46116</v>
+      </c>
+      <c r="Q143" s="4">
+        <v>46124</v>
+      </c>
+      <c r="R143" s="4">
+        <v>46125</v>
+      </c>
+      <c r="S143" s="4">
+        <v>46126</v>
+      </c>
+      <c r="T143" s="4">
+        <v>46126</v>
+      </c>
+      <c r="V143" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="W143" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X143" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y143" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="144" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A144" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="B144" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="C144" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D144" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E144" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F144" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G144" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="H144" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I144" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="J144" s="2">
+        <v>1</v>
+      </c>
+      <c r="K144" s="2">
+        <v>1</v>
+      </c>
+      <c r="L144" s="4">
+        <v>46111</v>
+      </c>
+      <c r="N144" s="4">
+        <v>46111</v>
+      </c>
+      <c r="P144" s="4">
+        <v>46116</v>
+      </c>
+      <c r="Q144" s="4">
+        <v>46124</v>
+      </c>
+      <c r="R144" s="4">
+        <v>46125</v>
+      </c>
+      <c r="S144" s="4">
+        <v>46126</v>
+      </c>
+      <c r="T144" s="4">
+        <v>46126</v>
+      </c>
+      <c r="V144" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="W144" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X144" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y144" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="145" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A145" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B145" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="C145" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="D145" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E145" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F145" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G145" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="H145" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I145" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="J145" s="2">
+        <v>1</v>
+      </c>
+      <c r="K145" s="2">
+        <v>1</v>
+      </c>
+      <c r="L145" s="4">
+        <v>46062</v>
+      </c>
+      <c r="N145" s="4">
+        <v>46063</v>
+      </c>
+      <c r="O145" s="4">
+        <v>46119</v>
+      </c>
+      <c r="P145" s="4">
+        <v>46126</v>
+      </c>
+      <c r="V145" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="W145" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X145" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y145" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="146" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A146" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B146" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="C146" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="D146" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E146" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F146" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G146" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="H146" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I146" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="J146" s="2">
+        <v>1</v>
+      </c>
+      <c r="K146" s="2">
+        <v>1</v>
+      </c>
+      <c r="L146" s="4">
+        <v>46062</v>
+      </c>
+      <c r="M146" s="16"/>
+      <c r="N146" s="4">
+        <v>46063</v>
+      </c>
+      <c r="O146" s="4">
+        <v>46119</v>
+      </c>
+      <c r="P146" s="4">
+        <v>46126</v>
+      </c>
+      <c r="V146" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="W146" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X146" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y146" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="147" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A147" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B147" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C147" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D147" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E147" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F147" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G147" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="H147" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I147" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="J147" s="2">
+        <v>1</v>
+      </c>
+      <c r="K147" s="2">
+        <v>2</v>
+      </c>
+      <c r="L147" s="4">
+        <v>46092</v>
+      </c>
+      <c r="M147" s="16">
+        <v>46114</v>
+      </c>
+      <c r="N147" s="4">
+        <v>46121</v>
+      </c>
+      <c r="O147" s="4">
+        <v>46121</v>
+      </c>
+      <c r="P147" s="4">
+        <v>46127</v>
+      </c>
+      <c r="V147" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="W147" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X147" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="Y147" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="148" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A148" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B148" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C148" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D148" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E148" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F148" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G148" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="H148" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I148" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="J148" s="2">
+        <v>1</v>
+      </c>
+      <c r="K148" s="2">
+        <v>2</v>
+      </c>
+      <c r="L148" s="4">
+        <v>46092</v>
+      </c>
+      <c r="M148" s="16">
+        <v>46114</v>
+      </c>
+      <c r="N148" s="4">
+        <v>46121</v>
+      </c>
+      <c r="O148" s="4">
+        <v>46121</v>
+      </c>
+      <c r="P148" s="4">
+        <v>46127</v>
+      </c>
+      <c r="V148" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="W148" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X148" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="Y148" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="149" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A149" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B149" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C149" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D149" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E149" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F149" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G149" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="H149" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I149" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="J149" s="2">
+        <v>1</v>
+      </c>
+      <c r="K149" s="2">
+        <v>2</v>
+      </c>
+      <c r="L149" s="4">
+        <v>46092</v>
+      </c>
+      <c r="M149" s="16">
+        <v>46114</v>
+      </c>
+      <c r="N149" s="4">
+        <v>46121</v>
+      </c>
+      <c r="O149" s="4">
+        <v>46121</v>
+      </c>
+      <c r="P149" s="4">
+        <v>46127</v>
+      </c>
+      <c r="V149" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="W149" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X149" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="Y149" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="150" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A150" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B150" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C150" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D150" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E150" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F150" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G150" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="H150" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I150" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="J150" s="2">
+        <v>1</v>
+      </c>
+      <c r="K150" s="2">
+        <v>2</v>
+      </c>
+      <c r="L150" s="4">
+        <v>46092</v>
+      </c>
+      <c r="M150" s="16">
+        <v>46114</v>
+      </c>
+      <c r="N150" s="4">
+        <v>46121</v>
+      </c>
+      <c r="O150" s="4">
+        <v>46121</v>
+      </c>
+      <c r="P150" s="4">
+        <v>46127</v>
+      </c>
+      <c r="V150" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="W150" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X150" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="Y150" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="151" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A151" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="B151" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C151" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="D151" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E151" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F151" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G151" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="H151" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I151" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="J151" s="2">
+        <v>1</v>
+      </c>
+      <c r="K151" s="2">
+        <v>1</v>
+      </c>
+      <c r="L151" s="4">
+        <v>46119</v>
+      </c>
+      <c r="M151" s="16"/>
+      <c r="N151" s="4">
+        <v>46063</v>
+      </c>
+      <c r="O151" s="4">
+        <v>46119</v>
+      </c>
+      <c r="P151" s="4">
+        <v>46125</v>
+      </c>
+      <c r="V151" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="W151" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X151" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="Y151" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="152" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A152" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="B152" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C152" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="D152" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E152" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F152" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G152" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="H152" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I152" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="J152" s="2">
+        <v>1</v>
+      </c>
+      <c r="K152" s="2">
+        <v>1</v>
+      </c>
+      <c r="L152" s="4">
+        <v>46119</v>
+      </c>
+      <c r="M152" s="16"/>
+      <c r="N152" s="4">
+        <v>46063</v>
+      </c>
+      <c r="O152" s="4">
+        <v>46119</v>
+      </c>
+      <c r="P152" s="4">
+        <v>46125</v>
+      </c>
+      <c r="V152" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="W152" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X152" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="Y152" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="153" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A153" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B153" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="C153" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="D153" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E153" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F153" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G153" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="H153" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I153" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="J153" s="2">
+        <v>1</v>
+      </c>
+      <c r="K153" s="2">
+        <v>1</v>
+      </c>
+      <c r="L153" s="4">
+        <v>46062</v>
+      </c>
+      <c r="N153" s="4">
+        <v>46063</v>
+      </c>
+      <c r="O153" s="4">
+        <v>46119</v>
+      </c>
+      <c r="P153" s="4">
+        <v>46126</v>
+      </c>
+      <c r="V153" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="W153" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X153" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="Y153" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="154" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A154" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B154" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="C154" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D154" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E154" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F154" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G154" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="H154" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I154" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="J154" s="2">
+        <v>1</v>
+      </c>
+      <c r="K154" s="2">
+        <v>1</v>
+      </c>
+      <c r="L154" s="4">
+        <v>46105</v>
+      </c>
+      <c r="N154" s="4">
+        <v>46121</v>
+      </c>
+      <c r="O154" s="4">
+        <v>46122</v>
+      </c>
+      <c r="P154" s="4">
+        <v>46126</v>
+      </c>
+      <c r="V154" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="W154" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X154" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="Y154" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="155" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A155" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B155" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="C155" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="D155" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E155" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F155" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G155" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="H155" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I155" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="J155" s="2">
+        <v>1</v>
+      </c>
+      <c r="K155" s="2">
+        <v>1</v>
+      </c>
+      <c r="L155" s="4">
+        <v>46106</v>
+      </c>
+      <c r="N155" s="4">
+        <v>46108</v>
+      </c>
+      <c r="O155" s="4">
+        <v>46111</v>
+      </c>
+      <c r="P155" s="4">
+        <v>46126</v>
+      </c>
+      <c r="Q155" s="4">
+        <v>46126</v>
+      </c>
+      <c r="R155" s="4">
+        <v>46127</v>
+      </c>
+      <c r="S155" s="4">
+        <v>46128</v>
+      </c>
+      <c r="T155" s="4">
+        <v>46128</v>
+      </c>
+      <c r="V155" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="W155" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X155" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y155" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="156" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A156" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B156" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="C156" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="D156" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E156" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F156" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G156" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="H156" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I156" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="J156" s="2">
+        <v>1</v>
+      </c>
+      <c r="K156" s="2">
+        <v>1</v>
+      </c>
+      <c r="L156" s="4">
+        <v>46106</v>
+      </c>
+      <c r="N156" s="4">
+        <v>46108</v>
+      </c>
+      <c r="O156" s="4">
+        <v>46111</v>
+      </c>
+      <c r="P156" s="4">
+        <v>46126</v>
+      </c>
+      <c r="Q156" s="4">
+        <v>46126</v>
+      </c>
+      <c r="R156" s="4">
+        <v>46127</v>
+      </c>
+      <c r="S156" s="4">
+        <v>46128</v>
+      </c>
+      <c r="T156" s="4">
+        <v>46128</v>
+      </c>
+      <c r="V156" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="W156" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X156" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y156" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="157" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="V157" s="4"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AB141"/>
+  <autoFilter ref="A1:AB156"/>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="I65:I72">
-    <cfRule type="expression" dxfId="23" priority="6" stopIfTrue="1">
-      <formula>$E3107:$E1048576="sub"</formula>
+  <conditionalFormatting sqref="I84">
+    <cfRule type="expression" dxfId="23" priority="73" stopIfTrue="1">
+      <formula>$E11:$E3144="sub"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I81">
-    <cfRule type="expression" dxfId="22" priority="73" stopIfTrue="1">
-      <formula>$E11:$E3141="sub"</formula>
+  <conditionalFormatting sqref="I99">
+    <cfRule type="expression" dxfId="22" priority="96" stopIfTrue="1">
+      <formula>$E14:$E3147="sub"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I98">
+    <cfRule type="expression" dxfId="21" priority="102" stopIfTrue="1">
+      <formula>$E14:$E3147="sub"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I97">
+    <cfRule type="expression" dxfId="20" priority="108" stopIfTrue="1">
+      <formula>$E14:$E3147="sub"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I96">
-    <cfRule type="expression" dxfId="21" priority="96" stopIfTrue="1">
-      <formula>$E14:$E3144="sub"</formula>
+    <cfRule type="expression" dxfId="19" priority="114" stopIfTrue="1">
+      <formula>$E14:$E3147="sub"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I95">
-    <cfRule type="expression" dxfId="20" priority="102" stopIfTrue="1">
-      <formula>$E14:$E3144="sub"</formula>
+    <cfRule type="expression" dxfId="18" priority="120" stopIfTrue="1">
+      <formula>$E14:$E3147="sub"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I94">
-    <cfRule type="expression" dxfId="19" priority="108" stopIfTrue="1">
-      <formula>$E14:$E3144="sub"</formula>
+    <cfRule type="expression" dxfId="17" priority="126" stopIfTrue="1">
+      <formula>$E14:$E3147="sub"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I106">
+    <cfRule type="expression" dxfId="16" priority="150" stopIfTrue="1">
+      <formula>$E15:$E3148="sub"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I105">
+    <cfRule type="expression" dxfId="15" priority="157" stopIfTrue="1">
+      <formula>$E15:$E3148="sub"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I104">
+    <cfRule type="expression" dxfId="14" priority="164" stopIfTrue="1">
+      <formula>$E15:$E3148="sub"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I103">
+    <cfRule type="expression" dxfId="13" priority="171" stopIfTrue="1">
+      <formula>$E15:$E3148="sub"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I102">
+    <cfRule type="expression" dxfId="12" priority="178" stopIfTrue="1">
+      <formula>$E15:$E3148="sub"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I85 I83">
+    <cfRule type="expression" dxfId="11" priority="1" stopIfTrue="1">
+      <formula>$E11:$E3145="sub"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I93">
-    <cfRule type="expression" dxfId="18" priority="114" stopIfTrue="1">
-      <formula>$E14:$E3144="sub"</formula>
+    <cfRule type="expression" dxfId="10" priority="282" stopIfTrue="1">
+      <formula>$E14:$E3147="sub"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I92">
-    <cfRule type="expression" dxfId="17" priority="120" stopIfTrue="1">
-      <formula>$E14:$E3144="sub"</formula>
+  <conditionalFormatting sqref="I82">
+    <cfRule type="expression" dxfId="9" priority="294" stopIfTrue="1">
+      <formula>$E8:$E3144="sub"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I91">
-    <cfRule type="expression" dxfId="16" priority="126" stopIfTrue="1">
-      <formula>$E14:$E3144="sub"</formula>
+  <conditionalFormatting sqref="I110">
+    <cfRule type="expression" dxfId="8" priority="360" stopIfTrue="1">
+      <formula>$E17:$E3150="sub"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I103">
-    <cfRule type="expression" dxfId="15" priority="150" stopIfTrue="1">
-      <formula>$E15:$E3145="sub"</formula>
+  <conditionalFormatting sqref="I68:I75">
+    <cfRule type="expression" dxfId="7" priority="412" stopIfTrue="1">
+      <formula>$E1:$E3110="sub"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I102">
-    <cfRule type="expression" dxfId="14" priority="157" stopIfTrue="1">
-      <formula>$E15:$E3145="sub"</formula>
+  <conditionalFormatting sqref="I107:I109">
+    <cfRule type="expression" dxfId="6" priority="413" stopIfTrue="1">
+      <formula>$E15:$E3148="sub"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I101">
-    <cfRule type="expression" dxfId="13" priority="164" stopIfTrue="1">
-      <formula>$E15:$E3145="sub"</formula>
+  <conditionalFormatting sqref="I65:I67">
+    <cfRule type="expression" dxfId="5" priority="414" stopIfTrue="1">
+      <formula>$E1:$E3114="sub"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I100">
-    <cfRule type="expression" dxfId="12" priority="171" stopIfTrue="1">
-      <formula>$E15:$E3145="sub"</formula>
+  <conditionalFormatting sqref="I86:I88">
+    <cfRule type="expression" dxfId="4" priority="415" stopIfTrue="1">
+      <formula>$E12:$E3145="sub"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I99">
-    <cfRule type="expression" dxfId="11" priority="178" stopIfTrue="1">
-      <formula>$E15:$E3145="sub"</formula>
+  <conditionalFormatting sqref="I89:I92">
+    <cfRule type="expression" dxfId="3" priority="416" stopIfTrue="1">
+      <formula>$E12:$E3145="sub"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I82 I80">
-    <cfRule type="expression" dxfId="10" priority="1" stopIfTrue="1">
-      <formula>$E11:$E3142="sub"</formula>
+  <conditionalFormatting sqref="I100:I101">
+    <cfRule type="expression" dxfId="2" priority="417" stopIfTrue="1">
+      <formula>$E14:$E3147="sub"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I90">
-    <cfRule type="expression" dxfId="9" priority="282" stopIfTrue="1">
-      <formula>$E14:$E3144="sub"</formula>
+  <conditionalFormatting sqref="I77:I81">
+    <cfRule type="expression" dxfId="1" priority="418" stopIfTrue="1">
+      <formula>$E2:$E3138="sub"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I79">
-    <cfRule type="expression" dxfId="8" priority="294" stopIfTrue="1">
-      <formula>$E8:$E3141="sub"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I107">
-    <cfRule type="expression" dxfId="7" priority="360" stopIfTrue="1">
-      <formula>$E17:$E3147="sub"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I104:I106">
-    <cfRule type="expression" dxfId="6" priority="387" stopIfTrue="1">
-      <formula>$E15:$E3145="sub"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I62:I64">
-    <cfRule type="expression" dxfId="5" priority="388" stopIfTrue="1">
-      <formula>$E1:$E3111="sub"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I83:I85">
-    <cfRule type="expression" dxfId="4" priority="389" stopIfTrue="1">
-      <formula>$E12:$E3142="sub"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I86:I89">
-    <cfRule type="expression" dxfId="3" priority="390" stopIfTrue="1">
-      <formula>$E12:$E3142="sub"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I97:I98">
-    <cfRule type="expression" dxfId="2" priority="391" stopIfTrue="1">
-      <formula>$E14:$E3144="sub"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I74:I78">
-    <cfRule type="expression" dxfId="1" priority="392" stopIfTrue="1">
-      <formula>$E2:$E3135="sub"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I73">
-    <cfRule type="expression" dxfId="0" priority="393" stopIfTrue="1">
-      <formula>$E3133:$E1048576="sub"</formula>
+  <conditionalFormatting sqref="I76">
+    <cfRule type="expression" dxfId="0" priority="419" stopIfTrue="1">
+      <formula>$E3136:$E1048576="sub"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="9">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="10">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>Sheet2!$F$2:$F$4</xm:f>
           </x14:formula1>
-          <xm:sqref>Y46:Y47 W46:W1048576 W2:W44</xm:sqref>
+          <xm:sqref>Y49:Y50 W157:W1048576 W49:W144 W147:W152 W2:W47</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>Sheet2!$G$2:$G$5</xm:f>
           </x14:formula1>
-          <xm:sqref>X2:X44 X46:X1048576</xm:sqref>
+          <xm:sqref>X147:X1048576 X49:X144 X2:X47</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>Sheet2!$E$2:$E$4</xm:f>
           </x14:formula1>
-          <xm:sqref>H2:H44 H46:H1048576</xm:sqref>
+          <xm:sqref>H157:H1048576 H49:H144 H147:H152 H2:H47</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>Sheet2!$D$2:$D$5</xm:f>
           </x14:formula1>
-          <xm:sqref>G2:G44 G46:G1048576</xm:sqref>
+          <xm:sqref>G157:G1048576 G49:G144 G147:G152 G2:G47</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>Sheet2!$C$2:$C$5</xm:f>
           </x14:formula1>
-          <xm:sqref>F2:F44 F46:F1048576</xm:sqref>
+          <xm:sqref>F157:F1048576 F49:F144 F147:F152 F2:F47</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>Sheet2!$B$2:$B$3</xm:f>
           </x14:formula1>
-          <xm:sqref>E2:E44 E46:E1048576</xm:sqref>
+          <xm:sqref>E157:E1048576 E49:E144 E147:E152 E2:E47</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>Sheet2!$A$2:$A$4</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D44 D46:D1048576</xm:sqref>
+          <xm:sqref>D157:D1048576 D49:D144 D147:D152 D2:D47</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'[복사본 sample-list.xlsx]Sheet2'!#REF!</xm:f>
           </x14:formula1>
-          <xm:sqref>D45:H45 W45:X45</xm:sqref>
+          <xm:sqref>D48:H48 W48:X48</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>Sheet2!$H$2:$H$7</xm:f>
           </x14:formula1>
-          <xm:sqref>Y48:Y1048576 Y2:Y45</xm:sqref>
+          <xm:sqref>Y157:Y1048576 Y51:Y144 Y147:Y152 Y2:Y48</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>'[sample-list_1.xlsx]Sheet2'!#REF!</xm:f>
+          </x14:formula1>
+          <xm:sqref>Y153:Y156 W153:W156 W145:Y146 D145:H146 D153:H156</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/sample-list.xlsx
+++ b/sample-list.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13635"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11835"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,14 +20,14 @@
     <externalReference r:id="rId4"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$AB$195</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$AB$206</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2253" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2308" uniqueCount="370">
   <si>
     <t>국가</t>
   </si>
@@ -1471,10 +1471,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>진행중</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Shimmering Gray 1D -3.25</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1484,6 +1480,22 @@
   </si>
   <si>
     <t>Drop</t>
+  </si>
+  <si>
+    <t>Dustity Brown A</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dustity Brown B</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dustity Gray A</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dustity Gray B</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1669,7 +1681,42 @@
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="40">
+  <dxfs count="45">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -2274,7 +2321,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AB201"/>
+  <dimension ref="A1:AB206"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.25" style="2" customWidth="1"/>
@@ -2498,6 +2545,9 @@
       <c r="Q3" s="4">
         <v>46149</v>
       </c>
+      <c r="R3" s="4">
+        <v>46150</v>
+      </c>
       <c r="S3" s="4">
         <v>46174</v>
       </c>
@@ -2559,6 +2609,12 @@
       </c>
       <c r="P4" s="4">
         <v>46140</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>46150</v>
+      </c>
+      <c r="R4" s="4">
+        <v>46151</v>
       </c>
       <c r="S4" s="4">
         <v>46174</v>
@@ -4326,7 +4382,7 @@
         <v>30</v>
       </c>
       <c r="X30" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="Y30" s="2" t="s">
         <v>58</v>
@@ -8220,13 +8276,13 @@
     </row>
     <row r="87" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>83</v>
+        <v>310</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>34</v>
@@ -8238,13 +8294,13 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G87" s="7">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="H87" s="2" t="s">
         <v>28</v>
       </c>
       <c r="I87" s="2" t="s">
-        <v>85</v>
+        <v>366</v>
       </c>
       <c r="J87" s="2">
         <v>1</v>
@@ -8253,32 +8309,28 @@
         <v>1</v>
       </c>
       <c r="L87" s="4">
-        <v>45995</v>
-      </c>
-      <c r="M87" s="5"/>
-      <c r="N87" s="4">
-        <v>46003</v>
-      </c>
-      <c r="O87" s="4">
-        <v>46007</v>
-      </c>
+        <v>46142</v>
+      </c>
+      <c r="M87" s="6"/>
+      <c r="N87" s="6"/>
+      <c r="O87" s="6"/>
       <c r="P87" s="4">
-        <v>46003</v>
+        <v>46143</v>
       </c>
       <c r="Q87" s="4">
-        <v>46014</v>
+        <v>46150</v>
       </c>
       <c r="R87" s="4">
-        <v>46015</v>
+        <v>46151</v>
       </c>
       <c r="S87" s="4">
-        <v>46015</v>
+        <v>46153</v>
       </c>
       <c r="T87" s="4">
-        <v>46015</v>
+        <v>46153</v>
       </c>
       <c r="V87" s="2" t="s">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="W87" s="2" t="s">
         <v>29</v>
@@ -8287,18 +8339,18 @@
         <v>53</v>
       </c>
       <c r="Y87" s="2" t="s">
-        <v>58</v>
+        <v>141</v>
       </c>
     </row>
     <row r="88" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>83</v>
+        <v>310</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>34</v>
@@ -8310,52 +8362,43 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G88" s="7">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="H88" s="2" t="s">
         <v>28</v>
       </c>
       <c r="I88" s="2" t="s">
-        <v>85</v>
+        <v>367</v>
       </c>
       <c r="J88" s="2">
         <v>1</v>
       </c>
       <c r="K88" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L88" s="4">
-        <v>45995</v>
-      </c>
-      <c r="M88" s="4">
-        <v>46055</v>
-      </c>
-      <c r="N88" s="4">
-        <v>46057</v>
-      </c>
-      <c r="O88" s="4">
-        <v>46064</v>
-      </c>
-      <c r="P88" s="10">
-        <v>46065</v>
+        <v>46142</v>
+      </c>
+      <c r="M88" s="6"/>
+      <c r="N88" s="6"/>
+      <c r="O88" s="6"/>
+      <c r="P88" s="4">
+        <v>46143</v>
       </c>
       <c r="Q88" s="4">
-        <v>46075</v>
+        <v>46150</v>
       </c>
       <c r="R88" s="4">
-        <v>46076</v>
+        <v>46151</v>
       </c>
       <c r="S88" s="4">
-        <v>46076</v>
+        <v>46153</v>
       </c>
       <c r="T88" s="4">
-        <v>46076</v>
-      </c>
-      <c r="U88" s="4">
-        <v>46077</v>
+        <v>46153</v>
       </c>
       <c r="V88" s="2" t="s">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="W88" s="2" t="s">
         <v>29</v>
@@ -8364,42 +8407,36 @@
         <v>53</v>
       </c>
       <c r="Y88" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="Z88" s="4">
-        <v>46107</v>
-      </c>
-      <c r="AB88" s="9" t="s">
-        <v>87</v>
+        <v>141</v>
       </c>
     </row>
     <row r="89" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
-        <v>285</v>
+        <v>62</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>287</v>
+        <v>310</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>288</v>
+        <v>64</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>27</v>
       </c>
       <c r="F89" s="3">
-        <v>0.45</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="G89" s="7">
-        <v>14.2</v>
+        <v>15</v>
       </c>
       <c r="H89" s="2" t="s">
         <v>28</v>
       </c>
       <c r="I89" s="2" t="s">
-        <v>291</v>
+        <v>368</v>
       </c>
       <c r="J89" s="2">
         <v>1</v>
@@ -8408,30 +8445,31 @@
         <v>1</v>
       </c>
       <c r="L89" s="4">
-        <v>46122</v>
-      </c>
-      <c r="N89" s="17"/>
-      <c r="O89" s="17"/>
+        <v>46142</v>
+      </c>
+      <c r="M89" s="6"/>
+      <c r="N89" s="6"/>
+      <c r="O89" s="6"/>
       <c r="P89" s="4">
-        <v>46122</v>
+        <v>46143</v>
       </c>
       <c r="Q89" s="4">
-        <v>46127</v>
+        <v>46150</v>
       </c>
       <c r="R89" s="4">
-        <v>46132</v>
+        <v>46151</v>
       </c>
       <c r="S89" s="4">
-        <v>46133</v>
+        <v>46153</v>
       </c>
       <c r="T89" s="4">
-        <v>46133</v>
+        <v>46153</v>
       </c>
       <c r="V89" s="2" t="s">
-        <v>294</v>
+        <v>97</v>
       </c>
       <c r="W89" s="2" t="s">
-        <v>295</v>
+        <v>29</v>
       </c>
       <c r="X89" s="2" t="s">
         <v>53</v>
@@ -8442,31 +8480,31 @@
     </row>
     <row r="90" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
-        <v>286</v>
+        <v>62</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>287</v>
+        <v>310</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>288</v>
+        <v>64</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>27</v>
       </c>
       <c r="F90" s="3">
-        <v>0.45</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="G90" s="7">
-        <v>14.2</v>
+        <v>15</v>
       </c>
       <c r="H90" s="2" t="s">
         <v>28</v>
       </c>
       <c r="I90" s="2" t="s">
-        <v>292</v>
+        <v>369</v>
       </c>
       <c r="J90" s="2">
         <v>1</v>
@@ -8475,30 +8513,31 @@
         <v>1</v>
       </c>
       <c r="L90" s="4">
-        <v>46122</v>
-      </c>
-      <c r="N90" s="17"/>
-      <c r="O90" s="17"/>
+        <v>46142</v>
+      </c>
+      <c r="M90" s="6"/>
+      <c r="N90" s="6"/>
+      <c r="O90" s="6"/>
       <c r="P90" s="4">
-        <v>46122</v>
+        <v>46143</v>
       </c>
       <c r="Q90" s="4">
-        <v>46127</v>
+        <v>46150</v>
       </c>
       <c r="R90" s="4">
-        <v>46132</v>
+        <v>46151</v>
       </c>
       <c r="S90" s="4">
-        <v>46133</v>
+        <v>46153</v>
       </c>
       <c r="T90" s="4">
-        <v>46133</v>
+        <v>46153</v>
       </c>
       <c r="V90" s="2" t="s">
-        <v>294</v>
+        <v>97</v>
       </c>
       <c r="W90" s="2" t="s">
-        <v>295</v>
+        <v>29</v>
       </c>
       <c r="X90" s="2" t="s">
         <v>53</v>
@@ -8542,25 +8581,29 @@
         <v>1</v>
       </c>
       <c r="L91" s="4">
-        <v>46055</v>
+        <v>45995</v>
       </c>
       <c r="M91" s="5"/>
-      <c r="N91" s="5"/>
-      <c r="O91" s="5"/>
+      <c r="N91" s="4">
+        <v>46003</v>
+      </c>
+      <c r="O91" s="4">
+        <v>46007</v>
+      </c>
       <c r="P91" s="4">
-        <v>46038</v>
+        <v>46003</v>
       </c>
       <c r="Q91" s="4">
-        <v>46043</v>
+        <v>46014</v>
       </c>
       <c r="R91" s="4">
-        <v>46045</v>
+        <v>46015</v>
       </c>
       <c r="S91" s="4">
-        <v>46045</v>
+        <v>46015</v>
       </c>
       <c r="T91" s="4">
-        <v>46045</v>
+        <v>46015</v>
       </c>
       <c r="V91" s="2" t="s">
         <v>81</v>
@@ -8573,9 +8616,6 @@
       </c>
       <c r="Y91" s="2" t="s">
         <v>58</v>
-      </c>
-      <c r="AB91" s="2" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="92" spans="1:28" x14ac:dyDescent="0.3">
@@ -8604,38 +8644,43 @@
         <v>28</v>
       </c>
       <c r="I92" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J92" s="2">
         <v>1</v>
       </c>
       <c r="K92" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L92" s="4">
         <v>45995</v>
       </c>
-      <c r="M92" s="5"/>
+      <c r="M92" s="4">
+        <v>46055</v>
+      </c>
       <c r="N92" s="4">
-        <v>46003</v>
+        <v>46057</v>
       </c>
       <c r="O92" s="4">
-        <v>46007</v>
-      </c>
-      <c r="P92" s="4">
-        <v>46003</v>
+        <v>46064</v>
+      </c>
+      <c r="P92" s="10">
+        <v>46065</v>
       </c>
       <c r="Q92" s="4">
-        <v>46014</v>
+        <v>46075</v>
       </c>
       <c r="R92" s="4">
-        <v>46015</v>
+        <v>46076</v>
       </c>
       <c r="S92" s="4">
-        <v>46015</v>
+        <v>46076</v>
       </c>
       <c r="T92" s="4">
-        <v>46015</v>
+        <v>46076</v>
+      </c>
+      <c r="U92" s="4">
+        <v>46077</v>
       </c>
       <c r="V92" s="2" t="s">
         <v>81</v>
@@ -8649,161 +8694,156 @@
       <c r="Y92" s="2" t="s">
         <v>58</v>
       </c>
+      <c r="Z92" s="4">
+        <v>46107</v>
+      </c>
+      <c r="AB92" s="9" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="93" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
-        <v>82</v>
+        <v>285</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>83</v>
+        <v>287</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>84</v>
+        <v>288</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>27</v>
       </c>
       <c r="F93" s="3">
-        <v>0.55000000000000004</v>
+        <v>0.45</v>
       </c>
       <c r="G93" s="7">
-        <v>14.5</v>
+        <v>14.2</v>
       </c>
       <c r="H93" s="2" t="s">
         <v>28</v>
       </c>
       <c r="I93" s="2" t="s">
-        <v>86</v>
+        <v>291</v>
       </c>
       <c r="J93" s="2">
         <v>1</v>
       </c>
       <c r="K93" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L93" s="4">
-        <v>45995</v>
-      </c>
-      <c r="M93" s="4">
-        <v>46055</v>
-      </c>
-      <c r="N93" s="4">
-        <v>46057</v>
-      </c>
-      <c r="O93" s="4">
-        <v>46064</v>
-      </c>
-      <c r="P93" s="10">
-        <v>46065</v>
+        <v>46122</v>
+      </c>
+      <c r="N93" s="17"/>
+      <c r="O93" s="17"/>
+      <c r="P93" s="4">
+        <v>46122</v>
       </c>
       <c r="Q93" s="4">
-        <v>46075</v>
+        <v>46127</v>
       </c>
       <c r="R93" s="4">
-        <v>46076</v>
+        <v>46132</v>
       </c>
       <c r="S93" s="4">
-        <v>46076</v>
+        <v>46133</v>
       </c>
       <c r="T93" s="4">
-        <v>46076</v>
-      </c>
-      <c r="U93" s="4">
-        <v>46077</v>
+        <v>46133</v>
       </c>
       <c r="V93" s="2" t="s">
-        <v>81</v>
+        <v>294</v>
       </c>
       <c r="W93" s="2" t="s">
-        <v>29</v>
+        <v>295</v>
       </c>
       <c r="X93" s="2" t="s">
         <v>53</v>
       </c>
       <c r="Y93" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="AB93" s="9" t="s">
-        <v>87</v>
+        <v>141</v>
       </c>
     </row>
     <row r="94" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
-        <v>311</v>
+        <v>286</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>312</v>
+        <v>287</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>112</v>
+        <v>288</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>27</v>
       </c>
       <c r="F94" s="3">
-        <v>0.55000000000000004</v>
+        <v>0.45</v>
       </c>
       <c r="G94" s="7">
-        <v>14.5</v>
+        <v>14.2</v>
       </c>
       <c r="H94" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I94" s="11" t="s">
-        <v>315</v>
+      <c r="I94" s="2" t="s">
+        <v>292</v>
       </c>
       <c r="J94" s="2">
         <v>1</v>
       </c>
       <c r="K94" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L94" s="4">
         <v>46122</v>
       </c>
-      <c r="O94" s="4">
+      <c r="N94" s="17"/>
+      <c r="O94" s="17"/>
+      <c r="P94" s="4">
+        <v>46122</v>
+      </c>
+      <c r="Q94" s="4">
+        <v>46127</v>
+      </c>
+      <c r="R94" s="4">
         <v>46132</v>
       </c>
-      <c r="P94" s="4">
-        <v>46134</v>
-      </c>
-      <c r="Q94" s="4">
-        <v>46139</v>
-      </c>
-      <c r="R94" s="4">
-        <v>46140</v>
-      </c>
       <c r="S94" s="4">
-        <v>46141</v>
+        <v>46133</v>
       </c>
       <c r="T94" s="4">
-        <v>46141</v>
+        <v>46133</v>
       </c>
       <c r="V94" s="2" t="s">
-        <v>261</v>
+        <v>294</v>
       </c>
       <c r="W94" s="2" t="s">
-        <v>29</v>
+        <v>295</v>
       </c>
       <c r="X94" s="2" t="s">
         <v>53</v>
+      </c>
+      <c r="Y94" s="2" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="95" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
-        <v>114</v>
+        <v>82</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>113</v>
+        <v>83</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>112</v>
+        <v>84</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>34</v>
@@ -8821,43 +8861,37 @@
         <v>28</v>
       </c>
       <c r="I95" s="2" t="s">
-        <v>119</v>
+        <v>85</v>
       </c>
       <c r="J95" s="2">
         <v>1</v>
       </c>
       <c r="K95" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L95" s="4">
-        <v>45868</v>
-      </c>
-      <c r="M95" s="4">
         <v>46055</v>
       </c>
-      <c r="N95" s="4">
-        <v>46056</v>
-      </c>
-      <c r="O95" s="4">
-        <v>46056</v>
-      </c>
+      <c r="M95" s="5"/>
+      <c r="N95" s="5"/>
+      <c r="O95" s="5"/>
       <c r="P95" s="4">
-        <v>46058</v>
+        <v>46038</v>
       </c>
       <c r="Q95" s="4">
-        <v>46065</v>
+        <v>46043</v>
       </c>
       <c r="R95" s="4">
-        <v>46066</v>
+        <v>46045</v>
       </c>
       <c r="S95" s="4">
-        <v>46066</v>
+        <v>46045</v>
       </c>
       <c r="T95" s="4">
-        <v>46066</v>
+        <v>46045</v>
       </c>
       <c r="V95" s="2" t="s">
-        <v>122</v>
+        <v>81</v>
       </c>
       <c r="W95" s="2" t="s">
         <v>29</v>
@@ -8865,16 +8899,22 @@
       <c r="X95" s="2" t="s">
         <v>53</v>
       </c>
+      <c r="Y95" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="AB95" s="2" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="96" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
-        <v>114</v>
+        <v>82</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>113</v>
+        <v>83</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>112</v>
+        <v>84</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>34</v>
@@ -8892,43 +8932,41 @@
         <v>28</v>
       </c>
       <c r="I96" s="2" t="s">
-        <v>119</v>
+        <v>86</v>
       </c>
       <c r="J96" s="2">
         <v>1</v>
       </c>
       <c r="K96" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L96" s="4">
-        <v>45868</v>
-      </c>
-      <c r="M96" s="4">
-        <v>46122</v>
-      </c>
+        <v>45995</v>
+      </c>
+      <c r="M96" s="5"/>
       <c r="N96" s="4">
-        <v>46127</v>
+        <v>46003</v>
       </c>
       <c r="O96" s="4">
-        <v>46129</v>
+        <v>46007</v>
       </c>
       <c r="P96" s="4">
-        <v>46133</v>
+        <v>46003</v>
       </c>
       <c r="Q96" s="4">
-        <v>46137</v>
+        <v>46014</v>
       </c>
       <c r="R96" s="4">
-        <v>46140</v>
+        <v>46015</v>
       </c>
       <c r="S96" s="4">
-        <v>46141</v>
+        <v>46015</v>
       </c>
       <c r="T96" s="4">
-        <v>46141</v>
+        <v>46015</v>
       </c>
       <c r="V96" s="2" t="s">
-        <v>122</v>
+        <v>81</v>
       </c>
       <c r="W96" s="2" t="s">
         <v>29</v>
@@ -8936,10 +8974,13 @@
       <c r="X96" s="2" t="s">
         <v>53</v>
       </c>
+      <c r="Y96" s="2" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="97" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>83</v>
@@ -8969,58 +9010,63 @@
         <v>1</v>
       </c>
       <c r="K97" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L97" s="4">
         <v>45995</v>
       </c>
       <c r="M97" s="4">
-        <v>46107</v>
+        <v>46055</v>
       </c>
       <c r="N97" s="4">
-        <v>46111</v>
+        <v>46057</v>
       </c>
       <c r="O97" s="4">
-        <v>46112</v>
+        <v>46064</v>
       </c>
       <c r="P97" s="10">
-        <v>46117</v>
+        <v>46065</v>
       </c>
       <c r="Q97" s="4">
-        <v>46125</v>
+        <v>46075</v>
       </c>
       <c r="R97" s="4">
-        <v>46126</v>
+        <v>46076</v>
       </c>
       <c r="S97" s="4">
-        <v>46127</v>
+        <v>46076</v>
       </c>
       <c r="T97" s="4">
-        <v>46127</v>
+        <v>46076</v>
+      </c>
+      <c r="U97" s="4">
+        <v>46077</v>
       </c>
       <c r="V97" s="2" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="W97" s="2" t="s">
         <v>29</v>
       </c>
       <c r="X97" s="2" t="s">
-        <v>282</v>
+        <v>53</v>
       </c>
       <c r="Y97" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="AB97" s="9"/>
+      <c r="AB97" s="9" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="98" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
-        <v>82</v>
+        <v>311</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>83</v>
+        <v>312</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>84</v>
+        <v>112</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>34</v>
@@ -9037,38 +9083,38 @@
       <c r="H98" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I98" s="2" t="s">
-        <v>86</v>
+      <c r="I98" s="11" t="s">
+        <v>315</v>
       </c>
       <c r="J98" s="2">
         <v>1</v>
       </c>
       <c r="K98" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L98" s="4">
-        <v>46055</v>
-      </c>
-      <c r="M98" s="5"/>
-      <c r="N98" s="5"/>
-      <c r="O98" s="5"/>
+        <v>46122</v>
+      </c>
+      <c r="O98" s="4">
+        <v>46132</v>
+      </c>
       <c r="P98" s="4">
-        <v>46038</v>
+        <v>46134</v>
       </c>
       <c r="Q98" s="4">
-        <v>46043</v>
+        <v>46139</v>
       </c>
       <c r="R98" s="4">
-        <v>46045</v>
+        <v>46140</v>
       </c>
       <c r="S98" s="4">
-        <v>46045</v>
+        <v>46141</v>
       </c>
       <c r="T98" s="4">
-        <v>46045</v>
+        <v>46141</v>
       </c>
       <c r="V98" s="2" t="s">
-        <v>81</v>
+        <v>261</v>
       </c>
       <c r="W98" s="2" t="s">
         <v>29</v>
@@ -9076,22 +9122,16 @@
       <c r="X98" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="Y98" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="AB98" s="2" t="s">
-        <v>89</v>
-      </c>
     </row>
     <row r="99" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>299</v>
+        <v>113</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>34</v>
@@ -9103,28 +9143,34 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G99" s="7">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="H99" s="2" t="s">
         <v>28</v>
       </c>
       <c r="I99" s="2" t="s">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="J99" s="2">
         <v>1</v>
       </c>
       <c r="K99" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L99" s="4">
-        <v>46052</v>
-      </c>
-      <c r="M99" s="6"/>
-      <c r="N99" s="6"/>
-      <c r="O99" s="6"/>
+        <v>45868</v>
+      </c>
+      <c r="M99" s="4">
+        <v>46055</v>
+      </c>
+      <c r="N99" s="4">
+        <v>46056</v>
+      </c>
+      <c r="O99" s="4">
+        <v>46056</v>
+      </c>
       <c r="P99" s="4">
-        <v>46053</v>
+        <v>46058</v>
       </c>
       <c r="Q99" s="4">
         <v>46065</v>
@@ -9139,27 +9185,24 @@
         <v>46066</v>
       </c>
       <c r="V99" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="W99" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X99" s="2" t="s">
         <v>53</v>
-      </c>
-      <c r="Y99" s="2" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="100" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>299</v>
+        <v>113</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>34</v>
@@ -9171,52 +9214,55 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G100" s="7">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="H100" s="2" t="s">
         <v>28</v>
       </c>
       <c r="I100" s="2" t="s">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="J100" s="2">
         <v>1</v>
       </c>
       <c r="K100" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L100" s="4">
-        <v>46052</v>
-      </c>
-      <c r="M100" s="6"/>
-      <c r="N100" s="6"/>
-      <c r="O100" s="6"/>
+        <v>45868</v>
+      </c>
+      <c r="M100" s="4">
+        <v>46122</v>
+      </c>
+      <c r="N100" s="4">
+        <v>46127</v>
+      </c>
+      <c r="O100" s="4">
+        <v>46129</v>
+      </c>
       <c r="P100" s="4">
-        <v>46053</v>
+        <v>46133</v>
       </c>
       <c r="Q100" s="4">
-        <v>46065</v>
+        <v>46137</v>
       </c>
       <c r="R100" s="4">
-        <v>46066</v>
+        <v>46140</v>
       </c>
       <c r="S100" s="4">
-        <v>46066</v>
+        <v>46141</v>
       </c>
       <c r="T100" s="4">
-        <v>46066</v>
+        <v>46141</v>
       </c>
       <c r="V100" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="W100" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X100" s="2" t="s">
         <v>53</v>
-      </c>
-      <c r="Y100" s="2" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="101" spans="1:28" x14ac:dyDescent="0.3">
@@ -9224,10 +9270,10 @@
         <v>62</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>296</v>
+        <v>83</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>297</v>
+        <v>84</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>34</v>
@@ -9245,60 +9291,64 @@
         <v>28</v>
       </c>
       <c r="I101" s="2" t="s">
-        <v>352</v>
+        <v>86</v>
       </c>
       <c r="J101" s="2">
         <v>1</v>
       </c>
       <c r="K101" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L101" s="4">
-        <v>46062</v>
+        <v>45995</v>
+      </c>
+      <c r="M101" s="4">
+        <v>46107</v>
       </c>
       <c r="N101" s="4">
-        <v>46063</v>
+        <v>46111</v>
       </c>
       <c r="O101" s="4">
-        <v>46119</v>
-      </c>
-      <c r="P101" s="4">
+        <v>46112</v>
+      </c>
+      <c r="P101" s="10">
+        <v>46117</v>
+      </c>
+      <c r="Q101" s="4">
+        <v>46125</v>
+      </c>
+      <c r="R101" s="4">
         <v>46126</v>
       </c>
-      <c r="Q101" s="4">
-        <v>46129</v>
-      </c>
-      <c r="R101" s="4">
-        <v>46133</v>
-      </c>
       <c r="S101" s="4">
-        <v>46136</v>
+        <v>46127</v>
       </c>
       <c r="T101" s="4">
-        <v>46136</v>
+        <v>46127</v>
       </c>
       <c r="V101" s="2" t="s">
-        <v>146</v>
+        <v>66</v>
       </c>
       <c r="W101" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X101" s="2" t="s">
-        <v>53</v>
+        <v>282</v>
       </c>
       <c r="Y101" s="2" t="s">
-        <v>140</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="AB101" s="9"/>
     </row>
     <row r="102" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>299</v>
+        <v>83</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>34</v>
@@ -9310,13 +9360,13 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G102" s="7">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="H102" s="2" t="s">
         <v>28</v>
       </c>
       <c r="I102" s="2" t="s">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="J102" s="2">
         <v>1</v>
@@ -9325,48 +9375,51 @@
         <v>1</v>
       </c>
       <c r="L102" s="4">
-        <v>46052</v>
-      </c>
-      <c r="M102" s="6"/>
-      <c r="N102" s="6"/>
-      <c r="O102" s="6"/>
+        <v>46055</v>
+      </c>
+      <c r="M102" s="5"/>
+      <c r="N102" s="5"/>
+      <c r="O102" s="5"/>
       <c r="P102" s="4">
-        <v>46053</v>
+        <v>46038</v>
       </c>
       <c r="Q102" s="4">
-        <v>46065</v>
+        <v>46043</v>
       </c>
       <c r="R102" s="4">
-        <v>46066</v>
+        <v>46045</v>
       </c>
       <c r="S102" s="4">
-        <v>46066</v>
+        <v>46045</v>
       </c>
       <c r="T102" s="4">
-        <v>46066</v>
+        <v>46045</v>
       </c>
       <c r="V102" s="2" t="s">
-        <v>121</v>
+        <v>81</v>
       </c>
       <c r="W102" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X102" s="2" t="s">
         <v>53</v>
       </c>
       <c r="Y102" s="2" t="s">
-        <v>140</v>
+        <v>58</v>
+      </c>
+      <c r="AB102" s="2" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="103" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A103" s="2" t="s">
-        <v>62</v>
+        <v>104</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>297</v>
+        <v>103</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>34</v>
@@ -9378,13 +9431,13 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G103" s="7">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="H103" s="2" t="s">
         <v>28</v>
       </c>
       <c r="I103" s="2" t="s">
-        <v>353</v>
+        <v>101</v>
       </c>
       <c r="J103" s="2">
         <v>1</v>
@@ -9393,31 +9446,28 @@
         <v>1</v>
       </c>
       <c r="L103" s="4">
-        <v>46062</v>
-      </c>
-      <c r="N103" s="4">
-        <v>46063</v>
-      </c>
-      <c r="O103" s="4">
-        <v>46119</v>
-      </c>
+        <v>46052</v>
+      </c>
+      <c r="M103" s="6"/>
+      <c r="N103" s="6"/>
+      <c r="O103" s="6"/>
       <c r="P103" s="4">
-        <v>46126</v>
+        <v>46053</v>
       </c>
       <c r="Q103" s="4">
-        <v>46129</v>
+        <v>46065</v>
       </c>
       <c r="R103" s="4">
-        <v>46133</v>
+        <v>46066</v>
       </c>
       <c r="S103" s="4">
-        <v>46136</v>
+        <v>46066</v>
       </c>
       <c r="T103" s="4">
-        <v>46136</v>
+        <v>46066</v>
       </c>
       <c r="V103" s="2" t="s">
-        <v>146</v>
+        <v>121</v>
       </c>
       <c r="W103" s="2" t="s">
         <v>30</v>
@@ -9431,16 +9481,16 @@
     </row>
     <row r="104" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="s">
-        <v>43</v>
+        <v>104</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>44</v>
+        <v>299</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>45</v>
+        <v>103</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>27</v>
@@ -9449,13 +9499,13 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G104" s="7">
-        <v>14.2</v>
+        <v>15</v>
       </c>
       <c r="H104" s="2" t="s">
         <v>28</v>
       </c>
       <c r="I104" s="2" t="s">
-        <v>47</v>
+        <v>102</v>
       </c>
       <c r="J104" s="2">
         <v>1</v>
@@ -9464,60 +9514,51 @@
         <v>1</v>
       </c>
       <c r="L104" s="4">
-        <v>45978</v>
-      </c>
-      <c r="M104" s="4">
-        <v>45978</v>
-      </c>
-      <c r="N104" s="4">
-        <v>45985</v>
-      </c>
-      <c r="O104" s="4">
-        <v>45996</v>
-      </c>
+        <v>46052</v>
+      </c>
+      <c r="M104" s="6"/>
+      <c r="N104" s="6"/>
+      <c r="O104" s="6"/>
       <c r="P104" s="4">
-        <v>45989</v>
+        <v>46053</v>
       </c>
       <c r="Q104" s="4">
-        <v>46003</v>
+        <v>46065</v>
       </c>
       <c r="R104" s="4">
-        <v>46006</v>
+        <v>46066</v>
       </c>
       <c r="S104" s="4">
-        <v>46006</v>
+        <v>46066</v>
       </c>
       <c r="T104" s="4">
-        <v>46006</v>
+        <v>46066</v>
       </c>
       <c r="V104" s="2" t="s">
-        <v>51</v>
+        <v>121</v>
       </c>
       <c r="W104" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="X104" s="2" t="s">
         <v>53</v>
       </c>
       <c r="Y104" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="Z104" s="4">
-        <v>46041</v>
+        <v>140</v>
       </c>
     </row>
     <row r="105" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A105" s="2" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>44</v>
+        <v>296</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>45</v>
+        <v>297</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>27</v>
@@ -9526,13 +9567,13 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G105" s="7">
-        <v>14.2</v>
+        <v>14.5</v>
       </c>
       <c r="H105" s="2" t="s">
         <v>28</v>
       </c>
       <c r="I105" s="2" t="s">
-        <v>46</v>
+        <v>352</v>
       </c>
       <c r="J105" s="2">
         <v>1</v>
@@ -9541,57 +9582,51 @@
         <v>1</v>
       </c>
       <c r="L105" s="4">
-        <v>45978</v>
-      </c>
-      <c r="M105" s="4">
-        <v>45978</v>
+        <v>46062</v>
       </c>
       <c r="N105" s="4">
-        <v>45985</v>
+        <v>46063</v>
       </c>
       <c r="O105" s="4">
-        <v>45996</v>
+        <v>46119</v>
       </c>
       <c r="P105" s="4">
-        <v>45989</v>
+        <v>46126</v>
       </c>
       <c r="Q105" s="4">
-        <v>46003</v>
+        <v>46129</v>
       </c>
       <c r="R105" s="4">
-        <v>46006</v>
+        <v>46133</v>
       </c>
       <c r="S105" s="4">
-        <v>46006</v>
+        <v>46136</v>
       </c>
       <c r="T105" s="4">
-        <v>46006</v>
+        <v>46136</v>
       </c>
       <c r="V105" s="2" t="s">
-        <v>51</v>
+        <v>146</v>
       </c>
       <c r="W105" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="X105" s="2" t="s">
         <v>53</v>
       </c>
       <c r="Y105" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="Z105" s="4">
-        <v>46041</v>
+        <v>140</v>
       </c>
     </row>
     <row r="106" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A106" s="2" t="s">
-        <v>256</v>
+        <v>104</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>257</v>
+        <v>299</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>34</v>
@@ -9603,13 +9638,13 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G106" s="7">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="H106" s="2" t="s">
         <v>28</v>
       </c>
       <c r="I106" s="2" t="s">
-        <v>259</v>
+        <v>100</v>
       </c>
       <c r="J106" s="2">
         <v>1</v>
@@ -9618,28 +9653,28 @@
         <v>1</v>
       </c>
       <c r="L106" s="4">
-        <v>46111</v>
-      </c>
-      <c r="N106" s="4">
-        <v>46111</v>
-      </c>
+        <v>46052</v>
+      </c>
+      <c r="M106" s="6"/>
+      <c r="N106" s="6"/>
+      <c r="O106" s="6"/>
       <c r="P106" s="4">
-        <v>46116</v>
+        <v>46053</v>
       </c>
       <c r="Q106" s="4">
-        <v>46124</v>
+        <v>46065</v>
       </c>
       <c r="R106" s="4">
-        <v>46125</v>
+        <v>46066</v>
       </c>
       <c r="S106" s="4">
-        <v>46126</v>
+        <v>46066</v>
       </c>
       <c r="T106" s="4">
-        <v>46126</v>
+        <v>46066</v>
       </c>
       <c r="V106" s="2" t="s">
-        <v>261</v>
+        <v>121</v>
       </c>
       <c r="W106" s="2" t="s">
         <v>30</v>
@@ -9653,13 +9688,13 @@
     </row>
     <row r="107" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A107" s="2" t="s">
-        <v>256</v>
+        <v>62</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>257</v>
+        <v>296</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>103</v>
+        <v>297</v>
       </c>
       <c r="D107" s="2" t="s">
         <v>34</v>
@@ -9677,7 +9712,7 @@
         <v>28</v>
       </c>
       <c r="I107" s="2" t="s">
-        <v>259</v>
+        <v>353</v>
       </c>
       <c r="J107" s="2">
         <v>1</v>
@@ -9686,45 +9721,54 @@
         <v>1</v>
       </c>
       <c r="L107" s="4">
-        <v>46143</v>
+        <v>46062</v>
       </c>
       <c r="N107" s="4">
-        <v>46146</v>
+        <v>46063</v>
+      </c>
+      <c r="O107" s="4">
+        <v>46119</v>
       </c>
       <c r="P107" s="4">
-        <v>46146</v>
+        <v>46126</v>
+      </c>
+      <c r="Q107" s="4">
+        <v>46129</v>
+      </c>
+      <c r="R107" s="4">
+        <v>46133</v>
       </c>
       <c r="S107" s="4">
-        <v>46153</v>
+        <v>46136</v>
       </c>
       <c r="T107" s="4">
-        <v>46153</v>
+        <v>46136</v>
       </c>
       <c r="V107" s="2" t="s">
-        <v>309</v>
+        <v>146</v>
       </c>
       <c r="W107" s="2" t="s">
         <v>30</v>
       </c>
       <c r="X107" s="2" t="s">
-        <v>99</v>
+        <v>53</v>
       </c>
       <c r="Y107" s="2" t="s">
-        <v>58</v>
+        <v>140</v>
       </c>
     </row>
     <row r="108" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A108" s="2" t="s">
-        <v>148</v>
+        <v>43</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>279</v>
+        <v>44</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>112</v>
+        <v>45</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="E108" s="2" t="s">
         <v>27</v>
@@ -9733,13 +9777,13 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G108" s="7">
-        <v>14.5</v>
+        <v>14.2</v>
       </c>
       <c r="H108" s="2" t="s">
         <v>28</v>
       </c>
       <c r="I108" s="2" t="s">
-        <v>277</v>
+        <v>47</v>
       </c>
       <c r="J108" s="2">
         <v>1</v>
@@ -9748,54 +9792,60 @@
         <v>1</v>
       </c>
       <c r="L108" s="4">
-        <v>46105</v>
+        <v>45978</v>
+      </c>
+      <c r="M108" s="4">
+        <v>45978</v>
       </c>
       <c r="N108" s="4">
-        <v>46121</v>
+        <v>45985</v>
       </c>
       <c r="O108" s="4">
-        <v>46122</v>
+        <v>45996</v>
       </c>
       <c r="P108" s="4">
-        <v>46126</v>
+        <v>45989</v>
       </c>
       <c r="Q108" s="4">
-        <v>46131</v>
+        <v>46003</v>
       </c>
       <c r="R108" s="4">
-        <v>46132</v>
+        <v>46006</v>
       </c>
       <c r="S108" s="4">
-        <v>46133</v>
+        <v>46006</v>
       </c>
       <c r="T108" s="4">
-        <v>46133</v>
+        <v>46006</v>
       </c>
       <c r="V108" s="2" t="s">
-        <v>122</v>
+        <v>51</v>
       </c>
       <c r="W108" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X108" s="2" t="s">
-        <v>304</v>
+        <v>53</v>
       </c>
       <c r="Y108" s="2" t="s">
-        <v>141</v>
+        <v>58</v>
+      </c>
+      <c r="Z108" s="4">
+        <v>46041</v>
       </c>
     </row>
     <row r="109" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A109" s="2" t="s">
-        <v>311</v>
+        <v>43</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>312</v>
+        <v>44</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>112</v>
+        <v>45</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>27</v>
@@ -9804,60 +9854,72 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G109" s="7">
-        <v>14.5</v>
+        <v>14.2</v>
       </c>
       <c r="H109" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I109" s="11" t="s">
-        <v>316</v>
+      <c r="I109" s="2" t="s">
+        <v>46</v>
       </c>
       <c r="J109" s="2">
         <v>1</v>
       </c>
       <c r="K109" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L109" s="4">
-        <v>46122</v>
+        <v>45978</v>
+      </c>
+      <c r="M109" s="4">
+        <v>45978</v>
+      </c>
+      <c r="N109" s="4">
+        <v>45985</v>
       </c>
       <c r="O109" s="4">
-        <v>46132</v>
+        <v>45996</v>
       </c>
       <c r="P109" s="4">
-        <v>46134</v>
+        <v>45989</v>
       </c>
       <c r="Q109" s="4">
-        <v>46139</v>
+        <v>46003</v>
       </c>
       <c r="R109" s="4">
-        <v>46140</v>
+        <v>46006</v>
       </c>
       <c r="S109" s="4">
-        <v>46141</v>
+        <v>46006</v>
       </c>
       <c r="T109" s="4">
-        <v>46141</v>
+        <v>46006</v>
       </c>
       <c r="V109" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="W109" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X109" s="2" t="s">
         <v>53</v>
+      </c>
+      <c r="Y109" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="Z109" s="4">
+        <v>46041</v>
       </c>
     </row>
     <row r="110" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="s">
-        <v>114</v>
+        <v>256</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>113</v>
+        <v>257</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>112</v>
+        <v>84</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>34</v>
@@ -9875,63 +9937,57 @@
         <v>28</v>
       </c>
       <c r="I110" s="2" t="s">
-        <v>118</v>
+        <v>259</v>
       </c>
       <c r="J110" s="2">
         <v>1</v>
       </c>
       <c r="K110" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L110" s="4">
-        <v>45868</v>
-      </c>
-      <c r="M110" s="4">
-        <v>46055</v>
+        <v>46111</v>
       </c>
       <c r="N110" s="4">
-        <v>46056</v>
-      </c>
-      <c r="O110" s="4">
-        <v>46056</v>
+        <v>46111</v>
       </c>
       <c r="P110" s="4">
-        <v>46057</v>
+        <v>46116</v>
       </c>
       <c r="Q110" s="4">
-        <v>46065</v>
+        <v>46124</v>
       </c>
       <c r="R110" s="4">
-        <v>46066</v>
+        <v>46125</v>
       </c>
       <c r="S110" s="4">
-        <v>46066</v>
+        <v>46126</v>
       </c>
       <c r="T110" s="4">
-        <v>46066</v>
+        <v>46126</v>
       </c>
       <c r="V110" s="2" t="s">
-        <v>123</v>
+        <v>261</v>
       </c>
       <c r="W110" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="X110" s="2" t="s">
         <v>53</v>
       </c>
       <c r="Y110" s="2" t="s">
-        <v>58</v>
+        <v>140</v>
       </c>
     </row>
     <row r="111" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A111" s="2" t="s">
-        <v>114</v>
+        <v>256</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>113</v>
+        <v>257</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>34</v>
@@ -9949,34 +10005,37 @@
         <v>28</v>
       </c>
       <c r="I111" s="2" t="s">
-        <v>118</v>
+        <v>259</v>
       </c>
       <c r="J111" s="2">
         <v>1</v>
       </c>
       <c r="K111" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L111" s="4">
-        <v>45868</v>
-      </c>
-      <c r="M111" s="4">
-        <v>46129</v>
+        <v>46143</v>
       </c>
       <c r="N111" s="4">
-        <v>46132</v>
-      </c>
-      <c r="O111" s="4">
-        <v>46132</v>
+        <v>46146</v>
+      </c>
+      <c r="P111" s="4">
+        <v>46146</v>
+      </c>
+      <c r="S111" s="4">
+        <v>46153</v>
+      </c>
+      <c r="T111" s="4">
+        <v>46153</v>
       </c>
       <c r="V111" s="2" t="s">
-        <v>52</v>
+        <v>309</v>
       </c>
       <c r="W111" s="2" t="s">
-        <v>308</v>
+        <v>30</v>
       </c>
       <c r="X111" s="2" t="s">
-        <v>53</v>
+        <v>99</v>
       </c>
       <c r="Y111" s="2" t="s">
         <v>58</v>
@@ -9984,31 +10043,31 @@
     </row>
     <row r="112" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
-        <v>168</v>
+        <v>148</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>169</v>
+        <v>279</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>170</v>
+        <v>112</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>171</v>
+        <v>27</v>
       </c>
       <c r="F112" s="3">
         <v>0.55000000000000004</v>
       </c>
       <c r="G112" s="7">
-        <v>14.2</v>
+        <v>14.5</v>
       </c>
       <c r="H112" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I112" s="11" t="s">
-        <v>191</v>
+      <c r="I112" s="2" t="s">
+        <v>277</v>
       </c>
       <c r="J112" s="2">
         <v>1</v>
@@ -10017,229 +10076,229 @@
         <v>1</v>
       </c>
       <c r="L112" s="4">
-        <v>46086</v>
+        <v>46105</v>
+      </c>
+      <c r="N112" s="4">
+        <v>46121</v>
+      </c>
+      <c r="O112" s="4">
+        <v>46122</v>
       </c>
       <c r="P112" s="4">
-        <v>46094</v>
+        <v>46126</v>
       </c>
       <c r="Q112" s="4">
-        <v>46103</v>
+        <v>46131</v>
       </c>
       <c r="R112" s="4">
-        <v>46105</v>
+        <v>46132</v>
       </c>
       <c r="S112" s="4">
-        <v>46112</v>
+        <v>46133</v>
       </c>
       <c r="T112" s="4">
-        <v>46112</v>
+        <v>46133</v>
       </c>
       <c r="V112" s="2" t="s">
-        <v>146</v>
+        <v>122</v>
       </c>
       <c r="W112" s="2" t="s">
         <v>30</v>
       </c>
       <c r="X112" s="2" t="s">
-        <v>53</v>
+        <v>304</v>
       </c>
       <c r="Y112" s="2" t="s">
-        <v>58</v>
+        <v>141</v>
       </c>
     </row>
     <row r="113" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A113" s="2" t="s">
-        <v>43</v>
+        <v>148</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>44</v>
+        <v>279</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>45</v>
+        <v>112</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F113" s="3">
-        <v>0.43</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="G113" s="7">
-        <v>14.2</v>
+        <v>14.5</v>
       </c>
       <c r="H113" s="2" t="s">
-        <v>130</v>
+        <v>28</v>
       </c>
       <c r="I113" s="2" t="s">
-        <v>131</v>
+        <v>277</v>
       </c>
       <c r="J113" s="2">
         <v>1</v>
       </c>
       <c r="K113" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L113" s="4">
-        <v>46077</v>
+        <v>46105</v>
       </c>
       <c r="M113" s="4">
-        <v>46077</v>
+        <v>46150</v>
       </c>
       <c r="N113" s="4">
-        <v>46078</v>
-      </c>
-      <c r="O113" s="4">
-        <v>46078</v>
-      </c>
-      <c r="P113" s="4">
-        <v>46084</v>
-      </c>
-      <c r="Q113" s="4">
-        <v>46089</v>
-      </c>
-      <c r="R113" s="4">
-        <v>46090</v>
-      </c>
-      <c r="S113" s="4">
-        <v>46092</v>
-      </c>
-      <c r="T113" s="4">
-        <v>46092</v>
+        <v>46150</v>
       </c>
       <c r="V113" s="2" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="W113" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="X113" s="2" t="s">
-        <v>53</v>
+        <v>135</v>
       </c>
       <c r="Y113" s="2" t="s">
-        <v>233</v>
+        <v>58</v>
       </c>
     </row>
     <row r="114" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
-        <v>253</v>
+        <v>311</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>44</v>
+        <v>312</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>45</v>
+        <v>112</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F114" s="3">
-        <v>0.43</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="G114" s="7">
-        <v>14.2</v>
+        <v>14.5</v>
       </c>
       <c r="H114" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="I114" s="2" t="s">
-        <v>131</v>
+        <v>28</v>
+      </c>
+      <c r="I114" s="11" t="s">
+        <v>316</v>
       </c>
       <c r="J114" s="2">
         <v>1</v>
       </c>
       <c r="K114" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L114" s="4">
-        <v>46077</v>
-      </c>
-      <c r="M114" s="4">
-        <v>46113</v>
-      </c>
-      <c r="N114" s="4">
-        <v>46125</v>
+        <v>46122</v>
       </c>
       <c r="O114" s="4">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="P114" s="4">
-        <v>46130</v>
+        <v>46134</v>
+      </c>
+      <c r="Q114" s="4">
+        <v>46139</v>
+      </c>
+      <c r="R114" s="4">
+        <v>46140</v>
+      </c>
+      <c r="S114" s="4">
+        <v>46141</v>
+      </c>
+      <c r="T114" s="4">
+        <v>46141</v>
       </c>
       <c r="V114" s="2" t="s">
-        <v>76</v>
+        <v>52</v>
       </c>
       <c r="W114" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="X114" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="Y114" s="2" t="s">
-        <v>233</v>
+        <v>53</v>
       </c>
     </row>
     <row r="115" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A115" s="2" t="s">
-        <v>168</v>
+        <v>114</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>169</v>
+        <v>113</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>170</v>
+        <v>112</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>171</v>
+        <v>27</v>
       </c>
       <c r="F115" s="3">
         <v>0.55000000000000004</v>
       </c>
       <c r="G115" s="7">
-        <v>14.2</v>
+        <v>14.5</v>
       </c>
       <c r="H115" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I115" s="11" t="s">
-        <v>160</v>
+      <c r="I115" s="2" t="s">
+        <v>118</v>
       </c>
       <c r="J115" s="2">
         <v>1</v>
       </c>
       <c r="K115" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L115" s="4">
-        <v>46086</v>
+        <v>45868</v>
+      </c>
+      <c r="M115" s="4">
+        <v>46055</v>
+      </c>
+      <c r="N115" s="4">
+        <v>46056</v>
+      </c>
+      <c r="O115" s="4">
+        <v>46056</v>
       </c>
       <c r="P115" s="4">
-        <v>46094</v>
+        <v>46057</v>
       </c>
       <c r="Q115" s="4">
-        <v>46103</v>
+        <v>46065</v>
       </c>
       <c r="R115" s="4">
-        <v>46105</v>
+        <v>46066</v>
       </c>
       <c r="S115" s="4">
-        <v>46112</v>
+        <v>46066</v>
       </c>
       <c r="T115" s="4">
-        <v>46112</v>
+        <v>46066</v>
       </c>
       <c r="V115" s="2" t="s">
-        <v>146</v>
+        <v>123</v>
       </c>
       <c r="W115" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X115" s="2" t="s">
         <v>53</v>
@@ -10250,16 +10309,16 @@
     </row>
     <row r="116" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A116" s="2" t="s">
-        <v>62</v>
+        <v>114</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>63</v>
+        <v>113</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>64</v>
+        <v>112</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>27</v>
@@ -10268,62 +10327,43 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G116" s="7">
-        <v>14.2</v>
+        <v>14.5</v>
       </c>
       <c r="H116" s="2" t="s">
         <v>28</v>
       </c>
       <c r="I116" s="2" t="s">
-        <v>65</v>
+        <v>118</v>
       </c>
       <c r="J116" s="2">
         <v>1</v>
       </c>
       <c r="K116" s="2">
-        <v>9</v>
-      </c>
-      <c r="L116" s="5"/>
+        <v>5</v>
+      </c>
+      <c r="L116" s="4">
+        <v>45868</v>
+      </c>
       <c r="M116" s="4">
-        <v>45954</v>
+        <v>46129</v>
       </c>
       <c r="N116" s="4">
-        <v>45954</v>
+        <v>46132</v>
       </c>
       <c r="O116" s="4">
-        <v>45955</v>
-      </c>
-      <c r="P116" s="4">
-        <v>45965</v>
-      </c>
-      <c r="Q116" s="4">
-        <v>45974</v>
-      </c>
-      <c r="R116" s="4">
-        <v>45975</v>
-      </c>
-      <c r="S116" s="4">
-        <v>45975</v>
-      </c>
-      <c r="T116" s="4">
-        <v>45975</v>
+        <v>46132</v>
       </c>
       <c r="V116" s="2" t="s">
-        <v>250</v>
+        <v>52</v>
       </c>
       <c r="W116" s="2" t="s">
-        <v>30</v>
+        <v>308</v>
       </c>
       <c r="X116" s="2" t="s">
         <v>53</v>
       </c>
       <c r="Y116" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="Z116" s="4">
-        <v>45982</v>
-      </c>
-      <c r="AA116" s="4">
-        <v>46030</v>
+        <v>58</v>
       </c>
     </row>
     <row r="117" spans="1:27" x14ac:dyDescent="0.3">
@@ -10352,7 +10392,7 @@
         <v>28</v>
       </c>
       <c r="I117" s="11" t="s">
-        <v>328</v>
+        <v>191</v>
       </c>
       <c r="J117" s="2">
         <v>1</v>
@@ -10361,22 +10401,22 @@
         <v>1</v>
       </c>
       <c r="L117" s="4">
-        <v>46126</v>
+        <v>46086</v>
       </c>
       <c r="P117" s="4">
-        <v>46132</v>
+        <v>46094</v>
       </c>
       <c r="Q117" s="4">
-        <v>46139</v>
+        <v>46103</v>
       </c>
       <c r="R117" s="4">
-        <v>46140</v>
+        <v>46105</v>
       </c>
       <c r="S117" s="4">
-        <v>46162</v>
+        <v>46112</v>
       </c>
       <c r="T117" s="4">
-        <v>46150</v>
+        <v>46112</v>
       </c>
       <c r="V117" s="2" t="s">
         <v>146</v>
@@ -10393,31 +10433,31 @@
     </row>
     <row r="118" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A118" s="2" t="s">
-        <v>168</v>
+        <v>43</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>169</v>
+        <v>44</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>170</v>
+        <v>45</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>171</v>
+        <v>32</v>
       </c>
       <c r="F118" s="3">
-        <v>0.55000000000000004</v>
+        <v>0.43</v>
       </c>
       <c r="G118" s="7">
         <v>14.2</v>
       </c>
       <c r="H118" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="I118" s="11" t="s">
-        <v>329</v>
+        <v>130</v>
+      </c>
+      <c r="I118" s="2" t="s">
+        <v>131</v>
       </c>
       <c r="J118" s="2">
         <v>1</v>
@@ -10426,116 +10466,122 @@
         <v>1</v>
       </c>
       <c r="L118" s="4">
-        <v>46126</v>
+        <v>46077</v>
+      </c>
+      <c r="M118" s="4">
+        <v>46077</v>
+      </c>
+      <c r="N118" s="4">
+        <v>46078</v>
+      </c>
+      <c r="O118" s="4">
+        <v>46078</v>
       </c>
       <c r="P118" s="4">
-        <v>46132</v>
+        <v>46084</v>
       </c>
       <c r="Q118" s="4">
-        <v>46139</v>
+        <v>46089</v>
       </c>
       <c r="R118" s="4">
-        <v>46140</v>
+        <v>46090</v>
       </c>
       <c r="S118" s="4">
-        <v>46162</v>
+        <v>46092</v>
       </c>
       <c r="T118" s="4">
-        <v>46150</v>
+        <v>46092</v>
       </c>
       <c r="V118" s="2" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="W118" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="X118" s="2" t="s">
         <v>53</v>
       </c>
       <c r="Y118" s="2" t="s">
-        <v>58</v>
+        <v>233</v>
       </c>
     </row>
     <row r="119" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A119" s="2" t="s">
-        <v>168</v>
+        <v>253</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>169</v>
+        <v>44</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>170</v>
+        <v>45</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F119" s="3">
-        <v>0.55000000000000004</v>
+        <v>0.43</v>
       </c>
       <c r="G119" s="7">
         <v>14.2</v>
       </c>
       <c r="H119" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="I119" s="11" t="s">
-        <v>161</v>
+        <v>130</v>
+      </c>
+      <c r="I119" s="2" t="s">
+        <v>131</v>
       </c>
       <c r="J119" s="2">
         <v>1</v>
       </c>
       <c r="K119" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L119" s="4">
-        <v>46086</v>
+        <v>46077</v>
+      </c>
+      <c r="M119" s="4">
+        <v>46113</v>
+      </c>
+      <c r="N119" s="4">
+        <v>46125</v>
+      </c>
+      <c r="O119" s="4">
+        <v>46129</v>
       </c>
       <c r="P119" s="4">
-        <v>46094</v>
-      </c>
-      <c r="Q119" s="4">
-        <v>46103</v>
-      </c>
-      <c r="R119" s="4">
-        <v>46105</v>
-      </c>
-      <c r="S119" s="4">
-        <v>46112</v>
-      </c>
-      <c r="T119" s="4">
-        <v>46112</v>
+        <v>46130</v>
       </c>
       <c r="V119" s="2" t="s">
-        <v>146</v>
+        <v>76</v>
       </c>
       <c r="W119" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="X119" s="2" t="s">
-        <v>53</v>
+        <v>99</v>
       </c>
       <c r="Y119" s="2" t="s">
-        <v>58</v>
+        <v>233</v>
       </c>
     </row>
     <row r="120" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A120" s="2" t="s">
-        <v>184</v>
+        <v>168</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>186</v>
+        <v>170</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>27</v>
+        <v>171</v>
       </c>
       <c r="F120" s="3">
         <v>0.55000000000000004</v>
@@ -10546,8 +10592,8 @@
       <c r="H120" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I120" s="2" t="s">
-        <v>213</v>
+      <c r="I120" s="11" t="s">
+        <v>160</v>
       </c>
       <c r="J120" s="2">
         <v>1</v>
@@ -10556,20 +10602,31 @@
         <v>1</v>
       </c>
       <c r="L120" s="4">
-        <v>46104</v>
-      </c>
-      <c r="M120" s="6"/>
-      <c r="N120" s="4">
-        <v>46106</v>
+        <v>46086</v>
+      </c>
+      <c r="P120" s="4">
+        <v>46094</v>
+      </c>
+      <c r="Q120" s="4">
+        <v>46103</v>
+      </c>
+      <c r="R120" s="4">
+        <v>46105</v>
+      </c>
+      <c r="S120" s="4">
+        <v>46112</v>
+      </c>
+      <c r="T120" s="4">
+        <v>46112</v>
       </c>
       <c r="V120" s="2" t="s">
-        <v>217</v>
+        <v>146</v>
       </c>
       <c r="W120" s="2" t="s">
         <v>30</v>
       </c>
       <c r="X120" s="2" t="s">
-        <v>135</v>
+        <v>53</v>
       </c>
       <c r="Y120" s="2" t="s">
         <v>58</v>
@@ -10577,13 +10634,13 @@
     </row>
     <row r="121" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A121" s="2" t="s">
-        <v>168</v>
+        <v>62</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>169</v>
+        <v>63</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>170</v>
+        <v>64</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>26</v>
@@ -10600,35 +10657,42 @@
       <c r="H121" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I121" s="11" t="s">
-        <v>330</v>
+      <c r="I121" s="2" t="s">
+        <v>65</v>
       </c>
       <c r="J121" s="2">
         <v>1</v>
       </c>
       <c r="K121" s="2">
-        <v>1</v>
-      </c>
-      <c r="L121" s="4">
-        <v>46126</v>
+        <v>9</v>
+      </c>
+      <c r="L121" s="5"/>
+      <c r="M121" s="4">
+        <v>45954</v>
+      </c>
+      <c r="N121" s="4">
+        <v>45954</v>
+      </c>
+      <c r="O121" s="4">
+        <v>45955</v>
       </c>
       <c r="P121" s="4">
-        <v>46132</v>
+        <v>45965</v>
       </c>
       <c r="Q121" s="4">
-        <v>46139</v>
+        <v>45974</v>
       </c>
       <c r="R121" s="4">
-        <v>46140</v>
+        <v>45975</v>
       </c>
       <c r="S121" s="4">
-        <v>46162</v>
+        <v>45975</v>
       </c>
       <c r="T121" s="4">
-        <v>46150</v>
+        <v>45975</v>
       </c>
       <c r="V121" s="2" t="s">
-        <v>146</v>
+        <v>250</v>
       </c>
       <c r="W121" s="2" t="s">
         <v>30</v>
@@ -10637,7 +10701,13 @@
         <v>53</v>
       </c>
       <c r="Y121" s="2" t="s">
-        <v>58</v>
+        <v>67</v>
+      </c>
+      <c r="Z121" s="4">
+        <v>45982</v>
+      </c>
+      <c r="AA121" s="4">
+        <v>46030</v>
       </c>
     </row>
     <row r="122" spans="1:27" x14ac:dyDescent="0.3">
@@ -10654,7 +10724,7 @@
         <v>26</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>27</v>
+        <v>171</v>
       </c>
       <c r="F122" s="3">
         <v>0.55000000000000004</v>
@@ -10666,7 +10736,7 @@
         <v>28</v>
       </c>
       <c r="I122" s="11" t="s">
-        <v>162</v>
+        <v>328</v>
       </c>
       <c r="J122" s="2">
         <v>1</v>
@@ -10675,22 +10745,22 @@
         <v>1</v>
       </c>
       <c r="L122" s="4">
-        <v>46086</v>
+        <v>46126</v>
       </c>
       <c r="P122" s="4">
-        <v>46094</v>
+        <v>46132</v>
       </c>
       <c r="Q122" s="4">
-        <v>46103</v>
+        <v>46139</v>
       </c>
       <c r="R122" s="4">
-        <v>46105</v>
+        <v>46140</v>
       </c>
       <c r="S122" s="4">
-        <v>46112</v>
+        <v>46162</v>
       </c>
       <c r="T122" s="4">
-        <v>46112</v>
+        <v>46150</v>
       </c>
       <c r="V122" s="2" t="s">
         <v>146</v>
@@ -10719,7 +10789,7 @@
         <v>26</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>27</v>
+        <v>171</v>
       </c>
       <c r="F123" s="3">
         <v>0.55000000000000004</v>
@@ -10731,7 +10801,7 @@
         <v>28</v>
       </c>
       <c r="I123" s="11" t="s">
-        <v>163</v>
+        <v>329</v>
       </c>
       <c r="J123" s="2">
         <v>1</v>
@@ -10740,22 +10810,22 @@
         <v>1</v>
       </c>
       <c r="L123" s="4">
-        <v>46086</v>
+        <v>46126</v>
       </c>
       <c r="P123" s="4">
-        <v>46094</v>
+        <v>46132</v>
       </c>
       <c r="Q123" s="4">
-        <v>46103</v>
+        <v>46139</v>
       </c>
       <c r="R123" s="4">
-        <v>46105</v>
+        <v>46140</v>
       </c>
       <c r="S123" s="4">
-        <v>46112</v>
+        <v>46162</v>
       </c>
       <c r="T123" s="4">
-        <v>46112</v>
+        <v>46150</v>
       </c>
       <c r="V123" s="2" t="s">
         <v>146</v>
@@ -10778,7 +10848,7 @@
         <v>169</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>45</v>
+        <v>170</v>
       </c>
       <c r="D124" s="2" t="s">
         <v>26</v>
@@ -10796,7 +10866,7 @@
         <v>28</v>
       </c>
       <c r="I124" s="11" t="s">
-        <v>307</v>
+        <v>161</v>
       </c>
       <c r="J124" s="2">
         <v>1</v>
@@ -10808,22 +10878,28 @@
         <v>46086</v>
       </c>
       <c r="P124" s="4">
-        <v>46132</v>
+        <v>46094</v>
+      </c>
+      <c r="Q124" s="4">
+        <v>46103</v>
+      </c>
+      <c r="R124" s="4">
+        <v>46105</v>
       </c>
       <c r="S124" s="4">
-        <v>46148</v>
+        <v>46112</v>
       </c>
       <c r="T124" s="4">
-        <v>46148</v>
+        <v>46112</v>
       </c>
       <c r="V124" s="2" t="s">
-        <v>122</v>
+        <v>146</v>
       </c>
       <c r="W124" s="2" t="s">
         <v>30</v>
       </c>
       <c r="X124" s="2" t="s">
-        <v>365</v>
+        <v>53</v>
       </c>
       <c r="Y124" s="2" t="s">
         <v>58</v>
@@ -10831,13 +10907,13 @@
     </row>
     <row r="125" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A125" s="2" t="s">
-        <v>168</v>
+        <v>184</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>45</v>
+        <v>186</v>
       </c>
       <c r="D125" s="2" t="s">
         <v>26</v>
@@ -10854,8 +10930,8 @@
       <c r="H125" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I125" s="11" t="s">
-        <v>200</v>
+      <c r="I125" s="2" t="s">
+        <v>213</v>
       </c>
       <c r="J125" s="2">
         <v>1</v>
@@ -10864,22 +10940,20 @@
         <v>1</v>
       </c>
       <c r="L125" s="4">
-        <v>46086</v>
-      </c>
-      <c r="S125" s="4">
-        <v>46142</v>
-      </c>
-      <c r="T125" s="4">
-        <v>46142</v>
+        <v>46104</v>
+      </c>
+      <c r="M125" s="6"/>
+      <c r="N125" s="4">
+        <v>46106</v>
       </c>
       <c r="V125" s="2" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="W125" s="2" t="s">
         <v>30</v>
       </c>
       <c r="X125" s="2" t="s">
-        <v>366</v>
+        <v>135</v>
       </c>
       <c r="Y125" s="2" t="s">
         <v>58</v>
@@ -10893,7 +10967,7 @@
         <v>169</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>45</v>
+        <v>170</v>
       </c>
       <c r="D126" s="2" t="s">
         <v>26</v>
@@ -10911,7 +10985,7 @@
         <v>28</v>
       </c>
       <c r="I126" s="11" t="s">
-        <v>201</v>
+        <v>330</v>
       </c>
       <c r="J126" s="2">
         <v>1</v>
@@ -10920,22 +10994,31 @@
         <v>1</v>
       </c>
       <c r="L126" s="4">
-        <v>46086</v>
+        <v>46126</v>
+      </c>
+      <c r="P126" s="4">
+        <v>46132</v>
+      </c>
+      <c r="Q126" s="4">
+        <v>46139</v>
+      </c>
+      <c r="R126" s="4">
+        <v>46140</v>
       </c>
       <c r="S126" s="4">
-        <v>46142</v>
+        <v>46162</v>
       </c>
       <c r="T126" s="4">
-        <v>46142</v>
+        <v>46150</v>
       </c>
       <c r="V126" s="2" t="s">
-        <v>207</v>
+        <v>146</v>
       </c>
       <c r="W126" s="2" t="s">
         <v>30</v>
       </c>
       <c r="X126" s="2" t="s">
-        <v>366</v>
+        <v>53</v>
       </c>
       <c r="Y126" s="2" t="s">
         <v>58</v>
@@ -10949,7 +11032,7 @@
         <v>169</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>45</v>
+        <v>170</v>
       </c>
       <c r="D127" s="2" t="s">
         <v>26</v>
@@ -10967,7 +11050,7 @@
         <v>28</v>
       </c>
       <c r="I127" s="11" t="s">
-        <v>202</v>
+        <v>162</v>
       </c>
       <c r="J127" s="2">
         <v>1</v>
@@ -10978,20 +11061,29 @@
       <c r="L127" s="4">
         <v>46086</v>
       </c>
+      <c r="P127" s="4">
+        <v>46094</v>
+      </c>
+      <c r="Q127" s="4">
+        <v>46103</v>
+      </c>
+      <c r="R127" s="4">
+        <v>46105</v>
+      </c>
       <c r="S127" s="4">
-        <v>46142</v>
+        <v>46112</v>
       </c>
       <c r="T127" s="4">
-        <v>46142</v>
+        <v>46112</v>
       </c>
       <c r="V127" s="2" t="s">
-        <v>207</v>
+        <v>146</v>
       </c>
       <c r="W127" s="2" t="s">
         <v>30</v>
       </c>
       <c r="X127" s="2" t="s">
-        <v>366</v>
+        <v>53</v>
       </c>
       <c r="Y127" s="2" t="s">
         <v>58</v>
@@ -11005,7 +11097,7 @@
         <v>169</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>45</v>
+        <v>170</v>
       </c>
       <c r="D128" s="2" t="s">
         <v>26</v>
@@ -11023,7 +11115,7 @@
         <v>28</v>
       </c>
       <c r="I128" s="11" t="s">
-        <v>364</v>
+        <v>163</v>
       </c>
       <c r="J128" s="2">
         <v>1</v>
@@ -11034,26 +11126,35 @@
       <c r="L128" s="4">
         <v>46086</v>
       </c>
+      <c r="P128" s="4">
+        <v>46094</v>
+      </c>
+      <c r="Q128" s="4">
+        <v>46103</v>
+      </c>
+      <c r="R128" s="4">
+        <v>46105</v>
+      </c>
       <c r="S128" s="4">
-        <v>46142</v>
+        <v>46112</v>
       </c>
       <c r="T128" s="4">
-        <v>46142</v>
+        <v>46112</v>
       </c>
       <c r="V128" s="2" t="s">
-        <v>207</v>
+        <v>146</v>
       </c>
       <c r="W128" s="2" t="s">
         <v>30</v>
       </c>
       <c r="X128" s="2" t="s">
-        <v>366</v>
+        <v>53</v>
       </c>
       <c r="Y128" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="129" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A129" s="2" t="s">
         <v>168</v>
       </c>
@@ -11079,7 +11180,7 @@
         <v>28</v>
       </c>
       <c r="I129" s="11" t="s">
-        <v>203</v>
+        <v>307</v>
       </c>
       <c r="J129" s="2">
         <v>1</v>
@@ -11090,26 +11191,29 @@
       <c r="L129" s="4">
         <v>46086</v>
       </c>
+      <c r="P129" s="4">
+        <v>46132</v>
+      </c>
       <c r="S129" s="4">
-        <v>46142</v>
+        <v>46148</v>
       </c>
       <c r="T129" s="4">
-        <v>46142</v>
+        <v>46148</v>
       </c>
       <c r="V129" s="2" t="s">
-        <v>207</v>
+        <v>122</v>
       </c>
       <c r="W129" s="2" t="s">
         <v>30</v>
       </c>
       <c r="X129" s="2" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="Y129" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="130" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A130" s="2" t="s">
         <v>168</v>
       </c>
@@ -11135,7 +11239,7 @@
         <v>28</v>
       </c>
       <c r="I130" s="11" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="J130" s="2">
         <v>1</v>
@@ -11159,13 +11263,13 @@
         <v>30</v>
       </c>
       <c r="X130" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="Y130" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="131" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A131" s="2" t="s">
         <v>168</v>
       </c>
@@ -11191,7 +11295,7 @@
         <v>28</v>
       </c>
       <c r="I131" s="11" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="J131" s="2">
         <v>1</v>
@@ -11215,13 +11319,13 @@
         <v>30</v>
       </c>
       <c r="X131" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="Y131" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="132" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A132" s="2" t="s">
         <v>168</v>
       </c>
@@ -11247,7 +11351,7 @@
         <v>28</v>
       </c>
       <c r="I132" s="11" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="J132" s="2">
         <v>1</v>
@@ -11271,13 +11375,13 @@
         <v>30</v>
       </c>
       <c r="X132" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="Y132" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="133" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A133" s="2" t="s">
         <v>168</v>
       </c>
@@ -11285,7 +11389,7 @@
         <v>169</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>170</v>
+        <v>45</v>
       </c>
       <c r="D133" s="2" t="s">
         <v>26</v>
@@ -11303,7 +11407,7 @@
         <v>28</v>
       </c>
       <c r="I133" s="11" t="s">
-        <v>164</v>
+        <v>363</v>
       </c>
       <c r="J133" s="2">
         <v>1</v>
@@ -11314,35 +11418,26 @@
       <c r="L133" s="4">
         <v>46086</v>
       </c>
-      <c r="P133" s="4">
-        <v>46094</v>
-      </c>
-      <c r="Q133" s="4">
-        <v>46103</v>
-      </c>
-      <c r="R133" s="4">
-        <v>46105</v>
-      </c>
       <c r="S133" s="4">
-        <v>46112</v>
+        <v>46142</v>
       </c>
       <c r="T133" s="4">
-        <v>46112</v>
+        <v>46142</v>
       </c>
       <c r="V133" s="2" t="s">
-        <v>146</v>
+        <v>207</v>
       </c>
       <c r="W133" s="2" t="s">
         <v>30</v>
       </c>
       <c r="X133" s="2" t="s">
-        <v>53</v>
+        <v>365</v>
       </c>
       <c r="Y133" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="134" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A134" s="2" t="s">
         <v>168</v>
       </c>
@@ -11350,7 +11445,7 @@
         <v>169</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>170</v>
+        <v>45</v>
       </c>
       <c r="D134" s="2" t="s">
         <v>26</v>
@@ -11368,7 +11463,7 @@
         <v>28</v>
       </c>
       <c r="I134" s="11" t="s">
-        <v>331</v>
+        <v>203</v>
       </c>
       <c r="J134" s="2">
         <v>1</v>
@@ -11377,51 +11472,39 @@
         <v>1</v>
       </c>
       <c r="L134" s="4">
-        <v>46126</v>
-      </c>
-      <c r="M134" s="6"/>
-      <c r="N134" s="6"/>
-      <c r="O134" s="6"/>
-      <c r="P134" s="4">
-        <v>46132</v>
-      </c>
-      <c r="Q134" s="4">
-        <v>46139</v>
-      </c>
-      <c r="R134" s="4">
-        <v>46140</v>
+        <v>46086</v>
       </c>
       <c r="S134" s="4">
-        <v>46162</v>
+        <v>46142</v>
       </c>
       <c r="T134" s="4">
-        <v>46150</v>
+        <v>46142</v>
       </c>
       <c r="V134" s="2" t="s">
-        <v>146</v>
+        <v>207</v>
       </c>
       <c r="W134" s="2" t="s">
         <v>30</v>
       </c>
       <c r="X134" s="2" t="s">
-        <v>53</v>
+        <v>365</v>
       </c>
       <c r="Y134" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="135" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A135" s="2" t="s">
-        <v>142</v>
+        <v>168</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>143</v>
+        <v>169</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>144</v>
+        <v>45</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="E135" s="2" t="s">
         <v>27</v>
@@ -11430,13 +11513,13 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G135" s="7">
-        <v>15</v>
+        <v>14.2</v>
       </c>
       <c r="H135" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I135" s="2" t="s">
-        <v>145</v>
+      <c r="I135" s="11" t="s">
+        <v>204</v>
       </c>
       <c r="J135" s="2">
         <v>1</v>
@@ -11445,39 +11528,28 @@
         <v>1</v>
       </c>
       <c r="L135" s="4">
-        <v>46055</v>
-      </c>
-      <c r="N135" s="6"/>
-      <c r="O135" s="6"/>
-      <c r="P135" s="4">
-        <v>46060</v>
-      </c>
-      <c r="Q135" s="4">
-        <v>46063</v>
-      </c>
-      <c r="R135" s="4">
-        <v>46064</v>
+        <v>46086</v>
       </c>
       <c r="S135" s="4">
-        <v>46066</v>
+        <v>46142</v>
       </c>
       <c r="T135" s="4">
-        <v>46066</v>
+        <v>46142</v>
       </c>
       <c r="V135" s="2" t="s">
-        <v>254</v>
+        <v>207</v>
       </c>
       <c r="W135" s="2" t="s">
         <v>30</v>
       </c>
       <c r="X135" s="2" t="s">
-        <v>53</v>
+        <v>365</v>
       </c>
       <c r="Y135" s="2" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="136" spans="1:26" x14ac:dyDescent="0.3">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="136" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A136" s="2" t="s">
         <v>168</v>
       </c>
@@ -11485,7 +11557,7 @@
         <v>169</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>170</v>
+        <v>45</v>
       </c>
       <c r="D136" s="2" t="s">
         <v>26</v>
@@ -11503,7 +11575,7 @@
         <v>28</v>
       </c>
       <c r="I136" s="11" t="s">
-        <v>165</v>
+        <v>205</v>
       </c>
       <c r="J136" s="2">
         <v>1</v>
@@ -11514,35 +11586,26 @@
       <c r="L136" s="4">
         <v>46086</v>
       </c>
-      <c r="P136" s="4">
-        <v>46094</v>
-      </c>
-      <c r="Q136" s="4">
-        <v>46103</v>
-      </c>
-      <c r="R136" s="4">
-        <v>46105</v>
-      </c>
       <c r="S136" s="4">
-        <v>46112</v>
+        <v>46142</v>
       </c>
       <c r="T136" s="4">
-        <v>46112</v>
+        <v>46142</v>
       </c>
       <c r="V136" s="2" t="s">
-        <v>146</v>
+        <v>207</v>
       </c>
       <c r="W136" s="2" t="s">
         <v>30</v>
       </c>
       <c r="X136" s="2" t="s">
-        <v>53</v>
+        <v>365</v>
       </c>
       <c r="Y136" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="137" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A137" s="2" t="s">
         <v>168</v>
       </c>
@@ -11550,7 +11613,7 @@
         <v>169</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>170</v>
+        <v>45</v>
       </c>
       <c r="D137" s="2" t="s">
         <v>26</v>
@@ -11568,7 +11631,7 @@
         <v>28</v>
       </c>
       <c r="I137" s="11" t="s">
-        <v>332</v>
+        <v>206</v>
       </c>
       <c r="J137" s="2">
         <v>1</v>
@@ -11577,40 +11640,28 @@
         <v>1</v>
       </c>
       <c r="L137" s="4">
-        <v>46126</v>
-      </c>
-      <c r="M137" s="10"/>
-      <c r="N137" s="10"/>
-      <c r="O137" s="10"/>
-      <c r="P137" s="4">
-        <v>46132</v>
-      </c>
-      <c r="Q137" s="4">
-        <v>46139</v>
-      </c>
-      <c r="R137" s="4">
-        <v>46140</v>
+        <v>46086</v>
       </c>
       <c r="S137" s="4">
-        <v>46162</v>
+        <v>46142</v>
       </c>
       <c r="T137" s="4">
-        <v>46150</v>
+        <v>46142</v>
       </c>
       <c r="V137" s="2" t="s">
-        <v>146</v>
+        <v>207</v>
       </c>
       <c r="W137" s="2" t="s">
         <v>30</v>
       </c>
       <c r="X137" s="2" t="s">
-        <v>53</v>
+        <v>365</v>
       </c>
       <c r="Y137" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="138" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A138" s="2" t="s">
         <v>168</v>
       </c>
@@ -11636,7 +11687,7 @@
         <v>28</v>
       </c>
       <c r="I138" s="11" t="s">
-        <v>333</v>
+        <v>164</v>
       </c>
       <c r="J138" s="2">
         <v>1</v>
@@ -11645,25 +11696,22 @@
         <v>1</v>
       </c>
       <c r="L138" s="4">
-        <v>46126</v>
-      </c>
-      <c r="M138" s="10"/>
-      <c r="N138" s="10"/>
-      <c r="O138" s="10"/>
+        <v>46086</v>
+      </c>
       <c r="P138" s="4">
-        <v>46132</v>
+        <v>46094</v>
       </c>
       <c r="Q138" s="4">
-        <v>46139</v>
+        <v>46103</v>
       </c>
       <c r="R138" s="4">
-        <v>46140</v>
+        <v>46105</v>
       </c>
       <c r="S138" s="4">
-        <v>46162</v>
+        <v>46112</v>
       </c>
       <c r="T138" s="4">
-        <v>46150</v>
+        <v>46112</v>
       </c>
       <c r="V138" s="2" t="s">
         <v>146</v>
@@ -11678,7 +11726,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="139" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A139" s="2" t="s">
         <v>168</v>
       </c>
@@ -11704,7 +11752,7 @@
         <v>28</v>
       </c>
       <c r="I139" s="11" t="s">
-        <v>166</v>
+        <v>331</v>
       </c>
       <c r="J139" s="2">
         <v>1</v>
@@ -11713,22 +11761,25 @@
         <v>1</v>
       </c>
       <c r="L139" s="4">
-        <v>46086</v>
-      </c>
+        <v>46126</v>
+      </c>
+      <c r="M139" s="6"/>
+      <c r="N139" s="6"/>
+      <c r="O139" s="6"/>
       <c r="P139" s="4">
-        <v>46094</v>
+        <v>46132</v>
       </c>
       <c r="Q139" s="4">
-        <v>46103</v>
+        <v>46139</v>
       </c>
       <c r="R139" s="4">
-        <v>46105</v>
+        <v>46140</v>
       </c>
       <c r="S139" s="4">
-        <v>46112</v>
+        <v>46162</v>
       </c>
       <c r="T139" s="4">
-        <v>46112</v>
+        <v>46150</v>
       </c>
       <c r="V139" s="2" t="s">
         <v>146</v>
@@ -11743,18 +11794,18 @@
         <v>58</v>
       </c>
     </row>
-    <row r="140" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A140" s="2" t="s">
-        <v>168</v>
+        <v>142</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>169</v>
+        <v>143</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>170</v>
+        <v>144</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E140" s="2" t="s">
         <v>27</v>
@@ -11763,13 +11814,13 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G140" s="7">
-        <v>14.2</v>
+        <v>15</v>
       </c>
       <c r="H140" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I140" s="11" t="s">
-        <v>167</v>
+      <c r="I140" s="2" t="s">
+        <v>145</v>
       </c>
       <c r="J140" s="2">
         <v>1</v>
@@ -11778,25 +11829,27 @@
         <v>1</v>
       </c>
       <c r="L140" s="4">
-        <v>46086</v>
-      </c>
+        <v>46055</v>
+      </c>
+      <c r="N140" s="6"/>
+      <c r="O140" s="6"/>
       <c r="P140" s="4">
-        <v>46094</v>
+        <v>46060</v>
       </c>
       <c r="Q140" s="4">
-        <v>46103</v>
+        <v>46063</v>
       </c>
       <c r="R140" s="4">
-        <v>46105</v>
+        <v>46064</v>
       </c>
       <c r="S140" s="4">
-        <v>46112</v>
+        <v>46066</v>
       </c>
       <c r="T140" s="4">
-        <v>46112</v>
+        <v>46066</v>
       </c>
       <c r="V140" s="2" t="s">
-        <v>146</v>
+        <v>254</v>
       </c>
       <c r="W140" s="2" t="s">
         <v>30</v>
@@ -11805,10 +11858,10 @@
         <v>53</v>
       </c>
       <c r="Y140" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="141" spans="1:26" x14ac:dyDescent="0.3">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="141" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A141" s="2" t="s">
         <v>168</v>
       </c>
@@ -11834,7 +11887,7 @@
         <v>28</v>
       </c>
       <c r="I141" s="11" t="s">
-        <v>334</v>
+        <v>165</v>
       </c>
       <c r="J141" s="2">
         <v>1</v>
@@ -11843,22 +11896,22 @@
         <v>1</v>
       </c>
       <c r="L141" s="4">
-        <v>46126</v>
+        <v>46086</v>
       </c>
       <c r="P141" s="4">
-        <v>46132</v>
+        <v>46094</v>
       </c>
       <c r="Q141" s="4">
-        <v>46139</v>
+        <v>46103</v>
       </c>
       <c r="R141" s="4">
-        <v>46140</v>
+        <v>46105</v>
       </c>
       <c r="S141" s="4">
-        <v>46162</v>
+        <v>46112</v>
       </c>
       <c r="T141" s="4">
-        <v>46150</v>
+        <v>46112</v>
       </c>
       <c r="V141" s="2" t="s">
         <v>146</v>
@@ -11873,7 +11926,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="142" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A142" s="2" t="s">
         <v>168</v>
       </c>
@@ -11899,7 +11952,7 @@
         <v>28</v>
       </c>
       <c r="I142" s="11" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="J142" s="2">
         <v>1</v>
@@ -11910,6 +11963,9 @@
       <c r="L142" s="4">
         <v>46126</v>
       </c>
+      <c r="M142" s="10"/>
+      <c r="N142" s="10"/>
+      <c r="O142" s="10"/>
       <c r="P142" s="4">
         <v>46132</v>
       </c>
@@ -11938,15 +11994,15 @@
         <v>58</v>
       </c>
     </row>
-    <row r="143" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A143" s="2" t="s">
-        <v>43</v>
+        <v>168</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>44</v>
+        <v>169</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>45</v>
+        <v>170</v>
       </c>
       <c r="D143" s="2" t="s">
         <v>26</v>
@@ -11963,8 +12019,8 @@
       <c r="H143" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I143" s="2" t="s">
-        <v>48</v>
+      <c r="I143" s="11" t="s">
+        <v>333</v>
       </c>
       <c r="J143" s="2">
         <v>1</v>
@@ -11973,37 +12029,31 @@
         <v>1</v>
       </c>
       <c r="L143" s="4">
-        <v>45978</v>
-      </c>
-      <c r="M143" s="4">
-        <v>45978</v>
-      </c>
-      <c r="N143" s="4">
-        <v>45985</v>
-      </c>
-      <c r="O143" s="4">
-        <v>45996</v>
-      </c>
+        <v>46126</v>
+      </c>
+      <c r="M143" s="10"/>
+      <c r="N143" s="10"/>
+      <c r="O143" s="10"/>
       <c r="P143" s="4">
-        <v>45989</v>
+        <v>46132</v>
       </c>
       <c r="Q143" s="4">
-        <v>46003</v>
+        <v>46139</v>
       </c>
       <c r="R143" s="4">
-        <v>46006</v>
+        <v>46140</v>
       </c>
       <c r="S143" s="4">
-        <v>46006</v>
+        <v>46162</v>
       </c>
       <c r="T143" s="4">
-        <v>46006</v>
+        <v>46150</v>
       </c>
       <c r="V143" s="2" t="s">
-        <v>81</v>
+        <v>146</v>
       </c>
       <c r="W143" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="X143" s="2" t="s">
         <v>53</v>
@@ -12011,11 +12061,8 @@
       <c r="Y143" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="Z143" s="4">
-        <v>46041</v>
-      </c>
-    </row>
-    <row r="144" spans="1:26" x14ac:dyDescent="0.3">
+    </row>
+    <row r="144" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A144" s="2" t="s">
         <v>168</v>
       </c>
@@ -12023,7 +12070,7 @@
         <v>169</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>45</v>
+        <v>170</v>
       </c>
       <c r="D144" s="2" t="s">
         <v>26</v>
@@ -12041,7 +12088,7 @@
         <v>28</v>
       </c>
       <c r="I144" s="11" t="s">
-        <v>300</v>
+        <v>166</v>
       </c>
       <c r="J144" s="2">
         <v>1</v>
@@ -12050,22 +12097,22 @@
         <v>1</v>
       </c>
       <c r="L144" s="4">
-        <v>46126</v>
+        <v>46086</v>
       </c>
       <c r="P144" s="4">
-        <v>46132</v>
+        <v>46094</v>
       </c>
       <c r="Q144" s="4">
-        <v>46139</v>
+        <v>46103</v>
       </c>
       <c r="R144" s="4">
-        <v>46140</v>
+        <v>46105</v>
       </c>
       <c r="S144" s="4">
-        <v>46162</v>
+        <v>46112</v>
       </c>
       <c r="T144" s="4">
-        <v>46150</v>
+        <v>46112</v>
       </c>
       <c r="V144" s="2" t="s">
         <v>146</v>
@@ -12106,7 +12153,7 @@
         <v>28</v>
       </c>
       <c r="I145" s="11" t="s">
-        <v>341</v>
+        <v>167</v>
       </c>
       <c r="J145" s="2">
         <v>1</v>
@@ -12171,7 +12218,7 @@
         <v>28</v>
       </c>
       <c r="I146" s="11" t="s">
-        <v>192</v>
+        <v>334</v>
       </c>
       <c r="J146" s="2">
         <v>1</v>
@@ -12180,22 +12227,22 @@
         <v>1</v>
       </c>
       <c r="L146" s="4">
-        <v>46086</v>
+        <v>46126</v>
       </c>
       <c r="P146" s="4">
-        <v>46094</v>
+        <v>46132</v>
       </c>
       <c r="Q146" s="4">
-        <v>46103</v>
+        <v>46139</v>
       </c>
       <c r="R146" s="4">
-        <v>46105</v>
+        <v>46140</v>
       </c>
       <c r="S146" s="4">
-        <v>46112</v>
+        <v>46162</v>
       </c>
       <c r="T146" s="4">
-        <v>46112</v>
+        <v>46150</v>
       </c>
       <c r="V146" s="2" t="s">
         <v>146</v>
@@ -12236,7 +12283,7 @@
         <v>28</v>
       </c>
       <c r="I147" s="11" t="s">
-        <v>193</v>
+        <v>335</v>
       </c>
       <c r="J147" s="2">
         <v>1</v>
@@ -12245,22 +12292,22 @@
         <v>1</v>
       </c>
       <c r="L147" s="4">
-        <v>46086</v>
+        <v>46126</v>
       </c>
       <c r="P147" s="4">
-        <v>46094</v>
+        <v>46132</v>
       </c>
       <c r="Q147" s="4">
-        <v>46103</v>
+        <v>46139</v>
       </c>
       <c r="R147" s="4">
-        <v>46105</v>
+        <v>46140</v>
       </c>
       <c r="S147" s="4">
-        <v>46112</v>
+        <v>46162</v>
       </c>
       <c r="T147" s="4">
-        <v>46112</v>
+        <v>46150</v>
       </c>
       <c r="V147" s="2" t="s">
         <v>146</v>
@@ -12277,16 +12324,16 @@
     </row>
     <row r="148" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A148" s="2" t="s">
-        <v>184</v>
+        <v>43</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>257</v>
+        <v>44</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>103</v>
+        <v>45</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="E148" s="2" t="s">
         <v>27</v>
@@ -12295,13 +12342,13 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G148" s="7">
-        <v>15</v>
+        <v>14.2</v>
       </c>
       <c r="H148" s="2" t="s">
         <v>28</v>
       </c>
       <c r="I148" s="2" t="s">
-        <v>321</v>
+        <v>48</v>
       </c>
       <c r="J148" s="2">
         <v>1</v>
@@ -12310,42 +12357,60 @@
         <v>1</v>
       </c>
       <c r="L148" s="4">
-        <v>46141</v>
+        <v>45978</v>
+      </c>
+      <c r="M148" s="4">
+        <v>45978</v>
       </c>
       <c r="N148" s="4">
-        <v>46142</v>
+        <v>45985</v>
       </c>
       <c r="O148" s="4">
-        <v>46142</v>
+        <v>45996</v>
       </c>
       <c r="P148" s="4">
-        <v>46142</v>
+        <v>45989</v>
+      </c>
+      <c r="Q148" s="4">
+        <v>46003</v>
+      </c>
+      <c r="R148" s="4">
+        <v>46006</v>
+      </c>
+      <c r="S148" s="4">
+        <v>46006</v>
+      </c>
+      <c r="T148" s="4">
+        <v>46006</v>
       </c>
       <c r="V148" s="2" t="s">
-        <v>324</v>
+        <v>81</v>
       </c>
       <c r="W148" s="2" t="s">
-        <v>326</v>
+        <v>29</v>
       </c>
       <c r="X148" s="2" t="s">
-        <v>99</v>
+        <v>53</v>
       </c>
       <c r="Y148" s="2" t="s">
         <v>58</v>
       </c>
+      <c r="Z148" s="4">
+        <v>46041</v>
+      </c>
     </row>
     <row r="149" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A149" s="2" t="s">
-        <v>184</v>
+        <v>168</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>257</v>
+        <v>169</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>103</v>
+        <v>45</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="E149" s="2" t="s">
         <v>27</v>
@@ -12354,13 +12419,13 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G149" s="7">
-        <v>15</v>
+        <v>14.2</v>
       </c>
       <c r="H149" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I149" s="2" t="s">
-        <v>322</v>
+      <c r="I149" s="11" t="s">
+        <v>300</v>
       </c>
       <c r="J149" s="2">
         <v>1</v>
@@ -12369,25 +12434,31 @@
         <v>1</v>
       </c>
       <c r="L149" s="4">
-        <v>46141</v>
-      </c>
-      <c r="N149" s="4">
-        <v>46142</v>
-      </c>
-      <c r="O149" s="4">
-        <v>46142</v>
+        <v>46126</v>
       </c>
       <c r="P149" s="4">
-        <v>46142</v>
+        <v>46132</v>
+      </c>
+      <c r="Q149" s="4">
+        <v>46139</v>
+      </c>
+      <c r="R149" s="4">
+        <v>46140</v>
+      </c>
+      <c r="S149" s="4">
+        <v>46162</v>
+      </c>
+      <c r="T149" s="4">
+        <v>46150</v>
       </c>
       <c r="V149" s="2" t="s">
-        <v>325</v>
+        <v>146</v>
       </c>
       <c r="W149" s="2" t="s">
-        <v>326</v>
+        <v>30</v>
       </c>
       <c r="X149" s="2" t="s">
-        <v>99</v>
+        <v>53</v>
       </c>
       <c r="Y149" s="2" t="s">
         <v>58</v>
@@ -12395,16 +12466,16 @@
     </row>
     <row r="150" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A150" s="2" t="s">
-        <v>184</v>
+        <v>168</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>257</v>
+        <v>169</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>103</v>
+        <v>170</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="E150" s="2" t="s">
         <v>27</v>
@@ -12413,13 +12484,13 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G150" s="7">
-        <v>15</v>
+        <v>14.2</v>
       </c>
       <c r="H150" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I150" s="2" t="s">
-        <v>323</v>
+      <c r="I150" s="11" t="s">
+        <v>341</v>
       </c>
       <c r="J150" s="2">
         <v>1</v>
@@ -12428,25 +12499,31 @@
         <v>1</v>
       </c>
       <c r="L150" s="4">
-        <v>46141</v>
-      </c>
-      <c r="N150" s="4">
-        <v>46142</v>
-      </c>
-      <c r="O150" s="4">
-        <v>46142</v>
+        <v>46086</v>
       </c>
       <c r="P150" s="4">
-        <v>46142</v>
+        <v>46094</v>
+      </c>
+      <c r="Q150" s="4">
+        <v>46103</v>
+      </c>
+      <c r="R150" s="4">
+        <v>46105</v>
+      </c>
+      <c r="S150" s="4">
+        <v>46112</v>
+      </c>
+      <c r="T150" s="4">
+        <v>46112</v>
       </c>
       <c r="V150" s="2" t="s">
-        <v>325</v>
+        <v>146</v>
       </c>
       <c r="W150" s="2" t="s">
-        <v>326</v>
+        <v>30</v>
       </c>
       <c r="X150" s="2" t="s">
-        <v>99</v>
+        <v>53</v>
       </c>
       <c r="Y150" s="2" t="s">
         <v>58</v>
@@ -12454,16 +12531,16 @@
     </row>
     <row r="151" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A151" s="2" t="s">
-        <v>62</v>
+        <v>168</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>63</v>
+        <v>169</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>64</v>
+        <v>170</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="E151" s="2" t="s">
         <v>27</v>
@@ -12472,13 +12549,13 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G151" s="7">
-        <v>14.5</v>
+        <v>14.2</v>
       </c>
       <c r="H151" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I151" s="15" t="s">
-        <v>138</v>
+      <c r="I151" s="11" t="s">
+        <v>192</v>
       </c>
       <c r="J151" s="2">
         <v>1</v>
@@ -12487,51 +12564,48 @@
         <v>1</v>
       </c>
       <c r="L151" s="4">
-        <v>46066</v>
-      </c>
-      <c r="M151" s="6"/>
-      <c r="N151" s="6"/>
-      <c r="O151" s="6"/>
+        <v>46086</v>
+      </c>
       <c r="P151" s="4">
-        <v>46076</v>
+        <v>46094</v>
       </c>
       <c r="Q151" s="4">
-        <v>46083</v>
+        <v>46103</v>
       </c>
       <c r="R151" s="4">
-        <v>46093</v>
+        <v>46105</v>
       </c>
       <c r="S151" s="4">
-        <v>46094</v>
+        <v>46112</v>
       </c>
       <c r="T151" s="4">
-        <v>46094</v>
+        <v>46112</v>
       </c>
       <c r="V151" s="2" t="s">
-        <v>52</v>
+        <v>146</v>
       </c>
       <c r="W151" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="X151" s="2" t="s">
         <v>53</v>
       </c>
       <c r="Y151" s="2" t="s">
-        <v>140</v>
+        <v>58</v>
       </c>
     </row>
     <row r="152" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A152" s="2" t="s">
-        <v>62</v>
+        <v>168</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>63</v>
+        <v>169</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>64</v>
+        <v>170</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="E152" s="2" t="s">
         <v>27</v>
@@ -12540,76 +12614,60 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G152" s="7">
-        <v>14.5</v>
+        <v>14.2</v>
       </c>
       <c r="H152" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I152" s="2" t="s">
-        <v>176</v>
+      <c r="I152" s="11" t="s">
+        <v>193</v>
       </c>
       <c r="J152" s="2">
         <v>1</v>
       </c>
       <c r="K152" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L152" s="4">
-        <v>45800</v>
-      </c>
-      <c r="M152" s="10">
-        <v>45999</v>
-      </c>
-      <c r="N152" s="10">
-        <v>46000</v>
-      </c>
-      <c r="O152" s="10">
-        <v>46001</v>
-      </c>
-      <c r="P152" s="10">
-        <v>46011</v>
+        <v>46086</v>
+      </c>
+      <c r="P152" s="4">
+        <v>46094</v>
       </c>
       <c r="Q152" s="4">
-        <v>46025</v>
+        <v>46103</v>
       </c>
       <c r="R152" s="4">
-        <v>46034</v>
+        <v>46105</v>
       </c>
       <c r="S152" s="4">
-        <v>46035</v>
+        <v>46112</v>
       </c>
       <c r="T152" s="4">
-        <v>46035</v>
+        <v>46112</v>
       </c>
       <c r="V152" s="2" t="s">
-        <v>76</v>
+        <v>146</v>
       </c>
       <c r="W152" s="2" t="s">
-        <v>92</v>
+        <v>30</v>
       </c>
       <c r="X152" s="2" t="s">
         <v>53</v>
       </c>
       <c r="Y152" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="Z152" s="4">
-        <v>46065</v>
-      </c>
-      <c r="AA152" s="4">
-        <v>46112</v>
-      </c>
-      <c r="AB152" s="4"/>
+        <v>58</v>
+      </c>
     </row>
     <row r="153" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A153" s="2" t="s">
-        <v>62</v>
+        <v>184</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>63</v>
+        <v>257</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>64</v>
+        <v>103</v>
       </c>
       <c r="D153" s="2" t="s">
         <v>34</v>
@@ -12621,72 +12679,54 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G153" s="7">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="H153" s="2" t="s">
-        <v>177</v>
+        <v>28</v>
       </c>
       <c r="I153" s="2" t="s">
-        <v>178</v>
+        <v>321</v>
       </c>
       <c r="J153" s="2">
         <v>1</v>
       </c>
       <c r="K153" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L153" s="4">
-        <v>45302</v>
-      </c>
-      <c r="M153" s="10">
-        <v>45645</v>
-      </c>
-      <c r="N153" s="10">
-        <v>45652</v>
-      </c>
-      <c r="O153" s="10">
-        <v>45652</v>
-      </c>
-      <c r="P153" s="10">
-        <v>45670</v>
-      </c>
-      <c r="Q153" s="10">
-        <v>45672</v>
-      </c>
-      <c r="R153" s="10">
-        <v>45672</v>
-      </c>
-      <c r="S153" s="4">
-        <v>45673</v>
-      </c>
-      <c r="T153" s="4">
-        <v>45673</v>
+        <v>46141</v>
+      </c>
+      <c r="N153" s="4">
+        <v>46142</v>
+      </c>
+      <c r="O153" s="4">
+        <v>46142</v>
+      </c>
+      <c r="P153" s="4">
+        <v>46142</v>
       </c>
       <c r="V153" s="2" t="s">
-        <v>76</v>
+        <v>324</v>
       </c>
       <c r="W153" s="2" t="s">
-        <v>92</v>
+        <v>326</v>
       </c>
       <c r="X153" s="2" t="s">
-        <v>53</v>
+        <v>99</v>
       </c>
       <c r="Y153" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="Z153" s="4">
-        <v>46092</v>
+        <v>58</v>
       </c>
     </row>
     <row r="154" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A154" s="2" t="s">
-        <v>62</v>
+        <v>184</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>80</v>
+        <v>257</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>64</v>
+        <v>103</v>
       </c>
       <c r="D154" s="2" t="s">
         <v>34</v>
@@ -12698,69 +12738,54 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G154" s="7">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="H154" s="2" t="s">
         <v>28</v>
       </c>
       <c r="I154" s="2" t="s">
-        <v>90</v>
+        <v>322</v>
       </c>
       <c r="J154" s="2">
         <v>1</v>
       </c>
       <c r="K154" s="2">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L154" s="4">
-        <v>45644</v>
-      </c>
-      <c r="M154" s="10">
-        <v>46063</v>
-      </c>
-      <c r="N154" s="10">
-        <v>46063</v>
-      </c>
-      <c r="O154" s="10">
-        <v>46063</v>
-      </c>
-      <c r="P154" s="10">
-        <v>46063</v>
-      </c>
-      <c r="Q154" s="10">
-        <v>46073</v>
-      </c>
-      <c r="R154" s="4">
-        <v>46076</v>
-      </c>
-      <c r="S154" s="4">
-        <v>46079</v>
-      </c>
-      <c r="T154" s="4">
-        <v>46079</v>
+        <v>46141</v>
+      </c>
+      <c r="N154" s="4">
+        <v>46142</v>
+      </c>
+      <c r="O154" s="4">
+        <v>46142</v>
+      </c>
+      <c r="P154" s="4">
+        <v>46142</v>
       </c>
       <c r="V154" s="2" t="s">
-        <v>93</v>
+        <v>325</v>
       </c>
       <c r="W154" s="2" t="s">
-        <v>92</v>
+        <v>326</v>
       </c>
       <c r="X154" s="2" t="s">
-        <v>53</v>
+        <v>99</v>
       </c>
       <c r="Y154" s="2" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
     </row>
     <row r="155" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A155" s="2" t="s">
-        <v>62</v>
+        <v>184</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>80</v>
+        <v>257</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>64</v>
+        <v>103</v>
       </c>
       <c r="D155" s="2" t="s">
         <v>34</v>
@@ -12772,61 +12797,43 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G155" s="7">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="H155" s="2" t="s">
         <v>28</v>
       </c>
       <c r="I155" s="2" t="s">
-        <v>91</v>
+        <v>323</v>
       </c>
       <c r="J155" s="2">
         <v>1</v>
       </c>
       <c r="K155" s="2">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L155" s="4">
-        <v>45644</v>
-      </c>
-      <c r="M155" s="10">
-        <v>46063</v>
-      </c>
-      <c r="N155" s="10">
-        <v>46063</v>
-      </c>
-      <c r="O155" s="10">
-        <v>46063</v>
-      </c>
-      <c r="P155" s="10">
-        <v>46063</v>
-      </c>
-      <c r="Q155" s="10">
-        <v>46073</v>
-      </c>
-      <c r="R155" s="4">
-        <v>46076</v>
-      </c>
-      <c r="S155" s="4">
-        <v>46079</v>
-      </c>
-      <c r="T155" s="4">
-        <v>46079</v>
+        <v>46141</v>
+      </c>
+      <c r="N155" s="4">
+        <v>46142</v>
+      </c>
+      <c r="O155" s="4">
+        <v>46142</v>
+      </c>
+      <c r="P155" s="4">
+        <v>46142</v>
       </c>
       <c r="V155" s="2" t="s">
-        <v>94</v>
+        <v>325</v>
       </c>
       <c r="W155" s="2" t="s">
-        <v>92</v>
+        <v>326</v>
       </c>
       <c r="X155" s="2" t="s">
-        <v>53</v>
+        <v>99</v>
       </c>
       <c r="Y155" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="Z155" s="4">
-        <v>46092</v>
+        <v>58</v>
       </c>
     </row>
     <row r="156" spans="1:28" x14ac:dyDescent="0.3">
@@ -12854,56 +12861,47 @@
       <c r="H156" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I156" s="2" t="s">
-        <v>175</v>
+      <c r="I156" s="15" t="s">
+        <v>138</v>
       </c>
       <c r="J156" s="2">
         <v>1</v>
       </c>
       <c r="K156" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="L156" s="4">
-        <v>45644</v>
-      </c>
-      <c r="M156" s="10">
-        <v>46063</v>
-      </c>
-      <c r="N156" s="10">
-        <v>45940</v>
-      </c>
-      <c r="O156" s="10">
-        <v>45940</v>
-      </c>
+        <v>46066</v>
+      </c>
+      <c r="M156" s="6"/>
+      <c r="N156" s="6"/>
+      <c r="O156" s="6"/>
       <c r="P156" s="4">
-        <v>45959</v>
+        <v>46076</v>
       </c>
       <c r="Q156" s="4">
-        <v>45963</v>
+        <v>46083</v>
       </c>
       <c r="R156" s="4">
-        <v>45965</v>
+        <v>46093</v>
       </c>
       <c r="S156" s="4">
-        <v>45966</v>
+        <v>46094</v>
       </c>
       <c r="T156" s="4">
-        <v>45966</v>
+        <v>46094</v>
       </c>
       <c r="V156" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="W156" s="2" t="s">
-        <v>92</v>
+        <v>29</v>
       </c>
       <c r="X156" s="2" t="s">
         <v>53</v>
       </c>
       <c r="Y156" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="Z156" s="4">
-        <v>46065</v>
+        <v>140</v>
       </c>
     </row>
     <row r="157" spans="1:28" x14ac:dyDescent="0.3">
@@ -12911,10 +12909,10 @@
         <v>62</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>278</v>
+        <v>63</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>271</v>
+        <v>64</v>
       </c>
       <c r="D157" s="2" t="s">
         <v>34</v>
@@ -12932,60 +12930,70 @@
         <v>28</v>
       </c>
       <c r="I157" s="2" t="s">
-        <v>280</v>
+        <v>176</v>
       </c>
       <c r="J157" s="2">
         <v>1</v>
       </c>
       <c r="K157" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L157" s="4">
-        <v>46106</v>
-      </c>
-      <c r="N157" s="4">
-        <v>46108</v>
-      </c>
-      <c r="O157" s="4">
-        <v>46111</v>
-      </c>
-      <c r="P157" s="4">
-        <v>46126</v>
+        <v>45800</v>
+      </c>
+      <c r="M157" s="10">
+        <v>45999</v>
+      </c>
+      <c r="N157" s="10">
+        <v>46000</v>
+      </c>
+      <c r="O157" s="10">
+        <v>46001</v>
+      </c>
+      <c r="P157" s="10">
+        <v>46011</v>
       </c>
       <c r="Q157" s="4">
-        <v>46126</v>
+        <v>46025</v>
       </c>
       <c r="R157" s="4">
-        <v>46127</v>
+        <v>46034</v>
       </c>
       <c r="S157" s="4">
-        <v>46128</v>
+        <v>46035</v>
       </c>
       <c r="T157" s="4">
-        <v>46128</v>
+        <v>46035</v>
       </c>
       <c r="V157" s="2" t="s">
-        <v>122</v>
+        <v>76</v>
       </c>
       <c r="W157" s="2" t="s">
-        <v>30</v>
+        <v>92</v>
       </c>
       <c r="X157" s="2" t="s">
         <v>53</v>
       </c>
       <c r="Y157" s="2" t="s">
-        <v>141</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="Z157" s="4">
+        <v>46065</v>
+      </c>
+      <c r="AA157" s="4">
+        <v>46112</v>
+      </c>
+      <c r="AB157" s="4"/>
     </row>
     <row r="158" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A158" s="2" t="s">
         <v>62</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>278</v>
+        <v>63</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>271</v>
+        <v>64</v>
       </c>
       <c r="D158" s="2" t="s">
         <v>34</v>
@@ -13000,140 +13008,146 @@
         <v>14.5</v>
       </c>
       <c r="H158" s="2" t="s">
-        <v>28</v>
+        <v>177</v>
       </c>
       <c r="I158" s="2" t="s">
-        <v>281</v>
+        <v>178</v>
       </c>
       <c r="J158" s="2">
         <v>1</v>
       </c>
       <c r="K158" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L158" s="4">
-        <v>46106</v>
-      </c>
-      <c r="N158" s="4">
-        <v>46108</v>
-      </c>
-      <c r="O158" s="4">
-        <v>46111</v>
-      </c>
-      <c r="P158" s="4">
-        <v>46126</v>
-      </c>
-      <c r="Q158" s="4">
-        <v>46126</v>
-      </c>
-      <c r="R158" s="4">
-        <v>46127</v>
+        <v>45302</v>
+      </c>
+      <c r="M158" s="10">
+        <v>45645</v>
+      </c>
+      <c r="N158" s="10">
+        <v>45652</v>
+      </c>
+      <c r="O158" s="10">
+        <v>45652</v>
+      </c>
+      <c r="P158" s="10">
+        <v>45670</v>
+      </c>
+      <c r="Q158" s="10">
+        <v>45672</v>
+      </c>
+      <c r="R158" s="10">
+        <v>45672</v>
       </c>
       <c r="S158" s="4">
-        <v>46128</v>
+        <v>45673</v>
       </c>
       <c r="T158" s="4">
-        <v>46128</v>
+        <v>45673</v>
       </c>
       <c r="V158" s="2" t="s">
-        <v>122</v>
+        <v>76</v>
       </c>
       <c r="W158" s="2" t="s">
-        <v>30</v>
+        <v>92</v>
       </c>
       <c r="X158" s="2" t="s">
         <v>53</v>
       </c>
       <c r="Y158" s="2" t="s">
-        <v>141</v>
+        <v>67</v>
+      </c>
+      <c r="Z158" s="4">
+        <v>46092</v>
       </c>
     </row>
     <row r="159" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A159" s="2" t="s">
-        <v>124</v>
+        <v>62</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>125</v>
+        <v>80</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>126</v>
+        <v>64</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E159" s="2" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F159" s="3">
         <v>0.55000000000000004</v>
       </c>
       <c r="G159" s="7">
-        <v>14.2</v>
+        <v>14.5</v>
       </c>
       <c r="H159" s="2" t="s">
         <v>28</v>
       </c>
       <c r="I159" s="2" t="s">
-        <v>127</v>
+        <v>90</v>
       </c>
       <c r="J159" s="2">
         <v>1</v>
       </c>
       <c r="K159" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L159" s="4">
-        <v>46062</v>
-      </c>
-      <c r="M159" s="4">
-        <v>46062</v>
-      </c>
-      <c r="N159" s="4">
+        <v>45644</v>
+      </c>
+      <c r="M159" s="10">
         <v>46063</v>
       </c>
-      <c r="O159" s="4">
+      <c r="N159" s="10">
         <v>46063</v>
       </c>
-      <c r="P159" s="4">
+      <c r="O159" s="10">
         <v>46063</v>
       </c>
-      <c r="Q159" s="4">
-        <v>46065</v>
+      <c r="P159" s="10">
+        <v>46063</v>
+      </c>
+      <c r="Q159" s="10">
+        <v>46073</v>
       </c>
       <c r="R159" s="4">
-        <v>46066</v>
+        <v>46076</v>
       </c>
       <c r="S159" s="4">
-        <v>46072</v>
+        <v>46079</v>
       </c>
       <c r="T159" s="4">
-        <v>46072</v>
+        <v>46079</v>
       </c>
       <c r="V159" s="2" t="s">
-        <v>128</v>
+        <v>93</v>
       </c>
       <c r="W159" s="2" t="s">
-        <v>129</v>
+        <v>92</v>
       </c>
       <c r="X159" s="2" t="s">
         <v>53</v>
       </c>
       <c r="Y159" s="2" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
     </row>
     <row r="160" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A160" s="2" t="s">
-        <v>168</v>
+        <v>62</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>169</v>
+        <v>80</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>170</v>
+        <v>64</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E160" s="2" t="s">
         <v>27</v>
@@ -13142,63 +13156,75 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G160" s="7">
-        <v>14.2</v>
+        <v>14.5</v>
       </c>
       <c r="H160" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I160" s="11" t="s">
-        <v>234</v>
+      <c r="I160" s="2" t="s">
+        <v>91</v>
       </c>
       <c r="J160" s="2">
         <v>1</v>
       </c>
       <c r="K160" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L160" s="4">
-        <v>46126</v>
-      </c>
-      <c r="P160" s="4">
-        <v>46132</v>
-      </c>
-      <c r="Q160" s="4">
-        <v>46139</v>
+        <v>45644</v>
+      </c>
+      <c r="M160" s="10">
+        <v>46063</v>
+      </c>
+      <c r="N160" s="10">
+        <v>46063</v>
+      </c>
+      <c r="O160" s="10">
+        <v>46063</v>
+      </c>
+      <c r="P160" s="10">
+        <v>46063</v>
+      </c>
+      <c r="Q160" s="10">
+        <v>46073</v>
       </c>
       <c r="R160" s="4">
-        <v>46140</v>
+        <v>46076</v>
       </c>
       <c r="S160" s="4">
-        <v>46162</v>
+        <v>46079</v>
       </c>
       <c r="T160" s="4">
-        <v>46150</v>
+        <v>46079</v>
       </c>
       <c r="V160" s="2" t="s">
-        <v>146</v>
+        <v>94</v>
       </c>
       <c r="W160" s="2" t="s">
-        <v>30</v>
+        <v>92</v>
       </c>
       <c r="X160" s="2" t="s">
         <v>53</v>
       </c>
       <c r="Y160" s="2" t="s">
-        <v>58</v>
+        <v>67</v>
+      </c>
+      <c r="Z160" s="4">
+        <v>46092</v>
       </c>
     </row>
     <row r="161" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A161" s="2" t="s">
-        <v>168</v>
+        <v>62</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>169</v>
+        <v>63</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>170</v>
+        <v>64</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E161" s="2" t="s">
         <v>27</v>
@@ -13207,63 +13233,75 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G161" s="7">
-        <v>14.2</v>
+        <v>14.5</v>
       </c>
       <c r="H161" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I161" s="11" t="s">
-        <v>235</v>
+      <c r="I161" s="2" t="s">
+        <v>175</v>
       </c>
       <c r="J161" s="2">
         <v>1</v>
       </c>
       <c r="K161" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L161" s="4">
-        <v>46126</v>
+        <v>45644</v>
+      </c>
+      <c r="M161" s="10">
+        <v>46063</v>
+      </c>
+      <c r="N161" s="10">
+        <v>45940</v>
+      </c>
+      <c r="O161" s="10">
+        <v>45940</v>
       </c>
       <c r="P161" s="4">
-        <v>46132</v>
+        <v>45959</v>
       </c>
       <c r="Q161" s="4">
-        <v>46139</v>
+        <v>45963</v>
       </c>
       <c r="R161" s="4">
-        <v>46140</v>
+        <v>45965</v>
       </c>
       <c r="S161" s="4">
-        <v>46162</v>
+        <v>45966</v>
       </c>
       <c r="T161" s="4">
-        <v>46150</v>
+        <v>45966</v>
       </c>
       <c r="V161" s="2" t="s">
-        <v>146</v>
+        <v>51</v>
       </c>
       <c r="W161" s="2" t="s">
-        <v>30</v>
+        <v>92</v>
       </c>
       <c r="X161" s="2" t="s">
         <v>53</v>
       </c>
       <c r="Y161" s="2" t="s">
-        <v>58</v>
+        <v>67</v>
+      </c>
+      <c r="Z161" s="4">
+        <v>46065</v>
       </c>
     </row>
     <row r="162" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A162" s="2" t="s">
-        <v>168</v>
+        <v>62</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>169</v>
+        <v>278</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>170</v>
+        <v>271</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E162" s="2" t="s">
         <v>27</v>
@@ -13272,13 +13310,13 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G162" s="7">
-        <v>14.2</v>
+        <v>14.5</v>
       </c>
       <c r="H162" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I162" s="11" t="s">
-        <v>194</v>
+      <c r="I162" s="2" t="s">
+        <v>280</v>
       </c>
       <c r="J162" s="2">
         <v>1</v>
@@ -13287,25 +13325,31 @@
         <v>1</v>
       </c>
       <c r="L162" s="4">
-        <v>46086</v>
+        <v>46106</v>
+      </c>
+      <c r="N162" s="4">
+        <v>46108</v>
+      </c>
+      <c r="O162" s="4">
+        <v>46111</v>
       </c>
       <c r="P162" s="4">
-        <v>46094</v>
+        <v>46126</v>
       </c>
       <c r="Q162" s="4">
-        <v>46103</v>
+        <v>46126</v>
       </c>
       <c r="R162" s="4">
-        <v>46105</v>
+        <v>46127</v>
       </c>
       <c r="S162" s="4">
-        <v>46112</v>
+        <v>46128</v>
       </c>
       <c r="T162" s="4">
-        <v>46112</v>
+        <v>46128</v>
       </c>
       <c r="V162" s="2" t="s">
-        <v>146</v>
+        <v>122</v>
       </c>
       <c r="W162" s="2" t="s">
         <v>30</v>
@@ -13314,21 +13358,21 @@
         <v>53</v>
       </c>
       <c r="Y162" s="2" t="s">
-        <v>58</v>
+        <v>141</v>
       </c>
     </row>
     <row r="163" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A163" s="2" t="s">
-        <v>168</v>
+        <v>62</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>169</v>
+        <v>278</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>170</v>
+        <v>271</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E163" s="2" t="s">
         <v>27</v>
@@ -13337,13 +13381,13 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G163" s="7">
-        <v>14.2</v>
+        <v>14.5</v>
       </c>
       <c r="H163" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I163" s="11" t="s">
-        <v>236</v>
+      <c r="I163" s="2" t="s">
+        <v>281</v>
       </c>
       <c r="J163" s="2">
         <v>1</v>
@@ -13352,25 +13396,31 @@
         <v>1</v>
       </c>
       <c r="L163" s="4">
+        <v>46106</v>
+      </c>
+      <c r="N163" s="4">
+        <v>46108</v>
+      </c>
+      <c r="O163" s="4">
+        <v>46111</v>
+      </c>
+      <c r="P163" s="4">
         <v>46126</v>
       </c>
-      <c r="P163" s="4">
-        <v>46132</v>
-      </c>
       <c r="Q163" s="4">
-        <v>46139</v>
+        <v>46126</v>
       </c>
       <c r="R163" s="4">
-        <v>46140</v>
+        <v>46127</v>
       </c>
       <c r="S163" s="4">
-        <v>46162</v>
+        <v>46128</v>
       </c>
       <c r="T163" s="4">
-        <v>46150</v>
+        <v>46128</v>
       </c>
       <c r="V163" s="2" t="s">
-        <v>146</v>
+        <v>122</v>
       </c>
       <c r="W163" s="2" t="s">
         <v>30</v>
@@ -13379,24 +13429,24 @@
         <v>53</v>
       </c>
       <c r="Y163" s="2" t="s">
-        <v>58</v>
+        <v>141</v>
       </c>
     </row>
     <row r="164" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A164" s="2" t="s">
-        <v>168</v>
+        <v>124</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>169</v>
+        <v>125</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>170</v>
+        <v>126</v>
       </c>
       <c r="D164" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E164" s="2" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F164" s="3">
         <v>0.55000000000000004</v>
@@ -13407,8 +13457,8 @@
       <c r="H164" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I164" s="11" t="s">
-        <v>195</v>
+      <c r="I164" s="2" t="s">
+        <v>127</v>
       </c>
       <c r="J164" s="2">
         <v>1</v>
@@ -13417,28 +13467,37 @@
         <v>1</v>
       </c>
       <c r="L164" s="4">
-        <v>46086</v>
+        <v>46062</v>
+      </c>
+      <c r="M164" s="4">
+        <v>46062</v>
+      </c>
+      <c r="N164" s="4">
+        <v>46063</v>
+      </c>
+      <c r="O164" s="4">
+        <v>46063</v>
       </c>
       <c r="P164" s="4">
-        <v>46094</v>
+        <v>46063</v>
       </c>
       <c r="Q164" s="4">
-        <v>46103</v>
+        <v>46065</v>
       </c>
       <c r="R164" s="4">
-        <v>46105</v>
+        <v>46066</v>
       </c>
       <c r="S164" s="4">
-        <v>46112</v>
+        <v>46072</v>
       </c>
       <c r="T164" s="4">
-        <v>46112</v>
+        <v>46072</v>
       </c>
       <c r="V164" s="2" t="s">
-        <v>146</v>
+        <v>128</v>
       </c>
       <c r="W164" s="2" t="s">
-        <v>30</v>
+        <v>129</v>
       </c>
       <c r="X164" s="2" t="s">
         <v>53</v>
@@ -13473,7 +13532,7 @@
         <v>28</v>
       </c>
       <c r="I165" s="11" t="s">
-        <v>196</v>
+        <v>234</v>
       </c>
       <c r="J165" s="2">
         <v>1</v>
@@ -13482,22 +13541,22 @@
         <v>1</v>
       </c>
       <c r="L165" s="4">
-        <v>46086</v>
+        <v>46126</v>
       </c>
       <c r="P165" s="4">
-        <v>46094</v>
+        <v>46132</v>
       </c>
       <c r="Q165" s="4">
-        <v>46103</v>
+        <v>46139</v>
       </c>
       <c r="R165" s="4">
-        <v>46105</v>
+        <v>46140</v>
       </c>
       <c r="S165" s="4">
-        <v>46112</v>
+        <v>46162</v>
       </c>
       <c r="T165" s="4">
-        <v>46112</v>
+        <v>46150</v>
       </c>
       <c r="V165" s="2" t="s">
         <v>146</v>
@@ -13538,7 +13597,7 @@
         <v>28</v>
       </c>
       <c r="I166" s="11" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="J166" s="2">
         <v>1</v>
@@ -13603,7 +13662,7 @@
         <v>28</v>
       </c>
       <c r="I167" s="11" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="J167" s="2">
         <v>1</v>
@@ -13668,7 +13727,7 @@
         <v>28</v>
       </c>
       <c r="I168" s="11" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="J168" s="2">
         <v>1</v>
@@ -13733,7 +13792,7 @@
         <v>28</v>
       </c>
       <c r="I169" s="11" t="s">
-        <v>239</v>
+        <v>195</v>
       </c>
       <c r="J169" s="2">
         <v>1</v>
@@ -13742,22 +13801,22 @@
         <v>1</v>
       </c>
       <c r="L169" s="4">
-        <v>46126</v>
+        <v>46086</v>
       </c>
       <c r="P169" s="4">
-        <v>46132</v>
+        <v>46094</v>
       </c>
       <c r="Q169" s="4">
-        <v>46139</v>
+        <v>46103</v>
       </c>
       <c r="R169" s="4">
-        <v>46140</v>
+        <v>46105</v>
       </c>
       <c r="S169" s="4">
-        <v>46162</v>
+        <v>46112</v>
       </c>
       <c r="T169" s="4">
-        <v>46150</v>
+        <v>46112</v>
       </c>
       <c r="V169" s="2" t="s">
         <v>146</v>
@@ -13798,7 +13857,7 @@
         <v>28</v>
       </c>
       <c r="I170" s="11" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="J170" s="2">
         <v>1</v>
@@ -13863,7 +13922,7 @@
         <v>28</v>
       </c>
       <c r="I171" s="11" t="s">
-        <v>199</v>
+        <v>237</v>
       </c>
       <c r="J171" s="2">
         <v>1</v>
@@ -13872,22 +13931,22 @@
         <v>1</v>
       </c>
       <c r="L171" s="4">
-        <v>46086</v>
+        <v>46126</v>
       </c>
       <c r="P171" s="4">
-        <v>46094</v>
+        <v>46132</v>
       </c>
       <c r="Q171" s="4">
-        <v>46103</v>
+        <v>46139</v>
       </c>
       <c r="R171" s="4">
-        <v>46105</v>
+        <v>46140</v>
       </c>
       <c r="S171" s="4">
-        <v>46112</v>
+        <v>46162</v>
       </c>
       <c r="T171" s="4">
-        <v>46112</v>
+        <v>46150</v>
       </c>
       <c r="V171" s="2" t="s">
         <v>146</v>
@@ -13928,7 +13987,7 @@
         <v>28</v>
       </c>
       <c r="I172" s="11" t="s">
-        <v>240</v>
+        <v>197</v>
       </c>
       <c r="J172" s="2">
         <v>1</v>
@@ -13937,22 +13996,22 @@
         <v>1</v>
       </c>
       <c r="L172" s="4">
-        <v>46126</v>
+        <v>46086</v>
       </c>
       <c r="P172" s="4">
-        <v>46132</v>
+        <v>46094</v>
       </c>
       <c r="Q172" s="4">
-        <v>46139</v>
+        <v>46103</v>
       </c>
       <c r="R172" s="4">
-        <v>46140</v>
+        <v>46105</v>
       </c>
       <c r="S172" s="4">
-        <v>46162</v>
+        <v>46112</v>
       </c>
       <c r="T172" s="4">
-        <v>46150</v>
+        <v>46112</v>
       </c>
       <c r="V172" s="2" t="s">
         <v>146</v>
@@ -13993,7 +14052,7 @@
         <v>28</v>
       </c>
       <c r="I173" s="11" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="J173" s="2">
         <v>1</v>
@@ -14034,13 +14093,13 @@
     </row>
     <row r="174" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A174" s="2" t="s">
-        <v>336</v>
+        <v>168</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>337</v>
+        <v>169</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>338</v>
+        <v>170</v>
       </c>
       <c r="D174" s="2" t="s">
         <v>26</v>
@@ -14049,16 +14108,16 @@
         <v>27</v>
       </c>
       <c r="F174" s="3">
-        <v>0.43</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="G174" s="7">
-        <v>14.5</v>
+        <v>14.2</v>
       </c>
       <c r="H174" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I174" s="2" t="s">
-        <v>339</v>
+      <c r="I174" s="11" t="s">
+        <v>239</v>
       </c>
       <c r="J174" s="2">
         <v>1</v>
@@ -14067,28 +14126,28 @@
         <v>1</v>
       </c>
       <c r="L174" s="4">
-        <v>45979</v>
-      </c>
-      <c r="N174" s="4">
-        <v>45979</v>
-      </c>
-      <c r="O174" s="4">
-        <v>45979</v>
+        <v>46126</v>
       </c>
       <c r="P174" s="4">
-        <v>45979</v>
+        <v>46132</v>
+      </c>
+      <c r="Q174" s="4">
+        <v>46139</v>
+      </c>
+      <c r="R174" s="4">
+        <v>46140</v>
       </c>
       <c r="S174" s="4">
-        <v>46010</v>
+        <v>46162</v>
       </c>
       <c r="T174" s="4">
-        <v>46010</v>
+        <v>46150</v>
       </c>
       <c r="V174" s="2" t="s">
-        <v>66</v>
+        <v>146</v>
       </c>
       <c r="W174" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="X174" s="2" t="s">
         <v>53</v>
@@ -14096,37 +14155,34 @@
       <c r="Y174" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="Z174" s="4">
-        <v>46028</v>
-      </c>
     </row>
     <row r="175" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A175" s="2" t="s">
-        <v>245</v>
+        <v>168</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>246</v>
+        <v>169</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>247</v>
+        <v>170</v>
       </c>
       <c r="D175" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E175" s="2" t="s">
-        <v>248</v>
+        <v>27</v>
       </c>
       <c r="F175" s="3">
-        <v>0.45</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="G175" s="7">
-        <v>14.5</v>
+        <v>14.2</v>
       </c>
       <c r="H175" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="I175" s="2" t="s">
-        <v>242</v>
+        <v>28</v>
+      </c>
+      <c r="I175" s="11" t="s">
+        <v>198</v>
       </c>
       <c r="J175" s="2">
         <v>1</v>
@@ -14135,54 +14191,48 @@
         <v>1</v>
       </c>
       <c r="L175" s="4">
-        <v>46104</v>
-      </c>
-      <c r="N175" s="4">
+        <v>46086</v>
+      </c>
+      <c r="P175" s="4">
+        <v>46094</v>
+      </c>
+      <c r="Q175" s="4">
+        <v>46103</v>
+      </c>
+      <c r="R175" s="4">
         <v>46105</v>
       </c>
-      <c r="O175" s="4">
-        <v>46110</v>
-      </c>
-      <c r="P175" s="4">
-        <v>46111</v>
-      </c>
-      <c r="Q175" s="4">
+      <c r="S175" s="4">
         <v>46112</v>
       </c>
-      <c r="R175" s="4">
-        <v>46115</v>
-      </c>
-      <c r="S175" s="4">
-        <v>46118</v>
-      </c>
       <c r="T175" s="4">
-        <v>46118</v>
+        <v>46112</v>
       </c>
       <c r="V175" s="2" t="s">
         <v>146</v>
       </c>
       <c r="W175" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="X175" s="2" t="s">
         <v>53</v>
       </c>
       <c r="Y175" s="2" t="s">
-        <v>140</v>
+        <v>58</v>
       </c>
     </row>
     <row r="176" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A176" s="2" t="s">
-        <v>62</v>
+        <v>168</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>310</v>
+        <v>169</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>64</v>
+        <v>170</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="E176" s="2" t="s">
         <v>27</v>
@@ -14191,13 +14241,13 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G176" s="7">
-        <v>15</v>
+        <v>14.2</v>
       </c>
       <c r="H176" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I176" s="2" t="s">
-        <v>327</v>
+      <c r="I176" s="11" t="s">
+        <v>199</v>
       </c>
       <c r="J176" s="2">
         <v>1</v>
@@ -14206,39 +14256,54 @@
         <v>1</v>
       </c>
       <c r="L176" s="4">
-        <v>46146</v>
+        <v>46086</v>
+      </c>
+      <c r="P176" s="4">
+        <v>46094</v>
+      </c>
+      <c r="Q176" s="4">
+        <v>46103</v>
+      </c>
+      <c r="R176" s="4">
+        <v>46105</v>
+      </c>
+      <c r="S176" s="4">
+        <v>46112</v>
+      </c>
+      <c r="T176" s="4">
+        <v>46112</v>
       </c>
       <c r="V176" s="2" t="s">
-        <v>325</v>
+        <v>146</v>
       </c>
       <c r="W176" s="2" t="s">
-        <v>326</v>
+        <v>30</v>
       </c>
       <c r="X176" s="2" t="s">
-        <v>135</v>
+        <v>53</v>
       </c>
       <c r="Y176" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="177" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A177" s="2" t="s">
-        <v>148</v>
+        <v>168</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>298</v>
+        <v>169</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>149</v>
+        <v>170</v>
       </c>
       <c r="D177" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E177" s="2" t="s">
-        <v>150</v>
+        <v>27</v>
       </c>
       <c r="F177" s="3">
-        <v>0.45</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="G177" s="7">
         <v>14.2</v>
@@ -14246,8 +14311,8 @@
       <c r="H177" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I177" s="2" t="s">
-        <v>154</v>
+      <c r="I177" s="11" t="s">
+        <v>240</v>
       </c>
       <c r="J177" s="2">
         <v>1</v>
@@ -14256,35 +14321,28 @@
         <v>1</v>
       </c>
       <c r="L177" s="4">
-        <v>46090</v>
-      </c>
-      <c r="M177" s="12"/>
-      <c r="N177" s="4">
-        <v>46085</v>
-      </c>
-      <c r="O177" s="4">
-        <v>46086</v>
+        <v>46126</v>
       </c>
       <c r="P177" s="4">
-        <v>46087</v>
+        <v>46132</v>
       </c>
       <c r="Q177" s="4">
-        <v>46138</v>
+        <v>46139</v>
       </c>
       <c r="R177" s="4">
-        <v>46141</v>
+        <v>46140</v>
       </c>
       <c r="S177" s="4">
-        <v>46142</v>
+        <v>46162</v>
       </c>
       <c r="T177" s="4">
-        <v>46142</v>
+        <v>46150</v>
       </c>
       <c r="V177" s="2" t="s">
-        <v>182</v>
+        <v>146</v>
       </c>
       <c r="W177" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="X177" s="2" t="s">
         <v>53</v>
@@ -14293,24 +14351,24 @@
         <v>58</v>
       </c>
     </row>
-    <row r="178" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A178" s="2" t="s">
-        <v>148</v>
+        <v>168</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>298</v>
+        <v>169</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>149</v>
+        <v>170</v>
       </c>
       <c r="D178" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E178" s="2" t="s">
-        <v>150</v>
+        <v>27</v>
       </c>
       <c r="F178" s="3">
-        <v>0.45</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="G178" s="7">
         <v>14.2</v>
@@ -14318,8 +14376,8 @@
       <c r="H178" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I178" s="2" t="s">
-        <v>183</v>
+      <c r="I178" s="11" t="s">
+        <v>241</v>
       </c>
       <c r="J178" s="2">
         <v>1</v>
@@ -14328,35 +14386,28 @@
         <v>1</v>
       </c>
       <c r="L178" s="4">
-        <v>46090</v>
-      </c>
-      <c r="M178" s="12"/>
-      <c r="N178" s="4">
-        <v>46085</v>
-      </c>
-      <c r="O178" s="4">
-        <v>46086</v>
+        <v>46126</v>
       </c>
       <c r="P178" s="4">
-        <v>46087</v>
+        <v>46132</v>
       </c>
       <c r="Q178" s="4">
-        <v>46138</v>
+        <v>46139</v>
       </c>
       <c r="R178" s="4">
-        <v>46141</v>
+        <v>46140</v>
       </c>
       <c r="S178" s="4">
-        <v>46142</v>
+        <v>46162</v>
       </c>
       <c r="T178" s="4">
-        <v>46142</v>
+        <v>46150</v>
       </c>
       <c r="V178" s="2" t="s">
-        <v>182</v>
+        <v>146</v>
       </c>
       <c r="W178" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="X178" s="2" t="s">
         <v>53</v>
@@ -14365,33 +14416,33 @@
         <v>58</v>
       </c>
     </row>
-    <row r="179" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A179" s="2" t="s">
-        <v>148</v>
+        <v>336</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>298</v>
+        <v>337</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>149</v>
+        <v>338</v>
       </c>
       <c r="D179" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E179" s="2" t="s">
-        <v>150</v>
+        <v>27</v>
       </c>
       <c r="F179" s="3">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="G179" s="7">
-        <v>14.2</v>
+        <v>14.5</v>
       </c>
       <c r="H179" s="2" t="s">
         <v>28</v>
       </c>
       <c r="I179" s="2" t="s">
-        <v>155</v>
+        <v>339</v>
       </c>
       <c r="J179" s="2">
         <v>1</v>
@@ -14400,32 +14451,25 @@
         <v>1</v>
       </c>
       <c r="L179" s="4">
-        <v>46090</v>
-      </c>
-      <c r="M179" s="12"/>
+        <v>45979</v>
+      </c>
       <c r="N179" s="4">
-        <v>46085</v>
+        <v>45979</v>
       </c>
       <c r="O179" s="4">
-        <v>46086</v>
+        <v>45979</v>
       </c>
       <c r="P179" s="4">
-        <v>46087</v>
-      </c>
-      <c r="Q179" s="4">
-        <v>46138</v>
-      </c>
-      <c r="R179" s="4">
-        <v>46141</v>
+        <v>45979</v>
       </c>
       <c r="S179" s="4">
-        <v>46142</v>
+        <v>46010</v>
       </c>
       <c r="T179" s="4">
-        <v>46142</v>
+        <v>46010</v>
       </c>
       <c r="V179" s="2" t="s">
-        <v>182</v>
+        <v>66</v>
       </c>
       <c r="W179" s="2" t="s">
         <v>29</v>
@@ -14436,34 +14480,37 @@
       <c r="Y179" s="2" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="180" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z179" s="4">
+        <v>46028</v>
+      </c>
+    </row>
+    <row r="180" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A180" s="2" t="s">
-        <v>148</v>
+        <v>245</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>298</v>
+        <v>246</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>149</v>
+        <v>247</v>
       </c>
       <c r="D180" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E180" s="2" t="s">
-        <v>150</v>
+        <v>248</v>
       </c>
       <c r="F180" s="3">
         <v>0.45</v>
       </c>
       <c r="G180" s="7">
-        <v>14.2</v>
+        <v>14.5</v>
       </c>
       <c r="H180" s="2" t="s">
-        <v>28</v>
+        <v>130</v>
       </c>
       <c r="I180" s="2" t="s">
-        <v>156</v>
+        <v>242</v>
       </c>
       <c r="J180" s="2">
         <v>1</v>
@@ -14472,32 +14519,31 @@
         <v>1</v>
       </c>
       <c r="L180" s="4">
-        <v>46090</v>
-      </c>
-      <c r="M180" s="12"/>
+        <v>46104</v>
+      </c>
       <c r="N180" s="4">
-        <v>46085</v>
+        <v>46105</v>
       </c>
       <c r="O180" s="4">
-        <v>46086</v>
+        <v>46110</v>
       </c>
       <c r="P180" s="4">
-        <v>46087</v>
+        <v>46111</v>
       </c>
       <c r="Q180" s="4">
-        <v>46138</v>
+        <v>46112</v>
       </c>
       <c r="R180" s="4">
-        <v>46141</v>
+        <v>46115</v>
       </c>
       <c r="S180" s="4">
-        <v>46142</v>
+        <v>46118</v>
       </c>
       <c r="T180" s="4">
-        <v>46142</v>
+        <v>46118</v>
       </c>
       <c r="V180" s="2" t="s">
-        <v>182</v>
+        <v>146</v>
       </c>
       <c r="W180" s="2" t="s">
         <v>29</v>
@@ -14506,36 +14552,36 @@
         <v>53</v>
       </c>
       <c r="Y180" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="181" spans="1:25" x14ac:dyDescent="0.3">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="181" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A181" s="2" t="s">
-        <v>148</v>
+        <v>62</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>149</v>
+        <v>64</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E181" s="2" t="s">
-        <v>150</v>
+        <v>27</v>
       </c>
       <c r="F181" s="3">
-        <v>0.45</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="G181" s="7">
-        <v>14.2</v>
+        <v>15</v>
       </c>
       <c r="H181" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I181" s="11" t="s">
-        <v>158</v>
+      <c r="I181" s="2" t="s">
+        <v>327</v>
       </c>
       <c r="J181" s="2">
         <v>1</v>
@@ -14544,44 +14590,22 @@
         <v>1</v>
       </c>
       <c r="L181" s="4">
-        <v>46090</v>
-      </c>
-      <c r="M181" s="12"/>
-      <c r="N181" s="4">
-        <v>46085</v>
-      </c>
-      <c r="O181" s="4">
-        <v>46086</v>
-      </c>
-      <c r="P181" s="4">
-        <v>46087</v>
-      </c>
-      <c r="Q181" s="4">
-        <v>46138</v>
-      </c>
-      <c r="R181" s="4">
-        <v>46141</v>
-      </c>
-      <c r="S181" s="4">
-        <v>46142</v>
-      </c>
-      <c r="T181" s="4">
-        <v>46142</v>
+        <v>46146</v>
       </c>
       <c r="V181" s="2" t="s">
-        <v>182</v>
+        <v>325</v>
       </c>
       <c r="W181" s="2" t="s">
-        <v>29</v>
+        <v>326</v>
       </c>
       <c r="X181" s="2" t="s">
-        <v>53</v>
+        <v>135</v>
       </c>
       <c r="Y181" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="182" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A182" s="2" t="s">
         <v>148</v>
       </c>
@@ -14606,8 +14630,8 @@
       <c r="H182" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I182" s="11" t="s">
-        <v>159</v>
+      <c r="I182" s="2" t="s">
+        <v>154</v>
       </c>
       <c r="J182" s="2">
         <v>1</v>
@@ -14653,7 +14677,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="183" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A183" s="2" t="s">
         <v>148</v>
       </c>
@@ -14678,8 +14702,8 @@
       <c r="H183" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I183" s="11" t="s">
-        <v>157</v>
+      <c r="I183" s="2" t="s">
+        <v>183</v>
       </c>
       <c r="J183" s="2">
         <v>1</v>
@@ -14725,33 +14749,33 @@
         <v>58</v>
       </c>
     </row>
-    <row r="184" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A184" s="2" t="s">
-        <v>62</v>
+        <v>148</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>63</v>
+        <v>298</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>64</v>
+        <v>149</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="E184" s="2" t="s">
-        <v>27</v>
+        <v>150</v>
       </c>
       <c r="F184" s="3">
-        <v>0.55000000000000004</v>
+        <v>0.45</v>
       </c>
       <c r="G184" s="7">
-        <v>15</v>
+        <v>14.2</v>
       </c>
       <c r="H184" s="2" t="s">
         <v>28</v>
       </c>
       <c r="I184" s="2" t="s">
-        <v>111</v>
+        <v>155</v>
       </c>
       <c r="J184" s="2">
         <v>1</v>
@@ -14759,27 +14783,33 @@
       <c r="K184" s="2">
         <v>1</v>
       </c>
-      <c r="L184" s="6"/>
-      <c r="M184" s="6"/>
-      <c r="N184" s="6"/>
-      <c r="O184" s="6"/>
-      <c r="P184" s="10">
-        <v>46066</v>
-      </c>
-      <c r="Q184" s="10">
-        <v>46071</v>
+      <c r="L184" s="4">
+        <v>46090</v>
+      </c>
+      <c r="M184" s="12"/>
+      <c r="N184" s="4">
+        <v>46085</v>
+      </c>
+      <c r="O184" s="4">
+        <v>46086</v>
+      </c>
+      <c r="P184" s="4">
+        <v>46087</v>
+      </c>
+      <c r="Q184" s="4">
+        <v>46138</v>
       </c>
       <c r="R184" s="4">
-        <v>46077</v>
+        <v>46141</v>
       </c>
       <c r="S184" s="4">
-        <v>46077</v>
+        <v>46142</v>
       </c>
       <c r="T184" s="4">
-        <v>46077</v>
+        <v>46142</v>
       </c>
       <c r="V184" s="2" t="s">
-        <v>98</v>
+        <v>182</v>
       </c>
       <c r="W184" s="2" t="s">
         <v>29</v>
@@ -14788,36 +14818,36 @@
         <v>53</v>
       </c>
       <c r="Y184" s="2" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="185" spans="1:25" x14ac:dyDescent="0.3">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="185" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A185" s="2" t="s">
-        <v>62</v>
+        <v>148</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>63</v>
+        <v>298</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>64</v>
+        <v>149</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="E185" s="2" t="s">
-        <v>27</v>
+        <v>150</v>
       </c>
       <c r="F185" s="3">
-        <v>0.55000000000000004</v>
+        <v>0.45</v>
       </c>
       <c r="G185" s="7">
-        <v>14.5</v>
+        <v>14.2</v>
       </c>
       <c r="H185" s="2" t="s">
         <v>28</v>
       </c>
       <c r="I185" s="2" t="s">
-        <v>108</v>
+        <v>156</v>
       </c>
       <c r="J185" s="2">
         <v>1</v>
@@ -14825,27 +14855,33 @@
       <c r="K185" s="2">
         <v>1</v>
       </c>
-      <c r="L185" s="6"/>
-      <c r="M185" s="6"/>
-      <c r="N185" s="6"/>
-      <c r="O185" s="6"/>
-      <c r="P185" s="10">
-        <v>46065</v>
-      </c>
-      <c r="Q185" s="10">
-        <v>46075</v>
+      <c r="L185" s="4">
+        <v>46090</v>
+      </c>
+      <c r="M185" s="12"/>
+      <c r="N185" s="4">
+        <v>46085</v>
+      </c>
+      <c r="O185" s="4">
+        <v>46086</v>
+      </c>
+      <c r="P185" s="4">
+        <v>46087</v>
+      </c>
+      <c r="Q185" s="4">
+        <v>46138</v>
       </c>
       <c r="R185" s="4">
-        <v>46076</v>
+        <v>46141</v>
       </c>
       <c r="S185" s="4">
-        <v>46077</v>
+        <v>46142</v>
       </c>
       <c r="T185" s="4">
-        <v>46077</v>
+        <v>46142</v>
       </c>
       <c r="V185" s="2" t="s">
-        <v>98</v>
+        <v>182</v>
       </c>
       <c r="W185" s="2" t="s">
         <v>29</v>
@@ -14854,36 +14890,36 @@
         <v>53</v>
       </c>
       <c r="Y185" s="2" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="186" spans="1:25" x14ac:dyDescent="0.3">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="186" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A186" s="2" t="s">
-        <v>62</v>
+        <v>148</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>63</v>
+        <v>298</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>64</v>
+        <v>149</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="E186" s="2" t="s">
-        <v>27</v>
+        <v>150</v>
       </c>
       <c r="F186" s="3">
-        <v>0.55000000000000004</v>
+        <v>0.45</v>
       </c>
       <c r="G186" s="7">
-        <v>14.5</v>
+        <v>14.2</v>
       </c>
       <c r="H186" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I186" s="2" t="s">
-        <v>105</v>
+      <c r="I186" s="11" t="s">
+        <v>158</v>
       </c>
       <c r="J186" s="2">
         <v>1</v>
@@ -14891,27 +14927,33 @@
       <c r="K186" s="2">
         <v>1</v>
       </c>
-      <c r="L186" s="6"/>
-      <c r="M186" s="6"/>
-      <c r="N186" s="6"/>
-      <c r="O186" s="6"/>
-      <c r="P186" s="10">
-        <v>46065</v>
-      </c>
-      <c r="Q186" s="10">
-        <v>46075</v>
+      <c r="L186" s="4">
+        <v>46090</v>
+      </c>
+      <c r="M186" s="12"/>
+      <c r="N186" s="4">
+        <v>46085</v>
+      </c>
+      <c r="O186" s="4">
+        <v>46086</v>
+      </c>
+      <c r="P186" s="4">
+        <v>46087</v>
+      </c>
+      <c r="Q186" s="4">
+        <v>46138</v>
       </c>
       <c r="R186" s="4">
-        <v>46076</v>
+        <v>46141</v>
       </c>
       <c r="S186" s="4">
-        <v>46077</v>
+        <v>46142</v>
       </c>
       <c r="T186" s="4">
-        <v>46077</v>
+        <v>46142</v>
       </c>
       <c r="V186" s="2" t="s">
-        <v>76</v>
+        <v>182</v>
       </c>
       <c r="W186" s="2" t="s">
         <v>29</v>
@@ -14919,34 +14961,37 @@
       <c r="X186" s="2" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="187" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Y186" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="187" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A187" s="2" t="s">
-        <v>62</v>
+        <v>148</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>63</v>
+        <v>298</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>64</v>
+        <v>149</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="E187" s="2" t="s">
-        <v>27</v>
+        <v>150</v>
       </c>
       <c r="F187" s="3">
-        <v>0.55000000000000004</v>
+        <v>0.45</v>
       </c>
       <c r="G187" s="7">
-        <v>14.5</v>
+        <v>14.2</v>
       </c>
       <c r="H187" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I187" s="2" t="s">
-        <v>106</v>
+      <c r="I187" s="11" t="s">
+        <v>159</v>
       </c>
       <c r="J187" s="2">
         <v>1</v>
@@ -14954,27 +14999,33 @@
       <c r="K187" s="2">
         <v>1</v>
       </c>
-      <c r="L187" s="6"/>
-      <c r="M187" s="6"/>
-      <c r="N187" s="6"/>
-      <c r="O187" s="6"/>
-      <c r="P187" s="10">
-        <v>46065</v>
-      </c>
-      <c r="Q187" s="10">
-        <v>46075</v>
+      <c r="L187" s="4">
+        <v>46090</v>
+      </c>
+      <c r="M187" s="12"/>
+      <c r="N187" s="4">
+        <v>46085</v>
+      </c>
+      <c r="O187" s="4">
+        <v>46086</v>
+      </c>
+      <c r="P187" s="4">
+        <v>46087</v>
+      </c>
+      <c r="Q187" s="4">
+        <v>46138</v>
       </c>
       <c r="R187" s="4">
-        <v>46076</v>
+        <v>46141</v>
       </c>
       <c r="S187" s="4">
-        <v>46077</v>
+        <v>46142</v>
       </c>
       <c r="T187" s="4">
-        <v>46077</v>
+        <v>46142</v>
       </c>
       <c r="V187" s="2" t="s">
-        <v>76</v>
+        <v>182</v>
       </c>
       <c r="W187" s="2" t="s">
         <v>29</v>
@@ -14982,34 +15033,37 @@
       <c r="X187" s="2" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="188" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Y187" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="188" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A188" s="2" t="s">
-        <v>245</v>
+        <v>148</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>246</v>
+        <v>298</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>247</v>
+        <v>149</v>
       </c>
       <c r="D188" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E188" s="2" t="s">
-        <v>248</v>
+        <v>150</v>
       </c>
       <c r="F188" s="3">
         <v>0.45</v>
       </c>
       <c r="G188" s="7">
-        <v>14.5</v>
+        <v>14.2</v>
       </c>
       <c r="H188" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="I188" s="2" t="s">
-        <v>243</v>
+        <v>28</v>
+      </c>
+      <c r="I188" s="11" t="s">
+        <v>157</v>
       </c>
       <c r="J188" s="2">
         <v>1</v>
@@ -15018,31 +15072,32 @@
         <v>1</v>
       </c>
       <c r="L188" s="4">
-        <v>46104</v>
-      </c>
+        <v>46090</v>
+      </c>
+      <c r="M188" s="12"/>
       <c r="N188" s="4">
-        <v>46105</v>
+        <v>46085</v>
       </c>
       <c r="O188" s="4">
-        <v>46110</v>
+        <v>46086</v>
       </c>
       <c r="P188" s="4">
-        <v>46111</v>
+        <v>46087</v>
       </c>
       <c r="Q188" s="4">
-        <v>46112</v>
+        <v>46138</v>
       </c>
       <c r="R188" s="4">
-        <v>46115</v>
+        <v>46141</v>
       </c>
       <c r="S188" s="4">
-        <v>46118</v>
+        <v>46142</v>
       </c>
       <c r="T188" s="4">
-        <v>46118</v>
+        <v>46142</v>
       </c>
       <c r="V188" s="2" t="s">
-        <v>146</v>
+        <v>182</v>
       </c>
       <c r="W188" s="2" t="s">
         <v>29</v>
@@ -15051,36 +15106,36 @@
         <v>53</v>
       </c>
       <c r="Y188" s="2" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="189" spans="1:25" x14ac:dyDescent="0.3">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="189" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A189" s="2" t="s">
-        <v>245</v>
+        <v>62</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>246</v>
+        <v>63</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>247</v>
+        <v>64</v>
       </c>
       <c r="D189" s="2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E189" s="2" t="s">
-        <v>248</v>
+        <v>27</v>
       </c>
       <c r="F189" s="3">
-        <v>0.45</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="G189" s="7">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="H189" s="2" t="s">
-        <v>130</v>
+        <v>28</v>
       </c>
       <c r="I189" s="2" t="s">
-        <v>244</v>
+        <v>111</v>
       </c>
       <c r="J189" s="2">
         <v>1</v>
@@ -15088,32 +15143,27 @@
       <c r="K189" s="2">
         <v>1</v>
       </c>
-      <c r="L189" s="4">
-        <v>46104</v>
-      </c>
-      <c r="N189" s="4">
-        <v>46105</v>
-      </c>
-      <c r="O189" s="4">
-        <v>46110</v>
-      </c>
-      <c r="P189" s="4">
-        <v>46111</v>
-      </c>
-      <c r="Q189" s="4">
-        <v>46112</v>
+      <c r="L189" s="6"/>
+      <c r="M189" s="6"/>
+      <c r="N189" s="6"/>
+      <c r="O189" s="6"/>
+      <c r="P189" s="10">
+        <v>46066</v>
+      </c>
+      <c r="Q189" s="10">
+        <v>46071</v>
       </c>
       <c r="R189" s="4">
-        <v>46115</v>
+        <v>46077</v>
       </c>
       <c r="S189" s="4">
-        <v>46118</v>
+        <v>46077</v>
       </c>
       <c r="T189" s="4">
-        <v>46118</v>
+        <v>46077</v>
       </c>
       <c r="V189" s="2" t="s">
-        <v>146</v>
+        <v>98</v>
       </c>
       <c r="W189" s="2" t="s">
         <v>29</v>
@@ -15122,10 +15172,10 @@
         <v>53</v>
       </c>
       <c r="Y189" s="2" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="190" spans="1:25" x14ac:dyDescent="0.3">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="190" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A190" s="2" t="s">
         <v>62</v>
       </c>
@@ -15145,13 +15195,13 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G190" s="7">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="H190" s="2" t="s">
         <v>28</v>
       </c>
       <c r="I190" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J190" s="2">
         <v>1</v>
@@ -15179,7 +15229,7 @@
         <v>46077</v>
       </c>
       <c r="V190" s="2" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="W190" s="2" t="s">
         <v>29</v>
@@ -15187,34 +15237,37 @@
       <c r="X190" s="2" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="191" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Y190" s="2" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="191" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A191" s="2" t="s">
-        <v>148</v>
+        <v>62</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>298</v>
+        <v>63</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>149</v>
+        <v>64</v>
       </c>
       <c r="D191" s="2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E191" s="2" t="s">
-        <v>150</v>
+        <v>27</v>
       </c>
       <c r="F191" s="3">
-        <v>0.45</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="G191" s="7">
-        <v>14.2</v>
+        <v>14.5</v>
       </c>
       <c r="H191" s="2" t="s">
         <v>28</v>
       </c>
       <c r="I191" s="2" t="s">
-        <v>152</v>
+        <v>105</v>
       </c>
       <c r="J191" s="2">
         <v>1</v>
@@ -15222,33 +15275,27 @@
       <c r="K191" s="2">
         <v>1</v>
       </c>
-      <c r="L191" s="4">
-        <v>46090</v>
-      </c>
-      <c r="M191" s="12"/>
-      <c r="N191" s="4">
-        <v>46085</v>
-      </c>
-      <c r="O191" s="4">
-        <v>46086</v>
-      </c>
-      <c r="P191" s="4">
-        <v>46087</v>
-      </c>
-      <c r="Q191" s="4">
-        <v>46098</v>
+      <c r="L191" s="6"/>
+      <c r="M191" s="6"/>
+      <c r="N191" s="6"/>
+      <c r="O191" s="6"/>
+      <c r="P191" s="10">
+        <v>46065</v>
+      </c>
+      <c r="Q191" s="10">
+        <v>46075</v>
       </c>
       <c r="R191" s="4">
-        <v>46099</v>
+        <v>46076</v>
       </c>
       <c r="S191" s="4">
-        <v>46100</v>
+        <v>46077</v>
       </c>
       <c r="T191" s="4">
-        <v>46100</v>
+        <v>46077</v>
       </c>
       <c r="V191" s="2" t="s">
-        <v>182</v>
+        <v>76</v>
       </c>
       <c r="W191" s="2" t="s">
         <v>29</v>
@@ -15256,37 +15303,34 @@
       <c r="X191" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="Y191" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="192" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="192" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A192" s="2" t="s">
-        <v>148</v>
+        <v>62</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>298</v>
+        <v>63</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>149</v>
+        <v>64</v>
       </c>
       <c r="D192" s="2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E192" s="2" t="s">
-        <v>150</v>
+        <v>27</v>
       </c>
       <c r="F192" s="3">
-        <v>0.45</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="G192" s="7">
-        <v>14.2</v>
+        <v>14.5</v>
       </c>
       <c r="H192" s="2" t="s">
         <v>28</v>
       </c>
       <c r="I192" s="2" t="s">
-        <v>151</v>
+        <v>106</v>
       </c>
       <c r="J192" s="2">
         <v>1</v>
@@ -15294,33 +15338,27 @@
       <c r="K192" s="2">
         <v>1</v>
       </c>
-      <c r="L192" s="4">
-        <v>46090</v>
-      </c>
-      <c r="M192" s="12"/>
-      <c r="N192" s="4">
-        <v>46085</v>
-      </c>
-      <c r="O192" s="4">
-        <v>46086</v>
-      </c>
-      <c r="P192" s="4">
-        <v>46087</v>
-      </c>
-      <c r="Q192" s="4">
-        <v>46098</v>
+      <c r="L192" s="6"/>
+      <c r="M192" s="6"/>
+      <c r="N192" s="6"/>
+      <c r="O192" s="6"/>
+      <c r="P192" s="10">
+        <v>46065</v>
+      </c>
+      <c r="Q192" s="10">
+        <v>46075</v>
       </c>
       <c r="R192" s="4">
-        <v>46099</v>
+        <v>46076</v>
       </c>
       <c r="S192" s="4">
-        <v>46100</v>
+        <v>46077</v>
       </c>
       <c r="T192" s="4">
-        <v>46100</v>
+        <v>46077</v>
       </c>
       <c r="V192" s="2" t="s">
-        <v>182</v>
+        <v>76</v>
       </c>
       <c r="W192" s="2" t="s">
         <v>29</v>
@@ -15328,37 +15366,34 @@
       <c r="X192" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="Y192" s="2" t="s">
-        <v>58</v>
-      </c>
     </row>
     <row r="193" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A193" s="2" t="s">
-        <v>148</v>
+        <v>245</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>298</v>
+        <v>246</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>149</v>
+        <v>247</v>
       </c>
       <c r="D193" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E193" s="2" t="s">
-        <v>150</v>
+        <v>248</v>
       </c>
       <c r="F193" s="3">
         <v>0.45</v>
       </c>
       <c r="G193" s="7">
-        <v>14.2</v>
+        <v>14.5</v>
       </c>
       <c r="H193" s="2" t="s">
-        <v>28</v>
+        <v>130</v>
       </c>
       <c r="I193" s="2" t="s">
-        <v>153</v>
+        <v>243</v>
       </c>
       <c r="J193" s="2">
         <v>1</v>
@@ -15367,32 +15402,31 @@
         <v>1</v>
       </c>
       <c r="L193" s="4">
-        <v>46090</v>
-      </c>
-      <c r="M193" s="12"/>
+        <v>46104</v>
+      </c>
       <c r="N193" s="4">
-        <v>46085</v>
+        <v>46105</v>
       </c>
       <c r="O193" s="4">
-        <v>46086</v>
+        <v>46110</v>
       </c>
       <c r="P193" s="4">
-        <v>46087</v>
+        <v>46111</v>
       </c>
       <c r="Q193" s="4">
-        <v>46098</v>
+        <v>46112</v>
       </c>
       <c r="R193" s="4">
-        <v>46099</v>
+        <v>46115</v>
       </c>
       <c r="S193" s="4">
-        <v>46100</v>
+        <v>46118</v>
       </c>
       <c r="T193" s="4">
-        <v>46100</v>
+        <v>46118</v>
       </c>
       <c r="V193" s="2" t="s">
-        <v>182</v>
+        <v>146</v>
       </c>
       <c r="W193" s="2" t="s">
         <v>29</v>
@@ -15401,36 +15435,36 @@
         <v>53</v>
       </c>
       <c r="Y193" s="2" t="s">
-        <v>58</v>
+        <v>140</v>
       </c>
     </row>
     <row r="194" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A194" s="2" t="s">
-        <v>349</v>
+        <v>245</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>350</v>
+        <v>246</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>144</v>
+        <v>247</v>
       </c>
       <c r="D194" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E194" s="2" t="s">
-        <v>27</v>
+        <v>248</v>
       </c>
       <c r="F194" s="3">
-        <v>0.55000000000000004</v>
+        <v>0.45</v>
       </c>
       <c r="G194" s="7">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="H194" s="2" t="s">
-        <v>37</v>
+        <v>130</v>
       </c>
       <c r="I194" s="2" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="J194" s="2">
         <v>1</v>
@@ -15439,28 +15473,34 @@
         <v>1</v>
       </c>
       <c r="L194" s="4">
-        <v>46044</v>
+        <v>46104</v>
+      </c>
+      <c r="N194" s="4">
+        <v>46105</v>
+      </c>
+      <c r="O194" s="4">
+        <v>46110</v>
       </c>
       <c r="P194" s="4">
-        <v>46044</v>
+        <v>46111</v>
       </c>
       <c r="Q194" s="4">
-        <v>46044</v>
+        <v>46112</v>
       </c>
       <c r="R194" s="4">
-        <v>46045</v>
+        <v>46115</v>
       </c>
       <c r="S194" s="4">
-        <v>46045</v>
+        <v>46118</v>
       </c>
       <c r="T194" s="4">
-        <v>46045</v>
+        <v>46118</v>
       </c>
       <c r="V194" s="2" t="s">
         <v>146</v>
       </c>
       <c r="W194" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X194" s="2" t="s">
         <v>53</v>
@@ -15471,16 +15511,16 @@
     </row>
     <row r="195" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A195" s="2" t="s">
-        <v>349</v>
+        <v>62</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>350</v>
+        <v>63</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>144</v>
+        <v>64</v>
       </c>
       <c r="D195" s="2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E195" s="2" t="s">
         <v>27</v>
@@ -15492,10 +15532,10 @@
         <v>15</v>
       </c>
       <c r="H195" s="2" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="I195" s="2" t="s">
-        <v>348</v>
+        <v>109</v>
       </c>
       <c r="J195" s="2">
         <v>1</v>
@@ -15503,64 +15543,62 @@
       <c r="K195" s="2">
         <v>1</v>
       </c>
-      <c r="L195" s="4">
-        <v>46044</v>
-      </c>
-      <c r="P195" s="4">
-        <v>46044</v>
-      </c>
-      <c r="Q195" s="4">
-        <v>46044</v>
+      <c r="L195" s="6"/>
+      <c r="M195" s="6"/>
+      <c r="N195" s="6"/>
+      <c r="O195" s="6"/>
+      <c r="P195" s="10">
+        <v>46065</v>
+      </c>
+      <c r="Q195" s="10">
+        <v>46075</v>
       </c>
       <c r="R195" s="4">
-        <v>46045</v>
+        <v>46076</v>
       </c>
       <c r="S195" s="4">
-        <v>46045</v>
+        <v>46077</v>
       </c>
       <c r="T195" s="4">
-        <v>46045</v>
+        <v>46077</v>
       </c>
       <c r="V195" s="2" t="s">
-        <v>146</v>
+        <v>76</v>
       </c>
       <c r="W195" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X195" s="2" t="s">
         <v>53</v>
-      </c>
-      <c r="Y195" s="2" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="196" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A196" s="2" t="s">
-        <v>349</v>
+        <v>148</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>350</v>
+        <v>298</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>297</v>
+        <v>149</v>
       </c>
       <c r="D196" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="E196" s="2" t="s">
-        <v>27</v>
+        <v>150</v>
       </c>
       <c r="F196" s="3">
-        <v>0.55000000000000004</v>
+        <v>0.45</v>
       </c>
       <c r="G196" s="7">
-        <v>14.5</v>
+        <v>14.2</v>
       </c>
       <c r="H196" s="2" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="I196" s="2" t="s">
-        <v>356</v>
+        <v>152</v>
       </c>
       <c r="J196" s="2">
         <v>1</v>
@@ -15569,25 +15607,32 @@
         <v>1</v>
       </c>
       <c r="L196" s="4">
-        <v>46041</v>
+        <v>46090</v>
+      </c>
+      <c r="M196" s="12"/>
+      <c r="N196" s="4">
+        <v>46085</v>
+      </c>
+      <c r="O196" s="4">
+        <v>46086</v>
       </c>
       <c r="P196" s="4">
-        <v>46041</v>
+        <v>46087</v>
       </c>
       <c r="Q196" s="4">
-        <v>46043</v>
+        <v>46098</v>
       </c>
       <c r="R196" s="4">
-        <v>46044</v>
+        <v>46099</v>
       </c>
       <c r="S196" s="4">
-        <v>46045</v>
+        <v>46100</v>
       </c>
       <c r="T196" s="4">
-        <v>46045</v>
+        <v>46100</v>
       </c>
       <c r="V196" s="2" t="s">
-        <v>146</v>
+        <v>182</v>
       </c>
       <c r="W196" s="2" t="s">
         <v>29</v>
@@ -15596,36 +15641,36 @@
         <v>53</v>
       </c>
       <c r="Y196" s="2" t="s">
-        <v>140</v>
+        <v>58</v>
       </c>
     </row>
     <row r="197" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A197" s="2" t="s">
-        <v>349</v>
+        <v>148</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>350</v>
+        <v>298</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>297</v>
+        <v>149</v>
       </c>
       <c r="D197" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="E197" s="2" t="s">
-        <v>27</v>
+        <v>150</v>
       </c>
       <c r="F197" s="3">
-        <v>0.55000000000000004</v>
+        <v>0.45</v>
       </c>
       <c r="G197" s="7">
-        <v>15</v>
+        <v>14.2</v>
       </c>
       <c r="H197" s="2" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="I197" s="2" t="s">
-        <v>354</v>
+        <v>151</v>
       </c>
       <c r="J197" s="2">
         <v>1</v>
@@ -15634,25 +15679,32 @@
         <v>1</v>
       </c>
       <c r="L197" s="4">
-        <v>46041</v>
+        <v>46090</v>
+      </c>
+      <c r="M197" s="12"/>
+      <c r="N197" s="4">
+        <v>46085</v>
+      </c>
+      <c r="O197" s="4">
+        <v>46086</v>
       </c>
       <c r="P197" s="4">
-        <v>46041</v>
+        <v>46087</v>
       </c>
       <c r="Q197" s="4">
-        <v>46043</v>
+        <v>46098</v>
       </c>
       <c r="R197" s="4">
-        <v>46044</v>
+        <v>46099</v>
       </c>
       <c r="S197" s="4">
-        <v>46045</v>
+        <v>46100</v>
       </c>
       <c r="T197" s="4">
-        <v>46045</v>
+        <v>46100</v>
       </c>
       <c r="V197" s="2" t="s">
-        <v>146</v>
+        <v>182</v>
       </c>
       <c r="W197" s="2" t="s">
         <v>29</v>
@@ -15661,36 +15713,36 @@
         <v>53</v>
       </c>
       <c r="Y197" s="2" t="s">
-        <v>140</v>
+        <v>58</v>
       </c>
     </row>
     <row r="198" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A198" s="2" t="s">
-        <v>349</v>
+        <v>148</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>350</v>
+        <v>298</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>297</v>
+        <v>149</v>
       </c>
       <c r="D198" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="E198" s="2" t="s">
-        <v>27</v>
+        <v>150</v>
       </c>
       <c r="F198" s="3">
-        <v>0.55000000000000004</v>
+        <v>0.45</v>
       </c>
       <c r="G198" s="7">
-        <v>14.5</v>
+        <v>14.2</v>
       </c>
       <c r="H198" s="2" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="I198" s="2" t="s">
-        <v>355</v>
+        <v>153</v>
       </c>
       <c r="J198" s="2">
         <v>1</v>
@@ -15699,63 +15751,70 @@
         <v>1</v>
       </c>
       <c r="L198" s="4">
-        <v>46041</v>
+        <v>46090</v>
+      </c>
+      <c r="M198" s="12"/>
+      <c r="N198" s="4">
+        <v>46085</v>
+      </c>
+      <c r="O198" s="4">
+        <v>46086</v>
       </c>
       <c r="P198" s="4">
-        <v>46041</v>
+        <v>46087</v>
       </c>
       <c r="Q198" s="4">
-        <v>46043</v>
+        <v>46098</v>
       </c>
       <c r="R198" s="4">
-        <v>46044</v>
+        <v>46099</v>
       </c>
       <c r="S198" s="4">
-        <v>46045</v>
+        <v>46100</v>
       </c>
       <c r="T198" s="4">
-        <v>46045</v>
+        <v>46100</v>
       </c>
       <c r="V198" s="2" t="s">
-        <v>146</v>
+        <v>182</v>
       </c>
       <c r="W198" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X198" s="2" t="s">
         <v>53</v>
       </c>
       <c r="Y198" s="2" t="s">
-        <v>140</v>
+        <v>58</v>
       </c>
     </row>
     <row r="199" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A199" s="2" t="s">
-        <v>245</v>
+        <v>349</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>246</v>
+        <v>350</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>247</v>
+        <v>144</v>
       </c>
       <c r="D199" s="2" t="s">
-        <v>357</v>
+        <v>26</v>
       </c>
       <c r="E199" s="2" t="s">
-        <v>248</v>
+        <v>27</v>
       </c>
       <c r="F199" s="3">
         <v>0.55000000000000004</v>
       </c>
       <c r="G199" s="7">
-        <v>14.2</v>
+        <v>15</v>
       </c>
       <c r="H199" s="2" t="s">
-        <v>130</v>
+        <v>37</v>
       </c>
       <c r="I199" s="2" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="J199" s="2">
         <v>1</v>
@@ -15764,19 +15823,25 @@
         <v>1</v>
       </c>
       <c r="L199" s="4">
-        <v>46140</v>
+        <v>46044</v>
       </c>
       <c r="P199" s="4">
-        <v>46142</v>
+        <v>46044</v>
+      </c>
+      <c r="Q199" s="4">
+        <v>46044</v>
+      </c>
+      <c r="R199" s="4">
+        <v>46045</v>
       </c>
       <c r="S199" s="4">
-        <v>46157</v>
+        <v>46045</v>
       </c>
       <c r="T199" s="4">
-        <v>46157</v>
+        <v>46045</v>
       </c>
       <c r="V199" s="2" t="s">
-        <v>361</v>
+        <v>146</v>
       </c>
       <c r="W199" s="2" t="s">
         <v>30</v>
@@ -15785,36 +15850,36 @@
         <v>53</v>
       </c>
       <c r="Y199" s="2" t="s">
-        <v>58</v>
+        <v>140</v>
       </c>
     </row>
     <row r="200" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A200" s="2" t="s">
-        <v>245</v>
+        <v>349</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>246</v>
+        <v>350</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>247</v>
+        <v>144</v>
       </c>
       <c r="D200" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E200" s="2" t="s">
-        <v>248</v>
+        <v>27</v>
       </c>
       <c r="F200" s="3">
         <v>0.55000000000000004</v>
       </c>
       <c r="G200" s="7">
-        <v>14.2</v>
+        <v>15</v>
       </c>
       <c r="H200" s="2" t="s">
-        <v>130</v>
+        <v>37</v>
       </c>
       <c r="I200" s="2" t="s">
-        <v>359</v>
+        <v>348</v>
       </c>
       <c r="J200" s="2">
         <v>1</v>
@@ -15823,48 +15888,51 @@
         <v>1</v>
       </c>
       <c r="L200" s="4">
-        <v>46140</v>
+        <v>46044</v>
       </c>
       <c r="P200" s="4">
-        <v>46142</v>
+        <v>46044</v>
       </c>
       <c r="Q200" s="4">
-        <v>46149</v>
+        <v>46044</v>
+      </c>
+      <c r="R200" s="4">
+        <v>46045</v>
       </c>
       <c r="S200" s="4">
-        <v>46157</v>
+        <v>46045</v>
       </c>
       <c r="T200" s="4">
-        <v>46157</v>
+        <v>46045</v>
       </c>
       <c r="V200" s="2" t="s">
-        <v>361</v>
+        <v>146</v>
       </c>
       <c r="W200" s="2" t="s">
         <v>30</v>
       </c>
       <c r="X200" s="2" t="s">
-        <v>362</v>
+        <v>53</v>
       </c>
       <c r="Y200" s="2" t="s">
-        <v>58</v>
+        <v>140</v>
       </c>
     </row>
     <row r="201" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A201" s="2" t="s">
-        <v>245</v>
+        <v>349</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>246</v>
+        <v>350</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>247</v>
+        <v>297</v>
       </c>
       <c r="D201" s="2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E201" s="2" t="s">
-        <v>248</v>
+        <v>27</v>
       </c>
       <c r="F201" s="3">
         <v>0.55000000000000004</v>
@@ -15873,243 +15941,585 @@
         <v>14.5</v>
       </c>
       <c r="H201" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="I201" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="J201" s="2">
+        <v>1</v>
+      </c>
+      <c r="K201" s="2">
+        <v>1</v>
+      </c>
+      <c r="L201" s="4">
+        <v>46041</v>
+      </c>
+      <c r="P201" s="4">
+        <v>46041</v>
+      </c>
+      <c r="Q201" s="4">
+        <v>46043</v>
+      </c>
+      <c r="R201" s="4">
+        <v>46044</v>
+      </c>
+      <c r="S201" s="4">
+        <v>46045</v>
+      </c>
+      <c r="T201" s="4">
+        <v>46045</v>
+      </c>
+      <c r="V201" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="W201" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="X201" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y201" s="2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="202" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A202" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="B202" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="C202" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="D202" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E202" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F202" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G202" s="7">
+        <v>15</v>
+      </c>
+      <c r="H202" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="I202" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="J202" s="2">
+        <v>1</v>
+      </c>
+      <c r="K202" s="2">
+        <v>1</v>
+      </c>
+      <c r="L202" s="4">
+        <v>46041</v>
+      </c>
+      <c r="P202" s="4">
+        <v>46041</v>
+      </c>
+      <c r="Q202" s="4">
+        <v>46043</v>
+      </c>
+      <c r="R202" s="4">
+        <v>46044</v>
+      </c>
+      <c r="S202" s="4">
+        <v>46045</v>
+      </c>
+      <c r="T202" s="4">
+        <v>46045</v>
+      </c>
+      <c r="V202" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="W202" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="X202" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y202" s="2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="203" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A203" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="B203" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="C203" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="D203" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E203" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F203" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G203" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="H203" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="I203" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="J203" s="2">
+        <v>1</v>
+      </c>
+      <c r="K203" s="2">
+        <v>1</v>
+      </c>
+      <c r="L203" s="4">
+        <v>46041</v>
+      </c>
+      <c r="P203" s="4">
+        <v>46041</v>
+      </c>
+      <c r="Q203" s="4">
+        <v>46043</v>
+      </c>
+      <c r="R203" s="4">
+        <v>46044</v>
+      </c>
+      <c r="S203" s="4">
+        <v>46045</v>
+      </c>
+      <c r="T203" s="4">
+        <v>46045</v>
+      </c>
+      <c r="V203" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="W203" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X203" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y203" s="2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="204" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A204" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="B204" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="C204" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="D204" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="E204" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="F204" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G204" s="7">
+        <v>14.2</v>
+      </c>
+      <c r="H204" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="I201" s="2" t="s">
+      <c r="I204" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="J204" s="2">
+        <v>1</v>
+      </c>
+      <c r="K204" s="2">
+        <v>1</v>
+      </c>
+      <c r="L204" s="4">
+        <v>46140</v>
+      </c>
+      <c r="P204" s="4">
+        <v>46142</v>
+      </c>
+      <c r="S204" s="4">
+        <v>46157</v>
+      </c>
+      <c r="T204" s="4">
+        <v>46157</v>
+      </c>
+      <c r="V204" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="W204" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X204" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y204" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="205" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A205" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="B205" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="C205" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="D205" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E205" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="F205" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G205" s="7">
+        <v>14.2</v>
+      </c>
+      <c r="H205" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="I205" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="J205" s="2">
+        <v>1</v>
+      </c>
+      <c r="K205" s="2">
+        <v>1</v>
+      </c>
+      <c r="L205" s="4">
+        <v>46140</v>
+      </c>
+      <c r="P205" s="4">
+        <v>46142</v>
+      </c>
+      <c r="Q205" s="4">
+        <v>46149</v>
+      </c>
+      <c r="R205" s="4">
+        <v>46150</v>
+      </c>
+      <c r="S205" s="4">
+        <v>46157</v>
+      </c>
+      <c r="T205" s="4">
+        <v>46157</v>
+      </c>
+      <c r="V205" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="W205" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X205" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="Y205" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="206" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A206" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="B206" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="C206" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="D206" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E206" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="F206" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G206" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="H206" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="I206" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="J201" s="2">
-        <v>1</v>
-      </c>
-      <c r="K201" s="2">
-        <v>1</v>
-      </c>
-      <c r="L201" s="4">
+      <c r="J206" s="2">
+        <v>1</v>
+      </c>
+      <c r="K206" s="2">
+        <v>1</v>
+      </c>
+      <c r="L206" s="4">
         <v>46140</v>
       </c>
-      <c r="P201" s="4">
+      <c r="P206" s="4">
         <v>46142</v>
       </c>
-      <c r="S201" s="4">
+      <c r="Q206" s="4">
+        <v>46150</v>
+      </c>
+      <c r="S206" s="4">
         <v>46157</v>
       </c>
-      <c r="T201" s="4">
+      <c r="T206" s="4">
         <v>46157</v>
       </c>
-      <c r="V201" s="2" t="s">
+      <c r="V206" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="W201" s="2" t="s">
+      <c r="W206" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="X201" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="Y201" s="2" t="s">
+      <c r="X206" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y206" s="2" t="s">
         <v>58</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AB195"/>
+  <autoFilter ref="A1:AB206"/>
   <phoneticPr fontId="2" type="noConversion"/>
+  <conditionalFormatting sqref="I110">
+    <cfRule type="expression" dxfId="44" priority="105" stopIfTrue="1">
+      <formula>$E15:$E3171="sub"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I109">
+    <cfRule type="expression" dxfId="43" priority="111" stopIfTrue="1">
+      <formula>$E15:$E3171="sub"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I108">
+    <cfRule type="expression" dxfId="42" priority="117" stopIfTrue="1">
+      <formula>$E15:$E3171="sub"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I107">
+    <cfRule type="expression" dxfId="41" priority="123" stopIfTrue="1">
+      <formula>$E15:$E3171="sub"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="I106">
-    <cfRule type="expression" dxfId="39" priority="104" stopIfTrue="1">
-      <formula>$E15:$E3166="sub"</formula>
+    <cfRule type="expression" dxfId="40" priority="129" stopIfTrue="1">
+      <formula>$E15:$E3171="sub"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I105">
-    <cfRule type="expression" dxfId="38" priority="110" stopIfTrue="1">
-      <formula>$E15:$E3166="sub"</formula>
+    <cfRule type="expression" dxfId="39" priority="135" stopIfTrue="1">
+      <formula>$E15:$E3171="sub"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I122">
+    <cfRule type="expression" dxfId="38" priority="159" stopIfTrue="1">
+      <formula>$E16:$E3172="sub"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I121">
+    <cfRule type="expression" dxfId="37" priority="166" stopIfTrue="1">
+      <formula>$E16:$E3172="sub"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I120">
+    <cfRule type="expression" dxfId="36" priority="173" stopIfTrue="1">
+      <formula>$E16:$E3172="sub"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I119">
+    <cfRule type="expression" dxfId="35" priority="180" stopIfTrue="1">
+      <formula>$E16:$E3172="sub"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I118">
+    <cfRule type="expression" dxfId="34" priority="187" stopIfTrue="1">
+      <formula>$E16:$E3172="sub"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I96">
+    <cfRule type="expression" dxfId="33" priority="10" stopIfTrue="1">
+      <formula>$E13:$E3171="sub"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I104">
-    <cfRule type="expression" dxfId="37" priority="116" stopIfTrue="1">
-      <formula>$E15:$E3166="sub"</formula>
+    <cfRule type="expression" dxfId="32" priority="291" stopIfTrue="1">
+      <formula>$E15:$E3171="sub"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I103">
-    <cfRule type="expression" dxfId="36" priority="122" stopIfTrue="1">
-      <formula>$E15:$E3166="sub"</formula>
+  <conditionalFormatting sqref="I95">
+    <cfRule type="expression" dxfId="31" priority="456" stopIfTrue="1">
+      <formula>$E13:$E3168="sub"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I102">
-    <cfRule type="expression" dxfId="35" priority="128" stopIfTrue="1">
-      <formula>$E15:$E3166="sub"</formula>
+  <conditionalFormatting sqref="I97 I99">
+    <cfRule type="expression" dxfId="30" priority="460" stopIfTrue="1">
+      <formula>$E13:$E3169="sub"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I100 I102:I103">
+    <cfRule type="expression" dxfId="29" priority="462" stopIfTrue="1">
+      <formula>$E13:$E3169="sub"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I126">
+    <cfRule type="expression" dxfId="28" priority="467" stopIfTrue="1">
+      <formula>$E17:$E3174="sub"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I115">
+    <cfRule type="expression" dxfId="27" priority="6" stopIfTrue="1">
+      <formula>$E22:$E3175="sub"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I114">
+    <cfRule type="expression" dxfId="26" priority="7" stopIfTrue="1">
+      <formula>$E22:$E3175="sub"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I112">
+    <cfRule type="expression" dxfId="25" priority="8" stopIfTrue="1">
+      <formula>$E22:$E3175="sub"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I111">
+    <cfRule type="expression" dxfId="24" priority="9" stopIfTrue="1">
+      <formula>$E22:$E3175="sub"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I82">
+    <cfRule type="expression" dxfId="23" priority="509" stopIfTrue="1">
+      <formula>$E12:$E3141="sub"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I189">
+    <cfRule type="expression" dxfId="22" priority="548" stopIfTrue="1">
+      <formula>$E91:$E3234="sub"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I188">
+    <cfRule type="expression" dxfId="21" priority="550" stopIfTrue="1">
+      <formula>$E92:$E3235="sub"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I125">
+    <cfRule type="expression" dxfId="20" priority="571" stopIfTrue="1">
+      <formula>$E20:$E3174="sub"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I74">
+    <cfRule type="expression" dxfId="19" priority="671" stopIfTrue="1">
+      <formula>$E6:$E3140="sub"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I84">
+    <cfRule type="expression" dxfId="18" priority="678" stopIfTrue="1">
+      <formula>$E2:$E3162="sub"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I5">
+    <cfRule type="expression" dxfId="17" priority="2" stopIfTrue="1">
+      <formula>$E3074:$E1048499="sub"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I98">
+    <cfRule type="expression" dxfId="16" priority="688" stopIfTrue="1">
+      <formula>$E13:$E3170="sub"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I101">
-    <cfRule type="expression" dxfId="34" priority="134" stopIfTrue="1">
-      <formula>$E15:$E3166="sub"</formula>
+    <cfRule type="expression" dxfId="15" priority="690" stopIfTrue="1">
+      <formula>$E13:$E3170="sub"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I117">
-    <cfRule type="expression" dxfId="33" priority="158" stopIfTrue="1">
-      <formula>$E16:$E3167="sub"</formula>
+  <conditionalFormatting sqref="I93:I94">
+    <cfRule type="expression" dxfId="14" priority="813" stopIfTrue="1">
+      <formula>$E12:$E3168="sub"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I116">
-    <cfRule type="expression" dxfId="32" priority="165" stopIfTrue="1">
-      <formula>$E16:$E3167="sub"</formula>
+  <conditionalFormatting sqref="I190:I191">
+    <cfRule type="expression" dxfId="13" priority="826" stopIfTrue="1">
+      <formula>$E91:$E3234="sub"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I115">
-    <cfRule type="expression" dxfId="31" priority="172" stopIfTrue="1">
-      <formula>$E16:$E3167="sub"</formula>
+  <conditionalFormatting sqref="I186:I187">
+    <cfRule type="expression" dxfId="12" priority="827" stopIfTrue="1">
+      <formula>$E91:$E3234="sub"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I114">
-    <cfRule type="expression" dxfId="30" priority="179" stopIfTrue="1">
-      <formula>$E16:$E3167="sub"</formula>
+  <conditionalFormatting sqref="I89:I90">
+    <cfRule type="expression" dxfId="11" priority="828" stopIfTrue="1">
+      <formula>$E8:$E3165="sub"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I184:I185">
+    <cfRule type="expression" dxfId="10" priority="830" stopIfTrue="1">
+      <formula>$E85:$E3232="sub"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I123:I124">
+    <cfRule type="expression" dxfId="9" priority="831" stopIfTrue="1">
+      <formula>$E16:$E3172="sub"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I116:I117">
+    <cfRule type="expression" dxfId="8" priority="832" stopIfTrue="1">
+      <formula>$E15:$E3171="sub"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I77:I81">
+    <cfRule type="expression" dxfId="7" priority="833" stopIfTrue="1">
+      <formula>$E6:$E3136="sub"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I85:I88">
+    <cfRule type="expression" dxfId="6" priority="834" stopIfTrue="1">
+      <formula>$E6:$E3163="sub"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I91:I92">
+    <cfRule type="expression" dxfId="5" priority="835" stopIfTrue="1">
+      <formula>$E8:$E3165="sub"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I75:I76">
+    <cfRule type="expression" dxfId="4" priority="836" stopIfTrue="1">
+      <formula>$E1:$E3134="sub"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I72:I73">
+    <cfRule type="expression" dxfId="3" priority="837" stopIfTrue="1">
+      <formula>$E1:$E3138="sub"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I83">
+    <cfRule type="expression" dxfId="2" priority="838" stopIfTrue="1">
+      <formula>$E3160:$E1048576="sub"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I113">
-    <cfRule type="expression" dxfId="29" priority="186" stopIfTrue="1">
-      <formula>$E16:$E3167="sub"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I92">
-    <cfRule type="expression" dxfId="28" priority="9" stopIfTrue="1">
-      <formula>$E13:$E3166="sub"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I100">
-    <cfRule type="expression" dxfId="27" priority="290" stopIfTrue="1">
-      <formula>$E15:$E3166="sub"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I91">
-    <cfRule type="expression" dxfId="26" priority="455" stopIfTrue="1">
-      <formula>$E13:$E3163="sub"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I93 I95">
-    <cfRule type="expression" dxfId="25" priority="459" stopIfTrue="1">
-      <formula>$E13:$E3164="sub"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I96 I98:I99">
-    <cfRule type="expression" dxfId="24" priority="461" stopIfTrue="1">
-      <formula>$E13:$E3164="sub"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I121">
-    <cfRule type="expression" dxfId="23" priority="466" stopIfTrue="1">
-      <formula>$E17:$E3169="sub"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I110">
-    <cfRule type="expression" dxfId="22" priority="5" stopIfTrue="1">
-      <formula>$E22:$E3170="sub"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I109">
-    <cfRule type="expression" dxfId="21" priority="6" stopIfTrue="1">
-      <formula>$E22:$E3170="sub"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I108">
-    <cfRule type="expression" dxfId="20" priority="7" stopIfTrue="1">
-      <formula>$E22:$E3170="sub"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I107">
-    <cfRule type="expression" dxfId="19" priority="8" stopIfTrue="1">
-      <formula>$E22:$E3170="sub"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I82">
-    <cfRule type="expression" dxfId="18" priority="508" stopIfTrue="1">
-      <formula>$E12:$E3136="sub"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I184">
-    <cfRule type="expression" dxfId="17" priority="547" stopIfTrue="1">
-      <formula>$E87:$E3229="sub"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I183">
-    <cfRule type="expression" dxfId="16" priority="549" stopIfTrue="1">
-      <formula>$E88:$E3230="sub"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I120">
-    <cfRule type="expression" dxfId="15" priority="570" stopIfTrue="1">
-      <formula>$E20:$E3169="sub"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I74">
-    <cfRule type="expression" dxfId="14" priority="670" stopIfTrue="1">
-      <formula>$E6:$E3135="sub"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I84">
-    <cfRule type="expression" dxfId="13" priority="677" stopIfTrue="1">
-      <formula>$E2:$E3157="sub"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I5">
-    <cfRule type="expression" dxfId="12" priority="1" stopIfTrue="1">
-      <formula>$E3069:$E1048494="sub"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I94">
-    <cfRule type="expression" dxfId="11" priority="687" stopIfTrue="1">
-      <formula>$E13:$E3165="sub"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I97">
-    <cfRule type="expression" dxfId="10" priority="689" stopIfTrue="1">
-      <formula>$E13:$E3165="sub"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I185:I186">
-    <cfRule type="expression" dxfId="9" priority="710" stopIfTrue="1">
-      <formula>$E87:$E3229="sub"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I179:I182">
-    <cfRule type="expression" dxfId="8" priority="711" stopIfTrue="1">
-      <formula>$E85:$E3227="sub"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I118:I119">
-    <cfRule type="expression" dxfId="7" priority="712" stopIfTrue="1">
-      <formula>$E16:$E3167="sub"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I111:I112">
-    <cfRule type="expression" dxfId="6" priority="713" stopIfTrue="1">
-      <formula>$E15:$E3166="sub"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I89:I90">
-    <cfRule type="expression" dxfId="5" priority="714" stopIfTrue="1">
-      <formula>$E12:$E3163="sub"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I77:I81">
-    <cfRule type="expression" dxfId="4" priority="715" stopIfTrue="1">
-      <formula>$E6:$E3131="sub"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I85:I88">
-    <cfRule type="expression" dxfId="3" priority="716" stopIfTrue="1">
-      <formula>$E6:$E3158="sub"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I75:I76">
-    <cfRule type="expression" dxfId="2" priority="717" stopIfTrue="1">
-      <formula>$E1:$E3129="sub"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I72:I73">
-    <cfRule type="expression" dxfId="1" priority="718" stopIfTrue="1">
-      <formula>$E1:$E3133="sub"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I83">
-    <cfRule type="expression" dxfId="0" priority="719" stopIfTrue="1">
-      <formula>$E3155:$E1048576="sub"</formula>
+    <cfRule type="expression" dxfId="0" priority="1" stopIfTrue="1">
+      <formula>$E23:$E3176="sub"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -16121,37 +16531,37 @@
           <x14:formula1>
             <xm:f>Sheet2!$F$2:$F$4</xm:f>
           </x14:formula1>
-          <xm:sqref>Y56:Y57 W172:W1048576 W162:W167 W2:W54 W56:W160</xm:sqref>
+          <xm:sqref>Y56:Y57 W177:W1048576 W167:W172 W2:W54 W56:W165</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>Sheet2!$E$2:$E$4</xm:f>
           </x14:formula1>
-          <xm:sqref>H2:H54 H162:H167 H194:H1048576 H176:H192 H56:H160</xm:sqref>
+          <xm:sqref>H2:H54 H167:H172 H199:H1048576 H181:H197 H56:H165</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>Sheet2!$D$2:$D$5</xm:f>
           </x14:formula1>
-          <xm:sqref>G2:G54 G162:G167 G172:G1048576 G56:G160</xm:sqref>
+          <xm:sqref>G2:G54 G167:G172 G177:G1048576 G56:G165</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>Sheet2!$C$2:$C$5</xm:f>
           </x14:formula1>
-          <xm:sqref>F2:F54 F162:F167 F172:F1048576 F56:F160</xm:sqref>
+          <xm:sqref>F2:F54 F167:F172 F177:F1048576 F56:F165</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>Sheet2!$B$2:$B$3</xm:f>
           </x14:formula1>
-          <xm:sqref>E2:E54 E162:E167 E194:E1048576 E176:E192 E56:E160</xm:sqref>
+          <xm:sqref>E2:E54 E167:E172 E199:E1048576 E181:E197 E56:E165</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>Sheet2!$A$2:$A$4</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D54 D162:D167 D172:D1048576 D56:D160</xm:sqref>
+          <xm:sqref>D2:D54 D167:D172 D177:D1048576 D56:D165</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
@@ -16163,13 +16573,13 @@
           <x14:formula1>
             <xm:f>Sheet2!$H$2:$H$7</xm:f>
           </x14:formula1>
-          <xm:sqref>Y58:Y100 Y162:Y167 Y2:Y55 Y176:Y1048576 Y102:Y160</xm:sqref>
+          <xm:sqref>Y58:Y104 Y167:Y172 Y2:Y55 Y181:Y1048576 Y106:Y165</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'[sample-list_1.xlsx]Sheet2'!#REF!</xm:f>
           </x14:formula1>
-          <xm:sqref>Y168:Y175 W168:W171 H172:H175 D161:H161 D168:H171 E172:E175 Y161 W161 E193 H193</xm:sqref>
+          <xm:sqref>Y173:Y180 W173:W176 H177:H180 D166:H166 D173:H176 E177:E180 Y166 W166 E198 H198</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>

--- a/sample-list.xlsx
+++ b/sample-list.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.14.76\Lens Design\11. 문서\생산납기\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\서동훈\Desktop\업무\32.샘플진도현황\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -2367,7 +2367,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:AB209"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -2476,7 +2475,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>282</v>
       </c>
@@ -4140,7 +4139,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="27" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>42</v>
       </c>
@@ -4214,7 +4213,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="28" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>255</v>
       </c>
@@ -4438,7 +4437,7 @@
         <v>46078</v>
       </c>
     </row>
-    <row r="31" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>68</v>
       </c>
@@ -4512,7 +4511,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="32" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>167</v>
       </c>
@@ -4571,7 +4570,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="33" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>167</v>
       </c>
@@ -4627,7 +4626,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="34" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>222</v>
       </c>
@@ -4701,7 +4700,7 @@
         <v>46112</v>
       </c>
     </row>
-    <row r="35" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>222</v>
       </c>
@@ -4775,7 +4774,7 @@
         <v>46112</v>
       </c>
     </row>
-    <row r="36" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>68</v>
       </c>
@@ -4849,7 +4848,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="37" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>68</v>
       </c>
@@ -4923,7 +4922,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="38" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>283</v>
       </c>
@@ -4990,7 +4989,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="39" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
         <v>61</v>
       </c>
@@ -5046,7 +5045,7 @@
         <v>29</v>
       </c>
       <c r="X39" s="2" t="s">
-        <v>98</v>
+        <v>52</v>
       </c>
       <c r="Y39" s="2" t="s">
         <v>57</v>
@@ -5200,7 +5199,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="42" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>141</v>
       </c>
@@ -5267,7 +5266,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="43" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>61</v>
       </c>
@@ -5335,7 +5334,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="44" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
         <v>183</v>
       </c>
@@ -5394,7 +5393,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="45" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>183</v>
       </c>
@@ -5453,7 +5452,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="46" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>183</v>
       </c>
@@ -5512,7 +5511,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="47" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>183</v>
       </c>
@@ -5571,7 +5570,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="48" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
         <v>183</v>
       </c>
@@ -5716,7 +5715,7 @@
         <v>46141</v>
       </c>
     </row>
-    <row r="50" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
         <v>310</v>
       </c>
@@ -5855,7 +5854,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="52" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
         <v>147</v>
       </c>
@@ -5924,7 +5923,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="53" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
         <v>147</v>
       </c>
@@ -5986,7 +5985,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="54" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
         <v>147</v>
       </c>
@@ -6055,7 +6054,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="55" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
         <v>147</v>
       </c>
@@ -6117,7 +6116,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="56" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
         <v>271</v>
       </c>
@@ -6177,7 +6176,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="57" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
         <v>271</v>
       </c>
@@ -6237,7 +6236,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="58" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
         <v>61</v>
       </c>
@@ -6308,7 +6307,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="59" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
         <v>310</v>
       </c>
@@ -6373,7 +6372,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="60" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
         <v>113</v>
       </c>
@@ -6444,7 +6443,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="61" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
         <v>222</v>
       </c>
@@ -6894,7 +6893,7 @@
         <v>46141</v>
       </c>
     </row>
-    <row r="67" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
         <v>222</v>
       </c>
@@ -6968,7 +6967,7 @@
         <v>46112</v>
       </c>
     </row>
-    <row r="68" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
         <v>222</v>
       </c>
@@ -7042,7 +7041,7 @@
         <v>46112</v>
       </c>
     </row>
-    <row r="69" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
         <v>222</v>
       </c>
@@ -7116,7 +7115,7 @@
         <v>46112</v>
       </c>
     </row>
-    <row r="70" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
         <v>42</v>
       </c>
@@ -7193,7 +7192,7 @@
         <v>46041</v>
       </c>
     </row>
-    <row r="71" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
         <v>42</v>
       </c>
@@ -7270,7 +7269,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="72" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
         <v>42</v>
       </c>
@@ -7347,7 +7346,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="73" spans="1:28" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
         <v>42</v>
       </c>
@@ -7424,7 +7423,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="74" spans="1:28" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
         <v>147</v>
       </c>
@@ -7493,7 +7492,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="75" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
         <v>147</v>
       </c>
@@ -7562,7 +7561,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="76" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
         <v>147</v>
       </c>
@@ -7624,7 +7623,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="77" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
         <v>167</v>
       </c>
@@ -7683,7 +7682,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="78" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
         <v>183</v>
       </c>
@@ -7755,7 +7754,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="79" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
         <v>183</v>
       </c>
@@ -7832,7 +7831,7 @@
         <v>46141</v>
       </c>
     </row>
-    <row r="80" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
         <v>183</v>
       </c>
@@ -7904,7 +7903,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="81" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
         <v>183</v>
       </c>
@@ -7981,7 +7980,7 @@
         <v>46141</v>
       </c>
     </row>
-    <row r="82" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
         <v>183</v>
       </c>
@@ -8053,7 +8052,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="83" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
         <v>183</v>
       </c>
@@ -8130,7 +8129,7 @@
         <v>46141</v>
       </c>
     </row>
-    <row r="84" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
         <v>183</v>
       </c>
@@ -8204,7 +8203,7 @@
         <v>46141</v>
       </c>
     </row>
-    <row r="85" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
         <v>183</v>
       </c>
@@ -8278,7 +8277,7 @@
         <v>46141</v>
       </c>
     </row>
-    <row r="86" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
         <v>183</v>
       </c>
@@ -8352,7 +8351,7 @@
         <v>46141</v>
       </c>
     </row>
-    <row r="87" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
         <v>147</v>
       </c>
@@ -8973,7 +8972,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="96" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
         <v>284</v>
       </c>
@@ -9040,7 +9039,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="97" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
         <v>285</v>
       </c>
@@ -9330,7 +9329,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="101" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="s">
         <v>310</v>
       </c>
@@ -9395,7 +9394,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="102" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
         <v>113</v>
       </c>
@@ -9466,7 +9465,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="103" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A103" s="2" t="s">
         <v>113</v>
       </c>
@@ -10029,7 +10028,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="111" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A111" s="2" t="s">
         <v>42</v>
       </c>
@@ -10103,7 +10102,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="112" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
         <v>42</v>
       </c>
@@ -10177,7 +10176,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="113" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A113" s="2" t="s">
         <v>255</v>
       </c>
@@ -10248,7 +10247,7 @@
         <v>46107</v>
       </c>
     </row>
-    <row r="114" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
         <v>255</v>
       </c>
@@ -10280,7 +10279,7 @@
         <v>1</v>
       </c>
       <c r="K114" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L114" s="4">
         <v>46143</v>
@@ -10304,13 +10303,13 @@
         <v>29</v>
       </c>
       <c r="X114" s="2" t="s">
-        <v>98</v>
+        <v>52</v>
       </c>
       <c r="Y114" s="2" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="115" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A115" s="2" t="s">
         <v>147</v>
       </c>
@@ -10381,7 +10380,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="116" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A116" s="2" t="s">
         <v>147</v>
       </c>
@@ -10437,7 +10436,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="117" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A117" s="2" t="s">
         <v>310</v>
       </c>
@@ -10502,7 +10501,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="118" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A118" s="2" t="s">
         <v>113</v>
       </c>
@@ -10576,7 +10575,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="119" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A119" s="2" t="s">
         <v>113</v>
       </c>
@@ -10700,7 +10699,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="121" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A121" s="2" t="s">
         <v>42</v>
       </c>
@@ -10774,7 +10773,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="122" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
         <v>252</v>
       </c>
@@ -10913,7 +10912,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="124" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A124" s="2" t="s">
         <v>61</v>
       </c>
@@ -11183,7 +11182,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="128" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A128" s="2" t="s">
         <v>183</v>
       </c>
@@ -11438,7 +11437,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="132" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A132" s="2" t="s">
         <v>167</v>
       </c>
@@ -11497,7 +11496,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="133" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A133" s="2" t="s">
         <v>167</v>
       </c>
@@ -11553,7 +11552,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="134" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A134" s="2" t="s">
         <v>167</v>
       </c>
@@ -11609,7 +11608,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="135" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A135" s="2" t="s">
         <v>167</v>
       </c>
@@ -11665,7 +11664,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="136" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A136" s="2" t="s">
         <v>167</v>
       </c>
@@ -11721,7 +11720,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="137" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A137" s="2" t="s">
         <v>167</v>
       </c>
@@ -11777,7 +11776,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="138" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A138" s="2" t="s">
         <v>167</v>
       </c>
@@ -11833,7 +11832,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="139" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A139" s="2" t="s">
         <v>167</v>
       </c>
@@ -11889,7 +11888,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="140" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A140" s="2" t="s">
         <v>167</v>
       </c>
@@ -12081,7 +12080,7 @@
         <v>45982</v>
       </c>
     </row>
-    <row r="143" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A143" s="2" t="s">
         <v>141</v>
       </c>
@@ -12943,7 +12942,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="156" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A156" s="2" t="s">
         <v>183</v>
       </c>
@@ -13002,7 +13001,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="157" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A157" s="2" t="s">
         <v>183</v>
       </c>
@@ -13061,7 +13060,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="158" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A158" s="2" t="s">
         <v>183</v>
       </c>
@@ -13120,7 +13119,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="159" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A159" s="2" t="s">
         <v>61</v>
       </c>
@@ -13188,7 +13187,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="160" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A160" s="2" t="s">
         <v>61</v>
       </c>
@@ -13266,7 +13265,7 @@
       </c>
       <c r="AB160" s="4"/>
     </row>
-    <row r="161" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A161" s="2" t="s">
         <v>61</v>
       </c>
@@ -13340,7 +13339,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="162" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A162" s="2" t="s">
         <v>61</v>
       </c>
@@ -13414,7 +13413,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="163" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A163" s="2" t="s">
         <v>61</v>
       </c>
@@ -13488,7 +13487,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="164" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A164" s="2" t="s">
         <v>61</v>
       </c>
@@ -13562,7 +13561,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="165" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A165" s="2" t="s">
         <v>61</v>
       </c>
@@ -13633,7 +13632,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="166" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A166" s="2" t="s">
         <v>61</v>
       </c>
@@ -13704,7 +13703,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="167" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A167" s="2" t="s">
         <v>123</v>
       </c>
@@ -14839,7 +14838,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="184" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A184" s="2" t="s">
         <v>61</v>
       </c>
@@ -14895,7 +14894,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="185" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A185" s="2" t="s">
         <v>147</v>
       </c>
@@ -14967,7 +14966,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="186" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A186" s="2" t="s">
         <v>147</v>
       </c>
@@ -15039,7 +15038,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="187" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A187" s="2" t="s">
         <v>147</v>
       </c>
@@ -15111,7 +15110,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="188" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A188" s="2" t="s">
         <v>147</v>
       </c>
@@ -15183,7 +15182,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="189" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A189" s="2" t="s">
         <v>147</v>
       </c>
@@ -15255,7 +15254,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="190" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A190" s="2" t="s">
         <v>147</v>
       </c>
@@ -15327,7 +15326,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="191" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A191" s="2" t="s">
         <v>147</v>
       </c>
@@ -15399,7 +15398,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="192" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A192" s="2" t="s">
         <v>61</v>
       </c>
@@ -15465,7 +15464,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="193" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A193" s="2" t="s">
         <v>61</v>
       </c>
@@ -15531,7 +15530,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="194" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A194" s="2" t="s">
         <v>61</v>
       </c>
@@ -15594,7 +15593,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="195" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A195" s="2" t="s">
         <v>61</v>
       </c>
@@ -15799,7 +15798,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="198" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A198" s="2" t="s">
         <v>61</v>
       </c>
@@ -15862,7 +15861,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="199" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A199" s="2" t="s">
         <v>147</v>
       </c>
@@ -15934,7 +15933,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="200" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A200" s="2" t="s">
         <v>147</v>
       </c>
@@ -16009,7 +16008,7 @@
         <v>46028</v>
       </c>
     </row>
-    <row r="201" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A201" s="2" t="s">
         <v>147</v>
       </c>
@@ -16406,7 +16405,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="207" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A207" s="2" t="s">
         <v>244</v>
       </c>
@@ -16471,7 +16470,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="208" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A208" s="2" t="s">
         <v>244</v>
       </c>
@@ -16536,7 +16535,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="209" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A209" s="2" t="s">
         <v>244</v>
       </c>
@@ -16602,13 +16601,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AB209">
-    <filterColumn colId="21">
-      <filters>
-        <filter val="정세희"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:AB209"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="I113">
     <cfRule type="expression" dxfId="43" priority="105" stopIfTrue="1">
